--- a/data/default/MachineryAndEnergyMgmt.xlsx
+++ b/data/default/MachineryAndEnergyMgmt.xlsx
@@ -477,7 +477,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="946" uniqueCount="335">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="949" uniqueCount="336">
   <si>
     <t>f_crop</t>
   </si>
@@ -979,9 +979,6 @@
     <t>Transport kärna</t>
   </si>
   <si>
-    <t>Transport halm</t>
-  </si>
-  <si>
     <t>Transport vagn allmän</t>
   </si>
   <si>
@@ -1660,6 +1657,12 @@
   </si>
   <si>
     <t>Natural gas</t>
+  </si>
+  <si>
+    <t>kWh/ton DM</t>
+  </si>
+  <si>
+    <t>Adjusted to dry matter. Transport halm</t>
   </si>
 </sst>
 </file>
@@ -2461,25 +2464,25 @@
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B1" s="14" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D1" s="14" t="s">
+        <v>202</v>
+      </c>
+      <c r="E1" s="14" t="s">
         <v>203</v>
       </c>
-      <c r="E1" s="14" t="s">
-        <v>204</v>
-      </c>
       <c r="F1" s="14" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G1" s="14" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H1" s="14" t="s">
         <v>52</v>
@@ -2491,7 +2494,7 @@
         <v>129</v>
       </c>
       <c r="K1" s="14" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="L1" s="14" t="s">
         <v>1</v>
@@ -2511,7 +2514,7 @@
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="L2" s="20" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="M2" s="9">
         <v>0</v>
@@ -2525,13 +2528,13 @@
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="L4" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="M4" s="18">
         <f>(241822577+237201100)/(241822577+237201100+5856000+8368914)*100</f>
@@ -2541,18 +2544,18 @@
         <v>128</v>
       </c>
       <c r="P4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="M5" s="18">
         <f>100-M4</f>
@@ -2562,18 +2565,18 @@
         <v>128</v>
       </c>
       <c r="P5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="M6" s="10">
         <v>0</v>
@@ -2584,13 +2587,13 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="L7" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="M7" s="10">
         <v>0</v>
@@ -2606,16 +2609,16 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="L9" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="M9" s="10">
         <v>100</v>
@@ -2626,10 +2629,10 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C10" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G10" s="4"/>
       <c r="L10" s="6"/>
@@ -2637,16 +2640,16 @@
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C11" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="L11" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="M11" s="10">
         <v>100</v>
@@ -2657,16 +2660,16 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C12" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="M12" s="10">
         <v>100</v>
@@ -2682,19 +2685,19 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C14" t="s">
+        <v>235</v>
+      </c>
+      <c r="D14" t="s">
         <v>236</v>
       </c>
-      <c r="D14" t="s">
-        <v>237</v>
-      </c>
       <c r="G14" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="L14" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="M14" s="10">
         <v>100</v>
@@ -2705,19 +2708,19 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C15" t="s">
+        <v>235</v>
+      </c>
+      <c r="D15" t="s">
         <v>236</v>
       </c>
-      <c r="D15" t="s">
-        <v>237</v>
-      </c>
       <c r="G15" s="6" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="M15" s="10">
         <v>100</v>
@@ -2728,19 +2731,19 @@
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C16" t="s">
+        <v>235</v>
+      </c>
+      <c r="D16" t="s">
         <v>236</v>
       </c>
-      <c r="D16" t="s">
-        <v>237</v>
-      </c>
       <c r="G16" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="M16" s="10">
         <v>100</v>
@@ -2756,19 +2759,19 @@
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C18" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E18" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="M18" s="10">
         <v>100</v>
@@ -2777,24 +2780,24 @@
         <v>128</v>
       </c>
       <c r="P18" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C19" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E19" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="M19">
         <v>4</v>
@@ -2803,24 +2806,24 @@
         <v>128</v>
       </c>
       <c r="P19" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C20" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E20" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="M20">
         <v>76</v>
@@ -2829,24 +2832,24 @@
         <v>128</v>
       </c>
       <c r="P20" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C21" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E21" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="L21" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="M21">
         <v>20</v>
@@ -2855,24 +2858,24 @@
         <v>128</v>
       </c>
       <c r="P21" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C22" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E22" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="M22" s="10">
         <v>100</v>
@@ -2881,24 +2884,24 @@
         <v>128</v>
       </c>
       <c r="P22" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C23" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E23" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="L23" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="M23" s="10">
         <v>100</v>
@@ -2907,24 +2910,24 @@
         <v>128</v>
       </c>
       <c r="P23" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C24" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E24" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="L24" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="M24">
         <v>20</v>
@@ -2933,24 +2936,24 @@
         <v>128</v>
       </c>
       <c r="P24" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C25" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E25" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="L25" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="M25">
         <v>60</v>
@@ -2959,24 +2962,24 @@
         <v>128</v>
       </c>
       <c r="P25" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C26" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E26" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="L26" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="M26">
         <v>20.000000000000018</v>
@@ -2985,24 +2988,24 @@
         <v>128</v>
       </c>
       <c r="P26" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C27" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E27" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="L27" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="M27" s="10">
         <v>100</v>
@@ -3011,7 +3014,7 @@
         <v>128</v>
       </c>
       <c r="P27" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
@@ -3021,13 +3024,13 @@
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>153</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="L29" s="6" t="s">
         <v>154</v>
-      </c>
-      <c r="G29" s="6" t="s">
-        <v>330</v>
-      </c>
-      <c r="L29" s="6" t="s">
-        <v>155</v>
       </c>
       <c r="M29" s="11">
         <v>6.4777062142923141</v>
@@ -3036,18 +3039,18 @@
         <v>128</v>
       </c>
       <c r="P29" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>153</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="L30" s="6" t="s">
         <v>154</v>
-      </c>
-      <c r="G30" s="6" t="s">
-        <v>334</v>
-      </c>
-      <c r="L30" s="6" t="s">
-        <v>155</v>
       </c>
       <c r="M30" s="11">
         <v>8.7567853491111922</v>
@@ -3056,21 +3059,21 @@
         <v>128</v>
       </c>
       <c r="O30" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P30" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>153</v>
+      </c>
+      <c r="G31" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="L31" s="6" t="s">
         <v>154</v>
-      </c>
-      <c r="G31" s="6" t="s">
-        <v>331</v>
-      </c>
-      <c r="L31" s="6" t="s">
-        <v>155</v>
       </c>
       <c r="M31" s="18">
         <v>59.671114354829328</v>
@@ -3079,21 +3082,21 @@
         <v>128</v>
       </c>
       <c r="O31" s="19" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P31" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>153</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="L32" s="6" t="s">
         <v>154</v>
-      </c>
-      <c r="G32" s="6" t="s">
-        <v>329</v>
-      </c>
-      <c r="L32" s="6" t="s">
-        <v>155</v>
       </c>
       <c r="M32" s="18">
         <v>16.802918820320372</v>
@@ -3104,13 +3107,13 @@
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>153</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="L33" s="6" t="s">
         <v>154</v>
-      </c>
-      <c r="G33" s="6" t="s">
-        <v>333</v>
-      </c>
-      <c r="L33" s="6" t="s">
-        <v>155</v>
       </c>
       <c r="M33" s="11">
         <v>7.4851294970113242</v>
@@ -3121,13 +3124,13 @@
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>153</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="L34" s="6" t="s">
         <v>154</v>
-      </c>
-      <c r="G34" s="6" t="s">
-        <v>332</v>
-      </c>
-      <c r="L34" s="6" t="s">
-        <v>155</v>
       </c>
       <c r="M34" s="11">
         <v>0.80634576443547301</v>
@@ -3180,7 +3183,7 @@
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -3201,14 +3204,14 @@
     <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="G40" s="4"/>
       <c r="L40" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="M40" s="23">
         <v>0</v>
       </c>
       <c r="N40" s="9"/>
       <c r="O40" s="9" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.25">
@@ -3217,377 +3220,377 @@
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="G42" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="K42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="L42" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="M42" s="18">
         <f>74100</f>
         <v>74100</v>
       </c>
       <c r="N42" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="O42" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P42" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="G43" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="K43" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="L43" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="M43" s="11">
         <f>3.9</f>
         <v>3.9</v>
       </c>
       <c r="N43" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="P43" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="G44" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="K44" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="L44" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="M44" s="11">
         <f>3.9</f>
         <v>3.9</v>
       </c>
       <c r="N44" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="P44" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="G45" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="K45" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="L45" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="M45" s="18">
         <v>0</v>
       </c>
       <c r="N45" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="G46" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="K46" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="L46" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="M46" s="22">
         <f t="shared" ref="M46:M47" si="0">M43</f>
         <v>3.9</v>
       </c>
       <c r="N46" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="O46" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.25">
       <c r="G47" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="K47" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="L47" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="M47" s="22">
         <f t="shared" si="0"/>
         <v>3.9</v>
       </c>
       <c r="N47" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="O47" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.25">
       <c r="G48" s="6" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="K48" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="L48" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="M48" s="18">
         <v>73300</v>
       </c>
       <c r="N48" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="O48" t="s">
+        <v>189</v>
+      </c>
+      <c r="P48" t="s">
         <v>190</v>
-      </c>
-      <c r="P48" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.25">
       <c r="G49" s="6" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="K49" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="L49" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="M49">
         <v>10</v>
       </c>
       <c r="N49" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="P49" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.25">
       <c r="G50" s="6" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="K50" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="L50" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="M50">
         <v>0.6</v>
       </c>
       <c r="N50" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="P50" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.25">
       <c r="G51" s="6" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="K51" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="L51" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="M51" s="18">
         <v>56100</v>
       </c>
       <c r="N51" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="O51" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P51" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="52" spans="1:16" x14ac:dyDescent="0.25">
       <c r="G52" s="6" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="K52" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="L52" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="M52">
         <v>5</v>
       </c>
       <c r="N52" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="P52" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.25">
       <c r="G53" s="6" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="K53" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="L53" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="M53">
         <v>0.1</v>
       </c>
       <c r="N53" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="P53" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.25">
       <c r="G54" s="6" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="K54" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="L54" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="M54" s="18">
         <v>0</v>
       </c>
       <c r="N54" t="s">
+        <v>186</v>
+      </c>
+      <c r="O54" t="s">
         <v>187</v>
       </c>
-      <c r="O54" t="s">
-        <v>188</v>
-      </c>
       <c r="P54" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.25">
       <c r="G55" s="6" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="K55" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="L55" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="M55" s="18">
         <v>300</v>
       </c>
       <c r="N55" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="P55" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.25">
       <c r="G56" s="6" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="K56" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="L56" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="M56" s="18">
         <v>4</v>
       </c>
       <c r="N56" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="P56" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.25">
       <c r="G57" s="6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="L57" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="M57" s="18">
         <v>0</v>
       </c>
       <c r="N57" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="O57" s="15"/>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.25">
       <c r="G58" s="6" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="L58" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="M58" s="18">
         <v>0</v>
       </c>
       <c r="N58" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="O58" s="15"/>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.25">
       <c r="G59" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="L59" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="M59" s="18">
         <v>0</v>
       </c>
       <c r="N59" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="O59" s="15" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.25">
       <c r="G60" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="L60" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="M60" s="18">
         <v>0</v>
       </c>
       <c r="N60" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="O60" s="15"/>
     </row>
@@ -3807,7 +3810,7 @@
       <c r="E71" s="4"/>
       <c r="F71" s="4"/>
       <c r="G71" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H71" s="4"/>
       <c r="I71" s="4"/>
@@ -3830,7 +3833,7 @@
       <c r="E72" s="4"/>
       <c r="F72" s="4"/>
       <c r="G72" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H72" s="4"/>
       <c r="I72" s="4"/>
@@ -3853,7 +3856,7 @@
       <c r="E73" s="4"/>
       <c r="F73" s="4"/>
       <c r="G73" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H73" s="4"/>
       <c r="I73" s="4"/>
@@ -3876,7 +3879,7 @@
       <c r="E74" s="4"/>
       <c r="F74" s="4"/>
       <c r="G74" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H74" s="6"/>
       <c r="I74" s="6"/>
@@ -4161,7 +4164,7 @@
         <v>0</v>
       </c>
       <c r="N96" s="9" t="s">
-        <v>57</v>
+        <v>334</v>
       </c>
       <c r="O96" s="9"/>
     </row>
@@ -4963,6 +4966,9 @@
       <c r="M148" s="13">
         <v>1.6176327916666666</v>
       </c>
+      <c r="N148" t="s">
+        <v>57</v>
+      </c>
       <c r="O148" s="6" t="s">
         <v>135</v>
       </c>
@@ -4978,10 +4984,14 @@
         <v>134</v>
       </c>
       <c r="M149" s="13">
-        <v>3.0774477499999997</v>
+        <f>3.07744775/0.85</f>
+        <v>3.6205267647058825</v>
+      </c>
+      <c r="N149" t="s">
+        <v>334</v>
       </c>
       <c r="O149" s="6" t="s">
-        <v>136</v>
+        <v>335</v>
       </c>
       <c r="P149" s="4" t="s">
         <v>91</v>
@@ -4997,8 +5007,11 @@
       <c r="M150" s="13">
         <v>0.25</v>
       </c>
+      <c r="N150" t="s">
+        <v>59</v>
+      </c>
       <c r="O150" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="P150" s="4" t="s">
         <v>112</v>
@@ -5040,12 +5053,12 @@
         <v>49</v>
       </c>
       <c r="M154" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="156" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
@@ -5065,13 +5078,13 @@
     </row>
     <row r="157" spans="1:16" x14ac:dyDescent="0.25">
       <c r="L157" s="9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="M157" s="9">
         <v>0</v>
       </c>
       <c r="N157" s="9" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="O157" s="9" t="s">
         <v>53</v>
@@ -5079,135 +5092,135 @@
     </row>
     <row r="158" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B158" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="L158" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="M158">
         <v>302</v>
       </c>
       <c r="N158" t="s">
+        <v>163</v>
+      </c>
+      <c r="O158" t="s">
         <v>164</v>
       </c>
-      <c r="O158" t="s">
-        <v>165</v>
-      </c>
       <c r="P158" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="159" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B159" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L159" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="M159">
         <v>197</v>
       </c>
       <c r="N159" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="O159" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P159" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="160" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B160" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L160" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="M160">
         <v>216</v>
       </c>
       <c r="N160" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="O160" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="P160" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="161" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B161" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="L161" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="M161">
         <v>216</v>
       </c>
       <c r="N161" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="O161" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="162" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B162" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L162" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="M162">
         <v>216</v>
       </c>
       <c r="N162" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="O162" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="163" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B163" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="L163" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="M163">
         <v>216</v>
       </c>
       <c r="N163" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="O163" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="164" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B164" t="s">
+        <v>161</v>
+      </c>
+      <c r="L164" t="s">
         <v>162</v>
-      </c>
-      <c r="L164" t="s">
-        <v>163</v>
       </c>
       <c r="M164">
         <v>216</v>
       </c>
       <c r="N164" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="O164" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="166" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B166" s="1"/>
       <c r="C166" s="1"/>
@@ -5227,13 +5240,13 @@
     </row>
     <row r="167" spans="1:16" x14ac:dyDescent="0.25">
       <c r="L167" s="9" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="M167" s="9">
         <v>0</v>
       </c>
       <c r="N167" s="9" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="O167" s="9" t="s">
         <v>53</v>
@@ -5241,13 +5254,13 @@
     </row>
     <row r="168" spans="1:16" x14ac:dyDescent="0.25">
       <c r="L168" s="9" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="M168" s="9">
         <v>0</v>
       </c>
       <c r="N168" s="9" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="O168" s="9" t="s">
         <v>53</v>
@@ -5255,13 +5268,13 @@
     </row>
     <row r="169" spans="1:16" x14ac:dyDescent="0.25">
       <c r="L169" s="9" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="M169" s="9">
         <v>0</v>
       </c>
       <c r="N169" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="O169" s="9" t="s">
         <v>53</v>
@@ -5269,143 +5282,143 @@
     </row>
     <row r="171" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C171" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D171" t="s">
+        <v>204</v>
+      </c>
+      <c r="E171" t="s">
         <v>205</v>
       </c>
-      <c r="E171" t="s">
-        <v>206</v>
-      </c>
       <c r="F171" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L171" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="M171" s="25">
         <f>'energy stables'!E24</f>
         <v>3.5302245250431775E-2</v>
       </c>
       <c r="N171" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O171" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P171" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="172" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C172" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D172" t="s">
+        <v>204</v>
+      </c>
+      <c r="E172" t="s">
         <v>205</v>
       </c>
-      <c r="E172" t="s">
-        <v>206</v>
-      </c>
       <c r="L172" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="M172" s="24">
         <f>'energy stables'!D26</f>
         <v>308.33833333333342</v>
       </c>
       <c r="N172" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="O172" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="P172" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="173" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C173" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D173" t="s">
+        <v>204</v>
+      </c>
+      <c r="E173" t="s">
         <v>205</v>
       </c>
-      <c r="E173" t="s">
-        <v>206</v>
-      </c>
       <c r="F173" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L173" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="M173" s="25">
         <f>'energy stables'!E27</f>
         <v>4.1036269430051814E-2</v>
       </c>
       <c r="N173" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="P173" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="175" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C175" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="L175" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="M175" s="24">
         <f>'energy stables'!D29</f>
         <v>170.33333333333331</v>
       </c>
       <c r="N175" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="O175" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P175" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="176" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C176" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="L176" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="M176" s="24">
         <f>'energy stables'!D31</f>
         <v>332.32333333333338</v>
       </c>
       <c r="N176" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="O176" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="P176" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="177" spans="1:16" x14ac:dyDescent="0.25">
@@ -5413,233 +5426,233 @@
     </row>
     <row r="178" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C178" t="s">
+        <v>235</v>
+      </c>
+      <c r="D178" t="s">
         <v>236</v>
       </c>
-      <c r="D178" t="s">
-        <v>237</v>
-      </c>
       <c r="E178" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L178" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="M178" s="25">
         <f>(290+1078)/100000</f>
         <v>1.3679999999999999E-2</v>
       </c>
       <c r="N178" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="O178" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="P178" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="179" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C179" t="s">
+        <v>235</v>
+      </c>
+      <c r="D179" t="s">
         <v>236</v>
       </c>
-      <c r="D179" t="s">
-        <v>237</v>
-      </c>
       <c r="E179" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L179" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="M179" s="25">
         <f>77000/100000</f>
         <v>0.77</v>
       </c>
       <c r="N179" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="P179" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="180" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C180" t="s">
+        <v>235</v>
+      </c>
+      <c r="D180" t="s">
         <v>236</v>
       </c>
-      <c r="D180" t="s">
-        <v>237</v>
-      </c>
       <c r="E180" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L180" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="M180" s="25">
         <f>(3340+9790)/100000</f>
         <v>0.1313</v>
       </c>
       <c r="N180" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="O180" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="P180" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="182" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C182" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E182" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="L182" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="M182">
         <f>'energy stables'!D49</f>
         <v>3.5</v>
       </c>
       <c r="N182" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="P182" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="183" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C183" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E183" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="L183" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="M183">
         <f>'energy stables'!D50</f>
         <v>12.5</v>
       </c>
       <c r="N183" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="P183" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="184" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C184" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E184" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="L184" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="M184">
         <f>'energy stables'!D51</f>
         <v>34</v>
       </c>
       <c r="N184" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="P184" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="185" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C185" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E185" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="L185" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="M185">
         <f>'energy stables'!D53</f>
         <v>0.04</v>
       </c>
       <c r="N185" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="P185" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="186" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C186" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E186" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="L186" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="M186" s="13">
         <f>'energy stables'!D54</f>
         <v>0.1</v>
       </c>
       <c r="N186" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="P186" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="187" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C187" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E187" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="L187" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="M187" s="13">
         <f>'energy stables'!D55</f>
         <v>0.26</v>
       </c>
       <c r="N187" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="P187" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
   </sheetData>
@@ -5661,7 +5674,7 @@
   <sheetData>
     <row r="3" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B3" s="53" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C3" s="54"/>
       <c r="D3" s="54"/>
@@ -5681,37 +5694,37 @@
     </row>
     <row r="4" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B4" s="51" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B5" s="27"/>
       <c r="C5" s="30"/>
       <c r="D5" s="46" t="s">
+        <v>207</v>
+      </c>
+      <c r="E5" s="28" t="s">
+        <v>205</v>
+      </c>
+      <c r="F5" s="30" t="s">
+        <v>224</v>
+      </c>
+      <c r="G5" s="29" t="s">
         <v>208</v>
       </c>
-      <c r="E5" s="28" t="s">
-        <v>206</v>
-      </c>
-      <c r="F5" s="30" t="s">
-        <v>225</v>
-      </c>
-      <c r="G5" s="29" t="s">
-        <v>209</v>
-      </c>
       <c r="H5" s="28" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I5" s="30" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="6" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B6" s="31" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C6" s="44" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D6" s="31">
         <v>150</v>
@@ -5726,10 +5739,10 @@
     </row>
     <row r="7" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B7" s="31" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C7" s="44" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D7" s="31">
         <v>150</v>
@@ -5744,10 +5757,10 @@
     </row>
     <row r="8" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B8" s="31" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C8" s="44" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D8" s="31">
         <v>10500</v>
@@ -5772,10 +5785,10 @@
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B10" s="31" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C10" s="44" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D10" s="31">
         <v>652</v>
@@ -5800,15 +5813,15 @@
         <v>123.33333333333333</v>
       </c>
       <c r="J10" s="26" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B11" s="31" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C11" s="44" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D11" s="31">
         <v>3</v>
@@ -5836,10 +5849,10 @@
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B12" s="31" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C12" s="44" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D12" s="31">
         <v>40</v>
@@ -5864,15 +5877,15 @@
         <v>10.333333333333332</v>
       </c>
       <c r="J12" s="26" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B13" s="31" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C13" s="44" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D13" s="31">
         <v>216</v>
@@ -5900,10 +5913,10 @@
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B14" s="31" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C14" s="44" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D14" s="31">
         <v>386</v>
@@ -5926,15 +5939,15 @@
         <v>0</v>
       </c>
       <c r="J14" s="26" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="15" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B15" s="31" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C15" s="44" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D15" s="31">
         <v>216</v>
@@ -5971,10 +5984,10 @@
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B17" s="36" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C17" s="44" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D17" s="36">
         <f>SUM(D10:D15)</f>
@@ -6003,10 +6016,10 @@
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B18" s="31" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C18" s="44" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D18" s="31">
         <v>868</v>
@@ -6061,7 +6074,7 @@
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B20" s="42" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C20" s="45" t="s">
         <v>128</v>
@@ -6079,25 +6092,25 @@
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B22" s="71" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B23" s="79"/>
       <c r="C23" s="80"/>
       <c r="D23" s="81" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E23" s="82" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B24" s="64" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C24" s="65" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D24" s="72">
         <v>0</v>
@@ -6109,10 +6122,10 @@
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B25" s="64" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C25" s="65" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D25" s="72">
         <v>0</v>
@@ -6123,10 +6136,10 @@
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B26" s="64" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C26" s="65" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D26" s="75">
         <f>SUM(E11:E13,E15,H11:H13,H15)/2</f>
@@ -6138,10 +6151,10 @@
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B27" s="64" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C27" s="65" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D27" s="72">
         <v>0</v>
@@ -6159,10 +6172,10 @@
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B29" s="64" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C29" s="65" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D29" s="75">
         <f>SUM(F10,I10)/2</f>
@@ -6174,10 +6187,10 @@
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B30" s="64" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C30" s="65" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D30" s="72">
         <v>0</v>
@@ -6188,10 +6201,10 @@
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B31" s="64" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C31" s="65" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D31" s="75">
         <f>SUM(F11:F13,F15,I11:I13,I15)</f>
@@ -6203,10 +6216,10 @@
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B32" s="66" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C32" s="67" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D32" s="76">
         <v>0</v>
@@ -6217,7 +6230,7 @@
     </row>
     <row r="34" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B34" s="53" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C34" s="54"/>
       <c r="D34" s="54"/>
@@ -6237,69 +6250,69 @@
     </row>
     <row r="35" spans="2:19" x14ac:dyDescent="0.25">
       <c r="J35" s="51" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="36" spans="2:19" x14ac:dyDescent="0.25">
       <c r="J36" s="46" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="K36" s="28"/>
       <c r="L36" s="28"/>
       <c r="M36" s="29" t="s">
+        <v>303</v>
+      </c>
+      <c r="N36" s="29" t="s">
         <v>304</v>
       </c>
-      <c r="N36" s="29" t="s">
+      <c r="O36" s="29" t="s">
         <v>305</v>
       </c>
-      <c r="O36" s="29" t="s">
+      <c r="P36" s="50" t="s">
         <v>306</v>
       </c>
-      <c r="P36" s="50" t="s">
-        <v>307</v>
-      </c>
       <c r="Q36" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="37" spans="2:19" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="51" t="s">
+        <v>253</v>
+      </c>
+      <c r="J37" s="42" t="s">
         <v>254</v>
-      </c>
-      <c r="J37" s="42" t="s">
-        <v>255</v>
       </c>
       <c r="K37" s="14"/>
       <c r="L37" s="14"/>
       <c r="M37" s="59" t="s">
+        <v>299</v>
+      </c>
+      <c r="N37" s="59" t="s">
         <v>300</v>
       </c>
-      <c r="N37" s="59" t="s">
+      <c r="O37" s="59" t="s">
         <v>301</v>
       </c>
-      <c r="O37" s="59" t="s">
+      <c r="P37" s="60" t="s">
         <v>302</v>
       </c>
-      <c r="P37" s="60" t="s">
-        <v>303</v>
-      </c>
       <c r="Q37" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="38" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B38" s="46" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C38" s="29"/>
       <c r="D38" s="29" t="s">
+        <v>247</v>
+      </c>
+      <c r="E38" s="50" t="s">
         <v>248</v>
       </c>
-      <c r="E38" s="50" t="s">
-        <v>249</v>
-      </c>
       <c r="J38" s="31" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -6316,14 +6329,14 @@
         <v>242</v>
       </c>
       <c r="Q38" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="R38" s="58"/>
       <c r="S38" s="58"/>
     </row>
     <row r="39" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="31" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C39" s="4"/>
       <c r="D39" s="4">
@@ -6333,7 +6346,7 @@
         <v>0.4</v>
       </c>
       <c r="J39" s="31" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -6347,17 +6360,17 @@
         <v>9.6</v>
       </c>
       <c r="P39" s="32" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q39" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="R39" s="58"/>
       <c r="S39" s="58"/>
     </row>
     <row r="40" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B40" s="31" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C40" s="4"/>
       <c r="D40" s="4">
@@ -6367,7 +6380,7 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="J40" s="31" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -6384,14 +6397,14 @@
         <v>43.2</v>
       </c>
       <c r="Q40" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="R40" s="58"/>
       <c r="S40" s="58"/>
     </row>
     <row r="41" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B41" s="31" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C41" s="4"/>
       <c r="D41" s="4">
@@ -6401,7 +6414,7 @@
         <v>0.06</v>
       </c>
       <c r="J41" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -6418,14 +6431,14 @@
         <v>340</v>
       </c>
       <c r="Q41" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="R41" s="58"/>
       <c r="S41" s="58"/>
     </row>
     <row r="42" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B42" s="31" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C42" s="4"/>
       <c r="D42" s="4">
@@ -6435,7 +6448,7 @@
         <v>0.04</v>
       </c>
       <c r="J42" s="31" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -6449,17 +6462,17 @@
         <v>4.2</v>
       </c>
       <c r="P42" s="32" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="Q42" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="R42" s="58"/>
       <c r="S42" s="58"/>
     </row>
     <row r="43" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B43" s="42" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C43" s="14"/>
       <c r="D43" s="14">
@@ -6491,41 +6504,41 @@
     </row>
     <row r="44" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C44" s="68" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D44" s="69">
         <f>D39*33+E39*26</f>
         <v>1660.4</v>
       </c>
       <c r="E44" s="70" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="J44" s="31" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
       <c r="M44" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="N44" s="4">
         <v>4</v>
       </c>
       <c r="O44" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="P44" s="32" t="s">
         <v>271</v>
       </c>
-      <c r="P44" s="32" t="s">
-        <v>272</v>
-      </c>
       <c r="Q44" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="R44" s="58"/>
       <c r="S44" s="58"/>
     </row>
     <row r="45" spans="2:19" x14ac:dyDescent="0.25">
       <c r="J45" s="31" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -6539,20 +6552,20 @@
         <v>0.7</v>
       </c>
       <c r="P45" s="32" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q45" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="R45" s="58"/>
       <c r="S45" s="58"/>
     </row>
     <row r="46" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B46" s="71" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="J46" s="31" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -6566,10 +6579,10 @@
         <v>87</v>
       </c>
       <c r="P46" s="32" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q46" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="R46" s="58"/>
       <c r="S46" s="58"/>
@@ -6578,16 +6591,16 @@
       <c r="B47" s="27"/>
       <c r="C47" s="28"/>
       <c r="D47" s="86" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E47" s="28" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F47" s="28"/>
       <c r="G47" s="28"/>
       <c r="H47" s="30"/>
       <c r="J47" s="31" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -6598,13 +6611,13 @@
         <v>15</v>
       </c>
       <c r="O47" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="P47" s="32" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q47" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="R47" s="58"/>
       <c r="S47" s="58"/>
@@ -6613,22 +6626,22 @@
       <c r="B48" s="42"/>
       <c r="C48" s="14"/>
       <c r="D48" s="87" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E48" s="14" t="s">
         <v>26</v>
       </c>
       <c r="F48" s="83" t="s">
+        <v>151</v>
+      </c>
+      <c r="G48" s="83" t="s">
         <v>152</v>
       </c>
-      <c r="G48" s="83" t="s">
-        <v>153</v>
-      </c>
       <c r="H48" s="84" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J48" s="31" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -6642,20 +6655,20 @@
         <v>1</v>
       </c>
       <c r="P48" s="32" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q48" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="R48" s="58"/>
       <c r="S48" s="58"/>
     </row>
     <row r="49" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B49" s="85" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C49" s="28" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D49" s="88">
         <f>D42</f>
@@ -6674,7 +6687,7 @@
         <v>0</v>
       </c>
       <c r="J49" s="46" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="K49" s="29"/>
       <c r="L49" s="29"/>
@@ -6691,17 +6704,17 @@
         <v>1252</v>
       </c>
       <c r="Q49" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="R49" s="58"/>
       <c r="S49" s="58"/>
     </row>
     <row r="50" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B50" s="31" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D50" s="88">
         <f>D39*0.25</f>
@@ -6723,7 +6736,7 @@
         <v>20</v>
       </c>
       <c r="J50" s="31" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -6744,10 +6757,10 @@
     </row>
     <row r="51" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B51" s="31" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D51" s="89">
         <f>D39-D49-D50</f>
@@ -6766,7 +6779,7 @@
         <v>100</v>
       </c>
       <c r="J51" s="61" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="K51" s="63"/>
       <c r="L51" s="63"/>
@@ -6787,7 +6800,7 @@
         <v>34</v>
       </c>
       <c r="Q51" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="R51" s="58"/>
       <c r="S51" s="58"/>
@@ -6801,7 +6814,7 @@
       <c r="G52" s="72"/>
       <c r="H52" s="74"/>
       <c r="J52" s="55" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="K52" s="56"/>
       <c r="L52" s="56"/>
@@ -6815,18 +6828,18 @@
         <v>87</v>
       </c>
       <c r="P52" s="57" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="Q52" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="53" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B53" s="64" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D53" s="88">
         <f>E42</f>
@@ -6845,32 +6858,32 @@
         <v>0</v>
       </c>
       <c r="J53" s="31" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
       <c r="M53" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="N53" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="O53" s="4" t="s">
         <v>87</v>
       </c>
       <c r="P53" s="32" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Q53" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="54" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B54" s="31" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D54" s="90">
         <f>E39*0.25</f>
@@ -6892,32 +6905,32 @@
         <v>20.000000000000018</v>
       </c>
       <c r="J54" s="31" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>
       <c r="M54" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="N54" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="O54" s="4" t="s">
         <v>87</v>
       </c>
       <c r="P54" s="32" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Q54" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="55" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B55" s="42" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C55" s="14" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D55" s="91">
         <f>E39-D53-D54</f>
@@ -6936,27 +6949,27 @@
         <v>100</v>
       </c>
       <c r="J55" s="31" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="K55" s="4"/>
       <c r="L55" s="4"/>
       <c r="M55" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="N55" s="4"/>
       <c r="O55" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="P55" s="32" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Q55" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="56" spans="2:19" x14ac:dyDescent="0.25">
       <c r="J56" s="42" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="K56" s="14"/>
       <c r="L56" s="14"/>
@@ -7008,7 +7021,7 @@
   <sheetData>
     <row r="3" spans="5:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F3">
         <v>90</v>
@@ -7025,7 +7038,7 @@
     </row>
     <row r="4" spans="5:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F4">
         <v>654</v>
@@ -7034,15 +7047,15 @@
         <v>80</v>
       </c>
       <c r="H4" t="s">
+        <v>260</v>
+      </c>
+      <c r="I4" t="s">
         <v>261</v>
-      </c>
-      <c r="I4" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="5" spans="5:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E5" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F5">
         <v>11</v>
@@ -7051,66 +7064,66 @@
         <v>12</v>
       </c>
       <c r="H5" t="s">
+        <v>263</v>
+      </c>
+      <c r="I5" t="s">
         <v>264</v>
-      </c>
-      <c r="I5" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="6" spans="5:20" x14ac:dyDescent="0.25">
       <c r="E6" t="s">
+        <v>292</v>
+      </c>
+      <c r="F6" t="s">
         <v>293</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>294</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>295</v>
       </c>
-      <c r="H6" t="s">
+      <c r="I6" t="s">
         <v>296</v>
-      </c>
-      <c r="I6" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="7" spans="5:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E7" t="s">
+        <v>255</v>
+      </c>
+      <c r="G7" t="s">
+        <v>265</v>
+      </c>
+      <c r="I7" t="s">
+        <v>266</v>
+      </c>
+      <c r="O7" t="s">
+        <v>267</v>
+      </c>
+      <c r="S7" t="s">
         <v>256</v>
-      </c>
-      <c r="G7" t="s">
-        <v>266</v>
-      </c>
-      <c r="I7" t="s">
-        <v>267</v>
-      </c>
-      <c r="O7" t="s">
-        <v>268</v>
-      </c>
-      <c r="S7" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="8" spans="5:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E8" t="s">
+        <v>268</v>
+      </c>
+      <c r="H8" t="s">
         <v>269</v>
-      </c>
-      <c r="H8" t="s">
-        <v>270</v>
       </c>
       <c r="K8">
         <v>4</v>
       </c>
       <c r="P8" t="s">
+        <v>270</v>
+      </c>
+      <c r="T8" t="s">
         <v>271</v>
-      </c>
-      <c r="T8" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="9" spans="5:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E9" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H9">
         <v>79</v>
@@ -7119,15 +7132,15 @@
         <v>7</v>
       </c>
       <c r="P9" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="T9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="10" spans="5:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E10" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H10" t="s">
         <v>87</v>
@@ -7139,12 +7152,12 @@
         <v>87</v>
       </c>
       <c r="T10" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="11" spans="5:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E11" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H11">
         <v>38</v>
@@ -7153,15 +7166,15 @@
         <v>15</v>
       </c>
       <c r="P11" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="T11" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="12" spans="5:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E12" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H12">
         <v>164</v>
@@ -7170,15 +7183,15 @@
         <v>66</v>
       </c>
       <c r="P12" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="T12" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="13" spans="5:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E13" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H13">
         <v>2433</v>
@@ -7187,7 +7200,7 @@
         <v>689</v>
       </c>
       <c r="P13" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="T13">
         <v>1252</v>
@@ -7195,7 +7208,7 @@
     </row>
     <row r="14" spans="5:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E14" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H14">
         <v>1441</v>
@@ -7204,7 +7217,7 @@
         <v>689</v>
       </c>
       <c r="P14" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="T14">
         <v>1218</v>
@@ -7212,47 +7225,47 @@
     </row>
     <row r="15" spans="5:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E15" t="s">
+        <v>282</v>
+      </c>
+      <c r="L15" t="s">
         <v>283</v>
       </c>
-      <c r="L15" t="s">
+      <c r="Q15" t="s">
         <v>284</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="16" spans="5:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E16" t="s">
+        <v>285</v>
+      </c>
+      <c r="H16" t="s">
         <v>286</v>
       </c>
-      <c r="H16" t="s">
-        <v>287</v>
-      </c>
       <c r="K16" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="P16" t="s">
         <v>87</v>
       </c>
       <c r="T16" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="17" spans="5:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E17" t="s">
+        <v>287</v>
+      </c>
+      <c r="H17" t="s">
         <v>288</v>
       </c>
-      <c r="H17" t="s">
+      <c r="K17" t="s">
         <v>289</v>
       </c>
-      <c r="K17" t="s">
+      <c r="P17" t="s">
         <v>290</v>
       </c>
-      <c r="P17" t="s">
+      <c r="T17" t="s">
         <v>291</v>
-      </c>
-      <c r="T17" t="s">
-        <v>292</v>
       </c>
     </row>
   </sheetData>
@@ -7271,47 +7284,47 @@
   <sheetData>
     <row r="3" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F3" s="49" t="s">
+        <v>303</v>
+      </c>
+      <c r="G3" s="49" t="s">
         <v>304</v>
       </c>
-      <c r="G3" s="49" t="s">
+      <c r="H3" s="49" t="s">
         <v>305</v>
       </c>
-      <c r="H3" s="49" t="s">
+      <c r="I3" s="49" t="s">
         <v>306</v>
       </c>
-      <c r="I3" s="49" t="s">
-        <v>307</v>
-      </c>
       <c r="J3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="4" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F4" t="s">
+        <v>299</v>
+      </c>
+      <c r="G4" t="s">
         <v>300</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>301</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>302</v>
       </c>
-      <c r="I4" t="s">
-        <v>303</v>
-      </c>
       <c r="J4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="5" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F5">
         <v>90</v>
@@ -7326,12 +7339,12 @@
         <v>242</v>
       </c>
       <c r="J5" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="6" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F6">
         <v>654</v>
@@ -7343,15 +7356,15 @@
         <v>9.6</v>
       </c>
       <c r="I6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="J6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="7" spans="3:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F7">
         <v>11</v>
@@ -7366,12 +7379,12 @@
         <v>43.2</v>
       </c>
       <c r="J7" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="8" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F8">
         <v>244</v>
@@ -7386,12 +7399,12 @@
         <v>340</v>
       </c>
       <c r="J8" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="9" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F9">
         <v>992</v>
@@ -7403,35 +7416,35 @@
         <v>4.2</v>
       </c>
       <c r="I9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="J9" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="10" spans="3:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
+        <v>268</v>
+      </c>
+      <c r="F10" t="s">
         <v>269</v>
-      </c>
-      <c r="F10" t="s">
-        <v>270</v>
       </c>
       <c r="G10">
         <v>4</v>
       </c>
       <c r="H10" t="s">
+        <v>270</v>
+      </c>
+      <c r="I10" t="s">
         <v>271</v>
       </c>
-      <c r="I10" t="s">
-        <v>272</v>
-      </c>
       <c r="J10" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F11">
         <v>79</v>
@@ -7443,15 +7456,15 @@
         <v>0.7</v>
       </c>
       <c r="I11" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="J11" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="12" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F12" t="s">
         <v>87</v>
@@ -7463,15 +7476,15 @@
         <v>87</v>
       </c>
       <c r="I12" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="J12" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="13" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F13">
         <v>38</v>
@@ -7480,18 +7493,18 @@
         <v>15</v>
       </c>
       <c r="H13" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="I13" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="J13" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="14" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F14">
         <v>164</v>
@@ -7503,15 +7516,15 @@
         <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="J14" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="15" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F15">
         <v>2433</v>
@@ -7526,12 +7539,12 @@
         <v>1252</v>
       </c>
       <c r="J15" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="16" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C16" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F16">
         <v>1441</v>
@@ -7546,12 +7559,12 @@
         <v>1218</v>
       </c>
       <c r="J16" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="17" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C17" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F17">
         <v>23</v>
@@ -7563,72 +7576,72 @@
         <v>87</v>
       </c>
       <c r="I17" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="J17" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="18" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C18" t="s">
+        <v>285</v>
+      </c>
+      <c r="F18" t="s">
         <v>286</v>
       </c>
-      <c r="F18" t="s">
-        <v>287</v>
-      </c>
       <c r="G18" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H18" t="s">
         <v>87</v>
       </c>
       <c r="I18" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="J18" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="19" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C19" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F19" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="G19" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H19" t="s">
         <v>87</v>
       </c>
       <c r="I19" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="J19" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="20" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C20" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F20" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H20" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="I20" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="J20" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="21" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C21" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F21">
         <v>1998</v>
@@ -7643,7 +7656,7 @@
         <v>2008</v>
       </c>
       <c r="J21" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
   </sheetData>
@@ -7659,62 +7672,62 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="17" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="17" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="17" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="48" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="48" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
   </sheetData>

--- a/data/default/MachineryAndEnergyMgmt.xlsx
+++ b/data/default/MachineryAndEnergyMgmt.xlsx
@@ -477,7 +477,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="949" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1017" uniqueCount="359">
   <si>
     <t>f_crop</t>
   </si>
@@ -1663,6 +1663,75 @@
   </si>
   <si>
     <t>Adjusted to dry matter. Transport halm</t>
+  </si>
+  <si>
+    <t>dryer_efficiency</t>
+  </si>
+  <si>
+    <t>Share of energy in fuel recovered as usefull energy for drying</t>
+  </si>
+  <si>
+    <t>water_content_at_harvest</t>
+  </si>
+  <si>
+    <t>water_content_after_drying</t>
+  </si>
+  <si>
+    <t>f_crop_group:crop</t>
+  </si>
+  <si>
+    <t>Cereals, winter</t>
+  </si>
+  <si>
+    <t>Cereals, spring</t>
+  </si>
+  <si>
+    <t>Grain legumes</t>
+  </si>
+  <si>
+    <t>Brassicaceae</t>
+  </si>
+  <si>
+    <t>water_content_at_harvest=-99 gives no drying assumed</t>
+  </si>
+  <si>
+    <t>Edström et al 2005, p. 14</t>
+  </si>
+  <si>
+    <t>dryer_auxiliary_energy</t>
+  </si>
+  <si>
+    <t>grain dryers</t>
+  </si>
+  <si>
+    <t>grain dryers auxiliary energy</t>
+  </si>
+  <si>
+    <t>Petersson 2016</t>
+  </si>
+  <si>
+    <t>kWh/kg water removed</t>
+  </si>
+  <si>
+    <t>Usefull energy per mass of water removed. Calculated from 0.16 L oil/kg (0.14-0.17) water assuming 10.36 kWh/L and a dryer efficiency of 90%</t>
+  </si>
+  <si>
+    <t>SJV 2010</t>
+  </si>
+  <si>
+    <t>Törner &amp; Norup 2009, p.5</t>
+  </si>
+  <si>
+    <t>Electricity use for fans, conveyers etc. Per kg harvest. Calculated from 75-90 kWh/ha divided by an average yield of cereals, grain legumes and oil crops of ~5200 kg/ha (2016-2020)</t>
+  </si>
+  <si>
+    <t>Energy use for grain dryers</t>
+  </si>
+  <si>
+    <t>dryer_energy_per_mass_water</t>
+  </si>
+  <si>
+    <t>Törner &amp; Norup 2009, p.11</t>
   </si>
 </sst>
 </file>
@@ -2072,7 +2141,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -2170,6 +2239,8 @@
     <xf numFmtId="2" fontId="23" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="23" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2451,1289 +2522,1260 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T187"/>
+  <dimension ref="A1:U216"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="7" max="11" width="12.28515625" customWidth="1"/>
-    <col min="12" max="12" width="36.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.28515625" customWidth="1"/>
-    <col min="14" max="14" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="58.7109375" customWidth="1"/>
-    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="8" max="12" width="12.28515625" customWidth="1"/>
+    <col min="13" max="13" width="36.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.28515625" customWidth="1"/>
+    <col min="15" max="15" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="58.7109375" customWidth="1"/>
+    <col min="17" max="17" width="22.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A1" s="49" t="s">
         <v>149</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="93" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="93" t="s">
+        <v>340</v>
+      </c>
+      <c r="D1" s="93" t="s">
         <v>194</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="E1" s="93" t="s">
         <v>202</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="F1" s="93" t="s">
         <v>203</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="G1" s="93" t="s">
         <v>227</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="H1" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="I1" s="93" t="s">
         <v>52</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="J1" s="93" t="s">
         <v>44</v>
       </c>
-      <c r="J1" s="14" t="s">
+      <c r="K1" s="93" t="s">
         <v>129</v>
       </c>
-      <c r="K1" s="14" t="s">
+      <c r="L1" s="93" t="s">
         <v>175</v>
       </c>
-      <c r="L1" s="14" t="s">
+      <c r="M1" s="93" t="s">
         <v>1</v>
       </c>
-      <c r="M1" s="14" t="s">
+      <c r="N1" s="93" t="s">
         <v>2</v>
       </c>
-      <c r="N1" s="14" t="s">
+      <c r="O1" s="93" t="s">
         <v>3</v>
       </c>
-      <c r="O1" s="14" t="s">
+      <c r="P1" s="93" t="s">
         <v>4</v>
       </c>
-      <c r="P1" s="14" t="s">
+      <c r="Q1" s="93" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="L2" s="20" t="s">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M2" s="20" t="s">
         <v>154</v>
       </c>
-      <c r="M2" s="9">
+      <c r="N2" s="9">
         <v>0</v>
       </c>
-      <c r="N2" s="9" t="s">
+      <c r="O2" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="O2" s="9" t="s">
+      <c r="P2" s="9" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>150</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="H4" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="L4" s="6" t="s">
+      <c r="M4" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="M4" s="18">
+      <c r="N4" s="18">
         <f>(241822577+237201100)/(241822577+237201100+5856000+8368914)*100</f>
         <v>97.116076100458642</v>
       </c>
-      <c r="N4" t="s">
+      <c r="O4" t="s">
         <v>128</v>
       </c>
-      <c r="P4" t="s">
+      <c r="Q4" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>150</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="H5" s="4" t="s">
         <v>326</v>
       </c>
-      <c r="L5" s="6" t="s">
+      <c r="M5" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="M5" s="18">
-        <f>100-M4</f>
+      <c r="N5" s="18">
+        <f>100-N4</f>
         <v>2.8839238995413581</v>
       </c>
-      <c r="N5" t="s">
+      <c r="O5" t="s">
         <v>128</v>
       </c>
-      <c r="P5" t="s">
+      <c r="Q5" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>150</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="H6" s="4" t="s">
         <v>327</v>
       </c>
-      <c r="L6" s="6" t="s">
+      <c r="M6" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="M6" s="10">
+      <c r="N6" s="10">
         <v>0</v>
       </c>
-      <c r="N6" t="s">
+      <c r="O6" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>150</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="H7" s="6" t="s">
         <v>328</v>
       </c>
-      <c r="L7" s="6" t="s">
+      <c r="M7" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="M7" s="10">
+      <c r="N7" s="10">
         <v>0</v>
       </c>
-      <c r="N7" t="s">
+      <c r="O7" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="G8" s="6"/>
-      <c r="L8" s="6"/>
-      <c r="M8" s="10"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H8" s="6"/>
+      <c r="M8" s="6"/>
+      <c r="N8" s="10"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>197</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>195</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="H9" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="L9" s="6" t="s">
+      <c r="M9" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="M9" s="10">
+      <c r="N9" s="10">
         <v>100</v>
       </c>
-      <c r="N9" t="s">
+      <c r="O9" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>198</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>195</v>
       </c>
-      <c r="G10" s="4"/>
-      <c r="L10" s="6"/>
-      <c r="M10" s="10"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="H10" s="4"/>
+      <c r="M10" s="6"/>
+      <c r="N10" s="10"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>201</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>195</v>
       </c>
-      <c r="G11" s="6" t="s">
+      <c r="H11" s="6" t="s">
         <v>328</v>
       </c>
-      <c r="L11" s="6" t="s">
+      <c r="M11" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="M11" s="10">
+      <c r="N11" s="10">
         <v>100</v>
       </c>
-      <c r="N11" t="s">
+      <c r="O11" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>199</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>195</v>
       </c>
-      <c r="G12" s="6" t="s">
+      <c r="H12" s="6" t="s">
         <v>328</v>
       </c>
-      <c r="L12" s="6" t="s">
+      <c r="M12" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="M12" s="10">
+      <c r="N12" s="10">
         <v>100</v>
       </c>
-      <c r="N12" t="s">
+      <c r="O12" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="G13" s="6"/>
-      <c r="L13" s="6"/>
-      <c r="M13" s="10"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H13" s="6"/>
+      <c r="M13" s="6"/>
+      <c r="N13" s="10"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>197</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>235</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>236</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="H14" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="L14" s="6" t="s">
+      <c r="M14" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="M14" s="10">
+      <c r="N14" s="10">
         <v>100</v>
       </c>
-      <c r="N14" t="s">
+      <c r="O14" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>198</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>235</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>236</v>
       </c>
-      <c r="G15" s="6" t="s">
+      <c r="H15" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="L15" s="6" t="s">
+      <c r="M15" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="M15" s="10">
+      <c r="N15" s="10">
         <v>100</v>
       </c>
-      <c r="N15" t="s">
+      <c r="O15" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>201</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>235</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>236</v>
       </c>
-      <c r="G16" s="6" t="s">
+      <c r="H16" s="6" t="s">
         <v>328</v>
       </c>
-      <c r="L16" s="6" t="s">
+      <c r="M16" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="M16" s="10">
+      <c r="N16" s="10">
         <v>100</v>
       </c>
-      <c r="N16" t="s">
+      <c r="O16" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="G17" s="6"/>
-      <c r="L17" s="6"/>
-      <c r="M17" s="10"/>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H17" s="6"/>
+      <c r="M17" s="6"/>
+      <c r="N17" s="10"/>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>197</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>242</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>318</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="H18" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="L18" s="6" t="s">
+      <c r="M18" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="M18" s="10">
+      <c r="N18" s="10">
         <v>100</v>
       </c>
-      <c r="N18" t="s">
+      <c r="O18" t="s">
         <v>128</v>
       </c>
-      <c r="P18" t="s">
+      <c r="Q18" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>198</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>242</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>318</v>
       </c>
-      <c r="G19" s="6" t="s">
+      <c r="H19" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="L19" s="6" t="s">
+      <c r="M19" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="M19">
+      <c r="N19">
         <v>4</v>
       </c>
-      <c r="N19" t="s">
+      <c r="O19" t="s">
         <v>128</v>
       </c>
-      <c r="P19" t="s">
+      <c r="Q19" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>198</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>242</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>318</v>
       </c>
-      <c r="G20" s="6" t="s">
+      <c r="H20" s="6" t="s">
         <v>330</v>
       </c>
-      <c r="L20" s="6" t="s">
+      <c r="M20" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="M20">
+      <c r="N20">
         <v>76</v>
       </c>
-      <c r="N20" t="s">
+      <c r="O20" t="s">
         <v>128</v>
       </c>
-      <c r="P20" t="s">
+      <c r="Q20" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>198</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>242</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>318</v>
       </c>
-      <c r="G21" s="6" t="s">
+      <c r="H21" s="6" t="s">
         <v>328</v>
       </c>
-      <c r="L21" s="6" t="s">
+      <c r="M21" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="M21">
+      <c r="N21">
         <v>20</v>
       </c>
-      <c r="N21" t="s">
+      <c r="O21" t="s">
         <v>128</v>
       </c>
-      <c r="P21" t="s">
+      <c r="Q21" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>201</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
         <v>242</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>318</v>
       </c>
-      <c r="G22" s="6" t="s">
+      <c r="H22" s="6" t="s">
         <v>328</v>
       </c>
-      <c r="L22" s="6" t="s">
+      <c r="M22" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="M22" s="10">
+      <c r="N22" s="10">
         <v>100</v>
       </c>
-      <c r="N22" t="s">
+      <c r="O22" t="s">
         <v>128</v>
       </c>
-      <c r="P22" t="s">
+      <c r="Q22" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>197</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D23" t="s">
         <v>242</v>
       </c>
-      <c r="E23" t="s">
+      <c r="F23" t="s">
         <v>321</v>
       </c>
-      <c r="G23" s="4" t="s">
+      <c r="H23" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="L23" s="6" t="s">
+      <c r="M23" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="M23" s="10">
+      <c r="N23" s="10">
         <v>100</v>
       </c>
-      <c r="N23" t="s">
+      <c r="O23" t="s">
         <v>128</v>
       </c>
-      <c r="P23" t="s">
+      <c r="Q23" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>198</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D24" t="s">
         <v>242</v>
       </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
         <v>321</v>
       </c>
-      <c r="G24" s="6" t="s">
+      <c r="H24" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="L24" s="6" t="s">
+      <c r="M24" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="M24">
+      <c r="N24">
         <v>20</v>
       </c>
-      <c r="N24" t="s">
+      <c r="O24" t="s">
         <v>128</v>
       </c>
-      <c r="P24" t="s">
+      <c r="Q24" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>198</v>
       </c>
-      <c r="C25" t="s">
+      <c r="D25" t="s">
         <v>242</v>
       </c>
-      <c r="E25" t="s">
+      <c r="F25" t="s">
         <v>321</v>
       </c>
-      <c r="G25" s="6" t="s">
+      <c r="H25" s="6" t="s">
         <v>330</v>
       </c>
-      <c r="L25" s="6" t="s">
+      <c r="M25" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="M25">
+      <c r="N25">
         <v>60</v>
       </c>
-      <c r="N25" t="s">
+      <c r="O25" t="s">
         <v>128</v>
       </c>
-      <c r="P25" t="s">
+      <c r="Q25" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>198</v>
       </c>
-      <c r="C26" t="s">
+      <c r="D26" t="s">
         <v>242</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>321</v>
       </c>
-      <c r="G26" s="6" t="s">
+      <c r="H26" s="6" t="s">
         <v>328</v>
       </c>
-      <c r="L26" s="6" t="s">
+      <c r="M26" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="M26">
+      <c r="N26">
         <v>20.000000000000018</v>
       </c>
-      <c r="N26" t="s">
+      <c r="O26" t="s">
         <v>128</v>
       </c>
-      <c r="P26" t="s">
+      <c r="Q26" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>201</v>
       </c>
-      <c r="C27" t="s">
+      <c r="D27" t="s">
         <v>242</v>
       </c>
-      <c r="E27" t="s">
+      <c r="F27" t="s">
         <v>321</v>
       </c>
-      <c r="G27" s="6" t="s">
+      <c r="H27" s="6" t="s">
         <v>328</v>
       </c>
-      <c r="L27" s="6" t="s">
+      <c r="M27" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="M27" s="10">
+      <c r="N27" s="10">
         <v>100</v>
       </c>
-      <c r="N27" t="s">
+      <c r="O27" t="s">
         <v>128</v>
       </c>
-      <c r="P27" t="s">
+      <c r="Q27" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="G28" s="6"/>
-      <c r="L28" s="6"/>
-      <c r="M28" s="15"/>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H28" s="6"/>
+      <c r="M28" s="6"/>
+      <c r="N28" s="15"/>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>153</v>
       </c>
-      <c r="G29" s="6" t="s">
+      <c r="H29" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="L29" s="6" t="s">
+      <c r="M29" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="M29" s="11">
+      <c r="N29" s="11">
         <v>6.4777062142923141</v>
       </c>
-      <c r="N29" t="s">
+      <c r="O29" t="s">
         <v>128</v>
       </c>
-      <c r="P29" t="s">
+      <c r="Q29" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>153</v>
       </c>
-      <c r="G30" s="6" t="s">
+      <c r="H30" s="6" t="s">
         <v>333</v>
       </c>
-      <c r="L30" s="6" t="s">
+      <c r="M30" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="M30" s="11">
+      <c r="N30" s="11">
         <v>8.7567853491111922</v>
       </c>
-      <c r="N30" t="s">
+      <c r="O30" t="s">
         <v>128</v>
       </c>
-      <c r="O30" t="s">
+      <c r="P30" t="s">
         <v>170</v>
       </c>
-      <c r="P30" t="s">
+      <c r="Q30" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>153</v>
       </c>
-      <c r="G31" s="6" t="s">
+      <c r="H31" s="6" t="s">
         <v>330</v>
       </c>
-      <c r="L31" s="6" t="s">
+      <c r="M31" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="M31" s="18">
+      <c r="N31" s="18">
         <v>59.671114354829328</v>
       </c>
-      <c r="N31" t="s">
+      <c r="O31" t="s">
         <v>128</v>
       </c>
-      <c r="O31" s="19" t="s">
+      <c r="P31" s="19" t="s">
         <v>171</v>
       </c>
-      <c r="P31" t="s">
+      <c r="Q31" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>153</v>
       </c>
-      <c r="G32" s="6" t="s">
+      <c r="H32" s="6" t="s">
         <v>328</v>
       </c>
-      <c r="L32" s="6" t="s">
+      <c r="M32" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="M32" s="18">
+      <c r="N32" s="18">
         <v>16.802918820320372</v>
       </c>
-      <c r="N32" t="s">
+      <c r="O32" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>153</v>
       </c>
-      <c r="G33" s="6" t="s">
+      <c r="H33" s="6" t="s">
         <v>332</v>
       </c>
-      <c r="L33" s="6" t="s">
+      <c r="M33" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="M33" s="11">
+      <c r="N33" s="11">
         <v>7.4851294970113242</v>
       </c>
-      <c r="N33" t="s">
+      <c r="O33" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>153</v>
       </c>
-      <c r="G34" s="6" t="s">
+      <c r="H34" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="L34" s="6" t="s">
+      <c r="M34" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="M34" s="11">
+      <c r="N34" s="11">
         <v>0.80634576443547301</v>
       </c>
-      <c r="N34" t="s">
+      <c r="O34" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="J36" t="s">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H35" s="6"/>
+      <c r="M35" s="6"/>
+      <c r="N35" s="11"/>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>348</v>
+      </c>
+      <c r="H36" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="M36" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="N36" s="94">
+        <v>10</v>
+      </c>
+      <c r="O36" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>348</v>
+      </c>
+      <c r="H37" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="M37" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="N37" s="94">
+        <v>90</v>
+      </c>
+      <c r="O37" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>349</v>
+      </c>
+      <c r="H38" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="M38" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="N38" s="18">
+        <v>100</v>
+      </c>
+      <c r="O38" s="10" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H39" s="6"/>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="K40" t="s">
         <v>121</v>
       </c>
-      <c r="L36" t="s">
+      <c r="M40" t="s">
         <v>130</v>
       </c>
-      <c r="M36" s="15">
+      <c r="N40" s="15">
         <v>80</v>
       </c>
-      <c r="N36" t="s">
+      <c r="O40" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="J37" t="s">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="K41" t="s">
         <v>122</v>
       </c>
-      <c r="L37" t="s">
+      <c r="M41" t="s">
         <v>130</v>
       </c>
-      <c r="M37" s="15">
+      <c r="N41" s="15">
         <v>10</v>
       </c>
-      <c r="N37" t="s">
+      <c r="O41" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="J38" t="s">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="K42" t="s">
         <v>123</v>
       </c>
-      <c r="L38" t="s">
+      <c r="M42" t="s">
         <v>130</v>
       </c>
-      <c r="M38" s="15">
+      <c r="N42" s="15">
         <v>10</v>
       </c>
-      <c r="N38" t="s">
+      <c r="O42" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="B39" s="1"/>
-      <c r="C39" s="1"/>
-      <c r="D39" s="1"/>
-      <c r="E39" s="1"/>
-      <c r="F39" s="1"/>
-      <c r="G39" s="1"/>
-      <c r="H39" s="1"/>
-      <c r="I39" s="1"/>
-      <c r="J39" s="1"/>
-      <c r="K39" s="1"/>
-      <c r="L39" s="1"/>
-      <c r="M39" s="1"/>
-      <c r="N39" s="1"/>
-      <c r="O39" s="1"/>
-      <c r="P39" s="1"/>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="G40" s="4"/>
-      <c r="L40" s="9" t="s">
+      <c r="B43" s="1"/>
+      <c r="C43" s="1"/>
+      <c r="D43" s="1"/>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
+      <c r="H43" s="1"/>
+      <c r="I43" s="1"/>
+      <c r="J43" s="1"/>
+      <c r="K43" s="1"/>
+      <c r="L43" s="1"/>
+      <c r="M43" s="1"/>
+      <c r="N43" s="1"/>
+      <c r="O43" s="1"/>
+      <c r="P43" s="1"/>
+      <c r="Q43" s="1"/>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H44" s="4"/>
+      <c r="M44" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="M40" s="23">
+      <c r="N44" s="23">
         <v>0</v>
       </c>
-      <c r="N40" s="9"/>
-      <c r="O40" s="9" t="s">
+      <c r="O44" s="9"/>
+      <c r="P44" s="9" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="G41" s="4"/>
-      <c r="M41" s="18"/>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="G42" s="4" t="s">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H45" s="4"/>
+      <c r="N45" s="18"/>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H46" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="K42" t="s">
+      <c r="L46" t="s">
         <v>177</v>
       </c>
-      <c r="L42" t="s">
+      <c r="M46" t="s">
         <v>176</v>
       </c>
-      <c r="M42" s="18">
+      <c r="N46" s="18">
         <f>74100</f>
         <v>74100</v>
       </c>
-      <c r="N42" t="s">
+      <c r="O46" t="s">
         <v>186</v>
       </c>
-      <c r="O42" t="s">
+      <c r="P46" t="s">
         <v>180</v>
       </c>
-      <c r="P42" t="s">
+      <c r="Q46" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="G43" s="4" t="s">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H47" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="K43" t="s">
+      <c r="L47" t="s">
         <v>184</v>
       </c>
-      <c r="L43" t="s">
+      <c r="M47" t="s">
         <v>176</v>
       </c>
-      <c r="M43" s="11">
+      <c r="N47" s="11">
         <f>3.9</f>
         <v>3.9</v>
       </c>
-      <c r="N43" t="s">
+      <c r="O47" t="s">
         <v>186</v>
       </c>
-      <c r="P43" t="s">
+      <c r="Q47" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="G44" s="4" t="s">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H48" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="K44" t="s">
+      <c r="L48" t="s">
         <v>178</v>
       </c>
-      <c r="L44" t="s">
+      <c r="M48" t="s">
         <v>176</v>
       </c>
-      <c r="M44" s="11">
+      <c r="N48" s="11">
         <f>3.9</f>
         <v>3.9</v>
       </c>
-      <c r="N44" t="s">
+      <c r="O48" t="s">
         <v>186</v>
       </c>
-      <c r="P44" t="s">
+      <c r="Q48" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="G45" s="4" t="s">
+    <row r="49" spans="8:17" x14ac:dyDescent="0.25">
+      <c r="H49" s="4" t="s">
         <v>326</v>
       </c>
-      <c r="K45" t="s">
+      <c r="L49" t="s">
         <v>177</v>
       </c>
-      <c r="L45" t="s">
+      <c r="M49" t="s">
         <v>176</v>
       </c>
-      <c r="M45" s="18">
+      <c r="N49" s="18">
         <v>0</v>
       </c>
-      <c r="N45" t="s">
+      <c r="O49" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="G46" s="4" t="s">
+    <row r="50" spans="8:17" x14ac:dyDescent="0.25">
+      <c r="H50" s="4" t="s">
         <v>326</v>
       </c>
-      <c r="K46" t="s">
+      <c r="L50" t="s">
         <v>185</v>
       </c>
-      <c r="L46" t="s">
+      <c r="M50" t="s">
         <v>176</v>
       </c>
-      <c r="M46" s="22">
-        <f t="shared" ref="M46:M47" si="0">M43</f>
+      <c r="N50" s="22">
+        <f t="shared" ref="N50:N51" si="0">N47</f>
         <v>3.9</v>
       </c>
-      <c r="N46" t="s">
+      <c r="O50" t="s">
         <v>186</v>
       </c>
-      <c r="O46" t="s">
+      <c r="P50" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="G47" s="4" t="s">
+    <row r="51" spans="8:17" x14ac:dyDescent="0.25">
+      <c r="H51" s="4" t="s">
         <v>326</v>
       </c>
-      <c r="K47" t="s">
+      <c r="L51" t="s">
         <v>178</v>
       </c>
-      <c r="L47" t="s">
+      <c r="M51" t="s">
         <v>176</v>
       </c>
-      <c r="M47" s="22">
+      <c r="N51" s="22">
         <f t="shared" si="0"/>
         <v>3.9</v>
       </c>
-      <c r="N47" t="s">
+      <c r="O51" t="s">
         <v>186</v>
       </c>
-      <c r="O47" t="s">
+      <c r="P51" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="G48" s="6" t="s">
+    <row r="52" spans="8:17" x14ac:dyDescent="0.25">
+      <c r="H52" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="K48" t="s">
+      <c r="L52" t="s">
         <v>177</v>
       </c>
-      <c r="L48" t="s">
+      <c r="M52" t="s">
         <v>176</v>
       </c>
-      <c r="M48" s="18">
+      <c r="N52" s="18">
         <v>73300</v>
       </c>
-      <c r="N48" t="s">
+      <c r="O52" t="s">
         <v>186</v>
       </c>
-      <c r="O48" t="s">
+      <c r="P52" t="s">
         <v>189</v>
       </c>
-      <c r="P48" t="s">
+      <c r="Q52" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="G49" s="6" t="s">
+    <row r="53" spans="8:17" x14ac:dyDescent="0.25">
+      <c r="H53" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="K49" t="s">
+      <c r="L53" t="s">
         <v>184</v>
       </c>
-      <c r="L49" t="s">
+      <c r="M53" t="s">
         <v>176</v>
       </c>
-      <c r="M49">
+      <c r="N53">
         <v>10</v>
       </c>
-      <c r="N49" t="s">
+      <c r="O53" t="s">
         <v>186</v>
       </c>
-      <c r="P49" t="s">
+      <c r="Q53" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="G50" s="6" t="s">
+    <row r="54" spans="8:17" x14ac:dyDescent="0.25">
+      <c r="H54" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="K50" t="s">
+      <c r="L54" t="s">
         <v>178</v>
       </c>
-      <c r="L50" t="s">
+      <c r="M54" t="s">
         <v>176</v>
       </c>
-      <c r="M50">
+      <c r="N54">
         <v>0.6</v>
       </c>
-      <c r="N50" t="s">
+      <c r="O54" t="s">
         <v>186</v>
       </c>
-      <c r="P50" t="s">
+      <c r="Q54" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="G51" s="6" t="s">
+    <row r="55" spans="8:17" x14ac:dyDescent="0.25">
+      <c r="H55" s="6" t="s">
         <v>333</v>
       </c>
-      <c r="K51" t="s">
+      <c r="L55" t="s">
         <v>177</v>
       </c>
-      <c r="L51" t="s">
+      <c r="M55" t="s">
         <v>176</v>
       </c>
-      <c r="M51" s="18">
+      <c r="N55" s="18">
         <v>56100</v>
       </c>
-      <c r="N51" t="s">
+      <c r="O55" t="s">
         <v>186</v>
       </c>
-      <c r="O51" t="s">
+      <c r="P55" t="s">
         <v>188</v>
       </c>
-      <c r="P51" t="s">
+      <c r="Q55" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="G52" s="6" t="s">
+    <row r="56" spans="8:17" x14ac:dyDescent="0.25">
+      <c r="H56" s="6" t="s">
         <v>333</v>
       </c>
-      <c r="K52" t="s">
+      <c r="L56" t="s">
         <v>184</v>
       </c>
-      <c r="L52" t="s">
+      <c r="M56" t="s">
         <v>176</v>
       </c>
-      <c r="M52">
+      <c r="N56">
         <v>5</v>
       </c>
-      <c r="N52" t="s">
+      <c r="O56" t="s">
         <v>186</v>
       </c>
-      <c r="P52" t="s">
+      <c r="Q56" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="G53" s="6" t="s">
+    <row r="57" spans="8:17" x14ac:dyDescent="0.25">
+      <c r="H57" s="6" t="s">
         <v>333</v>
       </c>
-      <c r="K53" t="s">
+      <c r="L57" t="s">
         <v>178</v>
       </c>
-      <c r="L53" t="s">
+      <c r="M57" t="s">
         <v>176</v>
       </c>
-      <c r="M53">
+      <c r="N57">
         <v>0.1</v>
       </c>
-      <c r="N53" t="s">
+      <c r="O57" t="s">
         <v>186</v>
       </c>
-      <c r="P53" t="s">
+      <c r="Q57" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="G54" s="6" t="s">
+    <row r="58" spans="8:17" x14ac:dyDescent="0.25">
+      <c r="H58" s="6" t="s">
         <v>330</v>
       </c>
-      <c r="K54" t="s">
+      <c r="L58" t="s">
         <v>177</v>
       </c>
-      <c r="L54" t="s">
+      <c r="M58" t="s">
         <v>176</v>
       </c>
-      <c r="M54" s="18">
+      <c r="N58" s="18">
         <v>0</v>
       </c>
-      <c r="N54" t="s">
+      <c r="O58" t="s">
         <v>186</v>
       </c>
-      <c r="O54" t="s">
+      <c r="P58" t="s">
         <v>187</v>
       </c>
-      <c r="P54" t="s">
+      <c r="Q58" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="G55" s="6" t="s">
+    <row r="59" spans="8:17" x14ac:dyDescent="0.25">
+      <c r="H59" s="6" t="s">
         <v>330</v>
       </c>
-      <c r="K55" t="s">
+      <c r="L59" t="s">
         <v>185</v>
       </c>
-      <c r="L55" t="s">
+      <c r="M59" t="s">
         <v>176</v>
       </c>
-      <c r="M55" s="18">
+      <c r="N59" s="18">
         <v>300</v>
       </c>
-      <c r="N55" t="s">
+      <c r="O59" t="s">
         <v>186</v>
       </c>
-      <c r="P55" t="s">
+      <c r="Q59" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="G56" s="6" t="s">
+    <row r="60" spans="8:17" x14ac:dyDescent="0.25">
+      <c r="H60" s="6" t="s">
         <v>330</v>
       </c>
-      <c r="K56" t="s">
+      <c r="L60" t="s">
         <v>178</v>
       </c>
-      <c r="L56" t="s">
+      <c r="M60" t="s">
         <v>176</v>
       </c>
-      <c r="M56" s="18">
+      <c r="N60" s="18">
         <v>4</v>
       </c>
-      <c r="N56" t="s">
+      <c r="O60" t="s">
         <v>186</v>
       </c>
-      <c r="P56" t="s">
+      <c r="Q60" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="G57" s="6" t="s">
+    <row r="61" spans="8:17" x14ac:dyDescent="0.25">
+      <c r="H61" s="6" t="s">
         <v>332</v>
       </c>
-      <c r="L57" t="s">
+      <c r="M61" t="s">
         <v>176</v>
       </c>
-      <c r="M57" s="18">
+      <c r="N61" s="18">
         <v>0</v>
       </c>
-      <c r="N57" t="s">
+      <c r="O61" t="s">
         <v>186</v>
       </c>
-      <c r="O57" s="15"/>
-    </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="G58" s="6" t="s">
+      <c r="P61" s="15"/>
+    </row>
+    <row r="62" spans="8:17" x14ac:dyDescent="0.25">
+      <c r="H62" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="L58" t="s">
+      <c r="M62" t="s">
         <v>176</v>
       </c>
-      <c r="M58" s="18">
+      <c r="N62" s="18">
         <v>0</v>
       </c>
-      <c r="N58" t="s">
+      <c r="O62" t="s">
         <v>186</v>
       </c>
-      <c r="O58" s="15"/>
-    </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="G59" s="4" t="s">
+      <c r="P62" s="15"/>
+    </row>
+    <row r="63" spans="8:17" x14ac:dyDescent="0.25">
+      <c r="H63" s="4" t="s">
         <v>327</v>
       </c>
-      <c r="L59" t="s">
+      <c r="M63" t="s">
         <v>176</v>
       </c>
-      <c r="M59" s="18">
+      <c r="N63" s="18">
         <v>0</v>
       </c>
-      <c r="N59" t="s">
+      <c r="O63" t="s">
         <v>186</v>
       </c>
-      <c r="O59" s="15" t="s">
+      <c r="P63" s="15" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="G60" s="6" t="s">
+    <row r="64" spans="8:17" x14ac:dyDescent="0.25">
+      <c r="H64" s="6" t="s">
         <v>328</v>
       </c>
-      <c r="L60" t="s">
+      <c r="M64" t="s">
         <v>176</v>
       </c>
-      <c r="M60" s="18">
+      <c r="N64" s="18">
         <v>0</v>
       </c>
-      <c r="N60" t="s">
+      <c r="O64" t="s">
         <v>186</v>
       </c>
-      <c r="O60" s="15"/>
-    </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="G61" s="6"/>
-      <c r="M61" s="18"/>
-      <c r="O61" s="15"/>
-    </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A62" s="1" t="s">
+      <c r="P64" s="15"/>
+    </row>
+    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H65" s="6"/>
+      <c r="N65" s="18"/>
+      <c r="P65" s="15"/>
+    </row>
+    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B62" s="1"/>
-      <c r="C62" s="1"/>
-      <c r="D62" s="1"/>
-      <c r="E62" s="1"/>
-      <c r="F62" s="1"/>
-      <c r="G62" s="1"/>
-      <c r="H62" s="1"/>
-      <c r="I62" s="1"/>
-      <c r="J62" s="1"/>
-      <c r="K62" s="1"/>
-      <c r="L62" s="1"/>
-      <c r="M62" s="1"/>
-      <c r="N62" s="1"/>
-      <c r="O62" s="1"/>
-      <c r="P62" s="1"/>
-    </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A63" s="2" t="s">
+      <c r="B66" s="1"/>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="1"/>
+      <c r="K66" s="1"/>
+      <c r="L66" s="1"/>
+      <c r="M66" s="1"/>
+      <c r="N66" s="1"/>
+      <c r="O66" s="1"/>
+      <c r="P66" s="1"/>
+      <c r="Q66" s="1"/>
+    </row>
+    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A67" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B63" s="2"/>
-      <c r="C63" s="2"/>
-      <c r="D63" s="2"/>
-      <c r="E63" s="2"/>
-      <c r="F63" s="2"/>
-      <c r="G63" s="2"/>
-      <c r="H63" s="2"/>
-      <c r="I63" s="2"/>
-      <c r="J63" s="2"/>
-      <c r="K63" s="2"/>
-      <c r="L63" s="3"/>
-      <c r="M63" s="3"/>
-      <c r="N63" s="3"/>
-      <c r="O63" s="3"/>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B64" s="4"/>
-      <c r="C64" s="4"/>
-      <c r="D64" s="4"/>
-      <c r="E64" s="4"/>
-      <c r="F64" s="4"/>
-      <c r="G64" s="4"/>
-      <c r="H64" s="4"/>
-      <c r="I64" s="4"/>
-      <c r="J64" s="4"/>
-      <c r="K64" s="4"/>
-      <c r="L64" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="M64">
-        <v>10800</v>
-      </c>
-      <c r="N64" t="s">
-        <v>11</v>
-      </c>
-      <c r="O64" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="B65" s="4"/>
-      <c r="C65" s="4"/>
-      <c r="D65" s="4"/>
-      <c r="E65" s="4"/>
-      <c r="F65" s="4"/>
-      <c r="G65" s="4"/>
-      <c r="H65" s="4"/>
-      <c r="I65" s="4"/>
-      <c r="J65" s="4"/>
-      <c r="K65" s="4"/>
-      <c r="L65" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="M65">
-        <v>5</v>
-      </c>
-      <c r="N65" t="s">
-        <v>13</v>
-      </c>
-      <c r="O65" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="B66" s="4"/>
-      <c r="C66" s="4"/>
-      <c r="D66" s="4"/>
-      <c r="E66" s="4"/>
-      <c r="F66" s="4"/>
-      <c r="G66" s="4"/>
-      <c r="H66" s="4"/>
-      <c r="I66" s="4"/>
-      <c r="J66" s="4"/>
-      <c r="K66" s="4"/>
-      <c r="L66" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="M66">
-        <v>2</v>
-      </c>
-      <c r="N66" t="s">
-        <v>126</v>
-      </c>
-      <c r="O66" s="7"/>
-    </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="B67" s="4"/>
-      <c r="C67" s="4"/>
-      <c r="D67" s="4"/>
-      <c r="E67" s="4"/>
-      <c r="F67" s="4"/>
-      <c r="G67" s="4"/>
-      <c r="H67" s="4"/>
-      <c r="I67" s="4"/>
-      <c r="J67" s="4"/>
-      <c r="K67" s="4"/>
-      <c r="L67" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="M67">
-        <v>0.2</v>
-      </c>
-      <c r="N67" t="s">
-        <v>15</v>
-      </c>
-      <c r="O67" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="B67" s="2"/>
+      <c r="C67" s="2"/>
+      <c r="D67" s="2"/>
+      <c r="E67" s="2"/>
+      <c r="F67" s="2"/>
+      <c r="G67" s="2"/>
+      <c r="H67" s="2"/>
+      <c r="I67" s="2"/>
+      <c r="J67" s="2"/>
+      <c r="K67" s="2"/>
+      <c r="L67" s="2"/>
+      <c r="M67" s="3"/>
+      <c r="N67" s="3"/>
+      <c r="O67" s="3"/>
+      <c r="P67" s="3"/>
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B68" s="4"/>
       <c r="C68" s="4"/>
       <c r="D68" s="4"/>
@@ -3744,20 +3786,21 @@
       <c r="I68" s="4"/>
       <c r="J68" s="4"/>
       <c r="K68" s="4"/>
-      <c r="L68" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="M68">
-        <v>3.5000000000000003E-2</v>
-      </c>
-      <c r="N68" t="s">
-        <v>17</v>
-      </c>
-      <c r="O68" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="L68" s="4"/>
+      <c r="M68" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="N68">
+        <v>10800</v>
+      </c>
+      <c r="O68" t="s">
+        <v>11</v>
+      </c>
+      <c r="P68" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B69" s="4"/>
       <c r="C69" s="4"/>
       <c r="D69" s="4"/>
@@ -3768,20 +3811,21 @@
       <c r="I69" s="4"/>
       <c r="J69" s="4"/>
       <c r="K69" s="4"/>
-      <c r="L69" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="M69">
-        <v>250</v>
-      </c>
-      <c r="N69" t="s">
-        <v>19</v>
-      </c>
-      <c r="O69" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="L69" s="4"/>
+      <c r="M69" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="N69">
+        <v>5</v>
+      </c>
+      <c r="O69" t="s">
+        <v>13</v>
+      </c>
+      <c r="P69" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B70" s="4"/>
       <c r="C70" s="4"/>
       <c r="D70" s="4"/>
@@ -3792,1273 +3836,1340 @@
       <c r="I70" s="4"/>
       <c r="J70" s="4"/>
       <c r="K70" s="4"/>
-      <c r="L70" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="M70" s="9">
-        <v>1</v>
-      </c>
-      <c r="N70" s="9"/>
-      <c r="O70" s="21" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="71" spans="1:20" ht="18" x14ac:dyDescent="0.35">
+      <c r="L70" s="4"/>
+      <c r="M70" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="N70">
+        <v>2</v>
+      </c>
+      <c r="O70" t="s">
+        <v>126</v>
+      </c>
+      <c r="P70" s="7"/>
+    </row>
+    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B71" s="4"/>
       <c r="C71" s="4"/>
       <c r="D71" s="4"/>
       <c r="E71" s="4"/>
       <c r="F71" s="4"/>
-      <c r="G71" s="4" t="s">
-        <v>252</v>
-      </c>
+      <c r="G71" s="4"/>
       <c r="H71" s="4"/>
       <c r="I71" s="4"/>
       <c r="J71" s="4"/>
       <c r="K71" s="4"/>
-      <c r="L71" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="M71">
-        <v>0.26</v>
-      </c>
-      <c r="O71" s="5" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="72" spans="1:20" ht="18" x14ac:dyDescent="0.35">
+      <c r="L71" s="4"/>
+      <c r="M71" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="N71">
+        <v>0.2</v>
+      </c>
+      <c r="O71" t="s">
+        <v>15</v>
+      </c>
+      <c r="P71" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B72" s="4"/>
       <c r="C72" s="4"/>
       <c r="D72" s="4"/>
       <c r="E72" s="4"/>
       <c r="F72" s="4"/>
-      <c r="G72" s="4" t="s">
-        <v>326</v>
-      </c>
+      <c r="G72" s="4"/>
       <c r="H72" s="4"/>
       <c r="I72" s="4"/>
       <c r="J72" s="4"/>
       <c r="K72" s="4"/>
-      <c r="L72" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="M72">
-        <v>0.26</v>
-      </c>
-      <c r="O72" s="5" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="73" spans="1:20" ht="18" x14ac:dyDescent="0.35">
+      <c r="L72" s="4"/>
+      <c r="M72" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="N72">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="O72" t="s">
+        <v>17</v>
+      </c>
+      <c r="P72" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B73" s="4"/>
       <c r="C73" s="4"/>
       <c r="D73" s="4"/>
       <c r="E73" s="4"/>
       <c r="F73" s="4"/>
-      <c r="G73" s="4" t="s">
-        <v>327</v>
-      </c>
+      <c r="G73" s="4"/>
       <c r="H73" s="4"/>
       <c r="I73" s="4"/>
       <c r="J73" s="4"/>
       <c r="K73" s="4"/>
-      <c r="L73" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="M73">
-        <v>0.45</v>
-      </c>
-      <c r="O73" s="5" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="74" spans="1:20" ht="18" x14ac:dyDescent="0.35">
+      <c r="L73" s="4"/>
+      <c r="M73" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N73">
+        <v>250</v>
+      </c>
+      <c r="O73" t="s">
+        <v>19</v>
+      </c>
+      <c r="P73" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B74" s="4"/>
       <c r="C74" s="4"/>
       <c r="D74" s="4"/>
       <c r="E74" s="4"/>
       <c r="F74" s="4"/>
-      <c r="G74" s="6" t="s">
-        <v>328</v>
-      </c>
-      <c r="H74" s="6"/>
-      <c r="I74" s="6"/>
-      <c r="J74" s="6"/>
-      <c r="K74" s="6"/>
-      <c r="L74" s="6" t="s">
+      <c r="G74" s="4"/>
+      <c r="H74" s="4"/>
+      <c r="I74" s="4"/>
+      <c r="J74" s="4"/>
+      <c r="K74" s="4"/>
+      <c r="L74" s="4"/>
+      <c r="M74" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="M74">
-        <v>0.76</v>
-      </c>
-      <c r="O74" s="5" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="N74" s="9">
+        <v>1</v>
+      </c>
+      <c r="O74" s="9"/>
+      <c r="P74" s="21" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="75" spans="1:17" ht="18" x14ac:dyDescent="0.35">
       <c r="B75" s="4"/>
       <c r="C75" s="4"/>
       <c r="D75" s="4"/>
       <c r="E75" s="4"/>
       <c r="F75" s="4"/>
       <c r="G75" s="4"/>
-      <c r="H75" s="4"/>
+      <c r="H75" s="4" t="s">
+        <v>252</v>
+      </c>
       <c r="I75" s="4"/>
       <c r="J75" s="4"/>
       <c r="K75" s="4"/>
-      <c r="L75" s="6" t="s">
+      <c r="L75" s="4"/>
+      <c r="M75" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="N75">
+        <v>0.26</v>
+      </c>
+      <c r="P75" s="5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="76" spans="1:17" ht="18" x14ac:dyDescent="0.35">
+      <c r="B76" s="4"/>
+      <c r="C76" s="4"/>
+      <c r="D76" s="4"/>
+      <c r="E76" s="4"/>
+      <c r="F76" s="4"/>
+      <c r="G76" s="4"/>
+      <c r="H76" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="I76" s="4"/>
+      <c r="J76" s="4"/>
+      <c r="K76" s="4"/>
+      <c r="L76" s="4"/>
+      <c r="M76" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="N76">
+        <v>0.26</v>
+      </c>
+      <c r="P76" s="5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="77" spans="1:17" ht="18" x14ac:dyDescent="0.35">
+      <c r="B77" s="4"/>
+      <c r="C77" s="4"/>
+      <c r="D77" s="4"/>
+      <c r="E77" s="4"/>
+      <c r="F77" s="4"/>
+      <c r="G77" s="4"/>
+      <c r="H77" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="I77" s="4"/>
+      <c r="J77" s="4"/>
+      <c r="K77" s="4"/>
+      <c r="L77" s="4"/>
+      <c r="M77" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="N77">
+        <v>0.45</v>
+      </c>
+      <c r="P77" s="5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="78" spans="1:17" ht="18" x14ac:dyDescent="0.35">
+      <c r="B78" s="4"/>
+      <c r="C78" s="4"/>
+      <c r="D78" s="4"/>
+      <c r="E78" s="4"/>
+      <c r="F78" s="4"/>
+      <c r="G78" s="4"/>
+      <c r="H78" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="I78" s="6"/>
+      <c r="J78" s="6"/>
+      <c r="K78" s="6"/>
+      <c r="L78" s="6"/>
+      <c r="M78" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="N78">
+        <v>0.76</v>
+      </c>
+      <c r="P78" s="5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B79" s="4"/>
+      <c r="C79" s="4"/>
+      <c r="D79" s="4"/>
+      <c r="E79" s="4"/>
+      <c r="F79" s="4"/>
+      <c r="G79" s="4"/>
+      <c r="H79" s="4"/>
+      <c r="I79" s="4"/>
+      <c r="J79" s="4"/>
+      <c r="K79" s="4"/>
+      <c r="L79" s="4"/>
+      <c r="M79" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="M75">
+      <c r="N79">
         <v>4</v>
       </c>
-      <c r="N75" t="s">
+      <c r="O79" t="s">
         <v>21</v>
       </c>
-      <c r="O75" s="7" t="s">
+      <c r="P79" s="7" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A77" s="2" t="s">
+    <row r="81" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A81" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B77" s="2"/>
-      <c r="C77" s="2"/>
-      <c r="D77" s="2"/>
-      <c r="E77" s="2"/>
-      <c r="F77" s="2"/>
-      <c r="G77" s="2"/>
-      <c r="H77" s="2"/>
-      <c r="I77" s="2"/>
-      <c r="J77" s="2"/>
-      <c r="K77" s="2"/>
-      <c r="L77" s="2"/>
-      <c r="M77" s="2"/>
-      <c r="N77" s="2"/>
-      <c r="O77" s="2"/>
-      <c r="P77" s="2"/>
-    </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="L78" t="s">
+      <c r="B81" s="2"/>
+      <c r="C81" s="2"/>
+      <c r="D81" s="2"/>
+      <c r="E81" s="2"/>
+      <c r="F81" s="2"/>
+      <c r="G81" s="2"/>
+      <c r="H81" s="2"/>
+      <c r="I81" s="2"/>
+      <c r="J81" s="2"/>
+      <c r="K81" s="2"/>
+      <c r="L81" s="2"/>
+      <c r="M81" s="2"/>
+      <c r="N81" s="2"/>
+      <c r="O81" s="2"/>
+      <c r="P81" s="2"/>
+      <c r="Q81" s="2"/>
+    </row>
+    <row r="82" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="M82" t="s">
         <v>127</v>
       </c>
-      <c r="M78">
+      <c r="N82">
         <v>4</v>
       </c>
-      <c r="N78" t="s">
+      <c r="O82" t="s">
         <v>29</v>
       </c>
-      <c r="O78" t="s">
+      <c r="P82" t="s">
         <v>28</v>
       </c>
-      <c r="T78" s="6"/>
-    </row>
-    <row r="79" spans="1:20" ht="18" x14ac:dyDescent="0.35">
-      <c r="L79" t="s">
+      <c r="U82" s="6"/>
+    </row>
+    <row r="83" spans="1:21" ht="18" x14ac:dyDescent="0.35">
+      <c r="M83" t="s">
         <v>45</v>
       </c>
-      <c r="M79">
+      <c r="N83">
         <v>0.9</v>
       </c>
-      <c r="O79" t="s">
+      <c r="P83" t="s">
         <v>30</v>
       </c>
-      <c r="T79" s="6"/>
-    </row>
-    <row r="80" spans="1:20" ht="18" x14ac:dyDescent="0.35">
-      <c r="L80" t="s">
+      <c r="U83" s="6"/>
+    </row>
+    <row r="84" spans="1:21" ht="18" x14ac:dyDescent="0.35">
+      <c r="M84" t="s">
         <v>38</v>
       </c>
-      <c r="M80">
+      <c r="N84">
         <v>1.2250000000000001</v>
       </c>
-      <c r="N80" t="s">
+      <c r="O84" t="s">
         <v>32</v>
       </c>
-      <c r="O80" t="s">
+      <c r="P84" t="s">
         <v>31</v>
       </c>
-      <c r="T80" s="6"/>
-    </row>
-    <row r="81" spans="1:20" ht="18" x14ac:dyDescent="0.35">
-      <c r="L81" t="s">
+      <c r="U84" s="6"/>
+    </row>
+    <row r="85" spans="1:21" ht="18" x14ac:dyDescent="0.35">
+      <c r="M85" t="s">
         <v>39</v>
       </c>
-      <c r="M81">
+      <c r="N85">
         <v>0.1</v>
       </c>
-      <c r="O81" t="s">
+      <c r="P85" t="s">
         <v>33</v>
       </c>
-      <c r="T81" s="6"/>
-    </row>
-    <row r="82" spans="1:20" ht="18" x14ac:dyDescent="0.35">
-      <c r="L82" t="s">
+      <c r="U85" s="6"/>
+    </row>
+    <row r="86" spans="1:21" ht="18" x14ac:dyDescent="0.35">
+      <c r="M86" t="s">
         <v>40</v>
       </c>
-      <c r="M82">
+      <c r="N86">
         <v>0.01</v>
       </c>
-      <c r="O82" t="s">
+      <c r="P86" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="83" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="L83" t="s">
+    <row r="87" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="M87" t="s">
         <v>41</v>
       </c>
-      <c r="M83">
+      <c r="N87">
         <v>0.2</v>
       </c>
-      <c r="O83" t="s">
+      <c r="P87" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="84" spans="1:20" ht="18" x14ac:dyDescent="0.35">
-      <c r="L84" t="s">
+    <row r="88" spans="1:21" ht="18" x14ac:dyDescent="0.35">
+      <c r="M88" t="s">
         <v>42</v>
       </c>
-      <c r="M84">
+      <c r="N88">
         <v>0.8</v>
       </c>
-      <c r="O84" t="s">
+      <c r="P88" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="85" spans="1:20" ht="18" x14ac:dyDescent="0.35">
-      <c r="L85" t="s">
+    <row r="89" spans="1:21" ht="18" x14ac:dyDescent="0.35">
+      <c r="M89" t="s">
         <v>43</v>
       </c>
-      <c r="M85">
+      <c r="N89">
         <v>55</v>
       </c>
-      <c r="O85" t="s">
+      <c r="P89" t="s">
         <v>37</v>
       </c>
-      <c r="S85" s="4"/>
-    </row>
-    <row r="87" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A87" s="1" t="s">
+      <c r="T89" s="4"/>
+    </row>
+    <row r="91" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A91" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B87" s="8"/>
-      <c r="C87" s="8"/>
-      <c r="D87" s="8"/>
-      <c r="E87" s="8"/>
-      <c r="F87" s="8"/>
-      <c r="G87" s="8"/>
-      <c r="H87" s="8"/>
-      <c r="I87" s="8"/>
-      <c r="J87" s="8"/>
-      <c r="K87" s="8"/>
-      <c r="L87" s="8"/>
-      <c r="M87" s="8"/>
-      <c r="N87" s="8"/>
-      <c r="O87" s="8"/>
-      <c r="P87" s="8"/>
-    </row>
-    <row r="88" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="L88" s="9" t="s">
+      <c r="B91" s="8"/>
+      <c r="C91" s="8"/>
+      <c r="D91" s="8"/>
+      <c r="E91" s="8"/>
+      <c r="F91" s="8"/>
+      <c r="G91" s="8"/>
+      <c r="H91" s="8"/>
+      <c r="I91" s="8"/>
+      <c r="J91" s="8"/>
+      <c r="K91" s="8"/>
+      <c r="L91" s="8"/>
+      <c r="M91" s="8"/>
+      <c r="N91" s="8"/>
+      <c r="O91" s="8"/>
+      <c r="P91" s="8"/>
+      <c r="Q91" s="8"/>
+    </row>
+    <row r="92" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="M92" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="M88" s="9">
+      <c r="N92" s="9">
         <v>0</v>
       </c>
-      <c r="N88" s="9" t="s">
+      <c r="O92" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="O88" s="9"/>
-    </row>
-    <row r="89" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="L89" s="9" t="s">
+      <c r="P92" s="9"/>
+    </row>
+    <row r="93" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="M93" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="M89" s="9">
+      <c r="N93" s="9">
         <v>0</v>
       </c>
-      <c r="N89" s="9" t="s">
+      <c r="O93" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="O89" s="9"/>
-    </row>
-    <row r="90" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="L90" s="9" t="s">
+      <c r="P93" s="9"/>
+    </row>
+    <row r="94" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="M94" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="M90" s="9">
+      <c r="N94" s="9">
         <v>0</v>
       </c>
-      <c r="N90" s="9" t="s">
+      <c r="O94" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="O90" s="9"/>
-    </row>
-    <row r="91" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="L91" s="9" t="s">
+      <c r="P94" s="9"/>
+    </row>
+    <row r="95" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="M95" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="M91" s="9">
+      <c r="N95" s="9">
         <v>0</v>
       </c>
-      <c r="N91" s="9" t="s">
+      <c r="O95" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="O91" s="9"/>
-    </row>
-    <row r="92" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="L92" s="9" t="s">
+      <c r="P95" s="9"/>
+    </row>
+    <row r="96" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="M96" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="M92" s="9">
+      <c r="N96" s="9">
         <v>0</v>
       </c>
-      <c r="N92" s="9" t="s">
+      <c r="O96" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="O92" s="9"/>
-    </row>
-    <row r="93" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="L93" s="9" t="s">
+      <c r="P96" s="9"/>
+    </row>
+    <row r="97" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="M97" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="M93" s="9">
+      <c r="N97" s="9">
         <v>1</v>
       </c>
-      <c r="N93" s="9" t="s">
+      <c r="O97" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="O93" s="9" t="s">
+      <c r="P97" s="9" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="94" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="L94" s="9" t="s">
+    <row r="98" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="M98" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="M94" s="9">
+      <c r="N98" s="9">
         <v>0</v>
       </c>
-      <c r="N94" s="9" t="s">
+      <c r="O98" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="O94" s="9"/>
-    </row>
-    <row r="95" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="L95" s="9" t="s">
+      <c r="P98" s="9"/>
+    </row>
+    <row r="99" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="M99" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="M95" s="9">
+      <c r="N99" s="9">
         <v>0</v>
       </c>
-      <c r="N95" s="9" t="s">
+      <c r="O99" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="O95" s="9"/>
-    </row>
-    <row r="96" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="L96" s="9" t="s">
+      <c r="P99" s="9"/>
+    </row>
+    <row r="100" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="M100" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="M96" s="9">
+      <c r="N100" s="9">
         <v>0</v>
       </c>
-      <c r="N96" s="9" t="s">
+      <c r="O100" s="9" t="s">
         <v>334</v>
       </c>
-      <c r="O96" s="9"/>
-    </row>
-    <row r="97" spans="8:16" x14ac:dyDescent="0.25">
-      <c r="L97" s="9" t="s">
+      <c r="P100" s="9"/>
+    </row>
+    <row r="101" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="M101" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="M97" s="9">
+      <c r="N101" s="9">
         <v>0</v>
       </c>
-      <c r="N97" s="9" t="s">
+      <c r="O101" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="O97" s="9"/>
-    </row>
-    <row r="98" spans="8:16" x14ac:dyDescent="0.25">
-      <c r="L98" s="9"/>
-      <c r="M98" s="9"/>
-      <c r="N98" s="9"/>
-      <c r="O98" s="9"/>
-    </row>
-    <row r="99" spans="8:16" x14ac:dyDescent="0.25">
-      <c r="H99" t="s">
+      <c r="P101" s="9"/>
+    </row>
+    <row r="102" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="M102" s="9"/>
+      <c r="N102" s="9"/>
+      <c r="O102" s="9"/>
+      <c r="P102" s="9"/>
+    </row>
+    <row r="103" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="I103" t="s">
         <v>60</v>
       </c>
-      <c r="L99" s="10" t="s">
+      <c r="M103" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="M99" s="10">
+      <c r="N103" s="10">
         <v>364</v>
       </c>
-      <c r="N99" s="10"/>
-      <c r="O99" s="10" t="s">
+      <c r="O103" s="10"/>
+      <c r="P103" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="P99" s="10"/>
-    </row>
-    <row r="100" spans="8:16" x14ac:dyDescent="0.25">
-      <c r="H100" t="s">
+      <c r="Q103" s="10"/>
+    </row>
+    <row r="104" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="I104" t="s">
         <v>60</v>
       </c>
-      <c r="L100" s="10" t="s">
+      <c r="M104" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="M100" s="10">
+      <c r="N104" s="10">
         <v>18.8</v>
       </c>
-      <c r="N100" s="10"/>
-      <c r="O100" s="10"/>
-      <c r="P100" s="10"/>
-    </row>
-    <row r="101" spans="8:16" x14ac:dyDescent="0.25">
-      <c r="H101" t="s">
-        <v>60</v>
-      </c>
-      <c r="L101" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="M101" s="10">
-        <v>0</v>
-      </c>
-      <c r="N101" s="10"/>
-      <c r="O101" s="10"/>
-      <c r="P101" s="10"/>
-    </row>
-    <row r="102" spans="8:16" x14ac:dyDescent="0.25">
-      <c r="H102" t="s">
-        <v>60</v>
-      </c>
-      <c r="L102" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="M102" s="10">
-        <v>10</v>
-      </c>
-      <c r="N102" s="10"/>
-      <c r="O102" s="10"/>
-      <c r="P102" s="10"/>
-    </row>
-    <row r="103" spans="8:16" x14ac:dyDescent="0.25">
-      <c r="H103" t="s">
-        <v>60</v>
-      </c>
-      <c r="I103" t="s">
-        <v>74</v>
-      </c>
-      <c r="L103" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="M103" s="12">
-        <v>1</v>
-      </c>
-      <c r="N103" s="10"/>
-      <c r="O103" s="10"/>
-      <c r="P103" s="10"/>
-    </row>
-    <row r="104" spans="8:16" x14ac:dyDescent="0.25">
-      <c r="H104" t="s">
-        <v>60</v>
-      </c>
-      <c r="I104" t="s">
-        <v>73</v>
-      </c>
-      <c r="L104" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="M104" s="10">
-        <v>0.88</v>
-      </c>
-      <c r="N104" s="10"/>
       <c r="O104" s="10"/>
       <c r="P104" s="10"/>
-    </row>
-    <row r="105" spans="8:16" x14ac:dyDescent="0.25">
-      <c r="H105" t="s">
+      <c r="Q104" s="10"/>
+    </row>
+    <row r="105" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="I105" t="s">
         <v>60</v>
       </c>
-      <c r="I105" t="s">
-        <v>72</v>
-      </c>
-      <c r="L105" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="M105" s="10">
-        <v>0.78</v>
-      </c>
-      <c r="N105" s="10"/>
+      <c r="M105" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="N105" s="10">
+        <v>0</v>
+      </c>
       <c r="O105" s="10"/>
       <c r="P105" s="10"/>
-    </row>
-    <row r="106" spans="8:16" x14ac:dyDescent="0.25">
-      <c r="L106" s="10"/>
-      <c r="M106" s="10"/>
-      <c r="N106" s="10"/>
+      <c r="Q105" s="10"/>
+    </row>
+    <row r="106" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="I106" t="s">
+        <v>60</v>
+      </c>
+      <c r="M106" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="N106" s="10">
+        <v>10</v>
+      </c>
       <c r="O106" s="10"/>
       <c r="P106" s="10"/>
-    </row>
-    <row r="107" spans="8:16" x14ac:dyDescent="0.25">
-      <c r="H107" t="s">
-        <v>63</v>
-      </c>
-      <c r="L107" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="M107" s="10">
-        <v>652</v>
-      </c>
-      <c r="N107" s="10"/>
-      <c r="O107" s="10" t="s">
-        <v>82</v>
-      </c>
+      <c r="Q106" s="10"/>
+    </row>
+    <row r="107" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="I107" t="s">
+        <v>60</v>
+      </c>
+      <c r="J107" t="s">
+        <v>74</v>
+      </c>
+      <c r="M107" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="N107" s="12">
+        <v>1</v>
+      </c>
+      <c r="O107" s="10"/>
       <c r="P107" s="10"/>
-    </row>
-    <row r="108" spans="8:16" x14ac:dyDescent="0.25">
-      <c r="H108" t="s">
-        <v>63</v>
-      </c>
-      <c r="L108" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="M108" s="10">
-        <v>0</v>
-      </c>
-      <c r="N108" s="10"/>
+      <c r="Q107" s="10"/>
+    </row>
+    <row r="108" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="I108" t="s">
+        <v>60</v>
+      </c>
+      <c r="J108" t="s">
+        <v>73</v>
+      </c>
+      <c r="M108" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="N108" s="10">
+        <v>0.88</v>
+      </c>
       <c r="O108" s="10"/>
       <c r="P108" s="10"/>
-    </row>
-    <row r="109" spans="8:16" x14ac:dyDescent="0.25">
-      <c r="H109" t="s">
-        <v>63</v>
-      </c>
-      <c r="L109" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="M109" s="10">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="N109" s="10"/>
+      <c r="Q108" s="10"/>
+    </row>
+    <row r="109" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="I109" t="s">
+        <v>60</v>
+      </c>
+      <c r="J109" t="s">
+        <v>72</v>
+      </c>
+      <c r="M109" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="N109" s="10">
+        <v>0.78</v>
+      </c>
       <c r="O109" s="10"/>
       <c r="P109" s="10"/>
-    </row>
-    <row r="110" spans="8:16" x14ac:dyDescent="0.25">
-      <c r="H110" t="s">
-        <v>63</v>
-      </c>
-      <c r="L110" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="M110" s="10">
-        <v>20</v>
-      </c>
+      <c r="Q109" s="10"/>
+    </row>
+    <row r="110" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="M110" s="10"/>
       <c r="N110" s="10"/>
       <c r="O110" s="10"/>
       <c r="P110" s="10"/>
-    </row>
-    <row r="111" spans="8:16" x14ac:dyDescent="0.25">
-      <c r="H111" t="s">
+      <c r="Q110" s="10"/>
+    </row>
+    <row r="111" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="I111" t="s">
         <v>63</v>
       </c>
-      <c r="I111" t="s">
-        <v>74</v>
-      </c>
-      <c r="L111" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="M111" s="12">
-        <v>1</v>
-      </c>
-      <c r="N111" s="10"/>
+      <c r="M111" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="N111" s="10">
+        <v>652</v>
+      </c>
       <c r="O111" s="10"/>
-      <c r="P111" s="10"/>
-    </row>
-    <row r="112" spans="8:16" x14ac:dyDescent="0.25">
-      <c r="H112" t="s">
+      <c r="P111" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q111" s="10"/>
+    </row>
+    <row r="112" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="I112" t="s">
         <v>63</v>
       </c>
-      <c r="I112" t="s">
-        <v>73</v>
-      </c>
-      <c r="L112" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="M112" s="12">
-        <v>0.7</v>
-      </c>
-      <c r="N112" s="10"/>
+      <c r="M112" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="N112" s="10">
+        <v>0</v>
+      </c>
       <c r="O112" s="10"/>
       <c r="P112" s="10"/>
-    </row>
-    <row r="113" spans="8:16" x14ac:dyDescent="0.25">
-      <c r="H113" t="s">
+      <c r="Q112" s="10"/>
+    </row>
+    <row r="113" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="I113" t="s">
         <v>63</v>
       </c>
-      <c r="I113" t="s">
-        <v>72</v>
-      </c>
-      <c r="L113" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="M113" s="10">
-        <v>0.45</v>
-      </c>
-      <c r="N113" s="10"/>
+      <c r="M113" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="N113" s="10">
+        <v>5.0999999999999996</v>
+      </c>
       <c r="O113" s="10"/>
       <c r="P113" s="10"/>
-    </row>
-    <row r="114" spans="8:16" x14ac:dyDescent="0.25">
-      <c r="L114" s="10"/>
-      <c r="M114" s="10"/>
-      <c r="N114" s="10"/>
+      <c r="Q113" s="10"/>
+    </row>
+    <row r="114" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="I114" t="s">
+        <v>63</v>
+      </c>
+      <c r="M114" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="N114" s="10">
+        <v>20</v>
+      </c>
       <c r="O114" s="10"/>
       <c r="P114" s="10"/>
-    </row>
-    <row r="115" spans="8:16" x14ac:dyDescent="0.25">
-      <c r="H115" t="s">
-        <v>62</v>
-      </c>
-      <c r="L115" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="M115" s="10">
-        <v>46</v>
-      </c>
-      <c r="N115" s="10"/>
-      <c r="O115" s="10" t="s">
-        <v>83</v>
-      </c>
+      <c r="Q114" s="10"/>
+    </row>
+    <row r="115" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="I115" t="s">
+        <v>63</v>
+      </c>
+      <c r="J115" t="s">
+        <v>74</v>
+      </c>
+      <c r="M115" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="N115" s="12">
+        <v>1</v>
+      </c>
+      <c r="O115" s="10"/>
       <c r="P115" s="10"/>
-    </row>
-    <row r="116" spans="8:16" x14ac:dyDescent="0.25">
-      <c r="H116" t="s">
-        <v>62</v>
-      </c>
-      <c r="L116" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="M116" s="10">
-        <v>2.8</v>
-      </c>
-      <c r="N116" s="10"/>
+      <c r="Q115" s="10"/>
+    </row>
+    <row r="116" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="I116" t="s">
+        <v>63</v>
+      </c>
+      <c r="J116" t="s">
+        <v>73</v>
+      </c>
+      <c r="M116" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="N116" s="12">
+        <v>0.7</v>
+      </c>
       <c r="O116" s="10"/>
       <c r="P116" s="10"/>
-    </row>
-    <row r="117" spans="8:16" x14ac:dyDescent="0.25">
-      <c r="H117" t="s">
-        <v>62</v>
-      </c>
-      <c r="L117" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="M117" s="10">
-        <v>0</v>
-      </c>
-      <c r="N117" s="10"/>
+      <c r="Q116" s="10"/>
+    </row>
+    <row r="117" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="I117" t="s">
+        <v>63</v>
+      </c>
+      <c r="J117" t="s">
+        <v>72</v>
+      </c>
+      <c r="M117" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="N117" s="10">
+        <v>0.45</v>
+      </c>
       <c r="O117" s="10"/>
       <c r="P117" s="10"/>
-    </row>
-    <row r="118" spans="8:16" x14ac:dyDescent="0.25">
-      <c r="H118" t="s">
-        <v>62</v>
-      </c>
-      <c r="L118" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="M118" s="10">
-        <v>5</v>
-      </c>
+      <c r="Q117" s="10"/>
+    </row>
+    <row r="118" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="M118" s="10"/>
       <c r="N118" s="10"/>
       <c r="O118" s="10"/>
       <c r="P118" s="10"/>
-    </row>
-    <row r="119" spans="8:16" x14ac:dyDescent="0.25">
-      <c r="H119" t="s">
+      <c r="Q118" s="10"/>
+    </row>
+    <row r="119" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="I119" t="s">
         <v>62</v>
       </c>
-      <c r="I119" t="s">
-        <v>74</v>
-      </c>
-      <c r="L119" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="M119" s="12">
-        <v>1</v>
-      </c>
-      <c r="N119" s="10"/>
+      <c r="M119" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="N119" s="10">
+        <v>46</v>
+      </c>
       <c r="O119" s="10"/>
-      <c r="P119" s="10"/>
-    </row>
-    <row r="120" spans="8:16" x14ac:dyDescent="0.25">
-      <c r="H120" t="s">
+      <c r="P119" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q119" s="10"/>
+    </row>
+    <row r="120" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="I120" t="s">
         <v>62</v>
       </c>
-      <c r="I120" t="s">
-        <v>73</v>
-      </c>
-      <c r="L120" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="M120" s="10">
-        <v>0.85</v>
-      </c>
-      <c r="N120" s="10"/>
+      <c r="M120" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="N120" s="10">
+        <v>2.8</v>
+      </c>
       <c r="O120" s="10"/>
       <c r="P120" s="10"/>
-    </row>
-    <row r="121" spans="8:16" x14ac:dyDescent="0.25">
-      <c r="H121" t="s">
+      <c r="Q120" s="10"/>
+    </row>
+    <row r="121" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="I121" t="s">
         <v>62</v>
       </c>
-      <c r="I121" t="s">
-        <v>72</v>
-      </c>
-      <c r="L121" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="M121" s="10">
-        <v>0.65</v>
-      </c>
-      <c r="N121" s="10"/>
+      <c r="M121" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="N121" s="10">
+        <v>0</v>
+      </c>
       <c r="O121" s="10"/>
       <c r="P121" s="10"/>
-    </row>
-    <row r="122" spans="8:16" x14ac:dyDescent="0.25">
-      <c r="L122" s="10"/>
-      <c r="M122" s="10"/>
-      <c r="N122" s="10"/>
+      <c r="Q121" s="10"/>
+    </row>
+    <row r="122" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="I122" t="s">
+        <v>62</v>
+      </c>
+      <c r="M122" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="N122" s="10">
+        <v>5</v>
+      </c>
       <c r="O122" s="10"/>
       <c r="P122" s="10"/>
-    </row>
-    <row r="123" spans="8:16" x14ac:dyDescent="0.25">
-      <c r="H123" t="s">
-        <v>65</v>
-      </c>
-      <c r="L123" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="M123" s="12">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="N123" s="10"/>
-      <c r="O123" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="P123" s="4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="124" spans="8:16" x14ac:dyDescent="0.25">
-      <c r="H124" t="s">
-        <v>66</v>
-      </c>
-      <c r="L124" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="M124" s="12">
-        <v>7.1</v>
-      </c>
-      <c r="N124" s="10"/>
-      <c r="O124" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="P124" s="4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="125" spans="8:16" x14ac:dyDescent="0.25">
-      <c r="L125" s="10"/>
-      <c r="M125" s="10"/>
-      <c r="N125" s="10"/>
+      <c r="Q122" s="10"/>
+    </row>
+    <row r="123" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="I123" t="s">
+        <v>62</v>
+      </c>
+      <c r="J123" t="s">
+        <v>74</v>
+      </c>
+      <c r="M123" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="N123" s="12">
+        <v>1</v>
+      </c>
+      <c r="O123" s="10"/>
+      <c r="P123" s="10"/>
+      <c r="Q123" s="10"/>
+    </row>
+    <row r="124" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="I124" t="s">
+        <v>62</v>
+      </c>
+      <c r="J124" t="s">
+        <v>73</v>
+      </c>
+      <c r="M124" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="N124" s="10">
+        <v>0.85</v>
+      </c>
+      <c r="O124" s="10"/>
+      <c r="P124" s="10"/>
+      <c r="Q124" s="10"/>
+    </row>
+    <row r="125" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="I125" t="s">
+        <v>62</v>
+      </c>
+      <c r="J125" t="s">
+        <v>72</v>
+      </c>
+      <c r="M125" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="N125" s="10">
+        <v>0.65</v>
+      </c>
       <c r="O125" s="10"/>
       <c r="P125" s="10"/>
-    </row>
-    <row r="126" spans="8:16" x14ac:dyDescent="0.25">
-      <c r="H126" t="s">
+      <c r="Q125" s="10"/>
+    </row>
+    <row r="126" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="M126" s="10"/>
+      <c r="N126" s="10"/>
+      <c r="O126" s="10"/>
+      <c r="P126" s="10"/>
+      <c r="Q126" s="10"/>
+    </row>
+    <row r="127" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="I127" t="s">
+        <v>65</v>
+      </c>
+      <c r="M127" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="N127" s="12">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="O127" s="10"/>
+      <c r="P127" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q127" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="128" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="I128" t="s">
+        <v>66</v>
+      </c>
+      <c r="M128" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="N128" s="12">
+        <v>7.1</v>
+      </c>
+      <c r="O128" s="10"/>
+      <c r="P128" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q128" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="129" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="M129" s="10"/>
+      <c r="N129" s="10"/>
+      <c r="O129" s="10"/>
+      <c r="P129" s="10"/>
+      <c r="Q129" s="10"/>
+    </row>
+    <row r="130" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="I130" t="s">
         <v>61</v>
       </c>
-      <c r="L126" s="10" t="s">
+      <c r="M130" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="M126" s="12">
+      <c r="N130" s="12">
         <v>3.7353333333333332</v>
       </c>
-      <c r="N126" s="10"/>
-      <c r="O126" s="10" t="s">
+      <c r="O130" s="10"/>
+      <c r="P130" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="P126" s="6" t="s">
+      <c r="Q130" s="6" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="127" spans="8:16" x14ac:dyDescent="0.25">
-      <c r="H127" t="s">
+    <row r="131" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="I131" t="s">
         <v>64</v>
       </c>
-      <c r="L127" s="10" t="s">
+      <c r="M131" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="M127" s="11">
+      <c r="N131" s="11">
         <v>17.096931944444446</v>
       </c>
-      <c r="N127" s="10"/>
-      <c r="O127" s="6" t="s">
+      <c r="O131" s="10"/>
+      <c r="P131" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="P127" s="4" t="s">
+      <c r="Q131" s="4" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="128" spans="8:16" x14ac:dyDescent="0.25">
-      <c r="H128" t="s">
+    <row r="132" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="I132" t="s">
         <v>67</v>
       </c>
-      <c r="L128" s="10" t="s">
+      <c r="M132" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="M128" s="12">
+      <c r="N132" s="12">
         <v>1.2451111111111113</v>
       </c>
-      <c r="N128" s="10"/>
-      <c r="O128" s="6" t="s">
+      <c r="O132" s="10"/>
+      <c r="P132" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="P128" s="10" t="s">
+      <c r="Q132" s="10" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="129" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="H129" t="s">
+    <row r="133" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="I133" t="s">
         <v>68</v>
       </c>
-      <c r="L129" s="10" t="s">
+      <c r="M133" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="M129" s="12">
+      <c r="N133" s="12">
         <v>3.1127777777777781</v>
       </c>
-      <c r="N129" s="10"/>
-      <c r="O129" s="6" t="s">
+      <c r="O133" s="10"/>
+      <c r="P133" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="P129" s="10" t="s">
+      <c r="Q133" s="10" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="130" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="H130" t="s">
+    <row r="134" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="I134" t="s">
         <v>97</v>
       </c>
-      <c r="L130" s="10" t="s">
+      <c r="M134" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="M130" s="12">
+      <c r="N134" s="12">
         <v>4.6691666666666665</v>
       </c>
-      <c r="N130" s="10"/>
-      <c r="O130" s="4" t="s">
+      <c r="O134" s="10"/>
+      <c r="P134" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="P130" s="10" t="s">
+      <c r="Q134" s="10" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="131" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="H131" t="s">
+    <row r="135" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="I135" t="s">
         <v>69</v>
       </c>
-      <c r="L131" s="10" t="s">
+      <c r="M135" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="M131" s="12">
+      <c r="N135" s="12">
         <v>3.1127777777777781</v>
       </c>
-      <c r="N131" s="10"/>
-      <c r="O131" s="4" t="s">
+      <c r="O135" s="10"/>
+      <c r="P135" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="P131" s="6" t="s">
+      <c r="Q135" s="6" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="132" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="H132" t="s">
+    <row r="136" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="I136" t="s">
         <v>70</v>
       </c>
-      <c r="L132" s="10" t="s">
+      <c r="M136" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="M132" s="11">
+      <c r="N136" s="11">
         <v>11.828555555555555</v>
       </c>
-      <c r="N132" s="10"/>
-      <c r="O132" s="4" t="s">
+      <c r="O136" s="10"/>
+      <c r="P136" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="P132" s="10" t="s">
+      <c r="Q136" s="10" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="133" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="H133" t="s">
+    <row r="137" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="I137" t="s">
         <v>100</v>
       </c>
-      <c r="L133" s="10" t="s">
+      <c r="M137" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="M133" s="11">
+      <c r="N137" s="11">
         <v>26.302972222222223</v>
       </c>
-      <c r="N133" s="10"/>
-      <c r="O133" s="6" t="s">
+      <c r="O137" s="10"/>
+      <c r="P137" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="P133" s="10" t="s">
+      <c r="Q137" s="10" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="134" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="H134" t="s">
+    <row r="138" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="I138" t="s">
         <v>101</v>
       </c>
-      <c r="L134" s="10" t="s">
+      <c r="M138" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="M134" s="11">
+      <c r="N138" s="11">
         <v>11.3</v>
       </c>
-      <c r="N134" s="10"/>
-      <c r="O134" s="6" t="s">
+      <c r="O138" s="10"/>
+      <c r="P138" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="P134" s="10" t="s">
+      <c r="Q138" s="10" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="135" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="H135" t="s">
+    <row r="139" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="I139" t="s">
         <v>102</v>
       </c>
-      <c r="L135" s="10" t="s">
+      <c r="M139" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="M135" s="11">
+      <c r="N139" s="11">
         <v>23.278130416666666</v>
       </c>
-      <c r="N135" s="10"/>
-      <c r="O135" s="6" t="s">
+      <c r="O139" s="10"/>
+      <c r="P139" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="P135" s="10" t="s">
+      <c r="Q139" s="10" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="136" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="H136" t="s">
+    <row r="140" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="I140" t="s">
         <v>71</v>
       </c>
-      <c r="L136" s="10" t="s">
+      <c r="M140" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="M136" s="10">
+      <c r="N140" s="10">
         <v>13.15</v>
       </c>
-      <c r="N136" s="10"/>
-      <c r="O136" s="10" t="s">
+      <c r="O140" s="10"/>
+      <c r="P140" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="P136" s="10" t="s">
+      <c r="Q140" s="10" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="137" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="H137" t="s">
+    <row r="141" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="I141" t="s">
         <v>71</v>
       </c>
-      <c r="L137" s="10" t="s">
+      <c r="M141" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="M137" s="10">
+      <c r="N141" s="10">
         <v>5.26</v>
       </c>
-      <c r="N137" s="10"/>
-      <c r="O137" s="10" t="s">
+      <c r="O141" s="10"/>
+      <c r="P141" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="P137" s="10" t="s">
+      <c r="Q141" s="10" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="138" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B138" t="s">
+    <row r="142" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B142" t="s">
         <v>110</v>
       </c>
-      <c r="H138" t="s">
+      <c r="I142" t="s">
         <v>71</v>
       </c>
-      <c r="L138" s="10" t="s">
+      <c r="M142" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="M138" s="12">
+      <c r="N142" s="12">
         <v>1.7546281240590185</v>
       </c>
-      <c r="N138" s="10"/>
-      <c r="O138" s="10" t="s">
+      <c r="O142" s="10"/>
+      <c r="P142" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="P138" s="4" t="s">
+      <c r="Q142" s="4" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="139" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B139" t="s">
+    <row r="143" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B143" t="s">
         <v>113</v>
       </c>
-      <c r="H139" t="s">
+      <c r="I143" t="s">
         <v>71</v>
       </c>
-      <c r="L139" s="10" t="s">
+      <c r="M143" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="M139" s="12">
+      <c r="N143" s="12">
         <v>5.1828516694033944</v>
       </c>
-      <c r="N139" s="10"/>
-      <c r="O139" s="6" t="s">
+      <c r="O143" s="10"/>
+      <c r="P143" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="P139" s="4" t="s">
+      <c r="Q143" s="4" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="140" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B140" t="s">
+    <row r="144" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B144" t="s">
         <v>114</v>
       </c>
-      <c r="H140" t="s">
+      <c r="I144" t="s">
         <v>71</v>
       </c>
-      <c r="L140" s="10" t="s">
+      <c r="M144" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="M140" s="13">
+      <c r="N144" s="13">
         <v>4.0531064740502947</v>
       </c>
-      <c r="O140" s="6" t="s">
+      <c r="P144" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="P140" s="4" t="s">
+      <c r="Q144" s="4" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="141" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B141" t="s">
+    <row r="145" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B145" t="s">
         <v>118</v>
       </c>
-      <c r="H141" t="s">
+      <c r="I145" t="s">
         <v>71</v>
       </c>
-      <c r="L141" s="10" t="s">
+      <c r="M145" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="M141" s="13">
+      <c r="N145" s="13">
         <v>4.3591310772039646</v>
       </c>
-      <c r="O141" s="6" t="s">
+      <c r="P145" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="P141" s="6" t="s">
+      <c r="Q145" s="6" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="142" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="L142" s="10"/>
-      <c r="M142" s="13"/>
-      <c r="O142" s="6"/>
-      <c r="P142" s="6"/>
-    </row>
-    <row r="143" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="H143" t="s">
+    <row r="146" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M146" s="10"/>
+      <c r="N146" s="13"/>
+      <c r="P146" s="6"/>
+      <c r="Q146" s="6"/>
+    </row>
+    <row r="147" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="I147" t="s">
         <v>120</v>
       </c>
-      <c r="L143" s="10" t="s">
+      <c r="M147" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="M143" s="13">
+      <c r="N147" s="13">
         <v>14.6</v>
       </c>
-      <c r="O143" s="6"/>
-      <c r="P143" s="4" t="s">
+      <c r="P147" s="6"/>
+      <c r="Q147" s="4" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="144" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="H144" t="s">
+    <row r="148" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="I148" t="s">
         <v>124</v>
       </c>
-      <c r="J144" t="s">
+      <c r="K148" t="s">
         <v>121</v>
       </c>
-      <c r="L144" s="10" t="s">
+      <c r="M148" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="M144" s="13">
+      <c r="N148" s="13">
         <v>37.744765138888887</v>
       </c>
-      <c r="O144" s="6"/>
-      <c r="P144" s="6" t="s">
+      <c r="P148" s="6"/>
+      <c r="Q148" s="6" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="145" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="H145" t="s">
+    <row r="149" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="I149" t="s">
         <v>124</v>
       </c>
-      <c r="J145" t="s">
+      <c r="K149" t="s">
         <v>122</v>
       </c>
-      <c r="L145" s="10" t="s">
+      <c r="M149" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="M145" s="13">
+      <c r="N149" s="13">
         <v>50.107162083333336</v>
       </c>
-      <c r="O145" s="6"/>
-      <c r="P145" s="6" t="s">
+      <c r="P149" s="6"/>
+      <c r="Q149" s="6" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="146" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="H146" t="s">
+    <row r="150" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="I150" t="s">
         <v>124</v>
       </c>
-      <c r="J146" t="s">
+      <c r="K150" t="s">
         <v>123</v>
       </c>
-      <c r="L146" s="10" t="s">
+      <c r="M150" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="M146" s="13">
+      <c r="N150" s="13">
         <v>36.955675972222224</v>
       </c>
-      <c r="O146" s="6"/>
-      <c r="P146" s="6" t="s">
+      <c r="P150" s="6"/>
+      <c r="Q150" s="6" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="147" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="L147" s="10"/>
-      <c r="M147" s="13"/>
-      <c r="O147" s="6"/>
-      <c r="P147" s="6"/>
-    </row>
-    <row r="148" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="H148" t="s">
+    <row r="151" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M151" s="10"/>
+      <c r="N151" s="13"/>
+      <c r="P151" s="6"/>
+      <c r="Q151" s="6"/>
+    </row>
+    <row r="152" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="I152" t="s">
         <v>131</v>
       </c>
-      <c r="L148" s="10" t="s">
+      <c r="M152" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="M148" s="13">
+      <c r="N152" s="13">
         <v>1.6176327916666666</v>
       </c>
-      <c r="N148" t="s">
+      <c r="O152" t="s">
         <v>57</v>
       </c>
-      <c r="O148" s="6" t="s">
+      <c r="P152" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="P148" s="4" t="s">
+      <c r="Q152" s="4" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="149" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="H149" t="s">
+    <row r="153" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="I153" t="s">
         <v>132</v>
       </c>
-      <c r="L149" s="10" t="s">
+      <c r="M153" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="M149" s="13">
+      <c r="N153" s="13">
         <f>3.07744775/0.85</f>
         <v>3.6205267647058825</v>
       </c>
-      <c r="N149" t="s">
+      <c r="O153" t="s">
         <v>334</v>
       </c>
-      <c r="O149" s="6" t="s">
+      <c r="P153" s="6" t="s">
         <v>335</v>
       </c>
-      <c r="P149" s="4" t="s">
+      <c r="Q153" s="4" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="150" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="H150" t="s">
+    <row r="154" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="I154" t="s">
         <v>133</v>
       </c>
-      <c r="L150" s="10" t="s">
+      <c r="M154" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="M150" s="13">
+      <c r="N154" s="13">
         <v>0.25</v>
       </c>
-      <c r="N150" t="s">
+      <c r="O154" t="s">
         <v>59</v>
       </c>
-      <c r="O150" s="6" t="s">
+      <c r="P154" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="P150" s="4" t="s">
+      <c r="Q154" s="4" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="152" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A152" s="1" t="s">
+    <row r="156" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A156" s="1" t="s">
         <v>81</v>
-      </c>
-      <c r="B152" s="1"/>
-      <c r="C152" s="1"/>
-      <c r="D152" s="1"/>
-      <c r="E152" s="1"/>
-      <c r="F152" s="1"/>
-      <c r="G152" s="1"/>
-      <c r="H152" s="1"/>
-      <c r="I152" s="1"/>
-      <c r="J152" s="1"/>
-      <c r="K152" s="1"/>
-      <c r="L152" s="8"/>
-      <c r="M152" s="8"/>
-      <c r="N152" s="8"/>
-      <c r="O152" s="8"/>
-      <c r="P152" s="8"/>
-    </row>
-    <row r="153" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="L153" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="M153" s="9">
-        <v>0</v>
-      </c>
-      <c r="O153" s="9" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="154" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="L154" t="s">
-        <v>49</v>
-      </c>
-      <c r="M154" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="156" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A156" s="1" t="s">
-        <v>192</v>
       </c>
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
@@ -5070,588 +5181,892 @@
       <c r="I156" s="1"/>
       <c r="J156" s="1"/>
       <c r="K156" s="1"/>
-      <c r="L156" s="8"/>
+      <c r="L156" s="1"/>
       <c r="M156" s="8"/>
       <c r="N156" s="8"/>
       <c r="O156" s="8"/>
       <c r="P156" s="8"/>
-    </row>
-    <row r="157" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="L157" s="9" t="s">
+      <c r="Q156" s="8"/>
+    </row>
+    <row r="157" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M157" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="N157" s="9">
+        <v>0</v>
+      </c>
+      <c r="P157" s="9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="158" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M158" t="s">
+        <v>49</v>
+      </c>
+      <c r="N158" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="160" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A160" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="B160" s="1"/>
+      <c r="C160" s="1"/>
+      <c r="D160" s="1"/>
+      <c r="E160" s="1"/>
+      <c r="F160" s="1"/>
+      <c r="G160" s="1"/>
+      <c r="H160" s="1"/>
+      <c r="I160" s="1"/>
+      <c r="J160" s="1"/>
+      <c r="K160" s="1"/>
+      <c r="L160" s="1"/>
+      <c r="M160" s="8"/>
+      <c r="N160" s="8"/>
+      <c r="O160" s="8"/>
+      <c r="P160" s="8"/>
+      <c r="Q160" s="8"/>
+    </row>
+    <row r="162" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="M162" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="N162" s="9">
+        <v>100</v>
+      </c>
+      <c r="O162" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="P162" s="9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="163" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="H163" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="M163" t="s">
+        <v>336</v>
+      </c>
+      <c r="N163">
+        <v>88</v>
+      </c>
+      <c r="O163" t="s">
+        <v>128</v>
+      </c>
+      <c r="P163" t="s">
+        <v>337</v>
+      </c>
+      <c r="Q163" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="164" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="H164" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="M164" t="s">
+        <v>336</v>
+      </c>
+      <c r="N164">
+        <v>90</v>
+      </c>
+      <c r="O164" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q164" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="165" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="H165" s="6"/>
+    </row>
+    <row r="166" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="H166" s="6"/>
+      <c r="M166" t="s">
+        <v>347</v>
+      </c>
+      <c r="N166">
+        <v>1.6E-2</v>
+      </c>
+      <c r="O166" t="s">
+        <v>229</v>
+      </c>
+      <c r="P166" t="s">
+        <v>355</v>
+      </c>
+      <c r="Q166" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="167" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="H167" s="6"/>
+    </row>
+    <row r="168" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="M168" t="s">
+        <v>357</v>
+      </c>
+      <c r="N168" s="13">
+        <f>0.16*10.36*0.9</f>
+        <v>1.4918400000000001</v>
+      </c>
+      <c r="O168" t="s">
+        <v>351</v>
+      </c>
+      <c r="P168" t="s">
+        <v>352</v>
+      </c>
+      <c r="Q168" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="171" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="M171" s="9" t="s">
+        <v>338</v>
+      </c>
+      <c r="N171" s="9">
+        <v>-99</v>
+      </c>
+      <c r="O171" s="9"/>
+      <c r="P171" s="9" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="172" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="C172" t="s">
+        <v>341</v>
+      </c>
+      <c r="M172" t="s">
+        <v>338</v>
+      </c>
+      <c r="N172">
+        <v>17</v>
+      </c>
+      <c r="O172" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q172" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="173" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="C173" t="s">
+        <v>342</v>
+      </c>
+      <c r="M173" t="s">
+        <v>338</v>
+      </c>
+      <c r="N173">
+        <v>17</v>
+      </c>
+      <c r="O173" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q173" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="174" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="C174" t="s">
+        <v>343</v>
+      </c>
+      <c r="M174" t="s">
+        <v>338</v>
+      </c>
+      <c r="N174">
+        <v>17</v>
+      </c>
+      <c r="O174" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q174" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="175" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="C175" t="s">
+        <v>344</v>
+      </c>
+      <c r="M175" t="s">
+        <v>338</v>
+      </c>
+      <c r="N175">
+        <v>14</v>
+      </c>
+      <c r="O175" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q175" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="177" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="C177" t="s">
+        <v>341</v>
+      </c>
+      <c r="M177" t="s">
+        <v>339</v>
+      </c>
+      <c r="N177">
+        <v>14</v>
+      </c>
+      <c r="O177" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q177" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="178" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="C178" t="s">
+        <v>342</v>
+      </c>
+      <c r="M178" t="s">
+        <v>339</v>
+      </c>
+      <c r="N178">
+        <v>14</v>
+      </c>
+      <c r="O178" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q178" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="179" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="C179" t="s">
+        <v>343</v>
+      </c>
+      <c r="M179" t="s">
+        <v>339</v>
+      </c>
+      <c r="N179">
+        <v>14</v>
+      </c>
+      <c r="O179" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q179" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="180" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="C180" t="s">
+        <v>344</v>
+      </c>
+      <c r="M180" t="s">
+        <v>339</v>
+      </c>
+      <c r="N180">
+        <v>9</v>
+      </c>
+      <c r="O180" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q180" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="182" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A182" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B182" s="1"/>
+      <c r="C182" s="1"/>
+      <c r="D182" s="1"/>
+      <c r="E182" s="1"/>
+      <c r="F182" s="1"/>
+      <c r="G182" s="1"/>
+      <c r="H182" s="1"/>
+      <c r="I182" s="1"/>
+      <c r="J182" s="1"/>
+      <c r="K182" s="1"/>
+      <c r="L182" s="1"/>
+      <c r="M182" s="8"/>
+      <c r="N182" s="8"/>
+      <c r="O182" s="8"/>
+      <c r="P182" s="8"/>
+      <c r="Q182" s="8"/>
+    </row>
+    <row r="186" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M186" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="M157" s="9">
+      <c r="N186" s="9">
         <v>0</v>
       </c>
-      <c r="N157" s="9" t="s">
+      <c r="O186" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="O157" s="9" t="s">
+      <c r="P186" s="9" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="158" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B158" t="s">
+    <row r="187" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B187" t="s">
         <v>155</v>
       </c>
-      <c r="L158" t="s">
+      <c r="M187" t="s">
         <v>162</v>
       </c>
-      <c r="M158">
+      <c r="N187">
         <v>302</v>
       </c>
-      <c r="N158" t="s">
+      <c r="O187" t="s">
         <v>163</v>
       </c>
-      <c r="O158" t="s">
+      <c r="P187" t="s">
         <v>164</v>
       </c>
-      <c r="P158" t="s">
+      <c r="Q187" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="159" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B159" t="s">
+    <row r="188" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B188" t="s">
         <v>156</v>
       </c>
-      <c r="L159" t="s">
+      <c r="M188" t="s">
         <v>162</v>
       </c>
-      <c r="M159">
+      <c r="N188">
         <v>197</v>
       </c>
-      <c r="N159" t="s">
+      <c r="O188" t="s">
         <v>163</v>
       </c>
-      <c r="O159" t="s">
+      <c r="P188" t="s">
         <v>165</v>
       </c>
-      <c r="P159" t="s">
+      <c r="Q188" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="160" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B160" t="s">
+    <row r="189" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B189" t="s">
         <v>157</v>
       </c>
-      <c r="L160" t="s">
+      <c r="M189" t="s">
         <v>162</v>
       </c>
-      <c r="M160">
+      <c r="N189">
         <v>216</v>
       </c>
-      <c r="N160" t="s">
+      <c r="O189" t="s">
         <v>163</v>
       </c>
-      <c r="O160" t="s">
+      <c r="P189" t="s">
         <v>166</v>
       </c>
-      <c r="P160" t="s">
+      <c r="Q189" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="161" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B161" t="s">
+    <row r="190" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B190" t="s">
         <v>158</v>
       </c>
-      <c r="L161" t="s">
+      <c r="M190" t="s">
         <v>162</v>
       </c>
-      <c r="M161">
+      <c r="N190">
         <v>216</v>
       </c>
-      <c r="N161" t="s">
+      <c r="O190" t="s">
         <v>163</v>
       </c>
-      <c r="O161" t="s">
+      <c r="P190" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="162" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B162" t="s">
+    <row r="191" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B191" t="s">
         <v>159</v>
       </c>
-      <c r="L162" t="s">
+      <c r="M191" t="s">
         <v>162</v>
       </c>
-      <c r="M162">
+      <c r="N191">
         <v>216</v>
       </c>
-      <c r="N162" t="s">
+      <c r="O191" t="s">
         <v>163</v>
       </c>
-      <c r="O162" t="s">
+      <c r="P191" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="163" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B163" t="s">
+    <row r="192" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B192" t="s">
         <v>160</v>
       </c>
-      <c r="L163" t="s">
+      <c r="M192" t="s">
         <v>162</v>
       </c>
-      <c r="M163">
+      <c r="N192">
         <v>216</v>
       </c>
-      <c r="N163" t="s">
+      <c r="O192" t="s">
         <v>163</v>
       </c>
-      <c r="O163" t="s">
+      <c r="P192" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="164" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B164" t="s">
+    <row r="193" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B193" t="s">
         <v>161</v>
       </c>
-      <c r="L164" t="s">
+      <c r="M193" t="s">
         <v>162</v>
       </c>
-      <c r="M164">
+      <c r="N193">
         <v>216</v>
       </c>
-      <c r="N164" t="s">
+      <c r="O193" t="s">
         <v>163</v>
       </c>
-      <c r="O164" t="s">
+      <c r="P193" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="166" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A166" s="1" t="s">
+    <row r="195" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A195" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="B166" s="1"/>
-      <c r="C166" s="1"/>
-      <c r="D166" s="1"/>
-      <c r="E166" s="1"/>
-      <c r="F166" s="1"/>
-      <c r="G166" s="1"/>
-      <c r="H166" s="1"/>
-      <c r="I166" s="1"/>
-      <c r="J166" s="1"/>
-      <c r="K166" s="1"/>
-      <c r="L166" s="8"/>
-      <c r="M166" s="8"/>
-      <c r="N166" s="8"/>
-      <c r="O166" s="8"/>
-      <c r="P166" s="8"/>
-    </row>
-    <row r="167" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="L167" s="9" t="s">
+      <c r="B195" s="1"/>
+      <c r="C195" s="1"/>
+      <c r="D195" s="1"/>
+      <c r="E195" s="1"/>
+      <c r="F195" s="1"/>
+      <c r="G195" s="1"/>
+      <c r="H195" s="1"/>
+      <c r="I195" s="1"/>
+      <c r="J195" s="1"/>
+      <c r="K195" s="1"/>
+      <c r="L195" s="1"/>
+      <c r="M195" s="8"/>
+      <c r="N195" s="8"/>
+      <c r="O195" s="8"/>
+      <c r="P195" s="8"/>
+      <c r="Q195" s="8"/>
+    </row>
+    <row r="196" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M196" s="9" t="s">
         <v>226</v>
       </c>
-      <c r="M167" s="9">
+      <c r="N196" s="9">
         <v>0</v>
       </c>
-      <c r="N167" s="9" t="s">
+      <c r="O196" s="9" t="s">
         <v>315</v>
       </c>
-      <c r="O167" s="9" t="s">
+      <c r="P196" s="9" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="168" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="L168" s="9" t="s">
+    <row r="197" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M197" s="9" t="s">
         <v>325</v>
       </c>
-      <c r="M168" s="9">
+      <c r="N197" s="9">
         <v>0</v>
       </c>
-      <c r="N168" s="9" t="s">
+      <c r="O197" s="9" t="s">
         <v>324</v>
       </c>
-      <c r="O168" s="9" t="s">
+      <c r="P197" s="9" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="169" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="L169" s="9" t="s">
+    <row r="198" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M198" s="9" t="s">
         <v>228</v>
       </c>
-      <c r="M169" s="9">
+      <c r="N198" s="9">
         <v>0</v>
       </c>
-      <c r="N169" s="9" t="s">
+      <c r="O198" s="9" t="s">
         <v>229</v>
       </c>
-      <c r="O169" s="9" t="s">
+      <c r="P198" s="9" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="171" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A171" t="s">
+    <row r="200" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
         <v>197</v>
       </c>
-      <c r="C171" t="s">
+      <c r="D200" t="s">
         <v>195</v>
       </c>
-      <c r="D171" t="s">
+      <c r="E200" t="s">
         <v>204</v>
       </c>
-      <c r="E171" t="s">
+      <c r="F200" t="s">
         <v>205</v>
       </c>
-      <c r="F171" t="s">
+      <c r="G200" t="s">
         <v>230</v>
       </c>
-      <c r="L171" t="s">
+      <c r="M200" t="s">
         <v>228</v>
       </c>
-      <c r="M171" s="25">
+      <c r="N200" s="25">
         <f>'energy stables'!E24</f>
         <v>3.5302245250431775E-2</v>
       </c>
-      <c r="N171" t="s">
+      <c r="O200" t="s">
         <v>200</v>
       </c>
-      <c r="O171" t="s">
+      <c r="P200" t="s">
         <v>214</v>
       </c>
-      <c r="P171" t="s">
+      <c r="Q200" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="172" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A172" t="s">
+    <row r="201" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
         <v>201</v>
       </c>
-      <c r="C172" t="s">
+      <c r="D201" t="s">
         <v>195</v>
       </c>
-      <c r="D172" t="s">
+      <c r="E201" t="s">
         <v>204</v>
       </c>
-      <c r="E172" t="s">
+      <c r="F201" t="s">
         <v>205</v>
       </c>
-      <c r="L172" t="s">
+      <c r="M201" t="s">
         <v>226</v>
       </c>
-      <c r="M172" s="24">
+      <c r="N201" s="24">
         <f>'energy stables'!D26</f>
         <v>308.33833333333342</v>
       </c>
-      <c r="N172" t="s">
+      <c r="O201" t="s">
         <v>315</v>
       </c>
-      <c r="O172" t="s">
+      <c r="P201" t="s">
         <v>234</v>
       </c>
-      <c r="P172" t="s">
+      <c r="Q201" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="173" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A173" t="s">
+    <row r="202" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
         <v>199</v>
       </c>
-      <c r="C173" t="s">
+      <c r="D202" t="s">
         <v>195</v>
       </c>
-      <c r="D173" t="s">
+      <c r="E202" t="s">
         <v>204</v>
       </c>
-      <c r="E173" t="s">
+      <c r="F202" t="s">
         <v>205</v>
       </c>
-      <c r="F173" t="s">
+      <c r="G202" t="s">
         <v>230</v>
       </c>
-      <c r="L173" t="s">
+      <c r="M202" t="s">
         <v>228</v>
       </c>
-      <c r="M173" s="25">
+      <c r="N202" s="25">
         <f>'energy stables'!E27</f>
         <v>4.1036269430051814E-2</v>
       </c>
-      <c r="N173" t="s">
+      <c r="O202" t="s">
         <v>200</v>
       </c>
-      <c r="P173" t="s">
+      <c r="Q202" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="175" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A175" t="s">
+    <row r="204" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
         <v>197</v>
       </c>
-      <c r="C175" t="s">
+      <c r="D204" t="s">
         <v>195</v>
       </c>
-      <c r="L175" t="s">
+      <c r="M204" t="s">
         <v>226</v>
       </c>
-      <c r="M175" s="24">
+      <c r="N204" s="24">
         <f>'energy stables'!D29</f>
         <v>170.33333333333331</v>
       </c>
-      <c r="N175" t="s">
+      <c r="O204" t="s">
         <v>315</v>
       </c>
-      <c r="O175" t="s">
+      <c r="P204" t="s">
         <v>239</v>
       </c>
-      <c r="P175" t="s">
+      <c r="Q204" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="176" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A176" t="s">
+    <row r="205" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
         <v>201</v>
       </c>
-      <c r="C176" t="s">
+      <c r="D205" t="s">
         <v>195</v>
       </c>
-      <c r="L176" t="s">
+      <c r="M205" t="s">
         <v>226</v>
       </c>
-      <c r="M176" s="24">
+      <c r="N205" s="24">
         <f>'energy stables'!D31</f>
         <v>332.32333333333338</v>
       </c>
-      <c r="N176" t="s">
+      <c r="O205" t="s">
         <v>315</v>
       </c>
-      <c r="O176" t="s">
+      <c r="P205" t="s">
         <v>240</v>
       </c>
-      <c r="P176" t="s">
+      <c r="Q205" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="177" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="M177" s="24"/>
-    </row>
-    <row r="178" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A178" t="s">
+    <row r="206" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="N206" s="24"/>
+    </row>
+    <row r="207" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
         <v>197</v>
       </c>
-      <c r="C178" t="s">
+      <c r="D207" t="s">
         <v>235</v>
       </c>
-      <c r="D178" t="s">
+      <c r="E207" t="s">
         <v>236</v>
       </c>
-      <c r="E178" t="s">
+      <c r="F207" t="s">
         <v>241</v>
       </c>
-      <c r="L178" t="s">
+      <c r="M207" t="s">
         <v>325</v>
       </c>
-      <c r="M178" s="25">
+      <c r="N207" s="25">
         <f>(290+1078)/100000</f>
         <v>1.3679999999999999E-2</v>
       </c>
-      <c r="N178" t="s">
+      <c r="O207" t="s">
         <v>324</v>
       </c>
-      <c r="O178" t="s">
+      <c r="P207" t="s">
         <v>237</v>
       </c>
-      <c r="P178" t="s">
+      <c r="Q207" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="179" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A179" t="s">
+    <row r="208" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
         <v>198</v>
       </c>
-      <c r="C179" t="s">
+      <c r="D208" t="s">
         <v>235</v>
       </c>
-      <c r="D179" t="s">
+      <c r="E208" t="s">
         <v>236</v>
       </c>
-      <c r="E179" t="s">
+      <c r="F208" t="s">
         <v>241</v>
       </c>
-      <c r="L179" t="s">
+      <c r="M208" t="s">
         <v>325</v>
       </c>
-      <c r="M179" s="25">
+      <c r="N208" s="25">
         <f>77000/100000</f>
         <v>0.77</v>
       </c>
-      <c r="N179" t="s">
+      <c r="O208" t="s">
         <v>324</v>
       </c>
-      <c r="P179" t="s">
+      <c r="Q208" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="180" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A180" t="s">
+    <row r="209" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
         <v>201</v>
       </c>
-      <c r="C180" t="s">
+      <c r="D209" t="s">
         <v>235</v>
       </c>
-      <c r="D180" t="s">
+      <c r="E209" t="s">
         <v>236</v>
       </c>
-      <c r="E180" t="s">
+      <c r="F209" t="s">
         <v>241</v>
       </c>
-      <c r="L180" t="s">
+      <c r="M209" t="s">
         <v>325</v>
       </c>
-      <c r="M180" s="25">
+      <c r="N209" s="25">
         <f>(3340+9790)/100000</f>
         <v>0.1313</v>
       </c>
-      <c r="N180" t="s">
+      <c r="O209" t="s">
         <v>324</v>
       </c>
-      <c r="O180" t="s">
+      <c r="P209" t="s">
         <v>238</v>
       </c>
-      <c r="P180" t="s">
+      <c r="Q209" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="182" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A182" t="s">
+    <row r="211" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
         <v>197</v>
       </c>
-      <c r="C182" t="s">
+      <c r="D211" t="s">
         <v>242</v>
       </c>
-      <c r="E182" t="s">
+      <c r="F211" t="s">
         <v>318</v>
       </c>
-      <c r="L182" t="s">
+      <c r="M211" t="s">
         <v>325</v>
       </c>
-      <c r="M182">
+      <c r="N211">
         <f>'energy stables'!D49</f>
         <v>3.5</v>
       </c>
-      <c r="N182" t="s">
+      <c r="O211" t="s">
         <v>324</v>
       </c>
-      <c r="P182" t="s">
+      <c r="Q211" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="183" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A183" t="s">
+    <row r="212" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
         <v>198</v>
       </c>
-      <c r="C183" t="s">
+      <c r="D212" t="s">
         <v>242</v>
       </c>
-      <c r="E183" t="s">
+      <c r="F212" t="s">
         <v>318</v>
       </c>
-      <c r="L183" t="s">
+      <c r="M212" t="s">
         <v>325</v>
       </c>
-      <c r="M183">
+      <c r="N212">
         <f>'energy stables'!D50</f>
         <v>12.5</v>
       </c>
-      <c r="N183" t="s">
+      <c r="O212" t="s">
         <v>324</v>
       </c>
-      <c r="P183" t="s">
+      <c r="Q212" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="184" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A184" t="s">
+    <row r="213" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
         <v>201</v>
       </c>
-      <c r="C184" t="s">
+      <c r="D213" t="s">
         <v>242</v>
       </c>
-      <c r="E184" t="s">
+      <c r="F213" t="s">
         <v>318</v>
       </c>
-      <c r="L184" t="s">
+      <c r="M213" t="s">
         <v>325</v>
       </c>
-      <c r="M184">
+      <c r="N213">
         <f>'energy stables'!D51</f>
         <v>34</v>
       </c>
-      <c r="N184" t="s">
+      <c r="O213" t="s">
         <v>324</v>
       </c>
-      <c r="P184" t="s">
+      <c r="Q213" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="185" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A185" t="s">
+    <row r="214" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
         <v>197</v>
       </c>
-      <c r="C185" t="s">
+      <c r="D214" t="s">
         <v>242</v>
       </c>
-      <c r="E185" t="s">
+      <c r="F214" t="s">
         <v>321</v>
       </c>
-      <c r="L185" t="s">
+      <c r="M214" t="s">
         <v>325</v>
       </c>
-      <c r="M185">
+      <c r="N214">
         <f>'energy stables'!D53</f>
         <v>0.04</v>
       </c>
-      <c r="N185" t="s">
+      <c r="O214" t="s">
         <v>324</v>
       </c>
-      <c r="P185" t="s">
+      <c r="Q214" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="186" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A186" t="s">
+    <row r="215" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
         <v>198</v>
       </c>
-      <c r="C186" t="s">
+      <c r="D215" t="s">
         <v>242</v>
       </c>
-      <c r="E186" t="s">
+      <c r="F215" t="s">
         <v>321</v>
       </c>
-      <c r="L186" t="s">
+      <c r="M215" t="s">
         <v>325</v>
       </c>
-      <c r="M186" s="13">
+      <c r="N215" s="13">
         <f>'energy stables'!D54</f>
         <v>0.1</v>
       </c>
-      <c r="N186" t="s">
+      <c r="O215" t="s">
         <v>324</v>
       </c>
-      <c r="P186" t="s">
+      <c r="Q215" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="187" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A187" t="s">
+    <row r="216" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
         <v>201</v>
       </c>
-      <c r="C187" t="s">
+      <c r="D216" t="s">
         <v>242</v>
       </c>
-      <c r="E187" t="s">
+      <c r="F216" t="s">
         <v>321</v>
       </c>
-      <c r="L187" t="s">
+      <c r="M216" t="s">
         <v>325</v>
       </c>
-      <c r="M187" s="13">
+      <c r="N216" s="13">
         <f>'energy stables'!D55</f>
         <v>0.26</v>
       </c>
-      <c r="N187" t="s">
+      <c r="O216" t="s">
         <v>324</v>
       </c>
-      <c r="P187" t="s">
+      <c r="Q216" t="s">
         <v>253</v>
       </c>
     </row>

--- a/data/default/MachineryAndEnergyMgmt.xlsx
+++ b/data/default/MachineryAndEnergyMgmt.xlsx
@@ -477,7 +477,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1017" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1020" uniqueCount="361">
   <si>
     <t>f_crop</t>
   </si>
@@ -1732,6 +1732,12 @@
   </si>
   <si>
     <t>Törner &amp; Norup 2009, p.11</t>
+  </si>
+  <si>
+    <t>Energimyndigheten. Statistikdatabas. Jordbrukets energianvändning</t>
+  </si>
+  <si>
+    <t>70% of dryers used oil as fuel and consumed 165 GWh oil year 2021</t>
   </si>
 </sst>
 </file>
@@ -2141,7 +2147,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -2240,7 +2246,6 @@
     <xf numFmtId="2" fontId="23" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3223,16 +3228,22 @@
         <v>348</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="M36" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="N36" s="94">
-        <v>10</v>
+      <c r="N36" s="18">
+        <v>70</v>
       </c>
       <c r="O36" t="s">
         <v>128</v>
+      </c>
+      <c r="P36" t="s">
+        <v>360</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
@@ -3240,16 +3251,19 @@
         <v>348</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="M37" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="N37" s="94">
-        <v>90</v>
+      <c r="N37" s="18">
+        <v>30</v>
       </c>
       <c r="O37" t="s">
         <v>128</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">

--- a/data/default/MachineryAndEnergyMgmt.xlsx
+++ b/data/default/MachineryAndEnergyMgmt.xlsx
@@ -477,7 +477,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1020" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1167" uniqueCount="403">
   <si>
     <t>f_crop</t>
   </si>
@@ -1739,6 +1739,132 @@
   <si>
     <t>70% of dryers used oil as fuel and consumed 165 GWh oil year 2021</t>
   </si>
+  <si>
+    <t>layer</t>
+  </si>
+  <si>
+    <t>laying chicks</t>
+  </si>
+  <si>
+    <t>Sonesson et al (2008), page 16</t>
+  </si>
+  <si>
+    <t>4.7 MJ for heating per delivered layer based on data for broilers</t>
+  </si>
+  <si>
+    <t>3 ggr/dag</t>
+  </si>
+  <si>
+    <t>8 ggr/dag</t>
+  </si>
+  <si>
+    <t>Belysning;</t>
+  </si>
+  <si>
+    <t>Effekt, ljusprogram</t>
+  </si>
+  <si>
+    <t>0,48 W/dp, 14 tim/dag</t>
+  </si>
+  <si>
+    <t>0,46 W/dp, 16 tim/dag</t>
+  </si>
+  <si>
+    <t>12 500 värphöns frigående system Wh/ djurplats, år</t>
+  </si>
+  <si>
+    <t>Städning mm mellan omg exkl värme</t>
+  </si>
+  <si>
+    <t>Ägg packning</t>
+  </si>
+  <si>
+    <t>Äggtvätt</t>
+  </si>
+  <si>
+    <t>Kylning</t>
+  </si>
+  <si>
+    <t>ingår i Övrigt</t>
+  </si>
+  <si>
+    <t>Städning</t>
+  </si>
+  <si>
+    <t>Ingår i Övrigt</t>
+  </si>
+  <si>
+    <t>Summa/dp</t>
+  </si>
+  <si>
+    <t>J</t>
+  </si>
+  <si>
+    <t>K</t>
+  </si>
+  <si>
+    <t>40 000 värphöns inredda burar Wh/djurplats, år</t>
+  </si>
+  <si>
+    <t>kWh/ ton ägg 20 kg/höna</t>
+  </si>
+  <si>
+    <t>156 kWh/ton ägg</t>
+  </si>
+  <si>
+    <t>251 kWh/ton ägg</t>
+  </si>
+  <si>
+    <t>18,8</t>
+  </si>
+  <si>
+    <t>Funktion</t>
+  </si>
+  <si>
+    <t>animal</t>
+  </si>
+  <si>
+    <t>Layers</t>
+  </si>
+  <si>
+    <t>Used values for layers</t>
+  </si>
+  <si>
+    <t>energy use for laying chicks expressed per inserted head</t>
+  </si>
+  <si>
+    <t>manure mgmt and feeding</t>
+  </si>
+  <si>
+    <t>mainly lighting and ventilation</t>
+  </si>
+  <si>
+    <t>sheep</t>
+  </si>
+  <si>
+    <t>lambs</t>
+  </si>
+  <si>
+    <t>Energy use for ewes assumed to include lambs</t>
+  </si>
+  <si>
+    <t>on farm diesel per animal and "stable-year"</t>
+  </si>
+  <si>
+    <t>Ahlgren et al. (2022)</t>
+  </si>
+  <si>
+    <t>on farm electricity per animal and "stable-year"</t>
+  </si>
+  <si>
+    <t>Ahlgren et al. (2022) Miljöpåverkan av svensk nöt- och lammköttsproduktion. RISE Rapport 2022:143</t>
+  </si>
+  <si>
+    <t>Sonesson et al (2008) Livscykelanalys (LCA) av svenska ägg (ver.2). SIK-rapport Nr 783 2008</t>
+  </si>
+  <si>
+    <t>"</t>
+  </si>
 </sst>
 </file>
 
@@ -1748,7 +1874,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1921,6 +2047,13 @@
     <font>
       <sz val="11"/>
       <color theme="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -2147,7 +2280,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="105">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -2246,6 +2379,27 @@
     <xf numFmtId="2" fontId="23" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2527,7 +2681,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U216"/>
+  <dimension ref="A1:U236"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="8" max="12" width="12.28515625" customWidth="1"/>
@@ -3099,961 +3253,921 @@
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H28" s="6"/>
       <c r="M28" s="6"/>
-      <c r="N28" s="15"/>
+      <c r="N28" s="10"/>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>153</v>
+        <v>197</v>
+      </c>
+      <c r="D29" t="s">
+        <v>235</v>
+      </c>
+      <c r="E29" t="s">
+        <v>361</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="M29" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="N29" s="11">
-        <v>6.4777062142923141</v>
+      <c r="N29" s="10">
+        <v>90</v>
       </c>
       <c r="O29" t="s">
         <v>128</v>
       </c>
-      <c r="Q29" t="s">
-        <v>167</v>
-      </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>153</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>333</v>
+        <v>197</v>
+      </c>
+      <c r="D30" t="s">
+        <v>235</v>
+      </c>
+      <c r="E30" t="s">
+        <v>361</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>252</v>
       </c>
       <c r="M30" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="N30" s="11">
-        <v>8.7567853491111922</v>
+      <c r="N30" s="10">
+        <v>10</v>
       </c>
       <c r="O30" t="s">
         <v>128</v>
       </c>
-      <c r="P30" t="s">
-        <v>170</v>
-      </c>
-      <c r="Q30" t="s">
-        <v>168</v>
-      </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>153</v>
+        <v>201</v>
+      </c>
+      <c r="D31" t="s">
+        <v>235</v>
+      </c>
+      <c r="E31" t="s">
+        <v>361</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="M31" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="N31" s="18">
-        <v>59.671114354829328</v>
+      <c r="N31" s="10">
+        <v>100</v>
       </c>
       <c r="O31" t="s">
         <v>128</v>
       </c>
-      <c r="P31" s="19" t="s">
-        <v>171</v>
-      </c>
-      <c r="Q31" t="s">
-        <v>169</v>
-      </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>153</v>
+        <v>198</v>
+      </c>
+      <c r="D32" t="s">
+        <v>235</v>
+      </c>
+      <c r="E32" t="s">
+        <v>361</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="M32" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="N32" s="18">
-        <v>16.802918820320372</v>
+      <c r="N32" s="10">
+        <v>90</v>
       </c>
       <c r="O32" t="s">
         <v>128</v>
       </c>
+      <c r="Q32" t="s">
+        <v>363</v>
+      </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>153</v>
+        <v>198</v>
+      </c>
+      <c r="D33" t="s">
+        <v>235</v>
+      </c>
+      <c r="E33" t="s">
+        <v>361</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="M33" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="N33" s="11">
-        <v>7.4851294970113242</v>
+      <c r="N33" s="10">
+        <v>10</v>
       </c>
       <c r="O33" t="s">
         <v>128</v>
       </c>
+      <c r="Q33" t="s">
+        <v>363</v>
+      </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>153</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>331</v>
-      </c>
-      <c r="M34" s="6" t="s">
+      <c r="H34" s="6"/>
+      <c r="M34" s="6"/>
+      <c r="N34" s="10"/>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>197</v>
+      </c>
+      <c r="D35" t="s">
+        <v>394</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="M35" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="N34" s="11">
-        <v>0.80634576443547301</v>
-      </c>
-      <c r="O34" t="s">
+      <c r="N35" s="10">
+        <v>100</v>
+      </c>
+      <c r="O35" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H35" s="6"/>
-      <c r="M35" s="6"/>
-      <c r="N35" s="11"/>
+      <c r="Q35" t="s">
+        <v>398</v>
+      </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>348</v>
+        <v>201</v>
+      </c>
+      <c r="D36" t="s">
+        <v>394</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="M36" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="N36" s="18">
-        <v>70</v>
+      <c r="N36" s="10">
+        <v>100</v>
       </c>
       <c r="O36" t="s">
         <v>128</v>
       </c>
-      <c r="P36" t="s">
-        <v>360</v>
-      </c>
       <c r="Q36" t="s">
-        <v>359</v>
+        <v>398</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>348</v>
-      </c>
-      <c r="H37" s="6" t="s">
-        <v>330</v>
-      </c>
-      <c r="M37" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="N37" s="18">
-        <v>30</v>
-      </c>
-      <c r="O37" t="s">
-        <v>128</v>
-      </c>
-      <c r="Q37" t="s">
-        <v>359</v>
-      </c>
+      <c r="H37" s="6"/>
+      <c r="M37" s="6"/>
+      <c r="N37" s="15"/>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>349</v>
+        <v>153</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M38" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="N38" s="18">
-        <v>100</v>
-      </c>
-      <c r="O38" s="10" t="s">
+      <c r="N38" s="11">
+        <v>6.4777062142923141</v>
+      </c>
+      <c r="O38" t="s">
         <v>128</v>
       </c>
+      <c r="Q38" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H39" s="6"/>
+      <c r="A39" t="s">
+        <v>153</v>
+      </c>
+      <c r="H39" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="M39" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="N39" s="11">
+        <v>8.7567853491111922</v>
+      </c>
+      <c r="O39" t="s">
+        <v>128</v>
+      </c>
+      <c r="P39" t="s">
+        <v>170</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>168</v>
+      </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="K40" t="s">
-        <v>121</v>
-      </c>
-      <c r="M40" t="s">
-        <v>130</v>
-      </c>
-      <c r="N40" s="15">
-        <v>80</v>
+      <c r="A40" t="s">
+        <v>153</v>
+      </c>
+      <c r="H40" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="M40" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="N40" s="18">
+        <v>59.671114354829328</v>
       </c>
       <c r="O40" t="s">
         <v>128</v>
       </c>
+      <c r="P40" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="K41" t="s">
-        <v>122</v>
-      </c>
-      <c r="M41" t="s">
-        <v>130</v>
-      </c>
-      <c r="N41" s="15">
-        <v>10</v>
+      <c r="A41" t="s">
+        <v>153</v>
+      </c>
+      <c r="H41" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="M41" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="N41" s="18">
+        <v>16.802918820320372</v>
       </c>
       <c r="O41" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="K42" t="s">
-        <v>123</v>
-      </c>
-      <c r="M42" t="s">
-        <v>130</v>
-      </c>
-      <c r="N42" s="15">
-        <v>10</v>
+      <c r="A42" t="s">
+        <v>153</v>
+      </c>
+      <c r="H42" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="M42" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="N42" s="11">
+        <v>7.4851294970113242</v>
       </c>
       <c r="O42" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
+      <c r="A43" t="s">
+        <v>153</v>
+      </c>
+      <c r="H43" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="M43" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="N43" s="11">
+        <v>0.80634576443547301</v>
+      </c>
+      <c r="O43" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H44" s="6"/>
+      <c r="M44" s="6"/>
+      <c r="N44" s="11"/>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>348</v>
+      </c>
+      <c r="H45" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="M45" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="N45" s="18">
+        <v>70</v>
+      </c>
+      <c r="O45" t="s">
+        <v>128</v>
+      </c>
+      <c r="P45" t="s">
+        <v>360</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>348</v>
+      </c>
+      <c r="H46" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="M46" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="N46" s="18">
+        <v>30</v>
+      </c>
+      <c r="O46" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>349</v>
+      </c>
+      <c r="H47" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="M47" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="N47" s="18">
+        <v>100</v>
+      </c>
+      <c r="O47" s="10" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H48" s="6"/>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="K49" t="s">
+        <v>121</v>
+      </c>
+      <c r="M49" t="s">
+        <v>130</v>
+      </c>
+      <c r="N49" s="15">
+        <v>80</v>
+      </c>
+      <c r="O49" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="K50" t="s">
+        <v>122</v>
+      </c>
+      <c r="M50" t="s">
+        <v>130</v>
+      </c>
+      <c r="N50" s="15">
+        <v>10</v>
+      </c>
+      <c r="O50" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="K51" t="s">
+        <v>123</v>
+      </c>
+      <c r="M51" t="s">
+        <v>130</v>
+      </c>
+      <c r="N51" s="15">
+        <v>10</v>
+      </c>
+      <c r="O51" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="B43" s="1"/>
-      <c r="C43" s="1"/>
-      <c r="D43" s="1"/>
-      <c r="E43" s="1"/>
-      <c r="F43" s="1"/>
-      <c r="G43" s="1"/>
-      <c r="H43" s="1"/>
-      <c r="I43" s="1"/>
-      <c r="J43" s="1"/>
-      <c r="K43" s="1"/>
-      <c r="L43" s="1"/>
-      <c r="M43" s="1"/>
-      <c r="N43" s="1"/>
-      <c r="O43" s="1"/>
-      <c r="P43" s="1"/>
-      <c r="Q43" s="1"/>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H44" s="4"/>
-      <c r="M44" s="9" t="s">
+      <c r="B52" s="1"/>
+      <c r="C52" s="1"/>
+      <c r="D52" s="1"/>
+      <c r="E52" s="1"/>
+      <c r="F52" s="1"/>
+      <c r="G52" s="1"/>
+      <c r="H52" s="1"/>
+      <c r="I52" s="1"/>
+      <c r="J52" s="1"/>
+      <c r="K52" s="1"/>
+      <c r="L52" s="1"/>
+      <c r="M52" s="1"/>
+      <c r="N52" s="1"/>
+      <c r="O52" s="1"/>
+      <c r="P52" s="1"/>
+      <c r="Q52" s="1"/>
+    </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H53" s="4"/>
+      <c r="M53" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="N44" s="23">
+      <c r="N53" s="23">
         <v>0</v>
       </c>
-      <c r="O44" s="9"/>
-      <c r="P44" s="9" t="s">
+      <c r="O53" s="9"/>
+      <c r="P53" s="9" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H45" s="4"/>
-      <c r="N45" s="18"/>
-    </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H46" s="4" t="s">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H54" s="4"/>
+      <c r="N54" s="18"/>
+    </row>
+    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H55" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="L46" t="s">
+      <c r="L55" t="s">
         <v>177</v>
       </c>
-      <c r="M46" t="s">
+      <c r="M55" t="s">
         <v>176</v>
       </c>
-      <c r="N46" s="18">
+      <c r="N55" s="18">
         <f>74100</f>
         <v>74100</v>
       </c>
-      <c r="O46" t="s">
+      <c r="O55" t="s">
         <v>186</v>
       </c>
-      <c r="P46" t="s">
+      <c r="P55" t="s">
         <v>180</v>
       </c>
-      <c r="Q46" t="s">
+      <c r="Q55" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H47" s="4" t="s">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H56" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="L47" t="s">
+      <c r="L56" t="s">
         <v>184</v>
       </c>
-      <c r="M47" t="s">
+      <c r="M56" t="s">
         <v>176</v>
       </c>
-      <c r="N47" s="11">
+      <c r="N56" s="11">
         <f>3.9</f>
         <v>3.9</v>
       </c>
-      <c r="O47" t="s">
+      <c r="O56" t="s">
         <v>186</v>
       </c>
-      <c r="Q47" t="s">
+      <c r="Q56" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H48" s="4" t="s">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H57" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="L48" t="s">
+      <c r="L57" t="s">
         <v>178</v>
       </c>
-      <c r="M48" t="s">
+      <c r="M57" t="s">
         <v>176</v>
       </c>
-      <c r="N48" s="11">
+      <c r="N57" s="11">
         <f>3.9</f>
         <v>3.9</v>
       </c>
-      <c r="O48" t="s">
+      <c r="O57" t="s">
         <v>186</v>
       </c>
-      <c r="Q48" t="s">
+      <c r="Q57" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="49" spans="8:17" x14ac:dyDescent="0.25">
-      <c r="H49" s="4" t="s">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H58" s="4" t="s">
         <v>326</v>
       </c>
-      <c r="L49" t="s">
+      <c r="L58" t="s">
         <v>177</v>
       </c>
-      <c r="M49" t="s">
+      <c r="M58" t="s">
         <v>176</v>
       </c>
-      <c r="N49" s="18">
+      <c r="N58" s="18">
         <v>0</v>
       </c>
-      <c r="O49" t="s">
+      <c r="O58" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="50" spans="8:17" x14ac:dyDescent="0.25">
-      <c r="H50" s="4" t="s">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H59" s="4" t="s">
         <v>326</v>
       </c>
-      <c r="L50" t="s">
+      <c r="L59" t="s">
         <v>185</v>
       </c>
-      <c r="M50" t="s">
+      <c r="M59" t="s">
         <v>176</v>
       </c>
-      <c r="N50" s="22">
-        <f t="shared" ref="N50:N51" si="0">N47</f>
+      <c r="N59" s="22">
+        <f t="shared" ref="N59:N60" si="0">N56</f>
         <v>3.9</v>
       </c>
-      <c r="O50" t="s">
+      <c r="O59" t="s">
         <v>186</v>
       </c>
-      <c r="P50" t="s">
+      <c r="P59" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="51" spans="8:17" x14ac:dyDescent="0.25">
-      <c r="H51" s="4" t="s">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H60" s="4" t="s">
         <v>326</v>
       </c>
-      <c r="L51" t="s">
+      <c r="L60" t="s">
         <v>178</v>
       </c>
-      <c r="M51" t="s">
+      <c r="M60" t="s">
         <v>176</v>
       </c>
-      <c r="N51" s="22">
+      <c r="N60" s="22">
         <f t="shared" si="0"/>
         <v>3.9</v>
       </c>
-      <c r="O51" t="s">
-        <v>186</v>
-      </c>
-      <c r="P51" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="52" spans="8:17" x14ac:dyDescent="0.25">
-      <c r="H52" s="6" t="s">
-        <v>329</v>
-      </c>
-      <c r="L52" t="s">
-        <v>177</v>
-      </c>
-      <c r="M52" t="s">
-        <v>176</v>
-      </c>
-      <c r="N52" s="18">
-        <v>73300</v>
-      </c>
-      <c r="O52" t="s">
-        <v>186</v>
-      </c>
-      <c r="P52" t="s">
-        <v>189</v>
-      </c>
-      <c r="Q52" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="53" spans="8:17" x14ac:dyDescent="0.25">
-      <c r="H53" s="6" t="s">
-        <v>329</v>
-      </c>
-      <c r="L53" t="s">
-        <v>184</v>
-      </c>
-      <c r="M53" t="s">
-        <v>176</v>
-      </c>
-      <c r="N53">
-        <v>10</v>
-      </c>
-      <c r="O53" t="s">
-        <v>186</v>
-      </c>
-      <c r="Q53" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="54" spans="8:17" x14ac:dyDescent="0.25">
-      <c r="H54" s="6" t="s">
-        <v>329</v>
-      </c>
-      <c r="L54" t="s">
-        <v>178</v>
-      </c>
-      <c r="M54" t="s">
-        <v>176</v>
-      </c>
-      <c r="N54">
-        <v>0.6</v>
-      </c>
-      <c r="O54" t="s">
-        <v>186</v>
-      </c>
-      <c r="Q54" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="55" spans="8:17" x14ac:dyDescent="0.25">
-      <c r="H55" s="6" t="s">
-        <v>333</v>
-      </c>
-      <c r="L55" t="s">
-        <v>177</v>
-      </c>
-      <c r="M55" t="s">
-        <v>176</v>
-      </c>
-      <c r="N55" s="18">
-        <v>56100</v>
-      </c>
-      <c r="O55" t="s">
-        <v>186</v>
-      </c>
-      <c r="P55" t="s">
-        <v>188</v>
-      </c>
-      <c r="Q55" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="56" spans="8:17" x14ac:dyDescent="0.25">
-      <c r="H56" s="6" t="s">
-        <v>333</v>
-      </c>
-      <c r="L56" t="s">
-        <v>184</v>
-      </c>
-      <c r="M56" t="s">
-        <v>176</v>
-      </c>
-      <c r="N56">
-        <v>5</v>
-      </c>
-      <c r="O56" t="s">
-        <v>186</v>
-      </c>
-      <c r="Q56" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="57" spans="8:17" x14ac:dyDescent="0.25">
-      <c r="H57" s="6" t="s">
-        <v>333</v>
-      </c>
-      <c r="L57" t="s">
-        <v>178</v>
-      </c>
-      <c r="M57" t="s">
-        <v>176</v>
-      </c>
-      <c r="N57">
-        <v>0.1</v>
-      </c>
-      <c r="O57" t="s">
-        <v>186</v>
-      </c>
-      <c r="Q57" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="58" spans="8:17" x14ac:dyDescent="0.25">
-      <c r="H58" s="6" t="s">
-        <v>330</v>
-      </c>
-      <c r="L58" t="s">
-        <v>177</v>
-      </c>
-      <c r="M58" t="s">
-        <v>176</v>
-      </c>
-      <c r="N58" s="18">
-        <v>0</v>
-      </c>
-      <c r="O58" t="s">
-        <v>186</v>
-      </c>
-      <c r="P58" t="s">
-        <v>187</v>
-      </c>
-      <c r="Q58" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="59" spans="8:17" x14ac:dyDescent="0.25">
-      <c r="H59" s="6" t="s">
-        <v>330</v>
-      </c>
-      <c r="L59" t="s">
-        <v>185</v>
-      </c>
-      <c r="M59" t="s">
-        <v>176</v>
-      </c>
-      <c r="N59" s="18">
-        <v>300</v>
-      </c>
-      <c r="O59" t="s">
-        <v>186</v>
-      </c>
-      <c r="Q59" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="60" spans="8:17" x14ac:dyDescent="0.25">
-      <c r="H60" s="6" t="s">
-        <v>330</v>
-      </c>
-      <c r="L60" t="s">
-        <v>178</v>
-      </c>
-      <c r="M60" t="s">
-        <v>176</v>
-      </c>
-      <c r="N60" s="18">
-        <v>4</v>
-      </c>
       <c r="O60" t="s">
         <v>186</v>
       </c>
-      <c r="Q60" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="61" spans="8:17" x14ac:dyDescent="0.25">
+      <c r="P60" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H61" s="6" t="s">
-        <v>332</v>
+        <v>329</v>
+      </c>
+      <c r="L61" t="s">
+        <v>177</v>
       </c>
       <c r="M61" t="s">
         <v>176</v>
       </c>
       <c r="N61" s="18">
-        <v>0</v>
+        <v>73300</v>
       </c>
       <c r="O61" t="s">
         <v>186</v>
       </c>
-      <c r="P61" s="15"/>
-    </row>
-    <row r="62" spans="8:17" x14ac:dyDescent="0.25">
+      <c r="P61" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H62" s="6" t="s">
-        <v>331</v>
+        <v>329</v>
+      </c>
+      <c r="L62" t="s">
+        <v>184</v>
       </c>
       <c r="M62" t="s">
         <v>176</v>
       </c>
-      <c r="N62" s="18">
-        <v>0</v>
+      <c r="N62">
+        <v>10</v>
       </c>
       <c r="O62" t="s">
         <v>186</v>
       </c>
-      <c r="P62" s="15"/>
-    </row>
-    <row r="63" spans="8:17" x14ac:dyDescent="0.25">
-      <c r="H63" s="4" t="s">
-        <v>327</v>
+      <c r="Q62" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H63" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="L63" t="s">
+        <v>178</v>
       </c>
       <c r="M63" t="s">
         <v>176</v>
       </c>
-      <c r="N63" s="18">
-        <v>0</v>
+      <c r="N63">
+        <v>0.6</v>
       </c>
       <c r="O63" t="s">
         <v>186</v>
       </c>
-      <c r="P63" s="15" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="64" spans="8:17" x14ac:dyDescent="0.25">
+      <c r="Q63" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H64" s="6" t="s">
-        <v>328</v>
+        <v>333</v>
+      </c>
+      <c r="L64" t="s">
+        <v>177</v>
       </c>
       <c r="M64" t="s">
         <v>176</v>
       </c>
       <c r="N64" s="18">
-        <v>0</v>
+        <v>56100</v>
       </c>
       <c r="O64" t="s">
         <v>186</v>
       </c>
-      <c r="P64" s="15"/>
+      <c r="P64" t="s">
+        <v>188</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H65" s="6"/>
-      <c r="N65" s="18"/>
-      <c r="P65" s="15"/>
+      <c r="H65" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="L65" t="s">
+        <v>184</v>
+      </c>
+      <c r="M65" t="s">
+        <v>176</v>
+      </c>
+      <c r="N65">
+        <v>5</v>
+      </c>
+      <c r="O65" t="s">
+        <v>186</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A66" s="1" t="s">
+      <c r="H66" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="L66" t="s">
+        <v>178</v>
+      </c>
+      <c r="M66" t="s">
+        <v>176</v>
+      </c>
+      <c r="N66">
+        <v>0.1</v>
+      </c>
+      <c r="O66" t="s">
+        <v>186</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H67" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="L67" t="s">
+        <v>177</v>
+      </c>
+      <c r="M67" t="s">
+        <v>176</v>
+      </c>
+      <c r="N67" s="18">
+        <v>0</v>
+      </c>
+      <c r="O67" t="s">
+        <v>186</v>
+      </c>
+      <c r="P67" t="s">
+        <v>187</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H68" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="L68" t="s">
+        <v>185</v>
+      </c>
+      <c r="M68" t="s">
+        <v>176</v>
+      </c>
+      <c r="N68" s="18">
+        <v>300</v>
+      </c>
+      <c r="O68" t="s">
+        <v>186</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H69" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="L69" t="s">
+        <v>178</v>
+      </c>
+      <c r="M69" t="s">
+        <v>176</v>
+      </c>
+      <c r="N69" s="18">
+        <v>4</v>
+      </c>
+      <c r="O69" t="s">
+        <v>186</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H70" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="M70" t="s">
+        <v>176</v>
+      </c>
+      <c r="N70" s="18">
+        <v>0</v>
+      </c>
+      <c r="O70" t="s">
+        <v>186</v>
+      </c>
+      <c r="P70" s="15"/>
+    </row>
+    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H71" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="M71" t="s">
+        <v>176</v>
+      </c>
+      <c r="N71" s="18">
+        <v>0</v>
+      </c>
+      <c r="O71" t="s">
+        <v>186</v>
+      </c>
+      <c r="P71" s="15"/>
+    </row>
+    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H72" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="M72" t="s">
+        <v>176</v>
+      </c>
+      <c r="N72" s="18">
+        <v>0</v>
+      </c>
+      <c r="O72" t="s">
+        <v>186</v>
+      </c>
+      <c r="P72" s="15" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H73" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="M73" t="s">
+        <v>176</v>
+      </c>
+      <c r="N73" s="18">
+        <v>0</v>
+      </c>
+      <c r="O73" t="s">
+        <v>186</v>
+      </c>
+      <c r="P73" s="15"/>
+    </row>
+    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H74" s="6"/>
+      <c r="N74" s="18"/>
+      <c r="P74" s="15"/>
+    </row>
+    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B66" s="1"/>
-      <c r="C66" s="1"/>
-      <c r="D66" s="1"/>
-      <c r="E66" s="1"/>
-      <c r="F66" s="1"/>
-      <c r="G66" s="1"/>
-      <c r="H66" s="1"/>
-      <c r="I66" s="1"/>
-      <c r="J66" s="1"/>
-      <c r="K66" s="1"/>
-      <c r="L66" s="1"/>
-      <c r="M66" s="1"/>
-      <c r="N66" s="1"/>
-      <c r="O66" s="1"/>
-      <c r="P66" s="1"/>
-      <c r="Q66" s="1"/>
-    </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A67" s="2" t="s">
+      <c r="B75" s="1"/>
+      <c r="C75" s="1"/>
+      <c r="D75" s="1"/>
+      <c r="E75" s="1"/>
+      <c r="F75" s="1"/>
+      <c r="G75" s="1"/>
+      <c r="H75" s="1"/>
+      <c r="I75" s="1"/>
+      <c r="J75" s="1"/>
+      <c r="K75" s="1"/>
+      <c r="L75" s="1"/>
+      <c r="M75" s="1"/>
+      <c r="N75" s="1"/>
+      <c r="O75" s="1"/>
+      <c r="P75" s="1"/>
+      <c r="Q75" s="1"/>
+    </row>
+    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A76" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B67" s="2"/>
-      <c r="C67" s="2"/>
-      <c r="D67" s="2"/>
-      <c r="E67" s="2"/>
-      <c r="F67" s="2"/>
-      <c r="G67" s="2"/>
-      <c r="H67" s="2"/>
-      <c r="I67" s="2"/>
-      <c r="J67" s="2"/>
-      <c r="K67" s="2"/>
-      <c r="L67" s="2"/>
-      <c r="M67" s="3"/>
-      <c r="N67" s="3"/>
-      <c r="O67" s="3"/>
-      <c r="P67" s="3"/>
-      <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B68" s="4"/>
-      <c r="C68" s="4"/>
-      <c r="D68" s="4"/>
-      <c r="E68" s="4"/>
-      <c r="F68" s="4"/>
-      <c r="G68" s="4"/>
-      <c r="H68" s="4"/>
-      <c r="I68" s="4"/>
-      <c r="J68" s="4"/>
-      <c r="K68" s="4"/>
-      <c r="L68" s="4"/>
-      <c r="M68" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="N68">
-        <v>10800</v>
-      </c>
-      <c r="O68" t="s">
-        <v>11</v>
-      </c>
-      <c r="P68" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B69" s="4"/>
-      <c r="C69" s="4"/>
-      <c r="D69" s="4"/>
-      <c r="E69" s="4"/>
-      <c r="F69" s="4"/>
-      <c r="G69" s="4"/>
-      <c r="H69" s="4"/>
-      <c r="I69" s="4"/>
-      <c r="J69" s="4"/>
-      <c r="K69" s="4"/>
-      <c r="L69" s="4"/>
-      <c r="M69" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="N69">
-        <v>5</v>
-      </c>
-      <c r="O69" t="s">
-        <v>13</v>
-      </c>
-      <c r="P69" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B70" s="4"/>
-      <c r="C70" s="4"/>
-      <c r="D70" s="4"/>
-      <c r="E70" s="4"/>
-      <c r="F70" s="4"/>
-      <c r="G70" s="4"/>
-      <c r="H70" s="4"/>
-      <c r="I70" s="4"/>
-      <c r="J70" s="4"/>
-      <c r="K70" s="4"/>
-      <c r="L70" s="4"/>
-      <c r="M70" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="N70">
-        <v>2</v>
-      </c>
-      <c r="O70" t="s">
-        <v>126</v>
-      </c>
-      <c r="P70" s="7"/>
-    </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B71" s="4"/>
-      <c r="C71" s="4"/>
-      <c r="D71" s="4"/>
-      <c r="E71" s="4"/>
-      <c r="F71" s="4"/>
-      <c r="G71" s="4"/>
-      <c r="H71" s="4"/>
-      <c r="I71" s="4"/>
-      <c r="J71" s="4"/>
-      <c r="K71" s="4"/>
-      <c r="L71" s="4"/>
-      <c r="M71" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="N71">
-        <v>0.2</v>
-      </c>
-      <c r="O71" t="s">
-        <v>15</v>
-      </c>
-      <c r="P71" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B72" s="4"/>
-      <c r="C72" s="4"/>
-      <c r="D72" s="4"/>
-      <c r="E72" s="4"/>
-      <c r="F72" s="4"/>
-      <c r="G72" s="4"/>
-      <c r="H72" s="4"/>
-      <c r="I72" s="4"/>
-      <c r="J72" s="4"/>
-      <c r="K72" s="4"/>
-      <c r="L72" s="4"/>
-      <c r="M72" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="N72">
-        <v>3.5000000000000003E-2</v>
-      </c>
-      <c r="O72" t="s">
-        <v>17</v>
-      </c>
-      <c r="P72" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B73" s="4"/>
-      <c r="C73" s="4"/>
-      <c r="D73" s="4"/>
-      <c r="E73" s="4"/>
-      <c r="F73" s="4"/>
-      <c r="G73" s="4"/>
-      <c r="H73" s="4"/>
-      <c r="I73" s="4"/>
-      <c r="J73" s="4"/>
-      <c r="K73" s="4"/>
-      <c r="L73" s="4"/>
-      <c r="M73" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N73">
-        <v>250</v>
-      </c>
-      <c r="O73" t="s">
-        <v>19</v>
-      </c>
-      <c r="P73" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B74" s="4"/>
-      <c r="C74" s="4"/>
-      <c r="D74" s="4"/>
-      <c r="E74" s="4"/>
-      <c r="F74" s="4"/>
-      <c r="G74" s="4"/>
-      <c r="H74" s="4"/>
-      <c r="I74" s="4"/>
-      <c r="J74" s="4"/>
-      <c r="K74" s="4"/>
-      <c r="L74" s="4"/>
-      <c r="M74" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="N74" s="9">
-        <v>1</v>
-      </c>
-      <c r="O74" s="9"/>
-      <c r="P74" s="21" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="75" spans="1:17" ht="18" x14ac:dyDescent="0.35">
-      <c r="B75" s="4"/>
-      <c r="C75" s="4"/>
-      <c r="D75" s="4"/>
-      <c r="E75" s="4"/>
-      <c r="F75" s="4"/>
-      <c r="G75" s="4"/>
-      <c r="H75" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="I75" s="4"/>
-      <c r="J75" s="4"/>
-      <c r="K75" s="4"/>
-      <c r="L75" s="4"/>
-      <c r="M75" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="N75">
-        <v>0.26</v>
-      </c>
-      <c r="P75" s="5" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="76" spans="1:17" ht="18" x14ac:dyDescent="0.35">
-      <c r="B76" s="4"/>
-      <c r="C76" s="4"/>
-      <c r="D76" s="4"/>
-      <c r="E76" s="4"/>
-      <c r="F76" s="4"/>
-      <c r="G76" s="4"/>
-      <c r="H76" s="4" t="s">
-        <v>326</v>
-      </c>
-      <c r="I76" s="4"/>
-      <c r="J76" s="4"/>
-      <c r="K76" s="4"/>
-      <c r="L76" s="4"/>
-      <c r="M76" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="N76">
-        <v>0.26</v>
-      </c>
-      <c r="P76" s="5" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="77" spans="1:17" ht="18" x14ac:dyDescent="0.35">
+      <c r="B76" s="2"/>
+      <c r="C76" s="2"/>
+      <c r="D76" s="2"/>
+      <c r="E76" s="2"/>
+      <c r="F76" s="2"/>
+      <c r="G76" s="2"/>
+      <c r="H76" s="2"/>
+      <c r="I76" s="2"/>
+      <c r="J76" s="2"/>
+      <c r="K76" s="2"/>
+      <c r="L76" s="2"/>
+      <c r="M76" s="3"/>
+      <c r="N76" s="3"/>
+      <c r="O76" s="3"/>
+      <c r="P76" s="3"/>
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B77" s="4"/>
       <c r="C77" s="4"/>
       <c r="D77" s="4"/>
       <c r="E77" s="4"/>
       <c r="F77" s="4"/>
       <c r="G77" s="4"/>
-      <c r="H77" s="4" t="s">
-        <v>327</v>
-      </c>
+      <c r="H77" s="4"/>
       <c r="I77" s="4"/>
       <c r="J77" s="4"/>
       <c r="K77" s="4"/>
       <c r="L77" s="4"/>
-      <c r="M77" s="6" t="s">
-        <v>50</v>
+      <c r="M77" s="4" t="s">
+        <v>9</v>
       </c>
       <c r="N77">
-        <v>0.45</v>
-      </c>
-      <c r="P77" s="5" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="78" spans="1:17" ht="18" x14ac:dyDescent="0.35">
+        <v>10800</v>
+      </c>
+      <c r="O77" t="s">
+        <v>11</v>
+      </c>
+      <c r="P77" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
       <c r="D78" s="4"/>
       <c r="E78" s="4"/>
       <c r="F78" s="4"/>
       <c r="G78" s="4"/>
-      <c r="H78" s="6" t="s">
-        <v>328</v>
-      </c>
-      <c r="I78" s="6"/>
-      <c r="J78" s="6"/>
-      <c r="K78" s="6"/>
-      <c r="L78" s="6"/>
-      <c r="M78" s="6" t="s">
-        <v>50</v>
+      <c r="H78" s="4"/>
+      <c r="I78" s="4"/>
+      <c r="J78" s="4"/>
+      <c r="K78" s="4"/>
+      <c r="L78" s="4"/>
+      <c r="M78" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="N78">
-        <v>0.76</v>
-      </c>
-      <c r="P78" s="5" t="s">
-        <v>51</v>
+        <v>5</v>
+      </c>
+      <c r="O78" t="s">
+        <v>13</v>
+      </c>
+      <c r="P78" s="4" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.25">
@@ -4069,442 +4183,529 @@
       <c r="K79" s="4"/>
       <c r="L79" s="4"/>
       <c r="M79" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="N79">
+        <v>2</v>
+      </c>
+      <c r="O79" t="s">
+        <v>126</v>
+      </c>
+      <c r="P79" s="7"/>
+    </row>
+    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B80" s="4"/>
+      <c r="C80" s="4"/>
+      <c r="D80" s="4"/>
+      <c r="E80" s="4"/>
+      <c r="F80" s="4"/>
+      <c r="G80" s="4"/>
+      <c r="H80" s="4"/>
+      <c r="I80" s="4"/>
+      <c r="J80" s="4"/>
+      <c r="K80" s="4"/>
+      <c r="L80" s="4"/>
+      <c r="M80" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="N80">
+        <v>0.2</v>
+      </c>
+      <c r="O80" t="s">
+        <v>15</v>
+      </c>
+      <c r="P80" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="81" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B81" s="4"/>
+      <c r="C81" s="4"/>
+      <c r="D81" s="4"/>
+      <c r="E81" s="4"/>
+      <c r="F81" s="4"/>
+      <c r="G81" s="4"/>
+      <c r="H81" s="4"/>
+      <c r="I81" s="4"/>
+      <c r="J81" s="4"/>
+      <c r="K81" s="4"/>
+      <c r="L81" s="4"/>
+      <c r="M81" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="N81">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="O81" t="s">
+        <v>17</v>
+      </c>
+      <c r="P81" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="82" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B82" s="4"/>
+      <c r="C82" s="4"/>
+      <c r="D82" s="4"/>
+      <c r="E82" s="4"/>
+      <c r="F82" s="4"/>
+      <c r="G82" s="4"/>
+      <c r="H82" s="4"/>
+      <c r="I82" s="4"/>
+      <c r="J82" s="4"/>
+      <c r="K82" s="4"/>
+      <c r="L82" s="4"/>
+      <c r="M82" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N82">
+        <v>250</v>
+      </c>
+      <c r="O82" t="s">
+        <v>19</v>
+      </c>
+      <c r="P82" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="83" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B83" s="4"/>
+      <c r="C83" s="4"/>
+      <c r="D83" s="4"/>
+      <c r="E83" s="4"/>
+      <c r="F83" s="4"/>
+      <c r="G83" s="4"/>
+      <c r="H83" s="4"/>
+      <c r="I83" s="4"/>
+      <c r="J83" s="4"/>
+      <c r="K83" s="4"/>
+      <c r="L83" s="4"/>
+      <c r="M83" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="N83" s="9">
+        <v>1</v>
+      </c>
+      <c r="O83" s="9"/>
+      <c r="P83" s="21" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="84" spans="1:21" ht="18" x14ac:dyDescent="0.35">
+      <c r="B84" s="4"/>
+      <c r="C84" s="4"/>
+      <c r="D84" s="4"/>
+      <c r="E84" s="4"/>
+      <c r="F84" s="4"/>
+      <c r="G84" s="4"/>
+      <c r="H84" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="I84" s="4"/>
+      <c r="J84" s="4"/>
+      <c r="K84" s="4"/>
+      <c r="L84" s="4"/>
+      <c r="M84" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="N84">
+        <v>0.26</v>
+      </c>
+      <c r="P84" s="5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="85" spans="1:21" ht="18" x14ac:dyDescent="0.35">
+      <c r="B85" s="4"/>
+      <c r="C85" s="4"/>
+      <c r="D85" s="4"/>
+      <c r="E85" s="4"/>
+      <c r="F85" s="4"/>
+      <c r="G85" s="4"/>
+      <c r="H85" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="I85" s="4"/>
+      <c r="J85" s="4"/>
+      <c r="K85" s="4"/>
+      <c r="L85" s="4"/>
+      <c r="M85" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="N85">
+        <v>0.26</v>
+      </c>
+      <c r="P85" s="5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="86" spans="1:21" ht="18" x14ac:dyDescent="0.35">
+      <c r="B86" s="4"/>
+      <c r="C86" s="4"/>
+      <c r="D86" s="4"/>
+      <c r="E86" s="4"/>
+      <c r="F86" s="4"/>
+      <c r="G86" s="4"/>
+      <c r="H86" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="I86" s="4"/>
+      <c r="J86" s="4"/>
+      <c r="K86" s="4"/>
+      <c r="L86" s="4"/>
+      <c r="M86" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="N86">
+        <v>0.45</v>
+      </c>
+      <c r="P86" s="5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="87" spans="1:21" ht="18" x14ac:dyDescent="0.35">
+      <c r="B87" s="4"/>
+      <c r="C87" s="4"/>
+      <c r="D87" s="4"/>
+      <c r="E87" s="4"/>
+      <c r="F87" s="4"/>
+      <c r="G87" s="4"/>
+      <c r="H87" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="I87" s="6"/>
+      <c r="J87" s="6"/>
+      <c r="K87" s="6"/>
+      <c r="L87" s="6"/>
+      <c r="M87" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="N87">
+        <v>0.76</v>
+      </c>
+      <c r="P87" s="5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="88" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B88" s="4"/>
+      <c r="C88" s="4"/>
+      <c r="D88" s="4"/>
+      <c r="E88" s="4"/>
+      <c r="F88" s="4"/>
+      <c r="G88" s="4"/>
+      <c r="H88" s="4"/>
+      <c r="I88" s="4"/>
+      <c r="J88" s="4"/>
+      <c r="K88" s="4"/>
+      <c r="L88" s="4"/>
+      <c r="M88" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="N79">
+      <c r="N88">
         <v>4</v>
       </c>
-      <c r="O79" t="s">
+      <c r="O88" t="s">
         <v>21</v>
       </c>
-      <c r="P79" s="7" t="s">
+      <c r="P88" s="7" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="81" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A81" s="2" t="s">
+    <row r="90" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A90" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B81" s="2"/>
-      <c r="C81" s="2"/>
-      <c r="D81" s="2"/>
-      <c r="E81" s="2"/>
-      <c r="F81" s="2"/>
-      <c r="G81" s="2"/>
-      <c r="H81" s="2"/>
-      <c r="I81" s="2"/>
-      <c r="J81" s="2"/>
-      <c r="K81" s="2"/>
-      <c r="L81" s="2"/>
-      <c r="M81" s="2"/>
-      <c r="N81" s="2"/>
-      <c r="O81" s="2"/>
-      <c r="P81" s="2"/>
-      <c r="Q81" s="2"/>
-    </row>
-    <row r="82" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="M82" t="s">
+      <c r="B90" s="2"/>
+      <c r="C90" s="2"/>
+      <c r="D90" s="2"/>
+      <c r="E90" s="2"/>
+      <c r="F90" s="2"/>
+      <c r="G90" s="2"/>
+      <c r="H90" s="2"/>
+      <c r="I90" s="2"/>
+      <c r="J90" s="2"/>
+      <c r="K90" s="2"/>
+      <c r="L90" s="2"/>
+      <c r="M90" s="2"/>
+      <c r="N90" s="2"/>
+      <c r="O90" s="2"/>
+      <c r="P90" s="2"/>
+      <c r="Q90" s="2"/>
+    </row>
+    <row r="91" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="M91" t="s">
         <v>127</v>
       </c>
-      <c r="N82">
+      <c r="N91">
         <v>4</v>
       </c>
-      <c r="O82" t="s">
+      <c r="O91" t="s">
         <v>29</v>
       </c>
-      <c r="P82" t="s">
+      <c r="P91" t="s">
         <v>28</v>
       </c>
-      <c r="U82" s="6"/>
-    </row>
-    <row r="83" spans="1:21" ht="18" x14ac:dyDescent="0.35">
-      <c r="M83" t="s">
+      <c r="U91" s="6"/>
+    </row>
+    <row r="92" spans="1:21" ht="18" x14ac:dyDescent="0.35">
+      <c r="M92" t="s">
         <v>45</v>
       </c>
-      <c r="N83">
+      <c r="N92">
         <v>0.9</v>
       </c>
-      <c r="P83" t="s">
+      <c r="P92" t="s">
         <v>30</v>
       </c>
-      <c r="U83" s="6"/>
-    </row>
-    <row r="84" spans="1:21" ht="18" x14ac:dyDescent="0.35">
-      <c r="M84" t="s">
+      <c r="U92" s="6"/>
+    </row>
+    <row r="93" spans="1:21" ht="18" x14ac:dyDescent="0.35">
+      <c r="M93" t="s">
         <v>38</v>
       </c>
-      <c r="N84">
+      <c r="N93">
         <v>1.2250000000000001</v>
       </c>
-      <c r="O84" t="s">
+      <c r="O93" t="s">
         <v>32</v>
       </c>
-      <c r="P84" t="s">
+      <c r="P93" t="s">
         <v>31</v>
       </c>
-      <c r="U84" s="6"/>
-    </row>
-    <row r="85" spans="1:21" ht="18" x14ac:dyDescent="0.35">
-      <c r="M85" t="s">
+      <c r="U93" s="6"/>
+    </row>
+    <row r="94" spans="1:21" ht="18" x14ac:dyDescent="0.35">
+      <c r="M94" t="s">
         <v>39</v>
       </c>
-      <c r="N85">
+      <c r="N94">
         <v>0.1</v>
       </c>
-      <c r="P85" t="s">
+      <c r="P94" t="s">
         <v>33</v>
       </c>
-      <c r="U85" s="6"/>
-    </row>
-    <row r="86" spans="1:21" ht="18" x14ac:dyDescent="0.35">
-      <c r="M86" t="s">
+      <c r="U94" s="6"/>
+    </row>
+    <row r="95" spans="1:21" ht="18" x14ac:dyDescent="0.35">
+      <c r="M95" t="s">
         <v>40</v>
       </c>
-      <c r="N86">
+      <c r="N95">
         <v>0.01</v>
       </c>
-      <c r="P86" t="s">
+      <c r="P95" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="87" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="M87" t="s">
+    <row r="96" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="M96" t="s">
         <v>41</v>
       </c>
-      <c r="N87">
+      <c r="N96">
         <v>0.2</v>
       </c>
-      <c r="P87" t="s">
+      <c r="P96" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="88" spans="1:21" ht="18" x14ac:dyDescent="0.35">
-      <c r="M88" t="s">
+    <row r="97" spans="1:20" ht="18" x14ac:dyDescent="0.35">
+      <c r="M97" t="s">
         <v>42</v>
       </c>
-      <c r="N88">
+      <c r="N97">
         <v>0.8</v>
       </c>
-      <c r="P88" t="s">
+      <c r="P97" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="89" spans="1:21" ht="18" x14ac:dyDescent="0.35">
-      <c r="M89" t="s">
+    <row r="98" spans="1:20" ht="18" x14ac:dyDescent="0.35">
+      <c r="M98" t="s">
         <v>43</v>
       </c>
-      <c r="N89">
+      <c r="N98">
         <v>55</v>
       </c>
-      <c r="P89" t="s">
+      <c r="P98" t="s">
         <v>37</v>
       </c>
-      <c r="T89" s="4"/>
-    </row>
-    <row r="91" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A91" s="1" t="s">
+      <c r="T98" s="4"/>
+    </row>
+    <row r="100" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A100" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B91" s="8"/>
-      <c r="C91" s="8"/>
-      <c r="D91" s="8"/>
-      <c r="E91" s="8"/>
-      <c r="F91" s="8"/>
-      <c r="G91" s="8"/>
-      <c r="H91" s="8"/>
-      <c r="I91" s="8"/>
-      <c r="J91" s="8"/>
-      <c r="K91" s="8"/>
-      <c r="L91" s="8"/>
-      <c r="M91" s="8"/>
-      <c r="N91" s="8"/>
-      <c r="O91" s="8"/>
-      <c r="P91" s="8"/>
-      <c r="Q91" s="8"/>
-    </row>
-    <row r="92" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="M92" s="9" t="s">
+      <c r="B100" s="8"/>
+      <c r="C100" s="8"/>
+      <c r="D100" s="8"/>
+      <c r="E100" s="8"/>
+      <c r="F100" s="8"/>
+      <c r="G100" s="8"/>
+      <c r="H100" s="8"/>
+      <c r="I100" s="8"/>
+      <c r="J100" s="8"/>
+      <c r="K100" s="8"/>
+      <c r="L100" s="8"/>
+      <c r="M100" s="8"/>
+      <c r="N100" s="8"/>
+      <c r="O100" s="8"/>
+      <c r="P100" s="8"/>
+      <c r="Q100" s="8"/>
+    </row>
+    <row r="101" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="M101" s="9" t="s">
         <v>76</v>
-      </c>
-      <c r="N92" s="9">
-        <v>0</v>
-      </c>
-      <c r="O92" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="P92" s="9"/>
-    </row>
-    <row r="93" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="M93" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="N93" s="9">
-        <v>0</v>
-      </c>
-      <c r="O93" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="P93" s="9"/>
-    </row>
-    <row r="94" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="M94" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="N94" s="9">
-        <v>0</v>
-      </c>
-      <c r="O94" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="P94" s="9"/>
-    </row>
-    <row r="95" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="M95" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="N95" s="9">
-        <v>0</v>
-      </c>
-      <c r="O95" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="P95" s="9"/>
-    </row>
-    <row r="96" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="M96" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="N96" s="9">
-        <v>0</v>
-      </c>
-      <c r="O96" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="P96" s="9"/>
-    </row>
-    <row r="97" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="M97" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="N97" s="9">
-        <v>1</v>
-      </c>
-      <c r="O97" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="P97" s="9" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="98" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="M98" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="N98" s="9">
-        <v>0</v>
-      </c>
-      <c r="O98" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="P98" s="9"/>
-    </row>
-    <row r="99" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="M99" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="N99" s="9">
-        <v>0</v>
-      </c>
-      <c r="O99" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="P99" s="9"/>
-    </row>
-    <row r="100" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="M100" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="N100" s="9">
-        <v>0</v>
-      </c>
-      <c r="O100" s="9" t="s">
-        <v>334</v>
-      </c>
-      <c r="P100" s="9"/>
-    </row>
-    <row r="101" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="M101" s="9" t="s">
-        <v>58</v>
       </c>
       <c r="N101" s="9">
         <v>0</v>
       </c>
       <c r="O101" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="P101" s="9"/>
+    </row>
+    <row r="102" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="M102" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="N102" s="9">
+        <v>0</v>
+      </c>
+      <c r="O102" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="P102" s="9"/>
+    </row>
+    <row r="103" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="M103" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="N103" s="9">
+        <v>0</v>
+      </c>
+      <c r="O103" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="P103" s="9"/>
+    </row>
+    <row r="104" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="M104" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="N104" s="9">
+        <v>0</v>
+      </c>
+      <c r="O104" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="P104" s="9"/>
+    </row>
+    <row r="105" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="M105" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="N105" s="9">
+        <v>0</v>
+      </c>
+      <c r="O105" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="P105" s="9"/>
+    </row>
+    <row r="106" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="M106" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="N106" s="9">
+        <v>1</v>
+      </c>
+      <c r="O106" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="P106" s="9" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="107" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="M107" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="N107" s="9">
+        <v>0</v>
+      </c>
+      <c r="O107" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="P107" s="9"/>
+    </row>
+    <row r="108" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="M108" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="N108" s="9">
+        <v>0</v>
+      </c>
+      <c r="O108" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="P108" s="9"/>
+    </row>
+    <row r="109" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="M109" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="N109" s="9">
+        <v>0</v>
+      </c>
+      <c r="O109" s="9" t="s">
+        <v>334</v>
+      </c>
+      <c r="P109" s="9"/>
+    </row>
+    <row r="110" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="M110" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="N110" s="9">
+        <v>0</v>
+      </c>
+      <c r="O110" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="P101" s="9"/>
-    </row>
-    <row r="102" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="M102" s="9"/>
-      <c r="N102" s="9"/>
-      <c r="O102" s="9"/>
-      <c r="P102" s="9"/>
-    </row>
-    <row r="103" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="I103" t="s">
+      <c r="P110" s="9"/>
+    </row>
+    <row r="111" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="M111" s="9"/>
+      <c r="N111" s="9"/>
+      <c r="O111" s="9"/>
+      <c r="P111" s="9"/>
+    </row>
+    <row r="112" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="I112" t="s">
         <v>60</v>
       </c>
-      <c r="M103" s="10" t="s">
+      <c r="M112" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="N103" s="10">
+      <c r="N112" s="10">
         <v>364</v>
       </c>
-      <c r="O103" s="10"/>
-      <c r="P103" s="10" t="s">
+      <c r="O112" s="10"/>
+      <c r="P112" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="Q103" s="10"/>
-    </row>
-    <row r="104" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="I104" t="s">
-        <v>60</v>
-      </c>
-      <c r="M104" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="N104" s="10">
-        <v>18.8</v>
-      </c>
-      <c r="O104" s="10"/>
-      <c r="P104" s="10"/>
-      <c r="Q104" s="10"/>
-    </row>
-    <row r="105" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="I105" t="s">
-        <v>60</v>
-      </c>
-      <c r="M105" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="N105" s="10">
-        <v>0</v>
-      </c>
-      <c r="O105" s="10"/>
-      <c r="P105" s="10"/>
-      <c r="Q105" s="10"/>
-    </row>
-    <row r="106" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="I106" t="s">
-        <v>60</v>
-      </c>
-      <c r="M106" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="N106" s="10">
-        <v>10</v>
-      </c>
-      <c r="O106" s="10"/>
-      <c r="P106" s="10"/>
-      <c r="Q106" s="10"/>
-    </row>
-    <row r="107" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="I107" t="s">
-        <v>60</v>
-      </c>
-      <c r="J107" t="s">
-        <v>74</v>
-      </c>
-      <c r="M107" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="N107" s="12">
-        <v>1</v>
-      </c>
-      <c r="O107" s="10"/>
-      <c r="P107" s="10"/>
-      <c r="Q107" s="10"/>
-    </row>
-    <row r="108" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="I108" t="s">
-        <v>60</v>
-      </c>
-      <c r="J108" t="s">
-        <v>73</v>
-      </c>
-      <c r="M108" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="N108" s="10">
-        <v>0.88</v>
-      </c>
-      <c r="O108" s="10"/>
-      <c r="P108" s="10"/>
-      <c r="Q108" s="10"/>
-    </row>
-    <row r="109" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="I109" t="s">
-        <v>60</v>
-      </c>
-      <c r="J109" t="s">
-        <v>72</v>
-      </c>
-      <c r="M109" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="N109" s="10">
-        <v>0.78</v>
-      </c>
-      <c r="O109" s="10"/>
-      <c r="P109" s="10"/>
-      <c r="Q109" s="10"/>
-    </row>
-    <row r="110" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="M110" s="10"/>
-      <c r="N110" s="10"/>
-      <c r="O110" s="10"/>
-      <c r="P110" s="10"/>
-      <c r="Q110" s="10"/>
-    </row>
-    <row r="111" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="I111" t="s">
-        <v>63</v>
-      </c>
-      <c r="M111" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="N111" s="10">
-        <v>652</v>
-      </c>
-      <c r="O111" s="10"/>
-      <c r="P111" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q111" s="10"/>
-    </row>
-    <row r="112" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="I112" t="s">
-        <v>63</v>
-      </c>
-      <c r="M112" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="N112" s="10">
-        <v>0</v>
-      </c>
-      <c r="O112" s="10"/>
-      <c r="P112" s="10"/>
       <c r="Q112" s="10"/>
     </row>
     <row r="113" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I113" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="M113" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N113" s="10">
-        <v>5.0999999999999996</v>
+        <v>18.8</v>
       </c>
       <c r="O113" s="10"/>
       <c r="P113" s="10"/>
@@ -4512,13 +4713,13 @@
     </row>
     <row r="114" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I114" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="M114" s="10" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="N114" s="10">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="O114" s="10"/>
       <c r="P114" s="10"/>
@@ -4526,16 +4727,13 @@
     </row>
     <row r="115" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I115" t="s">
-        <v>63</v>
-      </c>
-      <c r="J115" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="M115" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="N115" s="12">
-        <v>1</v>
+        <v>75</v>
+      </c>
+      <c r="N115" s="10">
+        <v>10</v>
       </c>
       <c r="O115" s="10"/>
       <c r="P115" s="10"/>
@@ -4543,16 +4741,16 @@
     </row>
     <row r="116" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I116" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="J116" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M116" s="10" t="s">
         <v>79</v>
       </c>
       <c r="N116" s="12">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="O116" s="10"/>
       <c r="P116" s="10"/>
@@ -4560,64 +4758,67 @@
     </row>
     <row r="117" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I117" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="J117" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M117" s="10" t="s">
         <v>79</v>
       </c>
       <c r="N117" s="10">
-        <v>0.45</v>
+        <v>0.88</v>
       </c>
       <c r="O117" s="10"/>
       <c r="P117" s="10"/>
       <c r="Q117" s="10"/>
     </row>
     <row r="118" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="M118" s="10"/>
-      <c r="N118" s="10"/>
+      <c r="I118" t="s">
+        <v>60</v>
+      </c>
+      <c r="J118" t="s">
+        <v>72</v>
+      </c>
+      <c r="M118" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="N118" s="10">
+        <v>0.78</v>
+      </c>
       <c r="O118" s="10"/>
       <c r="P118" s="10"/>
       <c r="Q118" s="10"/>
     </row>
     <row r="119" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="I119" t="s">
-        <v>62</v>
-      </c>
-      <c r="M119" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="N119" s="10">
-        <v>46</v>
-      </c>
+      <c r="M119" s="10"/>
+      <c r="N119" s="10"/>
       <c r="O119" s="10"/>
-      <c r="P119" s="10" t="s">
-        <v>83</v>
-      </c>
+      <c r="P119" s="10"/>
       <c r="Q119" s="10"/>
     </row>
     <row r="120" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I120" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M120" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N120" s="10">
-        <v>2.8</v>
+        <v>652</v>
       </c>
       <c r="O120" s="10"/>
-      <c r="P120" s="10"/>
+      <c r="P120" s="10" t="s">
+        <v>82</v>
+      </c>
       <c r="Q120" s="10"/>
     </row>
     <row r="121" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I121" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M121" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N121" s="10">
         <v>0</v>
@@ -4628,13 +4829,13 @@
     </row>
     <row r="122" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I122" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M122" s="10" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="N122" s="10">
-        <v>5</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="O122" s="10"/>
       <c r="P122" s="10"/>
@@ -4642,16 +4843,13 @@
     </row>
     <row r="123" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I123" t="s">
-        <v>62</v>
-      </c>
-      <c r="J123" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="M123" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="N123" s="12">
-        <v>1</v>
+        <v>75</v>
+      </c>
+      <c r="N123" s="10">
+        <v>20</v>
       </c>
       <c r="O123" s="10"/>
       <c r="P123" s="10"/>
@@ -4659,16 +4857,16 @@
     </row>
     <row r="124" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I124" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J124" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M124" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="N124" s="10">
-        <v>0.85</v>
+      <c r="N124" s="12">
+        <v>1</v>
       </c>
       <c r="O124" s="10"/>
       <c r="P124" s="10"/>
@@ -4676,1412 +4874,1775 @@
     </row>
     <row r="125" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I125" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J125" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M125" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="N125" s="10">
-        <v>0.65</v>
+      <c r="N125" s="12">
+        <v>0.7</v>
       </c>
       <c r="O125" s="10"/>
       <c r="P125" s="10"/>
       <c r="Q125" s="10"/>
     </row>
     <row r="126" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="M126" s="10"/>
-      <c r="N126" s="10"/>
+      <c r="I126" t="s">
+        <v>63</v>
+      </c>
+      <c r="J126" t="s">
+        <v>72</v>
+      </c>
+      <c r="M126" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="N126" s="10">
+        <v>0.45</v>
+      </c>
       <c r="O126" s="10"/>
       <c r="P126" s="10"/>
       <c r="Q126" s="10"/>
     </row>
     <row r="127" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="I127" t="s">
-        <v>65</v>
-      </c>
-      <c r="M127" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="N127" s="12">
-        <v>5.0999999999999996</v>
-      </c>
+      <c r="M127" s="10"/>
+      <c r="N127" s="10"/>
       <c r="O127" s="10"/>
-      <c r="P127" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="Q127" s="4" t="s">
-        <v>96</v>
-      </c>
+      <c r="P127" s="10"/>
+      <c r="Q127" s="10"/>
     </row>
     <row r="128" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I128" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="M128" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="N128" s="12">
-        <v>7.1</v>
+        <v>76</v>
+      </c>
+      <c r="N128" s="10">
+        <v>46</v>
       </c>
       <c r="O128" s="10"/>
-      <c r="P128" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="Q128" s="4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="129" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="M129" s="10"/>
-      <c r="N129" s="10"/>
+      <c r="P128" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q128" s="10"/>
+    </row>
+    <row r="129" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="I129" t="s">
+        <v>62</v>
+      </c>
+      <c r="M129" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="N129" s="10">
+        <v>2.8</v>
+      </c>
       <c r="O129" s="10"/>
       <c r="P129" s="10"/>
       <c r="Q129" s="10"/>
     </row>
-    <row r="130" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="130" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I130" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M130" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="N130" s="12">
-        <v>3.7353333333333332</v>
+        <v>78</v>
+      </c>
+      <c r="N130" s="10">
+        <v>0</v>
       </c>
       <c r="O130" s="10"/>
-      <c r="P130" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q130" s="6" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="131" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="P130" s="10"/>
+      <c r="Q130" s="10"/>
+    </row>
+    <row r="131" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I131" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="M131" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="N131" s="11">
-        <v>17.096931944444446</v>
+        <v>75</v>
+      </c>
+      <c r="N131" s="10">
+        <v>5</v>
       </c>
       <c r="O131" s="10"/>
-      <c r="P131" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q131" s="4" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="132" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="P131" s="10"/>
+      <c r="Q131" s="10"/>
+    </row>
+    <row r="132" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I132" t="s">
-        <v>67</v>
+        <v>62</v>
+      </c>
+      <c r="J132" t="s">
+        <v>74</v>
       </c>
       <c r="M132" s="10" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="N132" s="12">
-        <v>1.2451111111111113</v>
+        <v>1</v>
       </c>
       <c r="O132" s="10"/>
-      <c r="P132" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q132" s="10" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="133" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="P132" s="10"/>
+      <c r="Q132" s="10"/>
+    </row>
+    <row r="133" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I133" t="s">
-        <v>68</v>
+        <v>62</v>
+      </c>
+      <c r="J133" t="s">
+        <v>73</v>
       </c>
       <c r="M133" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="N133" s="12">
-        <v>3.1127777777777781</v>
+        <v>79</v>
+      </c>
+      <c r="N133" s="10">
+        <v>0.85</v>
       </c>
       <c r="O133" s="10"/>
-      <c r="P133" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q133" s="10" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="134" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="P133" s="10"/>
+      <c r="Q133" s="10"/>
+    </row>
+    <row r="134" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I134" t="s">
-        <v>97</v>
+        <v>62</v>
+      </c>
+      <c r="J134" t="s">
+        <v>72</v>
       </c>
       <c r="M134" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="N134" s="12">
-        <v>4.6691666666666665</v>
+        <v>79</v>
+      </c>
+      <c r="N134" s="10">
+        <v>0.65</v>
       </c>
       <c r="O134" s="10"/>
-      <c r="P134" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q134" s="10" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="135" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="I135" t="s">
-        <v>69</v>
-      </c>
-      <c r="M135" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="N135" s="12">
-        <v>3.1127777777777781</v>
-      </c>
+      <c r="P134" s="10"/>
+      <c r="Q134" s="10"/>
+    </row>
+    <row r="135" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="M135" s="10"/>
+      <c r="N135" s="10"/>
       <c r="O135" s="10"/>
-      <c r="P135" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q135" s="6" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="136" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="P135" s="10"/>
+      <c r="Q135" s="10"/>
+    </row>
+    <row r="136" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I136" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="M136" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="N136" s="11">
-        <v>11.828555555555555</v>
+        <v>92</v>
+      </c>
+      <c r="N136" s="12">
+        <v>5.0999999999999996</v>
       </c>
       <c r="O136" s="10"/>
-      <c r="P136" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q136" s="10" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="137" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="P136" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q136" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="137" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I137" t="s">
-        <v>100</v>
+        <v>66</v>
       </c>
       <c r="M137" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="N137" s="11">
-        <v>26.302972222222223</v>
+        <v>92</v>
+      </c>
+      <c r="N137" s="12">
+        <v>7.1</v>
       </c>
       <c r="O137" s="10"/>
       <c r="P137" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q137" s="10" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="138" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="I138" t="s">
-        <v>101</v>
-      </c>
-      <c r="M138" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="N138" s="11">
-        <v>11.3</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="Q137" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="138" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="M138" s="10"/>
+      <c r="N138" s="10"/>
       <c r="O138" s="10"/>
-      <c r="P138" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="Q138" s="10" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="139" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="P138" s="10"/>
+      <c r="Q138" s="10"/>
+    </row>
+    <row r="139" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I139" t="s">
-        <v>102</v>
+        <v>61</v>
       </c>
       <c r="M139" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="N139" s="11">
-        <v>23.278130416666666</v>
+      <c r="N139" s="12">
+        <v>3.7353333333333332</v>
       </c>
       <c r="O139" s="10"/>
-      <c r="P139" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q139" s="10" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="140" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="P139" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q139" s="6" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="140" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I140" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="M140" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="N140" s="10">
-        <v>13.15</v>
+      <c r="N140" s="11">
+        <v>17.096931944444446</v>
       </c>
       <c r="O140" s="10"/>
-      <c r="P140" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="Q140" s="10" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="141" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="P140" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q140" s="4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="141" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I141" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="M141" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="N141" s="10">
-        <v>5.26</v>
+        <v>54</v>
+      </c>
+      <c r="N141" s="12">
+        <v>1.2451111111111113</v>
       </c>
       <c r="O141" s="10"/>
-      <c r="P141" s="10" t="s">
-        <v>109</v>
+      <c r="P141" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="Q141" s="10" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="142" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B142" t="s">
-        <v>110</v>
-      </c>
+        <v>89</v>
+      </c>
+    </row>
+    <row r="142" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I142" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="M142" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N142" s="12">
-        <v>1.7546281240590185</v>
+        <v>3.1127777777777781</v>
       </c>
       <c r="O142" s="10"/>
-      <c r="P142" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q142" s="4" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="143" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B143" t="s">
-        <v>113</v>
-      </c>
+      <c r="P142" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q142" s="10" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="143" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I143" t="s">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="M143" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N143" s="12">
-        <v>5.1828516694033944</v>
+        <v>4.6691666666666665</v>
       </c>
       <c r="O143" s="10"/>
-      <c r="P143" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q143" s="4" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="144" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B144" t="s">
-        <v>114</v>
-      </c>
+      <c r="P143" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q143" s="10" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="144" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I144" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="M144" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="N144" s="13">
-        <v>4.0531064740502947</v>
-      </c>
-      <c r="P144" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q144" s="4" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B145" t="s">
-        <v>118</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="N144" s="12">
+        <v>3.1127777777777781</v>
+      </c>
+      <c r="O144" s="10"/>
+      <c r="P144" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q144" s="6" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="145" spans="2:17" x14ac:dyDescent="0.25">
       <c r="I145" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M145" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="N145" s="13">
-        <v>4.3591310772039646</v>
-      </c>
-      <c r="P145" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q145" s="6" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M146" s="10"/>
-      <c r="N146" s="13"/>
-      <c r="P146" s="6"/>
-      <c r="Q146" s="6"/>
-    </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+      <c r="N145" s="11">
+        <v>11.828555555555555</v>
+      </c>
+      <c r="O145" s="10"/>
+      <c r="P145" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q145" s="10" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="146" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="I146" t="s">
+        <v>100</v>
+      </c>
+      <c r="M146" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="N146" s="11">
+        <v>26.302972222222223</v>
+      </c>
+      <c r="O146" s="10"/>
+      <c r="P146" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q146" s="10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="147" spans="2:17" x14ac:dyDescent="0.25">
       <c r="I147" t="s">
-        <v>120</v>
+        <v>101</v>
       </c>
       <c r="M147" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="N147" s="13">
-        <v>14.6</v>
-      </c>
-      <c r="P147" s="6"/>
-      <c r="Q147" s="4" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="N147" s="11">
+        <v>11.3</v>
+      </c>
+      <c r="O147" s="10"/>
+      <c r="P147" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q147" s="10" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="148" spans="2:17" x14ac:dyDescent="0.25">
       <c r="I148" t="s">
-        <v>124</v>
-      </c>
-      <c r="K148" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="M148" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="N148" s="13">
-        <v>37.744765138888887</v>
-      </c>
-      <c r="P148" s="6"/>
-      <c r="Q148" s="6" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="N148" s="11">
+        <v>23.278130416666666</v>
+      </c>
+      <c r="O148" s="10"/>
+      <c r="P148" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q148" s="10" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="149" spans="2:17" x14ac:dyDescent="0.25">
       <c r="I149" t="s">
-        <v>124</v>
-      </c>
-      <c r="K149" t="s">
-        <v>122</v>
+        <v>71</v>
       </c>
       <c r="M149" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="N149" s="13">
-        <v>50.107162083333336</v>
-      </c>
-      <c r="P149" s="6"/>
-      <c r="Q149" s="6" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="N149" s="10">
+        <v>13.15</v>
+      </c>
+      <c r="O149" s="10"/>
+      <c r="P149" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q149" s="10" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="150" spans="2:17" x14ac:dyDescent="0.25">
       <c r="I150" t="s">
-        <v>124</v>
-      </c>
-      <c r="K150" t="s">
-        <v>123</v>
+        <v>71</v>
       </c>
       <c r="M150" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="N150" s="13">
-        <v>36.955675972222224</v>
-      </c>
-      <c r="P150" s="6"/>
-      <c r="Q150" s="6" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M151" s="10"/>
-      <c r="N151" s="13"/>
-      <c r="P151" s="6"/>
-      <c r="Q151" s="6"/>
-    </row>
-    <row r="152" spans="1:17" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+      <c r="N150" s="10">
+        <v>5.26</v>
+      </c>
+      <c r="O150" s="10"/>
+      <c r="P150" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q150" s="10" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="151" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B151" t="s">
+        <v>110</v>
+      </c>
+      <c r="I151" t="s">
+        <v>71</v>
+      </c>
+      <c r="M151" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="N151" s="12">
+        <v>1.7546281240590185</v>
+      </c>
+      <c r="O151" s="10"/>
+      <c r="P151" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q151" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="152" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B152" t="s">
+        <v>113</v>
+      </c>
       <c r="I152" t="s">
-        <v>131</v>
+        <v>71</v>
       </c>
       <c r="M152" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="N152" s="13">
+      <c r="N152" s="12">
+        <v>5.1828516694033944</v>
+      </c>
+      <c r="O152" s="10"/>
+      <c r="P152" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q152" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="153" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B153" t="s">
+        <v>114</v>
+      </c>
+      <c r="I153" t="s">
+        <v>71</v>
+      </c>
+      <c r="M153" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="N153" s="13">
+        <v>4.0531064740502947</v>
+      </c>
+      <c r="P153" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q153" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="154" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B154" t="s">
+        <v>118</v>
+      </c>
+      <c r="I154" t="s">
+        <v>71</v>
+      </c>
+      <c r="M154" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="N154" s="13">
+        <v>4.3591310772039646</v>
+      </c>
+      <c r="P154" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q154" s="6" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="155" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="M155" s="10"/>
+      <c r="N155" s="13"/>
+      <c r="P155" s="6"/>
+      <c r="Q155" s="6"/>
+    </row>
+    <row r="156" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="I156" t="s">
+        <v>120</v>
+      </c>
+      <c r="M156" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="N156" s="13">
+        <v>14.6</v>
+      </c>
+      <c r="P156" s="6"/>
+      <c r="Q156" s="4" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="157" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="I157" t="s">
+        <v>124</v>
+      </c>
+      <c r="K157" t="s">
+        <v>121</v>
+      </c>
+      <c r="M157" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="N157" s="13">
+        <v>37.744765138888887</v>
+      </c>
+      <c r="P157" s="6"/>
+      <c r="Q157" s="6" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="158" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="I158" t="s">
+        <v>124</v>
+      </c>
+      <c r="K158" t="s">
+        <v>122</v>
+      </c>
+      <c r="M158" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="N158" s="13">
+        <v>50.107162083333336</v>
+      </c>
+      <c r="P158" s="6"/>
+      <c r="Q158" s="6" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="159" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="I159" t="s">
+        <v>124</v>
+      </c>
+      <c r="K159" t="s">
+        <v>123</v>
+      </c>
+      <c r="M159" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="N159" s="13">
+        <v>36.955675972222224</v>
+      </c>
+      <c r="P159" s="6"/>
+      <c r="Q159" s="6" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="160" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="M160" s="10"/>
+      <c r="N160" s="13"/>
+      <c r="P160" s="6"/>
+      <c r="Q160" s="6"/>
+    </row>
+    <row r="161" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="I161" t="s">
+        <v>131</v>
+      </c>
+      <c r="M161" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="N161" s="13">
         <v>1.6176327916666666</v>
       </c>
-      <c r="O152" t="s">
+      <c r="O161" t="s">
         <v>57</v>
       </c>
-      <c r="P152" s="6" t="s">
+      <c r="P161" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="Q152" s="4" t="s">
+      <c r="Q161" s="4" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="I153" t="s">
+    <row r="162" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="I162" t="s">
         <v>132</v>
       </c>
-      <c r="M153" s="10" t="s">
+      <c r="M162" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="N153" s="13">
+      <c r="N162" s="13">
         <f>3.07744775/0.85</f>
         <v>3.6205267647058825</v>
       </c>
-      <c r="O153" t="s">
+      <c r="O162" t="s">
         <v>334</v>
       </c>
-      <c r="P153" s="6" t="s">
+      <c r="P162" s="6" t="s">
         <v>335</v>
       </c>
-      <c r="Q153" s="4" t="s">
+      <c r="Q162" s="4" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="154" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="I154" t="s">
+    <row r="163" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="I163" t="s">
         <v>133</v>
       </c>
-      <c r="M154" s="10" t="s">
+      <c r="M163" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="N154" s="13">
+      <c r="N163" s="13">
         <v>0.25</v>
       </c>
-      <c r="O154" t="s">
+      <c r="O163" t="s">
         <v>59</v>
       </c>
-      <c r="P154" s="6" t="s">
+      <c r="P163" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="Q154" s="4" t="s">
+      <c r="Q163" s="4" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A156" s="1" t="s">
+    <row r="165" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A165" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B156" s="1"/>
-      <c r="C156" s="1"/>
-      <c r="D156" s="1"/>
-      <c r="E156" s="1"/>
-      <c r="F156" s="1"/>
-      <c r="G156" s="1"/>
-      <c r="H156" s="1"/>
-      <c r="I156" s="1"/>
-      <c r="J156" s="1"/>
-      <c r="K156" s="1"/>
-      <c r="L156" s="1"/>
-      <c r="M156" s="8"/>
-      <c r="N156" s="8"/>
-      <c r="O156" s="8"/>
-      <c r="P156" s="8"/>
-      <c r="Q156" s="8"/>
-    </row>
-    <row r="157" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M157" s="9" t="s">
+      <c r="B165" s="1"/>
+      <c r="C165" s="1"/>
+      <c r="D165" s="1"/>
+      <c r="E165" s="1"/>
+      <c r="F165" s="1"/>
+      <c r="G165" s="1"/>
+      <c r="H165" s="1"/>
+      <c r="I165" s="1"/>
+      <c r="J165" s="1"/>
+      <c r="K165" s="1"/>
+      <c r="L165" s="1"/>
+      <c r="M165" s="8"/>
+      <c r="N165" s="8"/>
+      <c r="O165" s="8"/>
+      <c r="P165" s="8"/>
+      <c r="Q165" s="8"/>
+    </row>
+    <row r="166" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M166" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="N157" s="9">
+      <c r="N166" s="9">
         <v>0</v>
       </c>
-      <c r="P157" s="9" t="s">
+      <c r="P166" s="9" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="158" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M158" t="s">
+    <row r="167" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M167" t="s">
         <v>49</v>
       </c>
-      <c r="N158" t="s">
+      <c r="N167" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="160" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A160" s="1" t="s">
+    <row r="169" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A169" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="B160" s="1"/>
-      <c r="C160" s="1"/>
-      <c r="D160" s="1"/>
-      <c r="E160" s="1"/>
-      <c r="F160" s="1"/>
-      <c r="G160" s="1"/>
-      <c r="H160" s="1"/>
-      <c r="I160" s="1"/>
-      <c r="J160" s="1"/>
-      <c r="K160" s="1"/>
-      <c r="L160" s="1"/>
-      <c r="M160" s="8"/>
-      <c r="N160" s="8"/>
-      <c r="O160" s="8"/>
-      <c r="P160" s="8"/>
-      <c r="Q160" s="8"/>
-    </row>
-    <row r="162" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="M162" s="9" t="s">
+      <c r="B169" s="1"/>
+      <c r="C169" s="1"/>
+      <c r="D169" s="1"/>
+      <c r="E169" s="1"/>
+      <c r="F169" s="1"/>
+      <c r="G169" s="1"/>
+      <c r="H169" s="1"/>
+      <c r="I169" s="1"/>
+      <c r="J169" s="1"/>
+      <c r="K169" s="1"/>
+      <c r="L169" s="1"/>
+      <c r="M169" s="8"/>
+      <c r="N169" s="8"/>
+      <c r="O169" s="8"/>
+      <c r="P169" s="8"/>
+      <c r="Q169" s="8"/>
+    </row>
+    <row r="171" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M171" s="9" t="s">
         <v>336</v>
       </c>
-      <c r="N162" s="9">
+      <c r="N171" s="9">
         <v>100</v>
       </c>
-      <c r="O162" s="9" t="s">
+      <c r="O171" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="P162" s="9" t="s">
+      <c r="P171" s="9" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="163" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="H163" s="6" t="s">
+    <row r="172" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H172" s="6" t="s">
         <v>330</v>
       </c>
-      <c r="M163" t="s">
+      <c r="M172" t="s">
         <v>336</v>
       </c>
-      <c r="N163">
+      <c r="N172">
         <v>88</v>
       </c>
-      <c r="O163" t="s">
+      <c r="O172" t="s">
         <v>128</v>
       </c>
-      <c r="P163" t="s">
+      <c r="P172" t="s">
         <v>337</v>
       </c>
-      <c r="Q163" t="s">
+      <c r="Q172" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="164" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="H164" s="6" t="s">
+    <row r="173" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H173" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="M164" t="s">
+      <c r="M173" t="s">
         <v>336</v>
       </c>
-      <c r="N164">
+      <c r="N173">
         <v>90</v>
       </c>
-      <c r="O164" t="s">
+      <c r="O173" t="s">
         <v>128</v>
       </c>
-      <c r="Q164" t="s">
+      <c r="Q173" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="165" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="H165" s="6"/>
-    </row>
-    <row r="166" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="H166" s="6"/>
-      <c r="M166" t="s">
+    <row r="174" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H174" s="6"/>
+    </row>
+    <row r="175" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H175" s="6"/>
+      <c r="M175" t="s">
         <v>347</v>
       </c>
-      <c r="N166">
+      <c r="N175">
         <v>1.6E-2</v>
       </c>
-      <c r="O166" t="s">
+      <c r="O175" t="s">
         <v>229</v>
       </c>
-      <c r="P166" t="s">
+      <c r="P175" t="s">
         <v>355</v>
       </c>
-      <c r="Q166" t="s">
+      <c r="Q175" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="167" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="H167" s="6"/>
-    </row>
-    <row r="168" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="M168" t="s">
+    <row r="176" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H176" s="6"/>
+    </row>
+    <row r="177" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M177" t="s">
         <v>357</v>
       </c>
-      <c r="N168" s="13">
+      <c r="N177" s="13">
         <f>0.16*10.36*0.9</f>
         <v>1.4918400000000001</v>
       </c>
-      <c r="O168" t="s">
+      <c r="O177" t="s">
         <v>351</v>
       </c>
-      <c r="P168" t="s">
+      <c r="P177" t="s">
         <v>352</v>
       </c>
-      <c r="Q168" t="s">
+      <c r="Q177" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="171" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="M171" s="9" t="s">
+    <row r="180" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M180" s="9" t="s">
         <v>338</v>
       </c>
-      <c r="N171" s="9">
+      <c r="N180" s="9">
         <v>-99</v>
       </c>
-      <c r="O171" s="9"/>
-      <c r="P171" s="9" t="s">
+      <c r="O180" s="9"/>
+      <c r="P180" s="9" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="172" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C172" t="s">
+    <row r="181" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="C181" t="s">
         <v>341</v>
       </c>
-      <c r="M172" t="s">
+      <c r="M181" t="s">
         <v>338</v>
       </c>
-      <c r="N172">
+      <c r="N181">
         <v>17</v>
       </c>
-      <c r="O172" t="s">
+      <c r="O181" t="s">
         <v>128</v>
       </c>
-      <c r="Q172" t="s">
+      <c r="Q181" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="173" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C173" t="s">
+    <row r="182" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="C182" t="s">
         <v>342</v>
       </c>
-      <c r="M173" t="s">
+      <c r="M182" t="s">
         <v>338</v>
       </c>
-      <c r="N173">
+      <c r="N182">
         <v>17</v>
       </c>
-      <c r="O173" t="s">
+      <c r="O182" t="s">
         <v>128</v>
       </c>
-      <c r="Q173" t="s">
+      <c r="Q182" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="174" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C174" t="s">
+    <row r="183" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="C183" t="s">
         <v>343</v>
       </c>
-      <c r="M174" t="s">
+      <c r="M183" t="s">
         <v>338</v>
       </c>
-      <c r="N174">
+      <c r="N183">
         <v>17</v>
       </c>
-      <c r="O174" t="s">
+      <c r="O183" t="s">
         <v>128</v>
       </c>
-      <c r="Q174" t="s">
+      <c r="Q183" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="175" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C175" t="s">
+    <row r="184" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="C184" t="s">
         <v>344</v>
       </c>
-      <c r="M175" t="s">
+      <c r="M184" t="s">
         <v>338</v>
       </c>
-      <c r="N175">
+      <c r="N184">
         <v>14</v>
       </c>
-      <c r="O175" t="s">
+      <c r="O184" t="s">
         <v>128</v>
       </c>
-      <c r="Q175" t="s">
+      <c r="Q184" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="177" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C177" t="s">
+    <row r="186" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="C186" t="s">
         <v>341</v>
       </c>
-      <c r="M177" t="s">
+      <c r="M186" t="s">
         <v>339</v>
       </c>
-      <c r="N177">
+      <c r="N186">
         <v>14</v>
       </c>
-      <c r="O177" t="s">
+      <c r="O186" t="s">
         <v>128</v>
       </c>
-      <c r="Q177" t="s">
+      <c r="Q186" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="178" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C178" t="s">
+    <row r="187" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="C187" t="s">
         <v>342</v>
       </c>
-      <c r="M178" t="s">
+      <c r="M187" t="s">
         <v>339</v>
       </c>
-      <c r="N178">
+      <c r="N187">
         <v>14</v>
       </c>
-      <c r="O178" t="s">
+      <c r="O187" t="s">
         <v>128</v>
       </c>
-      <c r="Q178" t="s">
+      <c r="Q187" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="179" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C179" t="s">
+    <row r="188" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="C188" t="s">
         <v>343</v>
       </c>
-      <c r="M179" t="s">
+      <c r="M188" t="s">
         <v>339</v>
       </c>
-      <c r="N179">
+      <c r="N188">
         <v>14</v>
       </c>
-      <c r="O179" t="s">
+      <c r="O188" t="s">
         <v>128</v>
       </c>
-      <c r="Q179" t="s">
+      <c r="Q188" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="180" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C180" t="s">
+    <row r="189" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="C189" t="s">
         <v>344</v>
       </c>
-      <c r="M180" t="s">
+      <c r="M189" t="s">
         <v>339</v>
       </c>
-      <c r="N180">
+      <c r="N189">
         <v>9</v>
       </c>
-      <c r="O180" t="s">
+      <c r="O189" t="s">
         <v>128</v>
       </c>
-      <c r="Q180" t="s">
+      <c r="Q189" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="182" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A182" s="1" t="s">
+    <row r="191" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A191" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="B182" s="1"/>
-      <c r="C182" s="1"/>
-      <c r="D182" s="1"/>
-      <c r="E182" s="1"/>
-      <c r="F182" s="1"/>
-      <c r="G182" s="1"/>
-      <c r="H182" s="1"/>
-      <c r="I182" s="1"/>
-      <c r="J182" s="1"/>
-      <c r="K182" s="1"/>
-      <c r="L182" s="1"/>
-      <c r="M182" s="8"/>
-      <c r="N182" s="8"/>
-      <c r="O182" s="8"/>
-      <c r="P182" s="8"/>
-      <c r="Q182" s="8"/>
-    </row>
-    <row r="186" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M186" s="9" t="s">
+      <c r="B191" s="1"/>
+      <c r="C191" s="1"/>
+      <c r="D191" s="1"/>
+      <c r="E191" s="1"/>
+      <c r="F191" s="1"/>
+      <c r="G191" s="1"/>
+      <c r="H191" s="1"/>
+      <c r="I191" s="1"/>
+      <c r="J191" s="1"/>
+      <c r="K191" s="1"/>
+      <c r="L191" s="1"/>
+      <c r="M191" s="8"/>
+      <c r="N191" s="8"/>
+      <c r="O191" s="8"/>
+      <c r="P191" s="8"/>
+      <c r="Q191" s="8"/>
+    </row>
+    <row r="195" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M195" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="N186" s="9">
+      <c r="N195" s="9">
         <v>0</v>
       </c>
-      <c r="O186" s="9" t="s">
+      <c r="O195" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="P186" s="9" t="s">
+      <c r="P195" s="9" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="187" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B187" t="s">
+    <row r="196" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B196" t="s">
         <v>155</v>
       </c>
-      <c r="M187" t="s">
+      <c r="M196" t="s">
         <v>162</v>
       </c>
-      <c r="N187">
+      <c r="N196">
         <v>302</v>
       </c>
-      <c r="O187" t="s">
+      <c r="O196" t="s">
         <v>163</v>
       </c>
-      <c r="P187" t="s">
+      <c r="P196" t="s">
         <v>164</v>
       </c>
-      <c r="Q187" t="s">
+      <c r="Q196" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="188" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B188" t="s">
+    <row r="197" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B197" t="s">
         <v>156</v>
       </c>
-      <c r="M188" t="s">
+      <c r="M197" t="s">
         <v>162</v>
       </c>
-      <c r="N188">
+      <c r="N197">
         <v>197</v>
       </c>
-      <c r="O188" t="s">
+      <c r="O197" t="s">
         <v>163</v>
       </c>
-      <c r="P188" t="s">
+      <c r="P197" t="s">
         <v>165</v>
       </c>
-      <c r="Q188" t="s">
+      <c r="Q197" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="189" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B189" t="s">
+    <row r="198" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B198" t="s">
         <v>157</v>
       </c>
-      <c r="M189" t="s">
+      <c r="M198" t="s">
         <v>162</v>
       </c>
-      <c r="N189">
+      <c r="N198">
         <v>216</v>
       </c>
-      <c r="O189" t="s">
+      <c r="O198" t="s">
         <v>163</v>
       </c>
-      <c r="P189" t="s">
+      <c r="P198" t="s">
         <v>166</v>
       </c>
-      <c r="Q189" t="s">
+      <c r="Q198" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="190" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B190" t="s">
+    <row r="199" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B199" t="s">
         <v>158</v>
       </c>
-      <c r="M190" t="s">
+      <c r="M199" t="s">
         <v>162</v>
       </c>
-      <c r="N190">
+      <c r="N199">
         <v>216</v>
       </c>
-      <c r="O190" t="s">
+      <c r="O199" t="s">
         <v>163</v>
       </c>
-      <c r="P190" t="s">
+      <c r="P199" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="191" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B191" t="s">
+      <c r="Q199" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="200" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B200" t="s">
         <v>159</v>
       </c>
-      <c r="M191" t="s">
+      <c r="M200" t="s">
         <v>162</v>
       </c>
-      <c r="N191">
+      <c r="N200">
         <v>216</v>
       </c>
-      <c r="O191" t="s">
+      <c r="O200" t="s">
         <v>163</v>
       </c>
-      <c r="P191" t="s">
+      <c r="P200" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="192" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B192" t="s">
+      <c r="Q200" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="201" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B201" t="s">
         <v>160</v>
       </c>
-      <c r="M192" t="s">
+      <c r="M201" t="s">
         <v>162</v>
       </c>
-      <c r="N192">
+      <c r="N201">
         <v>216</v>
       </c>
-      <c r="O192" t="s">
+      <c r="O201" t="s">
         <v>163</v>
       </c>
-      <c r="P192" t="s">
+      <c r="P201" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="193" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B193" t="s">
+      <c r="Q201" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="202" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B202" t="s">
         <v>161</v>
       </c>
-      <c r="M193" t="s">
+      <c r="M202" t="s">
         <v>162</v>
       </c>
-      <c r="N193">
+      <c r="N202">
         <v>216</v>
       </c>
-      <c r="O193" t="s">
+      <c r="O202" t="s">
         <v>163</v>
       </c>
-      <c r="P193" t="s">
+      <c r="P202" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="195" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A195" s="1" t="s">
+      <c r="Q202" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="204" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A204" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="B195" s="1"/>
-      <c r="C195" s="1"/>
-      <c r="D195" s="1"/>
-      <c r="E195" s="1"/>
-      <c r="F195" s="1"/>
-      <c r="G195" s="1"/>
-      <c r="H195" s="1"/>
-      <c r="I195" s="1"/>
-      <c r="J195" s="1"/>
-      <c r="K195" s="1"/>
-      <c r="L195" s="1"/>
-      <c r="M195" s="8"/>
-      <c r="N195" s="8"/>
-      <c r="O195" s="8"/>
-      <c r="P195" s="8"/>
-      <c r="Q195" s="8"/>
-    </row>
-    <row r="196" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M196" s="9" t="s">
+      <c r="B204" s="1"/>
+      <c r="C204" s="1"/>
+      <c r="D204" s="1"/>
+      <c r="E204" s="1"/>
+      <c r="F204" s="1"/>
+      <c r="G204" s="1"/>
+      <c r="H204" s="1"/>
+      <c r="I204" s="1"/>
+      <c r="J204" s="1"/>
+      <c r="K204" s="1"/>
+      <c r="L204" s="1"/>
+      <c r="M204" s="8"/>
+      <c r="N204" s="8"/>
+      <c r="O204" s="8"/>
+      <c r="P204" s="8"/>
+      <c r="Q204" s="8"/>
+    </row>
+    <row r="205" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M205" s="9" t="s">
         <v>226</v>
       </c>
-      <c r="N196" s="9">
+      <c r="N205" s="9">
         <v>0</v>
       </c>
-      <c r="O196" s="9" t="s">
+      <c r="O205" s="9" t="s">
         <v>315</v>
       </c>
-      <c r="P196" s="9" t="s">
+      <c r="P205" s="9" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="197" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M197" s="9" t="s">
+    <row r="206" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M206" s="9" t="s">
         <v>325</v>
       </c>
-      <c r="N197" s="9">
+      <c r="N206" s="9">
         <v>0</v>
       </c>
-      <c r="O197" s="9" t="s">
+      <c r="O206" s="9" t="s">
         <v>324</v>
       </c>
-      <c r="P197" s="9" t="s">
+      <c r="P206" s="9" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="198" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M198" s="9" t="s">
+    <row r="207" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M207" s="9" t="s">
         <v>228</v>
       </c>
-      <c r="N198" s="9">
+      <c r="N207" s="9">
         <v>0</v>
       </c>
-      <c r="O198" s="9" t="s">
+      <c r="O207" s="9" t="s">
         <v>229</v>
       </c>
-      <c r="P198" s="9" t="s">
+      <c r="P207" s="9" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="200" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A200" t="s">
+    <row r="209" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
         <v>197</v>
       </c>
-      <c r="D200" t="s">
+      <c r="D209" t="s">
         <v>195</v>
       </c>
-      <c r="E200" t="s">
+      <c r="E209" t="s">
         <v>204</v>
       </c>
-      <c r="F200" t="s">
+      <c r="F209" t="s">
         <v>205</v>
       </c>
-      <c r="G200" t="s">
+      <c r="G209" t="s">
         <v>230</v>
       </c>
-      <c r="M200" t="s">
+      <c r="M209" t="s">
         <v>228</v>
       </c>
-      <c r="N200" s="25">
+      <c r="N209" s="25">
         <f>'energy stables'!E24</f>
         <v>3.5302245250431775E-2</v>
       </c>
-      <c r="O200" t="s">
+      <c r="O209" t="s">
         <v>200</v>
       </c>
-      <c r="P200" t="s">
+      <c r="P209" t="s">
         <v>214</v>
       </c>
-      <c r="Q200" t="s">
+      <c r="Q209" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="201" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A201" t="s">
+    <row r="210" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
         <v>201</v>
       </c>
-      <c r="D201" t="s">
+      <c r="D210" t="s">
         <v>195</v>
       </c>
-      <c r="E201" t="s">
+      <c r="E210" t="s">
         <v>204</v>
       </c>
-      <c r="F201" t="s">
+      <c r="F210" t="s">
         <v>205</v>
       </c>
-      <c r="M201" t="s">
+      <c r="M210" t="s">
         <v>226</v>
       </c>
-      <c r="N201" s="24">
+      <c r="N210" s="24">
         <f>'energy stables'!D26</f>
         <v>308.33833333333342</v>
       </c>
-      <c r="O201" t="s">
+      <c r="O210" t="s">
         <v>315</v>
       </c>
-      <c r="P201" t="s">
+      <c r="P210" t="s">
         <v>234</v>
       </c>
-      <c r="Q201" t="s">
+      <c r="Q210" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="202" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A202" t="s">
+    <row r="211" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
         <v>199</v>
       </c>
-      <c r="D202" t="s">
+      <c r="D211" t="s">
         <v>195</v>
       </c>
-      <c r="E202" t="s">
+      <c r="E211" t="s">
         <v>204</v>
       </c>
-      <c r="F202" t="s">
+      <c r="F211" t="s">
         <v>205</v>
       </c>
-      <c r="G202" t="s">
+      <c r="G211" t="s">
         <v>230</v>
       </c>
-      <c r="M202" t="s">
+      <c r="M211" t="s">
         <v>228</v>
       </c>
-      <c r="N202" s="25">
+      <c r="N211" s="25">
         <f>'energy stables'!E27</f>
         <v>4.1036269430051814E-2</v>
       </c>
-      <c r="O202" t="s">
+      <c r="O211" t="s">
         <v>200</v>
       </c>
-      <c r="Q202" t="s">
+      <c r="Q211" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="204" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A204" t="s">
+    <row r="213" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
         <v>197</v>
       </c>
-      <c r="D204" t="s">
+      <c r="D213" t="s">
         <v>195</v>
       </c>
-      <c r="M204" t="s">
+      <c r="M213" t="s">
         <v>226</v>
       </c>
-      <c r="N204" s="24">
+      <c r="N213" s="24">
         <f>'energy stables'!D29</f>
         <v>170.33333333333331</v>
       </c>
-      <c r="O204" t="s">
+      <c r="O213" t="s">
         <v>315</v>
       </c>
-      <c r="P204" t="s">
+      <c r="P213" t="s">
         <v>239</v>
       </c>
-      <c r="Q204" t="s">
+      <c r="Q213" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="205" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A205" t="s">
+    <row r="214" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
         <v>201</v>
       </c>
-      <c r="D205" t="s">
+      <c r="D214" t="s">
         <v>195</v>
       </c>
-      <c r="M205" t="s">
+      <c r="M214" t="s">
         <v>226</v>
       </c>
-      <c r="N205" s="24">
+      <c r="N214" s="24">
         <f>'energy stables'!D31</f>
         <v>332.32333333333338</v>
       </c>
-      <c r="O205" t="s">
+      <c r="O214" t="s">
         <v>315</v>
       </c>
-      <c r="P205" t="s">
+      <c r="P214" t="s">
         <v>240</v>
       </c>
-      <c r="Q205" t="s">
+      <c r="Q214" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="206" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N206" s="24"/>
-    </row>
-    <row r="207" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A207" t="s">
+    <row r="215" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="N215" s="24"/>
+    </row>
+    <row r="216" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
         <v>197</v>
       </c>
-      <c r="D207" t="s">
+      <c r="D216" t="s">
         <v>235</v>
       </c>
-      <c r="E207" t="s">
+      <c r="E216" t="s">
         <v>236</v>
       </c>
-      <c r="F207" t="s">
+      <c r="F216" t="s">
         <v>241</v>
       </c>
-      <c r="M207" t="s">
+      <c r="M216" t="s">
         <v>325</v>
       </c>
-      <c r="N207" s="25">
+      <c r="N216" s="25">
         <f>(290+1078)/100000</f>
         <v>1.3679999999999999E-2</v>
       </c>
-      <c r="O207" t="s">
+      <c r="O216" t="s">
         <v>324</v>
       </c>
-      <c r="P207" t="s">
+      <c r="P216" t="s">
         <v>237</v>
       </c>
-      <c r="Q207" t="s">
+      <c r="Q216" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="208" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A208" t="s">
+    <row r="217" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
         <v>198</v>
       </c>
-      <c r="D208" t="s">
+      <c r="D217" t="s">
         <v>235</v>
       </c>
-      <c r="E208" t="s">
+      <c r="E217" t="s">
         <v>236</v>
       </c>
-      <c r="F208" t="s">
+      <c r="F217" t="s">
         <v>241</v>
       </c>
-      <c r="M208" t="s">
+      <c r="M217" t="s">
         <v>325</v>
       </c>
-      <c r="N208" s="25">
+      <c r="N217" s="25">
         <f>77000/100000</f>
         <v>0.77</v>
       </c>
-      <c r="O208" t="s">
+      <c r="O217" t="s">
         <v>324</v>
       </c>
-      <c r="Q208" t="s">
+      <c r="Q217" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="209" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A209" t="s">
+    <row r="218" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
         <v>201</v>
       </c>
-      <c r="D209" t="s">
+      <c r="D218" t="s">
         <v>235</v>
       </c>
-      <c r="E209" t="s">
+      <c r="E218" t="s">
         <v>236</v>
       </c>
-      <c r="F209" t="s">
+      <c r="F218" t="s">
         <v>241</v>
       </c>
-      <c r="M209" t="s">
+      <c r="M218" t="s">
         <v>325</v>
       </c>
-      <c r="N209" s="25">
+      <c r="N218" s="25">
         <f>(3340+9790)/100000</f>
         <v>0.1313</v>
       </c>
-      <c r="O209" t="s">
+      <c r="O218" t="s">
         <v>324</v>
       </c>
-      <c r="P209" t="s">
+      <c r="P218" t="s">
         <v>238</v>
       </c>
-      <c r="Q209" t="s">
+      <c r="Q218" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="211" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A211" t="s">
+    <row r="220" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
         <v>197</v>
       </c>
-      <c r="D211" t="s">
+      <c r="D220" t="s">
         <v>242</v>
       </c>
-      <c r="F211" t="s">
+      <c r="F220" t="s">
         <v>318</v>
       </c>
-      <c r="M211" t="s">
+      <c r="M220" t="s">
         <v>325</v>
       </c>
-      <c r="N211">
+      <c r="N220">
         <f>'energy stables'!D49</f>
         <v>3.5</v>
       </c>
-      <c r="O211" t="s">
+      <c r="O220" t="s">
         <v>324</v>
       </c>
-      <c r="Q211" t="s">
+      <c r="Q220" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="212" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A212" t="s">
+    <row r="221" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
         <v>198</v>
       </c>
-      <c r="D212" t="s">
+      <c r="D221" t="s">
         <v>242</v>
       </c>
-      <c r="F212" t="s">
+      <c r="F221" t="s">
         <v>318</v>
       </c>
-      <c r="M212" t="s">
+      <c r="M221" t="s">
         <v>325</v>
       </c>
-      <c r="N212">
+      <c r="N221">
         <f>'energy stables'!D50</f>
         <v>12.5</v>
       </c>
-      <c r="O212" t="s">
+      <c r="O221" t="s">
         <v>324</v>
       </c>
-      <c r="Q212" t="s">
+      <c r="Q221" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="213" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A213" t="s">
+    <row r="222" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
         <v>201</v>
       </c>
-      <c r="D213" t="s">
+      <c r="D222" t="s">
         <v>242</v>
       </c>
-      <c r="F213" t="s">
+      <c r="F222" t="s">
         <v>318</v>
       </c>
-      <c r="M213" t="s">
+      <c r="M222" t="s">
         <v>325</v>
       </c>
-      <c r="N213">
+      <c r="N222">
         <f>'energy stables'!D51</f>
         <v>34</v>
       </c>
-      <c r="O213" t="s">
+      <c r="O222" t="s">
         <v>324</v>
       </c>
-      <c r="Q213" t="s">
+      <c r="Q222" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="214" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A214" t="s">
+    <row r="223" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
         <v>197</v>
       </c>
-      <c r="D214" t="s">
+      <c r="D223" t="s">
         <v>242</v>
       </c>
-      <c r="F214" t="s">
+      <c r="F223" t="s">
         <v>321</v>
       </c>
-      <c r="M214" t="s">
+      <c r="M223" t="s">
         <v>325</v>
       </c>
-      <c r="N214">
+      <c r="N223">
         <f>'energy stables'!D53</f>
         <v>0.04</v>
       </c>
-      <c r="O214" t="s">
+      <c r="O223" t="s">
         <v>324</v>
       </c>
-      <c r="Q214" t="s">
+      <c r="Q223" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="215" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A215" t="s">
+    <row r="224" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
         <v>198</v>
       </c>
-      <c r="D215" t="s">
+      <c r="D224" t="s">
         <v>242</v>
       </c>
-      <c r="F215" t="s">
+      <c r="F224" t="s">
         <v>321</v>
       </c>
-      <c r="M215" t="s">
+      <c r="M224" t="s">
         <v>325</v>
       </c>
-      <c r="N215" s="13">
+      <c r="N224" s="13">
         <f>'energy stables'!D54</f>
         <v>0.1</v>
       </c>
-      <c r="O215" t="s">
+      <c r="O224" t="s">
         <v>324</v>
       </c>
-      <c r="Q215" t="s">
+      <c r="Q224" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="216" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A216" t="s">
+    <row r="225" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
         <v>201</v>
       </c>
-      <c r="D216" t="s">
+      <c r="D225" t="s">
         <v>242</v>
       </c>
-      <c r="F216" t="s">
+      <c r="F225" t="s">
         <v>321</v>
       </c>
-      <c r="M216" t="s">
+      <c r="M225" t="s">
         <v>325</v>
       </c>
-      <c r="N216" s="13">
+      <c r="N225" s="13">
         <f>'energy stables'!D55</f>
         <v>0.26</v>
       </c>
-      <c r="O216" t="s">
+      <c r="O225" t="s">
         <v>324</v>
       </c>
-      <c r="Q216" t="s">
+      <c r="Q225" t="s">
         <v>253</v>
+      </c>
+    </row>
+    <row r="227" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>197</v>
+      </c>
+      <c r="D227" t="s">
+        <v>235</v>
+      </c>
+      <c r="E227" t="s">
+        <v>361</v>
+      </c>
+      <c r="M227" t="s">
+        <v>226</v>
+      </c>
+      <c r="N227" s="13">
+        <f>'energy stables'!D65</f>
+        <v>0.14449999999999999</v>
+      </c>
+      <c r="O227" t="s">
+        <v>315</v>
+      </c>
+      <c r="P227" t="s">
+        <v>392</v>
+      </c>
+      <c r="Q227" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="228" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>201</v>
+      </c>
+      <c r="D228" t="s">
+        <v>235</v>
+      </c>
+      <c r="E228" t="s">
+        <v>361</v>
+      </c>
+      <c r="M228" t="s">
+        <v>226</v>
+      </c>
+      <c r="N228" s="13">
+        <f>'energy stables'!D67</f>
+        <v>3.9295</v>
+      </c>
+      <c r="O228" t="s">
+        <v>315</v>
+      </c>
+      <c r="P228" t="s">
+        <v>393</v>
+      </c>
+      <c r="Q228" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="229" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>197</v>
+      </c>
+      <c r="D229" t="s">
+        <v>235</v>
+      </c>
+      <c r="E229" t="s">
+        <v>361</v>
+      </c>
+      <c r="F229" t="s">
+        <v>362</v>
+      </c>
+      <c r="M229" t="s">
+        <v>226</v>
+      </c>
+      <c r="N229">
+        <v>0</v>
+      </c>
+      <c r="O229" t="s">
+        <v>315</v>
+      </c>
+      <c r="P229" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="230" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>201</v>
+      </c>
+      <c r="D230" t="s">
+        <v>235</v>
+      </c>
+      <c r="E230" t="s">
+        <v>361</v>
+      </c>
+      <c r="F230" t="s">
+        <v>362</v>
+      </c>
+      <c r="M230" t="s">
+        <v>226</v>
+      </c>
+      <c r="N230">
+        <v>0</v>
+      </c>
+      <c r="O230">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>198</v>
+      </c>
+      <c r="D231" t="s">
+        <v>235</v>
+      </c>
+      <c r="E231" t="s">
+        <v>361</v>
+      </c>
+      <c r="F231" t="s">
+        <v>362</v>
+      </c>
+      <c r="M231" t="s">
+        <v>325</v>
+      </c>
+      <c r="N231" s="13">
+        <f>4.7*(1/3.6)</f>
+        <v>1.3055555555555556</v>
+      </c>
+      <c r="O231" t="s">
+        <v>324</v>
+      </c>
+      <c r="P231" t="s">
+        <v>364</v>
+      </c>
+      <c r="Q231" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="233" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>197</v>
+      </c>
+      <c r="D233" t="s">
+        <v>394</v>
+      </c>
+      <c r="M233" t="s">
+        <v>226</v>
+      </c>
+      <c r="N233" s="24">
+        <f>0.05*1000*(1/3.6)</f>
+        <v>13.888888888888889</v>
+      </c>
+      <c r="O233" t="s">
+        <v>315</v>
+      </c>
+      <c r="P233" t="s">
+        <v>397</v>
+      </c>
+      <c r="Q233" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="234" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>201</v>
+      </c>
+      <c r="D234" t="s">
+        <v>394</v>
+      </c>
+      <c r="M234" t="s">
+        <v>226</v>
+      </c>
+      <c r="N234" s="24">
+        <f>0.05*1000*(1/3.6)</f>
+        <v>13.888888888888889</v>
+      </c>
+      <c r="O234" t="s">
+        <v>315</v>
+      </c>
+      <c r="P234" t="s">
+        <v>399</v>
+      </c>
+      <c r="Q234" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="235" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
+        <v>197</v>
+      </c>
+      <c r="D235" t="s">
+        <v>394</v>
+      </c>
+      <c r="F235" t="s">
+        <v>395</v>
+      </c>
+      <c r="M235" t="s">
+        <v>226</v>
+      </c>
+      <c r="N235">
+        <v>0</v>
+      </c>
+      <c r="P235" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="236" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>201</v>
+      </c>
+      <c r="D236" t="s">
+        <v>394</v>
+      </c>
+      <c r="F236" t="s">
+        <v>395</v>
+      </c>
+      <c r="M236" t="s">
+        <v>226</v>
+      </c>
+      <c r="N236">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -6092,13 +6653,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B3:S58"/>
+  <dimension ref="B3:S75"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="17.28515625" customWidth="1"/>
     <col min="3" max="3" width="12.28515625" customWidth="1"/>
     <col min="10" max="10" width="8.7109375" customWidth="1"/>
     <col min="11" max="13" width="13.5703125" customWidth="1"/>
+    <col min="16" max="16" width="9.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:17" x14ac:dyDescent="0.25">
@@ -7416,7 +7978,9 @@
       </c>
     </row>
     <row r="58" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B58" s="52"/>
+      <c r="B58" s="53" t="s">
+        <v>389</v>
+      </c>
       <c r="C58" s="52"/>
       <c r="D58" s="52"/>
       <c r="E58" s="52"/>
@@ -7433,7 +7997,360 @@
       <c r="P58" s="52"/>
       <c r="Q58" s="52"/>
     </row>
+    <row r="59" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="J59" s="51" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="60" spans="2:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J60" s="27" t="s">
+        <v>298</v>
+      </c>
+      <c r="K60" s="28"/>
+      <c r="L60" s="28"/>
+      <c r="M60" s="103" t="s">
+        <v>380</v>
+      </c>
+      <c r="N60" s="103"/>
+      <c r="O60" s="103" t="s">
+        <v>381</v>
+      </c>
+      <c r="P60" s="104"/>
+      <c r="Q60" s="4"/>
+    </row>
+    <row r="61" spans="2:19" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J61" s="100" t="s">
+        <v>387</v>
+      </c>
+      <c r="K61" s="14"/>
+      <c r="L61" s="14"/>
+      <c r="M61" s="101" t="s">
+        <v>382</v>
+      </c>
+      <c r="N61" s="101"/>
+      <c r="O61" s="101" t="s">
+        <v>371</v>
+      </c>
+      <c r="P61" s="102"/>
+      <c r="Q61" s="4"/>
+    </row>
+    <row r="62" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B62" s="71" t="s">
+        <v>390</v>
+      </c>
+      <c r="J62" s="27" t="s">
+        <v>258</v>
+      </c>
+      <c r="K62" s="28"/>
+      <c r="L62" s="28"/>
+      <c r="M62" s="28">
+        <v>130</v>
+      </c>
+      <c r="N62" s="96" t="s">
+        <v>365</v>
+      </c>
+      <c r="O62" s="28">
+        <v>106</v>
+      </c>
+      <c r="P62" s="97" t="s">
+        <v>366</v>
+      </c>
+      <c r="Q62" s="4"/>
+    </row>
+    <row r="63" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B63" s="27"/>
+      <c r="C63" s="28"/>
+      <c r="D63" s="86" t="s">
+        <v>322</v>
+      </c>
+      <c r="E63" s="28" t="s">
+        <v>319</v>
+      </c>
+      <c r="F63" s="28"/>
+      <c r="G63" s="28"/>
+      <c r="H63" s="30"/>
+      <c r="J63" s="31" t="s">
+        <v>259</v>
+      </c>
+      <c r="K63" s="4"/>
+      <c r="L63" s="4"/>
+      <c r="M63" s="4">
+        <v>1250</v>
+      </c>
+      <c r="N63" s="4"/>
+      <c r="O63" s="4">
+        <v>2156</v>
+      </c>
+      <c r="P63" s="32"/>
+      <c r="Q63" s="4"/>
+    </row>
+    <row r="64" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B64" s="42"/>
+      <c r="C64" s="14"/>
+      <c r="D64" s="87" t="s">
+        <v>388</v>
+      </c>
+      <c r="E64" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="F64" s="83" t="s">
+        <v>151</v>
+      </c>
+      <c r="G64" s="83" t="s">
+        <v>152</v>
+      </c>
+      <c r="H64" s="84" t="s">
+        <v>148</v>
+      </c>
+      <c r="J64" s="31" t="s">
+        <v>262</v>
+      </c>
+      <c r="K64" s="4"/>
+      <c r="L64" s="4"/>
+      <c r="M64" s="4">
+        <v>11</v>
+      </c>
+      <c r="N64" s="4"/>
+      <c r="O64" s="4">
+        <v>42</v>
+      </c>
+      <c r="P64" s="32"/>
+      <c r="Q64" s="4"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B65" s="85" t="s">
+        <v>197</v>
+      </c>
+      <c r="C65" s="28"/>
+      <c r="D65" s="90">
+        <f>SUM(M62,O62,M64,O64)/2/1000</f>
+        <v>0.14449999999999999</v>
+      </c>
+      <c r="E65" s="75">
+        <v>10</v>
+      </c>
+      <c r="F65" s="75">
+        <v>0</v>
+      </c>
+      <c r="G65" s="75">
+        <v>0</v>
+      </c>
+      <c r="H65" s="78">
+        <v>90</v>
+      </c>
+      <c r="J65" s="31" t="s">
+        <v>367</v>
+      </c>
+      <c r="K65" s="4"/>
+      <c r="L65" s="4"/>
+      <c r="M65" s="4">
+        <v>1454</v>
+      </c>
+      <c r="N65" s="4"/>
+      <c r="O65" s="4">
+        <v>2431</v>
+      </c>
+      <c r="P65" s="32"/>
+      <c r="Q65" s="4"/>
+    </row>
+    <row r="66" spans="2:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B66" s="31" t="s">
+        <v>198</v>
+      </c>
+      <c r="C66" s="4"/>
+      <c r="D66" s="88">
+        <v>0</v>
+      </c>
+      <c r="E66" s="75"/>
+      <c r="F66" s="75"/>
+      <c r="G66" s="75"/>
+      <c r="H66" s="78"/>
+      <c r="J66" s="94" t="s">
+        <v>368</v>
+      </c>
+      <c r="K66" s="95"/>
+      <c r="L66" s="95"/>
+      <c r="M66" s="95" t="s">
+        <v>369</v>
+      </c>
+      <c r="N66" s="95"/>
+      <c r="O66" s="95" t="s">
+        <v>370</v>
+      </c>
+      <c r="P66" s="44"/>
+      <c r="Q66" s="4"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B67" s="42" t="s">
+        <v>201</v>
+      </c>
+      <c r="C67" s="14"/>
+      <c r="D67" s="91">
+        <f>SUM(M63,O63,M65,O65,M67,O67,M68,O68,O69,O70,M71,O71)/2/1000</f>
+        <v>3.9295</v>
+      </c>
+      <c r="E67" s="76">
+        <v>0</v>
+      </c>
+      <c r="F67" s="76">
+        <v>0</v>
+      </c>
+      <c r="G67" s="76">
+        <v>0</v>
+      </c>
+      <c r="H67" s="77">
+        <v>100</v>
+      </c>
+      <c r="J67" s="31" t="s">
+        <v>373</v>
+      </c>
+      <c r="K67" s="4"/>
+      <c r="L67" s="4"/>
+      <c r="M67" s="4">
+        <v>29</v>
+      </c>
+      <c r="N67" s="4"/>
+      <c r="O67" s="4">
+        <v>26</v>
+      </c>
+      <c r="P67" s="32"/>
+      <c r="Q67" s="4"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="J68" s="31" t="s">
+        <v>374</v>
+      </c>
+      <c r="K68" s="4"/>
+      <c r="L68" s="4"/>
+      <c r="M68" s="4">
+        <v>16</v>
+      </c>
+      <c r="N68" s="4"/>
+      <c r="O68" s="4">
+        <v>36</v>
+      </c>
+      <c r="P68" s="32"/>
+      <c r="Q68" s="4"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="J69" s="31" t="s">
+        <v>375</v>
+      </c>
+      <c r="K69" s="4"/>
+      <c r="L69" s="4"/>
+      <c r="M69" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="N69" s="4"/>
+      <c r="O69" s="4">
+        <v>150</v>
+      </c>
+      <c r="P69" s="32"/>
+      <c r="Q69" s="4"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="J70" s="31" t="s">
+        <v>377</v>
+      </c>
+      <c r="K70" s="4"/>
+      <c r="L70" s="4"/>
+      <c r="M70" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="N70" s="4"/>
+      <c r="O70" s="4">
+        <v>18</v>
+      </c>
+      <c r="P70" s="32"/>
+      <c r="Q70" s="4"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="J71" s="31" t="s">
+        <v>257</v>
+      </c>
+      <c r="K71" s="4"/>
+      <c r="L71" s="4"/>
+      <c r="M71" s="4">
+        <v>228</v>
+      </c>
+      <c r="N71" s="4"/>
+      <c r="O71" s="4">
+        <v>65</v>
+      </c>
+      <c r="P71" s="32"/>
+      <c r="Q71" s="4"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="J72" s="98" t="s">
+        <v>379</v>
+      </c>
+      <c r="K72" s="93"/>
+      <c r="L72" s="93"/>
+      <c r="M72" s="93">
+        <v>3118</v>
+      </c>
+      <c r="N72" s="93"/>
+      <c r="O72" s="93">
+        <v>5030</v>
+      </c>
+      <c r="P72" s="99"/>
+      <c r="Q72" s="4"/>
+    </row>
+    <row r="73" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J73" s="55" t="s">
+        <v>383</v>
+      </c>
+      <c r="K73" s="56"/>
+      <c r="L73" s="56"/>
+      <c r="M73" s="56" t="s">
+        <v>384</v>
+      </c>
+      <c r="N73" s="56"/>
+      <c r="O73" s="56" t="s">
+        <v>385</v>
+      </c>
+      <c r="P73" s="57"/>
+      <c r="Q73" s="4"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="J74" s="31" t="s">
+        <v>372</v>
+      </c>
+      <c r="K74" s="4"/>
+      <c r="L74" s="4"/>
+      <c r="M74" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="N74" s="4"/>
+      <c r="O74" s="4">
+        <v>10</v>
+      </c>
+      <c r="P74" s="32"/>
+      <c r="Q74" s="4"/>
+    </row>
+    <row r="75" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J75" s="55" t="s">
+        <v>310</v>
+      </c>
+      <c r="K75" s="56"/>
+      <c r="L75" s="56"/>
+      <c r="M75" s="56">
+        <v>2004</v>
+      </c>
+      <c r="N75" s="56"/>
+      <c r="O75" s="56">
+        <v>2003</v>
+      </c>
+      <c r="P75" s="57"/>
+      <c r="Q75" s="4"/>
+    </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="O61:P61"/>
+    <mergeCell ref="M60:N60"/>
+    <mergeCell ref="O60:P60"/>
+    <mergeCell ref="M61:N61"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
@@ -8096,67 +9013,77 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="16" t="s">
         <v>137</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="17" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="17" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="17" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" s="17" t="s">
         <v>146</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="48" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="48" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" s="48" t="s">
         <v>244</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" s="48" t="s">
+        <v>401</v>
       </c>
     </row>
   </sheetData>

--- a/data/default/MachineryAndEnergyMgmt.xlsx
+++ b/data/default/MachineryAndEnergyMgmt.xlsx
@@ -477,7 +477,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1167" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1166" uniqueCount="403">
   <si>
     <t>f_crop</t>
   </si>
@@ -703,9 +703,6 @@
     <t>Konstgödsel</t>
   </si>
   <si>
-    <t>Flytgödsel</t>
-  </si>
-  <si>
     <t>field_operations</t>
   </si>
   <si>
@@ -775,9 +772,6 @@
     <t>minreal fert</t>
   </si>
   <si>
-    <t>liquid manure</t>
-  </si>
-  <si>
     <t>spraying</t>
   </si>
   <si>
@@ -860,12 +854,6 @@
   </si>
   <si>
     <t>ASAE, 2000</t>
-  </si>
-  <si>
-    <t>semi-solid manure</t>
-  </si>
-  <si>
-    <t>Kletgödselspridning</t>
   </si>
   <si>
     <t>Ogräsbekämpning, kemisk, Sprejspridning</t>
@@ -1864,6 +1852,18 @@
   </si>
   <si>
     <t>"</t>
+  </si>
+  <si>
+    <t>Avg. "Flytgödsel" and "Kletgödsel"</t>
+  </si>
+  <si>
+    <t>manure appl</t>
+  </si>
+  <si>
+    <t>Only applies to area with manure application</t>
+  </si>
+  <si>
+    <t>E_per_area_manure</t>
   </si>
 </sst>
 </file>
@@ -2694,40 +2694,40 @@
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="49" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B1" s="93" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="93" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="D1" s="93" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="E1" s="93" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="F1" s="93" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="G1" s="93" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="H1" s="93" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="I1" s="93" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J1" s="93" t="s">
         <v>44</v>
       </c>
       <c r="K1" s="93" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="L1" s="93" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="M1" s="93" t="s">
         <v>1</v>
@@ -2747,92 +2747,92 @@
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="M2" s="20" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="N2" s="9">
         <v>0</v>
       </c>
       <c r="O2" s="9" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="P2" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>146</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="M4" s="6" t="s">
         <v>150</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="M4" s="6" t="s">
-        <v>154</v>
       </c>
       <c r="N4" s="18">
         <f>(241822577+237201100)/(241822577+237201100+5856000+8368914)*100</f>
         <v>97.116076100458642</v>
       </c>
       <c r="O4" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="Q4" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>146</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="M5" s="6" t="s">
         <v>150</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>326</v>
-      </c>
-      <c r="M5" s="6" t="s">
-        <v>154</v>
       </c>
       <c r="N5" s="18">
         <f>100-N4</f>
         <v>2.8839238995413581</v>
       </c>
       <c r="O5" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="Q5" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>146</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="M6" s="6" t="s">
         <v>150</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>327</v>
-      </c>
-      <c r="M6" s="6" t="s">
-        <v>154</v>
       </c>
       <c r="N6" s="10">
         <v>0</v>
       </c>
       <c r="O6" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>146</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="M7" s="6" t="s">
         <v>150</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>328</v>
-      </c>
-      <c r="M7" s="6" t="s">
-        <v>154</v>
       </c>
       <c r="N7" s="10">
         <v>0</v>
       </c>
       <c r="O7" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
@@ -2842,30 +2842,30 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="D9" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="N9" s="10">
         <v>100</v>
       </c>
       <c r="O9" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D10" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="H10" s="4"/>
       <c r="M10" s="6"/>
@@ -2873,42 +2873,42 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="D11" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="M11" s="6" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="N11" s="10">
         <v>100</v>
       </c>
       <c r="O11" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="D12" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="M12" s="6" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="N12" s="10">
         <v>100</v>
       </c>
       <c r="O12" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
@@ -2918,71 +2918,71 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="D14" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="E14" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="M14" s="6" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="N14" s="10">
         <v>100</v>
       </c>
       <c r="O14" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D15" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="E15" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="N15" s="10">
         <v>100</v>
       </c>
       <c r="O15" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="D16" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="E16" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="N16" s="10">
         <v>100</v>
       </c>
       <c r="O16" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
@@ -2992,262 +2992,262 @@
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="D18" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="F18" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="M18" s="6" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="N18" s="10">
         <v>100</v>
       </c>
       <c r="O18" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="Q18" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D19" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="F19" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="M19" s="6" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="N19">
         <v>4</v>
       </c>
       <c r="O19" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="Q19" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D20" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="F20" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="M20" s="6" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="N20">
         <v>76</v>
       </c>
       <c r="O20" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="Q20" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D21" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="F21" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="M21" s="6" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="N21">
         <v>20</v>
       </c>
       <c r="O21" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="Q21" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="D22" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="F22" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="N22" s="10">
         <v>100</v>
       </c>
       <c r="O22" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="Q22" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="D23" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="F23" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="M23" s="6" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="N23" s="10">
         <v>100</v>
       </c>
       <c r="O23" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="Q23" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D24" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="F24" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="M24" s="6" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="N24">
         <v>20</v>
       </c>
       <c r="O24" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="Q24" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D25" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="F25" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="M25" s="6" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="N25">
         <v>60</v>
       </c>
       <c r="O25" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="Q25" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D26" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="F26" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="M26" s="6" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="N26">
         <v>20.000000000000018</v>
       </c>
       <c r="O26" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="Q26" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="D27" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="F27" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="M27" s="6" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="N27" s="10">
         <v>100</v>
       </c>
       <c r="O27" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="Q27" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
@@ -3257,123 +3257,123 @@
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="D29" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="E29" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="M29" s="6" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="N29" s="10">
         <v>90</v>
       </c>
       <c r="O29" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="D30" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="E30" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="M30" s="6" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="N30" s="10">
         <v>10</v>
       </c>
       <c r="O30" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="D31" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="E31" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="M31" s="6" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="N31" s="10">
         <v>100</v>
       </c>
       <c r="O31" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D32" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="E32" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="M32" s="6" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="N32" s="10">
         <v>90</v>
       </c>
       <c r="O32" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="Q32" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D33" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="E33" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="M33" s="6" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="N33" s="10">
         <v>10</v>
       </c>
       <c r="O33" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="Q33" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
@@ -3383,48 +3383,48 @@
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="D35" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="M35" s="6" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="N35" s="10">
         <v>100</v>
       </c>
       <c r="O35" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="Q35" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="D36" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="M36" s="6" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="N36" s="10">
         <v>100</v>
       </c>
       <c r="O36" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="Q36" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
@@ -3434,119 +3434,119 @@
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="M38" s="6" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="N38" s="11">
         <v>6.4777062142923141</v>
       </c>
       <c r="O38" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="Q38" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="M39" s="6" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="N39" s="11">
         <v>8.7567853491111922</v>
       </c>
       <c r="O39" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="P39" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="Q39" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="M40" s="6" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="N40" s="18">
         <v>59.671114354829328</v>
       </c>
       <c r="O40" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="P40" s="19" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="Q40" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="M41" s="6" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="N41" s="18">
         <v>16.802918820320372</v>
       </c>
       <c r="O41" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="M42" s="6" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="N42" s="11">
         <v>7.4851294970113242</v>
       </c>
       <c r="O42" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="M43" s="6" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="N43" s="11">
         <v>0.80634576443547301</v>
       </c>
       <c r="O43" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
@@ -3556,62 +3556,62 @@
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="M45" s="6" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="N45" s="18">
         <v>70</v>
       </c>
       <c r="O45" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="P45" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="Q45" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="M46" s="6" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="N46" s="18">
         <v>30</v>
       </c>
       <c r="O46" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="Q46" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="M47" s="6" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="N47" s="18">
         <v>100</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
@@ -3619,49 +3619,49 @@
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="K49" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="M49" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="N49" s="15">
         <v>80</v>
       </c>
       <c r="O49" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="K50" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="M50" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="N50" s="15">
         <v>10</v>
       </c>
       <c r="O50" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="K51" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="M51" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="N51" s="15">
         <v>10</v>
       </c>
       <c r="O51" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -3683,14 +3683,14 @@
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H53" s="4"/>
       <c r="M53" s="9" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="N53" s="23">
         <v>0</v>
       </c>
       <c r="O53" s="9"/>
       <c r="P53" s="9" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
@@ -3699,377 +3699,377 @@
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H55" s="4" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="L55" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="M55" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="N55" s="18">
         <f>74100</f>
         <v>74100</v>
       </c>
       <c r="O55" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="P55" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="Q55" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H56" s="4" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="L56" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="M56" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="N56" s="11">
         <f>3.9</f>
         <v>3.9</v>
       </c>
       <c r="O56" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="Q56" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H57" s="4" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="L57" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="M57" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="N57" s="11">
         <f>3.9</f>
         <v>3.9</v>
       </c>
       <c r="O57" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="Q57" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H58" s="4" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="L58" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="M58" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="N58" s="18">
         <v>0</v>
       </c>
       <c r="O58" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H59" s="4" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="L59" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="M59" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="N59" s="22">
         <f t="shared" ref="N59:N60" si="0">N56</f>
         <v>3.9</v>
       </c>
       <c r="O59" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="P59" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H60" s="4" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="L60" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="M60" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="N60" s="22">
         <f t="shared" si="0"/>
         <v>3.9</v>
       </c>
       <c r="O60" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="P60" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H61" s="6" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="L61" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="M61" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="N61" s="18">
         <v>73300</v>
       </c>
       <c r="O61" t="s">
+        <v>182</v>
+      </c>
+      <c r="P61" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q61" t="s">
         <v>186</v>
-      </c>
-      <c r="P61" t="s">
-        <v>189</v>
-      </c>
-      <c r="Q61" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H62" s="6" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="L62" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="M62" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="N62">
         <v>10</v>
       </c>
       <c r="O62" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q62" t="s">
         <v>186</v>
-      </c>
-      <c r="Q62" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H63" s="6" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="L63" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="M63" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="N63">
         <v>0.6</v>
       </c>
       <c r="O63" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q63" t="s">
         <v>186</v>
-      </c>
-      <c r="Q63" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H64" s="6" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="L64" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="M64" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="N64" s="18">
         <v>56100</v>
       </c>
       <c r="O64" t="s">
+        <v>182</v>
+      </c>
+      <c r="P64" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q64" t="s">
         <v>186</v>
-      </c>
-      <c r="P64" t="s">
-        <v>188</v>
-      </c>
-      <c r="Q64" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H65" s="6" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="L65" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="M65" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="N65">
         <v>5</v>
       </c>
       <c r="O65" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q65" t="s">
         <v>186</v>
-      </c>
-      <c r="Q65" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H66" s="6" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="L66" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="M66" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="N66">
         <v>0.1</v>
       </c>
       <c r="O66" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q66" t="s">
         <v>186</v>
-      </c>
-      <c r="Q66" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H67" s="6" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="L67" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="M67" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="N67" s="18">
         <v>0</v>
       </c>
       <c r="O67" t="s">
+        <v>182</v>
+      </c>
+      <c r="P67" t="s">
+        <v>183</v>
+      </c>
+      <c r="Q67" t="s">
         <v>186</v>
-      </c>
-      <c r="P67" t="s">
-        <v>187</v>
-      </c>
-      <c r="Q67" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H68" s="6" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="L68" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="M68" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="N68" s="18">
         <v>300</v>
       </c>
       <c r="O68" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q68" t="s">
         <v>186</v>
-      </c>
-      <c r="Q68" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H69" s="6" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="L69" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="M69" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="N69" s="18">
         <v>4</v>
       </c>
       <c r="O69" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q69" t="s">
         <v>186</v>
-      </c>
-      <c r="Q69" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H70" s="6" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="M70" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="N70" s="18">
         <v>0</v>
       </c>
       <c r="O70" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="P70" s="15"/>
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H71" s="6" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="M71" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="N71" s="18">
         <v>0</v>
       </c>
       <c r="O71" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="P71" s="15"/>
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H72" s="4" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="M72" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="N72" s="18">
         <v>0</v>
       </c>
       <c r="O72" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="P72" s="15" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H73" s="6" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="M73" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="N73" s="18">
         <v>0</v>
       </c>
       <c r="O73" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="P73" s="15"/>
     </row>
@@ -4183,13 +4183,13 @@
       <c r="K79" s="4"/>
       <c r="L79" s="4"/>
       <c r="M79" s="6" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="N79">
         <v>2</v>
       </c>
       <c r="O79" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="P79" s="7"/>
     </row>
@@ -4281,14 +4281,14 @@
       <c r="K83" s="4"/>
       <c r="L83" s="4"/>
       <c r="M83" s="20" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N83" s="9">
         <v>1</v>
       </c>
       <c r="O83" s="9"/>
       <c r="P83" s="21" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="84" spans="1:21" ht="18" x14ac:dyDescent="0.35">
@@ -4299,20 +4299,20 @@
       <c r="F84" s="4"/>
       <c r="G84" s="4"/>
       <c r="H84" s="4" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="I84" s="4"/>
       <c r="J84" s="4"/>
       <c r="K84" s="4"/>
       <c r="L84" s="4"/>
       <c r="M84" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N84">
         <v>0.26</v>
       </c>
       <c r="P84" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="85" spans="1:21" ht="18" x14ac:dyDescent="0.35">
@@ -4323,20 +4323,20 @@
       <c r="F85" s="4"/>
       <c r="G85" s="4"/>
       <c r="H85" s="4" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="I85" s="4"/>
       <c r="J85" s="4"/>
       <c r="K85" s="4"/>
       <c r="L85" s="4"/>
       <c r="M85" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N85">
         <v>0.26</v>
       </c>
       <c r="P85" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="86" spans="1:21" ht="18" x14ac:dyDescent="0.35">
@@ -4347,20 +4347,20 @@
       <c r="F86" s="4"/>
       <c r="G86" s="4"/>
       <c r="H86" s="4" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="I86" s="4"/>
       <c r="J86" s="4"/>
       <c r="K86" s="4"/>
       <c r="L86" s="4"/>
       <c r="M86" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N86">
         <v>0.45</v>
       </c>
       <c r="P86" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="87" spans="1:21" ht="18" x14ac:dyDescent="0.35">
@@ -4371,20 +4371,20 @@
       <c r="F87" s="4"/>
       <c r="G87" s="4"/>
       <c r="H87" s="6" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="I87" s="6"/>
       <c r="J87" s="6"/>
       <c r="K87" s="6"/>
       <c r="L87" s="6"/>
       <c r="M87" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N87">
         <v>0.76</v>
       </c>
       <c r="P87" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
@@ -4435,7 +4435,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="M91" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="N91">
         <v>4</v>
@@ -4555,171 +4555,171 @@
     </row>
     <row r="101" spans="1:20" x14ac:dyDescent="0.25">
       <c r="M101" s="9" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="N101" s="9">
         <v>0</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="P101" s="9"/>
     </row>
     <row r="102" spans="1:20" x14ac:dyDescent="0.25">
       <c r="M102" s="9" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="N102" s="9">
         <v>0</v>
       </c>
       <c r="O102" s="9" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="P102" s="9"/>
     </row>
     <row r="103" spans="1:20" x14ac:dyDescent="0.25">
       <c r="M103" s="9" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="N103" s="9">
         <v>0</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="P103" s="9"/>
     </row>
     <row r="104" spans="1:20" x14ac:dyDescent="0.25">
       <c r="M104" s="9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="N104" s="9">
         <v>0</v>
       </c>
       <c r="O104" s="9" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="P104" s="9"/>
     </row>
     <row r="105" spans="1:20" x14ac:dyDescent="0.25">
       <c r="M105" s="9" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="N105" s="9">
         <v>0</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="P105" s="9"/>
     </row>
     <row r="106" spans="1:20" x14ac:dyDescent="0.25">
       <c r="M106" s="9" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="N106" s="9">
         <v>1</v>
       </c>
       <c r="O106" s="9" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="P106" s="9" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="107" spans="1:20" x14ac:dyDescent="0.25">
       <c r="M107" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="N107" s="9">
         <v>0</v>
       </c>
       <c r="O107" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P107" s="9"/>
     </row>
     <row r="108" spans="1:20" x14ac:dyDescent="0.25">
       <c r="M108" s="9" t="s">
-        <v>55</v>
+        <v>402</v>
       </c>
       <c r="N108" s="9">
         <v>0</v>
       </c>
       <c r="O108" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="P108" s="9"/>
+        <v>55</v>
+      </c>
+      <c r="P108" s="9" t="s">
+        <v>401</v>
+      </c>
     </row>
     <row r="109" spans="1:20" x14ac:dyDescent="0.25">
       <c r="M109" s="9" t="s">
-        <v>134</v>
+        <v>54</v>
       </c>
       <c r="N109" s="9">
         <v>0</v>
       </c>
       <c r="O109" s="9" t="s">
-        <v>334</v>
+        <v>56</v>
       </c>
       <c r="P109" s="9"/>
     </row>
     <row r="110" spans="1:20" x14ac:dyDescent="0.25">
       <c r="M110" s="9" t="s">
-        <v>58</v>
+        <v>130</v>
       </c>
       <c r="N110" s="9">
         <v>0</v>
       </c>
       <c r="O110" s="9" t="s">
-        <v>59</v>
+        <v>330</v>
       </c>
       <c r="P110" s="9"/>
     </row>
     <row r="111" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="M111" s="9"/>
-      <c r="N111" s="9"/>
-      <c r="O111" s="9"/>
+      <c r="M111" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="N111" s="9">
+        <v>0</v>
+      </c>
+      <c r="O111" s="9" t="s">
+        <v>58</v>
+      </c>
       <c r="P111" s="9"/>
     </row>
     <row r="112" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="I112" t="s">
-        <v>60</v>
-      </c>
-      <c r="M112" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="N112" s="10">
-        <v>364</v>
-      </c>
-      <c r="O112" s="10"/>
-      <c r="P112" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q112" s="10"/>
+      <c r="M112" s="9"/>
+      <c r="N112" s="9"/>
+      <c r="O112" s="9"/>
+      <c r="P112" s="9"/>
     </row>
     <row r="113" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I113" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M113" s="10" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="N113" s="10">
-        <v>18.8</v>
+        <v>364</v>
       </c>
       <c r="O113" s="10"/>
-      <c r="P113" s="10"/>
+      <c r="P113" s="10" t="s">
+        <v>82</v>
+      </c>
       <c r="Q113" s="10"/>
     </row>
     <row r="114" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I114" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M114" s="10" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="N114" s="10">
-        <v>0</v>
+        <v>18.8</v>
       </c>
       <c r="O114" s="10"/>
       <c r="P114" s="10"/>
@@ -4727,13 +4727,13 @@
     </row>
     <row r="115" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I115" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M115" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="N115" s="10">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O115" s="10"/>
       <c r="P115" s="10"/>
@@ -4741,16 +4741,13 @@
     </row>
     <row r="116" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I116" t="s">
-        <v>60</v>
-      </c>
-      <c r="J116" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="M116" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="N116" s="12">
-        <v>1</v>
+        <v>73</v>
+      </c>
+      <c r="N116" s="10">
+        <v>10</v>
       </c>
       <c r="O116" s="10"/>
       <c r="P116" s="10"/>
@@ -4758,16 +4755,16 @@
     </row>
     <row r="117" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I117" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J117" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M117" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="N117" s="10">
-        <v>0.88</v>
+        <v>77</v>
+      </c>
+      <c r="N117" s="12">
+        <v>1</v>
       </c>
       <c r="O117" s="10"/>
       <c r="P117" s="10"/>
@@ -4775,67 +4772,70 @@
     </row>
     <row r="118" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I118" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J118" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="M118" s="10" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="N118" s="10">
-        <v>0.78</v>
+        <v>0.88</v>
       </c>
       <c r="O118" s="10"/>
       <c r="P118" s="10"/>
       <c r="Q118" s="10"/>
     </row>
     <row r="119" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="M119" s="10"/>
-      <c r="N119" s="10"/>
+      <c r="I119" t="s">
+        <v>59</v>
+      </c>
+      <c r="J119" t="s">
+        <v>70</v>
+      </c>
+      <c r="M119" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="N119" s="10">
+        <v>0.78</v>
+      </c>
       <c r="O119" s="10"/>
       <c r="P119" s="10"/>
       <c r="Q119" s="10"/>
     </row>
     <row r="120" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="I120" t="s">
-        <v>63</v>
-      </c>
-      <c r="M120" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="N120" s="10">
-        <v>652</v>
-      </c>
+      <c r="M120" s="10"/>
+      <c r="N120" s="10"/>
       <c r="O120" s="10"/>
-      <c r="P120" s="10" t="s">
-        <v>82</v>
-      </c>
+      <c r="P120" s="10"/>
       <c r="Q120" s="10"/>
     </row>
     <row r="121" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I121" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M121" s="10" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="N121" s="10">
-        <v>0</v>
+        <v>652</v>
       </c>
       <c r="O121" s="10"/>
-      <c r="P121" s="10"/>
+      <c r="P121" s="10" t="s">
+        <v>80</v>
+      </c>
       <c r="Q121" s="10"/>
     </row>
     <row r="122" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I122" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M122" s="10" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="N122" s="10">
-        <v>5.0999999999999996</v>
+        <v>0</v>
       </c>
       <c r="O122" s="10"/>
       <c r="P122" s="10"/>
@@ -4843,13 +4843,13 @@
     </row>
     <row r="123" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I123" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M123" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="N123" s="10">
-        <v>20</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="O123" s="10"/>
       <c r="P123" s="10"/>
@@ -4857,16 +4857,13 @@
     </row>
     <row r="124" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I124" t="s">
-        <v>63</v>
-      </c>
-      <c r="J124" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="M124" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="N124" s="12">
-        <v>1</v>
+        <v>73</v>
+      </c>
+      <c r="N124" s="10">
+        <v>20</v>
       </c>
       <c r="O124" s="10"/>
       <c r="P124" s="10"/>
@@ -4874,16 +4871,16 @@
     </row>
     <row r="125" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I125" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J125" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M125" s="10" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="N125" s="12">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="O125" s="10"/>
       <c r="P125" s="10"/>
@@ -4891,67 +4888,70 @@
     </row>
     <row r="126" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I126" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J126" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="M126" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="N126" s="10">
-        <v>0.45</v>
+        <v>77</v>
+      </c>
+      <c r="N126" s="12">
+        <v>0.7</v>
       </c>
       <c r="O126" s="10"/>
       <c r="P126" s="10"/>
       <c r="Q126" s="10"/>
     </row>
     <row r="127" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="M127" s="10"/>
-      <c r="N127" s="10"/>
+      <c r="I127" t="s">
+        <v>62</v>
+      </c>
+      <c r="J127" t="s">
+        <v>70</v>
+      </c>
+      <c r="M127" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="N127" s="10">
+        <v>0.45</v>
+      </c>
       <c r="O127" s="10"/>
       <c r="P127" s="10"/>
       <c r="Q127" s="10"/>
     </row>
     <row r="128" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="I128" t="s">
-        <v>62</v>
-      </c>
-      <c r="M128" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="N128" s="10">
-        <v>46</v>
-      </c>
+      <c r="M128" s="10"/>
+      <c r="N128" s="10"/>
       <c r="O128" s="10"/>
-      <c r="P128" s="10" t="s">
-        <v>83</v>
-      </c>
+      <c r="P128" s="10"/>
       <c r="Q128" s="10"/>
     </row>
     <row r="129" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I129" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M129" s="10" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="N129" s="10">
-        <v>2.8</v>
+        <v>46</v>
       </c>
       <c r="O129" s="10"/>
-      <c r="P129" s="10"/>
+      <c r="P129" s="10" t="s">
+        <v>81</v>
+      </c>
       <c r="Q129" s="10"/>
     </row>
     <row r="130" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I130" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M130" s="10" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="N130" s="10">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O130" s="10"/>
       <c r="P130" s="10"/>
@@ -4959,13 +4959,13 @@
     </row>
     <row r="131" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I131" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M131" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="N131" s="10">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O131" s="10"/>
       <c r="P131" s="10"/>
@@ -4973,16 +4973,13 @@
     </row>
     <row r="132" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I132" t="s">
-        <v>62</v>
-      </c>
-      <c r="J132" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="M132" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="N132" s="12">
-        <v>1</v>
+        <v>73</v>
+      </c>
+      <c r="N132" s="10">
+        <v>5</v>
       </c>
       <c r="O132" s="10"/>
       <c r="P132" s="10"/>
@@ -4990,16 +4987,16 @@
     </row>
     <row r="133" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I133" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J133" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M133" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="N133" s="10">
-        <v>0.85</v>
+        <v>77</v>
+      </c>
+      <c r="N133" s="12">
+        <v>1</v>
       </c>
       <c r="O133" s="10"/>
       <c r="P133" s="10"/>
@@ -5007,367 +5004,367 @@
     </row>
     <row r="134" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I134" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J134" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="M134" s="10" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="N134" s="10">
-        <v>0.65</v>
+        <v>0.85</v>
       </c>
       <c r="O134" s="10"/>
       <c r="P134" s="10"/>
       <c r="Q134" s="10"/>
     </row>
     <row r="135" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="M135" s="10"/>
-      <c r="N135" s="10"/>
+      <c r="I135" t="s">
+        <v>61</v>
+      </c>
+      <c r="J135" t="s">
+        <v>70</v>
+      </c>
+      <c r="M135" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="N135" s="10">
+        <v>0.65</v>
+      </c>
       <c r="O135" s="10"/>
       <c r="P135" s="10"/>
       <c r="Q135" s="10"/>
     </row>
     <row r="136" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="I136" t="s">
-        <v>65</v>
-      </c>
-      <c r="M136" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="N136" s="12">
-        <v>5.0999999999999996</v>
-      </c>
+      <c r="M136" s="10"/>
+      <c r="N136" s="10"/>
       <c r="O136" s="10"/>
-      <c r="P136" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="Q136" s="4" t="s">
-        <v>96</v>
-      </c>
+      <c r="P136" s="10"/>
+      <c r="Q136" s="10"/>
     </row>
     <row r="137" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I137" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="M137" s="10" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="N137" s="12">
-        <v>7.1</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="O137" s="10"/>
       <c r="P137" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="Q137" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="138" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="M138" s="10"/>
-      <c r="N138" s="10"/>
+      <c r="I138" t="s">
+        <v>65</v>
+      </c>
+      <c r="M138" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="N138" s="12">
+        <v>7.1</v>
+      </c>
       <c r="O138" s="10"/>
-      <c r="P138" s="10"/>
-      <c r="Q138" s="10"/>
+      <c r="P138" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q138" s="4" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="139" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="I139" t="s">
-        <v>61</v>
-      </c>
-      <c r="M139" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="N139" s="12">
-        <v>3.7353333333333332</v>
-      </c>
+      <c r="M139" s="10"/>
+      <c r="N139" s="10"/>
       <c r="O139" s="10"/>
-      <c r="P139" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q139" s="6" t="s">
-        <v>89</v>
-      </c>
+      <c r="P139" s="10"/>
+      <c r="Q139" s="10"/>
     </row>
     <row r="140" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I140" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="M140" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="N140" s="11">
-        <v>17.096931944444446</v>
+        <v>53</v>
+      </c>
+      <c r="N140" s="12">
+        <v>3.7353333333333332</v>
       </c>
       <c r="O140" s="10"/>
-      <c r="P140" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q140" s="4" t="s">
-        <v>91</v>
+      <c r="P140" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q140" s="6" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="141" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I141" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="M141" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="N141" s="12">
-        <v>1.2451111111111113</v>
+        <v>53</v>
+      </c>
+      <c r="N141" s="11">
+        <v>17.096931944444446</v>
       </c>
       <c r="O141" s="10"/>
       <c r="P141" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q141" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q141" s="4" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="142" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I142" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="M142" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="N142" s="12">
-        <v>3.1127777777777781</v>
+        <v>1.2451111111111113</v>
       </c>
       <c r="O142" s="10"/>
       <c r="P142" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="Q142" s="10" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="143" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I143" t="s">
-        <v>97</v>
+        <v>400</v>
       </c>
       <c r="M143" s="10" t="s">
-        <v>54</v>
+        <v>402</v>
       </c>
       <c r="N143" s="12">
-        <v>4.6691666666666665</v>
+        <f>(3.11+4.67)/2</f>
+        <v>3.8899999999999997</v>
       </c>
       <c r="O143" s="10"/>
-      <c r="P143" s="4" t="s">
-        <v>98</v>
+      <c r="P143" s="6" t="s">
+        <v>399</v>
       </c>
       <c r="Q143" s="10" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="144" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I144" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M144" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="N144" s="12">
         <v>3.1127777777777781</v>
       </c>
       <c r="O144" s="10"/>
       <c r="P144" s="4" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="Q144" s="6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="145" spans="2:17" x14ac:dyDescent="0.25">
       <c r="I145" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="M145" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="N145" s="11">
         <v>11.828555555555555</v>
       </c>
       <c r="O145" s="10"/>
       <c r="P145" s="4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="Q145" s="10" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="146" spans="2:17" x14ac:dyDescent="0.25">
       <c r="I146" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="M146" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="N146" s="11">
         <v>26.302972222222223</v>
       </c>
       <c r="O146" s="10"/>
       <c r="P146" s="6" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="Q146" s="10" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="147" spans="2:17" x14ac:dyDescent="0.25">
       <c r="I147" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="M147" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="N147" s="11">
         <v>11.3</v>
       </c>
       <c r="O147" s="10"/>
       <c r="P147" s="6" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="Q147" s="10" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="148" spans="2:17" x14ac:dyDescent="0.25">
       <c r="I148" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="M148" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="N148" s="11">
         <v>23.278130416666666</v>
       </c>
       <c r="O148" s="10"/>
       <c r="P148" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="Q148" s="10" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="149" spans="2:17" x14ac:dyDescent="0.25">
       <c r="I149" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="M149" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="N149" s="10">
         <v>13.15</v>
       </c>
       <c r="O149" s="10"/>
       <c r="P149" s="10" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="Q149" s="10" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="150" spans="2:17" x14ac:dyDescent="0.25">
       <c r="I150" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="M150" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N150" s="10">
         <v>5.26</v>
       </c>
       <c r="O150" s="10"/>
       <c r="P150" s="10" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="Q150" s="10" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="151" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B151" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="I151" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="M151" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N151" s="12">
         <v>1.7546281240590185</v>
       </c>
       <c r="O151" s="10"/>
       <c r="P151" s="10" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="Q151" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="152" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B152" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="I152" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="M152" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N152" s="12">
         <v>5.1828516694033944</v>
       </c>
       <c r="O152" s="10"/>
       <c r="P152" s="6" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="Q152" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="153" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B153" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="I153" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="M153" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N153" s="13">
         <v>4.0531064740502947</v>
       </c>
       <c r="P153" s="6" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="Q153" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="154" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B154" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="I154" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="M154" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N154" s="13">
         <v>4.3591310772039646</v>
       </c>
       <c r="P154" s="6" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="Q154" s="6" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="155" spans="2:17" x14ac:dyDescent="0.25">
@@ -5378,71 +5375,71 @@
     </row>
     <row r="156" spans="2:17" x14ac:dyDescent="0.25">
       <c r="I156" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="M156" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="N156" s="13">
         <v>14.6</v>
       </c>
       <c r="P156" s="6"/>
       <c r="Q156" s="4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="157" spans="2:17" x14ac:dyDescent="0.25">
       <c r="I157" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="K157" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="M157" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="N157" s="13">
         <v>37.744765138888887</v>
       </c>
       <c r="P157" s="6"/>
       <c r="Q157" s="6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="158" spans="2:17" x14ac:dyDescent="0.25">
       <c r="I158" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="K158" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="M158" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="N158" s="13">
         <v>50.107162083333336</v>
       </c>
       <c r="P158" s="6"/>
       <c r="Q158" s="6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="159" spans="2:17" x14ac:dyDescent="0.25">
       <c r="I159" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="K159" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="M159" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="N159" s="13">
         <v>36.955675972222224</v>
       </c>
       <c r="P159" s="6"/>
       <c r="Q159" s="6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="160" spans="2:17" x14ac:dyDescent="0.25">
@@ -5453,68 +5450,68 @@
     </row>
     <row r="161" spans="1:17" x14ac:dyDescent="0.25">
       <c r="I161" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="M161" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N161" s="13">
         <v>1.6176327916666666</v>
       </c>
       <c r="O161" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P161" s="6" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="Q161" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="162" spans="1:17" x14ac:dyDescent="0.25">
       <c r="I162" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="M162" s="10" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="N162" s="13">
         <f>3.07744775/0.85</f>
         <v>3.6205267647058825</v>
       </c>
       <c r="O162" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="P162" s="6" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="Q162" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="163" spans="1:17" x14ac:dyDescent="0.25">
       <c r="I163" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="M163" s="10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N163" s="13">
         <v>0.25</v>
       </c>
       <c r="O163" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="P163" s="6" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="Q163" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="165" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B165" s="1"/>
       <c r="C165" s="1"/>
@@ -5535,26 +5532,26 @@
     </row>
     <row r="166" spans="1:17" x14ac:dyDescent="0.25">
       <c r="M166" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N166" s="9">
         <v>0</v>
       </c>
       <c r="P166" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="167" spans="1:17" x14ac:dyDescent="0.25">
       <c r="M167" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N167" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
     </row>
     <row r="169" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="B169" s="1"/>
       <c r="C169" s="1"/>
@@ -5575,53 +5572,53 @@
     </row>
     <row r="171" spans="1:17" x14ac:dyDescent="0.25">
       <c r="M171" s="9" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="N171" s="9">
         <v>100</v>
       </c>
       <c r="O171" s="9" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="P171" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="172" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H172" s="6" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="M172" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="N172">
         <v>88</v>
       </c>
       <c r="O172" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="P172" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="Q172" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
     </row>
     <row r="173" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H173" s="6" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="M173" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="N173">
         <v>90</v>
       </c>
       <c r="O173" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="Q173" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
     </row>
     <row r="174" spans="1:17" x14ac:dyDescent="0.25">
@@ -5630,19 +5627,19 @@
     <row r="175" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H175" s="6"/>
       <c r="M175" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="N175">
         <v>1.6E-2</v>
       </c>
       <c r="O175" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="P175" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="Q175" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
     </row>
     <row r="176" spans="1:17" x14ac:dyDescent="0.25">
@@ -5650,173 +5647,173 @@
     </row>
     <row r="177" spans="1:17" x14ac:dyDescent="0.25">
       <c r="M177" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="N177" s="13">
         <f>0.16*10.36*0.9</f>
         <v>1.4918400000000001</v>
       </c>
       <c r="O177" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="P177" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="Q177" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
     </row>
     <row r="180" spans="1:17" x14ac:dyDescent="0.25">
       <c r="M180" s="9" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="N180" s="9">
         <v>-99</v>
       </c>
       <c r="O180" s="9"/>
       <c r="P180" s="9" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
     </row>
     <row r="181" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C181" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="M181" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="N181">
         <v>17</v>
       </c>
       <c r="O181" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="Q181" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
     </row>
     <row r="182" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C182" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="M182" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="N182">
         <v>17</v>
       </c>
       <c r="O182" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="Q182" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
     </row>
     <row r="183" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C183" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="M183" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="N183">
         <v>17</v>
       </c>
       <c r="O183" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="Q183" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
     </row>
     <row r="184" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C184" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="M184" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="N184">
         <v>14</v>
       </c>
       <c r="O184" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="Q184" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
     </row>
     <row r="186" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C186" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="M186" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="N186">
         <v>14</v>
       </c>
       <c r="O186" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="Q186" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="187" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C187" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="M187" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="N187">
         <v>14</v>
       </c>
       <c r="O187" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="Q187" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="188" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C188" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="M188" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="N188">
         <v>14</v>
       </c>
       <c r="O188" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="Q188" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="189" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C189" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="M189" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="N189">
         <v>9</v>
       </c>
       <c r="O189" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="Q189" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="191" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
@@ -5837,161 +5834,161 @@
     </row>
     <row r="195" spans="1:17" x14ac:dyDescent="0.25">
       <c r="M195" s="9" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="N195" s="9">
         <v>0</v>
       </c>
       <c r="O195" s="9" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="P195" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="196" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B196" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="M196" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="N196">
         <v>302</v>
       </c>
       <c r="O196" t="s">
+        <v>159</v>
+      </c>
+      <c r="P196" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q196" t="s">
         <v>163</v>
-      </c>
-      <c r="P196" t="s">
-        <v>164</v>
-      </c>
-      <c r="Q196" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="197" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B197" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="M197" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="N197">
         <v>197</v>
       </c>
       <c r="O197" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="P197" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="Q197" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="198" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B198" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="M198" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="N198">
         <v>216</v>
       </c>
       <c r="O198" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="P198" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="Q198" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
     </row>
     <row r="199" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B199" t="s">
+        <v>154</v>
+      </c>
+      <c r="M199" t="s">
         <v>158</v>
-      </c>
-      <c r="M199" t="s">
-        <v>162</v>
       </c>
       <c r="N199">
         <v>216</v>
       </c>
       <c r="O199" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="P199" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="Q199" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
     </row>
     <row r="200" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B200" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="M200" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="N200">
         <v>216</v>
       </c>
       <c r="O200" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="P200" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="Q200" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
     </row>
     <row r="201" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B201" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="M201" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="N201">
         <v>216</v>
       </c>
       <c r="O201" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="P201" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="Q201" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
     </row>
     <row r="202" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B202" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="M202" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="N202">
         <v>216</v>
       </c>
       <c r="O202" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="P202" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="Q202" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
     </row>
     <row r="204" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="B204" s="1"/>
       <c r="C204" s="1"/>
@@ -6012,185 +6009,185 @@
     </row>
     <row r="205" spans="1:17" x14ac:dyDescent="0.25">
       <c r="M205" s="9" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="N205" s="9">
         <v>0</v>
       </c>
       <c r="O205" s="9" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="P205" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="206" spans="1:17" x14ac:dyDescent="0.25">
       <c r="M206" s="9" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="N206" s="9">
         <v>0</v>
       </c>
       <c r="O206" s="9" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="P206" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="207" spans="1:17" x14ac:dyDescent="0.25">
       <c r="M207" s="9" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="N207" s="9">
         <v>0</v>
       </c>
       <c r="O207" s="9" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="P207" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="209" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="D209" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="E209" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="F209" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="G209" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="M209" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="N209" s="25">
         <f>'energy stables'!E24</f>
         <v>3.5302245250431775E-2</v>
       </c>
       <c r="O209" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="P209" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="Q209" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="210" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
+        <v>197</v>
+      </c>
+      <c r="D210" t="s">
+        <v>191</v>
+      </c>
+      <c r="E210" t="s">
+        <v>200</v>
+      </c>
+      <c r="F210" t="s">
         <v>201</v>
       </c>
-      <c r="D210" t="s">
-        <v>195</v>
-      </c>
-      <c r="E210" t="s">
-        <v>204</v>
-      </c>
-      <c r="F210" t="s">
-        <v>205</v>
-      </c>
       <c r="M210" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="N210" s="24">
         <f>'energy stables'!D26</f>
         <v>308.33833333333342</v>
       </c>
       <c r="O210" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="P210" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="Q210" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="211" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="D211" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="E211" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="F211" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="G211" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="M211" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="N211" s="25">
         <f>'energy stables'!E27</f>
         <v>4.1036269430051814E-2</v>
       </c>
       <c r="O211" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="Q211" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="213" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="D213" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="M213" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="N213" s="24">
         <f>'energy stables'!D29</f>
         <v>170.33333333333331</v>
       </c>
       <c r="O213" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="P213" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="Q213" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="214" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="D214" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="M214" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="N214" s="24">
         <f>'energy stables'!D31</f>
         <v>332.32333333333338</v>
       </c>
       <c r="O214" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="P214" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="Q214" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="215" spans="1:17" x14ac:dyDescent="0.25">
@@ -6198,330 +6195,330 @@
     </row>
     <row r="216" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="D216" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="E216" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="F216" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="M216" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="N216" s="25">
         <f>(290+1078)/100000</f>
         <v>1.3679999999999999E-2</v>
       </c>
       <c r="O216" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="P216" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="Q216" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="217" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D217" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="E217" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="F217" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="M217" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="N217" s="25">
         <f>77000/100000</f>
         <v>0.77</v>
       </c>
       <c r="O217" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="Q217" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="218" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="D218" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="E218" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="F218" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="M218" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="N218" s="25">
         <f>(3340+9790)/100000</f>
         <v>0.1313</v>
       </c>
       <c r="O218" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="P218" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="Q218" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="220" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="D220" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="F220" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="M220" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="N220">
         <f>'energy stables'!D49</f>
         <v>3.5</v>
       </c>
       <c r="O220" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="Q220" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
     </row>
     <row r="221" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D221" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="F221" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="M221" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="N221">
         <f>'energy stables'!D50</f>
         <v>12.5</v>
       </c>
       <c r="O221" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="Q221" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
     </row>
     <row r="222" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="D222" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="F222" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="M222" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="N222">
         <f>'energy stables'!D51</f>
         <v>34</v>
       </c>
       <c r="O222" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="Q222" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
     </row>
     <row r="223" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="D223" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="F223" t="s">
+        <v>317</v>
+      </c>
+      <c r="M223" t="s">
         <v>321</v>
-      </c>
-      <c r="M223" t="s">
-        <v>325</v>
       </c>
       <c r="N223">
         <f>'energy stables'!D53</f>
         <v>0.04</v>
       </c>
       <c r="O223" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="Q223" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
     </row>
     <row r="224" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D224" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="F224" t="s">
+        <v>317</v>
+      </c>
+      <c r="M224" t="s">
         <v>321</v>
-      </c>
-      <c r="M224" t="s">
-        <v>325</v>
       </c>
       <c r="N224" s="13">
         <f>'energy stables'!D54</f>
         <v>0.1</v>
       </c>
       <c r="O224" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="Q224" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
     </row>
     <row r="225" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="D225" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="F225" t="s">
+        <v>317</v>
+      </c>
+      <c r="M225" t="s">
         <v>321</v>
-      </c>
-      <c r="M225" t="s">
-        <v>325</v>
       </c>
       <c r="N225" s="13">
         <f>'energy stables'!D55</f>
         <v>0.26</v>
       </c>
       <c r="O225" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="Q225" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
     </row>
     <row r="227" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="D227" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="E227" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="M227" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="N227" s="13">
         <f>'energy stables'!D65</f>
         <v>0.14449999999999999</v>
       </c>
       <c r="O227" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="P227" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="Q227" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="228" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="D228" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="E228" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="M228" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="N228" s="13">
         <f>'energy stables'!D67</f>
         <v>3.9295</v>
       </c>
       <c r="O228" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="P228" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="Q228" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="229" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="D229" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="E229" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="F229" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="M229" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="N229">
         <v>0</v>
       </c>
       <c r="O229" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="P229" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
     </row>
     <row r="230" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="D230" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="E230" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="F230" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="M230" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="N230">
         <v>0</v>
@@ -6532,114 +6529,114 @@
     </row>
     <row r="231" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D231" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="E231" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="F231" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="M231" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="N231" s="13">
         <f>4.7*(1/3.6)</f>
         <v>1.3055555555555556</v>
       </c>
       <c r="O231" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="P231" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="Q231" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
     </row>
     <row r="233" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="D233" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="M233" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="N233" s="24">
         <f>0.05*1000*(1/3.6)</f>
         <v>13.888888888888889</v>
       </c>
       <c r="O233" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="P233" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="Q233" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
     </row>
     <row r="234" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="D234" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="M234" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="N234" s="24">
         <f>0.05*1000*(1/3.6)</f>
         <v>13.888888888888889</v>
       </c>
       <c r="O234" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="P234" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="Q234" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
     </row>
     <row r="235" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="D235" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="F235" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="M235" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="N235">
         <v>0</v>
       </c>
       <c r="P235" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
     </row>
     <row r="236" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="D236" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="F236" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="M236" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="N236">
         <v>0</v>
@@ -6665,7 +6662,7 @@
   <sheetData>
     <row r="3" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B3" s="53" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C3" s="54"/>
       <c r="D3" s="54"/>
@@ -6685,37 +6682,37 @@
     </row>
     <row r="4" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B4" s="51" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B5" s="27"/>
       <c r="C5" s="30"/>
       <c r="D5" s="46" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="E5" s="28" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="F5" s="30" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="G5" s="29" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="H5" s="28" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="I5" s="30" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
     </row>
     <row r="6" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B6" s="31" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C6" s="44" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="D6" s="31">
         <v>150</v>
@@ -6730,10 +6727,10 @@
     </row>
     <row r="7" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B7" s="31" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C7" s="44" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="D7" s="31">
         <v>150</v>
@@ -6748,10 +6745,10 @@
     </row>
     <row r="8" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B8" s="31" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="C8" s="44" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="D8" s="31">
         <v>10500</v>
@@ -6776,10 +6773,10 @@
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B10" s="31" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C10" s="44" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="D10" s="31">
         <v>652</v>
@@ -6804,15 +6801,15 @@
         <v>123.33333333333333</v>
       </c>
       <c r="J10" s="26" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B11" s="31" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="C11" s="44" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="D11" s="31">
         <v>3</v>
@@ -6840,10 +6837,10 @@
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B12" s="31" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C12" s="44" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="D12" s="31">
         <v>40</v>
@@ -6868,15 +6865,15 @@
         <v>10.333333333333332</v>
       </c>
       <c r="J12" s="26" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B13" s="31" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="C13" s="44" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="D13" s="31">
         <v>216</v>
@@ -6904,10 +6901,10 @@
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B14" s="31" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="C14" s="44" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="D14" s="31">
         <v>386</v>
@@ -6930,15 +6927,15 @@
         <v>0</v>
       </c>
       <c r="J14" s="26" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
     <row r="15" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B15" s="31" t="s">
+        <v>215</v>
+      </c>
+      <c r="C15" s="44" t="s">
         <v>219</v>
-      </c>
-      <c r="C15" s="44" t="s">
-        <v>223</v>
       </c>
       <c r="D15" s="31">
         <v>216</v>
@@ -6975,10 +6972,10 @@
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B17" s="36" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="C17" s="44" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="D17" s="36">
         <f>SUM(D10:D15)</f>
@@ -7007,10 +7004,10 @@
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B18" s="31" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="C18" s="44" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="D18" s="31">
         <v>868</v>
@@ -7065,10 +7062,10 @@
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B20" s="42" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C20" s="45" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="D20" s="42">
         <v>23</v>
@@ -7083,25 +7080,25 @@
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B22" s="71" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B23" s="79"/>
       <c r="C23" s="80"/>
       <c r="D23" s="81" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="E23" s="82" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B24" s="64" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C24" s="65" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="D24" s="72">
         <v>0</v>
@@ -7113,10 +7110,10 @@
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B25" s="64" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="C25" s="65" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="D25" s="72">
         <v>0</v>
@@ -7127,10 +7124,10 @@
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B26" s="64" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C26" s="65" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="D26" s="75">
         <f>SUM(E11:E13,E15,H11:H13,H15)/2</f>
@@ -7142,10 +7139,10 @@
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B27" s="64" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C27" s="65" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="D27" s="72">
         <v>0</v>
@@ -7163,10 +7160,10 @@
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B29" s="64" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C29" s="65" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="D29" s="75">
         <f>SUM(F10,I10)/2</f>
@@ -7178,10 +7175,10 @@
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B30" s="64" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="C30" s="65" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="D30" s="72">
         <v>0</v>
@@ -7192,10 +7189,10 @@
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B31" s="64" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C31" s="65" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="D31" s="75">
         <f>SUM(F11:F13,F15,I11:I13,I15)</f>
@@ -7207,10 +7204,10 @@
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B32" s="66" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C32" s="67" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="D32" s="76">
         <v>0</v>
@@ -7221,7 +7218,7 @@
     </row>
     <row r="34" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B34" s="53" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C34" s="54"/>
       <c r="D34" s="54"/>
@@ -7241,69 +7238,69 @@
     </row>
     <row r="35" spans="2:19" x14ac:dyDescent="0.25">
       <c r="J35" s="51" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="36" spans="2:19" x14ac:dyDescent="0.25">
       <c r="J36" s="46" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="K36" s="28"/>
       <c r="L36" s="28"/>
       <c r="M36" s="29" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="N36" s="29" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="O36" s="29" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="P36" s="50" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="Q36" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
     <row r="37" spans="2:19" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="51" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="J37" s="42" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="K37" s="14"/>
       <c r="L37" s="14"/>
       <c r="M37" s="59" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="N37" s="59" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="O37" s="59" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="P37" s="60" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="Q37" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
     <row r="38" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B38" s="46" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C38" s="29"/>
       <c r="D38" s="29" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="E38" s="50" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="J38" s="31" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -7320,14 +7317,14 @@
         <v>242</v>
       </c>
       <c r="Q38" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="R38" s="58"/>
       <c r="S38" s="58"/>
     </row>
     <row r="39" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="31" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="C39" s="4"/>
       <c r="D39" s="4">
@@ -7337,7 +7334,7 @@
         <v>0.4</v>
       </c>
       <c r="J39" s="31" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -7351,17 +7348,17 @@
         <v>9.6</v>
       </c>
       <c r="P39" s="32" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="Q39" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="R39" s="58"/>
       <c r="S39" s="58"/>
     </row>
     <row r="40" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B40" s="31" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="C40" s="4"/>
       <c r="D40" s="4">
@@ -7371,7 +7368,7 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="J40" s="31" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -7388,14 +7385,14 @@
         <v>43.2</v>
       </c>
       <c r="Q40" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="R40" s="58"/>
       <c r="S40" s="58"/>
     </row>
     <row r="41" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B41" s="31" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="C41" s="4"/>
       <c r="D41" s="4">
@@ -7405,7 +7402,7 @@
         <v>0.06</v>
       </c>
       <c r="J41" s="31" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -7422,14 +7419,14 @@
         <v>340</v>
       </c>
       <c r="Q41" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="R41" s="58"/>
       <c r="S41" s="58"/>
     </row>
     <row r="42" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B42" s="31" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="C42" s="4"/>
       <c r="D42" s="4">
@@ -7439,7 +7436,7 @@
         <v>0.04</v>
       </c>
       <c r="J42" s="31" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -7453,17 +7450,17 @@
         <v>4.2</v>
       </c>
       <c r="P42" s="32" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="Q42" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="R42" s="58"/>
       <c r="S42" s="58"/>
     </row>
     <row r="43" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B43" s="42" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="C43" s="14"/>
       <c r="D43" s="14">
@@ -7495,41 +7492,41 @@
     </row>
     <row r="44" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C44" s="68" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="D44" s="69">
         <f>D39*33+E39*26</f>
         <v>1660.4</v>
       </c>
       <c r="E44" s="70" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="J44" s="31" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
       <c r="M44" s="4" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="N44" s="4">
         <v>4</v>
       </c>
       <c r="O44" s="4" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="P44" s="32" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="Q44" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="R44" s="58"/>
       <c r="S44" s="58"/>
     </row>
     <row r="45" spans="2:19" x14ac:dyDescent="0.25">
       <c r="J45" s="31" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -7543,37 +7540,37 @@
         <v>0.7</v>
       </c>
       <c r="P45" s="32" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="Q45" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="R45" s="58"/>
       <c r="S45" s="58"/>
     </row>
     <row r="46" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B46" s="71" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="J46" s="31" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
       <c r="M46" s="4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="N46" s="4">
         <v>11</v>
       </c>
       <c r="O46" s="4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="P46" s="32" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="Q46" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="R46" s="58"/>
       <c r="S46" s="58"/>
@@ -7582,16 +7579,16 @@
       <c r="B47" s="27"/>
       <c r="C47" s="28"/>
       <c r="D47" s="86" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="E47" s="28" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="F47" s="28"/>
       <c r="G47" s="28"/>
       <c r="H47" s="30"/>
       <c r="J47" s="31" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -7602,13 +7599,13 @@
         <v>15</v>
       </c>
       <c r="O47" s="4" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="P47" s="32" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="Q47" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="R47" s="58"/>
       <c r="S47" s="58"/>
@@ -7617,22 +7614,22 @@
       <c r="B48" s="42"/>
       <c r="C48" s="14"/>
       <c r="D48" s="87" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="E48" s="14" t="s">
         <v>26</v>
       </c>
       <c r="F48" s="83" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="G48" s="83" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="H48" s="84" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="J48" s="31" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -7646,20 +7643,20 @@
         <v>1</v>
       </c>
       <c r="P48" s="32" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="Q48" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="R48" s="58"/>
       <c r="S48" s="58"/>
     </row>
     <row r="49" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B49" s="85" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C49" s="28" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="D49" s="88">
         <f>D42</f>
@@ -7678,7 +7675,7 @@
         <v>0</v>
       </c>
       <c r="J49" s="46" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="K49" s="29"/>
       <c r="L49" s="29"/>
@@ -7695,17 +7692,17 @@
         <v>1252</v>
       </c>
       <c r="Q49" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="R49" s="58"/>
       <c r="S49" s="58"/>
     </row>
     <row r="50" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B50" s="31" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="D50" s="88">
         <f>D39*0.25</f>
@@ -7727,7 +7724,7 @@
         <v>20</v>
       </c>
       <c r="J50" s="31" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -7748,10 +7745,10 @@
     </row>
     <row r="51" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B51" s="31" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="D51" s="89">
         <f>D39-D49-D50</f>
@@ -7770,7 +7767,7 @@
         <v>100</v>
       </c>
       <c r="J51" s="61" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="K51" s="63"/>
       <c r="L51" s="63"/>
@@ -7791,7 +7788,7 @@
         <v>34</v>
       </c>
       <c r="Q51" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="R51" s="58"/>
       <c r="S51" s="58"/>
@@ -7805,7 +7802,7 @@
       <c r="G52" s="72"/>
       <c r="H52" s="74"/>
       <c r="J52" s="55" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="K52" s="56"/>
       <c r="L52" s="56"/>
@@ -7816,21 +7813,21 @@
         <v>38</v>
       </c>
       <c r="O52" s="56" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="P52" s="57" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="Q52" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
     <row r="53" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B53" s="64" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="D53" s="88">
         <f>E42</f>
@@ -7849,32 +7846,32 @@
         <v>0</v>
       </c>
       <c r="J53" s="31" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
       <c r="M53" s="4" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="N53" s="4" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="O53" s="4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="P53" s="32" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="Q53" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
     <row r="54" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B54" s="31" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="D54" s="90">
         <f>E39*0.25</f>
@@ -7896,32 +7893,32 @@
         <v>20.000000000000018</v>
       </c>
       <c r="J54" s="31" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>
       <c r="M54" s="4" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="N54" s="4" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="O54" s="4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="P54" s="32" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="Q54" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
     <row r="55" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B55" s="42" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C55" s="14" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="D55" s="91">
         <f>E39-D53-D54</f>
@@ -7940,27 +7937,27 @@
         <v>100</v>
       </c>
       <c r="J55" s="31" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="K55" s="4"/>
       <c r="L55" s="4"/>
       <c r="M55" s="4" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="N55" s="4"/>
       <c r="O55" s="4" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="P55" s="32" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="Q55" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
     <row r="56" spans="2:19" x14ac:dyDescent="0.25">
       <c r="J56" s="42" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="K56" s="14"/>
       <c r="L56" s="14"/>
@@ -7979,7 +7976,7 @@
     </row>
     <row r="58" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B58" s="53" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="C58" s="52"/>
       <c r="D58" s="52"/>
@@ -7999,47 +7996,47 @@
     </row>
     <row r="59" spans="2:19" x14ac:dyDescent="0.25">
       <c r="J59" s="51" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="60" spans="2:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J60" s="27" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="K60" s="28"/>
       <c r="L60" s="28"/>
       <c r="M60" s="103" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="N60" s="103"/>
       <c r="O60" s="103" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="P60" s="104"/>
       <c r="Q60" s="4"/>
     </row>
     <row r="61" spans="2:19" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J61" s="100" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="K61" s="14"/>
       <c r="L61" s="14"/>
       <c r="M61" s="101" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="N61" s="101"/>
       <c r="O61" s="101" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="P61" s="102"/>
       <c r="Q61" s="4"/>
     </row>
     <row r="62" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B62" s="71" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="J62" s="27" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="K62" s="28"/>
       <c r="L62" s="28"/>
@@ -8047,13 +8044,13 @@
         <v>130</v>
       </c>
       <c r="N62" s="96" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="O62" s="28">
         <v>106</v>
       </c>
       <c r="P62" s="97" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="Q62" s="4"/>
     </row>
@@ -8061,16 +8058,16 @@
       <c r="B63" s="27"/>
       <c r="C63" s="28"/>
       <c r="D63" s="86" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="E63" s="28" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="F63" s="28"/>
       <c r="G63" s="28"/>
       <c r="H63" s="30"/>
       <c r="J63" s="31" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="K63" s="4"/>
       <c r="L63" s="4"/>
@@ -8088,22 +8085,22 @@
       <c r="B64" s="42"/>
       <c r="C64" s="14"/>
       <c r="D64" s="87" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="E64" s="14" t="s">
         <v>26</v>
       </c>
       <c r="F64" s="83" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="G64" s="83" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="H64" s="84" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="J64" s="31" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="K64" s="4"/>
       <c r="L64" s="4"/>
@@ -8119,7 +8116,7 @@
     </row>
     <row r="65" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B65" s="85" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C65" s="28"/>
       <c r="D65" s="90">
@@ -8139,7 +8136,7 @@
         <v>90</v>
       </c>
       <c r="J65" s="31" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="K65" s="4"/>
       <c r="L65" s="4"/>
@@ -8155,7 +8152,7 @@
     </row>
     <row r="66" spans="2:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B66" s="31" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="C66" s="4"/>
       <c r="D66" s="88">
@@ -8166,23 +8163,23 @@
       <c r="G66" s="75"/>
       <c r="H66" s="78"/>
       <c r="J66" s="94" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="K66" s="95"/>
       <c r="L66" s="95"/>
       <c r="M66" s="95" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="N66" s="95"/>
       <c r="O66" s="95" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="P66" s="44"/>
       <c r="Q66" s="4"/>
     </row>
     <row r="67" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B67" s="42" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C67" s="14"/>
       <c r="D67" s="91">
@@ -8202,7 +8199,7 @@
         <v>100</v>
       </c>
       <c r="J67" s="31" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="K67" s="4"/>
       <c r="L67" s="4"/>
@@ -8218,7 +8215,7 @@
     </row>
     <row r="68" spans="2:17" x14ac:dyDescent="0.25">
       <c r="J68" s="31" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="K68" s="4"/>
       <c r="L68" s="4"/>
@@ -8234,12 +8231,12 @@
     </row>
     <row r="69" spans="2:17" x14ac:dyDescent="0.25">
       <c r="J69" s="31" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="K69" s="4"/>
       <c r="L69" s="4"/>
       <c r="M69" s="4" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="N69" s="4"/>
       <c r="O69" s="4">
@@ -8250,12 +8247,12 @@
     </row>
     <row r="70" spans="2:17" x14ac:dyDescent="0.25">
       <c r="J70" s="31" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="K70" s="4"/>
       <c r="L70" s="4"/>
       <c r="M70" s="4" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="N70" s="4"/>
       <c r="O70" s="4">
@@ -8266,7 +8263,7 @@
     </row>
     <row r="71" spans="2:17" x14ac:dyDescent="0.25">
       <c r="J71" s="31" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="K71" s="4"/>
       <c r="L71" s="4"/>
@@ -8282,7 +8279,7 @@
     </row>
     <row r="72" spans="2:17" x14ac:dyDescent="0.25">
       <c r="J72" s="98" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="K72" s="93"/>
       <c r="L72" s="93"/>
@@ -8298,28 +8295,28 @@
     </row>
     <row r="73" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J73" s="55" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="K73" s="56"/>
       <c r="L73" s="56"/>
       <c r="M73" s="56" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="N73" s="56"/>
       <c r="O73" s="56" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="P73" s="57"/>
       <c r="Q73" s="4"/>
     </row>
     <row r="74" spans="2:17" x14ac:dyDescent="0.25">
       <c r="J74" s="31" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="K74" s="4"/>
       <c r="L74" s="4"/>
       <c r="M74" s="4" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="N74" s="4"/>
       <c r="O74" s="4">
@@ -8330,7 +8327,7 @@
     </row>
     <row r="75" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J75" s="55" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="K75" s="56"/>
       <c r="L75" s="56"/>
@@ -8367,7 +8364,7 @@
   <sheetData>
     <row r="3" spans="5:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E3" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="F3">
         <v>90</v>
@@ -8384,7 +8381,7 @@
     </row>
     <row r="4" spans="5:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E4" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="F4">
         <v>654</v>
@@ -8393,15 +8390,15 @@
         <v>80</v>
       </c>
       <c r="H4" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="I4" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
     </row>
     <row r="5" spans="5:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E5" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="F5">
         <v>11</v>
@@ -8410,66 +8407,66 @@
         <v>12</v>
       </c>
       <c r="H5" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="I5" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="6" spans="5:20" x14ac:dyDescent="0.25">
       <c r="E6" t="s">
+        <v>288</v>
+      </c>
+      <c r="F6" t="s">
+        <v>289</v>
+      </c>
+      <c r="G6" t="s">
+        <v>290</v>
+      </c>
+      <c r="H6" t="s">
+        <v>291</v>
+      </c>
+      <c r="I6" t="s">
         <v>292</v>
-      </c>
-      <c r="F6" t="s">
-        <v>293</v>
-      </c>
-      <c r="G6" t="s">
-        <v>294</v>
-      </c>
-      <c r="H6" t="s">
-        <v>295</v>
-      </c>
-      <c r="I6" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="7" spans="5:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E7" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="G7" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="I7" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="O7" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="S7" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
     </row>
     <row r="8" spans="5:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E8" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="H8" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="K8">
         <v>4</v>
       </c>
       <c r="P8" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="T8" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
     </row>
     <row r="9" spans="5:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E9" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="H9">
         <v>79</v>
@@ -8478,32 +8475,32 @@
         <v>7</v>
       </c>
       <c r="P9" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="T9" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
     </row>
     <row r="10" spans="5:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E10" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="H10" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="K10">
         <v>11</v>
       </c>
       <c r="P10" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="T10" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
     </row>
     <row r="11" spans="5:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E11" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="H11">
         <v>38</v>
@@ -8512,15 +8509,15 @@
         <v>15</v>
       </c>
       <c r="P11" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="T11" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12" spans="5:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E12" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="H12">
         <v>164</v>
@@ -8529,15 +8526,15 @@
         <v>66</v>
       </c>
       <c r="P12" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="T12" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
     </row>
     <row r="13" spans="5:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E13" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="H13">
         <v>2433</v>
@@ -8546,7 +8543,7 @@
         <v>689</v>
       </c>
       <c r="P13" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="T13">
         <v>1252</v>
@@ -8554,7 +8551,7 @@
     </row>
     <row r="14" spans="5:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E14" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="H14">
         <v>1441</v>
@@ -8563,7 +8560,7 @@
         <v>689</v>
       </c>
       <c r="P14" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="T14">
         <v>1218</v>
@@ -8571,47 +8568,47 @@
     </row>
     <row r="15" spans="5:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E15" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="L15" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="Q15" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16" spans="5:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E16" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="H16" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="K16" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="P16" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="T16" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17" spans="5:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E17" t="s">
+        <v>283</v>
+      </c>
+      <c r="H17" t="s">
+        <v>284</v>
+      </c>
+      <c r="K17" t="s">
+        <v>285</v>
+      </c>
+      <c r="P17" t="s">
+        <v>286</v>
+      </c>
+      <c r="T17" t="s">
         <v>287</v>
-      </c>
-      <c r="H17" t="s">
-        <v>288</v>
-      </c>
-      <c r="K17" t="s">
-        <v>289</v>
-      </c>
-      <c r="P17" t="s">
-        <v>290</v>
-      </c>
-      <c r="T17" t="s">
-        <v>291</v>
       </c>
     </row>
   </sheetData>
@@ -8630,47 +8627,47 @@
   <sheetData>
     <row r="3" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="F3" s="49" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="G3" s="49" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="H3" s="49" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="I3" s="49" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="J3" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
     <row r="4" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="F4" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="G4" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="H4" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="I4" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="J4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
     <row r="5" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="F5">
         <v>90</v>
@@ -8685,12 +8682,12 @@
         <v>242</v>
       </c>
       <c r="J5" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
     <row r="6" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="F6">
         <v>654</v>
@@ -8702,15 +8699,15 @@
         <v>9.6</v>
       </c>
       <c r="I6" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="J6" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
     <row r="7" spans="3:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="F7">
         <v>11</v>
@@ -8725,12 +8722,12 @@
         <v>43.2</v>
       </c>
       <c r="J7" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
     <row r="8" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="F8">
         <v>244</v>
@@ -8745,12 +8742,12 @@
         <v>340</v>
       </c>
       <c r="J8" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
     <row r="9" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="F9">
         <v>992</v>
@@ -8762,35 +8759,35 @@
         <v>4.2</v>
       </c>
       <c r="I9" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="J9" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
     <row r="10" spans="3:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="F10" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="G10">
         <v>4</v>
       </c>
       <c r="H10" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="I10" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J10" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
     <row r="11" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="F11">
         <v>79</v>
@@ -8802,35 +8799,35 @@
         <v>0.7</v>
       </c>
       <c r="I11" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="J11" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
     <row r="12" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F12" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G12">
         <v>11</v>
       </c>
       <c r="H12" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I12" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="J12" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
     <row r="13" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="F13">
         <v>38</v>
@@ -8839,18 +8836,18 @@
         <v>15</v>
       </c>
       <c r="H13" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="I13" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="J13" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
     <row r="14" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="F14">
         <v>164</v>
@@ -8862,15 +8859,15 @@
         <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="J14" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
     <row r="15" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F15">
         <v>2433</v>
@@ -8885,12 +8882,12 @@
         <v>1252</v>
       </c>
       <c r="J15" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
     <row r="16" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C16" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="F16">
         <v>1441</v>
@@ -8905,12 +8902,12 @@
         <v>1218</v>
       </c>
       <c r="J16" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
     <row r="17" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C17" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="F17">
         <v>23</v>
@@ -8919,75 +8916,75 @@
         <v>38</v>
       </c>
       <c r="H17" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I17" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="J17" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
     <row r="18" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C18" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="F18" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="G18" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="H18" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I18" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="J18" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
     <row r="19" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C19" t="s">
+        <v>304</v>
+      </c>
+      <c r="F19" t="s">
+        <v>282</v>
+      </c>
+      <c r="G19" t="s">
+        <v>307</v>
+      </c>
+      <c r="H19" t="s">
+        <v>85</v>
+      </c>
+      <c r="I19" t="s">
+        <v>282</v>
+      </c>
+      <c r="J19" t="s">
         <v>308</v>
-      </c>
-      <c r="F19" t="s">
-        <v>286</v>
-      </c>
-      <c r="G19" t="s">
-        <v>311</v>
-      </c>
-      <c r="H19" t="s">
-        <v>87</v>
-      </c>
-      <c r="I19" t="s">
-        <v>286</v>
-      </c>
-      <c r="J19" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="20" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C20" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="F20" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="H20" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="I20" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="J20" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
     <row r="21" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C21" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="F21">
         <v>1998</v>
@@ -9002,7 +8999,7 @@
         <v>2008</v>
       </c>
       <c r="J21" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
   </sheetData>
@@ -9018,72 +9015,72 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="17" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="17" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="48" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="48" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="48" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
     </row>
   </sheetData>

--- a/data/default/MachineryAndEnergyMgmt.xlsx
+++ b/data/default/MachineryAndEnergyMgmt.xlsx
@@ -477,7 +477,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1166" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1199" uniqueCount="418">
   <si>
     <t>f_crop</t>
   </si>
@@ -1864,6 +1864,51 @@
   </si>
   <si>
     <t>E_per_area_manure</t>
+  </si>
+  <si>
+    <t>Horses</t>
+  </si>
+  <si>
+    <t>Maria Berglund &amp; Elisabeth Falkhaven (2011) Hästsektorns klimatpåverkan. Hushållningssällskapet Halland</t>
+  </si>
+  <si>
+    <t>Ridskolor</t>
+  </si>
+  <si>
+    <t>Stuterier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Professionell tävlingsverksamhet </t>
+  </si>
+  <si>
+    <t>trav</t>
+  </si>
+  <si>
+    <t>dresyr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Turridning / eventföretag </t>
+  </si>
+  <si>
+    <t>AVG</t>
+  </si>
+  <si>
+    <t>El (kWh)</t>
+  </si>
+  <si>
+    <t>Transport (kWh)</t>
+  </si>
+  <si>
+    <t>horses</t>
+  </si>
+  <si>
+    <t>Median of 14 farms</t>
+  </si>
+  <si>
+    <t>Median of 14 farms (excl. Personel/visitor transports)</t>
+  </si>
+  <si>
+    <t>Camilla Källman (2021) Energianvändning och utsläpp av klimatgaser inom den gårdsnära hästnäringen - En gårdsstudie av 12 hästgårdar. LRF. https://www.hastkorare.se/files/MH-nr-2-2021-energianvandning-och-utslapp-av-klimatgaser-inom-den-gardsnara-hastnaringen-1.pdf</t>
   </si>
 </sst>
 </file>
@@ -2280,7 +2325,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="105">
+  <cellXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -2400,6 +2445,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2681,7 +2727,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U236"/>
+  <dimension ref="A1:U242"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="8" max="12" width="12.28515625" customWidth="1"/>
@@ -3430,89 +3476,71 @@
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H37" s="6"/>
       <c r="M37" s="6"/>
-      <c r="N37" s="15"/>
+      <c r="N37" s="10"/>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>149</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>325</v>
+        <v>193</v>
+      </c>
+      <c r="D38" t="s">
+        <v>414</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>248</v>
       </c>
       <c r="M38" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="N38" s="11">
-        <v>6.4777062142923141</v>
+      <c r="N38" s="10">
+        <v>100</v>
       </c>
       <c r="O38" t="s">
         <v>124</v>
       </c>
-      <c r="Q38" t="s">
-        <v>163</v>
-      </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>149</v>
+        <v>197</v>
+      </c>
+      <c r="D39" t="s">
+        <v>414</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="M39" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="N39" s="11">
-        <v>8.7567853491111922</v>
+      <c r="N39" s="10">
+        <v>100</v>
       </c>
       <c r="O39" t="s">
         <v>124</v>
       </c>
-      <c r="P39" t="s">
-        <v>166</v>
-      </c>
-      <c r="Q39" t="s">
-        <v>164</v>
-      </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>149</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>326</v>
-      </c>
-      <c r="M40" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="N40" s="18">
-        <v>59.671114354829328</v>
-      </c>
-      <c r="O40" t="s">
-        <v>124</v>
-      </c>
-      <c r="P40" s="19" t="s">
-        <v>167</v>
-      </c>
-      <c r="Q40" t="s">
-        <v>165</v>
-      </c>
+      <c r="H40" s="6"/>
+      <c r="M40" s="6"/>
+      <c r="N40" s="15"/>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>149</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="M41" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="N41" s="18">
-        <v>16.802918820320372</v>
+      <c r="N41" s="11">
+        <v>6.4777062142923141</v>
       </c>
       <c r="O41" t="s">
         <v>124</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
@@ -3520,16 +3548,22 @@
         <v>149</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M42" s="6" t="s">
         <v>150</v>
       </c>
       <c r="N42" s="11">
-        <v>7.4851294970113242</v>
+        <v>8.7567853491111922</v>
       </c>
       <c r="O42" t="s">
         <v>124</v>
+      </c>
+      <c r="P42" t="s">
+        <v>166</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
@@ -3537,357 +3571,351 @@
         <v>149</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="M43" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="N43" s="11">
-        <v>0.80634576443547301</v>
+      <c r="N43" s="18">
+        <v>59.671114354829328</v>
       </c>
       <c r="O43" t="s">
         <v>124</v>
       </c>
+      <c r="P43" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H44" s="6"/>
-      <c r="M44" s="6"/>
-      <c r="N44" s="11"/>
+      <c r="A44" t="s">
+        <v>149</v>
+      </c>
+      <c r="H44" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="M44" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="N44" s="18">
+        <v>16.802918820320372</v>
+      </c>
+      <c r="O44" t="s">
+        <v>124</v>
+      </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>344</v>
+        <v>149</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="M45" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="N45" s="18">
-        <v>70</v>
+      <c r="N45" s="11">
+        <v>7.4851294970113242</v>
       </c>
       <c r="O45" t="s">
         <v>124</v>
       </c>
-      <c r="P45" t="s">
-        <v>356</v>
-      </c>
-      <c r="Q45" t="s">
-        <v>355</v>
-      </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>344</v>
+        <v>149</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="M46" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="N46" s="18">
-        <v>30</v>
+      <c r="N46" s="11">
+        <v>0.80634576443547301</v>
       </c>
       <c r="O46" t="s">
         <v>124</v>
       </c>
-      <c r="Q46" t="s">
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H47" s="6"/>
+      <c r="M47" s="6"/>
+      <c r="N47" s="11"/>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>344</v>
+      </c>
+      <c r="H48" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="M48" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="N48" s="18">
+        <v>70</v>
+      </c>
+      <c r="O48" t="s">
+        <v>124</v>
+      </c>
+      <c r="P48" t="s">
+        <v>356</v>
+      </c>
+      <c r="Q48" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>345</v>
-      </c>
-      <c r="H47" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="M47" s="6" t="s">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>344</v>
+      </c>
+      <c r="H49" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="M49" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="N47" s="18">
-        <v>100</v>
-      </c>
-      <c r="O47" s="10" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H48" s="6"/>
-    </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="K49" t="s">
-        <v>117</v>
-      </c>
-      <c r="M49" t="s">
-        <v>126</v>
-      </c>
-      <c r="N49" s="15">
-        <v>80</v>
+      <c r="N49" s="18">
+        <v>30</v>
       </c>
       <c r="O49" t="s">
         <v>124</v>
       </c>
+      <c r="Q49" t="s">
+        <v>355</v>
+      </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="K50" t="s">
+      <c r="A50" t="s">
+        <v>345</v>
+      </c>
+      <c r="H50" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="M50" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="N50" s="18">
+        <v>100</v>
+      </c>
+      <c r="O50" s="10" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H51" s="6"/>
+    </row>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="K52" t="s">
+        <v>117</v>
+      </c>
+      <c r="M52" t="s">
+        <v>126</v>
+      </c>
+      <c r="N52" s="15">
+        <v>80</v>
+      </c>
+      <c r="O52" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="K53" t="s">
         <v>118</v>
       </c>
-      <c r="M50" t="s">
+      <c r="M53" t="s">
         <v>126</v>
       </c>
-      <c r="N50" s="15">
+      <c r="N53" s="15">
         <v>10</v>
       </c>
-      <c r="O50" t="s">
+      <c r="O53" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="K51" t="s">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="K54" t="s">
         <v>119</v>
       </c>
-      <c r="M51" t="s">
+      <c r="M54" t="s">
         <v>126</v>
       </c>
-      <c r="N51" s="15">
+      <c r="N54" s="15">
         <v>10</v>
       </c>
-      <c r="O51" t="s">
+      <c r="O54" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="B52" s="1"/>
-      <c r="C52" s="1"/>
-      <c r="D52" s="1"/>
-      <c r="E52" s="1"/>
-      <c r="F52" s="1"/>
-      <c r="G52" s="1"/>
-      <c r="H52" s="1"/>
-      <c r="I52" s="1"/>
-      <c r="J52" s="1"/>
-      <c r="K52" s="1"/>
-      <c r="L52" s="1"/>
-      <c r="M52" s="1"/>
-      <c r="N52" s="1"/>
-      <c r="O52" s="1"/>
-      <c r="P52" s="1"/>
-      <c r="Q52" s="1"/>
-    </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H53" s="4"/>
-      <c r="M53" s="9" t="s">
+      <c r="B55" s="1"/>
+      <c r="C55" s="1"/>
+      <c r="D55" s="1"/>
+      <c r="E55" s="1"/>
+      <c r="F55" s="1"/>
+      <c r="G55" s="1"/>
+      <c r="H55" s="1"/>
+      <c r="I55" s="1"/>
+      <c r="J55" s="1"/>
+      <c r="K55" s="1"/>
+      <c r="L55" s="1"/>
+      <c r="M55" s="1"/>
+      <c r="N55" s="1"/>
+      <c r="O55" s="1"/>
+      <c r="P55" s="1"/>
+      <c r="Q55" s="1"/>
+    </row>
+    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H56" s="4"/>
+      <c r="M56" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="N53" s="23">
+      <c r="N56" s="23">
         <v>0</v>
       </c>
-      <c r="O53" s="9"/>
-      <c r="P53" s="9" t="s">
+      <c r="O56" s="9"/>
+      <c r="P56" s="9" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H54" s="4"/>
-      <c r="N54" s="18"/>
-    </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H55" s="4" t="s">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H57" s="4"/>
+      <c r="N57" s="18"/>
+    </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H58" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="L55" t="s">
+      <c r="L58" t="s">
         <v>173</v>
       </c>
-      <c r="M55" t="s">
+      <c r="M58" t="s">
         <v>172</v>
       </c>
-      <c r="N55" s="18">
+      <c r="N58" s="18">
         <f>74100</f>
         <v>74100</v>
       </c>
-      <c r="O55" t="s">
+      <c r="O58" t="s">
         <v>182</v>
       </c>
-      <c r="P55" t="s">
+      <c r="P58" t="s">
         <v>176</v>
       </c>
-      <c r="Q55" t="s">
+      <c r="Q58" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H56" s="4" t="s">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H59" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="L56" t="s">
+      <c r="L59" t="s">
         <v>180</v>
       </c>
-      <c r="M56" t="s">
+      <c r="M59" t="s">
         <v>172</v>
       </c>
-      <c r="N56" s="11">
+      <c r="N59" s="11">
         <f>3.9</f>
         <v>3.9</v>
       </c>
-      <c r="O56" t="s">
+      <c r="O59" t="s">
         <v>182</v>
       </c>
-      <c r="Q56" t="s">
+      <c r="Q59" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H57" s="4" t="s">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H60" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="L57" t="s">
+      <c r="L60" t="s">
         <v>174</v>
       </c>
-      <c r="M57" t="s">
+      <c r="M60" t="s">
         <v>172</v>
       </c>
-      <c r="N57" s="11">
+      <c r="N60" s="11">
         <f>3.9</f>
         <v>3.9</v>
       </c>
-      <c r="O57" t="s">
+      <c r="O60" t="s">
         <v>182</v>
       </c>
-      <c r="Q57" t="s">
+      <c r="Q60" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H58" s="4" t="s">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H61" s="4" t="s">
         <v>322</v>
       </c>
-      <c r="L58" t="s">
+      <c r="L61" t="s">
         <v>173</v>
       </c>
-      <c r="M58" t="s">
+      <c r="M61" t="s">
         <v>172</v>
       </c>
-      <c r="N58" s="18">
+      <c r="N61" s="18">
         <v>0</v>
       </c>
-      <c r="O58" t="s">
+      <c r="O61" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H59" s="4" t="s">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H62" s="4" t="s">
         <v>322</v>
       </c>
-      <c r="L59" t="s">
+      <c r="L62" t="s">
         <v>181</v>
       </c>
-      <c r="M59" t="s">
+      <c r="M62" t="s">
         <v>172</v>
       </c>
-      <c r="N59" s="22">
-        <f t="shared" ref="N59:N60" si="0">N56</f>
+      <c r="N62" s="22">
+        <f t="shared" ref="N62:N63" si="0">N59</f>
         <v>3.9</v>
       </c>
-      <c r="O59" t="s">
+      <c r="O62" t="s">
         <v>182</v>
       </c>
-      <c r="P59" t="s">
+      <c r="P62" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H60" s="4" t="s">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H63" s="4" t="s">
         <v>322</v>
       </c>
-      <c r="L60" t="s">
+      <c r="L63" t="s">
         <v>174</v>
       </c>
-      <c r="M60" t="s">
+      <c r="M63" t="s">
         <v>172</v>
       </c>
-      <c r="N60" s="22">
+      <c r="N63" s="22">
         <f t="shared" si="0"/>
         <v>3.9</v>
       </c>
-      <c r="O60" t="s">
-        <v>182</v>
-      </c>
-      <c r="P60" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H61" s="6" t="s">
-        <v>325</v>
-      </c>
-      <c r="L61" t="s">
-        <v>173</v>
-      </c>
-      <c r="M61" t="s">
-        <v>172</v>
-      </c>
-      <c r="N61" s="18">
-        <v>73300</v>
-      </c>
-      <c r="O61" t="s">
-        <v>182</v>
-      </c>
-      <c r="P61" t="s">
-        <v>185</v>
-      </c>
-      <c r="Q61" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H62" s="6" t="s">
-        <v>325</v>
-      </c>
-      <c r="L62" t="s">
-        <v>180</v>
-      </c>
-      <c r="M62" t="s">
-        <v>172</v>
-      </c>
-      <c r="N62">
-        <v>10</v>
-      </c>
-      <c r="O62" t="s">
-        <v>182</v>
-      </c>
-      <c r="Q62" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H63" s="6" t="s">
-        <v>325</v>
-      </c>
-      <c r="L63" t="s">
-        <v>174</v>
-      </c>
-      <c r="M63" t="s">
-        <v>172</v>
-      </c>
-      <c r="N63">
-        <v>0.6</v>
-      </c>
       <c r="O63" t="s">
         <v>182</v>
       </c>
-      <c r="Q63" t="s">
-        <v>186</v>
+      <c r="P63" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H64" s="6" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="L64" t="s">
         <v>173</v>
@@ -3896,13 +3924,13 @@
         <v>172</v>
       </c>
       <c r="N64" s="18">
-        <v>56100</v>
+        <v>73300</v>
       </c>
       <c r="O64" t="s">
         <v>182</v>
       </c>
       <c r="P64" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q64" t="s">
         <v>186</v>
@@ -3910,7 +3938,7 @@
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H65" s="6" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="L65" t="s">
         <v>180</v>
@@ -3919,7 +3947,7 @@
         <v>172</v>
       </c>
       <c r="N65">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O65" t="s">
         <v>182</v>
@@ -3930,7 +3958,7 @@
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H66" s="6" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="L66" t="s">
         <v>174</v>
@@ -3939,7 +3967,7 @@
         <v>172</v>
       </c>
       <c r="N66">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="O66" t="s">
         <v>182</v>
@@ -3950,7 +3978,7 @@
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H67" s="6" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="L67" t="s">
         <v>173</v>
@@ -3959,13 +3987,13 @@
         <v>172</v>
       </c>
       <c r="N67" s="18">
-        <v>0</v>
+        <v>56100</v>
       </c>
       <c r="O67" t="s">
         <v>182</v>
       </c>
       <c r="P67" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q67" t="s">
         <v>186</v>
@@ -3973,16 +4001,16 @@
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H68" s="6" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="L68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="M68" t="s">
         <v>172</v>
       </c>
-      <c r="N68" s="18">
-        <v>300</v>
+      <c r="N68">
+        <v>5</v>
       </c>
       <c r="O68" t="s">
         <v>182</v>
@@ -3993,7 +4021,7 @@
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H69" s="6" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="L69" t="s">
         <v>174</v>
@@ -4001,8 +4029,8 @@
       <c r="M69" t="s">
         <v>172</v>
       </c>
-      <c r="N69" s="18">
-        <v>4</v>
+      <c r="N69">
+        <v>0.1</v>
       </c>
       <c r="O69" t="s">
         <v>182</v>
@@ -4013,7 +4041,10 @@
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H70" s="6" t="s">
-        <v>328</v>
+        <v>326</v>
+      </c>
+      <c r="L70" t="s">
+        <v>173</v>
       </c>
       <c r="M70" t="s">
         <v>172</v>
@@ -4024,43 +4055,56 @@
       <c r="O70" t="s">
         <v>182</v>
       </c>
-      <c r="P70" s="15"/>
+      <c r="P70" t="s">
+        <v>183</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>186</v>
+      </c>
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H71" s="6" t="s">
-        <v>327</v>
+        <v>326</v>
+      </c>
+      <c r="L71" t="s">
+        <v>181</v>
       </c>
       <c r="M71" t="s">
         <v>172</v>
       </c>
       <c r="N71" s="18">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="O71" t="s">
         <v>182</v>
       </c>
-      <c r="P71" s="15"/>
+      <c r="Q71" t="s">
+        <v>186</v>
+      </c>
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H72" s="4" t="s">
-        <v>323</v>
+      <c r="H72" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="L72" t="s">
+        <v>174</v>
       </c>
       <c r="M72" t="s">
         <v>172</v>
       </c>
       <c r="N72" s="18">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O72" t="s">
         <v>182</v>
       </c>
-      <c r="P72" s="15" t="s">
-        <v>179</v>
+      <c r="Q72" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H73" s="6" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="M73" t="s">
         <v>172</v>
@@ -4074,124 +4118,98 @@
       <c r="P73" s="15"/>
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H74" s="6"/>
-      <c r="N74" s="18"/>
+      <c r="H74" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="M74" t="s">
+        <v>172</v>
+      </c>
+      <c r="N74" s="18">
+        <v>0</v>
+      </c>
+      <c r="O74" t="s">
+        <v>182</v>
+      </c>
       <c r="P74" s="15"/>
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A75" s="1" t="s">
+      <c r="H75" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="M75" t="s">
+        <v>172</v>
+      </c>
+      <c r="N75" s="18">
+        <v>0</v>
+      </c>
+      <c r="O75" t="s">
+        <v>182</v>
+      </c>
+      <c r="P75" s="15" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H76" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="M76" t="s">
+        <v>172</v>
+      </c>
+      <c r="N76" s="18">
+        <v>0</v>
+      </c>
+      <c r="O76" t="s">
+        <v>182</v>
+      </c>
+      <c r="P76" s="15"/>
+    </row>
+    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H77" s="6"/>
+      <c r="N77" s="18"/>
+      <c r="P77" s="15"/>
+    </row>
+    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B75" s="1"/>
-      <c r="C75" s="1"/>
-      <c r="D75" s="1"/>
-      <c r="E75" s="1"/>
-      <c r="F75" s="1"/>
-      <c r="G75" s="1"/>
-      <c r="H75" s="1"/>
-      <c r="I75" s="1"/>
-      <c r="J75" s="1"/>
-      <c r="K75" s="1"/>
-      <c r="L75" s="1"/>
-      <c r="M75" s="1"/>
-      <c r="N75" s="1"/>
-      <c r="O75" s="1"/>
-      <c r="P75" s="1"/>
-      <c r="Q75" s="1"/>
-    </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A76" s="2" t="s">
+      <c r="B78" s="1"/>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="1"/>
+      <c r="K78" s="1"/>
+      <c r="L78" s="1"/>
+      <c r="M78" s="1"/>
+      <c r="N78" s="1"/>
+      <c r="O78" s="1"/>
+      <c r="P78" s="1"/>
+      <c r="Q78" s="1"/>
+    </row>
+    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A79" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B76" s="2"/>
-      <c r="C76" s="2"/>
-      <c r="D76" s="2"/>
-      <c r="E76" s="2"/>
-      <c r="F76" s="2"/>
-      <c r="G76" s="2"/>
-      <c r="H76" s="2"/>
-      <c r="I76" s="2"/>
-      <c r="J76" s="2"/>
-      <c r="K76" s="2"/>
-      <c r="L76" s="2"/>
-      <c r="M76" s="3"/>
-      <c r="N76" s="3"/>
-      <c r="O76" s="3"/>
-      <c r="P76" s="3"/>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B77" s="4"/>
-      <c r="C77" s="4"/>
-      <c r="D77" s="4"/>
-      <c r="E77" s="4"/>
-      <c r="F77" s="4"/>
-      <c r="G77" s="4"/>
-      <c r="H77" s="4"/>
-      <c r="I77" s="4"/>
-      <c r="J77" s="4"/>
-      <c r="K77" s="4"/>
-      <c r="L77" s="4"/>
-      <c r="M77" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="N77">
-        <v>10800</v>
-      </c>
-      <c r="O77" t="s">
-        <v>11</v>
-      </c>
-      <c r="P77" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B78" s="4"/>
-      <c r="C78" s="4"/>
-      <c r="D78" s="4"/>
-      <c r="E78" s="4"/>
-      <c r="F78" s="4"/>
-      <c r="G78" s="4"/>
-      <c r="H78" s="4"/>
-      <c r="I78" s="4"/>
-      <c r="J78" s="4"/>
-      <c r="K78" s="4"/>
-      <c r="L78" s="4"/>
-      <c r="M78" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="N78">
-        <v>5</v>
-      </c>
-      <c r="O78" t="s">
-        <v>13</v>
-      </c>
-      <c r="P78" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B79" s="4"/>
-      <c r="C79" s="4"/>
-      <c r="D79" s="4"/>
-      <c r="E79" s="4"/>
-      <c r="F79" s="4"/>
-      <c r="G79" s="4"/>
-      <c r="H79" s="4"/>
-      <c r="I79" s="4"/>
-      <c r="J79" s="4"/>
-      <c r="K79" s="4"/>
-      <c r="L79" s="4"/>
-      <c r="M79" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="N79">
-        <v>2</v>
-      </c>
-      <c r="O79" t="s">
-        <v>122</v>
-      </c>
-      <c r="P79" s="7"/>
+      <c r="B79" s="2"/>
+      <c r="C79" s="2"/>
+      <c r="D79" s="2"/>
+      <c r="E79" s="2"/>
+      <c r="F79" s="2"/>
+      <c r="G79" s="2"/>
+      <c r="H79" s="2"/>
+      <c r="I79" s="2"/>
+      <c r="J79" s="2"/>
+      <c r="K79" s="2"/>
+      <c r="L79" s="2"/>
+      <c r="M79" s="3"/>
+      <c r="N79" s="3"/>
+      <c r="O79" s="3"/>
+      <c r="P79" s="3"/>
+      <c r="Q79" s="3"/>
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B80" s="4"/>
@@ -4206,16 +4224,16 @@
       <c r="K80" s="4"/>
       <c r="L80" s="4"/>
       <c r="M80" s="4" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="N80">
-        <v>0.2</v>
+        <v>10800</v>
       </c>
       <c r="O80" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="P80" s="4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
@@ -4231,16 +4249,16 @@
       <c r="K81" s="4"/>
       <c r="L81" s="4"/>
       <c r="M81" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="N81">
-        <v>3.5000000000000003E-2</v>
+        <v>5</v>
       </c>
       <c r="O81" t="s">
-        <v>17</v>
-      </c>
-      <c r="P81" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
+      </c>
+      <c r="P81" s="4" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
@@ -4256,17 +4274,15 @@
       <c r="K82" s="4"/>
       <c r="L82" s="4"/>
       <c r="M82" s="6" t="s">
-        <v>25</v>
+        <v>121</v>
       </c>
       <c r="N82">
-        <v>250</v>
+        <v>2</v>
       </c>
       <c r="O82" t="s">
-        <v>19</v>
-      </c>
-      <c r="P82" s="5" t="s">
-        <v>18</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="P82" s="7"/>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B83" s="4"/>
@@ -4280,87 +4296,90 @@
       <c r="J83" s="4"/>
       <c r="K83" s="4"/>
       <c r="L83" s="4"/>
-      <c r="M83" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="N83" s="9">
-        <v>1</v>
-      </c>
-      <c r="O83" s="9"/>
-      <c r="P83" s="21" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="84" spans="1:21" ht="18" x14ac:dyDescent="0.35">
+      <c r="M83" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="N83">
+        <v>0.2</v>
+      </c>
+      <c r="O83" t="s">
+        <v>15</v>
+      </c>
+      <c r="P83" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B84" s="4"/>
       <c r="C84" s="4"/>
       <c r="D84" s="4"/>
       <c r="E84" s="4"/>
       <c r="F84" s="4"/>
       <c r="G84" s="4"/>
-      <c r="H84" s="4" t="s">
-        <v>248</v>
-      </c>
+      <c r="H84" s="4"/>
       <c r="I84" s="4"/>
       <c r="J84" s="4"/>
       <c r="K84" s="4"/>
       <c r="L84" s="4"/>
-      <c r="M84" s="6" t="s">
-        <v>49</v>
+      <c r="M84" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="N84">
-        <v>0.26</v>
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="O84" t="s">
+        <v>17</v>
       </c>
       <c r="P84" s="5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="85" spans="1:21" ht="18" x14ac:dyDescent="0.35">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B85" s="4"/>
       <c r="C85" s="4"/>
       <c r="D85" s="4"/>
       <c r="E85" s="4"/>
       <c r="F85" s="4"/>
       <c r="G85" s="4"/>
-      <c r="H85" s="4" t="s">
-        <v>322</v>
-      </c>
+      <c r="H85" s="4"/>
       <c r="I85" s="4"/>
       <c r="J85" s="4"/>
       <c r="K85" s="4"/>
       <c r="L85" s="4"/>
       <c r="M85" s="6" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="N85">
-        <v>0.26</v>
+        <v>250</v>
+      </c>
+      <c r="O85" t="s">
+        <v>19</v>
       </c>
       <c r="P85" s="5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="86" spans="1:21" ht="18" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B86" s="4"/>
       <c r="C86" s="4"/>
       <c r="D86" s="4"/>
       <c r="E86" s="4"/>
       <c r="F86" s="4"/>
       <c r="G86" s="4"/>
-      <c r="H86" s="4" t="s">
-        <v>323</v>
-      </c>
+      <c r="H86" s="4"/>
       <c r="I86" s="4"/>
       <c r="J86" s="4"/>
       <c r="K86" s="4"/>
       <c r="L86" s="4"/>
-      <c r="M86" s="6" t="s">
+      <c r="M86" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="N86">
-        <v>0.45</v>
-      </c>
-      <c r="P86" s="5" t="s">
-        <v>50</v>
+      <c r="N86" s="9">
+        <v>1</v>
+      </c>
+      <c r="O86" s="9"/>
+      <c r="P86" s="21" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="87" spans="1:21" ht="18" x14ac:dyDescent="0.35">
@@ -4370,401 +4389,428 @@
       <c r="E87" s="4"/>
       <c r="F87" s="4"/>
       <c r="G87" s="4"/>
-      <c r="H87" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="I87" s="6"/>
-      <c r="J87" s="6"/>
-      <c r="K87" s="6"/>
-      <c r="L87" s="6"/>
+      <c r="H87" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="I87" s="4"/>
+      <c r="J87" s="4"/>
+      <c r="K87" s="4"/>
+      <c r="L87" s="4"/>
       <c r="M87" s="6" t="s">
         <v>49</v>
       </c>
       <c r="N87">
-        <v>0.76</v>
+        <v>0.26</v>
       </c>
       <c r="P87" s="5" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="88" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:21" ht="18" x14ac:dyDescent="0.35">
       <c r="B88" s="4"/>
       <c r="C88" s="4"/>
       <c r="D88" s="4"/>
       <c r="E88" s="4"/>
       <c r="F88" s="4"/>
       <c r="G88" s="4"/>
-      <c r="H88" s="4"/>
+      <c r="H88" s="4" t="s">
+        <v>322</v>
+      </c>
       <c r="I88" s="4"/>
       <c r="J88" s="4"/>
       <c r="K88" s="4"/>
       <c r="L88" s="4"/>
       <c r="M88" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="N88">
+        <v>0.26</v>
+      </c>
+      <c r="P88" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="89" spans="1:21" ht="18" x14ac:dyDescent="0.35">
+      <c r="B89" s="4"/>
+      <c r="C89" s="4"/>
+      <c r="D89" s="4"/>
+      <c r="E89" s="4"/>
+      <c r="F89" s="4"/>
+      <c r="G89" s="4"/>
+      <c r="H89" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="I89" s="4"/>
+      <c r="J89" s="4"/>
+      <c r="K89" s="4"/>
+      <c r="L89" s="4"/>
+      <c r="M89" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="N89">
+        <v>0.45</v>
+      </c>
+      <c r="P89" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="90" spans="1:21" ht="18" x14ac:dyDescent="0.35">
+      <c r="B90" s="4"/>
+      <c r="C90" s="4"/>
+      <c r="D90" s="4"/>
+      <c r="E90" s="4"/>
+      <c r="F90" s="4"/>
+      <c r="G90" s="4"/>
+      <c r="H90" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="I90" s="6"/>
+      <c r="J90" s="6"/>
+      <c r="K90" s="6"/>
+      <c r="L90" s="6"/>
+      <c r="M90" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="N90">
+        <v>0.76</v>
+      </c>
+      <c r="P90" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="91" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B91" s="4"/>
+      <c r="C91" s="4"/>
+      <c r="D91" s="4"/>
+      <c r="E91" s="4"/>
+      <c r="F91" s="4"/>
+      <c r="G91" s="4"/>
+      <c r="H91" s="4"/>
+      <c r="I91" s="4"/>
+      <c r="J91" s="4"/>
+      <c r="K91" s="4"/>
+      <c r="L91" s="4"/>
+      <c r="M91" s="6" t="s">
         <v>27</v>
-      </c>
-      <c r="N88">
-        <v>4</v>
-      </c>
-      <c r="O88" t="s">
-        <v>21</v>
-      </c>
-      <c r="P88" s="7" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="90" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A90" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B90" s="2"/>
-      <c r="C90" s="2"/>
-      <c r="D90" s="2"/>
-      <c r="E90" s="2"/>
-      <c r="F90" s="2"/>
-      <c r="G90" s="2"/>
-      <c r="H90" s="2"/>
-      <c r="I90" s="2"/>
-      <c r="J90" s="2"/>
-      <c r="K90" s="2"/>
-      <c r="L90" s="2"/>
-      <c r="M90" s="2"/>
-      <c r="N90" s="2"/>
-      <c r="O90" s="2"/>
-      <c r="P90" s="2"/>
-      <c r="Q90" s="2"/>
-    </row>
-    <row r="91" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="M91" t="s">
-        <v>123</v>
       </c>
       <c r="N91">
         <v>4</v>
       </c>
       <c r="O91" t="s">
+        <v>21</v>
+      </c>
+      <c r="P91" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="93" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A93" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B93" s="2"/>
+      <c r="C93" s="2"/>
+      <c r="D93" s="2"/>
+      <c r="E93" s="2"/>
+      <c r="F93" s="2"/>
+      <c r="G93" s="2"/>
+      <c r="H93" s="2"/>
+      <c r="I93" s="2"/>
+      <c r="J93" s="2"/>
+      <c r="K93" s="2"/>
+      <c r="L93" s="2"/>
+      <c r="M93" s="2"/>
+      <c r="N93" s="2"/>
+      <c r="O93" s="2"/>
+      <c r="P93" s="2"/>
+      <c r="Q93" s="2"/>
+    </row>
+    <row r="94" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="M94" t="s">
+        <v>123</v>
+      </c>
+      <c r="N94">
+        <v>4</v>
+      </c>
+      <c r="O94" t="s">
         <v>29</v>
       </c>
-      <c r="P91" t="s">
+      <c r="P94" t="s">
         <v>28</v>
-      </c>
-      <c r="U91" s="6"/>
-    </row>
-    <row r="92" spans="1:21" ht="18" x14ac:dyDescent="0.35">
-      <c r="M92" t="s">
-        <v>45</v>
-      </c>
-      <c r="N92">
-        <v>0.9</v>
-      </c>
-      <c r="P92" t="s">
-        <v>30</v>
-      </c>
-      <c r="U92" s="6"/>
-    </row>
-    <row r="93" spans="1:21" ht="18" x14ac:dyDescent="0.35">
-      <c r="M93" t="s">
-        <v>38</v>
-      </c>
-      <c r="N93">
-        <v>1.2250000000000001</v>
-      </c>
-      <c r="O93" t="s">
-        <v>32</v>
-      </c>
-      <c r="P93" t="s">
-        <v>31</v>
-      </c>
-      <c r="U93" s="6"/>
-    </row>
-    <row r="94" spans="1:21" ht="18" x14ac:dyDescent="0.35">
-      <c r="M94" t="s">
-        <v>39</v>
-      </c>
-      <c r="N94">
-        <v>0.1</v>
-      </c>
-      <c r="P94" t="s">
-        <v>33</v>
       </c>
       <c r="U94" s="6"/>
     </row>
     <row r="95" spans="1:21" ht="18" x14ac:dyDescent="0.35">
       <c r="M95" t="s">
+        <v>45</v>
+      </c>
+      <c r="N95">
+        <v>0.9</v>
+      </c>
+      <c r="P95" t="s">
+        <v>30</v>
+      </c>
+      <c r="U95" s="6"/>
+    </row>
+    <row r="96" spans="1:21" ht="18" x14ac:dyDescent="0.35">
+      <c r="M96" t="s">
+        <v>38</v>
+      </c>
+      <c r="N96">
+        <v>1.2250000000000001</v>
+      </c>
+      <c r="O96" t="s">
+        <v>32</v>
+      </c>
+      <c r="P96" t="s">
+        <v>31</v>
+      </c>
+      <c r="U96" s="6"/>
+    </row>
+    <row r="97" spans="1:21" ht="18" x14ac:dyDescent="0.35">
+      <c r="M97" t="s">
+        <v>39</v>
+      </c>
+      <c r="N97">
+        <v>0.1</v>
+      </c>
+      <c r="P97" t="s">
+        <v>33</v>
+      </c>
+      <c r="U97" s="6"/>
+    </row>
+    <row r="98" spans="1:21" ht="18" x14ac:dyDescent="0.35">
+      <c r="M98" t="s">
         <v>40</v>
       </c>
-      <c r="N95">
+      <c r="N98">
         <v>0.01</v>
       </c>
-      <c r="P95" t="s">
+      <c r="P98" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="96" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="M96" t="s">
+    <row r="99" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="M99" t="s">
         <v>41</v>
       </c>
-      <c r="N96">
+      <c r="N99">
         <v>0.2</v>
       </c>
-      <c r="P96" t="s">
+      <c r="P99" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="97" spans="1:20" ht="18" x14ac:dyDescent="0.35">
-      <c r="M97" t="s">
+    <row r="100" spans="1:21" ht="18" x14ac:dyDescent="0.35">
+      <c r="M100" t="s">
         <v>42</v>
       </c>
-      <c r="N97">
+      <c r="N100">
         <v>0.8</v>
       </c>
-      <c r="P97" t="s">
+      <c r="P100" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="98" spans="1:20" ht="18" x14ac:dyDescent="0.35">
-      <c r="M98" t="s">
+    <row r="101" spans="1:21" ht="18" x14ac:dyDescent="0.35">
+      <c r="M101" t="s">
         <v>43</v>
       </c>
-      <c r="N98">
+      <c r="N101">
         <v>55</v>
       </c>
-      <c r="P98" t="s">
+      <c r="P101" t="s">
         <v>37</v>
       </c>
-      <c r="T98" s="4"/>
-    </row>
-    <row r="100" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A100" s="1" t="s">
+      <c r="T101" s="4"/>
+    </row>
+    <row r="103" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A103" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B100" s="8"/>
-      <c r="C100" s="8"/>
-      <c r="D100" s="8"/>
-      <c r="E100" s="8"/>
-      <c r="F100" s="8"/>
-      <c r="G100" s="8"/>
-      <c r="H100" s="8"/>
-      <c r="I100" s="8"/>
-      <c r="J100" s="8"/>
-      <c r="K100" s="8"/>
-      <c r="L100" s="8"/>
-      <c r="M100" s="8"/>
-      <c r="N100" s="8"/>
-      <c r="O100" s="8"/>
-      <c r="P100" s="8"/>
-      <c r="Q100" s="8"/>
-    </row>
-    <row r="101" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="M101" s="9" t="s">
+      <c r="B103" s="8"/>
+      <c r="C103" s="8"/>
+      <c r="D103" s="8"/>
+      <c r="E103" s="8"/>
+      <c r="F103" s="8"/>
+      <c r="G103" s="8"/>
+      <c r="H103" s="8"/>
+      <c r="I103" s="8"/>
+      <c r="J103" s="8"/>
+      <c r="K103" s="8"/>
+      <c r="L103" s="8"/>
+      <c r="M103" s="8"/>
+      <c r="N103" s="8"/>
+      <c r="O103" s="8"/>
+      <c r="P103" s="8"/>
+      <c r="Q103" s="8"/>
+    </row>
+    <row r="104" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="M104" s="9" t="s">
         <v>74</v>
-      </c>
-      <c r="N101" s="9">
-        <v>0</v>
-      </c>
-      <c r="O101" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="P101" s="9"/>
-    </row>
-    <row r="102" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="M102" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="N102" s="9">
-        <v>0</v>
-      </c>
-      <c r="O102" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="P102" s="9"/>
-    </row>
-    <row r="103" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="M103" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="N103" s="9">
-        <v>0</v>
-      </c>
-      <c r="O103" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="P103" s="9"/>
-    </row>
-    <row r="104" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="M104" s="9" t="s">
-        <v>73</v>
       </c>
       <c r="N104" s="9">
         <v>0</v>
       </c>
       <c r="O104" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P104" s="9"/>
     </row>
-    <row r="105" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="M105" s="9" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="N105" s="9">
         <v>0</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="P105" s="9"/>
     </row>
-    <row r="106" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="M106" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N106" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O106" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="P106" s="9" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="107" spans="1:20" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+      <c r="P106" s="9"/>
+    </row>
+    <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="M107" s="9" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="N107" s="9">
         <v>0</v>
       </c>
       <c r="O107" s="9" t="s">
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="P107" s="9"/>
     </row>
-    <row r="108" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="M108" s="9" t="s">
-        <v>402</v>
+        <v>90</v>
       </c>
       <c r="N108" s="9">
         <v>0</v>
       </c>
       <c r="O108" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="P108" s="9" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="109" spans="1:20" x14ac:dyDescent="0.25">
+        <v>91</v>
+      </c>
+      <c r="P108" s="9"/>
+    </row>
+    <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="M109" s="9" t="s">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="N109" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O109" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="P109" s="9"/>
-    </row>
-    <row r="110" spans="1:20" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+      <c r="P109" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="M110" s="9" t="s">
-        <v>130</v>
+        <v>53</v>
       </c>
       <c r="N110" s="9">
         <v>0</v>
       </c>
       <c r="O110" s="9" t="s">
-        <v>330</v>
+        <v>55</v>
       </c>
       <c r="P110" s="9"/>
     </row>
-    <row r="111" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="M111" s="9" t="s">
-        <v>57</v>
+        <v>402</v>
       </c>
       <c r="N111" s="9">
         <v>0</v>
       </c>
       <c r="O111" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="P111" s="9" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="112" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="M112" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="N112" s="9">
+        <v>0</v>
+      </c>
+      <c r="O112" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="P112" s="9"/>
+    </row>
+    <row r="113" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="M113" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="N113" s="9">
+        <v>0</v>
+      </c>
+      <c r="O113" s="9" t="s">
+        <v>330</v>
+      </c>
+      <c r="P113" s="9"/>
+    </row>
+    <row r="114" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="M114" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="N114" s="9">
+        <v>0</v>
+      </c>
+      <c r="O114" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="P111" s="9"/>
-    </row>
-    <row r="112" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="M112" s="9"/>
-      <c r="N112" s="9"/>
-      <c r="O112" s="9"/>
-      <c r="P112" s="9"/>
-    </row>
-    <row r="113" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="I113" t="s">
-        <v>59</v>
-      </c>
-      <c r="M113" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="N113" s="10">
-        <v>364</v>
-      </c>
-      <c r="O113" s="10"/>
-      <c r="P113" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q113" s="10"/>
-    </row>
-    <row r="114" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="I114" t="s">
-        <v>59</v>
-      </c>
-      <c r="M114" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="N114" s="10">
-        <v>18.8</v>
-      </c>
-      <c r="O114" s="10"/>
-      <c r="P114" s="10"/>
-      <c r="Q114" s="10"/>
+      <c r="P114" s="9"/>
     </row>
     <row r="115" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="I115" t="s">
-        <v>59</v>
-      </c>
-      <c r="M115" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="N115" s="10">
-        <v>0</v>
-      </c>
-      <c r="O115" s="10"/>
-      <c r="P115" s="10"/>
-      <c r="Q115" s="10"/>
+      <c r="M115" s="9"/>
+      <c r="N115" s="9"/>
+      <c r="O115" s="9"/>
+      <c r="P115" s="9"/>
     </row>
     <row r="116" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I116" t="s">
         <v>59</v>
       </c>
       <c r="M116" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="N116" s="10">
-        <v>10</v>
+        <v>364</v>
       </c>
       <c r="O116" s="10"/>
-      <c r="P116" s="10"/>
+      <c r="P116" s="10" t="s">
+        <v>82</v>
+      </c>
       <c r="Q116" s="10"/>
     </row>
     <row r="117" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I117" t="s">
         <v>59</v>
       </c>
-      <c r="J117" t="s">
-        <v>72</v>
-      </c>
       <c r="M117" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="N117" s="12">
-        <v>1</v>
+        <v>75</v>
+      </c>
+      <c r="N117" s="10">
+        <v>18.8</v>
       </c>
       <c r="O117" s="10"/>
       <c r="P117" s="10"/>
@@ -4774,14 +4820,11 @@
       <c r="I118" t="s">
         <v>59</v>
       </c>
-      <c r="J118" t="s">
-        <v>71</v>
-      </c>
       <c r="M118" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N118" s="10">
-        <v>0.88</v>
+        <v>0</v>
       </c>
       <c r="O118" s="10"/>
       <c r="P118" s="10"/>
@@ -4791,66 +4834,70 @@
       <c r="I119" t="s">
         <v>59</v>
       </c>
-      <c r="J119" t="s">
-        <v>70</v>
-      </c>
       <c r="M119" s="10" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="N119" s="10">
-        <v>0.78</v>
+        <v>10</v>
       </c>
       <c r="O119" s="10"/>
       <c r="P119" s="10"/>
       <c r="Q119" s="10"/>
     </row>
     <row r="120" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="M120" s="10"/>
-      <c r="N120" s="10"/>
+      <c r="I120" t="s">
+        <v>59</v>
+      </c>
+      <c r="J120" t="s">
+        <v>72</v>
+      </c>
+      <c r="M120" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="N120" s="12">
+        <v>1</v>
+      </c>
       <c r="O120" s="10"/>
       <c r="P120" s="10"/>
       <c r="Q120" s="10"/>
     </row>
     <row r="121" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I121" t="s">
-        <v>62</v>
+        <v>59</v>
+      </c>
+      <c r="J121" t="s">
+        <v>71</v>
       </c>
       <c r="M121" s="10" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="N121" s="10">
-        <v>652</v>
+        <v>0.88</v>
       </c>
       <c r="O121" s="10"/>
-      <c r="P121" s="10" t="s">
-        <v>80</v>
-      </c>
+      <c r="P121" s="10"/>
       <c r="Q121" s="10"/>
     </row>
     <row r="122" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I122" t="s">
-        <v>62</v>
+        <v>59</v>
+      </c>
+      <c r="J122" t="s">
+        <v>70</v>
       </c>
       <c r="M122" s="10" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="N122" s="10">
-        <v>0</v>
+        <v>0.78</v>
       </c>
       <c r="O122" s="10"/>
       <c r="P122" s="10"/>
       <c r="Q122" s="10"/>
     </row>
     <row r="123" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="I123" t="s">
-        <v>62</v>
-      </c>
-      <c r="M123" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="N123" s="10">
-        <v>5.0999999999999996</v>
-      </c>
+      <c r="M123" s="10"/>
+      <c r="N123" s="10"/>
       <c r="O123" s="10"/>
       <c r="P123" s="10"/>
       <c r="Q123" s="10"/>
@@ -4860,27 +4907,26 @@
         <v>62</v>
       </c>
       <c r="M124" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="N124" s="10">
-        <v>20</v>
+        <v>652</v>
       </c>
       <c r="O124" s="10"/>
-      <c r="P124" s="10"/>
+      <c r="P124" s="10" t="s">
+        <v>80</v>
+      </c>
       <c r="Q124" s="10"/>
     </row>
     <row r="125" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I125" t="s">
         <v>62</v>
       </c>
-      <c r="J125" t="s">
-        <v>72</v>
-      </c>
       <c r="M125" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="N125" s="12">
-        <v>1</v>
+        <v>75</v>
+      </c>
+      <c r="N125" s="10">
+        <v>0</v>
       </c>
       <c r="O125" s="10"/>
       <c r="P125" s="10"/>
@@ -4890,14 +4936,11 @@
       <c r="I126" t="s">
         <v>62</v>
       </c>
-      <c r="J126" t="s">
-        <v>71</v>
-      </c>
       <c r="M126" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="N126" s="12">
-        <v>0.7</v>
+        <v>76</v>
+      </c>
+      <c r="N126" s="10">
+        <v>5.0999999999999996</v>
       </c>
       <c r="O126" s="10"/>
       <c r="P126" s="10"/>
@@ -4907,66 +4950,70 @@
       <c r="I127" t="s">
         <v>62</v>
       </c>
-      <c r="J127" t="s">
-        <v>70</v>
-      </c>
       <c r="M127" s="10" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="N127" s="10">
-        <v>0.45</v>
+        <v>20</v>
       </c>
       <c r="O127" s="10"/>
       <c r="P127" s="10"/>
       <c r="Q127" s="10"/>
     </row>
     <row r="128" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="M128" s="10"/>
-      <c r="N128" s="10"/>
+      <c r="I128" t="s">
+        <v>62</v>
+      </c>
+      <c r="J128" t="s">
+        <v>72</v>
+      </c>
+      <c r="M128" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="N128" s="12">
+        <v>1</v>
+      </c>
       <c r="O128" s="10"/>
       <c r="P128" s="10"/>
       <c r="Q128" s="10"/>
     </row>
     <row r="129" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I129" t="s">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="J129" t="s">
+        <v>71</v>
       </c>
       <c r="M129" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="N129" s="10">
-        <v>46</v>
+        <v>77</v>
+      </c>
+      <c r="N129" s="12">
+        <v>0.7</v>
       </c>
       <c r="O129" s="10"/>
-      <c r="P129" s="10" t="s">
-        <v>81</v>
-      </c>
+      <c r="P129" s="10"/>
       <c r="Q129" s="10"/>
     </row>
     <row r="130" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I130" t="s">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="J130" t="s">
+        <v>70</v>
       </c>
       <c r="M130" s="10" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="N130" s="10">
-        <v>2.8</v>
+        <v>0.45</v>
       </c>
       <c r="O130" s="10"/>
       <c r="P130" s="10"/>
       <c r="Q130" s="10"/>
     </row>
     <row r="131" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="I131" t="s">
-        <v>61</v>
-      </c>
-      <c r="M131" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="N131" s="10">
-        <v>0</v>
-      </c>
+      <c r="M131" s="10"/>
+      <c r="N131" s="10"/>
       <c r="O131" s="10"/>
       <c r="P131" s="10"/>
       <c r="Q131" s="10"/>
@@ -4976,27 +5023,26 @@
         <v>61</v>
       </c>
       <c r="M132" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="N132" s="10">
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="O132" s="10"/>
-      <c r="P132" s="10"/>
+      <c r="P132" s="10" t="s">
+        <v>81</v>
+      </c>
       <c r="Q132" s="10"/>
     </row>
     <row r="133" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I133" t="s">
         <v>61</v>
       </c>
-      <c r="J133" t="s">
-        <v>72</v>
-      </c>
       <c r="M133" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="N133" s="12">
-        <v>1</v>
+        <v>75</v>
+      </c>
+      <c r="N133" s="10">
+        <v>2.8</v>
       </c>
       <c r="O133" s="10"/>
       <c r="P133" s="10"/>
@@ -5006,14 +5052,11 @@
       <c r="I134" t="s">
         <v>61</v>
       </c>
-      <c r="J134" t="s">
-        <v>71</v>
-      </c>
       <c r="M134" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N134" s="10">
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="O134" s="10"/>
       <c r="P134" s="10"/>
@@ -5023,61 +5066,66 @@
       <c r="I135" t="s">
         <v>61</v>
       </c>
-      <c r="J135" t="s">
-        <v>70</v>
-      </c>
       <c r="M135" s="10" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="N135" s="10">
-        <v>0.65</v>
+        <v>5</v>
       </c>
       <c r="O135" s="10"/>
       <c r="P135" s="10"/>
       <c r="Q135" s="10"/>
     </row>
     <row r="136" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="M136" s="10"/>
-      <c r="N136" s="10"/>
+      <c r="I136" t="s">
+        <v>61</v>
+      </c>
+      <c r="J136" t="s">
+        <v>72</v>
+      </c>
+      <c r="M136" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="N136" s="12">
+        <v>1</v>
+      </c>
       <c r="O136" s="10"/>
       <c r="P136" s="10"/>
       <c r="Q136" s="10"/>
     </row>
     <row r="137" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I137" t="s">
-        <v>64</v>
+        <v>61</v>
+      </c>
+      <c r="J137" t="s">
+        <v>71</v>
       </c>
       <c r="M137" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="N137" s="12">
-        <v>5.0999999999999996</v>
+        <v>77</v>
+      </c>
+      <c r="N137" s="10">
+        <v>0.85</v>
       </c>
       <c r="O137" s="10"/>
-      <c r="P137" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="Q137" s="4" t="s">
-        <v>94</v>
-      </c>
+      <c r="P137" s="10"/>
+      <c r="Q137" s="10"/>
     </row>
     <row r="138" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I138" t="s">
-        <v>65</v>
+        <v>61</v>
+      </c>
+      <c r="J138" t="s">
+        <v>70</v>
       </c>
       <c r="M138" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="N138" s="12">
-        <v>7.1</v>
+        <v>77</v>
+      </c>
+      <c r="N138" s="10">
+        <v>0.65</v>
       </c>
       <c r="O138" s="10"/>
-      <c r="P138" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="Q138" s="4" t="s">
-        <v>94</v>
-      </c>
+      <c r="P138" s="10"/>
+      <c r="Q138" s="10"/>
     </row>
     <row r="139" spans="9:17" x14ac:dyDescent="0.25">
       <c r="M139" s="10"/>
@@ -5088,268 +5136,249 @@
     </row>
     <row r="140" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I140" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="M140" s="10" t="s">
-        <v>53</v>
+        <v>90</v>
       </c>
       <c r="N140" s="12">
-        <v>3.7353333333333332</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="O140" s="10"/>
-      <c r="P140" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="Q140" s="6" t="s">
-        <v>87</v>
+      <c r="P140" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q140" s="4" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="141" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I141" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M141" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="N141" s="11">
-        <v>17.096931944444446</v>
+        <v>90</v>
+      </c>
+      <c r="N141" s="12">
+        <v>7.1</v>
       </c>
       <c r="O141" s="10"/>
       <c r="P141" s="6" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="Q141" s="4" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
     </row>
     <row r="142" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="I142" t="s">
-        <v>66</v>
-      </c>
-      <c r="M142" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="N142" s="12">
-        <v>1.2451111111111113</v>
-      </c>
+      <c r="M142" s="10"/>
+      <c r="N142" s="10"/>
       <c r="O142" s="10"/>
-      <c r="P142" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q142" s="10" t="s">
-        <v>87</v>
-      </c>
+      <c r="P142" s="10"/>
+      <c r="Q142" s="10"/>
     </row>
     <row r="143" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I143" t="s">
+        <v>60</v>
+      </c>
+      <c r="M143" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="N143" s="12">
+        <v>3.7353333333333332</v>
+      </c>
+      <c r="O143" s="10"/>
+      <c r="P143" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q143" s="6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="144" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="I144" t="s">
+        <v>63</v>
+      </c>
+      <c r="M144" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="N144" s="11">
+        <v>17.096931944444446</v>
+      </c>
+      <c r="O144" s="10"/>
+      <c r="P144" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q144" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="145" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="I145" t="s">
+        <v>66</v>
+      </c>
+      <c r="M145" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="N145" s="12">
+        <v>1.2451111111111113</v>
+      </c>
+      <c r="O145" s="10"/>
+      <c r="P145" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q145" s="10" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="146" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="I146" t="s">
         <v>400</v>
       </c>
-      <c r="M143" s="10" t="s">
+      <c r="M146" s="10" t="s">
         <v>402</v>
       </c>
-      <c r="N143" s="12">
+      <c r="N146" s="12">
         <f>(3.11+4.67)/2</f>
         <v>3.8899999999999997</v>
       </c>
-      <c r="O143" s="10"/>
-      <c r="P143" s="6" t="s">
-        <v>399</v>
-      </c>
-      <c r="Q143" s="10" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="144" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="I144" t="s">
-        <v>67</v>
-      </c>
-      <c r="M144" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="N144" s="12">
-        <v>3.1127777777777781</v>
-      </c>
-      <c r="O144" s="10"/>
-      <c r="P144" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="Q144" s="6" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="145" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="I145" t="s">
-        <v>68</v>
-      </c>
-      <c r="M145" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="N145" s="11">
-        <v>11.828555555555555</v>
-      </c>
-      <c r="O145" s="10"/>
-      <c r="P145" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q145" s="10" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="146" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="I146" t="s">
-        <v>96</v>
-      </c>
-      <c r="M146" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="N146" s="11">
-        <v>26.302972222222223</v>
-      </c>
       <c r="O146" s="10"/>
       <c r="P146" s="6" t="s">
-        <v>100</v>
+        <v>399</v>
       </c>
       <c r="Q146" s="10" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="147" spans="2:17" x14ac:dyDescent="0.25">
       <c r="I147" t="s">
-        <v>97</v>
+        <v>67</v>
       </c>
       <c r="M147" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="N147" s="11">
-        <v>11.3</v>
+      <c r="N147" s="12">
+        <v>3.1127777777777781</v>
       </c>
       <c r="O147" s="10"/>
-      <c r="P147" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q147" s="10" t="s">
-        <v>103</v>
+      <c r="P147" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q147" s="6" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="148" spans="2:17" x14ac:dyDescent="0.25">
       <c r="I148" t="s">
-        <v>98</v>
+        <v>68</v>
       </c>
       <c r="M148" s="10" t="s">
         <v>53</v>
       </c>
       <c r="N148" s="11">
-        <v>23.278130416666666</v>
+        <v>11.828555555555555</v>
       </c>
       <c r="O148" s="10"/>
-      <c r="P148" s="6" t="s">
-        <v>101</v>
+      <c r="P148" s="4" t="s">
+        <v>99</v>
       </c>
       <c r="Q148" s="10" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
     </row>
     <row r="149" spans="2:17" x14ac:dyDescent="0.25">
       <c r="I149" t="s">
-        <v>69</v>
+        <v>96</v>
       </c>
       <c r="M149" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="N149" s="10">
-        <v>13.15</v>
+      <c r="N149" s="11">
+        <v>26.302972222222223</v>
       </c>
       <c r="O149" s="10"/>
-      <c r="P149" s="10" t="s">
-        <v>105</v>
+      <c r="P149" s="6" t="s">
+        <v>100</v>
       </c>
       <c r="Q149" s="10" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
     </row>
     <row r="150" spans="2:17" x14ac:dyDescent="0.25">
       <c r="I150" t="s">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="M150" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="N150" s="10">
-        <v>5.26</v>
+        <v>53</v>
+      </c>
+      <c r="N150" s="11">
+        <v>11.3</v>
       </c>
       <c r="O150" s="10"/>
-      <c r="P150" s="10" t="s">
-        <v>105</v>
+      <c r="P150" s="6" t="s">
+        <v>102</v>
       </c>
       <c r="Q150" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="151" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B151" t="s">
-        <v>106</v>
-      </c>
       <c r="I151" t="s">
-        <v>69</v>
+        <v>98</v>
       </c>
       <c r="M151" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="N151" s="12">
-        <v>1.7546281240590185</v>
+        <v>53</v>
+      </c>
+      <c r="N151" s="11">
+        <v>23.278130416666666</v>
       </c>
       <c r="O151" s="10"/>
-      <c r="P151" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="Q151" s="4" t="s">
-        <v>108</v>
+      <c r="P151" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q151" s="10" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="152" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B152" t="s">
-        <v>109</v>
-      </c>
       <c r="I152" t="s">
         <v>69</v>
       </c>
       <c r="M152" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="N152" s="12">
-        <v>5.1828516694033944</v>
+        <v>53</v>
+      </c>
+      <c r="N152" s="10">
+        <v>13.15</v>
       </c>
       <c r="O152" s="10"/>
-      <c r="P152" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q152" s="4" t="s">
-        <v>108</v>
+      <c r="P152" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q152" s="10" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="153" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B153" t="s">
-        <v>110</v>
-      </c>
       <c r="I153" t="s">
         <v>69</v>
       </c>
       <c r="M153" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="N153" s="13">
-        <v>4.0531064740502947</v>
-      </c>
-      <c r="P153" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="Q153" s="4" t="s">
-        <v>108</v>
+      <c r="N153" s="10">
+        <v>5.26</v>
+      </c>
+      <c r="O153" s="10"/>
+      <c r="P153" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q153" s="10" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="154" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B154" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="I154" t="s">
         <v>69</v>
@@ -5357,384 +5386,395 @@
       <c r="M154" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="N154" s="13">
+      <c r="N154" s="12">
+        <v>1.7546281240590185</v>
+      </c>
+      <c r="O154" s="10"/>
+      <c r="P154" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q154" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="155" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B155" t="s">
+        <v>109</v>
+      </c>
+      <c r="I155" t="s">
+        <v>69</v>
+      </c>
+      <c r="M155" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="N155" s="12">
+        <v>5.1828516694033944</v>
+      </c>
+      <c r="O155" s="10"/>
+      <c r="P155" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q155" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="156" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B156" t="s">
+        <v>110</v>
+      </c>
+      <c r="I156" t="s">
+        <v>69</v>
+      </c>
+      <c r="M156" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="N156" s="13">
+        <v>4.0531064740502947</v>
+      </c>
+      <c r="P156" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q156" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="157" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B157" t="s">
+        <v>114</v>
+      </c>
+      <c r="I157" t="s">
+        <v>69</v>
+      </c>
+      <c r="M157" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="N157" s="13">
         <v>4.3591310772039646</v>
       </c>
-      <c r="P154" s="6" t="s">
+      <c r="P157" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="Q154" s="6" t="s">
+      <c r="Q157" s="6" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="155" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="M155" s="10"/>
-      <c r="N155" s="13"/>
-      <c r="P155" s="6"/>
-      <c r="Q155" s="6"/>
-    </row>
-    <row r="156" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="I156" t="s">
-        <v>116</v>
-      </c>
-      <c r="M156" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="N156" s="13">
-        <v>14.6</v>
-      </c>
-      <c r="P156" s="6"/>
-      <c r="Q156" s="4" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="157" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="I157" t="s">
-        <v>120</v>
-      </c>
-      <c r="K157" t="s">
-        <v>117</v>
-      </c>
-      <c r="M157" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="N157" s="13">
-        <v>37.744765138888887</v>
-      </c>
-      <c r="P157" s="6"/>
-      <c r="Q157" s="6" t="s">
-        <v>89</v>
-      </c>
-    </row>
     <row r="158" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="I158" t="s">
-        <v>120</v>
-      </c>
-      <c r="K158" t="s">
-        <v>118</v>
-      </c>
-      <c r="M158" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="N158" s="13">
-        <v>50.107162083333336</v>
-      </c>
+      <c r="M158" s="10"/>
+      <c r="N158" s="13"/>
       <c r="P158" s="6"/>
-      <c r="Q158" s="6" t="s">
-        <v>89</v>
-      </c>
+      <c r="Q158" s="6"/>
     </row>
     <row r="159" spans="2:17" x14ac:dyDescent="0.25">
       <c r="I159" t="s">
-        <v>120</v>
-      </c>
-      <c r="K159" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="M159" s="10" t="s">
         <v>53</v>
       </c>
       <c r="N159" s="13">
-        <v>36.955675972222224</v>
+        <v>14.6</v>
       </c>
       <c r="P159" s="6"/>
-      <c r="Q159" s="6" t="s">
+      <c r="Q159" s="4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="160" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="I160" t="s">
+        <v>120</v>
+      </c>
+      <c r="K160" t="s">
+        <v>117</v>
+      </c>
+      <c r="M160" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="N160" s="13">
+        <v>37.744765138888887</v>
+      </c>
+      <c r="P160" s="6"/>
+      <c r="Q160" s="6" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="160" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="M160" s="10"/>
-      <c r="N160" s="13"/>
-      <c r="P160" s="6"/>
-      <c r="Q160" s="6"/>
     </row>
     <row r="161" spans="1:17" x14ac:dyDescent="0.25">
       <c r="I161" t="s">
-        <v>127</v>
+        <v>120</v>
+      </c>
+      <c r="K161" t="s">
+        <v>118</v>
       </c>
       <c r="M161" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="N161" s="13">
-        <v>1.6176327916666666</v>
-      </c>
-      <c r="O161" t="s">
-        <v>56</v>
-      </c>
-      <c r="P161" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="Q161" s="4" t="s">
+        <v>50.107162083333336</v>
+      </c>
+      <c r="P161" s="6"/>
+      <c r="Q161" s="6" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="162" spans="1:17" x14ac:dyDescent="0.25">
       <c r="I162" t="s">
+        <v>120</v>
+      </c>
+      <c r="K162" t="s">
+        <v>119</v>
+      </c>
+      <c r="M162" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="N162" s="13">
+        <v>36.955675972222224</v>
+      </c>
+      <c r="P162" s="6"/>
+      <c r="Q162" s="6" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="163" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M163" s="10"/>
+      <c r="N163" s="13"/>
+      <c r="P163" s="6"/>
+      <c r="Q163" s="6"/>
+    </row>
+    <row r="164" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="I164" t="s">
+        <v>127</v>
+      </c>
+      <c r="M164" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="N164" s="13">
+        <v>1.6176327916666666</v>
+      </c>
+      <c r="O164" t="s">
+        <v>56</v>
+      </c>
+      <c r="P164" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="Q164" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="165" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="I165" t="s">
         <v>128</v>
       </c>
-      <c r="M162" s="10" t="s">
+      <c r="M165" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="N162" s="13">
+      <c r="N165" s="13">
         <f>3.07744775/0.85</f>
         <v>3.6205267647058825</v>
       </c>
-      <c r="O162" t="s">
+      <c r="O165" t="s">
         <v>330</v>
       </c>
-      <c r="P162" s="6" t="s">
+      <c r="P165" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="Q162" s="4" t="s">
+      <c r="Q165" s="4" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="163" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="I163" t="s">
+    <row r="166" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="I166" t="s">
         <v>129</v>
       </c>
-      <c r="M163" s="10" t="s">
+      <c r="M166" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="N163" s="13">
+      <c r="N166" s="13">
         <v>0.25</v>
       </c>
-      <c r="O163" t="s">
+      <c r="O166" t="s">
         <v>58</v>
       </c>
-      <c r="P163" s="6" t="s">
+      <c r="P166" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="Q163" s="4" t="s">
+      <c r="Q166" s="4" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="165" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A165" s="1" t="s">
+    <row r="168" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A168" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B165" s="1"/>
-      <c r="C165" s="1"/>
-      <c r="D165" s="1"/>
-      <c r="E165" s="1"/>
-      <c r="F165" s="1"/>
-      <c r="G165" s="1"/>
-      <c r="H165" s="1"/>
-      <c r="I165" s="1"/>
-      <c r="J165" s="1"/>
-      <c r="K165" s="1"/>
-      <c r="L165" s="1"/>
-      <c r="M165" s="8"/>
-      <c r="N165" s="8"/>
-      <c r="O165" s="8"/>
-      <c r="P165" s="8"/>
-      <c r="Q165" s="8"/>
-    </row>
-    <row r="166" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M166" s="9" t="s">
+      <c r="B168" s="1"/>
+      <c r="C168" s="1"/>
+      <c r="D168" s="1"/>
+      <c r="E168" s="1"/>
+      <c r="F168" s="1"/>
+      <c r="G168" s="1"/>
+      <c r="H168" s="1"/>
+      <c r="I168" s="1"/>
+      <c r="J168" s="1"/>
+      <c r="K168" s="1"/>
+      <c r="L168" s="1"/>
+      <c r="M168" s="8"/>
+      <c r="N168" s="8"/>
+      <c r="O168" s="8"/>
+      <c r="P168" s="8"/>
+      <c r="Q168" s="8"/>
+    </row>
+    <row r="169" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M169" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="N166" s="9">
+      <c r="N169" s="9">
         <v>0</v>
       </c>
-      <c r="P166" s="9" t="s">
+      <c r="P169" s="9" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="167" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M167" t="s">
+    <row r="170" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M170" t="s">
         <v>48</v>
       </c>
-      <c r="N167" t="s">
+      <c r="N170" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="169" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A169" s="1" t="s">
+    <row r="172" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A172" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="B169" s="1"/>
-      <c r="C169" s="1"/>
-      <c r="D169" s="1"/>
-      <c r="E169" s="1"/>
-      <c r="F169" s="1"/>
-      <c r="G169" s="1"/>
-      <c r="H169" s="1"/>
-      <c r="I169" s="1"/>
-      <c r="J169" s="1"/>
-      <c r="K169" s="1"/>
-      <c r="L169" s="1"/>
-      <c r="M169" s="8"/>
-      <c r="N169" s="8"/>
-      <c r="O169" s="8"/>
-      <c r="P169" s="8"/>
-      <c r="Q169" s="8"/>
-    </row>
-    <row r="171" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M171" s="9" t="s">
+      <c r="B172" s="1"/>
+      <c r="C172" s="1"/>
+      <c r="D172" s="1"/>
+      <c r="E172" s="1"/>
+      <c r="F172" s="1"/>
+      <c r="G172" s="1"/>
+      <c r="H172" s="1"/>
+      <c r="I172" s="1"/>
+      <c r="J172" s="1"/>
+      <c r="K172" s="1"/>
+      <c r="L172" s="1"/>
+      <c r="M172" s="8"/>
+      <c r="N172" s="8"/>
+      <c r="O172" s="8"/>
+      <c r="P172" s="8"/>
+      <c r="Q172" s="8"/>
+    </row>
+    <row r="174" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M174" s="9" t="s">
         <v>332</v>
       </c>
-      <c r="N171" s="9">
+      <c r="N174" s="9">
         <v>100</v>
       </c>
-      <c r="O171" s="9" t="s">
+      <c r="O174" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="P171" s="9" t="s">
+      <c r="P174" s="9" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="172" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H172" s="6" t="s">
+    <row r="175" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H175" s="6" t="s">
         <v>326</v>
       </c>
-      <c r="M172" t="s">
+      <c r="M175" t="s">
         <v>332</v>
       </c>
-      <c r="N172">
+      <c r="N175">
         <v>88</v>
       </c>
-      <c r="O172" t="s">
+      <c r="O175" t="s">
         <v>124</v>
       </c>
-      <c r="P172" t="s">
+      <c r="P175" t="s">
         <v>333</v>
       </c>
-      <c r="Q172" t="s">
+      <c r="Q175" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="173" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H173" s="6" t="s">
+    <row r="176" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H176" s="6" t="s">
         <v>325</v>
       </c>
-      <c r="M173" t="s">
+      <c r="M176" t="s">
         <v>332</v>
       </c>
-      <c r="N173">
+      <c r="N176">
         <v>90</v>
       </c>
-      <c r="O173" t="s">
+      <c r="O176" t="s">
         <v>124</v>
       </c>
-      <c r="Q173" t="s">
+      <c r="Q176" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="174" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H174" s="6"/>
-    </row>
-    <row r="175" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H175" s="6"/>
-      <c r="M175" t="s">
+    <row r="177" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="H177" s="6"/>
+    </row>
+    <row r="178" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="H178" s="6"/>
+      <c r="M178" t="s">
         <v>343</v>
       </c>
-      <c r="N175">
+      <c r="N178">
         <v>1.6E-2</v>
       </c>
-      <c r="O175" t="s">
+      <c r="O178" t="s">
         <v>225</v>
       </c>
-      <c r="P175" t="s">
+      <c r="P178" t="s">
         <v>351</v>
       </c>
-      <c r="Q175" t="s">
+      <c r="Q178" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="176" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H176" s="6"/>
-    </row>
-    <row r="177" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M177" t="s">
+    <row r="179" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="H179" s="6"/>
+    </row>
+    <row r="180" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="M180" t="s">
         <v>353</v>
       </c>
-      <c r="N177" s="13">
+      <c r="N180" s="13">
         <f>0.16*10.36*0.9</f>
         <v>1.4918400000000001</v>
       </c>
-      <c r="O177" t="s">
+      <c r="O180" t="s">
         <v>347</v>
       </c>
-      <c r="P177" t="s">
+      <c r="P180" t="s">
         <v>348</v>
       </c>
-      <c r="Q177" t="s">
+      <c r="Q180" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="180" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M180" s="9" t="s">
+    <row r="183" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="M183" s="9" t="s">
         <v>334</v>
       </c>
-      <c r="N180" s="9">
+      <c r="N183" s="9">
         <v>-99</v>
       </c>
-      <c r="O180" s="9"/>
-      <c r="P180" s="9" t="s">
+      <c r="O183" s="9"/>
+      <c r="P183" s="9" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="181" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C181" t="s">
+    <row r="184" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="C184" t="s">
         <v>337</v>
-      </c>
-      <c r="M181" t="s">
-        <v>334</v>
-      </c>
-      <c r="N181">
-        <v>17</v>
-      </c>
-      <c r="O181" t="s">
-        <v>124</v>
-      </c>
-      <c r="Q181" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="182" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C182" t="s">
-        <v>338</v>
-      </c>
-      <c r="M182" t="s">
-        <v>334</v>
-      </c>
-      <c r="N182">
-        <v>17</v>
-      </c>
-      <c r="O182" t="s">
-        <v>124</v>
-      </c>
-      <c r="Q182" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="183" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C183" t="s">
-        <v>339</v>
-      </c>
-      <c r="M183" t="s">
-        <v>334</v>
-      </c>
-      <c r="N183">
-        <v>17</v>
-      </c>
-      <c r="O183" t="s">
-        <v>124</v>
-      </c>
-      <c r="Q183" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="184" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C184" t="s">
-        <v>340</v>
       </c>
       <c r="M184" t="s">
         <v>334</v>
       </c>
       <c r="N184">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="O184" t="s">
         <v>124</v>
@@ -5743,29 +5783,46 @@
         <v>354</v>
       </c>
     </row>
-    <row r="186" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="185" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="C185" t="s">
+        <v>338</v>
+      </c>
+      <c r="M185" t="s">
+        <v>334</v>
+      </c>
+      <c r="N185">
+        <v>17</v>
+      </c>
+      <c r="O185" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q185" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="186" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C186" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="M186" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="N186">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="O186" t="s">
         <v>124</v>
       </c>
       <c r="Q186" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="187" spans="1:17" x14ac:dyDescent="0.25">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="187" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C187" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="M187" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="N187">
         <v>14</v>
@@ -5774,35 +5831,18 @@
         <v>124</v>
       </c>
       <c r="Q187" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="188" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C188" t="s">
-        <v>339</v>
-      </c>
-      <c r="M188" t="s">
-        <v>335</v>
-      </c>
-      <c r="N188">
-        <v>14</v>
-      </c>
-      <c r="O188" t="s">
-        <v>124</v>
-      </c>
-      <c r="Q188" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="189" spans="1:17" x14ac:dyDescent="0.25">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="189" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C189" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="M189" t="s">
         <v>335</v>
       </c>
       <c r="N189">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="O189" t="s">
         <v>124</v>
@@ -5811,144 +5851,135 @@
         <v>342</v>
       </c>
     </row>
-    <row r="191" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A191" s="1" t="s">
+    <row r="190" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="C190" t="s">
+        <v>338</v>
+      </c>
+      <c r="M190" t="s">
+        <v>335</v>
+      </c>
+      <c r="N190">
+        <v>14</v>
+      </c>
+      <c r="O190" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q190" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="191" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="C191" t="s">
+        <v>339</v>
+      </c>
+      <c r="M191" t="s">
+        <v>335</v>
+      </c>
+      <c r="N191">
+        <v>14</v>
+      </c>
+      <c r="O191" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q191" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="192" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="C192" t="s">
+        <v>340</v>
+      </c>
+      <c r="M192" t="s">
+        <v>335</v>
+      </c>
+      <c r="N192">
+        <v>9</v>
+      </c>
+      <c r="O192" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q192" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="194" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A194" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="B191" s="1"/>
-      <c r="C191" s="1"/>
-      <c r="D191" s="1"/>
-      <c r="E191" s="1"/>
-      <c r="F191" s="1"/>
-      <c r="G191" s="1"/>
-      <c r="H191" s="1"/>
-      <c r="I191" s="1"/>
-      <c r="J191" s="1"/>
-      <c r="K191" s="1"/>
-      <c r="L191" s="1"/>
-      <c r="M191" s="8"/>
-      <c r="N191" s="8"/>
-      <c r="O191" s="8"/>
-      <c r="P191" s="8"/>
-      <c r="Q191" s="8"/>
-    </row>
-    <row r="195" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M195" s="9" t="s">
+      <c r="B194" s="1"/>
+      <c r="C194" s="1"/>
+      <c r="D194" s="1"/>
+      <c r="E194" s="1"/>
+      <c r="F194" s="1"/>
+      <c r="G194" s="1"/>
+      <c r="H194" s="1"/>
+      <c r="I194" s="1"/>
+      <c r="J194" s="1"/>
+      <c r="K194" s="1"/>
+      <c r="L194" s="1"/>
+      <c r="M194" s="8"/>
+      <c r="N194" s="8"/>
+      <c r="O194" s="8"/>
+      <c r="P194" s="8"/>
+      <c r="Q194" s="8"/>
+    </row>
+    <row r="198" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M198" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="N195" s="9">
+      <c r="N198" s="9">
         <v>0</v>
       </c>
-      <c r="O195" s="9" t="s">
+      <c r="O198" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="P195" s="9" t="s">
+      <c r="P198" s="9" t="s">
         <v>52</v>
-      </c>
-    </row>
-    <row r="196" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B196" t="s">
-        <v>151</v>
-      </c>
-      <c r="M196" t="s">
-        <v>158</v>
-      </c>
-      <c r="N196">
-        <v>302</v>
-      </c>
-      <c r="O196" t="s">
-        <v>159</v>
-      </c>
-      <c r="P196" t="s">
-        <v>160</v>
-      </c>
-      <c r="Q196" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="197" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B197" t="s">
-        <v>152</v>
-      </c>
-      <c r="M197" t="s">
-        <v>158</v>
-      </c>
-      <c r="N197">
-        <v>197</v>
-      </c>
-      <c r="O197" t="s">
-        <v>159</v>
-      </c>
-      <c r="P197" t="s">
-        <v>161</v>
-      </c>
-      <c r="Q197" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="198" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B198" t="s">
-        <v>153</v>
-      </c>
-      <c r="M198" t="s">
-        <v>158</v>
-      </c>
-      <c r="N198">
-        <v>216</v>
-      </c>
-      <c r="O198" t="s">
-        <v>159</v>
-      </c>
-      <c r="P198" t="s">
-        <v>162</v>
-      </c>
-      <c r="Q198" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="199" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B199" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="M199" t="s">
         <v>158</v>
       </c>
       <c r="N199">
-        <v>216</v>
+        <v>302</v>
       </c>
       <c r="O199" t="s">
         <v>159</v>
       </c>
       <c r="P199" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="Q199" t="s">
-        <v>398</v>
+        <v>163</v>
       </c>
     </row>
     <row r="200" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B200" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="M200" t="s">
         <v>158</v>
       </c>
       <c r="N200">
-        <v>216</v>
+        <v>197</v>
       </c>
       <c r="O200" t="s">
         <v>159</v>
       </c>
       <c r="P200" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="Q200" t="s">
-        <v>398</v>
+        <v>164</v>
       </c>
     </row>
     <row r="201" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B201" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="M201" t="s">
         <v>158</v>
@@ -5963,12 +5994,12 @@
         <v>162</v>
       </c>
       <c r="Q201" t="s">
-        <v>398</v>
+        <v>165</v>
       </c>
     </row>
     <row r="202" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B202" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="M202" t="s">
         <v>158</v>
@@ -5986,370 +6017,358 @@
         <v>398</v>
       </c>
     </row>
+    <row r="203" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B203" t="s">
+        <v>155</v>
+      </c>
+      <c r="M203" t="s">
+        <v>158</v>
+      </c>
+      <c r="N203">
+        <v>216</v>
+      </c>
+      <c r="O203" t="s">
+        <v>159</v>
+      </c>
+      <c r="P203" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q203" t="s">
+        <v>398</v>
+      </c>
+    </row>
     <row r="204" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A204" s="1" t="s">
+      <c r="B204" t="s">
+        <v>156</v>
+      </c>
+      <c r="M204" t="s">
+        <v>158</v>
+      </c>
+      <c r="N204">
+        <v>216</v>
+      </c>
+      <c r="O204" t="s">
+        <v>159</v>
+      </c>
+      <c r="P204" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q204" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="205" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B205" t="s">
+        <v>157</v>
+      </c>
+      <c r="M205" t="s">
+        <v>158</v>
+      </c>
+      <c r="N205">
+        <v>216</v>
+      </c>
+      <c r="O205" t="s">
+        <v>159</v>
+      </c>
+      <c r="P205" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q205" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="207" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A207" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="B204" s="1"/>
-      <c r="C204" s="1"/>
-      <c r="D204" s="1"/>
-      <c r="E204" s="1"/>
-      <c r="F204" s="1"/>
-      <c r="G204" s="1"/>
-      <c r="H204" s="1"/>
-      <c r="I204" s="1"/>
-      <c r="J204" s="1"/>
-      <c r="K204" s="1"/>
-      <c r="L204" s="1"/>
-      <c r="M204" s="8"/>
-      <c r="N204" s="8"/>
-      <c r="O204" s="8"/>
-      <c r="P204" s="8"/>
-      <c r="Q204" s="8"/>
-    </row>
-    <row r="205" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M205" s="9" t="s">
+      <c r="B207" s="1"/>
+      <c r="C207" s="1"/>
+      <c r="D207" s="1"/>
+      <c r="E207" s="1"/>
+      <c r="F207" s="1"/>
+      <c r="G207" s="1"/>
+      <c r="H207" s="1"/>
+      <c r="I207" s="1"/>
+      <c r="J207" s="1"/>
+      <c r="K207" s="1"/>
+      <c r="L207" s="1"/>
+      <c r="M207" s="8"/>
+      <c r="N207" s="8"/>
+      <c r="O207" s="8"/>
+      <c r="P207" s="8"/>
+      <c r="Q207" s="8"/>
+    </row>
+    <row r="208" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M208" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="N205" s="9">
+      <c r="N208" s="9">
         <v>0</v>
       </c>
-      <c r="O205" s="9" t="s">
+      <c r="O208" s="9" t="s">
         <v>311</v>
       </c>
-      <c r="P205" s="9" t="s">
+      <c r="P208" s="9" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="206" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M206" s="9" t="s">
+    <row r="209" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M209" s="9" t="s">
         <v>321</v>
       </c>
-      <c r="N206" s="9">
+      <c r="N209" s="9">
         <v>0</v>
       </c>
-      <c r="O206" s="9" t="s">
+      <c r="O209" s="9" t="s">
         <v>320</v>
       </c>
-      <c r="P206" s="9" t="s">
+      <c r="P209" s="9" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="207" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M207" s="9" t="s">
+    <row r="210" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M210" s="9" t="s">
         <v>224</v>
       </c>
-      <c r="N207" s="9">
+      <c r="N210" s="9">
         <v>0</v>
       </c>
-      <c r="O207" s="9" t="s">
+      <c r="O210" s="9" t="s">
         <v>225</v>
       </c>
-      <c r="P207" s="9" t="s">
+      <c r="P210" s="9" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="209" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A209" t="s">
+    <row r="212" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
         <v>193</v>
       </c>
-      <c r="D209" t="s">
+      <c r="D212" t="s">
         <v>191</v>
       </c>
-      <c r="E209" t="s">
+      <c r="E212" t="s">
         <v>200</v>
       </c>
-      <c r="F209" t="s">
+      <c r="F212" t="s">
         <v>201</v>
       </c>
-      <c r="G209" t="s">
+      <c r="G212" t="s">
         <v>226</v>
       </c>
-      <c r="M209" t="s">
+      <c r="M212" t="s">
         <v>224</v>
       </c>
-      <c r="N209" s="25">
+      <c r="N212" s="25">
         <f>'energy stables'!E24</f>
         <v>3.5302245250431775E-2</v>
       </c>
-      <c r="O209" t="s">
+      <c r="O212" t="s">
         <v>196</v>
       </c>
-      <c r="P209" t="s">
+      <c r="P212" t="s">
         <v>210</v>
       </c>
-      <c r="Q209" t="s">
+      <c r="Q212" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="210" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A210" t="s">
+    <row r="213" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
         <v>197</v>
       </c>
-      <c r="D210" t="s">
+      <c r="D213" t="s">
         <v>191</v>
       </c>
-      <c r="E210" t="s">
+      <c r="E213" t="s">
         <v>200</v>
       </c>
-      <c r="F210" t="s">
+      <c r="F213" t="s">
         <v>201</v>
       </c>
-      <c r="M210" t="s">
+      <c r="M213" t="s">
         <v>222</v>
       </c>
-      <c r="N210" s="24">
+      <c r="N213" s="24">
         <f>'energy stables'!D26</f>
         <v>308.33833333333342</v>
       </c>
-      <c r="O210" t="s">
+      <c r="O213" t="s">
         <v>311</v>
       </c>
-      <c r="P210" t="s">
+      <c r="P213" t="s">
         <v>230</v>
       </c>
-      <c r="Q210" t="s">
+      <c r="Q213" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="211" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A211" t="s">
+    <row r="214" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
         <v>195</v>
       </c>
-      <c r="D211" t="s">
+      <c r="D214" t="s">
         <v>191</v>
       </c>
-      <c r="E211" t="s">
+      <c r="E214" t="s">
         <v>200</v>
       </c>
-      <c r="F211" t="s">
+      <c r="F214" t="s">
         <v>201</v>
       </c>
-      <c r="G211" t="s">
+      <c r="G214" t="s">
         <v>226</v>
       </c>
-      <c r="M211" t="s">
+      <c r="M214" t="s">
         <v>224</v>
       </c>
-      <c r="N211" s="25">
+      <c r="N214" s="25">
         <f>'energy stables'!E27</f>
         <v>4.1036269430051814E-2</v>
       </c>
-      <c r="O211" t="s">
+      <c r="O214" t="s">
         <v>196</v>
-      </c>
-      <c r="Q211" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="213" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A213" t="s">
-        <v>193</v>
-      </c>
-      <c r="D213" t="s">
-        <v>191</v>
-      </c>
-      <c r="M213" t="s">
-        <v>222</v>
-      </c>
-      <c r="N213" s="24">
-        <f>'energy stables'!D29</f>
-        <v>170.33333333333331</v>
-      </c>
-      <c r="O213" t="s">
-        <v>311</v>
-      </c>
-      <c r="P213" t="s">
-        <v>235</v>
-      </c>
-      <c r="Q213" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="214" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A214" t="s">
-        <v>197</v>
-      </c>
-      <c r="D214" t="s">
-        <v>191</v>
-      </c>
-      <c r="M214" t="s">
-        <v>222</v>
-      </c>
-      <c r="N214" s="24">
-        <f>'energy stables'!D31</f>
-        <v>332.32333333333338</v>
-      </c>
-      <c r="O214" t="s">
-        <v>311</v>
-      </c>
-      <c r="P214" t="s">
-        <v>236</v>
       </c>
       <c r="Q214" t="s">
         <v>229</v>
       </c>
-    </row>
-    <row r="215" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N215" s="24"/>
     </row>
     <row r="216" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>193</v>
       </c>
       <c r="D216" t="s">
+        <v>191</v>
+      </c>
+      <c r="M216" t="s">
+        <v>222</v>
+      </c>
+      <c r="N216" s="24">
+        <f>'energy stables'!D29</f>
+        <v>170.33333333333331</v>
+      </c>
+      <c r="O216" t="s">
+        <v>311</v>
+      </c>
+      <c r="P216" t="s">
+        <v>235</v>
+      </c>
+      <c r="Q216" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="217" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>197</v>
+      </c>
+      <c r="D217" t="s">
+        <v>191</v>
+      </c>
+      <c r="M217" t="s">
+        <v>222</v>
+      </c>
+      <c r="N217" s="24">
+        <f>'energy stables'!D31</f>
+        <v>332.32333333333338</v>
+      </c>
+      <c r="O217" t="s">
+        <v>311</v>
+      </c>
+      <c r="P217" t="s">
+        <v>236</v>
+      </c>
+      <c r="Q217" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="218" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="N218" s="24"/>
+    </row>
+    <row r="219" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>193</v>
+      </c>
+      <c r="D219" t="s">
         <v>231</v>
       </c>
-      <c r="E216" t="s">
+      <c r="E219" t="s">
         <v>232</v>
       </c>
-      <c r="F216" t="s">
+      <c r="F219" t="s">
         <v>237</v>
       </c>
-      <c r="M216" t="s">
+      <c r="M219" t="s">
         <v>321</v>
       </c>
-      <c r="N216" s="25">
+      <c r="N219" s="25">
         <f>(290+1078)/100000</f>
         <v>1.3679999999999999E-2</v>
       </c>
-      <c r="O216" t="s">
+      <c r="O219" t="s">
         <v>320</v>
       </c>
-      <c r="P216" t="s">
+      <c r="P219" t="s">
         <v>233</v>
       </c>
-      <c r="Q216" t="s">
+      <c r="Q219" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="217" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A217" t="s">
+    <row r="220" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
         <v>194</v>
       </c>
-      <c r="D217" t="s">
+      <c r="D220" t="s">
         <v>231</v>
       </c>
-      <c r="E217" t="s">
+      <c r="E220" t="s">
         <v>232</v>
       </c>
-      <c r="F217" t="s">
+      <c r="F220" t="s">
         <v>237</v>
       </c>
-      <c r="M217" t="s">
+      <c r="M220" t="s">
         <v>321</v>
       </c>
-      <c r="N217" s="25">
+      <c r="N220" s="25">
         <f>77000/100000</f>
         <v>0.77</v>
       </c>
-      <c r="O217" t="s">
+      <c r="O220" t="s">
         <v>320</v>
       </c>
-      <c r="Q217" t="s">
+      <c r="Q220" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="218" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A218" t="s">
+    <row r="221" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
         <v>197</v>
       </c>
-      <c r="D218" t="s">
+      <c r="D221" t="s">
         <v>231</v>
       </c>
-      <c r="E218" t="s">
+      <c r="E221" t="s">
         <v>232</v>
       </c>
-      <c r="F218" t="s">
+      <c r="F221" t="s">
         <v>237</v>
       </c>
-      <c r="M218" t="s">
+      <c r="M221" t="s">
         <v>321</v>
       </c>
-      <c r="N218" s="25">
+      <c r="N221" s="25">
         <f>(3340+9790)/100000</f>
         <v>0.1313</v>
       </c>
-      <c r="O218" t="s">
-        <v>320</v>
-      </c>
-      <c r="P218" t="s">
-        <v>234</v>
-      </c>
-      <c r="Q218" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="220" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A220" t="s">
-        <v>193</v>
-      </c>
-      <c r="D220" t="s">
-        <v>238</v>
-      </c>
-      <c r="F220" t="s">
-        <v>314</v>
-      </c>
-      <c r="M220" t="s">
-        <v>321</v>
-      </c>
-      <c r="N220">
-        <f>'energy stables'!D49</f>
-        <v>3.5</v>
-      </c>
-      <c r="O220" t="s">
-        <v>320</v>
-      </c>
-      <c r="Q220" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="221" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A221" t="s">
-        <v>194</v>
-      </c>
-      <c r="D221" t="s">
-        <v>238</v>
-      </c>
-      <c r="F221" t="s">
-        <v>314</v>
-      </c>
-      <c r="M221" t="s">
-        <v>321</v>
-      </c>
-      <c r="N221">
-        <f>'energy stables'!D50</f>
-        <v>12.5</v>
-      </c>
       <c r="O221" t="s">
         <v>320</v>
       </c>
+      <c r="P221" t="s">
+        <v>234</v>
+      </c>
       <c r="Q221" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="222" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A222" t="s">
-        <v>197</v>
-      </c>
-      <c r="D222" t="s">
-        <v>238</v>
-      </c>
-      <c r="F222" t="s">
-        <v>314</v>
-      </c>
-      <c r="M222" t="s">
-        <v>321</v>
-      </c>
-      <c r="N222">
-        <f>'energy stables'!D51</f>
-        <v>34</v>
-      </c>
-      <c r="O222" t="s">
-        <v>320</v>
-      </c>
-      <c r="Q222" t="s">
-        <v>249</v>
+        <v>229</v>
       </c>
     </row>
     <row r="223" spans="1:17" x14ac:dyDescent="0.25">
@@ -6360,14 +6379,14 @@
         <v>238</v>
       </c>
       <c r="F223" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="M223" t="s">
         <v>321</v>
       </c>
       <c r="N223">
-        <f>'energy stables'!D53</f>
-        <v>0.04</v>
+        <f>'energy stables'!D49</f>
+        <v>3.5</v>
       </c>
       <c r="O223" t="s">
         <v>320</v>
@@ -6384,14 +6403,14 @@
         <v>238</v>
       </c>
       <c r="F224" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="M224" t="s">
         <v>321</v>
       </c>
-      <c r="N224" s="13">
-        <f>'energy stables'!D54</f>
-        <v>0.1</v>
+      <c r="N224">
+        <f>'energy stables'!D50</f>
+        <v>12.5</v>
       </c>
       <c r="O224" t="s">
         <v>320</v>
@@ -6408,14 +6427,14 @@
         <v>238</v>
       </c>
       <c r="F225" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="M225" t="s">
         <v>321</v>
       </c>
-      <c r="N225" s="13">
-        <f>'energy stables'!D55</f>
-        <v>0.26</v>
+      <c r="N225">
+        <f>'energy stables'!D51</f>
+        <v>34</v>
       </c>
       <c r="O225" t="s">
         <v>320</v>
@@ -6424,31 +6443,52 @@
         <v>249</v>
       </c>
     </row>
+    <row r="226" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>193</v>
+      </c>
+      <c r="D226" t="s">
+        <v>238</v>
+      </c>
+      <c r="F226" t="s">
+        <v>317</v>
+      </c>
+      <c r="M226" t="s">
+        <v>321</v>
+      </c>
+      <c r="N226">
+        <f>'energy stables'!D53</f>
+        <v>0.04</v>
+      </c>
+      <c r="O226" t="s">
+        <v>320</v>
+      </c>
+      <c r="Q226" t="s">
+        <v>249</v>
+      </c>
+    </row>
     <row r="227" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D227" t="s">
-        <v>231</v>
-      </c>
-      <c r="E227" t="s">
-        <v>357</v>
+        <v>238</v>
+      </c>
+      <c r="F227" t="s">
+        <v>317</v>
       </c>
       <c r="M227" t="s">
-        <v>222</v>
+        <v>321</v>
       </c>
       <c r="N227" s="13">
-        <f>'energy stables'!D65</f>
-        <v>0.14449999999999999</v>
+        <f>'energy stables'!D54</f>
+        <v>0.1</v>
       </c>
       <c r="O227" t="s">
-        <v>311</v>
-      </c>
-      <c r="P227" t="s">
-        <v>388</v>
+        <v>320</v>
       </c>
       <c r="Q227" t="s">
-        <v>229</v>
+        <v>249</v>
       </c>
     </row>
     <row r="228" spans="1:17" x14ac:dyDescent="0.25">
@@ -6456,190 +6496,287 @@
         <v>197</v>
       </c>
       <c r="D228" t="s">
+        <v>238</v>
+      </c>
+      <c r="F228" t="s">
+        <v>317</v>
+      </c>
+      <c r="M228" t="s">
+        <v>321</v>
+      </c>
+      <c r="N228" s="13">
+        <f>'energy stables'!D55</f>
+        <v>0.26</v>
+      </c>
+      <c r="O228" t="s">
+        <v>320</v>
+      </c>
+      <c r="Q228" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="230" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>193</v>
+      </c>
+      <c r="D230" t="s">
         <v>231</v>
       </c>
-      <c r="E228" t="s">
+      <c r="E230" t="s">
         <v>357</v>
       </c>
-      <c r="M228" t="s">
+      <c r="M230" t="s">
         <v>222</v>
       </c>
-      <c r="N228" s="13">
+      <c r="N230" s="13">
+        <f>'energy stables'!D65</f>
+        <v>0.14449999999999999</v>
+      </c>
+      <c r="O230" t="s">
+        <v>311</v>
+      </c>
+      <c r="P230" t="s">
+        <v>388</v>
+      </c>
+      <c r="Q230" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="231" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>197</v>
+      </c>
+      <c r="D231" t="s">
+        <v>231</v>
+      </c>
+      <c r="E231" t="s">
+        <v>357</v>
+      </c>
+      <c r="M231" t="s">
+        <v>222</v>
+      </c>
+      <c r="N231" s="13">
         <f>'energy stables'!D67</f>
         <v>3.9295</v>
       </c>
-      <c r="O228" t="s">
+      <c r="O231" t="s">
         <v>311</v>
       </c>
-      <c r="P228" t="s">
+      <c r="P231" t="s">
         <v>389</v>
       </c>
-      <c r="Q228" t="s">
+      <c r="Q231" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="229" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A229" t="s">
+    <row r="232" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
         <v>193</v>
       </c>
-      <c r="D229" t="s">
+      <c r="D232" t="s">
         <v>231</v>
       </c>
-      <c r="E229" t="s">
+      <c r="E232" t="s">
         <v>357</v>
       </c>
-      <c r="F229" t="s">
+      <c r="F232" t="s">
         <v>358</v>
       </c>
-      <c r="M229" t="s">
+      <c r="M232" t="s">
         <v>222</v>
       </c>
-      <c r="N229">
+      <c r="N232">
         <v>0</v>
       </c>
-      <c r="O229" t="s">
+      <c r="O232" t="s">
         <v>311</v>
       </c>
-      <c r="P229" t="s">
+      <c r="P232" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="230" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A230" t="s">
+    <row r="233" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
         <v>197</v>
       </c>
-      <c r="D230" t="s">
+      <c r="D233" t="s">
         <v>231</v>
       </c>
-      <c r="E230" t="s">
+      <c r="E233" t="s">
         <v>357</v>
       </c>
-      <c r="F230" t="s">
+      <c r="F233" t="s">
         <v>358</v>
       </c>
-      <c r="M230" t="s">
+      <c r="M233" t="s">
         <v>222</v>
       </c>
-      <c r="N230">
+      <c r="N233">
         <v>0</v>
       </c>
-      <c r="O230">
+      <c r="O233">
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A231" t="s">
+    <row r="234" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
         <v>194</v>
       </c>
-      <c r="D231" t="s">
+      <c r="D234" t="s">
         <v>231</v>
       </c>
-      <c r="E231" t="s">
+      <c r="E234" t="s">
         <v>357</v>
       </c>
-      <c r="F231" t="s">
+      <c r="F234" t="s">
         <v>358</v>
       </c>
-      <c r="M231" t="s">
+      <c r="M234" t="s">
         <v>321</v>
       </c>
-      <c r="N231" s="13">
+      <c r="N234" s="13">
         <f>4.7*(1/3.6)</f>
         <v>1.3055555555555556</v>
       </c>
-      <c r="O231" t="s">
+      <c r="O234" t="s">
         <v>320</v>
       </c>
-      <c r="P231" t="s">
+      <c r="P234" t="s">
         <v>360</v>
       </c>
-      <c r="Q231" t="s">
+      <c r="Q234" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="233" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A233" t="s">
+    <row r="236" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
         <v>193</v>
       </c>
-      <c r="D233" t="s">
+      <c r="D236" t="s">
         <v>390</v>
       </c>
-      <c r="M233" t="s">
+      <c r="M236" t="s">
         <v>222</v>
       </c>
-      <c r="N233" s="24">
+      <c r="N236" s="24">
         <f>0.05*1000*(1/3.6)</f>
         <v>13.888888888888889</v>
       </c>
-      <c r="O233" t="s">
+      <c r="O236" t="s">
         <v>311</v>
       </c>
-      <c r="P233" t="s">
+      <c r="P236" t="s">
         <v>393</v>
       </c>
-      <c r="Q233" t="s">
+      <c r="Q236" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="234" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A234" t="s">
+    <row r="237" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
         <v>197</v>
       </c>
-      <c r="D234" t="s">
+      <c r="D237" t="s">
         <v>390</v>
       </c>
-      <c r="M234" t="s">
+      <c r="M237" t="s">
         <v>222</v>
       </c>
-      <c r="N234" s="24">
+      <c r="N237" s="24">
         <f>0.05*1000*(1/3.6)</f>
         <v>13.888888888888889</v>
       </c>
-      <c r="O234" t="s">
+      <c r="O237" t="s">
         <v>311</v>
       </c>
-      <c r="P234" t="s">
+      <c r="P237" t="s">
         <v>395</v>
       </c>
-      <c r="Q234" t="s">
+      <c r="Q237" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="235" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A235" t="s">
+    <row r="238" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
         <v>193</v>
       </c>
-      <c r="D235" t="s">
+      <c r="D238" t="s">
         <v>390</v>
       </c>
-      <c r="F235" t="s">
+      <c r="F238" t="s">
         <v>391</v>
       </c>
-      <c r="M235" t="s">
+      <c r="M238" t="s">
         <v>222</v>
       </c>
-      <c r="N235">
+      <c r="N238">
         <v>0</v>
       </c>
-      <c r="P235" t="s">
+      <c r="P238" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="236" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A236" t="s">
+    <row r="239" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
         <v>197</v>
       </c>
-      <c r="D236" t="s">
+      <c r="D239" t="s">
         <v>390</v>
       </c>
-      <c r="F236" t="s">
+      <c r="F239" t="s">
         <v>391</v>
       </c>
-      <c r="M236" t="s">
+      <c r="M239" t="s">
         <v>222</v>
       </c>
-      <c r="N236">
+      <c r="N239">
         <v>0</v>
+      </c>
+    </row>
+    <row r="241" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>193</v>
+      </c>
+      <c r="D241" t="s">
+        <v>414</v>
+      </c>
+      <c r="M241" t="s">
+        <v>222</v>
+      </c>
+      <c r="N241">
+        <v>840</v>
+      </c>
+      <c r="O241" t="s">
+        <v>311</v>
+      </c>
+      <c r="P241" t="s">
+        <v>416</v>
+      </c>
+      <c r="Q241" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="242" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
+        <v>197</v>
+      </c>
+      <c r="D242" t="s">
+        <v>414</v>
+      </c>
+      <c r="M242" t="s">
+        <v>222</v>
+      </c>
+      <c r="N242">
+        <v>2700</v>
+      </c>
+      <c r="O242" t="s">
+        <v>311</v>
+      </c>
+      <c r="P242" t="s">
+        <v>415</v>
+      </c>
+      <c r="Q242" t="s">
+        <v>417</v>
       </c>
     </row>
   </sheetData>
@@ -6650,7 +6787,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B3:S75"/>
+  <dimension ref="B3:S98"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="17.28515625" customWidth="1"/>
@@ -8340,6 +8477,242 @@
       </c>
       <c r="P75" s="57"/>
       <c r="Q75" s="4"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B77" s="53" t="s">
+        <v>403</v>
+      </c>
+      <c r="C77" s="52"/>
+      <c r="D77" s="52"/>
+      <c r="E77" s="52"/>
+      <c r="F77" s="52"/>
+      <c r="G77" s="52"/>
+      <c r="H77" s="52"/>
+      <c r="I77" s="52"/>
+      <c r="J77" s="52"/>
+      <c r="K77" s="52"/>
+      <c r="L77" s="52"/>
+      <c r="M77" s="52"/>
+      <c r="N77" s="52"/>
+      <c r="O77" s="52"/>
+      <c r="P77" s="52"/>
+      <c r="Q77" s="52"/>
+    </row>
+    <row r="78" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B78" s="51" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="C79" t="s">
+        <v>412</v>
+      </c>
+      <c r="D79" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="80" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B80" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="81" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B81">
+        <v>1</v>
+      </c>
+      <c r="C81" s="105">
+        <v>2670</v>
+      </c>
+      <c r="D81" s="105">
+        <f>5054*(0.1+0.08)</f>
+        <v>909.71999999999991</v>
+      </c>
+    </row>
+    <row r="82" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B82">
+        <v>2</v>
+      </c>
+      <c r="C82" s="105">
+        <v>1306</v>
+      </c>
+      <c r="D82" s="105">
+        <f>1994*0.12</f>
+        <v>239.28</v>
+      </c>
+    </row>
+    <row r="83" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B83">
+        <v>3</v>
+      </c>
+      <c r="C83" s="105">
+        <v>8928</v>
+      </c>
+      <c r="D83" s="105">
+        <f>4613*0.19</f>
+        <v>876.47</v>
+      </c>
+    </row>
+    <row r="84" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B84">
+        <v>4</v>
+      </c>
+      <c r="C84" s="105">
+        <v>2720</v>
+      </c>
+      <c r="D84" s="105">
+        <f>6113*0.13</f>
+        <v>794.69</v>
+      </c>
+    </row>
+    <row r="85" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B85">
+        <v>5</v>
+      </c>
+      <c r="C85" s="105">
+        <v>2421</v>
+      </c>
+      <c r="D85" s="105">
+        <f>1891*0.2</f>
+        <v>378.20000000000005</v>
+      </c>
+    </row>
+    <row r="86" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B86" t="s">
+        <v>406</v>
+      </c>
+      <c r="C86" s="105"/>
+      <c r="D86" s="105"/>
+    </row>
+    <row r="87" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B87">
+        <v>6</v>
+      </c>
+      <c r="C87" s="105">
+        <v>3603</v>
+      </c>
+      <c r="D87" s="105">
+        <f>4108*0.26</f>
+        <v>1068.08</v>
+      </c>
+    </row>
+    <row r="88" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B88">
+        <v>7</v>
+      </c>
+      <c r="C88" s="105">
+        <v>800</v>
+      </c>
+      <c r="D88" s="105">
+        <f>1536*1</f>
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="89" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B89" t="s">
+        <v>407</v>
+      </c>
+      <c r="C89" s="105"/>
+      <c r="D89" s="105"/>
+    </row>
+    <row r="90" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B90">
+        <v>8</v>
+      </c>
+      <c r="C90" s="105">
+        <v>8727</v>
+      </c>
+      <c r="D90" s="105">
+        <f>5917*0.9</f>
+        <v>5325.3</v>
+      </c>
+      <c r="E90" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="91" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B91">
+        <v>9</v>
+      </c>
+      <c r="C91" s="105">
+        <v>11160</v>
+      </c>
+      <c r="D91" s="105">
+        <f>10088*0.85</f>
+        <v>8574.7999999999993</v>
+      </c>
+      <c r="E91" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="92" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B92" t="s">
+        <v>410</v>
+      </c>
+      <c r="C92" s="105"/>
+      <c r="D92" s="105"/>
+    </row>
+    <row r="93" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B93">
+        <v>10</v>
+      </c>
+      <c r="C93" s="105">
+        <v>1600</v>
+      </c>
+      <c r="D93" s="105">
+        <f>2536*0.28</f>
+        <v>710.08</v>
+      </c>
+    </row>
+    <row r="94" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B94">
+        <v>11</v>
+      </c>
+      <c r="C94" s="105">
+        <v>442</v>
+      </c>
+      <c r="D94" s="105">
+        <f>5270*0.02</f>
+        <v>105.4</v>
+      </c>
+    </row>
+    <row r="95" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B95">
+        <v>12</v>
+      </c>
+      <c r="C95" s="105">
+        <v>3844</v>
+      </c>
+      <c r="D95" s="105">
+        <f>5111*0.08</f>
+        <v>408.88</v>
+      </c>
+    </row>
+    <row r="96" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C96" s="105"/>
+      <c r="D96" s="105"/>
+    </row>
+    <row r="97" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B97" t="s">
+        <v>411</v>
+      </c>
+      <c r="C97" s="105">
+        <f>AVERAGE(C81:C95)</f>
+        <v>4018.4166666666665</v>
+      </c>
+      <c r="D97" s="105">
+        <f>AVERAGE(D81:D95)</f>
+        <v>1743.9083333333338</v>
+      </c>
+    </row>
+    <row r="98" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C98" s="105">
+        <f>MEDIAN(C81:C95)</f>
+        <v>2695</v>
+      </c>
+      <c r="D98" s="105">
+        <f>MEDIAN(D81:D95)</f>
+        <v>835.58</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/data/default/MachineryAndEnergyMgmt.xlsx
+++ b/data/default/MachineryAndEnergyMgmt.xlsx
@@ -477,7 +477,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1166" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="403">
   <si>
     <t>f_crop</t>
   </si>
@@ -814,9 +814,6 @@
     <t>Moldboard plough</t>
   </si>
   <si>
-    <t>Field cultivator</t>
-  </si>
-  <si>
     <t>Disc harrow</t>
   </si>
   <si>
@@ -995,9 +992,6 @@
   </si>
   <si>
     <t xml:space="preserve">Reif, K., &amp; Dietsche, K.-H. (2014). Bosch Automotive Handbook (K. Reif Ed. 9th ed.). Robert Bosch GmbH, Germany: John Wiley &amp; Sons Ltd. </t>
-  </si>
-  <si>
-    <t>SAE. (2000). Agricultural Machinery Management Data. In. ASABE, St. Joseph, MI, USA: American Society of Agricultural Engineers</t>
   </si>
   <si>
     <t>f_energy_source</t>
@@ -1864,6 +1858,12 @@
   </si>
   <si>
     <t>E_per_area_manure</t>
+  </si>
+  <si>
+    <t>Field cultivator, 10 tools per meter</t>
+  </si>
+  <si>
+    <t>ASAE. (2000). Agricultural Machinery Management Data. In. ASABE, St. Joseph, MI, USA: American Society of Agricultural Engineers</t>
   </si>
 </sst>
 </file>
@@ -2694,28 +2694,28 @@
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="49" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B1" s="93" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="93" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D1" s="93" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E1" s="93" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F1" s="93" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="G1" s="93" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="H1" s="93" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="I1" s="93" t="s">
         <v>51</v>
@@ -2724,10 +2724,10 @@
         <v>44</v>
       </c>
       <c r="K1" s="93" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="L1" s="93" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="M1" s="93" t="s">
         <v>1</v>
@@ -2747,13 +2747,13 @@
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="M2" s="20" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="N2" s="9">
         <v>0</v>
       </c>
       <c r="O2" s="9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="P2" s="9" t="s">
         <v>52</v>
@@ -2761,78 +2761,78 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="M4" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="N4" s="18">
         <f>(241822577+237201100)/(241822577+237201100+5856000+8368914)*100</f>
         <v>97.116076100458642</v>
       </c>
       <c r="O4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Q4" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="M5" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="N5" s="18">
         <f>100-N4</f>
         <v>2.8839238995413581</v>
       </c>
       <c r="O5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Q5" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="M6" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="N6" s="10">
         <v>0</v>
       </c>
       <c r="O6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="M7" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="N7" s="10">
         <v>0</v>
       </c>
       <c r="O7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
@@ -2842,30 +2842,30 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D9" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="N9" s="10">
         <v>100</v>
       </c>
       <c r="O9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D10" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="H10" s="4"/>
       <c r="M10" s="6"/>
@@ -2873,42 +2873,42 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D11" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="M11" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="N11" s="10">
         <v>100</v>
       </c>
       <c r="O11" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D12" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="M12" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="N12" s="10">
         <v>100</v>
       </c>
       <c r="O12" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
@@ -2918,71 +2918,71 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D14" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E14" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="M14" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="N14" s="10">
         <v>100</v>
       </c>
       <c r="O14" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D15" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E15" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="N15" s="10">
         <v>100</v>
       </c>
       <c r="O15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D16" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E16" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="N16" s="10">
         <v>100</v>
       </c>
       <c r="O16" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
@@ -2992,262 +2992,262 @@
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D18" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F18" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="M18" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="N18" s="10">
         <v>100</v>
       </c>
       <c r="O18" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Q18" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D19" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F19" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="M19" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="N19">
         <v>4</v>
       </c>
       <c r="O19" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Q19" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D20" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F20" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="M20" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="N20">
         <v>76</v>
       </c>
       <c r="O20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Q20" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D21" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F21" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="M21" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="N21">
         <v>20</v>
       </c>
       <c r="O21" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Q21" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D22" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F22" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="N22" s="10">
         <v>100</v>
       </c>
       <c r="O22" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Q22" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D23" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F23" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="M23" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="N23" s="10">
         <v>100</v>
       </c>
       <c r="O23" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Q23" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D24" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F24" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="M24" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="N24">
         <v>20</v>
       </c>
       <c r="O24" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Q24" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D25" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F25" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="M25" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="N25">
         <v>60</v>
       </c>
       <c r="O25" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Q25" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D26" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F26" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="M26" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="N26">
         <v>20.000000000000018</v>
       </c>
       <c r="O26" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Q26" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D27" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F27" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="M27" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="N27" s="10">
         <v>100</v>
       </c>
       <c r="O27" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Q27" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
@@ -3257,123 +3257,123 @@
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D29" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E29" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="M29" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="N29" s="10">
         <v>90</v>
       </c>
       <c r="O29" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D30" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E30" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="M30" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="N30" s="10">
         <v>10</v>
       </c>
       <c r="O30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D31" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E31" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="M31" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="N31" s="10">
         <v>100</v>
       </c>
       <c r="O31" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D32" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E32" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="M32" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="N32" s="10">
         <v>90</v>
       </c>
       <c r="O32" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Q32" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D33" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E33" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="M33" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="N33" s="10">
         <v>10</v>
       </c>
       <c r="O33" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Q33" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
@@ -3383,48 +3383,48 @@
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D35" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="M35" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="N35" s="10">
         <v>100</v>
       </c>
       <c r="O35" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Q35" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D36" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="M36" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="N36" s="10">
         <v>100</v>
       </c>
       <c r="O36" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Q36" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
@@ -3434,119 +3434,119 @@
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="M38" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="N38" s="11">
         <v>6.4777062142923141</v>
       </c>
       <c r="O38" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Q38" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="M39" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="N39" s="11">
         <v>8.7567853491111922</v>
       </c>
       <c r="O39" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="P39" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="Q39" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="M40" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="N40" s="18">
         <v>59.671114354829328</v>
       </c>
       <c r="O40" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="P40" s="19" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="Q40" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="M41" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="N41" s="18">
         <v>16.802918820320372</v>
       </c>
       <c r="O41" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="M42" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="N42" s="11">
         <v>7.4851294970113242</v>
       </c>
       <c r="O42" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="M43" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="N43" s="11">
         <v>0.80634576443547301</v>
       </c>
       <c r="O43" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
@@ -3556,62 +3556,62 @@
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="M45" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="N45" s="18">
         <v>70</v>
       </c>
       <c r="O45" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="P45" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="Q45" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="M46" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="N46" s="18">
         <v>30</v>
       </c>
       <c r="O46" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Q46" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="M47" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="N47" s="18">
         <v>100</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
@@ -3619,49 +3619,49 @@
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="K49" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="M49" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N49" s="15">
         <v>80</v>
       </c>
       <c r="O49" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="K50" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M50" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N50" s="15">
         <v>10</v>
       </c>
       <c r="O50" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="K51" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M51" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N51" s="15">
         <v>10</v>
       </c>
       <c r="O51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -3683,14 +3683,14 @@
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H53" s="4"/>
       <c r="M53" s="9" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="N53" s="23">
         <v>0</v>
       </c>
       <c r="O53" s="9"/>
       <c r="P53" s="9" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
@@ -3699,377 +3699,377 @@
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H55" s="4" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="L55" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="M55" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="N55" s="18">
         <f>74100</f>
         <v>74100</v>
       </c>
       <c r="O55" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="P55" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="Q55" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H56" s="4" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="L56" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="M56" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="N56" s="11">
         <f>3.9</f>
         <v>3.9</v>
       </c>
       <c r="O56" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="Q56" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H57" s="4" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="L57" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="M57" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="N57" s="11">
         <f>3.9</f>
         <v>3.9</v>
       </c>
       <c r="O57" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="Q57" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H58" s="4" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="L58" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="M58" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="N58" s="18">
         <v>0</v>
       </c>
       <c r="O58" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H59" s="4" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="L59" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="M59" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="N59" s="22">
         <f t="shared" ref="N59:N60" si="0">N56</f>
         <v>3.9</v>
       </c>
       <c r="O59" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="P59" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H60" s="4" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="L60" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="M60" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="N60" s="22">
         <f t="shared" si="0"/>
         <v>3.9</v>
       </c>
       <c r="O60" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="P60" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H61" s="6" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="L61" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="M61" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="N61" s="18">
         <v>73300</v>
       </c>
       <c r="O61" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="P61" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="Q61" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H62" s="6" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="L62" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="M62" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="N62">
         <v>10</v>
       </c>
       <c r="O62" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="Q62" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H63" s="6" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="L63" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="M63" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="N63">
         <v>0.6</v>
       </c>
       <c r="O63" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="Q63" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H64" s="6" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="L64" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="M64" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="N64" s="18">
         <v>56100</v>
       </c>
       <c r="O64" t="s">
+        <v>180</v>
+      </c>
+      <c r="P64" t="s">
         <v>182</v>
       </c>
-      <c r="P64" t="s">
+      <c r="Q64" t="s">
         <v>184</v>
-      </c>
-      <c r="Q64" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H65" s="6" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="L65" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="M65" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="N65">
         <v>5</v>
       </c>
       <c r="O65" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="Q65" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H66" s="6" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="L66" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="M66" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="N66">
         <v>0.1</v>
       </c>
       <c r="O66" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="Q66" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H67" s="6" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="L67" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="M67" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="N67" s="18">
         <v>0</v>
       </c>
       <c r="O67" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="P67" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="Q67" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H68" s="6" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="L68" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="M68" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="N68" s="18">
         <v>300</v>
       </c>
       <c r="O68" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="Q68" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H69" s="6" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="L69" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="M69" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="N69" s="18">
         <v>4</v>
       </c>
       <c r="O69" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="Q69" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H70" s="6" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="M70" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="N70" s="18">
         <v>0</v>
       </c>
       <c r="O70" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="P70" s="15"/>
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H71" s="6" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="M71" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="N71" s="18">
         <v>0</v>
       </c>
       <c r="O71" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="P71" s="15"/>
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H72" s="4" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="M72" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="N72" s="18">
         <v>0</v>
       </c>
       <c r="O72" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="P72" s="15" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H73" s="6" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="M73" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="N73" s="18">
         <v>0</v>
       </c>
       <c r="O73" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="P73" s="15"/>
     </row>
@@ -4183,13 +4183,13 @@
       <c r="K79" s="4"/>
       <c r="L79" s="4"/>
       <c r="M79" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="N79">
         <v>2</v>
       </c>
       <c r="O79" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="P79" s="7"/>
     </row>
@@ -4299,7 +4299,7 @@
       <c r="F84" s="4"/>
       <c r="G84" s="4"/>
       <c r="H84" s="4" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="I84" s="4"/>
       <c r="J84" s="4"/>
@@ -4323,7 +4323,7 @@
       <c r="F85" s="4"/>
       <c r="G85" s="4"/>
       <c r="H85" s="4" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="I85" s="4"/>
       <c r="J85" s="4"/>
@@ -4347,7 +4347,7 @@
       <c r="F86" s="4"/>
       <c r="G86" s="4"/>
       <c r="H86" s="4" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="I86" s="4"/>
       <c r="J86" s="4"/>
@@ -4371,7 +4371,7 @@
       <c r="F87" s="4"/>
       <c r="G87" s="4"/>
       <c r="H87" s="6" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I87" s="6"/>
       <c r="J87" s="6"/>
@@ -4435,7 +4435,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="M91" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="N91">
         <v>4</v>
@@ -4561,7 +4561,7 @@
         <v>0</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="P101" s="9"/>
     </row>
@@ -4573,7 +4573,7 @@
         <v>0</v>
       </c>
       <c r="O102" s="9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="P102" s="9"/>
     </row>
@@ -4585,7 +4585,7 @@
         <v>0</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="P103" s="9"/>
     </row>
@@ -4597,19 +4597,19 @@
         <v>0</v>
       </c>
       <c r="O104" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P104" s="9"/>
     </row>
     <row r="105" spans="1:20" x14ac:dyDescent="0.25">
       <c r="M105" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N105" s="9">
         <v>0</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="P105" s="9"/>
     </row>
@@ -4621,7 +4621,7 @@
         <v>1</v>
       </c>
       <c r="O106" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P106" s="9" t="s">
         <v>78</v>
@@ -4641,7 +4641,7 @@
     </row>
     <row r="108" spans="1:20" x14ac:dyDescent="0.25">
       <c r="M108" s="9" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="N108" s="9">
         <v>0</v>
@@ -4650,7 +4650,7 @@
         <v>55</v>
       </c>
       <c r="P108" s="9" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="109" spans="1:20" x14ac:dyDescent="0.25">
@@ -4667,13 +4667,13 @@
     </row>
     <row r="110" spans="1:20" x14ac:dyDescent="0.25">
       <c r="M110" s="9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="N110" s="9">
         <v>0</v>
       </c>
       <c r="O110" s="9" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="P110" s="9"/>
     </row>
@@ -4707,9 +4707,11 @@
       </c>
       <c r="O113" s="10"/>
       <c r="P113" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q113" s="10"/>
+        <v>81</v>
+      </c>
+      <c r="Q113" s="4" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="114" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I114" t="s">
@@ -4723,7 +4725,9 @@
       </c>
       <c r="O114" s="10"/>
       <c r="P114" s="10"/>
-      <c r="Q114" s="10"/>
+      <c r="Q114" s="4" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="115" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I115" t="s">
@@ -4737,7 +4741,9 @@
       </c>
       <c r="O115" s="10"/>
       <c r="P115" s="10"/>
-      <c r="Q115" s="10"/>
+      <c r="Q115" s="4" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="116" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I116" t="s">
@@ -4768,7 +4774,9 @@
       </c>
       <c r="O117" s="10"/>
       <c r="P117" s="10"/>
-      <c r="Q117" s="10"/>
+      <c r="Q117" s="4" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="118" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I118" t="s">
@@ -4785,7 +4793,9 @@
       </c>
       <c r="O118" s="10"/>
       <c r="P118" s="10"/>
-      <c r="Q118" s="10"/>
+      <c r="Q118" s="4" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="119" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I119" t="s">
@@ -4802,7 +4812,9 @@
       </c>
       <c r="O119" s="10"/>
       <c r="P119" s="10"/>
-      <c r="Q119" s="10"/>
+      <c r="Q119" s="4" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="120" spans="9:17" x14ac:dyDescent="0.25">
       <c r="M120" s="10"/>
@@ -4825,7 +4837,9 @@
       <c r="P121" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="Q121" s="10"/>
+      <c r="Q121" s="4" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="122" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I122" t="s">
@@ -4839,7 +4853,9 @@
       </c>
       <c r="O122" s="10"/>
       <c r="P122" s="10"/>
-      <c r="Q122" s="10"/>
+      <c r="Q122" s="4" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="123" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I123" t="s">
@@ -4853,7 +4869,9 @@
       </c>
       <c r="O123" s="10"/>
       <c r="P123" s="10"/>
-      <c r="Q123" s="10"/>
+      <c r="Q123" s="4" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="124" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I124" t="s">
@@ -4884,7 +4902,9 @@
       </c>
       <c r="O125" s="10"/>
       <c r="P125" s="10"/>
-      <c r="Q125" s="10"/>
+      <c r="Q125" s="4" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="126" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I126" t="s">
@@ -4901,7 +4921,9 @@
       </c>
       <c r="O126" s="10"/>
       <c r="P126" s="10"/>
-      <c r="Q126" s="10"/>
+      <c r="Q126" s="4" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="127" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I127" t="s">
@@ -4918,7 +4940,9 @@
       </c>
       <c r="O127" s="10"/>
       <c r="P127" s="10"/>
-      <c r="Q127" s="10"/>
+      <c r="Q127" s="4" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="128" spans="9:17" x14ac:dyDescent="0.25">
       <c r="M128" s="10"/>
@@ -4935,13 +4959,16 @@
         <v>74</v>
       </c>
       <c r="N129" s="10">
-        <v>46</v>
+        <f>46*10</f>
+        <v>460</v>
       </c>
       <c r="O129" s="10"/>
       <c r="P129" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q129" s="10"/>
+        <v>401</v>
+      </c>
+      <c r="Q129" s="4" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="130" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I130" t="s">
@@ -4951,11 +4978,14 @@
         <v>75</v>
       </c>
       <c r="N130" s="10">
-        <v>2.8</v>
+        <f>2.8*10</f>
+        <v>28</v>
       </c>
       <c r="O130" s="10"/>
       <c r="P130" s="10"/>
-      <c r="Q130" s="10"/>
+      <c r="Q130" s="4" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="131" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I131" t="s">
@@ -4969,7 +4999,9 @@
       </c>
       <c r="O131" s="10"/>
       <c r="P131" s="10"/>
-      <c r="Q131" s="10"/>
+      <c r="Q131" s="4" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="132" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I132" t="s">
@@ -4979,7 +5011,7 @@
         <v>73</v>
       </c>
       <c r="N132" s="10">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O132" s="10"/>
       <c r="P132" s="10"/>
@@ -5000,7 +5032,9 @@
       </c>
       <c r="O133" s="10"/>
       <c r="P133" s="10"/>
-      <c r="Q133" s="10"/>
+      <c r="Q133" s="4" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="134" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I134" t="s">
@@ -5017,7 +5051,9 @@
       </c>
       <c r="O134" s="10"/>
       <c r="P134" s="10"/>
-      <c r="Q134" s="10"/>
+      <c r="Q134" s="4" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="135" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I135" t="s">
@@ -5034,7 +5070,9 @@
       </c>
       <c r="O135" s="10"/>
       <c r="P135" s="10"/>
-      <c r="Q135" s="10"/>
+      <c r="Q135" s="4" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="136" spans="9:17" x14ac:dyDescent="0.25">
       <c r="M136" s="10"/>
@@ -5048,17 +5086,17 @@
         <v>64</v>
       </c>
       <c r="M137" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N137" s="12">
         <v>5.0999999999999996</v>
       </c>
       <c r="O137" s="10"/>
       <c r="P137" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q137" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="138" spans="9:17" x14ac:dyDescent="0.25">
@@ -5066,17 +5104,17 @@
         <v>65</v>
       </c>
       <c r="M138" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N138" s="12">
         <v>7.1</v>
       </c>
       <c r="O138" s="10"/>
       <c r="P138" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q138" s="4" t="s">
         <v>93</v>
-      </c>
-      <c r="Q138" s="4" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="139" spans="9:17" x14ac:dyDescent="0.25">
@@ -5098,10 +5136,10 @@
       </c>
       <c r="O140" s="10"/>
       <c r="P140" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q140" s="6" t="s">
         <v>86</v>
-      </c>
-      <c r="Q140" s="6" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="141" spans="9:17" x14ac:dyDescent="0.25">
@@ -5116,10 +5154,10 @@
       </c>
       <c r="O141" s="10"/>
       <c r="P141" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q141" s="4" t="s">
         <v>88</v>
-      </c>
-      <c r="Q141" s="4" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="142" spans="9:17" x14ac:dyDescent="0.25">
@@ -5137,15 +5175,15 @@
         <v>47</v>
       </c>
       <c r="Q142" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="143" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I143" t="s">
+        <v>398</v>
+      </c>
+      <c r="M143" s="10" t="s">
         <v>400</v>
-      </c>
-      <c r="M143" s="10" t="s">
-        <v>402</v>
       </c>
       <c r="N143" s="12">
         <f>(3.11+4.67)/2</f>
@@ -5153,10 +5191,10 @@
       </c>
       <c r="O143" s="10"/>
       <c r="P143" s="6" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="Q143" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="144" spans="9:17" x14ac:dyDescent="0.25">
@@ -5171,10 +5209,10 @@
       </c>
       <c r="O144" s="10"/>
       <c r="P144" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="Q144" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="145" spans="2:17" x14ac:dyDescent="0.25">
@@ -5189,15 +5227,15 @@
       </c>
       <c r="O145" s="10"/>
       <c r="P145" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q145" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="146" spans="2:17" x14ac:dyDescent="0.25">
       <c r="I146" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M146" s="10" t="s">
         <v>53</v>
@@ -5207,15 +5245,15 @@
       </c>
       <c r="O146" s="10"/>
       <c r="P146" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Q146" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="147" spans="2:17" x14ac:dyDescent="0.25">
       <c r="I147" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="M147" s="10" t="s">
         <v>53</v>
@@ -5225,15 +5263,15 @@
       </c>
       <c r="O147" s="10"/>
       <c r="P147" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q147" s="10" t="s">
         <v>102</v>
-      </c>
-      <c r="Q147" s="10" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="148" spans="2:17" x14ac:dyDescent="0.25">
       <c r="I148" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="M148" s="10" t="s">
         <v>53</v>
@@ -5243,10 +5281,10 @@
       </c>
       <c r="O148" s="10"/>
       <c r="P148" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="Q148" s="10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="149" spans="2:17" x14ac:dyDescent="0.25">
@@ -5261,10 +5299,10 @@
       </c>
       <c r="O149" s="10"/>
       <c r="P149" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Q149" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="150" spans="2:17" x14ac:dyDescent="0.25">
@@ -5279,15 +5317,15 @@
       </c>
       <c r="O150" s="10"/>
       <c r="P150" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Q150" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="151" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B151" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I151" t="s">
         <v>69</v>
@@ -5300,15 +5338,15 @@
       </c>
       <c r="O151" s="10"/>
       <c r="P151" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q151" s="4" t="s">
         <v>107</v>
-      </c>
-      <c r="Q151" s="4" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="152" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B152" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="I152" t="s">
         <v>69</v>
@@ -5321,15 +5359,15 @@
       </c>
       <c r="O152" s="10"/>
       <c r="P152" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="Q152" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="153" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B153" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I153" t="s">
         <v>69</v>
@@ -5341,15 +5379,15 @@
         <v>4.0531064740502947</v>
       </c>
       <c r="P153" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q153" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="154" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B154" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I154" t="s">
         <v>69</v>
@@ -5361,10 +5399,10 @@
         <v>4.3591310772039646</v>
       </c>
       <c r="P154" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="Q154" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="155" spans="2:17" x14ac:dyDescent="0.25">
@@ -5375,7 +5413,7 @@
     </row>
     <row r="156" spans="2:17" x14ac:dyDescent="0.25">
       <c r="I156" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M156" s="10" t="s">
         <v>53</v>
@@ -5385,15 +5423,15 @@
       </c>
       <c r="P156" s="6"/>
       <c r="Q156" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="157" spans="2:17" x14ac:dyDescent="0.25">
       <c r="I157" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="K157" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="M157" s="10" t="s">
         <v>53</v>
@@ -5403,15 +5441,15 @@
       </c>
       <c r="P157" s="6"/>
       <c r="Q157" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="158" spans="2:17" x14ac:dyDescent="0.25">
       <c r="I158" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="K158" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M158" s="10" t="s">
         <v>53</v>
@@ -5421,15 +5459,15 @@
       </c>
       <c r="P158" s="6"/>
       <c r="Q158" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="159" spans="2:17" x14ac:dyDescent="0.25">
       <c r="I159" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="K159" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M159" s="10" t="s">
         <v>53</v>
@@ -5439,7 +5477,7 @@
       </c>
       <c r="P159" s="6"/>
       <c r="Q159" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="160" spans="2:17" x14ac:dyDescent="0.25">
@@ -5450,7 +5488,7 @@
     </row>
     <row r="161" spans="1:17" x14ac:dyDescent="0.25">
       <c r="I161" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="M161" s="10" t="s">
         <v>54</v>
@@ -5462,36 +5500,36 @@
         <v>56</v>
       </c>
       <c r="P161" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Q161" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="162" spans="1:17" x14ac:dyDescent="0.25">
       <c r="I162" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="M162" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="N162" s="13">
         <f>3.07744775/0.85</f>
         <v>3.6205267647058825</v>
       </c>
       <c r="O162" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="P162" s="6" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="Q162" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="163" spans="1:17" x14ac:dyDescent="0.25">
       <c r="I163" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="M163" s="10" t="s">
         <v>57</v>
@@ -5503,10 +5541,10 @@
         <v>58</v>
       </c>
       <c r="P163" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="Q163" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="165" spans="1:17" x14ac:dyDescent="0.25">
@@ -5546,12 +5584,12 @@
         <v>48</v>
       </c>
       <c r="N167" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="169" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B169" s="1"/>
       <c r="C169" s="1"/>
@@ -5572,13 +5610,13 @@
     </row>
     <row r="171" spans="1:17" x14ac:dyDescent="0.25">
       <c r="M171" s="9" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="N171" s="9">
         <v>100</v>
       </c>
       <c r="O171" s="9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="P171" s="9" t="s">
         <v>52</v>
@@ -5586,39 +5624,39 @@
     </row>
     <row r="172" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H172" s="6" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="M172" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="N172">
         <v>88</v>
       </c>
       <c r="O172" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="P172" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="Q172" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="173" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H173" s="6" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="M173" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="N173">
         <v>90</v>
       </c>
       <c r="O173" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Q173" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="174" spans="1:17" x14ac:dyDescent="0.25">
@@ -5627,19 +5665,19 @@
     <row r="175" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H175" s="6"/>
       <c r="M175" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="N175">
         <v>1.6E-2</v>
       </c>
       <c r="O175" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="P175" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="Q175" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="176" spans="1:17" x14ac:dyDescent="0.25">
@@ -5647,173 +5685,173 @@
     </row>
     <row r="177" spans="1:17" x14ac:dyDescent="0.25">
       <c r="M177" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="N177" s="13">
         <f>0.16*10.36*0.9</f>
         <v>1.4918400000000001</v>
       </c>
       <c r="O177" t="s">
+        <v>345</v>
+      </c>
+      <c r="P177" t="s">
+        <v>346</v>
+      </c>
+      <c r="Q177" t="s">
         <v>347</v>
-      </c>
-      <c r="P177" t="s">
-        <v>348</v>
-      </c>
-      <c r="Q177" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="180" spans="1:17" x14ac:dyDescent="0.25">
       <c r="M180" s="9" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="N180" s="9">
         <v>-99</v>
       </c>
       <c r="O180" s="9"/>
       <c r="P180" s="9" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="181" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C181" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="M181" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="N181">
         <v>17</v>
       </c>
       <c r="O181" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Q181" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="182" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C182" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="M182" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="N182">
         <v>17</v>
       </c>
       <c r="O182" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Q182" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="183" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C183" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="M183" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="N183">
         <v>17</v>
       </c>
       <c r="O183" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Q183" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="184" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C184" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="M184" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="N184">
         <v>14</v>
       </c>
       <c r="O184" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Q184" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="186" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C186" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="M186" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="N186">
         <v>14</v>
       </c>
       <c r="O186" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Q186" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="187" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C187" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="M187" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="N187">
         <v>14</v>
       </c>
       <c r="O187" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Q187" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="188" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C188" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="M188" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="N188">
         <v>14</v>
       </c>
       <c r="O188" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Q188" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="189" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C189" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="M189" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="N189">
         <v>9</v>
       </c>
       <c r="O189" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Q189" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="191" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
@@ -5834,13 +5872,13 @@
     </row>
     <row r="195" spans="1:17" x14ac:dyDescent="0.25">
       <c r="M195" s="9" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="N195" s="9">
         <v>0</v>
       </c>
       <c r="O195" s="9" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="P195" s="9" t="s">
         <v>52</v>
@@ -5848,147 +5886,147 @@
     </row>
     <row r="196" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B196" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="M196" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="N196">
         <v>302</v>
       </c>
       <c r="O196" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="P196" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="Q196" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="197" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B197" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="M197" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="N197">
         <v>197</v>
       </c>
       <c r="O197" t="s">
+        <v>157</v>
+      </c>
+      <c r="P197" t="s">
         <v>159</v>
       </c>
-      <c r="P197" t="s">
-        <v>161</v>
-      </c>
       <c r="Q197" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="198" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B198" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="M198" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="N198">
         <v>216</v>
       </c>
       <c r="O198" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="P198" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="Q198" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="199" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B199" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="M199" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="N199">
         <v>216</v>
       </c>
       <c r="O199" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="P199" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="Q199" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="200" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B200" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="M200" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="N200">
         <v>216</v>
       </c>
       <c r="O200" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="P200" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="Q200" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="201" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B201" t="s">
+        <v>154</v>
+      </c>
+      <c r="M201" t="s">
         <v>156</v>
-      </c>
-      <c r="M201" t="s">
-        <v>158</v>
       </c>
       <c r="N201">
         <v>216</v>
       </c>
       <c r="O201" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="P201" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="Q201" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="202" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B202" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="M202" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="N202">
         <v>216</v>
       </c>
       <c r="O202" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="P202" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="Q202" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="204" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B204" s="1"/>
       <c r="C204" s="1"/>
@@ -6009,13 +6047,13 @@
     </row>
     <row r="205" spans="1:17" x14ac:dyDescent="0.25">
       <c r="M205" s="9" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="N205" s="9">
         <v>0</v>
       </c>
       <c r="O205" s="9" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="P205" s="9" t="s">
         <v>52</v>
@@ -6023,13 +6061,13 @@
     </row>
     <row r="206" spans="1:17" x14ac:dyDescent="0.25">
       <c r="M206" s="9" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="N206" s="9">
         <v>0</v>
       </c>
       <c r="O206" s="9" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="P206" s="9" t="s">
         <v>52</v>
@@ -6037,13 +6075,13 @@
     </row>
     <row r="207" spans="1:17" x14ac:dyDescent="0.25">
       <c r="M207" s="9" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="N207" s="9">
         <v>0</v>
       </c>
       <c r="O207" s="9" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="P207" s="9" t="s">
         <v>52</v>
@@ -6051,143 +6089,143 @@
     </row>
     <row r="209" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D209" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E209" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="F209" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="G209" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="M209" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="N209" s="25">
         <f>'energy stables'!E24</f>
         <v>3.5302245250431775E-2</v>
       </c>
       <c r="O209" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="P209" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="Q209" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="210" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D210" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E210" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="F210" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="M210" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="N210" s="24">
         <f>'energy stables'!D26</f>
         <v>308.33833333333342</v>
       </c>
       <c r="O210" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="P210" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="Q210" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="211" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D211" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E211" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="F211" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="G211" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="M211" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="N211" s="25">
         <f>'energy stables'!E27</f>
         <v>4.1036269430051814E-2</v>
       </c>
       <c r="O211" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="Q211" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="213" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D213" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="M213" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="N213" s="24">
         <f>'energy stables'!D29</f>
         <v>170.33333333333331</v>
       </c>
       <c r="O213" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="P213" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="Q213" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="214" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D214" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="M214" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="N214" s="24">
         <f>'energy stables'!D31</f>
         <v>332.32333333333338</v>
       </c>
       <c r="O214" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="P214" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="Q214" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="215" spans="1:17" x14ac:dyDescent="0.25">
@@ -6195,330 +6233,330 @@
     </row>
     <row r="216" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D216" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E216" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F216" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="M216" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="N216" s="25">
         <f>(290+1078)/100000</f>
         <v>1.3679999999999999E-2</v>
       </c>
       <c r="O216" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="P216" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="Q216" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="217" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D217" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E217" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F217" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="M217" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="N217" s="25">
         <f>77000/100000</f>
         <v>0.77</v>
       </c>
       <c r="O217" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="Q217" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="218" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D218" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E218" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F218" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="M218" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="N218" s="25">
         <f>(3340+9790)/100000</f>
         <v>0.1313</v>
       </c>
       <c r="O218" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="P218" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="Q218" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="220" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D220" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F220" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="M220" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="N220">
         <f>'energy stables'!D49</f>
         <v>3.5</v>
       </c>
       <c r="O220" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="Q220" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="221" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D221" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F221" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="M221" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="N221">
         <f>'energy stables'!D50</f>
         <v>12.5</v>
       </c>
       <c r="O221" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="Q221" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="222" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D222" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F222" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="M222" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="N222">
         <f>'energy stables'!D51</f>
         <v>34</v>
       </c>
       <c r="O222" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="Q222" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="223" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D223" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F223" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="M223" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="N223">
         <f>'energy stables'!D53</f>
         <v>0.04</v>
       </c>
       <c r="O223" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="Q223" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="224" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D224" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F224" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="M224" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="N224" s="13">
         <f>'energy stables'!D54</f>
         <v>0.1</v>
       </c>
       <c r="O224" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="Q224" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="225" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D225" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F225" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="M225" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="N225" s="13">
         <f>'energy stables'!D55</f>
         <v>0.26</v>
       </c>
       <c r="O225" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="Q225" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="227" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D227" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E227" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="M227" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="N227" s="13">
         <f>'energy stables'!D65</f>
         <v>0.14449999999999999</v>
       </c>
       <c r="O227" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="P227" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="Q227" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="228" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D228" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E228" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="M228" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="N228" s="13">
         <f>'energy stables'!D67</f>
         <v>3.9295</v>
       </c>
       <c r="O228" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="P228" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="Q228" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="229" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D229" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E229" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="F229" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="M229" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="N229">
         <v>0</v>
       </c>
       <c r="O229" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="P229" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="230" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D230" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E230" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="F230" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="M230" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="N230">
         <v>0</v>
@@ -6529,114 +6567,114 @@
     </row>
     <row r="231" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D231" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E231" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="F231" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="M231" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="N231" s="13">
         <f>4.7*(1/3.6)</f>
         <v>1.3055555555555556</v>
       </c>
       <c r="O231" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="P231" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="Q231" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="233" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D233" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="M233" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="N233" s="24">
         <f>0.05*1000*(1/3.6)</f>
         <v>13.888888888888889</v>
       </c>
       <c r="O233" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="P233" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="Q233" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="234" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D234" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="M234" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="N234" s="24">
         <f>0.05*1000*(1/3.6)</f>
         <v>13.888888888888889</v>
       </c>
       <c r="O234" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="P234" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="Q234" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="235" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D235" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="F235" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="M235" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="N235">
         <v>0</v>
       </c>
       <c r="P235" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="236" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D236" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="F236" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="M236" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="N236">
         <v>0</v>
@@ -6662,7 +6700,7 @@
   <sheetData>
     <row r="3" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B3" s="53" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C3" s="54"/>
       <c r="D3" s="54"/>
@@ -6682,37 +6720,37 @@
     </row>
     <row r="4" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B4" s="51" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B5" s="27"/>
       <c r="C5" s="30"/>
       <c r="D5" s="46" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E5" s="28" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F5" s="30" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G5" s="29" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H5" s="28" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="I5" s="30" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="6" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B6" s="31" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C6" s="44" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D6" s="31">
         <v>150</v>
@@ -6727,10 +6765,10 @@
     </row>
     <row r="7" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B7" s="31" t="s">
+        <v>204</v>
+      </c>
+      <c r="C7" s="44" t="s">
         <v>206</v>
-      </c>
-      <c r="C7" s="44" t="s">
-        <v>208</v>
       </c>
       <c r="D7" s="31">
         <v>150</v>
@@ -6745,10 +6783,10 @@
     </row>
     <row r="8" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B8" s="31" t="s">
+        <v>205</v>
+      </c>
+      <c r="C8" s="44" t="s">
         <v>207</v>
-      </c>
-      <c r="C8" s="44" t="s">
-        <v>209</v>
       </c>
       <c r="D8" s="31">
         <v>10500</v>
@@ -6773,10 +6811,10 @@
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B10" s="31" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C10" s="44" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D10" s="31">
         <v>652</v>
@@ -6801,15 +6839,15 @@
         <v>123.33333333333333</v>
       </c>
       <c r="J10" s="26" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B11" s="31" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C11" s="44" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D11" s="31">
         <v>3</v>
@@ -6837,10 +6875,10 @@
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B12" s="31" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C12" s="44" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D12" s="31">
         <v>40</v>
@@ -6865,15 +6903,15 @@
         <v>10.333333333333332</v>
       </c>
       <c r="J12" s="26" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B13" s="31" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C13" s="44" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D13" s="31">
         <v>216</v>
@@ -6901,10 +6939,10 @@
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B14" s="31" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C14" s="44" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D14" s="31">
         <v>386</v>
@@ -6927,15 +6965,15 @@
         <v>0</v>
       </c>
       <c r="J14" s="26" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="15" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B15" s="31" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C15" s="44" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D15" s="31">
         <v>216</v>
@@ -6972,10 +7010,10 @@
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B17" s="36" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C17" s="44" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D17" s="36">
         <f>SUM(D10:D15)</f>
@@ -7004,10 +7042,10 @@
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B18" s="31" t="s">
+        <v>215</v>
+      </c>
+      <c r="C18" s="44" t="s">
         <v>217</v>
-      </c>
-      <c r="C18" s="44" t="s">
-        <v>219</v>
       </c>
       <c r="D18" s="31">
         <v>868</v>
@@ -7062,10 +7100,10 @@
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B20" s="42" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C20" s="45" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D20" s="42">
         <v>23</v>
@@ -7080,25 +7118,25 @@
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B22" s="71" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B23" s="79"/>
       <c r="C23" s="80"/>
       <c r="D23" s="81" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E23" s="82" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B24" s="64" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C24" s="65" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D24" s="72">
         <v>0</v>
@@ -7110,10 +7148,10 @@
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B25" s="64" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C25" s="65" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D25" s="72">
         <v>0</v>
@@ -7124,10 +7162,10 @@
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B26" s="64" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C26" s="65" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D26" s="75">
         <f>SUM(E11:E13,E15,H11:H13,H15)/2</f>
@@ -7139,10 +7177,10 @@
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B27" s="64" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C27" s="65" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D27" s="72">
         <v>0</v>
@@ -7160,10 +7198,10 @@
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B29" s="64" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C29" s="65" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D29" s="75">
         <f>SUM(F10,I10)/2</f>
@@ -7175,10 +7213,10 @@
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B30" s="64" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C30" s="65" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D30" s="72">
         <v>0</v>
@@ -7189,10 +7227,10 @@
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B31" s="64" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C31" s="65" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D31" s="75">
         <f>SUM(F11:F13,F15,I11:I13,I15)</f>
@@ -7204,10 +7242,10 @@
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B32" s="66" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C32" s="67" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D32" s="76">
         <v>0</v>
@@ -7218,7 +7256,7 @@
     </row>
     <row r="34" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B34" s="53" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C34" s="54"/>
       <c r="D34" s="54"/>
@@ -7238,69 +7276,69 @@
     </row>
     <row r="35" spans="2:19" x14ac:dyDescent="0.25">
       <c r="J35" s="51" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="36" spans="2:19" x14ac:dyDescent="0.25">
       <c r="J36" s="46" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="K36" s="28"/>
       <c r="L36" s="28"/>
       <c r="M36" s="29" t="s">
+        <v>297</v>
+      </c>
+      <c r="N36" s="29" t="s">
+        <v>298</v>
+      </c>
+      <c r="O36" s="29" t="s">
         <v>299</v>
       </c>
-      <c r="N36" s="29" t="s">
+      <c r="P36" s="50" t="s">
         <v>300</v>
       </c>
-      <c r="O36" s="29" t="s">
-        <v>301</v>
-      </c>
-      <c r="P36" s="50" t="s">
-        <v>302</v>
-      </c>
       <c r="Q36" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="37" spans="2:19" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="51" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="J37" s="42" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="K37" s="14"/>
       <c r="L37" s="14"/>
       <c r="M37" s="59" t="s">
+        <v>293</v>
+      </c>
+      <c r="N37" s="59" t="s">
+        <v>294</v>
+      </c>
+      <c r="O37" s="59" t="s">
         <v>295</v>
       </c>
-      <c r="N37" s="59" t="s">
+      <c r="P37" s="60" t="s">
         <v>296</v>
       </c>
-      <c r="O37" s="59" t="s">
-        <v>297</v>
-      </c>
-      <c r="P37" s="60" t="s">
-        <v>298</v>
-      </c>
       <c r="Q37" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="38" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B38" s="46" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C38" s="29"/>
       <c r="D38" s="29" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E38" s="50" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="J38" s="31" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -7317,14 +7355,14 @@
         <v>242</v>
       </c>
       <c r="Q38" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="R38" s="58"/>
       <c r="S38" s="58"/>
     </row>
     <row r="39" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="31" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C39" s="4"/>
       <c r="D39" s="4">
@@ -7334,7 +7372,7 @@
         <v>0.4</v>
       </c>
       <c r="J39" s="31" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -7348,17 +7386,17 @@
         <v>9.6</v>
       </c>
       <c r="P39" s="32" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="Q39" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="R39" s="58"/>
       <c r="S39" s="58"/>
     </row>
     <row r="40" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B40" s="31" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C40" s="4"/>
       <c r="D40" s="4">
@@ -7368,7 +7406,7 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="J40" s="31" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -7385,14 +7423,14 @@
         <v>43.2</v>
       </c>
       <c r="Q40" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="R40" s="58"/>
       <c r="S40" s="58"/>
     </row>
     <row r="41" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B41" s="31" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C41" s="4"/>
       <c r="D41" s="4">
@@ -7402,7 +7440,7 @@
         <v>0.06</v>
       </c>
       <c r="J41" s="31" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -7419,14 +7457,14 @@
         <v>340</v>
       </c>
       <c r="Q41" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="R41" s="58"/>
       <c r="S41" s="58"/>
     </row>
     <row r="42" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B42" s="31" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C42" s="4"/>
       <c r="D42" s="4">
@@ -7436,7 +7474,7 @@
         <v>0.04</v>
       </c>
       <c r="J42" s="31" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -7450,17 +7488,17 @@
         <v>4.2</v>
       </c>
       <c r="P42" s="32" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="Q42" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="R42" s="58"/>
       <c r="S42" s="58"/>
     </row>
     <row r="43" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B43" s="42" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C43" s="14"/>
       <c r="D43" s="14">
@@ -7492,41 +7530,41 @@
     </row>
     <row r="44" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C44" s="68" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D44" s="69">
         <f>D39*33+E39*26</f>
         <v>1660.4</v>
       </c>
       <c r="E44" s="70" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="J44" s="31" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
       <c r="M44" s="4" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="N44" s="4">
         <v>4</v>
       </c>
       <c r="O44" s="4" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="P44" s="32" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="Q44" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="R44" s="58"/>
       <c r="S44" s="58"/>
     </row>
     <row r="45" spans="2:19" x14ac:dyDescent="0.25">
       <c r="J45" s="31" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -7540,37 +7578,37 @@
         <v>0.7</v>
       </c>
       <c r="P45" s="32" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="Q45" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="R45" s="58"/>
       <c r="S45" s="58"/>
     </row>
     <row r="46" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B46" s="71" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="J46" s="31" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
       <c r="M46" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N46" s="4">
         <v>11</v>
       </c>
       <c r="O46" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P46" s="32" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="Q46" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="R46" s="58"/>
       <c r="S46" s="58"/>
@@ -7579,16 +7617,16 @@
       <c r="B47" s="27"/>
       <c r="C47" s="28"/>
       <c r="D47" s="86" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E47" s="28" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="F47" s="28"/>
       <c r="G47" s="28"/>
       <c r="H47" s="30"/>
       <c r="J47" s="31" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -7599,13 +7637,13 @@
         <v>15</v>
       </c>
       <c r="O47" s="4" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="P47" s="32" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="Q47" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="R47" s="58"/>
       <c r="S47" s="58"/>
@@ -7614,22 +7652,22 @@
       <c r="B48" s="42"/>
       <c r="C48" s="14"/>
       <c r="D48" s="87" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E48" s="14" t="s">
         <v>26</v>
       </c>
       <c r="F48" s="83" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G48" s="83" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="H48" s="84" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="J48" s="31" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -7643,20 +7681,20 @@
         <v>1</v>
       </c>
       <c r="P48" s="32" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="Q48" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="R48" s="58"/>
       <c r="S48" s="58"/>
     </row>
     <row r="49" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B49" s="85" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C49" s="28" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D49" s="88">
         <f>D42</f>
@@ -7675,7 +7713,7 @@
         <v>0</v>
       </c>
       <c r="J49" s="46" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="K49" s="29"/>
       <c r="L49" s="29"/>
@@ -7692,17 +7730,17 @@
         <v>1252</v>
       </c>
       <c r="Q49" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="R49" s="58"/>
       <c r="S49" s="58"/>
     </row>
     <row r="50" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B50" s="31" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D50" s="88">
         <f>D39*0.25</f>
@@ -7724,7 +7762,7 @@
         <v>20</v>
       </c>
       <c r="J50" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -7745,10 +7783,10 @@
     </row>
     <row r="51" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B51" s="31" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D51" s="89">
         <f>D39-D49-D50</f>
@@ -7767,7 +7805,7 @@
         <v>100</v>
       </c>
       <c r="J51" s="61" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="K51" s="63"/>
       <c r="L51" s="63"/>
@@ -7788,7 +7826,7 @@
         <v>34</v>
       </c>
       <c r="Q51" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="R51" s="58"/>
       <c r="S51" s="58"/>
@@ -7802,7 +7840,7 @@
       <c r="G52" s="72"/>
       <c r="H52" s="74"/>
       <c r="J52" s="55" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="K52" s="56"/>
       <c r="L52" s="56"/>
@@ -7813,21 +7851,21 @@
         <v>38</v>
       </c>
       <c r="O52" s="56" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P52" s="57" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="Q52" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="53" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B53" s="64" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D53" s="88">
         <f>E42</f>
@@ -7846,32 +7884,32 @@
         <v>0</v>
       </c>
       <c r="J53" s="31" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
       <c r="M53" s="4" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="N53" s="4" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="O53" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P53" s="32" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="Q53" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="54" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B54" s="31" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D54" s="90">
         <f>E39*0.25</f>
@@ -7893,32 +7931,32 @@
         <v>20.000000000000018</v>
       </c>
       <c r="J54" s="31" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>
       <c r="M54" s="4" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="N54" s="4" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="O54" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P54" s="32" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="Q54" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="55" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B55" s="42" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C55" s="14" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D55" s="91">
         <f>E39-D53-D54</f>
@@ -7937,27 +7975,27 @@
         <v>100</v>
       </c>
       <c r="J55" s="31" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="K55" s="4"/>
       <c r="L55" s="4"/>
       <c r="M55" s="4" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="N55" s="4"/>
       <c r="O55" s="4" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="P55" s="32" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="Q55" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="56" spans="2:19" x14ac:dyDescent="0.25">
       <c r="J56" s="42" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="K56" s="14"/>
       <c r="L56" s="14"/>
@@ -7976,7 +8014,7 @@
     </row>
     <row r="58" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B58" s="53" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C58" s="52"/>
       <c r="D58" s="52"/>
@@ -7996,47 +8034,47 @@
     </row>
     <row r="59" spans="2:19" x14ac:dyDescent="0.25">
       <c r="J59" s="51" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="60" spans="2:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J60" s="27" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="K60" s="28"/>
       <c r="L60" s="28"/>
       <c r="M60" s="103" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="N60" s="103"/>
       <c r="O60" s="103" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="P60" s="104"/>
       <c r="Q60" s="4"/>
     </row>
     <row r="61" spans="2:19" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J61" s="100" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="K61" s="14"/>
       <c r="L61" s="14"/>
       <c r="M61" s="101" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="N61" s="101"/>
       <c r="O61" s="101" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="P61" s="102"/>
       <c r="Q61" s="4"/>
     </row>
     <row r="62" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B62" s="71" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="J62" s="27" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="K62" s="28"/>
       <c r="L62" s="28"/>
@@ -8044,13 +8082,13 @@
         <v>130</v>
       </c>
       <c r="N62" s="96" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="O62" s="28">
         <v>106</v>
       </c>
       <c r="P62" s="97" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="Q62" s="4"/>
     </row>
@@ -8058,16 +8096,16 @@
       <c r="B63" s="27"/>
       <c r="C63" s="28"/>
       <c r="D63" s="86" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E63" s="28" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="F63" s="28"/>
       <c r="G63" s="28"/>
       <c r="H63" s="30"/>
       <c r="J63" s="31" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="K63" s="4"/>
       <c r="L63" s="4"/>
@@ -8085,22 +8123,22 @@
       <c r="B64" s="42"/>
       <c r="C64" s="14"/>
       <c r="D64" s="87" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="E64" s="14" t="s">
         <v>26</v>
       </c>
       <c r="F64" s="83" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G64" s="83" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="H64" s="84" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="J64" s="31" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="K64" s="4"/>
       <c r="L64" s="4"/>
@@ -8116,7 +8154,7 @@
     </row>
     <row r="65" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B65" s="85" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C65" s="28"/>
       <c r="D65" s="90">
@@ -8136,7 +8174,7 @@
         <v>90</v>
       </c>
       <c r="J65" s="31" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="K65" s="4"/>
       <c r="L65" s="4"/>
@@ -8152,7 +8190,7 @@
     </row>
     <row r="66" spans="2:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B66" s="31" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C66" s="4"/>
       <c r="D66" s="88">
@@ -8163,23 +8201,23 @@
       <c r="G66" s="75"/>
       <c r="H66" s="78"/>
       <c r="J66" s="94" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="K66" s="95"/>
       <c r="L66" s="95"/>
       <c r="M66" s="95" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="N66" s="95"/>
       <c r="O66" s="95" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="P66" s="44"/>
       <c r="Q66" s="4"/>
     </row>
     <row r="67" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B67" s="42" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C67" s="14"/>
       <c r="D67" s="91">
@@ -8199,7 +8237,7 @@
         <v>100</v>
       </c>
       <c r="J67" s="31" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="K67" s="4"/>
       <c r="L67" s="4"/>
@@ -8215,7 +8253,7 @@
     </row>
     <row r="68" spans="2:17" x14ac:dyDescent="0.25">
       <c r="J68" s="31" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="K68" s="4"/>
       <c r="L68" s="4"/>
@@ -8231,12 +8269,12 @@
     </row>
     <row r="69" spans="2:17" x14ac:dyDescent="0.25">
       <c r="J69" s="31" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="K69" s="4"/>
       <c r="L69" s="4"/>
       <c r="M69" s="4" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="N69" s="4"/>
       <c r="O69" s="4">
@@ -8247,12 +8285,12 @@
     </row>
     <row r="70" spans="2:17" x14ac:dyDescent="0.25">
       <c r="J70" s="31" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="K70" s="4"/>
       <c r="L70" s="4"/>
       <c r="M70" s="4" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="N70" s="4"/>
       <c r="O70" s="4">
@@ -8263,7 +8301,7 @@
     </row>
     <row r="71" spans="2:17" x14ac:dyDescent="0.25">
       <c r="J71" s="31" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="K71" s="4"/>
       <c r="L71" s="4"/>
@@ -8279,7 +8317,7 @@
     </row>
     <row r="72" spans="2:17" x14ac:dyDescent="0.25">
       <c r="J72" s="98" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="K72" s="93"/>
       <c r="L72" s="93"/>
@@ -8295,28 +8333,28 @@
     </row>
     <row r="73" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J73" s="55" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="K73" s="56"/>
       <c r="L73" s="56"/>
       <c r="M73" s="56" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="N73" s="56"/>
       <c r="O73" s="56" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="P73" s="57"/>
       <c r="Q73" s="4"/>
     </row>
     <row r="74" spans="2:17" x14ac:dyDescent="0.25">
       <c r="J74" s="31" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="K74" s="4"/>
       <c r="L74" s="4"/>
       <c r="M74" s="4" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="N74" s="4"/>
       <c r="O74" s="4">
@@ -8327,7 +8365,7 @@
     </row>
     <row r="75" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J75" s="55" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="K75" s="56"/>
       <c r="L75" s="56"/>
@@ -8364,7 +8402,7 @@
   <sheetData>
     <row r="3" spans="5:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E3" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F3">
         <v>90</v>
@@ -8381,7 +8419,7 @@
     </row>
     <row r="4" spans="5:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E4" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F4">
         <v>654</v>
@@ -8390,15 +8428,15 @@
         <v>80</v>
       </c>
       <c r="H4" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="I4" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="5" spans="5:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E5" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="F5">
         <v>11</v>
@@ -8407,66 +8445,66 @@
         <v>12</v>
       </c>
       <c r="H5" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="I5" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="6" spans="5:20" x14ac:dyDescent="0.25">
       <c r="E6" t="s">
+        <v>286</v>
+      </c>
+      <c r="F6" t="s">
+        <v>287</v>
+      </c>
+      <c r="G6" t="s">
         <v>288</v>
       </c>
-      <c r="F6" t="s">
+      <c r="H6" t="s">
         <v>289</v>
       </c>
-      <c r="G6" t="s">
+      <c r="I6" t="s">
         <v>290</v>
-      </c>
-      <c r="H6" t="s">
-        <v>291</v>
-      </c>
-      <c r="I6" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="7" spans="5:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E7" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="G7" t="s">
+        <v>259</v>
+      </c>
+      <c r="I7" t="s">
+        <v>260</v>
+      </c>
+      <c r="O7" t="s">
         <v>261</v>
       </c>
-      <c r="I7" t="s">
-        <v>262</v>
-      </c>
-      <c r="O7" t="s">
-        <v>263</v>
-      </c>
       <c r="S7" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="8" spans="5:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E8" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="H8" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="K8">
         <v>4</v>
       </c>
       <c r="P8" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="T8" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="9" spans="5:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E9" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="H9">
         <v>79</v>
@@ -8475,32 +8513,32 @@
         <v>7</v>
       </c>
       <c r="P9" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="T9" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="10" spans="5:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E10" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="H10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K10">
         <v>11</v>
       </c>
       <c r="P10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T10" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="11" spans="5:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E11" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="H11">
         <v>38</v>
@@ -8509,15 +8547,15 @@
         <v>15</v>
       </c>
       <c r="P11" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="T11" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="12" spans="5:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E12" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="H12">
         <v>164</v>
@@ -8526,15 +8564,15 @@
         <v>66</v>
       </c>
       <c r="P12" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="T12" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="13" spans="5:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E13" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="H13">
         <v>2433</v>
@@ -8543,7 +8581,7 @@
         <v>689</v>
       </c>
       <c r="P13" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="T13">
         <v>1252</v>
@@ -8551,7 +8589,7 @@
     </row>
     <row r="14" spans="5:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E14" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="H14">
         <v>1441</v>
@@ -8560,7 +8598,7 @@
         <v>689</v>
       </c>
       <c r="P14" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="T14">
         <v>1218</v>
@@ -8568,47 +8606,47 @@
     </row>
     <row r="15" spans="5:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E15" t="s">
+        <v>276</v>
+      </c>
+      <c r="L15" t="s">
+        <v>277</v>
+      </c>
+      <c r="Q15" t="s">
         <v>278</v>
-      </c>
-      <c r="L15" t="s">
-        <v>279</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="16" spans="5:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E16" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="H16" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="K16" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="P16" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T16" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="17" spans="5:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E17" t="s">
+        <v>281</v>
+      </c>
+      <c r="H17" t="s">
+        <v>282</v>
+      </c>
+      <c r="K17" t="s">
         <v>283</v>
       </c>
-      <c r="H17" t="s">
+      <c r="P17" t="s">
         <v>284</v>
       </c>
-      <c r="K17" t="s">
+      <c r="T17" t="s">
         <v>285</v>
-      </c>
-      <c r="P17" t="s">
-        <v>286</v>
-      </c>
-      <c r="T17" t="s">
-        <v>287</v>
       </c>
     </row>
   </sheetData>
@@ -8627,47 +8665,47 @@
   <sheetData>
     <row r="3" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="F3" s="49" t="s">
+        <v>297</v>
+      </c>
+      <c r="G3" s="49" t="s">
+        <v>298</v>
+      </c>
+      <c r="H3" s="49" t="s">
         <v>299</v>
       </c>
-      <c r="G3" s="49" t="s">
+      <c r="I3" s="49" t="s">
         <v>300</v>
       </c>
-      <c r="H3" s="49" t="s">
-        <v>301</v>
-      </c>
-      <c r="I3" s="49" t="s">
-        <v>302</v>
-      </c>
       <c r="J3" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="4" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="F4" t="s">
+        <v>293</v>
+      </c>
+      <c r="G4" t="s">
+        <v>294</v>
+      </c>
+      <c r="H4" t="s">
         <v>295</v>
       </c>
-      <c r="G4" t="s">
+      <c r="I4" t="s">
         <v>296</v>
       </c>
-      <c r="H4" t="s">
-        <v>297</v>
-      </c>
-      <c r="I4" t="s">
-        <v>298</v>
-      </c>
       <c r="J4" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="5" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F5">
         <v>90</v>
@@ -8682,12 +8720,12 @@
         <v>242</v>
       </c>
       <c r="J5" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="6" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F6">
         <v>654</v>
@@ -8699,15 +8737,15 @@
         <v>9.6</v>
       </c>
       <c r="I6" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="J6" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="7" spans="3:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="F7">
         <v>11</v>
@@ -8722,12 +8760,12 @@
         <v>43.2</v>
       </c>
       <c r="J7" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="8" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F8">
         <v>244</v>
@@ -8742,12 +8780,12 @@
         <v>340</v>
       </c>
       <c r="J8" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="9" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F9">
         <v>992</v>
@@ -8759,35 +8797,35 @@
         <v>4.2</v>
       </c>
       <c r="I9" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="J9" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="10" spans="3:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F10" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="G10">
         <v>4</v>
       </c>
       <c r="H10" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="I10" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="J10" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="11" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="F11">
         <v>79</v>
@@ -8799,35 +8837,35 @@
         <v>0.7</v>
       </c>
       <c r="I11" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="J11" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="12" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="F12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G12">
         <v>11</v>
       </c>
       <c r="H12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I12" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="J12" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="13" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="F13">
         <v>38</v>
@@ -8836,18 +8874,18 @@
         <v>15</v>
       </c>
       <c r="H13" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="I13" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="J13" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="14" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F14">
         <v>164</v>
@@ -8859,15 +8897,15 @@
         <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="J14" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="15" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F15">
         <v>2433</v>
@@ -8882,12 +8920,12 @@
         <v>1252</v>
       </c>
       <c r="J15" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="16" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C16" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F16">
         <v>1441</v>
@@ -8902,12 +8940,12 @@
         <v>1218</v>
       </c>
       <c r="J16" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="17" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C17" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="F17">
         <v>23</v>
@@ -8916,75 +8954,75 @@
         <v>38</v>
       </c>
       <c r="H17" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I17" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="J17" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="18" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C18" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="F18" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="G18" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="H18" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I18" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="J18" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="19" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C19" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="F19" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="G19" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="H19" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I19" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="J19" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="20" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C20" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="F20" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="H20" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="I20" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="J20" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="21" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C21" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F21">
         <v>1998</v>
@@ -8999,7 +9037,7 @@
         <v>2008</v>
       </c>
       <c r="J21" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
   </sheetData>
@@ -9015,72 +9053,72 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="17" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="17" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
-        <v>142</v>
+        <v>402</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="48" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="48" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="48" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
   </sheetData>

--- a/data/default/MachineryAndEnergyMgmt.xlsx
+++ b/data/default/MachineryAndEnergyMgmt.xlsx
@@ -814,9 +814,6 @@
     <t>Moldboard plough</t>
   </si>
   <si>
-    <t>Disc harrow</t>
-  </si>
-  <si>
     <t>?</t>
   </si>
   <si>
@@ -1860,10 +1857,13 @@
     <t>E_per_area_manure</t>
   </si>
   <si>
-    <t>Field cultivator, 10 tools per meter</t>
-  </si>
-  <si>
     <t>ASAE. (2000). Agricultural Machinery Management Data. In. ASABE, St. Joseph, MI, USA: American Society of Agricultural Engineers</t>
+  </si>
+  <si>
+    <t>Field cultivator, primary tillage, 10 tools per meter</t>
+  </si>
+  <si>
+    <t>Chisel Plow, 7.5 cm shovel/35 cm sweep, 4 tools per meter</t>
   </si>
 </sst>
 </file>
@@ -2694,28 +2694,28 @@
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="49" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B1" s="93" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="93" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="D1" s="93" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E1" s="93" t="s">
+        <v>195</v>
+      </c>
+      <c r="F1" s="93" t="s">
         <v>196</v>
       </c>
-      <c r="F1" s="93" t="s">
-        <v>197</v>
-      </c>
       <c r="G1" s="93" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H1" s="93" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I1" s="93" t="s">
         <v>51</v>
@@ -2724,10 +2724,10 @@
         <v>44</v>
       </c>
       <c r="K1" s="93" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="L1" s="93" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="M1" s="93" t="s">
         <v>1</v>
@@ -2747,13 +2747,13 @@
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="M2" s="20" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="N2" s="9">
         <v>0</v>
       </c>
       <c r="O2" s="9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="P2" s="9" t="s">
         <v>52</v>
@@ -2761,78 +2761,78 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="M4" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="N4" s="18">
         <f>(241822577+237201100)/(241822577+237201100+5856000+8368914)*100</f>
         <v>97.116076100458642</v>
       </c>
       <c r="O4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="M5" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="N5" s="18">
         <f>100-N4</f>
         <v>2.8839238995413581</v>
       </c>
       <c r="O5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="M6" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="N6" s="10">
         <v>0</v>
       </c>
       <c r="O6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="M7" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="N7" s="10">
         <v>0</v>
       </c>
       <c r="O7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
@@ -2842,30 +2842,30 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="N9" s="10">
         <v>100</v>
       </c>
       <c r="O9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H10" s="4"/>
       <c r="M10" s="6"/>
@@ -2873,42 +2873,42 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D11" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="M11" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="N11" s="10">
         <v>100</v>
       </c>
       <c r="O11" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D12" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="M12" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="N12" s="10">
         <v>100</v>
       </c>
       <c r="O12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
@@ -2918,71 +2918,71 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D14" t="s">
+        <v>228</v>
+      </c>
+      <c r="E14" t="s">
         <v>229</v>
       </c>
-      <c r="E14" t="s">
-        <v>230</v>
-      </c>
       <c r="H14" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="M14" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="N14" s="10">
         <v>100</v>
       </c>
       <c r="O14" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D15" t="s">
+        <v>228</v>
+      </c>
+      <c r="E15" t="s">
         <v>229</v>
       </c>
-      <c r="E15" t="s">
-        <v>230</v>
-      </c>
       <c r="H15" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="N15" s="10">
         <v>100</v>
       </c>
       <c r="O15" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D16" t="s">
+        <v>228</v>
+      </c>
+      <c r="E16" t="s">
         <v>229</v>
       </c>
-      <c r="E16" t="s">
-        <v>230</v>
-      </c>
       <c r="H16" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="N16" s="10">
         <v>100</v>
       </c>
       <c r="O16" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
@@ -2992,262 +2992,262 @@
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D18" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F18" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="M18" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="N18" s="10">
         <v>100</v>
       </c>
       <c r="O18" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q18" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D19" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F19" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="M19" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="N19">
         <v>4</v>
       </c>
       <c r="O19" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q19" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D20" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F20" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="M20" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="N20">
         <v>76</v>
       </c>
       <c r="O20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q20" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D21" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F21" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="M21" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="N21">
         <v>20</v>
       </c>
       <c r="O21" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q21" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D22" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F22" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="N22" s="10">
         <v>100</v>
       </c>
       <c r="O22" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q22" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D23" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F23" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="M23" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="N23" s="10">
         <v>100</v>
       </c>
       <c r="O23" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q23" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D24" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F24" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="M24" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="N24">
         <v>20</v>
       </c>
       <c r="O24" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q24" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D25" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F25" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="M25" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="N25">
         <v>60</v>
       </c>
       <c r="O25" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q25" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D26" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F26" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="M26" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="N26">
         <v>20.000000000000018</v>
       </c>
       <c r="O26" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q26" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D27" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F27" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="M27" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="N27" s="10">
         <v>100</v>
       </c>
       <c r="O27" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q27" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
@@ -3257,123 +3257,123 @@
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D29" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E29" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="M29" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="N29" s="10">
         <v>90</v>
       </c>
       <c r="O29" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D30" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E30" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="M30" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="N30" s="10">
         <v>10</v>
       </c>
       <c r="O30" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D31" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E31" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="M31" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="N31" s="10">
         <v>100</v>
       </c>
       <c r="O31" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D32" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E32" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="M32" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="N32" s="10">
         <v>90</v>
       </c>
       <c r="O32" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q32" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D33" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E33" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="M33" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="N33" s="10">
         <v>10</v>
       </c>
       <c r="O33" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q33" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
@@ -3383,48 +3383,48 @@
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D35" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="M35" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="N35" s="10">
         <v>100</v>
       </c>
       <c r="O35" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q35" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D36" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="M36" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="N36" s="10">
         <v>100</v>
       </c>
       <c r="O36" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q36" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
@@ -3434,119 +3434,119 @@
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>146</v>
+      </c>
+      <c r="H38" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="M38" s="6" t="s">
         <v>147</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="M38" s="6" t="s">
-        <v>148</v>
       </c>
       <c r="N38" s="11">
         <v>6.4777062142923141</v>
       </c>
       <c r="O38" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q38" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>146</v>
+      </c>
+      <c r="H39" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="M39" s="6" t="s">
         <v>147</v>
-      </c>
-      <c r="H39" s="6" t="s">
-        <v>327</v>
-      </c>
-      <c r="M39" s="6" t="s">
-        <v>148</v>
       </c>
       <c r="N39" s="11">
         <v>8.7567853491111922</v>
       </c>
       <c r="O39" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="P39" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Q39" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>146</v>
+      </c>
+      <c r="H40" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="M40" s="6" t="s">
         <v>147</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="M40" s="6" t="s">
-        <v>148</v>
       </c>
       <c r="N40" s="18">
         <v>59.671114354829328</v>
       </c>
       <c r="O40" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="P40" s="19" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Q40" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>146</v>
+      </c>
+      <c r="H41" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="M41" s="6" t="s">
         <v>147</v>
-      </c>
-      <c r="H41" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="M41" s="6" t="s">
-        <v>148</v>
       </c>
       <c r="N41" s="18">
         <v>16.802918820320372</v>
       </c>
       <c r="O41" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>146</v>
+      </c>
+      <c r="H42" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="M42" s="6" t="s">
         <v>147</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>326</v>
-      </c>
-      <c r="M42" s="6" t="s">
-        <v>148</v>
       </c>
       <c r="N42" s="11">
         <v>7.4851294970113242</v>
       </c>
       <c r="O42" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>146</v>
+      </c>
+      <c r="H43" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="M43" s="6" t="s">
         <v>147</v>
-      </c>
-      <c r="H43" s="6" t="s">
-        <v>325</v>
-      </c>
-      <c r="M43" s="6" t="s">
-        <v>148</v>
       </c>
       <c r="N43" s="11">
         <v>0.80634576443547301</v>
       </c>
       <c r="O43" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
@@ -3556,62 +3556,62 @@
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="M45" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="N45" s="18">
         <v>70</v>
       </c>
       <c r="O45" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="P45" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="Q45" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="M46" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="N46" s="18">
         <v>30</v>
       </c>
       <c r="O46" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q46" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="M47" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="N47" s="18">
         <v>100</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
@@ -3619,49 +3619,49 @@
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="K49" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M49" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N49" s="15">
         <v>80</v>
       </c>
       <c r="O49" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="K50" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="M50" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N50" s="15">
         <v>10</v>
       </c>
       <c r="O50" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="K51" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M51" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N51" s="15">
         <v>10</v>
       </c>
       <c r="O51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -3683,14 +3683,14 @@
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H53" s="4"/>
       <c r="M53" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="N53" s="23">
         <v>0</v>
       </c>
       <c r="O53" s="9"/>
       <c r="P53" s="9" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
@@ -3699,377 +3699,377 @@
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H55" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="L55" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="M55" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="N55" s="18">
         <f>74100</f>
         <v>74100</v>
       </c>
       <c r="O55" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="P55" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q55" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H56" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="L56" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="M56" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="N56" s="11">
         <f>3.9</f>
         <v>3.9</v>
       </c>
       <c r="O56" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q56" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H57" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="L57" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="M57" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="N57" s="11">
         <f>3.9</f>
         <v>3.9</v>
       </c>
       <c r="O57" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q57" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H58" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="L58" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="M58" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="N58" s="18">
         <v>0</v>
       </c>
       <c r="O58" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H59" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="L59" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="M59" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="N59" s="22">
         <f t="shared" ref="N59:N60" si="0">N56</f>
         <v>3.9</v>
       </c>
       <c r="O59" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="P59" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H60" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="L60" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="M60" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="N60" s="22">
         <f t="shared" si="0"/>
         <v>3.9</v>
       </c>
       <c r="O60" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="P60" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H61" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="L61" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="M61" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="N61" s="18">
         <v>73300</v>
       </c>
       <c r="O61" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="P61" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q61" t="s">
         <v>183</v>
-      </c>
-      <c r="Q61" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H62" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="L62" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="M62" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="N62">
         <v>10</v>
       </c>
       <c r="O62" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q62" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H63" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="L63" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="M63" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="N63">
         <v>0.6</v>
       </c>
       <c r="O63" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q63" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H64" s="6" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="L64" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="M64" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="N64" s="18">
         <v>56100</v>
       </c>
       <c r="O64" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="P64" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q64" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H65" s="6" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="L65" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="M65" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="N65">
         <v>5</v>
       </c>
       <c r="O65" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q65" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H66" s="6" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="L66" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="M66" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="N66">
         <v>0.1</v>
       </c>
       <c r="O66" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q66" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H67" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="L67" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="M67" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="N67" s="18">
         <v>0</v>
       </c>
       <c r="O67" t="s">
+        <v>179</v>
+      </c>
+      <c r="P67" t="s">
         <v>180</v>
       </c>
-      <c r="P67" t="s">
-        <v>181</v>
-      </c>
       <c r="Q67" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H68" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="L68" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="M68" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="N68" s="18">
         <v>300</v>
       </c>
       <c r="O68" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q68" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H69" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="L69" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="M69" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="N69" s="18">
         <v>4</v>
       </c>
       <c r="O69" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q69" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H70" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="M70" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="N70" s="18">
         <v>0</v>
       </c>
       <c r="O70" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="P70" s="15"/>
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H71" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="M71" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="N71" s="18">
         <v>0</v>
       </c>
       <c r="O71" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="P71" s="15"/>
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H72" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="M72" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="N72" s="18">
         <v>0</v>
       </c>
       <c r="O72" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="P72" s="15" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H73" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="M73" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="N73" s="18">
         <v>0</v>
       </c>
       <c r="O73" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="P73" s="15"/>
     </row>
@@ -4183,13 +4183,13 @@
       <c r="K79" s="4"/>
       <c r="L79" s="4"/>
       <c r="M79" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="N79">
         <v>2</v>
       </c>
       <c r="O79" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="P79" s="7"/>
     </row>
@@ -4299,7 +4299,7 @@
       <c r="F84" s="4"/>
       <c r="G84" s="4"/>
       <c r="H84" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="I84" s="4"/>
       <c r="J84" s="4"/>
@@ -4323,7 +4323,7 @@
       <c r="F85" s="4"/>
       <c r="G85" s="4"/>
       <c r="H85" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="I85" s="4"/>
       <c r="J85" s="4"/>
@@ -4347,7 +4347,7 @@
       <c r="F86" s="4"/>
       <c r="G86" s="4"/>
       <c r="H86" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="I86" s="4"/>
       <c r="J86" s="4"/>
@@ -4371,7 +4371,7 @@
       <c r="F87" s="4"/>
       <c r="G87" s="4"/>
       <c r="H87" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I87" s="6"/>
       <c r="J87" s="6"/>
@@ -4435,7 +4435,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="M91" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="N91">
         <v>4</v>
@@ -4561,7 +4561,7 @@
         <v>0</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P101" s="9"/>
     </row>
@@ -4573,7 +4573,7 @@
         <v>0</v>
       </c>
       <c r="O102" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P102" s="9"/>
     </row>
@@ -4585,7 +4585,7 @@
         <v>0</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P103" s="9"/>
     </row>
@@ -4597,19 +4597,19 @@
         <v>0</v>
       </c>
       <c r="O104" s="9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="P104" s="9"/>
     </row>
     <row r="105" spans="1:20" x14ac:dyDescent="0.25">
       <c r="M105" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="N105" s="9">
         <v>0</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P105" s="9"/>
     </row>
@@ -4621,7 +4621,7 @@
         <v>1</v>
       </c>
       <c r="O106" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P106" s="9" t="s">
         <v>78</v>
@@ -4641,7 +4641,7 @@
     </row>
     <row r="108" spans="1:20" x14ac:dyDescent="0.25">
       <c r="M108" s="9" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="N108" s="9">
         <v>0</v>
@@ -4650,7 +4650,7 @@
         <v>55</v>
       </c>
       <c r="P108" s="9" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="109" spans="1:20" x14ac:dyDescent="0.25">
@@ -4667,13 +4667,13 @@
     </row>
     <row r="110" spans="1:20" x14ac:dyDescent="0.25">
       <c r="M110" s="9" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="N110" s="9">
         <v>0</v>
       </c>
       <c r="O110" s="9" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="P110" s="9"/>
     </row>
@@ -4703,14 +4703,15 @@
         <v>74</v>
       </c>
       <c r="N113" s="10">
-        <v>364</v>
+        <f>46*10</f>
+        <v>460</v>
       </c>
       <c r="O113" s="10"/>
       <c r="P113" s="10" t="s">
-        <v>81</v>
+        <v>401</v>
       </c>
       <c r="Q113" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="114" spans="9:17" x14ac:dyDescent="0.25">
@@ -4721,12 +4722,13 @@
         <v>75</v>
       </c>
       <c r="N114" s="10">
-        <v>18.8</v>
+        <f>2.8*10</f>
+        <v>28</v>
       </c>
       <c r="O114" s="10"/>
       <c r="P114" s="10"/>
       <c r="Q114" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="115" spans="9:17" x14ac:dyDescent="0.25">
@@ -4742,7 +4744,7 @@
       <c r="O115" s="10"/>
       <c r="P115" s="10"/>
       <c r="Q115" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="116" spans="9:17" x14ac:dyDescent="0.25">
@@ -4753,7 +4755,7 @@
         <v>73</v>
       </c>
       <c r="N116" s="10">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="O116" s="10"/>
       <c r="P116" s="10"/>
@@ -4775,7 +4777,7 @@
       <c r="O117" s="10"/>
       <c r="P117" s="10"/>
       <c r="Q117" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="118" spans="9:17" x14ac:dyDescent="0.25">
@@ -4794,7 +4796,7 @@
       <c r="O118" s="10"/>
       <c r="P118" s="10"/>
       <c r="Q118" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="119" spans="9:17" x14ac:dyDescent="0.25">
@@ -4813,7 +4815,7 @@
       <c r="O119" s="10"/>
       <c r="P119" s="10"/>
       <c r="Q119" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="120" spans="9:17" x14ac:dyDescent="0.25">
@@ -4838,7 +4840,7 @@
         <v>80</v>
       </c>
       <c r="Q121" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="122" spans="9:17" x14ac:dyDescent="0.25">
@@ -4854,7 +4856,7 @@
       <c r="O122" s="10"/>
       <c r="P122" s="10"/>
       <c r="Q122" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="123" spans="9:17" x14ac:dyDescent="0.25">
@@ -4870,7 +4872,7 @@
       <c r="O123" s="10"/>
       <c r="P123" s="10"/>
       <c r="Q123" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="124" spans="9:17" x14ac:dyDescent="0.25">
@@ -4903,7 +4905,7 @@
       <c r="O125" s="10"/>
       <c r="P125" s="10"/>
       <c r="Q125" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="126" spans="9:17" x14ac:dyDescent="0.25">
@@ -4922,7 +4924,7 @@
       <c r="O126" s="10"/>
       <c r="P126" s="10"/>
       <c r="Q126" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="127" spans="9:17" x14ac:dyDescent="0.25">
@@ -4941,7 +4943,7 @@
       <c r="O127" s="10"/>
       <c r="P127" s="10"/>
       <c r="Q127" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="128" spans="9:17" x14ac:dyDescent="0.25">
@@ -4959,15 +4961,15 @@
         <v>74</v>
       </c>
       <c r="N129" s="10">
-        <f>46*10</f>
-        <v>460</v>
+        <f>107*4</f>
+        <v>428</v>
       </c>
       <c r="O129" s="10"/>
       <c r="P129" s="10" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="Q129" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="130" spans="9:17" x14ac:dyDescent="0.25">
@@ -4978,13 +4980,13 @@
         <v>75</v>
       </c>
       <c r="N130" s="10">
-        <f>2.8*10</f>
-        <v>28</v>
+        <f>6.3*4</f>
+        <v>25.2</v>
       </c>
       <c r="O130" s="10"/>
       <c r="P130" s="10"/>
       <c r="Q130" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="131" spans="9:17" x14ac:dyDescent="0.25">
@@ -5000,7 +5002,7 @@
       <c r="O131" s="10"/>
       <c r="P131" s="10"/>
       <c r="Q131" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="132" spans="9:17" x14ac:dyDescent="0.25">
@@ -5033,7 +5035,7 @@
       <c r="O133" s="10"/>
       <c r="P133" s="10"/>
       <c r="Q133" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="134" spans="9:17" x14ac:dyDescent="0.25">
@@ -5052,7 +5054,7 @@
       <c r="O134" s="10"/>
       <c r="P134" s="10"/>
       <c r="Q134" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="135" spans="9:17" x14ac:dyDescent="0.25">
@@ -5071,7 +5073,7 @@
       <c r="O135" s="10"/>
       <c r="P135" s="10"/>
       <c r="Q135" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="136" spans="9:17" x14ac:dyDescent="0.25">
@@ -5086,17 +5088,17 @@
         <v>64</v>
       </c>
       <c r="M137" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="N137" s="12">
         <v>5.0999999999999996</v>
       </c>
       <c r="O137" s="10"/>
       <c r="P137" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="Q137" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="138" spans="9:17" x14ac:dyDescent="0.25">
@@ -5104,17 +5106,17 @@
         <v>65</v>
       </c>
       <c r="M138" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="N138" s="12">
         <v>7.1</v>
       </c>
       <c r="O138" s="10"/>
       <c r="P138" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q138" s="4" t="s">
         <v>92</v>
-      </c>
-      <c r="Q138" s="4" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="139" spans="9:17" x14ac:dyDescent="0.25">
@@ -5136,10 +5138,10 @@
       </c>
       <c r="O140" s="10"/>
       <c r="P140" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q140" s="6" t="s">
         <v>85</v>
-      </c>
-      <c r="Q140" s="6" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="141" spans="9:17" x14ac:dyDescent="0.25">
@@ -5154,10 +5156,10 @@
       </c>
       <c r="O141" s="10"/>
       <c r="P141" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q141" s="4" t="s">
         <v>87</v>
-      </c>
-      <c r="Q141" s="4" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="142" spans="9:17" x14ac:dyDescent="0.25">
@@ -5175,15 +5177,15 @@
         <v>47</v>
       </c>
       <c r="Q142" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="143" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I143" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="M143" s="10" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="N143" s="12">
         <f>(3.11+4.67)/2</f>
@@ -5191,10 +5193,10 @@
       </c>
       <c r="O143" s="10"/>
       <c r="P143" s="6" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q143" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="144" spans="9:17" x14ac:dyDescent="0.25">
@@ -5209,10 +5211,10 @@
       </c>
       <c r="O144" s="10"/>
       <c r="P144" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q144" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="145" spans="2:17" x14ac:dyDescent="0.25">
@@ -5227,15 +5229,15 @@
       </c>
       <c r="O145" s="10"/>
       <c r="P145" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="Q145" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="146" spans="2:17" x14ac:dyDescent="0.25">
       <c r="I146" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M146" s="10" t="s">
         <v>53</v>
@@ -5245,15 +5247,15 @@
       </c>
       <c r="O146" s="10"/>
       <c r="P146" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q146" s="10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="147" spans="2:17" x14ac:dyDescent="0.25">
       <c r="I147" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M147" s="10" t="s">
         <v>53</v>
@@ -5263,15 +5265,15 @@
       </c>
       <c r="O147" s="10"/>
       <c r="P147" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q147" s="10" t="s">
         <v>101</v>
-      </c>
-      <c r="Q147" s="10" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="148" spans="2:17" x14ac:dyDescent="0.25">
       <c r="I148" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="M148" s="10" t="s">
         <v>53</v>
@@ -5281,10 +5283,10 @@
       </c>
       <c r="O148" s="10"/>
       <c r="P148" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Q148" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="149" spans="2:17" x14ac:dyDescent="0.25">
@@ -5299,10 +5301,10 @@
       </c>
       <c r="O149" s="10"/>
       <c r="P149" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="Q149" s="10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="150" spans="2:17" x14ac:dyDescent="0.25">
@@ -5317,15 +5319,15 @@
       </c>
       <c r="O150" s="10"/>
       <c r="P150" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="Q150" s="10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="151" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B151" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I151" t="s">
         <v>69</v>
@@ -5338,15 +5340,15 @@
       </c>
       <c r="O151" s="10"/>
       <c r="P151" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q151" s="4" t="s">
         <v>106</v>
-      </c>
-      <c r="Q151" s="4" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="152" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B152" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I152" t="s">
         <v>69</v>
@@ -5359,15 +5361,15 @@
       </c>
       <c r="O152" s="10"/>
       <c r="P152" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="Q152" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="153" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B153" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="I153" t="s">
         <v>69</v>
@@ -5379,15 +5381,15 @@
         <v>4.0531064740502947</v>
       </c>
       <c r="P153" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="Q153" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="154" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B154" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I154" t="s">
         <v>69</v>
@@ -5399,10 +5401,10 @@
         <v>4.3591310772039646</v>
       </c>
       <c r="P154" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q154" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="155" spans="2:17" x14ac:dyDescent="0.25">
@@ -5413,7 +5415,7 @@
     </row>
     <row r="156" spans="2:17" x14ac:dyDescent="0.25">
       <c r="I156" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M156" s="10" t="s">
         <v>53</v>
@@ -5423,15 +5425,15 @@
       </c>
       <c r="P156" s="6"/>
       <c r="Q156" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="157" spans="2:17" x14ac:dyDescent="0.25">
       <c r="I157" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K157" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M157" s="10" t="s">
         <v>53</v>
@@ -5441,15 +5443,15 @@
       </c>
       <c r="P157" s="6"/>
       <c r="Q157" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="158" spans="2:17" x14ac:dyDescent="0.25">
       <c r="I158" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K158" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="M158" s="10" t="s">
         <v>53</v>
@@ -5459,15 +5461,15 @@
       </c>
       <c r="P158" s="6"/>
       <c r="Q158" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="159" spans="2:17" x14ac:dyDescent="0.25">
       <c r="I159" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K159" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M159" s="10" t="s">
         <v>53</v>
@@ -5477,7 +5479,7 @@
       </c>
       <c r="P159" s="6"/>
       <c r="Q159" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="160" spans="2:17" x14ac:dyDescent="0.25">
@@ -5488,7 +5490,7 @@
     </row>
     <row r="161" spans="1:17" x14ac:dyDescent="0.25">
       <c r="I161" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M161" s="10" t="s">
         <v>54</v>
@@ -5500,36 +5502,36 @@
         <v>56</v>
       </c>
       <c r="P161" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Q161" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="162" spans="1:17" x14ac:dyDescent="0.25">
       <c r="I162" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="M162" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="N162" s="13">
         <f>3.07744775/0.85</f>
         <v>3.6205267647058825</v>
       </c>
       <c r="O162" t="s">
+        <v>327</v>
+      </c>
+      <c r="P162" s="6" t="s">
         <v>328</v>
       </c>
-      <c r="P162" s="6" t="s">
-        <v>329</v>
-      </c>
       <c r="Q162" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="163" spans="1:17" x14ac:dyDescent="0.25">
       <c r="I163" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="M163" s="10" t="s">
         <v>57</v>
@@ -5541,10 +5543,10 @@
         <v>58</v>
       </c>
       <c r="P163" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Q163" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="165" spans="1:17" x14ac:dyDescent="0.25">
@@ -5584,12 +5586,12 @@
         <v>48</v>
       </c>
       <c r="N167" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="169" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B169" s="1"/>
       <c r="C169" s="1"/>
@@ -5610,13 +5612,13 @@
     </row>
     <row r="171" spans="1:17" x14ac:dyDescent="0.25">
       <c r="M171" s="9" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="N171" s="9">
         <v>100</v>
       </c>
       <c r="O171" s="9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="P171" s="9" t="s">
         <v>52</v>
@@ -5624,39 +5626,39 @@
     </row>
     <row r="172" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H172" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="M172" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="N172">
         <v>88</v>
       </c>
       <c r="O172" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="P172" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="Q172" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="173" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H173" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="M173" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="N173">
         <v>90</v>
       </c>
       <c r="O173" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q173" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="174" spans="1:17" x14ac:dyDescent="0.25">
@@ -5665,19 +5667,19 @@
     <row r="175" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H175" s="6"/>
       <c r="M175" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="N175">
         <v>1.6E-2</v>
       </c>
       <c r="O175" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="P175" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="Q175" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="176" spans="1:17" x14ac:dyDescent="0.25">
@@ -5685,173 +5687,173 @@
     </row>
     <row r="177" spans="1:17" x14ac:dyDescent="0.25">
       <c r="M177" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="N177" s="13">
         <f>0.16*10.36*0.9</f>
         <v>1.4918400000000001</v>
       </c>
       <c r="O177" t="s">
+        <v>344</v>
+      </c>
+      <c r="P177" t="s">
         <v>345</v>
       </c>
-      <c r="P177" t="s">
+      <c r="Q177" t="s">
         <v>346</v>
-      </c>
-      <c r="Q177" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="180" spans="1:17" x14ac:dyDescent="0.25">
       <c r="M180" s="9" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="N180" s="9">
         <v>-99</v>
       </c>
       <c r="O180" s="9"/>
       <c r="P180" s="9" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="181" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C181" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="M181" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="N181">
         <v>17</v>
       </c>
       <c r="O181" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q181" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="182" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C182" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="M182" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="N182">
         <v>17</v>
       </c>
       <c r="O182" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q182" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="183" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C183" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="M183" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="N183">
         <v>17</v>
       </c>
       <c r="O183" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q183" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="184" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C184" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="M184" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="N184">
         <v>14</v>
       </c>
       <c r="O184" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q184" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="186" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C186" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="M186" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="N186">
         <v>14</v>
       </c>
       <c r="O186" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q186" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="187" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C187" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="M187" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="N187">
         <v>14</v>
       </c>
       <c r="O187" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q187" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="188" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C188" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="M188" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="N188">
         <v>14</v>
       </c>
       <c r="O188" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q188" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="189" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C189" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="M189" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="N189">
         <v>9</v>
       </c>
       <c r="O189" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q189" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="191" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
@@ -5872,13 +5874,13 @@
     </row>
     <row r="195" spans="1:17" x14ac:dyDescent="0.25">
       <c r="M195" s="9" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="N195" s="9">
         <v>0</v>
       </c>
       <c r="O195" s="9" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="P195" s="9" t="s">
         <v>52</v>
@@ -5886,147 +5888,147 @@
     </row>
     <row r="196" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B196" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="M196" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="N196">
         <v>302</v>
       </c>
       <c r="O196" t="s">
+        <v>156</v>
+      </c>
+      <c r="P196" t="s">
         <v>157</v>
       </c>
-      <c r="P196" t="s">
-        <v>158</v>
-      </c>
       <c r="Q196" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="197" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B197" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="M197" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="N197">
         <v>197</v>
       </c>
       <c r="O197" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="P197" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="Q197" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="198" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B198" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="M198" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="N198">
         <v>216</v>
       </c>
       <c r="O198" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="P198" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Q198" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="199" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B199" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="M199" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="N199">
         <v>216</v>
       </c>
       <c r="O199" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="P199" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Q199" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="200" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B200" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="M200" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="N200">
         <v>216</v>
       </c>
       <c r="O200" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="P200" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Q200" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="201" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B201" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="M201" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="N201">
         <v>216</v>
       </c>
       <c r="O201" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="P201" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Q201" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="202" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B202" t="s">
+        <v>154</v>
+      </c>
+      <c r="M202" t="s">
         <v>155</v>
-      </c>
-      <c r="M202" t="s">
-        <v>156</v>
       </c>
       <c r="N202">
         <v>216</v>
       </c>
       <c r="O202" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="P202" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Q202" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="204" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B204" s="1"/>
       <c r="C204" s="1"/>
@@ -6047,13 +6049,13 @@
     </row>
     <row r="205" spans="1:17" x14ac:dyDescent="0.25">
       <c r="M205" s="9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="N205" s="9">
         <v>0</v>
       </c>
       <c r="O205" s="9" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="P205" s="9" t="s">
         <v>52</v>
@@ -6061,13 +6063,13 @@
     </row>
     <row r="206" spans="1:17" x14ac:dyDescent="0.25">
       <c r="M206" s="9" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="N206" s="9">
         <v>0</v>
       </c>
       <c r="O206" s="9" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="P206" s="9" t="s">
         <v>52</v>
@@ -6075,13 +6077,13 @@
     </row>
     <row r="207" spans="1:17" x14ac:dyDescent="0.25">
       <c r="M207" s="9" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="N207" s="9">
         <v>0</v>
       </c>
       <c r="O207" s="9" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="P207" s="9" t="s">
         <v>52</v>
@@ -6089,143 +6091,143 @@
     </row>
     <row r="209" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D209" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E209" t="s">
+        <v>197</v>
+      </c>
+      <c r="F209" t="s">
         <v>198</v>
       </c>
-      <c r="F209" t="s">
-        <v>199</v>
-      </c>
       <c r="G209" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="M209" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="N209" s="25">
         <f>'energy stables'!E24</f>
         <v>3.5302245250431775E-2</v>
       </c>
       <c r="O209" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="P209" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="Q209" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="210" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D210" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E210" t="s">
+        <v>197</v>
+      </c>
+      <c r="F210" t="s">
         <v>198</v>
       </c>
-      <c r="F210" t="s">
-        <v>199</v>
-      </c>
       <c r="M210" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="N210" s="24">
         <f>'energy stables'!D26</f>
         <v>308.33833333333342</v>
       </c>
       <c r="O210" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="P210" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q210" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="211" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D211" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E211" t="s">
+        <v>197</v>
+      </c>
+      <c r="F211" t="s">
         <v>198</v>
       </c>
-      <c r="F211" t="s">
-        <v>199</v>
-      </c>
       <c r="G211" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="M211" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="N211" s="25">
         <f>'energy stables'!E27</f>
         <v>4.1036269430051814E-2</v>
       </c>
       <c r="O211" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="Q211" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="213" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D213" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="M213" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="N213" s="24">
         <f>'energy stables'!D29</f>
         <v>170.33333333333331</v>
       </c>
       <c r="O213" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="P213" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q213" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="214" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D214" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="M214" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="N214" s="24">
         <f>'energy stables'!D31</f>
         <v>332.32333333333338</v>
       </c>
       <c r="O214" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="P214" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="Q214" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="215" spans="1:17" x14ac:dyDescent="0.25">
@@ -6233,330 +6235,330 @@
     </row>
     <row r="216" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D216" t="s">
+        <v>228</v>
+      </c>
+      <c r="E216" t="s">
         <v>229</v>
       </c>
-      <c r="E216" t="s">
-        <v>230</v>
-      </c>
       <c r="F216" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="M216" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="N216" s="25">
         <f>(290+1078)/100000</f>
         <v>1.3679999999999999E-2</v>
       </c>
       <c r="O216" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="P216" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="Q216" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="217" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D217" t="s">
+        <v>228</v>
+      </c>
+      <c r="E217" t="s">
         <v>229</v>
       </c>
-      <c r="E217" t="s">
-        <v>230</v>
-      </c>
       <c r="F217" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="M217" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="N217" s="25">
         <f>77000/100000</f>
         <v>0.77</v>
       </c>
       <c r="O217" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="Q217" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="218" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D218" t="s">
+        <v>228</v>
+      </c>
+      <c r="E218" t="s">
         <v>229</v>
       </c>
-      <c r="E218" t="s">
-        <v>230</v>
-      </c>
       <c r="F218" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="M218" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="N218" s="25">
         <f>(3340+9790)/100000</f>
         <v>0.1313</v>
       </c>
       <c r="O218" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="P218" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="Q218" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="220" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D220" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F220" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="M220" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="N220">
         <f>'energy stables'!D49</f>
         <v>3.5</v>
       </c>
       <c r="O220" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="Q220" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="221" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D221" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F221" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="M221" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="N221">
         <f>'energy stables'!D50</f>
         <v>12.5</v>
       </c>
       <c r="O221" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="Q221" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="222" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D222" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F222" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="M222" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="N222">
         <f>'energy stables'!D51</f>
         <v>34</v>
       </c>
       <c r="O222" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="Q222" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="223" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D223" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F223" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="M223" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="N223">
         <f>'energy stables'!D53</f>
         <v>0.04</v>
       </c>
       <c r="O223" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="Q223" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="224" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D224" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F224" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="M224" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="N224" s="13">
         <f>'energy stables'!D54</f>
         <v>0.1</v>
       </c>
       <c r="O224" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="Q224" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="225" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D225" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F225" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="M225" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="N225" s="13">
         <f>'energy stables'!D55</f>
         <v>0.26</v>
       </c>
       <c r="O225" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="Q225" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="227" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D227" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E227" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="M227" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="N227" s="13">
         <f>'energy stables'!D65</f>
         <v>0.14449999999999999</v>
       </c>
       <c r="O227" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="P227" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="Q227" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="228" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D228" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E228" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="M228" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="N228" s="13">
         <f>'energy stables'!D67</f>
         <v>3.9295</v>
       </c>
       <c r="O228" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="P228" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="Q228" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="229" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D229" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E229" t="s">
+        <v>354</v>
+      </c>
+      <c r="F229" t="s">
         <v>355</v>
       </c>
-      <c r="F229" t="s">
-        <v>356</v>
-      </c>
       <c r="M229" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="N229">
         <v>0</v>
       </c>
       <c r="O229" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="P229" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="230" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D230" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E230" t="s">
+        <v>354</v>
+      </c>
+      <c r="F230" t="s">
         <v>355</v>
       </c>
-      <c r="F230" t="s">
-        <v>356</v>
-      </c>
       <c r="M230" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="N230">
         <v>0</v>
@@ -6567,114 +6569,114 @@
     </row>
     <row r="231" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D231" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E231" t="s">
+        <v>354</v>
+      </c>
+      <c r="F231" t="s">
         <v>355</v>
       </c>
-      <c r="F231" t="s">
-        <v>356</v>
-      </c>
       <c r="M231" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="N231" s="13">
         <f>4.7*(1/3.6)</f>
         <v>1.3055555555555556</v>
       </c>
       <c r="O231" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="P231" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="Q231" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="233" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D233" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="M233" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="N233" s="24">
         <f>0.05*1000*(1/3.6)</f>
         <v>13.888888888888889</v>
       </c>
       <c r="O233" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="P233" t="s">
+        <v>390</v>
+      </c>
+      <c r="Q233" t="s">
         <v>391</v>
-      </c>
-      <c r="Q233" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="234" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D234" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="M234" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="N234" s="24">
         <f>0.05*1000*(1/3.6)</f>
         <v>13.888888888888889</v>
       </c>
       <c r="O234" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="P234" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="Q234" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="235" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D235" t="s">
+        <v>387</v>
+      </c>
+      <c r="F235" t="s">
         <v>388</v>
       </c>
-      <c r="F235" t="s">
-        <v>389</v>
-      </c>
       <c r="M235" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="N235">
         <v>0</v>
       </c>
       <c r="P235" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="236" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D236" t="s">
+        <v>387</v>
+      </c>
+      <c r="F236" t="s">
         <v>388</v>
       </c>
-      <c r="F236" t="s">
-        <v>389</v>
-      </c>
       <c r="M236" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="N236">
         <v>0</v>
@@ -6700,7 +6702,7 @@
   <sheetData>
     <row r="3" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B3" s="53" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C3" s="54"/>
       <c r="D3" s="54"/>
@@ -6720,37 +6722,37 @@
     </row>
     <row r="4" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B4" s="51" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B5" s="27"/>
       <c r="C5" s="30"/>
       <c r="D5" s="46" t="s">
+        <v>200</v>
+      </c>
+      <c r="E5" s="28" t="s">
+        <v>198</v>
+      </c>
+      <c r="F5" s="30" t="s">
+        <v>217</v>
+      </c>
+      <c r="G5" s="29" t="s">
         <v>201</v>
       </c>
-      <c r="E5" s="28" t="s">
-        <v>199</v>
-      </c>
-      <c r="F5" s="30" t="s">
-        <v>218</v>
-      </c>
-      <c r="G5" s="29" t="s">
-        <v>202</v>
-      </c>
       <c r="H5" s="28" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I5" s="30" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="6" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B6" s="31" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C6" s="44" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D6" s="31">
         <v>150</v>
@@ -6765,10 +6767,10 @@
     </row>
     <row r="7" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B7" s="31" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C7" s="44" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D7" s="31">
         <v>150</v>
@@ -6783,10 +6785,10 @@
     </row>
     <row r="8" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B8" s="31" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C8" s="44" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D8" s="31">
         <v>10500</v>
@@ -6811,10 +6813,10 @@
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B10" s="31" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C10" s="44" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D10" s="31">
         <v>652</v>
@@ -6839,15 +6841,15 @@
         <v>123.33333333333333</v>
       </c>
       <c r="J10" s="26" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B11" s="31" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C11" s="44" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D11" s="31">
         <v>3</v>
@@ -6875,10 +6877,10 @@
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B12" s="31" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C12" s="44" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D12" s="31">
         <v>40</v>
@@ -6903,15 +6905,15 @@
         <v>10.333333333333332</v>
       </c>
       <c r="J12" s="26" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B13" s="31" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C13" s="44" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D13" s="31">
         <v>216</v>
@@ -6939,10 +6941,10 @@
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B14" s="31" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C14" s="44" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D14" s="31">
         <v>386</v>
@@ -6965,15 +6967,15 @@
         <v>0</v>
       </c>
       <c r="J14" s="26" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="15" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B15" s="31" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C15" s="44" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D15" s="31">
         <v>216</v>
@@ -7010,10 +7012,10 @@
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B17" s="36" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C17" s="44" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D17" s="36">
         <f>SUM(D10:D15)</f>
@@ -7042,10 +7044,10 @@
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B18" s="31" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C18" s="44" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D18" s="31">
         <v>868</v>
@@ -7100,10 +7102,10 @@
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B20" s="42" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C20" s="45" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D20" s="42">
         <v>23</v>
@@ -7118,25 +7120,25 @@
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B22" s="71" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B23" s="79"/>
       <c r="C23" s="80"/>
       <c r="D23" s="81" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E23" s="82" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B24" s="64" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C24" s="65" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D24" s="72">
         <v>0</v>
@@ -7148,10 +7150,10 @@
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B25" s="64" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C25" s="65" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D25" s="72">
         <v>0</v>
@@ -7162,10 +7164,10 @@
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B26" s="64" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C26" s="65" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D26" s="75">
         <f>SUM(E11:E13,E15,H11:H13,H15)/2</f>
@@ -7177,10 +7179,10 @@
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B27" s="64" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C27" s="65" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D27" s="72">
         <v>0</v>
@@ -7198,10 +7200,10 @@
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B29" s="64" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C29" s="65" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D29" s="75">
         <f>SUM(F10,I10)/2</f>
@@ -7213,10 +7215,10 @@
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B30" s="64" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C30" s="65" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D30" s="72">
         <v>0</v>
@@ -7227,10 +7229,10 @@
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B31" s="64" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C31" s="65" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D31" s="75">
         <f>SUM(F11:F13,F15,I11:I13,I15)</f>
@@ -7242,10 +7244,10 @@
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B32" s="66" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C32" s="67" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D32" s="76">
         <v>0</v>
@@ -7256,7 +7258,7 @@
     </row>
     <row r="34" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B34" s="53" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C34" s="54"/>
       <c r="D34" s="54"/>
@@ -7276,69 +7278,69 @@
     </row>
     <row r="35" spans="2:19" x14ac:dyDescent="0.25">
       <c r="J35" s="51" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="36" spans="2:19" x14ac:dyDescent="0.25">
       <c r="J36" s="46" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="K36" s="28"/>
       <c r="L36" s="28"/>
       <c r="M36" s="29" t="s">
+        <v>296</v>
+      </c>
+      <c r="N36" s="29" t="s">
         <v>297</v>
       </c>
-      <c r="N36" s="29" t="s">
+      <c r="O36" s="29" t="s">
         <v>298</v>
       </c>
-      <c r="O36" s="29" t="s">
+      <c r="P36" s="50" t="s">
         <v>299</v>
       </c>
-      <c r="P36" s="50" t="s">
-        <v>300</v>
-      </c>
       <c r="Q36" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="37" spans="2:19" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="51" t="s">
+        <v>246</v>
+      </c>
+      <c r="J37" s="42" t="s">
         <v>247</v>
-      </c>
-      <c r="J37" s="42" t="s">
-        <v>248</v>
       </c>
       <c r="K37" s="14"/>
       <c r="L37" s="14"/>
       <c r="M37" s="59" t="s">
+        <v>292</v>
+      </c>
+      <c r="N37" s="59" t="s">
         <v>293</v>
       </c>
-      <c r="N37" s="59" t="s">
+      <c r="O37" s="59" t="s">
         <v>294</v>
       </c>
-      <c r="O37" s="59" t="s">
+      <c r="P37" s="60" t="s">
         <v>295</v>
       </c>
-      <c r="P37" s="60" t="s">
-        <v>296</v>
-      </c>
       <c r="Q37" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="38" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B38" s="46" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C38" s="29"/>
       <c r="D38" s="29" t="s">
+        <v>240</v>
+      </c>
+      <c r="E38" s="50" t="s">
         <v>241</v>
       </c>
-      <c r="E38" s="50" t="s">
-        <v>242</v>
-      </c>
       <c r="J38" s="31" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -7355,14 +7357,14 @@
         <v>242</v>
       </c>
       <c r="Q38" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R38" s="58"/>
       <c r="S38" s="58"/>
     </row>
     <row r="39" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="31" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C39" s="4"/>
       <c r="D39" s="4">
@@ -7372,7 +7374,7 @@
         <v>0.4</v>
       </c>
       <c r="J39" s="31" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -7386,17 +7388,17 @@
         <v>9.6</v>
       </c>
       <c r="P39" s="32" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="Q39" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R39" s="58"/>
       <c r="S39" s="58"/>
     </row>
     <row r="40" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B40" s="31" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C40" s="4"/>
       <c r="D40" s="4">
@@ -7406,7 +7408,7 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="J40" s="31" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -7423,14 +7425,14 @@
         <v>43.2</v>
       </c>
       <c r="Q40" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R40" s="58"/>
       <c r="S40" s="58"/>
     </row>
     <row r="41" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B41" s="31" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C41" s="4"/>
       <c r="D41" s="4">
@@ -7440,7 +7442,7 @@
         <v>0.06</v>
       </c>
       <c r="J41" s="31" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -7457,14 +7459,14 @@
         <v>340</v>
       </c>
       <c r="Q41" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R41" s="58"/>
       <c r="S41" s="58"/>
     </row>
     <row r="42" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B42" s="31" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C42" s="4"/>
       <c r="D42" s="4">
@@ -7474,7 +7476,7 @@
         <v>0.04</v>
       </c>
       <c r="J42" s="31" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -7488,17 +7490,17 @@
         <v>4.2</v>
       </c>
       <c r="P42" s="32" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="Q42" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R42" s="58"/>
       <c r="S42" s="58"/>
     </row>
     <row r="43" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B43" s="42" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C43" s="14"/>
       <c r="D43" s="14">
@@ -7530,41 +7532,41 @@
     </row>
     <row r="44" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C44" s="68" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D44" s="69">
         <f>D39*33+E39*26</f>
         <v>1660.4</v>
       </c>
       <c r="E44" s="70" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="J44" s="31" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
       <c r="M44" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="N44" s="4">
         <v>4</v>
       </c>
       <c r="O44" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="P44" s="32" t="s">
         <v>264</v>
       </c>
-      <c r="P44" s="32" t="s">
-        <v>265</v>
-      </c>
       <c r="Q44" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R44" s="58"/>
       <c r="S44" s="58"/>
     </row>
     <row r="45" spans="2:19" x14ac:dyDescent="0.25">
       <c r="J45" s="31" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -7578,37 +7580,37 @@
         <v>0.7</v>
       </c>
       <c r="P45" s="32" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="Q45" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R45" s="58"/>
       <c r="S45" s="58"/>
     </row>
     <row r="46" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B46" s="71" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="J46" s="31" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
       <c r="M46" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="N46" s="4">
         <v>11</v>
       </c>
       <c r="O46" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P46" s="32" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="Q46" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R46" s="58"/>
       <c r="S46" s="58"/>
@@ -7617,16 +7619,16 @@
       <c r="B47" s="27"/>
       <c r="C47" s="28"/>
       <c r="D47" s="86" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E47" s="28" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F47" s="28"/>
       <c r="G47" s="28"/>
       <c r="H47" s="30"/>
       <c r="J47" s="31" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -7637,13 +7639,13 @@
         <v>15</v>
       </c>
       <c r="O47" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="P47" s="32" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="Q47" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R47" s="58"/>
       <c r="S47" s="58"/>
@@ -7652,22 +7654,22 @@
       <c r="B48" s="42"/>
       <c r="C48" s="14"/>
       <c r="D48" s="87" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E48" s="14" t="s">
         <v>26</v>
       </c>
       <c r="F48" s="83" t="s">
+        <v>144</v>
+      </c>
+      <c r="G48" s="83" t="s">
         <v>145</v>
       </c>
-      <c r="G48" s="83" t="s">
-        <v>146</v>
-      </c>
       <c r="H48" s="84" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J48" s="31" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -7681,20 +7683,20 @@
         <v>1</v>
       </c>
       <c r="P48" s="32" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="Q48" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R48" s="58"/>
       <c r="S48" s="58"/>
     </row>
     <row r="49" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B49" s="85" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C49" s="28" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D49" s="88">
         <f>D42</f>
@@ -7713,7 +7715,7 @@
         <v>0</v>
       </c>
       <c r="J49" s="46" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="K49" s="29"/>
       <c r="L49" s="29"/>
@@ -7730,17 +7732,17 @@
         <v>1252</v>
       </c>
       <c r="Q49" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R49" s="58"/>
       <c r="S49" s="58"/>
     </row>
     <row r="50" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B50" s="31" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D50" s="88">
         <f>D39*0.25</f>
@@ -7762,7 +7764,7 @@
         <v>20</v>
       </c>
       <c r="J50" s="31" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -7783,10 +7785,10 @@
     </row>
     <row r="51" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B51" s="31" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D51" s="89">
         <f>D39-D49-D50</f>
@@ -7805,7 +7807,7 @@
         <v>100</v>
       </c>
       <c r="J51" s="61" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="K51" s="63"/>
       <c r="L51" s="63"/>
@@ -7826,7 +7828,7 @@
         <v>34</v>
       </c>
       <c r="Q51" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R51" s="58"/>
       <c r="S51" s="58"/>
@@ -7840,7 +7842,7 @@
       <c r="G52" s="72"/>
       <c r="H52" s="74"/>
       <c r="J52" s="55" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K52" s="56"/>
       <c r="L52" s="56"/>
@@ -7851,21 +7853,21 @@
         <v>38</v>
       </c>
       <c r="O52" s="56" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P52" s="57" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="Q52" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="53" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B53" s="64" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D53" s="88">
         <f>E42</f>
@@ -7884,32 +7886,32 @@
         <v>0</v>
       </c>
       <c r="J53" s="31" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
       <c r="M53" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="N53" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="O53" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P53" s="32" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="Q53" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="54" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B54" s="31" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D54" s="90">
         <f>E39*0.25</f>
@@ -7931,32 +7933,32 @@
         <v>20.000000000000018</v>
       </c>
       <c r="J54" s="31" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>
       <c r="M54" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="N54" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="O54" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="P54" s="32" t="s">
+        <v>279</v>
+      </c>
+      <c r="Q54" t="s">
         <v>305</v>
-      </c>
-      <c r="O54" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="P54" s="32" t="s">
-        <v>280</v>
-      </c>
-      <c r="Q54" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="55" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B55" s="42" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C55" s="14" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D55" s="91">
         <f>E39-D53-D54</f>
@@ -7975,27 +7977,27 @@
         <v>100</v>
       </c>
       <c r="J55" s="31" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="K55" s="4"/>
       <c r="L55" s="4"/>
       <c r="M55" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="N55" s="4"/>
       <c r="O55" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="P55" s="32" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="Q55" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="56" spans="2:19" x14ac:dyDescent="0.25">
       <c r="J56" s="42" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="K56" s="14"/>
       <c r="L56" s="14"/>
@@ -8014,7 +8016,7 @@
     </row>
     <row r="58" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B58" s="53" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C58" s="52"/>
       <c r="D58" s="52"/>
@@ -8034,47 +8036,47 @@
     </row>
     <row r="59" spans="2:19" x14ac:dyDescent="0.25">
       <c r="J59" s="51" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="60" spans="2:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J60" s="27" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="K60" s="28"/>
       <c r="L60" s="28"/>
       <c r="M60" s="103" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="N60" s="103"/>
       <c r="O60" s="103" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="P60" s="104"/>
       <c r="Q60" s="4"/>
     </row>
     <row r="61" spans="2:19" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J61" s="100" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="K61" s="14"/>
       <c r="L61" s="14"/>
       <c r="M61" s="101" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N61" s="101"/>
       <c r="O61" s="101" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="P61" s="102"/>
       <c r="Q61" s="4"/>
     </row>
     <row r="62" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B62" s="71" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="J62" s="27" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="K62" s="28"/>
       <c r="L62" s="28"/>
@@ -8082,13 +8084,13 @@
         <v>130</v>
       </c>
       <c r="N62" s="96" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="O62" s="28">
         <v>106</v>
       </c>
       <c r="P62" s="97" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="Q62" s="4"/>
     </row>
@@ -8096,16 +8098,16 @@
       <c r="B63" s="27"/>
       <c r="C63" s="28"/>
       <c r="D63" s="86" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E63" s="28" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F63" s="28"/>
       <c r="G63" s="28"/>
       <c r="H63" s="30"/>
       <c r="J63" s="31" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="K63" s="4"/>
       <c r="L63" s="4"/>
@@ -8123,22 +8125,22 @@
       <c r="B64" s="42"/>
       <c r="C64" s="14"/>
       <c r="D64" s="87" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E64" s="14" t="s">
         <v>26</v>
       </c>
       <c r="F64" s="83" t="s">
+        <v>144</v>
+      </c>
+      <c r="G64" s="83" t="s">
         <v>145</v>
       </c>
-      <c r="G64" s="83" t="s">
-        <v>146</v>
-      </c>
       <c r="H64" s="84" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J64" s="31" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="K64" s="4"/>
       <c r="L64" s="4"/>
@@ -8154,7 +8156,7 @@
     </row>
     <row r="65" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B65" s="85" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C65" s="28"/>
       <c r="D65" s="90">
@@ -8174,7 +8176,7 @@
         <v>90</v>
       </c>
       <c r="J65" s="31" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="K65" s="4"/>
       <c r="L65" s="4"/>
@@ -8190,7 +8192,7 @@
     </row>
     <row r="66" spans="2:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B66" s="31" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C66" s="4"/>
       <c r="D66" s="88">
@@ -8201,23 +8203,23 @@
       <c r="G66" s="75"/>
       <c r="H66" s="78"/>
       <c r="J66" s="94" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="K66" s="95"/>
       <c r="L66" s="95"/>
       <c r="M66" s="95" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="N66" s="95"/>
       <c r="O66" s="95" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="P66" s="44"/>
       <c r="Q66" s="4"/>
     </row>
     <row r="67" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B67" s="42" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C67" s="14"/>
       <c r="D67" s="91">
@@ -8237,7 +8239,7 @@
         <v>100</v>
       </c>
       <c r="J67" s="31" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="K67" s="4"/>
       <c r="L67" s="4"/>
@@ -8253,7 +8255,7 @@
     </row>
     <row r="68" spans="2:17" x14ac:dyDescent="0.25">
       <c r="J68" s="31" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="K68" s="4"/>
       <c r="L68" s="4"/>
@@ -8269,12 +8271,12 @@
     </row>
     <row r="69" spans="2:17" x14ac:dyDescent="0.25">
       <c r="J69" s="31" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="K69" s="4"/>
       <c r="L69" s="4"/>
       <c r="M69" s="4" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="N69" s="4"/>
       <c r="O69" s="4">
@@ -8285,12 +8287,12 @@
     </row>
     <row r="70" spans="2:17" x14ac:dyDescent="0.25">
       <c r="J70" s="31" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="K70" s="4"/>
       <c r="L70" s="4"/>
       <c r="M70" s="4" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="N70" s="4"/>
       <c r="O70" s="4">
@@ -8301,7 +8303,7 @@
     </row>
     <row r="71" spans="2:17" x14ac:dyDescent="0.25">
       <c r="J71" s="31" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="K71" s="4"/>
       <c r="L71" s="4"/>
@@ -8317,7 +8319,7 @@
     </row>
     <row r="72" spans="2:17" x14ac:dyDescent="0.25">
       <c r="J72" s="98" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="K72" s="93"/>
       <c r="L72" s="93"/>
@@ -8333,28 +8335,28 @@
     </row>
     <row r="73" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J73" s="55" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="K73" s="56"/>
       <c r="L73" s="56"/>
       <c r="M73" s="56" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="N73" s="56"/>
       <c r="O73" s="56" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="P73" s="57"/>
       <c r="Q73" s="4"/>
     </row>
     <row r="74" spans="2:17" x14ac:dyDescent="0.25">
       <c r="J74" s="31" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="K74" s="4"/>
       <c r="L74" s="4"/>
       <c r="M74" s="4" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="N74" s="4"/>
       <c r="O74" s="4">
@@ -8365,7 +8367,7 @@
     </row>
     <row r="75" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J75" s="55" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="K75" s="56"/>
       <c r="L75" s="56"/>
@@ -8402,7 +8404,7 @@
   <sheetData>
     <row r="3" spans="5:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F3">
         <v>90</v>
@@ -8419,7 +8421,7 @@
     </row>
     <row r="4" spans="5:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F4">
         <v>654</v>
@@ -8428,15 +8430,15 @@
         <v>80</v>
       </c>
       <c r="H4" t="s">
+        <v>253</v>
+      </c>
+      <c r="I4" t="s">
         <v>254</v>
-      </c>
-      <c r="I4" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="5" spans="5:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E5" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F5">
         <v>11</v>
@@ -8445,66 +8447,66 @@
         <v>12</v>
       </c>
       <c r="H5" t="s">
+        <v>256</v>
+      </c>
+      <c r="I5" t="s">
         <v>257</v>
-      </c>
-      <c r="I5" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="6" spans="5:20" x14ac:dyDescent="0.25">
       <c r="E6" t="s">
+        <v>285</v>
+      </c>
+      <c r="F6" t="s">
         <v>286</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>287</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>288</v>
       </c>
-      <c r="H6" t="s">
+      <c r="I6" t="s">
         <v>289</v>
-      </c>
-      <c r="I6" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="7" spans="5:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E7" t="s">
+        <v>248</v>
+      </c>
+      <c r="G7" t="s">
+        <v>258</v>
+      </c>
+      <c r="I7" t="s">
+        <v>259</v>
+      </c>
+      <c r="O7" t="s">
+        <v>260</v>
+      </c>
+      <c r="S7" t="s">
         <v>249</v>
-      </c>
-      <c r="G7" t="s">
-        <v>259</v>
-      </c>
-      <c r="I7" t="s">
-        <v>260</v>
-      </c>
-      <c r="O7" t="s">
-        <v>261</v>
-      </c>
-      <c r="S7" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="8" spans="5:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E8" t="s">
+        <v>261</v>
+      </c>
+      <c r="H8" t="s">
         <v>262</v>
-      </c>
-      <c r="H8" t="s">
-        <v>263</v>
       </c>
       <c r="K8">
         <v>4</v>
       </c>
       <c r="P8" t="s">
+        <v>263</v>
+      </c>
+      <c r="T8" t="s">
         <v>264</v>
-      </c>
-      <c r="T8" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="9" spans="5:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H9">
         <v>79</v>
@@ -8513,32 +8515,32 @@
         <v>7</v>
       </c>
       <c r="P9" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="T9" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="10" spans="5:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E10" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K10">
         <v>11</v>
       </c>
       <c r="P10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T10" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="11" spans="5:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E11" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H11">
         <v>38</v>
@@ -8547,15 +8549,15 @@
         <v>15</v>
       </c>
       <c r="P11" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="T11" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="12" spans="5:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E12" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H12">
         <v>164</v>
@@ -8564,15 +8566,15 @@
         <v>66</v>
       </c>
       <c r="P12" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="T12" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="13" spans="5:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E13" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H13">
         <v>2433</v>
@@ -8581,7 +8583,7 @@
         <v>689</v>
       </c>
       <c r="P13" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="T13">
         <v>1252</v>
@@ -8589,7 +8591,7 @@
     </row>
     <row r="14" spans="5:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E14" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H14">
         <v>1441</v>
@@ -8598,7 +8600,7 @@
         <v>689</v>
       </c>
       <c r="P14" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="T14">
         <v>1218</v>
@@ -8606,47 +8608,47 @@
     </row>
     <row r="15" spans="5:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E15" t="s">
+        <v>275</v>
+      </c>
+      <c r="L15" t="s">
         <v>276</v>
       </c>
-      <c r="L15" t="s">
+      <c r="Q15" t="s">
         <v>277</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="16" spans="5:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E16" t="s">
+        <v>278</v>
+      </c>
+      <c r="H16" t="s">
         <v>279</v>
       </c>
-      <c r="H16" t="s">
-        <v>280</v>
-      </c>
       <c r="K16" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="P16" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T16" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="17" spans="5:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E17" t="s">
+        <v>280</v>
+      </c>
+      <c r="H17" t="s">
         <v>281</v>
       </c>
-      <c r="H17" t="s">
+      <c r="K17" t="s">
         <v>282</v>
       </c>
-      <c r="K17" t="s">
+      <c r="P17" t="s">
         <v>283</v>
       </c>
-      <c r="P17" t="s">
+      <c r="T17" t="s">
         <v>284</v>
-      </c>
-      <c r="T17" t="s">
-        <v>285</v>
       </c>
     </row>
   </sheetData>
@@ -8665,47 +8667,47 @@
   <sheetData>
     <row r="3" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F3" s="49" t="s">
+        <v>296</v>
+      </c>
+      <c r="G3" s="49" t="s">
         <v>297</v>
       </c>
-      <c r="G3" s="49" t="s">
+      <c r="H3" s="49" t="s">
         <v>298</v>
       </c>
-      <c r="H3" s="49" t="s">
+      <c r="I3" s="49" t="s">
         <v>299</v>
       </c>
-      <c r="I3" s="49" t="s">
-        <v>300</v>
-      </c>
       <c r="J3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="4" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F4" t="s">
+        <v>292</v>
+      </c>
+      <c r="G4" t="s">
         <v>293</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>294</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>295</v>
       </c>
-      <c r="I4" t="s">
-        <v>296</v>
-      </c>
       <c r="J4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="5" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F5">
         <v>90</v>
@@ -8720,12 +8722,12 @@
         <v>242</v>
       </c>
       <c r="J5" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="6" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F6">
         <v>654</v>
@@ -8737,15 +8739,15 @@
         <v>9.6</v>
       </c>
       <c r="I6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="J6" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="7" spans="3:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F7">
         <v>11</v>
@@ -8760,12 +8762,12 @@
         <v>43.2</v>
       </c>
       <c r="J7" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="8" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F8">
         <v>244</v>
@@ -8780,12 +8782,12 @@
         <v>340</v>
       </c>
       <c r="J8" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="9" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F9">
         <v>992</v>
@@ -8797,35 +8799,35 @@
         <v>4.2</v>
       </c>
       <c r="I9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="J9" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10" spans="3:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
+        <v>261</v>
+      </c>
+      <c r="F10" t="s">
         <v>262</v>
-      </c>
-      <c r="F10" t="s">
-        <v>263</v>
       </c>
       <c r="G10">
         <v>4</v>
       </c>
       <c r="H10" t="s">
+        <v>263</v>
+      </c>
+      <c r="I10" t="s">
         <v>264</v>
       </c>
-      <c r="I10" t="s">
-        <v>265</v>
-      </c>
       <c r="J10" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="11" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F11">
         <v>79</v>
@@ -8837,35 +8839,35 @@
         <v>0.7</v>
       </c>
       <c r="I11" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="J11" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="12" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G12">
         <v>11</v>
       </c>
       <c r="H12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I12" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="J12" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="13" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F13">
         <v>38</v>
@@ -8874,18 +8876,18 @@
         <v>15</v>
       </c>
       <c r="H13" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="I13" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="J13" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="14" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F14">
         <v>164</v>
@@ -8897,15 +8899,15 @@
         <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="J14" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="15" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F15">
         <v>2433</v>
@@ -8920,12 +8922,12 @@
         <v>1252</v>
       </c>
       <c r="J15" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="16" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C16" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F16">
         <v>1441</v>
@@ -8940,12 +8942,12 @@
         <v>1218</v>
       </c>
       <c r="J16" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="17" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C17" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F17">
         <v>23</v>
@@ -8954,75 +8956,75 @@
         <v>38</v>
       </c>
       <c r="H17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I17" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="J17" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="18" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C18" t="s">
+        <v>278</v>
+      </c>
+      <c r="F18" t="s">
         <v>279</v>
       </c>
-      <c r="F18" t="s">
-        <v>280</v>
-      </c>
       <c r="G18" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I18" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J18" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="19" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C19" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F19" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G19" t="s">
+        <v>304</v>
+      </c>
+      <c r="H19" t="s">
+        <v>83</v>
+      </c>
+      <c r="I19" t="s">
+        <v>279</v>
+      </c>
+      <c r="J19" t="s">
         <v>305</v>
-      </c>
-      <c r="H19" t="s">
-        <v>84</v>
-      </c>
-      <c r="I19" t="s">
-        <v>280</v>
-      </c>
-      <c r="J19" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="20" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C20" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F20" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H20" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="I20" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J20" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="21" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C21" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F21">
         <v>1998</v>
@@ -9037,7 +9039,7 @@
         <v>2008</v>
       </c>
       <c r="J21" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
   </sheetData>
@@ -9053,72 +9055,72 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="17" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="17" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="48" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="48" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="48" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
   </sheetData>

--- a/data/default/MachineryAndEnergyMgmt.xlsx
+++ b/data/default/MachineryAndEnergyMgmt.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9514D7D-5125-4D6B-8BC7-778C4FFA1644}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="10650"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="default" sheetId="1" r:id="rId1"/>
@@ -13,22 +14,33 @@
     <sheet name="Sheet2" sheetId="5" r:id="rId4"/>
     <sheet name="references" sheetId="2" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029" iterate="1" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="M41" authorId="0" shapeId="0">
+    <comment ref="M41" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
       <text>
         <r>
           <rPr>
@@ -52,7 +64,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N41" authorId="0" shapeId="0">
+    <comment ref="N41" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000002000000}">
       <text>
         <r>
           <rPr>
@@ -76,7 +88,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O41" authorId="0" shapeId="0">
+    <comment ref="O41" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000003000000}">
       <text>
         <r>
           <rPr>
@@ -100,7 +112,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P41" authorId="0" shapeId="0">
+    <comment ref="P41" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000004000000}">
       <text>
         <r>
           <rPr>
@@ -125,7 +137,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M42" authorId="0" shapeId="0">
+    <comment ref="M42" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000005000000}">
       <text>
         <r>
           <rPr>
@@ -149,7 +161,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N42" authorId="0" shapeId="0">
+    <comment ref="N42" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000006000000}">
       <text>
         <r>
           <rPr>
@@ -173,7 +185,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O42" authorId="0" shapeId="0">
+    <comment ref="O42" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000007000000}">
       <text>
         <r>
           <rPr>
@@ -197,7 +209,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M52" authorId="0" shapeId="0">
+    <comment ref="M52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000008000000}">
       <text>
         <r>
           <rPr>
@@ -221,7 +233,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N52" authorId="0" shapeId="0">
+    <comment ref="N52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000009000000}">
       <text>
         <r>
           <rPr>
@@ -250,12 +262,12 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="F8" authorId="0" shapeId="0">
+    <comment ref="F8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000001000000}">
       <text>
         <r>
           <rPr>
@@ -279,7 +291,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G8" authorId="0" shapeId="0">
+    <comment ref="G8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000002000000}">
       <text>
         <r>
           <rPr>
@@ -303,7 +315,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H8" authorId="0" shapeId="0">
+    <comment ref="H8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000003000000}">
       <text>
         <r>
           <rPr>
@@ -327,7 +339,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I8" authorId="0" shapeId="0">
+    <comment ref="I8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000004000000}">
       <text>
         <r>
           <rPr>
@@ -352,7 +364,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F9" authorId="0" shapeId="0">
+    <comment ref="F9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000005000000}">
       <text>
         <r>
           <rPr>
@@ -376,7 +388,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G9" authorId="0" shapeId="0">
+    <comment ref="G9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000006000000}">
       <text>
         <r>
           <rPr>
@@ -400,7 +412,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H9" authorId="0" shapeId="0">
+    <comment ref="H9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000007000000}">
       <text>
         <r>
           <rPr>
@@ -424,7 +436,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F17" authorId="0" shapeId="0">
+    <comment ref="F17" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000008000000}">
       <text>
         <r>
           <rPr>
@@ -448,7 +460,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G17" authorId="0" shapeId="0">
+    <comment ref="G17" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000009000000}">
       <text>
         <r>
           <rPr>
@@ -847,9 +859,6 @@
     <t>Beet topper</t>
   </si>
   <si>
-    <t>ASAE, 2000</t>
-  </si>
-  <si>
     <t>Ogräsbekämpning, kemisk, Sprejspridning</t>
   </si>
   <si>
@@ -1857,19 +1866,22 @@
     <t>E_per_area_manure</t>
   </si>
   <si>
-    <t>ASAE. (2000). Agricultural Machinery Management Data. In. ASABE, St. Joseph, MI, USA: American Society of Agricultural Engineers</t>
-  </si>
-  <si>
     <t>Field cultivator, primary tillage, 10 tools per meter</t>
   </si>
   <si>
     <t>Chisel Plow, 7.5 cm shovel/35 cm sweep, 4 tools per meter</t>
+  </si>
+  <si>
+    <t>ASABE, 2006</t>
+  </si>
+  <si>
+    <t>ASABE. (2006). Agricultural Machinery Management Data. In. ASABE, St. Joseph, MI, USA: American Society of Agricultural Engineers</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
@@ -2280,15 +2292,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="105">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2300,9 +2309,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="1" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2314,12 +2321,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="1" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="14" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1"/>
@@ -2329,13 +2335,11 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="14" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
@@ -2357,10 +2361,10 @@
     <xf numFmtId="1" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="23" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="23" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -2368,8 +2372,6 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
@@ -2380,8 +2382,8 @@
     <xf numFmtId="9" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2403,7 +2405,7 @@
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Per cent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2680,8 +2682,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U236"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:Q236"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="8" max="12" width="12.28515625" customWidth="1"/>
@@ -2693,975 +2695,956 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1" s="49" t="s">
-        <v>142</v>
-      </c>
-      <c r="B1" s="93" t="s">
+      <c r="A1" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="B1" s="83" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="93" t="s">
-        <v>333</v>
-      </c>
-      <c r="D1" s="93" t="s">
-        <v>187</v>
-      </c>
-      <c r="E1" s="93" t="s">
+      <c r="C1" s="83" t="s">
+        <v>332</v>
+      </c>
+      <c r="D1" s="83" t="s">
+        <v>186</v>
+      </c>
+      <c r="E1" s="83" t="s">
+        <v>194</v>
+      </c>
+      <c r="F1" s="83" t="s">
         <v>195</v>
       </c>
-      <c r="F1" s="93" t="s">
-        <v>196</v>
-      </c>
-      <c r="G1" s="93" t="s">
-        <v>220</v>
-      </c>
-      <c r="H1" s="93" t="s">
-        <v>140</v>
-      </c>
-      <c r="I1" s="93" t="s">
+      <c r="G1" s="83" t="s">
+        <v>219</v>
+      </c>
+      <c r="H1" s="83" t="s">
+        <v>139</v>
+      </c>
+      <c r="I1" s="83" t="s">
         <v>51</v>
       </c>
-      <c r="J1" s="93" t="s">
+      <c r="J1" s="83" t="s">
         <v>44</v>
       </c>
-      <c r="K1" s="93" t="s">
-        <v>123</v>
-      </c>
-      <c r="L1" s="93" t="s">
-        <v>168</v>
-      </c>
-      <c r="M1" s="93" t="s">
+      <c r="K1" s="83" t="s">
+        <v>122</v>
+      </c>
+      <c r="L1" s="83" t="s">
+        <v>167</v>
+      </c>
+      <c r="M1" s="83" t="s">
         <v>1</v>
       </c>
-      <c r="N1" s="93" t="s">
+      <c r="N1" s="83" t="s">
         <v>2</v>
       </c>
-      <c r="O1" s="93" t="s">
+      <c r="O1" s="83" t="s">
         <v>3</v>
       </c>
-      <c r="P1" s="93" t="s">
+      <c r="P1" s="83" t="s">
         <v>4</v>
       </c>
-      <c r="Q1" s="93" t="s">
+      <c r="Q1" s="83" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M2" s="20" t="s">
-        <v>147</v>
-      </c>
-      <c r="N2" s="9">
+      <c r="M2" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="N2" s="6">
         <v>0</v>
       </c>
-      <c r="O2" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="P2" s="9" t="s">
+      <c r="O2" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="P2" s="6" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>143</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="M4" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="N4" s="18">
+        <v>142</v>
+      </c>
+      <c r="H4" t="s">
+        <v>244</v>
+      </c>
+      <c r="M4" t="s">
+        <v>146</v>
+      </c>
+      <c r="N4" s="15">
         <f>(241822577+237201100)/(241822577+237201100+5856000+8368914)*100</f>
         <v>97.116076100458642</v>
       </c>
       <c r="O4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>143</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>319</v>
-      </c>
-      <c r="M5" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="N5" s="18">
+        <v>142</v>
+      </c>
+      <c r="H5" t="s">
+        <v>318</v>
+      </c>
+      <c r="M5" t="s">
+        <v>146</v>
+      </c>
+      <c r="N5" s="15">
         <f>100-N4</f>
         <v>2.8839238995413581</v>
       </c>
       <c r="O5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>143</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="M6" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="N6" s="10">
+        <v>142</v>
+      </c>
+      <c r="H6" t="s">
+        <v>319</v>
+      </c>
+      <c r="M6" t="s">
+        <v>146</v>
+      </c>
+      <c r="N6" s="7">
         <v>0</v>
       </c>
       <c r="O6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>143</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="M7" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="N7" s="10">
+        <v>142</v>
+      </c>
+      <c r="H7" t="s">
+        <v>320</v>
+      </c>
+      <c r="M7" t="s">
+        <v>146</v>
+      </c>
+      <c r="N7" s="7">
         <v>0</v>
       </c>
       <c r="O7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H8" s="6"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="10"/>
+      <c r="N8" s="7"/>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D9" t="s">
-        <v>188</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="M9" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="N9" s="10">
+        <v>187</v>
+      </c>
+      <c r="H9" t="s">
+        <v>244</v>
+      </c>
+      <c r="M9" t="s">
+        <v>146</v>
+      </c>
+      <c r="N9" s="7">
         <v>100</v>
       </c>
       <c r="O9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D10" t="s">
-        <v>188</v>
-      </c>
-      <c r="H10" s="4"/>
-      <c r="M10" s="6"/>
-      <c r="N10" s="10"/>
+        <v>187</v>
+      </c>
+      <c r="N10" s="7"/>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D11" t="s">
-        <v>188</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="M11" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="N11" s="10">
+        <v>187</v>
+      </c>
+      <c r="H11" t="s">
+        <v>320</v>
+      </c>
+      <c r="M11" t="s">
+        <v>146</v>
+      </c>
+      <c r="N11" s="7">
         <v>100</v>
       </c>
       <c r="O11" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D12" t="s">
-        <v>188</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="M12" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="N12" s="10">
+        <v>187</v>
+      </c>
+      <c r="H12" t="s">
+        <v>320</v>
+      </c>
+      <c r="M12" t="s">
+        <v>146</v>
+      </c>
+      <c r="N12" s="7">
         <v>100</v>
       </c>
       <c r="O12" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H13" s="6"/>
-      <c r="M13" s="6"/>
-      <c r="N13" s="10"/>
+      <c r="N13" s="7"/>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D14" t="s">
+        <v>227</v>
+      </c>
+      <c r="E14" t="s">
         <v>228</v>
       </c>
-      <c r="E14" t="s">
-        <v>229</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="M14" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="N14" s="10">
+      <c r="H14" t="s">
+        <v>244</v>
+      </c>
+      <c r="M14" t="s">
+        <v>146</v>
+      </c>
+      <c r="N14" s="7">
         <v>100</v>
       </c>
       <c r="O14" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D15" t="s">
+        <v>227</v>
+      </c>
+      <c r="E15" t="s">
         <v>228</v>
       </c>
-      <c r="E15" t="s">
-        <v>229</v>
-      </c>
-      <c r="H15" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="M15" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="N15" s="10">
+      <c r="H15" t="s">
+        <v>321</v>
+      </c>
+      <c r="M15" t="s">
+        <v>146</v>
+      </c>
+      <c r="N15" s="7">
         <v>100</v>
       </c>
       <c r="O15" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D16" t="s">
+        <v>227</v>
+      </c>
+      <c r="E16" t="s">
         <v>228</v>
       </c>
-      <c r="E16" t="s">
-        <v>229</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="M16" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="N16" s="10">
+      <c r="H16" t="s">
+        <v>320</v>
+      </c>
+      <c r="M16" t="s">
+        <v>146</v>
+      </c>
+      <c r="N16" s="7">
         <v>100</v>
       </c>
       <c r="O16" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H17" s="6"/>
-      <c r="M17" s="6"/>
-      <c r="N17" s="10"/>
+      <c r="N17" s="7"/>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D18" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F18" t="s">
-        <v>311</v>
-      </c>
-      <c r="H18" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="H18" t="s">
+        <v>244</v>
+      </c>
+      <c r="M18" t="s">
+        <v>146</v>
+      </c>
+      <c r="N18" s="7">
+        <v>100</v>
+      </c>
+      <c r="O18" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q18" t="s">
         <v>245</v>
-      </c>
-      <c r="M18" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="N18" s="10">
-        <v>100</v>
-      </c>
-      <c r="O18" t="s">
-        <v>122</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D19" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F19" t="s">
-        <v>311</v>
-      </c>
-      <c r="H19" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="M19" s="6" t="s">
-        <v>147</v>
+        <v>310</v>
+      </c>
+      <c r="H19" t="s">
+        <v>321</v>
+      </c>
+      <c r="M19" t="s">
+        <v>146</v>
       </c>
       <c r="N19">
         <v>4</v>
       </c>
       <c r="O19" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q19" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D20" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F20" t="s">
-        <v>311</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="M20" s="6" t="s">
-        <v>147</v>
+        <v>310</v>
+      </c>
+      <c r="H20" t="s">
+        <v>322</v>
+      </c>
+      <c r="M20" t="s">
+        <v>146</v>
       </c>
       <c r="N20">
         <v>76</v>
       </c>
       <c r="O20" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q20" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D21" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F21" t="s">
-        <v>311</v>
-      </c>
-      <c r="H21" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="M21" s="6" t="s">
-        <v>147</v>
+        <v>310</v>
+      </c>
+      <c r="H21" t="s">
+        <v>320</v>
+      </c>
+      <c r="M21" t="s">
+        <v>146</v>
       </c>
       <c r="N21">
         <v>20</v>
       </c>
       <c r="O21" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q21" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D22" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F22" t="s">
-        <v>311</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="M22" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="N22" s="10">
+        <v>310</v>
+      </c>
+      <c r="H22" t="s">
+        <v>320</v>
+      </c>
+      <c r="M22" t="s">
+        <v>146</v>
+      </c>
+      <c r="N22" s="7">
         <v>100</v>
       </c>
       <c r="O22" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q22" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D23" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F23" t="s">
-        <v>314</v>
-      </c>
-      <c r="H23" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="H23" t="s">
+        <v>244</v>
+      </c>
+      <c r="M23" t="s">
+        <v>146</v>
+      </c>
+      <c r="N23" s="7">
+        <v>100</v>
+      </c>
+      <c r="O23" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q23" t="s">
         <v>245</v>
-      </c>
-      <c r="M23" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="N23" s="10">
-        <v>100</v>
-      </c>
-      <c r="O23" t="s">
-        <v>122</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D24" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F24" t="s">
-        <v>314</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="M24" s="6" t="s">
-        <v>147</v>
+        <v>313</v>
+      </c>
+      <c r="H24" t="s">
+        <v>321</v>
+      </c>
+      <c r="M24" t="s">
+        <v>146</v>
       </c>
       <c r="N24">
         <v>20</v>
       </c>
       <c r="O24" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q24" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D25" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F25" t="s">
-        <v>314</v>
-      </c>
-      <c r="H25" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="M25" s="6" t="s">
-        <v>147</v>
+        <v>313</v>
+      </c>
+      <c r="H25" t="s">
+        <v>322</v>
+      </c>
+      <c r="M25" t="s">
+        <v>146</v>
       </c>
       <c r="N25">
         <v>60</v>
       </c>
       <c r="O25" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q25" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D26" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F26" t="s">
-        <v>314</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="M26" s="6" t="s">
-        <v>147</v>
+        <v>313</v>
+      </c>
+      <c r="H26" t="s">
+        <v>320</v>
+      </c>
+      <c r="M26" t="s">
+        <v>146</v>
       </c>
       <c r="N26">
         <v>20.000000000000018</v>
       </c>
       <c r="O26" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q26" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D27" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F27" t="s">
-        <v>314</v>
-      </c>
-      <c r="H27" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="M27" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="N27" s="10">
+        <v>313</v>
+      </c>
+      <c r="H27" t="s">
+        <v>320</v>
+      </c>
+      <c r="M27" t="s">
+        <v>146</v>
+      </c>
+      <c r="N27" s="7">
         <v>100</v>
       </c>
       <c r="O27" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q27" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H28" s="6"/>
-      <c r="M28" s="6"/>
-      <c r="N28" s="10"/>
+      <c r="N28" s="7"/>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D29" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E29" t="s">
-        <v>354</v>
-      </c>
-      <c r="H29" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="M29" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="N29" s="10">
+        <v>353</v>
+      </c>
+      <c r="H29" t="s">
+        <v>320</v>
+      </c>
+      <c r="M29" t="s">
+        <v>146</v>
+      </c>
+      <c r="N29" s="7">
         <v>90</v>
       </c>
       <c r="O29" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D30" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E30" t="s">
-        <v>354</v>
-      </c>
-      <c r="H30" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="M30" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="N30" s="10">
+        <v>353</v>
+      </c>
+      <c r="H30" t="s">
+        <v>244</v>
+      </c>
+      <c r="M30" t="s">
+        <v>146</v>
+      </c>
+      <c r="N30" s="7">
         <v>10</v>
       </c>
       <c r="O30" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D31" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E31" t="s">
-        <v>354</v>
-      </c>
-      <c r="H31" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="M31" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="N31" s="10">
+        <v>353</v>
+      </c>
+      <c r="H31" t="s">
+        <v>320</v>
+      </c>
+      <c r="M31" t="s">
+        <v>146</v>
+      </c>
+      <c r="N31" s="7">
         <v>100</v>
       </c>
       <c r="O31" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D32" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E32" t="s">
-        <v>354</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="M32" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="N32" s="10">
+        <v>353</v>
+      </c>
+      <c r="H32" t="s">
+        <v>322</v>
+      </c>
+      <c r="M32" t="s">
+        <v>146</v>
+      </c>
+      <c r="N32" s="7">
         <v>90</v>
       </c>
       <c r="O32" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q32" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D33" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E33" t="s">
-        <v>354</v>
-      </c>
-      <c r="H33" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="M33" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="N33" s="10">
+        <v>353</v>
+      </c>
+      <c r="H33" t="s">
+        <v>321</v>
+      </c>
+      <c r="M33" t="s">
+        <v>146</v>
+      </c>
+      <c r="N33" s="7">
         <v>10</v>
       </c>
       <c r="O33" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q33" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H34" s="6"/>
-      <c r="M34" s="6"/>
-      <c r="N34" s="10"/>
+      <c r="N34" s="7"/>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D35" t="s">
-        <v>387</v>
-      </c>
-      <c r="H35" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="M35" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="N35" s="10">
+        <v>386</v>
+      </c>
+      <c r="H35" t="s">
+        <v>244</v>
+      </c>
+      <c r="M35" t="s">
+        <v>146</v>
+      </c>
+      <c r="N35" s="7">
         <v>100</v>
       </c>
       <c r="O35" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q35" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D36" t="s">
-        <v>387</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="M36" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="N36" s="10">
+        <v>386</v>
+      </c>
+      <c r="H36" t="s">
+        <v>320</v>
+      </c>
+      <c r="M36" t="s">
+        <v>146</v>
+      </c>
+      <c r="N36" s="7">
         <v>100</v>
       </c>
       <c r="O36" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q36" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H37" s="6"/>
-      <c r="M37" s="6"/>
-      <c r="N37" s="15"/>
+      <c r="N37" s="12"/>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>145</v>
+      </c>
+      <c r="H38" t="s">
+        <v>321</v>
+      </c>
+      <c r="M38" t="s">
         <v>146</v>
       </c>
-      <c r="H38" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="M38" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="N38" s="11">
+      <c r="N38" s="8">
         <v>6.4777062142923141</v>
       </c>
       <c r="O38" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q38" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>145</v>
+      </c>
+      <c r="H39" t="s">
+        <v>325</v>
+      </c>
+      <c r="M39" t="s">
         <v>146</v>
       </c>
-      <c r="H39" s="6" t="s">
-        <v>326</v>
-      </c>
-      <c r="M39" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="N39" s="11">
+      <c r="N39" s="8">
         <v>8.7567853491111922</v>
       </c>
       <c r="O39" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="P39" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="Q39" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>145</v>
+      </c>
+      <c r="H40" t="s">
+        <v>322</v>
+      </c>
+      <c r="M40" t="s">
         <v>146</v>
       </c>
-      <c r="H40" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="M40" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="N40" s="18">
+      <c r="N40" s="15">
         <v>59.671114354829328</v>
       </c>
       <c r="O40" t="s">
-        <v>122</v>
-      </c>
-      <c r="P40" s="19" t="s">
-        <v>164</v>
+        <v>121</v>
+      </c>
+      <c r="P40" t="s">
+        <v>163</v>
       </c>
       <c r="Q40" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>145</v>
+      </c>
+      <c r="H41" t="s">
+        <v>320</v>
+      </c>
+      <c r="M41" t="s">
         <v>146</v>
       </c>
-      <c r="H41" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="M41" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="N41" s="18">
+      <c r="N41" s="15">
         <v>16.802918820320372</v>
       </c>
       <c r="O41" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>145</v>
+      </c>
+      <c r="H42" t="s">
+        <v>324</v>
+      </c>
+      <c r="M42" t="s">
         <v>146</v>
       </c>
-      <c r="H42" s="6" t="s">
-        <v>325</v>
-      </c>
-      <c r="M42" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="N42" s="11">
+      <c r="N42" s="8">
         <v>7.4851294970113242</v>
       </c>
       <c r="O42" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>145</v>
+      </c>
+      <c r="H43" t="s">
+        <v>323</v>
+      </c>
+      <c r="M43" t="s">
         <v>146</v>
       </c>
-      <c r="H43" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="M43" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="N43" s="11">
+      <c r="N43" s="8">
         <v>0.80634576443547301</v>
       </c>
       <c r="O43" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H44" s="6"/>
-      <c r="M44" s="6"/>
-      <c r="N44" s="11"/>
+      <c r="N44" s="8"/>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>341</v>
-      </c>
-      <c r="H45" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="M45" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="N45" s="18">
+        <v>340</v>
+      </c>
+      <c r="H45" t="s">
+        <v>321</v>
+      </c>
+      <c r="M45" t="s">
+        <v>146</v>
+      </c>
+      <c r="N45" s="15">
         <v>70</v>
       </c>
       <c r="O45" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="P45" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="Q45" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>341</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="M46" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="N46" s="18">
+        <v>340</v>
+      </c>
+      <c r="H46" t="s">
+        <v>322</v>
+      </c>
+      <c r="M46" t="s">
+        <v>146</v>
+      </c>
+      <c r="N46" s="15">
         <v>30</v>
       </c>
       <c r="O46" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q46" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>342</v>
-      </c>
-      <c r="H47" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="M47" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="N47" s="18">
+        <v>341</v>
+      </c>
+      <c r="H47" t="s">
+        <v>320</v>
+      </c>
+      <c r="M47" t="s">
+        <v>146</v>
+      </c>
+      <c r="N47" s="15">
         <v>100</v>
       </c>
-      <c r="O47" s="10" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H48" s="6"/>
+      <c r="O47" s="7" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="K49" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M49" t="s">
-        <v>124</v>
-      </c>
-      <c r="N49" s="15">
+        <v>123</v>
+      </c>
+      <c r="N49" s="12">
         <v>80</v>
       </c>
       <c r="O49" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="K50" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M50" t="s">
-        <v>124</v>
-      </c>
-      <c r="N50" s="15">
+        <v>123</v>
+      </c>
+      <c r="N50" s="12">
         <v>10</v>
       </c>
       <c r="O50" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="K51" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="M51" t="s">
-        <v>124</v>
-      </c>
-      <c r="N51" s="15">
+        <v>123</v>
+      </c>
+      <c r="N51" s="12">
         <v>10</v>
       </c>
       <c r="O51" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -3681,402 +3664,399 @@
       <c r="Q52" s="1"/>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H53" s="4"/>
-      <c r="M53" s="9" t="s">
+      <c r="M53" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="N53" s="18">
+        <v>0</v>
+      </c>
+      <c r="O53" s="6"/>
+      <c r="P53" s="6" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="N54" s="15"/>
+    </row>
+    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H55" t="s">
+        <v>244</v>
+      </c>
+      <c r="L55" t="s">
         <v>169</v>
       </c>
-      <c r="N53" s="23">
-        <v>0</v>
-      </c>
-      <c r="O53" s="9"/>
-      <c r="P53" s="9" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H54" s="4"/>
-      <c r="N54" s="18"/>
-    </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H55" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="L55" t="s">
-        <v>170</v>
-      </c>
       <c r="M55" t="s">
-        <v>169</v>
-      </c>
-      <c r="N55" s="18">
+        <v>168</v>
+      </c>
+      <c r="N55" s="15">
         <f>74100</f>
         <v>74100</v>
       </c>
       <c r="O55" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="P55" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q55" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H56" s="4" t="s">
-        <v>245</v>
+      <c r="H56" t="s">
+        <v>244</v>
       </c>
       <c r="L56" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="M56" t="s">
-        <v>169</v>
-      </c>
-      <c r="N56" s="11">
+        <v>168</v>
+      </c>
+      <c r="N56" s="8">
         <f>3.9</f>
         <v>3.9</v>
       </c>
       <c r="O56" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q56" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H57" s="4" t="s">
-        <v>245</v>
+      <c r="H57" t="s">
+        <v>244</v>
       </c>
       <c r="L57" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="M57" t="s">
-        <v>169</v>
-      </c>
-      <c r="N57" s="11">
+        <v>168</v>
+      </c>
+      <c r="N57" s="8">
         <f>3.9</f>
         <v>3.9</v>
       </c>
       <c r="O57" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q57" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H58" s="4" t="s">
-        <v>319</v>
+      <c r="H58" t="s">
+        <v>318</v>
       </c>
       <c r="L58" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="M58" t="s">
-        <v>169</v>
-      </c>
-      <c r="N58" s="18">
+        <v>168</v>
+      </c>
+      <c r="N58" s="15">
         <v>0</v>
       </c>
       <c r="O58" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H59" s="4" t="s">
-        <v>319</v>
+      <c r="H59" t="s">
+        <v>318</v>
       </c>
       <c r="L59" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="M59" t="s">
-        <v>169</v>
-      </c>
-      <c r="N59" s="22">
+        <v>168</v>
+      </c>
+      <c r="N59" s="17">
         <f t="shared" ref="N59:N60" si="0">N56</f>
         <v>3.9</v>
       </c>
       <c r="O59" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="P59" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H60" s="4" t="s">
-        <v>319</v>
+      <c r="H60" t="s">
+        <v>318</v>
       </c>
       <c r="L60" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="M60" t="s">
-        <v>169</v>
-      </c>
-      <c r="N60" s="22">
+        <v>168</v>
+      </c>
+      <c r="N60" s="17">
         <f t="shared" si="0"/>
         <v>3.9</v>
       </c>
       <c r="O60" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="P60" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H61" s="6" t="s">
-        <v>322</v>
+      <c r="H61" t="s">
+        <v>321</v>
       </c>
       <c r="L61" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="M61" t="s">
-        <v>169</v>
-      </c>
-      <c r="N61" s="18">
+        <v>168</v>
+      </c>
+      <c r="N61" s="15">
         <v>73300</v>
       </c>
       <c r="O61" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="P61" t="s">
+        <v>181</v>
+      </c>
+      <c r="Q61" t="s">
         <v>182</v>
       </c>
-      <c r="Q61" t="s">
-        <v>183</v>
-      </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H62" s="6" t="s">
-        <v>322</v>
+      <c r="H62" t="s">
+        <v>321</v>
       </c>
       <c r="L62" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="M62" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="N62">
         <v>10</v>
       </c>
       <c r="O62" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q62" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H63" s="6" t="s">
-        <v>322</v>
+      <c r="H63" t="s">
+        <v>321</v>
       </c>
       <c r="L63" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="M63" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="N63">
         <v>0.6</v>
       </c>
       <c r="O63" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q63" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H64" s="6" t="s">
-        <v>326</v>
+      <c r="H64" t="s">
+        <v>325</v>
       </c>
       <c r="L64" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="M64" t="s">
-        <v>169</v>
-      </c>
-      <c r="N64" s="18">
+        <v>168</v>
+      </c>
+      <c r="N64" s="15">
         <v>56100</v>
       </c>
       <c r="O64" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="P64" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q64" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H65" s="6" t="s">
-        <v>326</v>
+      <c r="H65" t="s">
+        <v>325</v>
       </c>
       <c r="L65" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="M65" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="N65">
         <v>5</v>
       </c>
       <c r="O65" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q65" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H66" s="6" t="s">
-        <v>326</v>
+      <c r="H66" t="s">
+        <v>325</v>
       </c>
       <c r="L66" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="M66" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="N66">
         <v>0.1</v>
       </c>
       <c r="O66" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H67" t="s">
+        <v>322</v>
+      </c>
+      <c r="L67" t="s">
+        <v>169</v>
+      </c>
+      <c r="M67" t="s">
+        <v>168</v>
+      </c>
+      <c r="N67" s="15">
+        <v>0</v>
+      </c>
+      <c r="O67" t="s">
+        <v>178</v>
+      </c>
+      <c r="P67" t="s">
         <v>179</v>
       </c>
-      <c r="Q66" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H67" s="6" t="s">
+      <c r="Q67" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H68" t="s">
+        <v>322</v>
+      </c>
+      <c r="L68" t="s">
+        <v>177</v>
+      </c>
+      <c r="M68" t="s">
+        <v>168</v>
+      </c>
+      <c r="N68" s="15">
+        <v>300</v>
+      </c>
+      <c r="O68" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H69" t="s">
+        <v>322</v>
+      </c>
+      <c r="L69" t="s">
+        <v>170</v>
+      </c>
+      <c r="M69" t="s">
+        <v>168</v>
+      </c>
+      <c r="N69" s="15">
+        <v>4</v>
+      </c>
+      <c r="O69" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H70" t="s">
+        <v>324</v>
+      </c>
+      <c r="M70" t="s">
+        <v>168</v>
+      </c>
+      <c r="N70" s="15">
+        <v>0</v>
+      </c>
+      <c r="O70" t="s">
+        <v>178</v>
+      </c>
+      <c r="P70" s="12"/>
+    </row>
+    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H71" t="s">
         <v>323</v>
       </c>
-      <c r="L67" t="s">
-        <v>170</v>
-      </c>
-      <c r="M67" t="s">
-        <v>169</v>
-      </c>
-      <c r="N67" s="18">
+      <c r="M71" t="s">
+        <v>168</v>
+      </c>
+      <c r="N71" s="15">
         <v>0</v>
       </c>
-      <c r="O67" t="s">
-        <v>179</v>
-      </c>
-      <c r="P67" t="s">
-        <v>180</v>
-      </c>
-      <c r="Q67" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H68" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="L68" t="s">
+      <c r="O71" t="s">
         <v>178</v>
       </c>
-      <c r="M68" t="s">
-        <v>169</v>
-      </c>
-      <c r="N68" s="18">
-        <v>300</v>
-      </c>
-      <c r="O68" t="s">
-        <v>179</v>
-      </c>
-      <c r="Q68" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H69" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="L69" t="s">
-        <v>171</v>
-      </c>
-      <c r="M69" t="s">
-        <v>169</v>
-      </c>
-      <c r="N69" s="18">
-        <v>4</v>
-      </c>
-      <c r="O69" t="s">
-        <v>179</v>
-      </c>
-      <c r="Q69" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H70" s="6" t="s">
-        <v>325</v>
-      </c>
-      <c r="M70" t="s">
-        <v>169</v>
-      </c>
-      <c r="N70" s="18">
+      <c r="P71" s="12"/>
+    </row>
+    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H72" t="s">
+        <v>319</v>
+      </c>
+      <c r="M72" t="s">
+        <v>168</v>
+      </c>
+      <c r="N72" s="15">
         <v>0</v>
       </c>
-      <c r="O70" t="s">
-        <v>179</v>
-      </c>
-      <c r="P70" s="15"/>
-    </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H71" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="M71" t="s">
-        <v>169</v>
-      </c>
-      <c r="N71" s="18">
+      <c r="O72" t="s">
+        <v>178</v>
+      </c>
+      <c r="P72" s="12" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H73" t="s">
+        <v>320</v>
+      </c>
+      <c r="M73" t="s">
+        <v>168</v>
+      </c>
+      <c r="N73" s="15">
         <v>0</v>
       </c>
-      <c r="O71" t="s">
-        <v>179</v>
-      </c>
-      <c r="P71" s="15"/>
-    </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H72" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="M72" t="s">
-        <v>169</v>
-      </c>
-      <c r="N72" s="18">
-        <v>0</v>
-      </c>
-      <c r="O72" t="s">
-        <v>179</v>
-      </c>
-      <c r="P72" s="15" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H73" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="M73" t="s">
-        <v>169</v>
-      </c>
-      <c r="N73" s="18">
-        <v>0</v>
-      </c>
       <c r="O73" t="s">
-        <v>179</v>
-      </c>
-      <c r="P73" s="15"/>
+        <v>178</v>
+      </c>
+      <c r="P73" s="12"/>
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H74" s="6"/>
-      <c r="N74" s="18"/>
-      <c r="P74" s="15"/>
+      <c r="N74" s="15"/>
+      <c r="P74" s="12"/>
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
@@ -4121,18 +4101,7 @@
       <c r="Q76" s="3"/>
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B77" s="4"/>
-      <c r="C77" s="4"/>
-      <c r="D77" s="4"/>
-      <c r="E77" s="4"/>
-      <c r="F77" s="4"/>
-      <c r="G77" s="4"/>
-      <c r="H77" s="4"/>
-      <c r="I77" s="4"/>
-      <c r="J77" s="4"/>
-      <c r="K77" s="4"/>
-      <c r="L77" s="4"/>
-      <c r="M77" s="4" t="s">
+      <c r="M77" t="s">
         <v>9</v>
       </c>
       <c r="N77">
@@ -4141,23 +4110,12 @@
       <c r="O77" t="s">
         <v>11</v>
       </c>
-      <c r="P77" s="4" t="s">
+      <c r="P77" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B78" s="4"/>
-      <c r="C78" s="4"/>
-      <c r="D78" s="4"/>
-      <c r="E78" s="4"/>
-      <c r="F78" s="4"/>
-      <c r="G78" s="4"/>
-      <c r="H78" s="4"/>
-      <c r="I78" s="4"/>
-      <c r="J78" s="4"/>
-      <c r="K78" s="4"/>
-      <c r="L78" s="4"/>
-      <c r="M78" s="4" t="s">
+      <c r="M78" t="s">
         <v>22</v>
       </c>
       <c r="N78">
@@ -4166,46 +4124,24 @@
       <c r="O78" t="s">
         <v>13</v>
       </c>
-      <c r="P78" s="4" t="s">
+      <c r="P78" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B79" s="4"/>
-      <c r="C79" s="4"/>
-      <c r="D79" s="4"/>
-      <c r="E79" s="4"/>
-      <c r="F79" s="4"/>
-      <c r="G79" s="4"/>
-      <c r="H79" s="4"/>
-      <c r="I79" s="4"/>
-      <c r="J79" s="4"/>
-      <c r="K79" s="4"/>
-      <c r="L79" s="4"/>
-      <c r="M79" s="6" t="s">
-        <v>119</v>
+      <c r="M79" t="s">
+        <v>118</v>
       </c>
       <c r="N79">
         <v>2</v>
       </c>
       <c r="O79" t="s">
-        <v>120</v>
-      </c>
-      <c r="P79" s="7"/>
+        <v>119</v>
+      </c>
+      <c r="P79" s="4"/>
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B80" s="4"/>
-      <c r="C80" s="4"/>
-      <c r="D80" s="4"/>
-      <c r="E80" s="4"/>
-      <c r="F80" s="4"/>
-      <c r="G80" s="4"/>
-      <c r="H80" s="4"/>
-      <c r="I80" s="4"/>
-      <c r="J80" s="4"/>
-      <c r="K80" s="4"/>
-      <c r="L80" s="4"/>
-      <c r="M80" s="4" t="s">
+      <c r="M80" t="s">
         <v>23</v>
       </c>
       <c r="N80">
@@ -4214,23 +4150,12 @@
       <c r="O80" t="s">
         <v>15</v>
       </c>
-      <c r="P80" s="4" t="s">
+      <c r="P80" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="81" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B81" s="4"/>
-      <c r="C81" s="4"/>
-      <c r="D81" s="4"/>
-      <c r="E81" s="4"/>
-      <c r="F81" s="4"/>
-      <c r="G81" s="4"/>
-      <c r="H81" s="4"/>
-      <c r="I81" s="4"/>
-      <c r="J81" s="4"/>
-      <c r="K81" s="4"/>
-      <c r="L81" s="4"/>
-      <c r="M81" s="4" t="s">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M81" t="s">
         <v>24</v>
       </c>
       <c r="N81">
@@ -4239,23 +4164,12 @@
       <c r="O81" t="s">
         <v>17</v>
       </c>
-      <c r="P81" s="5" t="s">
+      <c r="P81" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="82" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B82" s="4"/>
-      <c r="C82" s="4"/>
-      <c r="D82" s="4"/>
-      <c r="E82" s="4"/>
-      <c r="F82" s="4"/>
-      <c r="G82" s="4"/>
-      <c r="H82" s="4"/>
-      <c r="I82" s="4"/>
-      <c r="J82" s="4"/>
-      <c r="K82" s="4"/>
-      <c r="L82" s="4"/>
-      <c r="M82" s="6" t="s">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M82" t="s">
         <v>25</v>
       </c>
       <c r="N82">
@@ -4264,142 +4178,80 @@
       <c r="O82" t="s">
         <v>19</v>
       </c>
-      <c r="P82" s="5" t="s">
+      <c r="P82" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="83" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B83" s="4"/>
-      <c r="C83" s="4"/>
-      <c r="D83" s="4"/>
-      <c r="E83" s="4"/>
-      <c r="F83" s="4"/>
-      <c r="G83" s="4"/>
-      <c r="H83" s="4"/>
-      <c r="I83" s="4"/>
-      <c r="J83" s="4"/>
-      <c r="K83" s="4"/>
-      <c r="L83" s="4"/>
-      <c r="M83" s="20" t="s">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M83" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="N83" s="9">
+      <c r="N83" s="6">
         <v>1</v>
       </c>
-      <c r="O83" s="9"/>
-      <c r="P83" s="21" t="s">
+      <c r="O83" s="6"/>
+      <c r="P83" s="16" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="84" spans="1:21" ht="18" x14ac:dyDescent="0.35">
-      <c r="B84" s="4"/>
-      <c r="C84" s="4"/>
-      <c r="D84" s="4"/>
-      <c r="E84" s="4"/>
-      <c r="F84" s="4"/>
-      <c r="G84" s="4"/>
-      <c r="H84" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="I84" s="4"/>
-      <c r="J84" s="4"/>
-      <c r="K84" s="4"/>
-      <c r="L84" s="4"/>
-      <c r="M84" s="6" t="s">
+    <row r="84" spans="1:17" ht="18" x14ac:dyDescent="0.35">
+      <c r="H84" t="s">
+        <v>244</v>
+      </c>
+      <c r="M84" t="s">
         <v>49</v>
       </c>
       <c r="N84">
         <v>0.26</v>
       </c>
-      <c r="P84" s="5" t="s">
+      <c r="P84" s="4" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="85" spans="1:21" ht="18" x14ac:dyDescent="0.35">
-      <c r="B85" s="4"/>
-      <c r="C85" s="4"/>
-      <c r="D85" s="4"/>
-      <c r="E85" s="4"/>
-      <c r="F85" s="4"/>
-      <c r="G85" s="4"/>
-      <c r="H85" s="4" t="s">
-        <v>319</v>
-      </c>
-      <c r="I85" s="4"/>
-      <c r="J85" s="4"/>
-      <c r="K85" s="4"/>
-      <c r="L85" s="4"/>
-      <c r="M85" s="6" t="s">
+    <row r="85" spans="1:17" ht="18" x14ac:dyDescent="0.35">
+      <c r="H85" t="s">
+        <v>318</v>
+      </c>
+      <c r="M85" t="s">
         <v>49</v>
       </c>
       <c r="N85">
         <v>0.26</v>
       </c>
-      <c r="P85" s="5" t="s">
+      <c r="P85" s="4" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="86" spans="1:21" ht="18" x14ac:dyDescent="0.35">
-      <c r="B86" s="4"/>
-      <c r="C86" s="4"/>
-      <c r="D86" s="4"/>
-      <c r="E86" s="4"/>
-      <c r="F86" s="4"/>
-      <c r="G86" s="4"/>
-      <c r="H86" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="I86" s="4"/>
-      <c r="J86" s="4"/>
-      <c r="K86" s="4"/>
-      <c r="L86" s="4"/>
-      <c r="M86" s="6" t="s">
+    <row r="86" spans="1:17" ht="18" x14ac:dyDescent="0.35">
+      <c r="H86" t="s">
+        <v>319</v>
+      </c>
+      <c r="M86" t="s">
         <v>49</v>
       </c>
       <c r="N86">
         <v>0.45</v>
       </c>
-      <c r="P86" s="5" t="s">
+      <c r="P86" s="4" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="87" spans="1:21" ht="18" x14ac:dyDescent="0.35">
-      <c r="B87" s="4"/>
-      <c r="C87" s="4"/>
-      <c r="D87" s="4"/>
-      <c r="E87" s="4"/>
-      <c r="F87" s="4"/>
-      <c r="G87" s="4"/>
-      <c r="H87" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="I87" s="6"/>
-      <c r="J87" s="6"/>
-      <c r="K87" s="6"/>
-      <c r="L87" s="6"/>
-      <c r="M87" s="6" t="s">
+    <row r="87" spans="1:17" ht="18" x14ac:dyDescent="0.35">
+      <c r="H87" t="s">
+        <v>320</v>
+      </c>
+      <c r="M87" t="s">
         <v>49</v>
       </c>
       <c r="N87">
         <v>0.76</v>
       </c>
-      <c r="P87" s="5" t="s">
+      <c r="P87" s="4" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="88" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B88" s="4"/>
-      <c r="C88" s="4"/>
-      <c r="D88" s="4"/>
-      <c r="E88" s="4"/>
-      <c r="F88" s="4"/>
-      <c r="G88" s="4"/>
-      <c r="H88" s="4"/>
-      <c r="I88" s="4"/>
-      <c r="J88" s="4"/>
-      <c r="K88" s="4"/>
-      <c r="L88" s="4"/>
-      <c r="M88" s="6" t="s">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M88" t="s">
         <v>27</v>
       </c>
       <c r="N88">
@@ -4408,11 +4260,11 @@
       <c r="O88" t="s">
         <v>21</v>
       </c>
-      <c r="P88" s="7" t="s">
+      <c r="P88" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="90" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>8</v>
       </c>
@@ -4433,9 +4285,9 @@
       <c r="P90" s="2"/>
       <c r="Q90" s="2"/>
     </row>
-    <row r="91" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
       <c r="M91" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="N91">
         <v>4</v>
@@ -4446,9 +4298,8 @@
       <c r="P91" t="s">
         <v>28</v>
       </c>
-      <c r="U91" s="6"/>
-    </row>
-    <row r="92" spans="1:21" ht="18" x14ac:dyDescent="0.35">
+    </row>
+    <row r="92" spans="1:17" ht="18" x14ac:dyDescent="0.35">
       <c r="M92" t="s">
         <v>45</v>
       </c>
@@ -4458,9 +4309,8 @@
       <c r="P92" t="s">
         <v>30</v>
       </c>
-      <c r="U92" s="6"/>
-    </row>
-    <row r="93" spans="1:21" ht="18" x14ac:dyDescent="0.35">
+    </row>
+    <row r="93" spans="1:17" ht="18" x14ac:dyDescent="0.35">
       <c r="M93" t="s">
         <v>38</v>
       </c>
@@ -4473,9 +4323,8 @@
       <c r="P93" t="s">
         <v>31</v>
       </c>
-      <c r="U93" s="6"/>
-    </row>
-    <row r="94" spans="1:21" ht="18" x14ac:dyDescent="0.35">
+    </row>
+    <row r="94" spans="1:17" ht="18" x14ac:dyDescent="0.35">
       <c r="M94" t="s">
         <v>39</v>
       </c>
@@ -4485,9 +4334,8 @@
       <c r="P94" t="s">
         <v>33</v>
       </c>
-      <c r="U94" s="6"/>
-    </row>
-    <row r="95" spans="1:21" ht="18" x14ac:dyDescent="0.35">
+    </row>
+    <row r="95" spans="1:17" ht="18" x14ac:dyDescent="0.35">
       <c r="M95" t="s">
         <v>40</v>
       </c>
@@ -4498,7 +4346,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="96" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
       <c r="M96" t="s">
         <v>41</v>
       </c>
@@ -4509,7 +4357,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="97" spans="1:20" ht="18" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:17" ht="18" x14ac:dyDescent="0.35">
       <c r="M97" t="s">
         <v>42</v>
       </c>
@@ -4520,7 +4368,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="98" spans="1:20" ht="18" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:17" ht="18" x14ac:dyDescent="0.35">
       <c r="M98" t="s">
         <v>43</v>
       </c>
@@ -4530,236 +4378,235 @@
       <c r="P98" t="s">
         <v>37</v>
       </c>
-      <c r="T98" s="4"/>
-    </row>
-    <row r="100" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B100" s="8"/>
-      <c r="C100" s="8"/>
-      <c r="D100" s="8"/>
-      <c r="E100" s="8"/>
-      <c r="F100" s="8"/>
-      <c r="G100" s="8"/>
-      <c r="H100" s="8"/>
-      <c r="I100" s="8"/>
-      <c r="J100" s="8"/>
-      <c r="K100" s="8"/>
-      <c r="L100" s="8"/>
-      <c r="M100" s="8"/>
-      <c r="N100" s="8"/>
-      <c r="O100" s="8"/>
-      <c r="P100" s="8"/>
-      <c r="Q100" s="8"/>
-    </row>
-    <row r="101" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="M101" s="9" t="s">
+      <c r="B100" s="5"/>
+      <c r="C100" s="5"/>
+      <c r="D100" s="5"/>
+      <c r="E100" s="5"/>
+      <c r="F100" s="5"/>
+      <c r="G100" s="5"/>
+      <c r="H100" s="5"/>
+      <c r="I100" s="5"/>
+      <c r="J100" s="5"/>
+      <c r="K100" s="5"/>
+      <c r="L100" s="5"/>
+      <c r="M100" s="5"/>
+      <c r="N100" s="5"/>
+      <c r="O100" s="5"/>
+      <c r="P100" s="5"/>
+      <c r="Q100" s="5"/>
+    </row>
+    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M101" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="N101" s="9">
+      <c r="N101" s="6">
         <v>0</v>
       </c>
-      <c r="O101" s="9" t="s">
+      <c r="O101" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="P101" s="9"/>
-    </row>
-    <row r="102" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="M102" s="9" t="s">
+      <c r="P101" s="6"/>
+    </row>
+    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M102" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="N102" s="9">
+      <c r="N102" s="6">
         <v>0</v>
       </c>
-      <c r="O102" s="9" t="s">
+      <c r="O102" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="P102" s="9"/>
-    </row>
-    <row r="103" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="M103" s="9" t="s">
+      <c r="P102" s="6"/>
+    </row>
+    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M103" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="N103" s="9">
+      <c r="N103" s="6">
         <v>0</v>
       </c>
-      <c r="O103" s="9" t="s">
+      <c r="O103" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="P103" s="9"/>
-    </row>
-    <row r="104" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="M104" s="9" t="s">
+      <c r="P103" s="6"/>
+    </row>
+    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M104" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="N104" s="9">
+      <c r="N104" s="6">
         <v>0</v>
       </c>
-      <c r="O104" s="9" t="s">
+      <c r="O104" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="P104" s="9"/>
-    </row>
-    <row r="105" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="M105" s="9" t="s">
+      <c r="P104" s="6"/>
+    </row>
+    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M105" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="N105" s="9">
+      <c r="N105" s="6">
         <v>0</v>
       </c>
-      <c r="O105" s="9" t="s">
+      <c r="O105" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="P105" s="9"/>
-    </row>
-    <row r="106" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="M106" s="9" t="s">
+      <c r="P105" s="6"/>
+    </row>
+    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M106" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="N106" s="9">
+      <c r="N106" s="6">
         <v>1</v>
       </c>
-      <c r="O106" s="9" t="s">
+      <c r="O106" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="P106" s="9" t="s">
+      <c r="P106" s="6" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="107" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="M107" s="9" t="s">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M107" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="N107" s="9">
+      <c r="N107" s="6">
         <v>0</v>
       </c>
-      <c r="O107" s="9" t="s">
+      <c r="O107" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="P107" s="9"/>
-    </row>
-    <row r="108" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="M108" s="9" t="s">
-        <v>399</v>
-      </c>
-      <c r="N108" s="9">
+      <c r="P107" s="6"/>
+    </row>
+    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M108" s="6" t="s">
+        <v>398</v>
+      </c>
+      <c r="N108" s="6">
         <v>0</v>
       </c>
-      <c r="O108" s="9" t="s">
+      <c r="O108" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="P108" s="9" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="109" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="M109" s="9" t="s">
+      <c r="P108" s="6" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M109" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="N109" s="9">
+      <c r="N109" s="6">
         <v>0</v>
       </c>
-      <c r="O109" s="9" t="s">
+      <c r="O109" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="P109" s="9"/>
-    </row>
-    <row r="110" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="M110" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="N110" s="9">
+      <c r="P109" s="6"/>
+    </row>
+    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M110" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="N110" s="6">
         <v>0</v>
       </c>
-      <c r="O110" s="9" t="s">
-        <v>327</v>
-      </c>
-      <c r="P110" s="9"/>
-    </row>
-    <row r="111" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="M111" s="9" t="s">
+      <c r="O110" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="P110" s="6"/>
+    </row>
+    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M111" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="N111" s="9">
+      <c r="N111" s="6">
         <v>0</v>
       </c>
-      <c r="O111" s="9" t="s">
+      <c r="O111" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="P111" s="9"/>
-    </row>
-    <row r="112" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="M112" s="9"/>
-      <c r="N112" s="9"/>
-      <c r="O112" s="9"/>
-      <c r="P112" s="9"/>
+      <c r="P111" s="6"/>
+    </row>
+    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M112" s="6"/>
+      <c r="N112" s="6"/>
+      <c r="O112" s="6"/>
+      <c r="P112" s="6"/>
     </row>
     <row r="113" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I113" t="s">
         <v>59</v>
       </c>
-      <c r="M113" s="10" t="s">
+      <c r="M113" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="N113" s="10">
+      <c r="N113" s="7">
         <f>46*10</f>
         <v>460</v>
       </c>
-      <c r="O113" s="10"/>
-      <c r="P113" s="10" t="s">
+      <c r="O113" s="7"/>
+      <c r="P113" s="7" t="s">
+        <v>399</v>
+      </c>
+      <c r="Q113" t="s">
         <v>401</v>
-      </c>
-      <c r="Q113" s="4" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="114" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I114" t="s">
         <v>59</v>
       </c>
-      <c r="M114" s="10" t="s">
+      <c r="M114" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="N114" s="10">
+      <c r="N114" s="7">
         <f>2.8*10</f>
         <v>28</v>
       </c>
-      <c r="O114" s="10"/>
-      <c r="P114" s="10"/>
-      <c r="Q114" s="4" t="s">
-        <v>92</v>
+      <c r="O114" s="7"/>
+      <c r="P114" s="7"/>
+      <c r="Q114" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="115" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I115" t="s">
         <v>59</v>
       </c>
-      <c r="M115" s="10" t="s">
+      <c r="M115" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="N115" s="10">
+      <c r="N115" s="7">
         <v>0</v>
       </c>
-      <c r="O115" s="10"/>
-      <c r="P115" s="10"/>
-      <c r="Q115" s="4" t="s">
-        <v>92</v>
+      <c r="O115" s="7"/>
+      <c r="P115" s="7"/>
+      <c r="Q115" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="116" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I116" t="s">
         <v>59</v>
       </c>
-      <c r="M116" s="10" t="s">
+      <c r="M116" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="N116" s="10">
+      <c r="N116" s="7">
         <v>5</v>
       </c>
-      <c r="O116" s="10"/>
-      <c r="P116" s="10"/>
-      <c r="Q116" s="10"/>
+      <c r="O116" s="7"/>
+      <c r="P116" s="7"/>
+      <c r="Q116" s="7"/>
     </row>
     <row r="117" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I117" t="s">
@@ -4768,16 +4615,16 @@
       <c r="J117" t="s">
         <v>72</v>
       </c>
-      <c r="M117" s="10" t="s">
+      <c r="M117" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="N117" s="12">
+      <c r="N117" s="9">
         <v>1</v>
       </c>
-      <c r="O117" s="10"/>
-      <c r="P117" s="10"/>
-      <c r="Q117" s="4" t="s">
-        <v>92</v>
+      <c r="O117" s="7"/>
+      <c r="P117" s="7"/>
+      <c r="Q117" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="118" spans="9:17" x14ac:dyDescent="0.25">
@@ -4787,16 +4634,16 @@
       <c r="J118" t="s">
         <v>71</v>
       </c>
-      <c r="M118" s="10" t="s">
+      <c r="M118" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="N118" s="10">
+      <c r="N118" s="7">
         <v>0.88</v>
       </c>
-      <c r="O118" s="10"/>
-      <c r="P118" s="10"/>
-      <c r="Q118" s="4" t="s">
-        <v>92</v>
+      <c r="O118" s="7"/>
+      <c r="P118" s="7"/>
+      <c r="Q118" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="119" spans="9:17" x14ac:dyDescent="0.25">
@@ -4806,88 +4653,88 @@
       <c r="J119" t="s">
         <v>70</v>
       </c>
-      <c r="M119" s="10" t="s">
+      <c r="M119" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="N119" s="10">
+      <c r="N119" s="7">
         <v>0.78</v>
       </c>
-      <c r="O119" s="10"/>
-      <c r="P119" s="10"/>
-      <c r="Q119" s="4" t="s">
-        <v>92</v>
+      <c r="O119" s="7"/>
+      <c r="P119" s="7"/>
+      <c r="Q119" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="120" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="M120" s="10"/>
-      <c r="N120" s="10"/>
-      <c r="O120" s="10"/>
-      <c r="P120" s="10"/>
-      <c r="Q120" s="10"/>
+      <c r="M120" s="7"/>
+      <c r="N120" s="7"/>
+      <c r="O120" s="7"/>
+      <c r="P120" s="7"/>
+      <c r="Q120" s="7"/>
     </row>
     <row r="121" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I121" t="s">
         <v>62</v>
       </c>
-      <c r="M121" s="10" t="s">
+      <c r="M121" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="N121" s="10">
+      <c r="N121" s="7">
         <v>652</v>
       </c>
-      <c r="O121" s="10"/>
-      <c r="P121" s="10" t="s">
+      <c r="O121" s="7"/>
+      <c r="P121" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="Q121" s="4" t="s">
-        <v>92</v>
+      <c r="Q121" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="122" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I122" t="s">
         <v>62</v>
       </c>
-      <c r="M122" s="10" t="s">
+      <c r="M122" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="N122" s="10">
+      <c r="N122" s="7">
         <v>0</v>
       </c>
-      <c r="O122" s="10"/>
-      <c r="P122" s="10"/>
-      <c r="Q122" s="4" t="s">
-        <v>92</v>
+      <c r="O122" s="7"/>
+      <c r="P122" s="7"/>
+      <c r="Q122" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="123" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I123" t="s">
         <v>62</v>
       </c>
-      <c r="M123" s="10" t="s">
+      <c r="M123" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="N123" s="10">
+      <c r="N123" s="7">
         <v>5.0999999999999996</v>
       </c>
-      <c r="O123" s="10"/>
-      <c r="P123" s="10"/>
-      <c r="Q123" s="4" t="s">
-        <v>92</v>
+      <c r="O123" s="7"/>
+      <c r="P123" s="7"/>
+      <c r="Q123" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="124" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I124" t="s">
         <v>62</v>
       </c>
-      <c r="M124" s="10" t="s">
+      <c r="M124" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="N124" s="10">
+      <c r="N124" s="7">
         <v>20</v>
       </c>
-      <c r="O124" s="10"/>
-      <c r="P124" s="10"/>
-      <c r="Q124" s="10"/>
+      <c r="O124" s="7"/>
+      <c r="P124" s="7"/>
+      <c r="Q124" s="7"/>
     </row>
     <row r="125" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I125" t="s">
@@ -4896,16 +4743,16 @@
       <c r="J125" t="s">
         <v>72</v>
       </c>
-      <c r="M125" s="10" t="s">
+      <c r="M125" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="N125" s="12">
+      <c r="N125" s="9">
         <v>1</v>
       </c>
-      <c r="O125" s="10"/>
-      <c r="P125" s="10"/>
-      <c r="Q125" s="4" t="s">
-        <v>92</v>
+      <c r="O125" s="7"/>
+      <c r="P125" s="7"/>
+      <c r="Q125" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="126" spans="9:17" x14ac:dyDescent="0.25">
@@ -4915,16 +4762,16 @@
       <c r="J126" t="s">
         <v>71</v>
       </c>
-      <c r="M126" s="10" t="s">
+      <c r="M126" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="N126" s="12">
+      <c r="N126" s="9">
         <v>0.7</v>
       </c>
-      <c r="O126" s="10"/>
-      <c r="P126" s="10"/>
-      <c r="Q126" s="4" t="s">
-        <v>92</v>
+      <c r="O126" s="7"/>
+      <c r="P126" s="7"/>
+      <c r="Q126" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="127" spans="9:17" x14ac:dyDescent="0.25">
@@ -4934,90 +4781,90 @@
       <c r="J127" t="s">
         <v>70</v>
       </c>
-      <c r="M127" s="10" t="s">
+      <c r="M127" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="N127" s="10">
+      <c r="N127" s="7">
         <v>0.45</v>
       </c>
-      <c r="O127" s="10"/>
-      <c r="P127" s="10"/>
-      <c r="Q127" s="4" t="s">
-        <v>92</v>
+      <c r="O127" s="7"/>
+      <c r="P127" s="7"/>
+      <c r="Q127" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="128" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="M128" s="10"/>
-      <c r="N128" s="10"/>
-      <c r="O128" s="10"/>
-      <c r="P128" s="10"/>
-      <c r="Q128" s="10"/>
+      <c r="M128" s="7"/>
+      <c r="N128" s="7"/>
+      <c r="O128" s="7"/>
+      <c r="P128" s="7"/>
+      <c r="Q128" s="7"/>
     </row>
     <row r="129" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I129" t="s">
         <v>61</v>
       </c>
-      <c r="M129" s="10" t="s">
+      <c r="M129" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="N129" s="10">
+      <c r="N129" s="7">
         <f>107*4</f>
         <v>428</v>
       </c>
-      <c r="O129" s="10"/>
-      <c r="P129" s="10" t="s">
-        <v>402</v>
-      </c>
-      <c r="Q129" s="4" t="s">
-        <v>92</v>
+      <c r="O129" s="7"/>
+      <c r="P129" s="7" t="s">
+        <v>400</v>
+      </c>
+      <c r="Q129" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="130" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I130" t="s">
         <v>61</v>
       </c>
-      <c r="M130" s="10" t="s">
+      <c r="M130" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="N130" s="10">
+      <c r="N130" s="7">
         <f>6.3*4</f>
         <v>25.2</v>
       </c>
-      <c r="O130" s="10"/>
-      <c r="P130" s="10"/>
-      <c r="Q130" s="4" t="s">
-        <v>92</v>
+      <c r="O130" s="7"/>
+      <c r="P130" s="7"/>
+      <c r="Q130" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="131" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I131" t="s">
         <v>61</v>
       </c>
-      <c r="M131" s="10" t="s">
+      <c r="M131" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="N131" s="10">
+      <c r="N131" s="7">
         <v>0</v>
       </c>
-      <c r="O131" s="10"/>
-      <c r="P131" s="10"/>
-      <c r="Q131" s="4" t="s">
-        <v>92</v>
+      <c r="O131" s="7"/>
+      <c r="P131" s="7"/>
+      <c r="Q131" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="132" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I132" t="s">
         <v>61</v>
       </c>
-      <c r="M132" s="10" t="s">
+      <c r="M132" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="N132" s="10">
+      <c r="N132" s="7">
         <v>10</v>
       </c>
-      <c r="O132" s="10"/>
-      <c r="P132" s="10"/>
-      <c r="Q132" s="10"/>
+      <c r="O132" s="7"/>
+      <c r="P132" s="7"/>
+      <c r="Q132" s="7"/>
     </row>
     <row r="133" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I133" t="s">
@@ -5026,16 +4873,16 @@
       <c r="J133" t="s">
         <v>72</v>
       </c>
-      <c r="M133" s="10" t="s">
+      <c r="M133" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="N133" s="12">
+      <c r="N133" s="9">
         <v>1</v>
       </c>
-      <c r="O133" s="10"/>
-      <c r="P133" s="10"/>
-      <c r="Q133" s="4" t="s">
-        <v>92</v>
+      <c r="O133" s="7"/>
+      <c r="P133" s="7"/>
+      <c r="Q133" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="134" spans="9:17" x14ac:dyDescent="0.25">
@@ -5045,16 +4892,16 @@
       <c r="J134" t="s">
         <v>71</v>
       </c>
-      <c r="M134" s="10" t="s">
+      <c r="M134" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="N134" s="10">
+      <c r="N134" s="7">
         <v>0.85</v>
       </c>
-      <c r="O134" s="10"/>
-      <c r="P134" s="10"/>
-      <c r="Q134" s="4" t="s">
-        <v>92</v>
+      <c r="O134" s="7"/>
+      <c r="P134" s="7"/>
+      <c r="Q134" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="135" spans="9:17" x14ac:dyDescent="0.25">
@@ -5064,83 +4911,83 @@
       <c r="J135" t="s">
         <v>70</v>
       </c>
-      <c r="M135" s="10" t="s">
+      <c r="M135" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="N135" s="10">
+      <c r="N135" s="7">
         <v>0.65</v>
       </c>
-      <c r="O135" s="10"/>
-      <c r="P135" s="10"/>
-      <c r="Q135" s="4" t="s">
-        <v>92</v>
+      <c r="O135" s="7"/>
+      <c r="P135" s="7"/>
+      <c r="Q135" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="136" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="M136" s="10"/>
-      <c r="N136" s="10"/>
-      <c r="O136" s="10"/>
-      <c r="P136" s="10"/>
-      <c r="Q136" s="10"/>
+      <c r="M136" s="7"/>
+      <c r="N136" s="7"/>
+      <c r="O136" s="7"/>
+      <c r="P136" s="7"/>
+      <c r="Q136" s="7"/>
     </row>
     <row r="137" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I137" t="s">
         <v>64</v>
       </c>
-      <c r="M137" s="10" t="s">
+      <c r="M137" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="N137" s="12">
+      <c r="N137" s="9">
         <v>5.0999999999999996</v>
       </c>
-      <c r="O137" s="10"/>
-      <c r="P137" s="6" t="s">
+      <c r="O137" s="7"/>
+      <c r="P137" t="s">
         <v>90</v>
       </c>
-      <c r="Q137" s="4" t="s">
-        <v>92</v>
+      <c r="Q137" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="138" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I138" t="s">
         <v>65</v>
       </c>
-      <c r="M138" s="10" t="s">
+      <c r="M138" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="N138" s="12">
+      <c r="N138" s="9">
         <v>7.1</v>
       </c>
-      <c r="O138" s="10"/>
-      <c r="P138" s="6" t="s">
+      <c r="O138" s="7"/>
+      <c r="P138" t="s">
         <v>91</v>
       </c>
-      <c r="Q138" s="4" t="s">
-        <v>92</v>
+      <c r="Q138" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="139" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="M139" s="10"/>
-      <c r="N139" s="10"/>
-      <c r="O139" s="10"/>
-      <c r="P139" s="10"/>
-      <c r="Q139" s="10"/>
+      <c r="M139" s="7"/>
+      <c r="N139" s="7"/>
+      <c r="O139" s="7"/>
+      <c r="P139" s="7"/>
+      <c r="Q139" s="7"/>
     </row>
     <row r="140" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I140" t="s">
         <v>60</v>
       </c>
-      <c r="M140" s="10" t="s">
+      <c r="M140" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="N140" s="12">
+      <c r="N140" s="9">
         <v>3.7353333333333332</v>
       </c>
-      <c r="O140" s="10"/>
-      <c r="P140" s="10" t="s">
+      <c r="O140" s="7"/>
+      <c r="P140" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="Q140" s="6" t="s">
+      <c r="Q140" t="s">
         <v>85</v>
       </c>
     </row>
@@ -5148,17 +4995,17 @@
       <c r="I141" t="s">
         <v>63</v>
       </c>
-      <c r="M141" s="10" t="s">
+      <c r="M141" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="N141" s="11">
+      <c r="N141" s="8">
         <v>17.096931944444446</v>
       </c>
-      <c r="O141" s="10"/>
-      <c r="P141" s="6" t="s">
+      <c r="O141" s="7"/>
+      <c r="P141" t="s">
         <v>86</v>
       </c>
-      <c r="Q141" s="4" t="s">
+      <c r="Q141" t="s">
         <v>87</v>
       </c>
     </row>
@@ -5166,36 +5013,36 @@
       <c r="I142" t="s">
         <v>66</v>
       </c>
-      <c r="M142" s="10" t="s">
+      <c r="M142" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="N142" s="12">
+      <c r="N142" s="9">
         <v>1.2451111111111113</v>
       </c>
-      <c r="O142" s="10"/>
-      <c r="P142" s="6" t="s">
+      <c r="O142" s="7"/>
+      <c r="P142" t="s">
         <v>47</v>
       </c>
-      <c r="Q142" s="10" t="s">
+      <c r="Q142" s="7" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="143" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I143" t="s">
-        <v>397</v>
-      </c>
-      <c r="M143" s="10" t="s">
-        <v>399</v>
-      </c>
-      <c r="N143" s="12">
+        <v>396</v>
+      </c>
+      <c r="M143" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="N143" s="9">
         <f>(3.11+4.67)/2</f>
         <v>3.8899999999999997</v>
       </c>
-      <c r="O143" s="10"/>
-      <c r="P143" s="6" t="s">
-        <v>396</v>
-      </c>
-      <c r="Q143" s="10" t="s">
+      <c r="O143" s="7"/>
+      <c r="P143" t="s">
+        <v>395</v>
+      </c>
+      <c r="Q143" s="7" t="s">
         <v>85</v>
       </c>
     </row>
@@ -5203,17 +5050,17 @@
       <c r="I144" t="s">
         <v>67</v>
       </c>
-      <c r="M144" s="10" t="s">
+      <c r="M144" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="N144" s="12">
+      <c r="N144" s="9">
         <v>3.1127777777777781</v>
       </c>
-      <c r="O144" s="10"/>
-      <c r="P144" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="Q144" s="6" t="s">
+      <c r="O144" s="7"/>
+      <c r="P144" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q144" t="s">
         <v>85</v>
       </c>
     </row>
@@ -5221,332 +5068,324 @@
       <c r="I145" t="s">
         <v>68</v>
       </c>
-      <c r="M145" s="10" t="s">
+      <c r="M145" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="N145" s="11">
+      <c r="N145" s="8">
         <v>11.828555555555555</v>
       </c>
-      <c r="O145" s="10"/>
-      <c r="P145" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="Q145" s="10" t="s">
+      <c r="O145" s="7"/>
+      <c r="P145" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q145" s="7" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="146" spans="2:17" x14ac:dyDescent="0.25">
       <c r="I146" t="s">
-        <v>94</v>
-      </c>
-      <c r="M146" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="M146" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="N146" s="11">
+      <c r="N146" s="8">
         <v>26.302972222222223</v>
       </c>
-      <c r="O146" s="10"/>
-      <c r="P146" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q146" s="10" t="s">
+      <c r="O146" s="7"/>
+      <c r="P146" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q146" s="7" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="147" spans="2:17" x14ac:dyDescent="0.25">
       <c r="I147" t="s">
-        <v>95</v>
-      </c>
-      <c r="M147" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="M147" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="N147" s="11">
+      <c r="N147" s="8">
         <v>11.3</v>
       </c>
-      <c r="O147" s="10"/>
-      <c r="P147" s="6" t="s">
+      <c r="O147" s="7"/>
+      <c r="P147" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q147" s="7" t="s">
         <v>100</v>
-      </c>
-      <c r="Q147" s="10" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="148" spans="2:17" x14ac:dyDescent="0.25">
       <c r="I148" t="s">
-        <v>96</v>
-      </c>
-      <c r="M148" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="M148" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="N148" s="11">
+      <c r="N148" s="8">
         <v>23.278130416666666</v>
       </c>
-      <c r="O148" s="10"/>
-      <c r="P148" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q148" s="10" t="s">
-        <v>101</v>
+      <c r="O148" s="7"/>
+      <c r="P148" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q148" s="7" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="149" spans="2:17" x14ac:dyDescent="0.25">
       <c r="I149" t="s">
         <v>69</v>
       </c>
-      <c r="M149" s="10" t="s">
+      <c r="M149" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="N149" s="10">
+      <c r="N149" s="7">
         <v>13.15</v>
       </c>
-      <c r="O149" s="10"/>
-      <c r="P149" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q149" s="10" t="s">
+      <c r="O149" s="7"/>
+      <c r="P149" s="7" t="s">
         <v>102</v>
+      </c>
+      <c r="Q149" s="7" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="150" spans="2:17" x14ac:dyDescent="0.25">
       <c r="I150" t="s">
         <v>69</v>
       </c>
-      <c r="M150" s="10" t="s">
+      <c r="M150" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="N150" s="10">
+      <c r="N150" s="7">
         <v>5.26</v>
       </c>
-      <c r="O150" s="10"/>
-      <c r="P150" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q150" s="10" t="s">
+      <c r="O150" s="7"/>
+      <c r="P150" s="7" t="s">
         <v>102</v>
+      </c>
+      <c r="Q150" s="7" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="151" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B151" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I151" t="s">
         <v>69</v>
       </c>
-      <c r="M151" s="10" t="s">
+      <c r="M151" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="N151" s="12">
+      <c r="N151" s="9">
         <v>1.7546281240590185</v>
       </c>
-      <c r="O151" s="10"/>
-      <c r="P151" s="10" t="s">
+      <c r="O151" s="7"/>
+      <c r="P151" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q151" t="s">
         <v>105</v>
-      </c>
-      <c r="Q151" s="4" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="152" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B152" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I152" t="s">
         <v>69</v>
       </c>
-      <c r="M152" s="10" t="s">
+      <c r="M152" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="N152" s="12">
+      <c r="N152" s="9">
         <v>5.1828516694033944</v>
       </c>
-      <c r="O152" s="10"/>
-      <c r="P152" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="Q152" s="4" t="s">
-        <v>106</v>
+      <c r="O152" s="7"/>
+      <c r="P152" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q152" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="153" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B153" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I153" t="s">
         <v>69</v>
       </c>
-      <c r="M153" s="10" t="s">
+      <c r="M153" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="N153" s="13">
+      <c r="N153" s="10">
         <v>4.0531064740502947</v>
       </c>
-      <c r="P153" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="Q153" s="4" t="s">
-        <v>106</v>
+      <c r="P153" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q153" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="154" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B154" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I154" t="s">
         <v>69</v>
       </c>
-      <c r="M154" s="10" t="s">
+      <c r="M154" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="N154" s="13">
+      <c r="N154" s="10">
         <v>4.3591310772039646</v>
       </c>
-      <c r="P154" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q154" s="6" t="s">
-        <v>101</v>
+      <c r="P154" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q154" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="155" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="M155" s="10"/>
-      <c r="N155" s="13"/>
-      <c r="P155" s="6"/>
-      <c r="Q155" s="6"/>
+      <c r="M155" s="7"/>
+      <c r="N155" s="10"/>
     </row>
     <row r="156" spans="2:17" x14ac:dyDescent="0.25">
       <c r="I156" t="s">
-        <v>114</v>
-      </c>
-      <c r="M156" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="M156" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="N156" s="13">
+      <c r="N156" s="10">
         <v>14.6</v>
       </c>
-      <c r="P156" s="6"/>
-      <c r="Q156" s="4" t="s">
-        <v>113</v>
+      <c r="Q156" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="157" spans="2:17" x14ac:dyDescent="0.25">
       <c r="I157" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K157" t="s">
-        <v>115</v>
-      </c>
-      <c r="M157" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="M157" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="N157" s="13">
+      <c r="N157" s="10">
         <v>37.744765138888887</v>
       </c>
-      <c r="P157" s="6"/>
-      <c r="Q157" s="6" t="s">
+      <c r="Q157" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="158" spans="2:17" x14ac:dyDescent="0.25">
       <c r="I158" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K158" t="s">
-        <v>116</v>
-      </c>
-      <c r="M158" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="M158" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="N158" s="13">
+      <c r="N158" s="10">
         <v>50.107162083333336</v>
       </c>
-      <c r="P158" s="6"/>
-      <c r="Q158" s="6" t="s">
+      <c r="Q158" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="159" spans="2:17" x14ac:dyDescent="0.25">
       <c r="I159" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K159" t="s">
-        <v>117</v>
-      </c>
-      <c r="M159" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="M159" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="N159" s="13">
+      <c r="N159" s="10">
         <v>36.955675972222224</v>
       </c>
-      <c r="P159" s="6"/>
-      <c r="Q159" s="6" t="s">
+      <c r="Q159" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="160" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="M160" s="10"/>
-      <c r="N160" s="13"/>
-      <c r="P160" s="6"/>
-      <c r="Q160" s="6"/>
+      <c r="M160" s="7"/>
+      <c r="N160" s="10"/>
     </row>
     <row r="161" spans="1:17" x14ac:dyDescent="0.25">
       <c r="I161" t="s">
-        <v>125</v>
-      </c>
-      <c r="M161" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="M161" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="N161" s="13">
+      <c r="N161" s="10">
         <v>1.6176327916666666</v>
       </c>
       <c r="O161" t="s">
         <v>56</v>
       </c>
-      <c r="P161" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="Q161" s="4" t="s">
+      <c r="P161" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q161" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="162" spans="1:17" x14ac:dyDescent="0.25">
       <c r="I162" t="s">
-        <v>126</v>
-      </c>
-      <c r="M162" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="N162" s="13">
+        <v>125</v>
+      </c>
+      <c r="M162" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="N162" s="10">
         <f>3.07744775/0.85</f>
         <v>3.6205267647058825</v>
       </c>
       <c r="O162" t="s">
+        <v>326</v>
+      </c>
+      <c r="P162" t="s">
         <v>327</v>
       </c>
-      <c r="P162" s="6" t="s">
-        <v>328</v>
-      </c>
-      <c r="Q162" s="4" t="s">
+      <c r="Q162" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="163" spans="1:17" x14ac:dyDescent="0.25">
       <c r="I163" t="s">
-        <v>127</v>
-      </c>
-      <c r="M163" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="M163" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="N163" s="13">
+      <c r="N163" s="10">
         <v>0.25</v>
       </c>
       <c r="O163" t="s">
         <v>58</v>
       </c>
-      <c r="P163" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="Q163" s="4" t="s">
-        <v>106</v>
+      <c r="P163" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q163" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="165" spans="1:17" x14ac:dyDescent="0.25">
@@ -5564,20 +5403,20 @@
       <c r="J165" s="1"/>
       <c r="K165" s="1"/>
       <c r="L165" s="1"/>
-      <c r="M165" s="8"/>
-      <c r="N165" s="8"/>
-      <c r="O165" s="8"/>
-      <c r="P165" s="8"/>
-      <c r="Q165" s="8"/>
+      <c r="M165" s="5"/>
+      <c r="N165" s="5"/>
+      <c r="O165" s="5"/>
+      <c r="P165" s="5"/>
+      <c r="Q165" s="5"/>
     </row>
     <row r="166" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M166" s="9" t="s">
+      <c r="M166" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="N166" s="9">
+      <c r="N166" s="6">
         <v>0</v>
       </c>
-      <c r="P166" s="9" t="s">
+      <c r="P166" s="6" t="s">
         <v>52</v>
       </c>
     </row>
@@ -5586,12 +5425,12 @@
         <v>48</v>
       </c>
       <c r="N167" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="169" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B169" s="1"/>
       <c r="C169" s="1"/>
@@ -5604,256 +5443,249 @@
       <c r="J169" s="1"/>
       <c r="K169" s="1"/>
       <c r="L169" s="1"/>
-      <c r="M169" s="8"/>
-      <c r="N169" s="8"/>
-      <c r="O169" s="8"/>
-      <c r="P169" s="8"/>
-      <c r="Q169" s="8"/>
+      <c r="M169" s="5"/>
+      <c r="N169" s="5"/>
+      <c r="O169" s="5"/>
+      <c r="P169" s="5"/>
+      <c r="Q169" s="5"/>
     </row>
     <row r="171" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M171" s="9" t="s">
-        <v>329</v>
-      </c>
-      <c r="N171" s="9">
+      <c r="M171" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="N171" s="6">
         <v>100</v>
       </c>
-      <c r="O171" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="P171" s="9" t="s">
+      <c r="O171" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="P171" s="6" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="172" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H172" s="6" t="s">
-        <v>323</v>
+      <c r="H172" t="s">
+        <v>322</v>
       </c>
       <c r="M172" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="N172">
         <v>88</v>
       </c>
       <c r="O172" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="P172" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="Q172" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="173" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H173" s="6" t="s">
-        <v>322</v>
+      <c r="H173" t="s">
+        <v>321</v>
       </c>
       <c r="M173" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="N173">
         <v>90</v>
       </c>
       <c r="O173" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q173" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="174" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H174" s="6"/>
+        <v>342</v>
+      </c>
     </row>
     <row r="175" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H175" s="6"/>
       <c r="M175" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="N175">
         <v>1.6E-2</v>
       </c>
       <c r="O175" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P175" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="Q175" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="176" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H176" s="6"/>
+        <v>346</v>
+      </c>
     </row>
     <row r="177" spans="1:17" x14ac:dyDescent="0.25">
       <c r="M177" t="s">
-        <v>350</v>
-      </c>
-      <c r="N177" s="13">
+        <v>349</v>
+      </c>
+      <c r="N177" s="10">
         <f>0.16*10.36*0.9</f>
         <v>1.4918400000000001</v>
       </c>
       <c r="O177" t="s">
+        <v>343</v>
+      </c>
+      <c r="P177" t="s">
         <v>344</v>
       </c>
-      <c r="P177" t="s">
+      <c r="Q177" t="s">
         <v>345</v>
       </c>
-      <c r="Q177" t="s">
-        <v>346</v>
-      </c>
     </row>
     <row r="180" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M180" s="9" t="s">
-        <v>331</v>
-      </c>
-      <c r="N180" s="9">
+      <c r="M180" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="N180" s="6">
         <v>-99</v>
       </c>
-      <c r="O180" s="9"/>
-      <c r="P180" s="9" t="s">
-        <v>338</v>
+      <c r="O180" s="6"/>
+      <c r="P180" s="6" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="181" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C181" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="M181" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="N181">
         <v>17</v>
       </c>
       <c r="O181" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q181" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="182" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C182" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="M182" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="N182">
         <v>17</v>
       </c>
       <c r="O182" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q182" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="183" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C183" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="M183" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="N183">
         <v>17</v>
       </c>
       <c r="O183" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q183" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="184" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C184" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="M184" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="N184">
         <v>14</v>
       </c>
       <c r="O184" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q184" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="186" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C186" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="M186" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="N186">
         <v>14</v>
       </c>
       <c r="O186" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q186" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="187" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C187" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="M187" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="N187">
         <v>14</v>
       </c>
       <c r="O187" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q187" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="188" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C188" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="M188" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="N188">
         <v>14</v>
       </c>
       <c r="O188" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q188" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="189" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C189" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="M189" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="N189">
         <v>9</v>
       </c>
       <c r="O189" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q189" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="191" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
@@ -5866,169 +5698,169 @@
       <c r="J191" s="1"/>
       <c r="K191" s="1"/>
       <c r="L191" s="1"/>
-      <c r="M191" s="8"/>
-      <c r="N191" s="8"/>
-      <c r="O191" s="8"/>
-      <c r="P191" s="8"/>
-      <c r="Q191" s="8"/>
+      <c r="M191" s="5"/>
+      <c r="N191" s="5"/>
+      <c r="O191" s="5"/>
+      <c r="P191" s="5"/>
+      <c r="Q191" s="5"/>
     </row>
     <row r="195" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M195" s="9" t="s">
+      <c r="M195" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="N195" s="6">
+        <v>0</v>
+      </c>
+      <c r="O195" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="N195" s="9">
-        <v>0</v>
-      </c>
-      <c r="O195" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="P195" s="9" t="s">
+      <c r="P195" s="6" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="196" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B196" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="M196" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="N196">
         <v>302</v>
       </c>
       <c r="O196" t="s">
+        <v>155</v>
+      </c>
+      <c r="P196" t="s">
         <v>156</v>
       </c>
-      <c r="P196" t="s">
-        <v>157</v>
-      </c>
       <c r="Q196" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="197" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B197" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="M197" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="N197">
         <v>197</v>
       </c>
       <c r="O197" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P197" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Q197" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="198" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B198" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="M198" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="N198">
         <v>216</v>
       </c>
       <c r="O198" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P198" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="Q198" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="199" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B199" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="M199" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="N199">
         <v>216</v>
       </c>
       <c r="O199" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P199" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="Q199" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="200" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B200" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="M200" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="N200">
         <v>216</v>
       </c>
       <c r="O200" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P200" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="Q200" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="201" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B201" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="M201" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="N201">
         <v>216</v>
       </c>
       <c r="O201" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P201" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="Q201" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="202" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B202" t="s">
+        <v>153</v>
+      </c>
+      <c r="M202" t="s">
         <v>154</v>
-      </c>
-      <c r="M202" t="s">
-        <v>155</v>
       </c>
       <c r="N202">
         <v>216</v>
       </c>
       <c r="O202" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P202" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="Q202" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="204" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B204" s="1"/>
       <c r="C204" s="1"/>
@@ -6041,524 +5873,524 @@
       <c r="J204" s="1"/>
       <c r="K204" s="1"/>
       <c r="L204" s="1"/>
-      <c r="M204" s="8"/>
-      <c r="N204" s="8"/>
-      <c r="O204" s="8"/>
-      <c r="P204" s="8"/>
-      <c r="Q204" s="8"/>
+      <c r="M204" s="5"/>
+      <c r="N204" s="5"/>
+      <c r="O204" s="5"/>
+      <c r="P204" s="5"/>
+      <c r="Q204" s="5"/>
     </row>
     <row r="205" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M205" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="N205" s="9">
+      <c r="M205" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="N205" s="6">
         <v>0</v>
       </c>
-      <c r="O205" s="9" t="s">
-        <v>308</v>
-      </c>
-      <c r="P205" s="9" t="s">
+      <c r="O205" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="P205" s="6" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="206" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M206" s="9" t="s">
-        <v>318</v>
-      </c>
-      <c r="N206" s="9">
+      <c r="M206" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="N206" s="6">
         <v>0</v>
       </c>
-      <c r="O206" s="9" t="s">
-        <v>317</v>
-      </c>
-      <c r="P206" s="9" t="s">
+      <c r="O206" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="P206" s="6" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="207" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M207" s="9" t="s">
+      <c r="M207" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="N207" s="6">
+        <v>0</v>
+      </c>
+      <c r="O207" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="N207" s="9">
-        <v>0</v>
-      </c>
-      <c r="O207" s="9" t="s">
-        <v>222</v>
-      </c>
-      <c r="P207" s="9" t="s">
+      <c r="P207" s="6" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="209" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D209" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E209" t="s">
+        <v>196</v>
+      </c>
+      <c r="F209" t="s">
         <v>197</v>
       </c>
-      <c r="F209" t="s">
-        <v>198</v>
-      </c>
       <c r="G209" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="M209" t="s">
-        <v>221</v>
-      </c>
-      <c r="N209" s="25">
+        <v>220</v>
+      </c>
+      <c r="N209" s="20">
         <f>'energy stables'!E24</f>
         <v>3.5302245250431775E-2</v>
       </c>
       <c r="O209" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="P209" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Q209" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="210" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D210" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E210" t="s">
+        <v>196</v>
+      </c>
+      <c r="F210" t="s">
         <v>197</v>
       </c>
-      <c r="F210" t="s">
-        <v>198</v>
-      </c>
       <c r="M210" t="s">
-        <v>219</v>
-      </c>
-      <c r="N210" s="24">
+        <v>218</v>
+      </c>
+      <c r="N210" s="19">
         <f>'energy stables'!D26</f>
         <v>308.33833333333342</v>
       </c>
       <c r="O210" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P210" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Q210" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="211" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D211" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E211" t="s">
+        <v>196</v>
+      </c>
+      <c r="F211" t="s">
         <v>197</v>
       </c>
-      <c r="F211" t="s">
-        <v>198</v>
-      </c>
       <c r="G211" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="M211" t="s">
-        <v>221</v>
-      </c>
-      <c r="N211" s="25">
+        <v>220</v>
+      </c>
+      <c r="N211" s="20">
         <f>'energy stables'!E27</f>
         <v>4.1036269430051814E-2</v>
       </c>
       <c r="O211" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Q211" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="213" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D213" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="M213" t="s">
-        <v>219</v>
-      </c>
-      <c r="N213" s="24">
+        <v>218</v>
+      </c>
+      <c r="N213" s="19">
         <f>'energy stables'!D29</f>
         <v>170.33333333333331</v>
       </c>
       <c r="O213" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P213" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="Q213" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="214" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D214" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="M214" t="s">
-        <v>219</v>
-      </c>
-      <c r="N214" s="24">
+        <v>218</v>
+      </c>
+      <c r="N214" s="19">
         <f>'energy stables'!D31</f>
         <v>332.32333333333338</v>
       </c>
       <c r="O214" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P214" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q214" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="215" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N215" s="24"/>
+      <c r="N215" s="19"/>
     </row>
     <row r="216" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D216" t="s">
+        <v>227</v>
+      </c>
+      <c r="E216" t="s">
         <v>228</v>
       </c>
-      <c r="E216" t="s">
-        <v>229</v>
-      </c>
       <c r="F216" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="M216" t="s">
-        <v>318</v>
-      </c>
-      <c r="N216" s="25">
+        <v>317</v>
+      </c>
+      <c r="N216" s="20">
         <f>(290+1078)/100000</f>
         <v>1.3679999999999999E-2</v>
       </c>
       <c r="O216" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P216" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="Q216" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="217" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D217" t="s">
+        <v>227</v>
+      </c>
+      <c r="E217" t="s">
         <v>228</v>
       </c>
-      <c r="E217" t="s">
-        <v>229</v>
-      </c>
       <c r="F217" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="M217" t="s">
-        <v>318</v>
-      </c>
-      <c r="N217" s="25">
+        <v>317</v>
+      </c>
+      <c r="N217" s="20">
         <f>77000/100000</f>
         <v>0.77</v>
       </c>
       <c r="O217" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="Q217" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="218" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D218" t="s">
+        <v>227</v>
+      </c>
+      <c r="E218" t="s">
         <v>228</v>
       </c>
-      <c r="E218" t="s">
-        <v>229</v>
-      </c>
       <c r="F218" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="M218" t="s">
-        <v>318</v>
-      </c>
-      <c r="N218" s="25">
+        <v>317</v>
+      </c>
+      <c r="N218" s="20">
         <f>(3340+9790)/100000</f>
         <v>0.1313</v>
       </c>
       <c r="O218" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P218" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="Q218" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="220" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D220" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F220" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M220" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="N220">
         <f>'energy stables'!D49</f>
         <v>3.5</v>
       </c>
       <c r="O220" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="Q220" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="221" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D221" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F221" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M221" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="N221">
         <f>'energy stables'!D50</f>
         <v>12.5</v>
       </c>
       <c r="O221" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="Q221" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="222" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D222" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F222" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M222" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="N222">
         <f>'energy stables'!D51</f>
         <v>34</v>
       </c>
       <c r="O222" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="Q222" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="223" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D223" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F223" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M223" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="N223">
         <f>'energy stables'!D53</f>
         <v>0.04</v>
       </c>
       <c r="O223" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="Q223" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="224" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D224" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F224" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M224" t="s">
-        <v>318</v>
-      </c>
-      <c r="N224" s="13">
+        <v>317</v>
+      </c>
+      <c r="N224" s="10">
         <f>'energy stables'!D54</f>
         <v>0.1</v>
       </c>
       <c r="O224" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="Q224" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="225" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D225" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F225" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M225" t="s">
-        <v>318</v>
-      </c>
-      <c r="N225" s="13">
+        <v>317</v>
+      </c>
+      <c r="N225" s="10">
         <f>'energy stables'!D55</f>
         <v>0.26</v>
       </c>
       <c r="O225" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="Q225" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="227" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D227" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E227" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="M227" t="s">
-        <v>219</v>
-      </c>
-      <c r="N227" s="13">
+        <v>218</v>
+      </c>
+      <c r="N227" s="10">
         <f>'energy stables'!D65</f>
         <v>0.14449999999999999</v>
       </c>
       <c r="O227" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P227" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="Q227" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="228" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D228" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E228" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="M228" t="s">
-        <v>219</v>
-      </c>
-      <c r="N228" s="13">
+        <v>218</v>
+      </c>
+      <c r="N228" s="10">
         <f>'energy stables'!D67</f>
         <v>3.9295</v>
       </c>
       <c r="O228" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P228" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="Q228" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="229" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D229" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E229" t="s">
+        <v>353</v>
+      </c>
+      <c r="F229" t="s">
         <v>354</v>
       </c>
-      <c r="F229" t="s">
-        <v>355</v>
-      </c>
       <c r="M229" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="N229">
         <v>0</v>
       </c>
       <c r="O229" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P229" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="230" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D230" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E230" t="s">
+        <v>353</v>
+      </c>
+      <c r="F230" t="s">
         <v>354</v>
       </c>
-      <c r="F230" t="s">
-        <v>355</v>
-      </c>
       <c r="M230" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="N230">
         <v>0</v>
@@ -6569,114 +6401,114 @@
     </row>
     <row r="231" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D231" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E231" t="s">
+        <v>353</v>
+      </c>
+      <c r="F231" t="s">
         <v>354</v>
       </c>
-      <c r="F231" t="s">
-        <v>355</v>
-      </c>
       <c r="M231" t="s">
-        <v>318</v>
-      </c>
-      <c r="N231" s="13">
+        <v>317</v>
+      </c>
+      <c r="N231" s="10">
         <f>4.7*(1/3.6)</f>
         <v>1.3055555555555556</v>
       </c>
       <c r="O231" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P231" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="Q231" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="233" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D233" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="M233" t="s">
-        <v>219</v>
-      </c>
-      <c r="N233" s="24">
+        <v>218</v>
+      </c>
+      <c r="N233" s="19">
         <f>0.05*1000*(1/3.6)</f>
         <v>13.888888888888889</v>
       </c>
       <c r="O233" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P233" t="s">
+        <v>389</v>
+      </c>
+      <c r="Q233" t="s">
         <v>390</v>
-      </c>
-      <c r="Q233" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="234" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D234" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="M234" t="s">
-        <v>219</v>
-      </c>
-      <c r="N234" s="24">
+        <v>218</v>
+      </c>
+      <c r="N234" s="19">
         <f>0.05*1000*(1/3.6)</f>
         <v>13.888888888888889</v>
       </c>
       <c r="O234" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P234" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="Q234" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="235" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D235" t="s">
+        <v>386</v>
+      </c>
+      <c r="F235" t="s">
         <v>387</v>
       </c>
-      <c r="F235" t="s">
-        <v>388</v>
-      </c>
       <c r="M235" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="N235">
         <v>0</v>
       </c>
       <c r="P235" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="236" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D236" t="s">
+        <v>386</v>
+      </c>
+      <c r="F236" t="s">
         <v>387</v>
       </c>
-      <c r="F236" t="s">
-        <v>388</v>
-      </c>
       <c r="M236" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="N236">
         <v>0</v>
@@ -6689,7 +6521,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B3:S75"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -6701,1685 +6533,1597 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B3" s="53" t="s">
+      <c r="B3" s="46" t="s">
+        <v>198</v>
+      </c>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="45"/>
+      <c r="H3" s="45"/>
+      <c r="I3" s="45"/>
+      <c r="J3" s="45"/>
+      <c r="K3" s="45"/>
+      <c r="L3" s="45"/>
+      <c r="M3" s="45"/>
+      <c r="N3" s="45"/>
+      <c r="O3" s="45"/>
+      <c r="P3" s="45"/>
+      <c r="Q3" s="45"/>
+    </row>
+    <row r="4" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B4" s="44" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="5" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B5" s="22"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="40" t="s">
         <v>199</v>
       </c>
-      <c r="C3" s="54"/>
-      <c r="D3" s="54"/>
-      <c r="E3" s="54"/>
-      <c r="F3" s="54"/>
-      <c r="G3" s="54"/>
-      <c r="H3" s="54"/>
-      <c r="I3" s="54"/>
-      <c r="J3" s="54"/>
-      <c r="K3" s="54"/>
-      <c r="L3" s="54"/>
-      <c r="M3" s="54"/>
-      <c r="N3" s="54"/>
-      <c r="O3" s="54"/>
-      <c r="P3" s="54"/>
-      <c r="Q3" s="54"/>
-    </row>
-    <row r="4" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B4" s="51" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B5" s="27"/>
-      <c r="C5" s="30"/>
-      <c r="D5" s="46" t="s">
+      <c r="E5" s="23" t="s">
+        <v>197</v>
+      </c>
+      <c r="F5" s="25" t="s">
+        <v>216</v>
+      </c>
+      <c r="G5" s="24" t="s">
         <v>200</v>
       </c>
-      <c r="E5" s="28" t="s">
-        <v>198</v>
-      </c>
-      <c r="F5" s="30" t="s">
-        <v>217</v>
-      </c>
-      <c r="G5" s="29" t="s">
+      <c r="H5" s="23" t="s">
+        <v>197</v>
+      </c>
+      <c r="I5" s="25" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="6" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B6" s="26" t="s">
         <v>201</v>
       </c>
-      <c r="H5" s="28" t="s">
-        <v>198</v>
-      </c>
-      <c r="I5" s="30" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="6" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B6" s="31" t="s">
+      <c r="C6" s="38" t="s">
+        <v>204</v>
+      </c>
+      <c r="D6" s="26">
+        <v>150</v>
+      </c>
+      <c r="F6" s="27"/>
+      <c r="G6">
+        <v>220</v>
+      </c>
+      <c r="I6" s="27"/>
+    </row>
+    <row r="7" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B7" s="26" t="s">
         <v>202</v>
       </c>
-      <c r="C6" s="44" t="s">
+      <c r="C7" s="38" t="s">
+        <v>204</v>
+      </c>
+      <c r="D7" s="26">
+        <v>150</v>
+      </c>
+      <c r="F7" s="27"/>
+      <c r="G7">
+        <v>220</v>
+      </c>
+      <c r="I7" s="27"/>
+    </row>
+    <row r="8" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B8" s="26" t="s">
+        <v>203</v>
+      </c>
+      <c r="C8" s="38" t="s">
         <v>205</v>
       </c>
-      <c r="D6" s="31">
-        <v>150</v>
-      </c>
-      <c r="E6" s="4"/>
-      <c r="F6" s="32"/>
-      <c r="G6" s="4">
-        <v>220</v>
-      </c>
-      <c r="H6" s="4"/>
-      <c r="I6" s="32"/>
-    </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B7" s="31" t="s">
-        <v>203</v>
-      </c>
-      <c r="C7" s="44" t="s">
-        <v>205</v>
-      </c>
-      <c r="D7" s="31">
-        <v>150</v>
-      </c>
-      <c r="E7" s="4"/>
-      <c r="F7" s="32"/>
-      <c r="G7" s="4">
-        <v>220</v>
-      </c>
-      <c r="H7" s="4"/>
-      <c r="I7" s="32"/>
-    </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B8" s="31" t="s">
-        <v>204</v>
-      </c>
-      <c r="C8" s="44" t="s">
+      <c r="D8" s="26">
+        <v>10500</v>
+      </c>
+      <c r="F8" s="27"/>
+      <c r="G8">
+        <v>8800</v>
+      </c>
+      <c r="I8" s="27"/>
+    </row>
+    <row r="9" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B9" s="26"/>
+      <c r="C9" s="38"/>
+      <c r="D9" s="26"/>
+      <c r="F9" s="27"/>
+      <c r="I9" s="27"/>
+    </row>
+    <row r="10" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B10" s="26" t="s">
         <v>206</v>
       </c>
-      <c r="D8" s="31">
-        <v>10500</v>
-      </c>
-      <c r="E8" s="4"/>
-      <c r="F8" s="32"/>
-      <c r="G8" s="4">
-        <v>8800</v>
-      </c>
-      <c r="H8" s="4"/>
-      <c r="I8" s="32"/>
-    </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B9" s="31"/>
-      <c r="C9" s="44"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="32"/>
-    </row>
-    <row r="10" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B10" s="31" t="s">
-        <v>207</v>
-      </c>
-      <c r="C10" s="44" t="s">
-        <v>216</v>
-      </c>
-      <c r="D10" s="31">
+      <c r="C10" s="38" t="s">
+        <v>215</v>
+      </c>
+      <c r="D10" s="26">
         <v>652</v>
       </c>
-      <c r="E10" s="33">
+      <c r="E10" s="28">
         <f>D10*(2/3)</f>
         <v>434.66666666666663</v>
       </c>
-      <c r="F10" s="34">
+      <c r="F10" s="29">
         <f>D10*(1/3)</f>
         <v>217.33333333333331</v>
       </c>
-      <c r="G10" s="4">
+      <c r="G10">
         <v>370</v>
       </c>
-      <c r="H10" s="33">
+      <c r="H10" s="28">
         <f>G10*(2/3)</f>
         <v>246.66666666666666</v>
       </c>
-      <c r="I10" s="34">
+      <c r="I10" s="29">
         <f>G10*(1/3)</f>
         <v>123.33333333333333</v>
       </c>
-      <c r="J10" s="26" t="s">
-        <v>218</v>
+      <c r="J10" s="21" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B11" s="31" t="s">
-        <v>208</v>
-      </c>
-      <c r="C11" s="44" t="s">
-        <v>216</v>
-      </c>
-      <c r="D11" s="31">
+      <c r="B11" s="26" t="s">
+        <v>207</v>
+      </c>
+      <c r="C11" s="38" t="s">
+        <v>215</v>
+      </c>
+      <c r="D11" s="26">
         <v>3</v>
       </c>
-      <c r="E11" s="33">
+      <c r="E11" s="28">
         <f>(E$17-E$10-E$12-E$14) * (D11/SUM(D$11,D$13,D$15))</f>
         <v>2.1908735632183913</v>
       </c>
-      <c r="F11" s="34">
+      <c r="F11" s="29">
         <f>(F$17-F$10-F$12-F$14) * (D11/SUM(D$11,D$13,D$15))</f>
         <v>0.80912643678160945</v>
       </c>
-      <c r="G11" s="4">
+      <c r="G11">
         <v>74</v>
       </c>
-      <c r="H11" s="33">
+      <c r="H11" s="28">
         <f>(H$17-H$10-H$12-H$14) * (G11/SUM(G$11,G$13,G$15))</f>
         <v>42.039127163280675</v>
       </c>
-      <c r="I11" s="34">
+      <c r="I11" s="29">
         <f>(I$17-I$10-I$12-I$14) * (G11/SUM(G$11,G$13,G$15))</f>
         <v>31.960872836719343</v>
       </c>
-      <c r="J11" s="26"/>
+      <c r="J11" s="21"/>
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B12" s="31" t="s">
-        <v>209</v>
-      </c>
-      <c r="C12" s="44" t="s">
-        <v>216</v>
-      </c>
-      <c r="D12" s="31">
+      <c r="B12" s="26" t="s">
+        <v>208</v>
+      </c>
+      <c r="C12" s="38" t="s">
+        <v>215</v>
+      </c>
+      <c r="D12" s="26">
         <v>40</v>
       </c>
-      <c r="E12" s="33">
+      <c r="E12" s="28">
         <f>D12*(2/3)</f>
         <v>26.666666666666664</v>
       </c>
-      <c r="F12" s="34">
+      <c r="F12" s="29">
         <f>D12*(1/3)</f>
         <v>13.333333333333332</v>
       </c>
-      <c r="G12" s="4">
+      <c r="G12">
         <v>31</v>
       </c>
-      <c r="H12" s="33">
+      <c r="H12" s="28">
         <f>G12*(2/3)</f>
         <v>20.666666666666664</v>
       </c>
-      <c r="I12" s="34">
+      <c r="I12" s="29">
         <f>G12*(1/3)</f>
         <v>10.333333333333332</v>
       </c>
-      <c r="J12" s="26" t="s">
-        <v>218</v>
+      <c r="J12" s="21" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B13" s="31" t="s">
-        <v>210</v>
-      </c>
-      <c r="C13" s="44" t="s">
+      <c r="B13" s="26" t="s">
+        <v>209</v>
+      </c>
+      <c r="C13" s="38" t="s">
+        <v>215</v>
+      </c>
+      <c r="D13" s="26">
         <v>216</v>
       </c>
-      <c r="D13" s="31">
-        <v>216</v>
-      </c>
-      <c r="E13" s="33">
+      <c r="E13" s="28">
         <f>(E$17-E$10-E$12-E$14) * (D13/SUM(D$11,D$13,D$15))</f>
         <v>157.74289655172416</v>
       </c>
-      <c r="F13" s="34">
+      <c r="F13" s="29">
         <f>(F$17-F$10-F$12-F$14) * (D13/SUM(D$11,D$13,D$15))</f>
         <v>58.257103448275878</v>
       </c>
-      <c r="G13" s="4">
+      <c r="G13">
         <v>224</v>
       </c>
-      <c r="H13" s="33">
+      <c r="H13" s="28">
         <f>(H$17-H$10-H$12-H$14) * (G13/SUM(G$11,G$13,G$15))</f>
         <v>127.25357411587665</v>
       </c>
-      <c r="I13" s="34">
+      <c r="I13" s="29">
         <f>(I$17-I$10-I$12-I$14) * (G13/SUM(G$11,G$13,G$15))</f>
         <v>96.746425884123411</v>
       </c>
-      <c r="J13" s="26"/>
+      <c r="J13" s="21"/>
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B14" s="31" t="s">
-        <v>211</v>
-      </c>
-      <c r="C14" s="44" t="s">
-        <v>216</v>
-      </c>
-      <c r="D14" s="31">
+      <c r="B14" s="26" t="s">
+        <v>210</v>
+      </c>
+      <c r="C14" s="38" t="s">
+        <v>215</v>
+      </c>
+      <c r="D14" s="26">
         <v>386</v>
       </c>
-      <c r="E14" s="33">
+      <c r="E14" s="28">
         <f>D14</f>
         <v>386</v>
       </c>
-      <c r="F14" s="34">
+      <c r="F14" s="29">
         <v>0</v>
       </c>
-      <c r="G14" s="4">
+      <c r="G14">
         <v>406</v>
       </c>
-      <c r="H14" s="33">
+      <c r="H14" s="28">
         <f>G14</f>
         <v>406</v>
       </c>
-      <c r="I14" s="34">
+      <c r="I14" s="29">
         <v>0</v>
       </c>
-      <c r="J14" s="26" t="s">
-        <v>224</v>
+      <c r="J14" s="21" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="15" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B15" s="31" t="s">
-        <v>212</v>
-      </c>
-      <c r="C15" s="44" t="s">
+      <c r="B15" s="26" t="s">
+        <v>211</v>
+      </c>
+      <c r="C15" s="38" t="s">
+        <v>215</v>
+      </c>
+      <c r="D15" s="26">
         <v>216</v>
       </c>
-      <c r="D15" s="31">
-        <v>216</v>
-      </c>
-      <c r="E15" s="33">
+      <c r="E15" s="28">
         <f>(E$17-E$10-E$12-E$14) * (D15/SUM(D$11,D$13,D$15))</f>
         <v>157.74289655172416</v>
       </c>
-      <c r="F15" s="34">
+      <c r="F15" s="29">
         <f>(F$17-F$10-F$12-F$14) * (D15/SUM(D$11,D$13,D$15))</f>
         <v>58.257103448275878</v>
       </c>
-      <c r="G15" s="4">
+      <c r="G15">
         <v>145</v>
       </c>
-      <c r="H15" s="33">
+      <c r="H15" s="28">
         <f>(H$17-H$10-H$12-H$14) * (G15/SUM(G$11,G$13,G$15))</f>
         <v>82.373965387509429</v>
       </c>
-      <c r="I15" s="34">
+      <c r="I15" s="29">
         <f>(I$17-I$10-I$12-I$14) * (G15/SUM(G$11,G$13,G$15))</f>
         <v>62.626034612490599</v>
       </c>
     </row>
     <row r="16" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B16" s="31"/>
-      <c r="C16" s="44"/>
-      <c r="D16" s="31"/>
-      <c r="E16" s="35"/>
-      <c r="F16" s="32"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="35"/>
-      <c r="I16" s="32"/>
+      <c r="B16" s="26"/>
+      <c r="C16" s="38"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="27"/>
+      <c r="H16" s="19"/>
+      <c r="I16" s="27"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B17" s="36" t="s">
-        <v>213</v>
-      </c>
-      <c r="C17" s="44" t="s">
-        <v>216</v>
-      </c>
-      <c r="D17" s="36">
+      <c r="B17" s="30" t="s">
+        <v>212</v>
+      </c>
+      <c r="C17" s="38" t="s">
+        <v>215</v>
+      </c>
+      <c r="D17" s="30">
         <f>SUM(D10:D15)</f>
         <v>1513</v>
       </c>
-      <c r="E17" s="38">
+      <c r="E17" s="32">
         <f t="shared" ref="E17" si="0">D17*(1-D$20/100)</f>
         <v>1165.01</v>
       </c>
-      <c r="F17" s="39">
+      <c r="F17" s="33">
         <f>D17*(D$20/100)</f>
         <v>347.99</v>
       </c>
-      <c r="G17" s="37">
+      <c r="G17" s="31">
         <f>SUM(G10:G15)</f>
         <v>1250</v>
       </c>
-      <c r="H17" s="38">
+      <c r="H17" s="32">
         <f t="shared" ref="H17" si="1">G17*(1-G$20/100)</f>
         <v>925</v>
       </c>
-      <c r="I17" s="39">
+      <c r="I17" s="33">
         <f>G17*(G$20/100)</f>
         <v>325</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B18" s="31" t="s">
-        <v>214</v>
-      </c>
-      <c r="C18" s="44" t="s">
-        <v>216</v>
-      </c>
-      <c r="D18" s="31">
+      <c r="B18" s="26" t="s">
+        <v>213</v>
+      </c>
+      <c r="C18" s="38" t="s">
+        <v>215</v>
+      </c>
+      <c r="D18" s="26">
         <v>868</v>
       </c>
-      <c r="E18" s="33">
+      <c r="E18" s="28">
         <f>SUM(E11:E15)</f>
         <v>730.34333333333336</v>
       </c>
-      <c r="F18" s="34">
+      <c r="F18" s="29">
         <f>SUM(F11:F15)</f>
         <v>130.65666666666669</v>
       </c>
-      <c r="G18" s="4">
+      <c r="G18">
         <v>994</v>
       </c>
-      <c r="H18" s="33">
+      <c r="H18" s="28">
         <f>SUM(H11:H15)</f>
         <v>678.33333333333337</v>
       </c>
-      <c r="I18" s="34">
+      <c r="I18" s="29">
         <f>SUM(I11:I15)</f>
         <v>201.66666666666669</v>
       </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B19" s="31"/>
-      <c r="C19" s="44"/>
-      <c r="D19" s="47">
+      <c r="B19" s="26"/>
+      <c r="C19" s="38"/>
+      <c r="D19" s="41">
         <f t="shared" ref="D19:I19" si="2">D18/D17</f>
         <v>0.57369464639788503</v>
       </c>
-      <c r="E19" s="40">
+      <c r="E19" s="34">
         <f t="shared" si="2"/>
         <v>0.62689876767867514</v>
       </c>
-      <c r="F19" s="41">
+      <c r="F19" s="35">
         <f t="shared" si="2"/>
         <v>0.37546098067952149</v>
       </c>
-      <c r="G19" s="40">
+      <c r="G19" s="34">
         <f t="shared" si="2"/>
         <v>0.79520000000000002</v>
       </c>
-      <c r="H19" s="40">
+      <c r="H19" s="34">
         <f t="shared" si="2"/>
         <v>0.73333333333333339</v>
       </c>
-      <c r="I19" s="41">
+      <c r="I19" s="35">
         <f t="shared" si="2"/>
         <v>0.62051282051282053</v>
       </c>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B20" s="42" t="s">
-        <v>215</v>
-      </c>
-      <c r="C20" s="45" t="s">
-        <v>122</v>
-      </c>
-      <c r="D20" s="42">
+      <c r="B20" s="36" t="s">
+        <v>214</v>
+      </c>
+      <c r="C20" s="39" t="s">
+        <v>121</v>
+      </c>
+      <c r="D20" s="36">
         <v>23</v>
       </c>
-      <c r="E20" s="14"/>
-      <c r="F20" s="43"/>
-      <c r="G20" s="14">
+      <c r="E20" s="11"/>
+      <c r="F20" s="37"/>
+      <c r="G20" s="11">
         <v>26</v>
       </c>
-      <c r="H20" s="14"/>
-      <c r="I20" s="43"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="37"/>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B22" s="71" t="s">
-        <v>313</v>
+      <c r="B22" s="63" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B23" s="79"/>
-      <c r="C23" s="80"/>
-      <c r="D23" s="81" t="s">
-        <v>308</v>
-      </c>
-      <c r="E23" s="82" t="s">
-        <v>193</v>
+      <c r="B23" s="71"/>
+      <c r="C23" s="72"/>
+      <c r="D23" s="73" t="s">
+        <v>307</v>
+      </c>
+      <c r="E23" s="74" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B24" s="64" t="s">
-        <v>190</v>
-      </c>
-      <c r="C24" s="65" t="s">
-        <v>202</v>
-      </c>
-      <c r="D24" s="72">
+      <c r="B24" s="56" t="s">
+        <v>189</v>
+      </c>
+      <c r="C24" s="57" t="s">
+        <v>201</v>
+      </c>
+      <c r="D24" s="64">
         <v>0</v>
       </c>
-      <c r="E24" s="73">
+      <c r="E24" s="65">
         <f>(E10+H10)/(D8+G8)</f>
         <v>3.5302245250431775E-2</v>
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B25" s="64" t="s">
-        <v>191</v>
-      </c>
-      <c r="C25" s="65" t="s">
-        <v>202</v>
-      </c>
-      <c r="D25" s="72">
+      <c r="B25" s="56" t="s">
+        <v>190</v>
+      </c>
+      <c r="C25" s="57" t="s">
+        <v>201</v>
+      </c>
+      <c r="D25" s="64">
         <v>0</v>
       </c>
-      <c r="E25" s="74">
+      <c r="E25" s="66">
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B26" s="64" t="s">
-        <v>194</v>
-      </c>
-      <c r="C26" s="65" t="s">
-        <v>202</v>
-      </c>
-      <c r="D26" s="75">
+      <c r="B26" s="56" t="s">
+        <v>193</v>
+      </c>
+      <c r="C26" s="57" t="s">
+        <v>201</v>
+      </c>
+      <c r="D26" s="67">
         <f>SUM(E11:E13,E15,H11:H13,H15)/2</f>
         <v>308.33833333333342</v>
       </c>
-      <c r="E26" s="74">
+      <c r="E26" s="66">
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B27" s="64" t="s">
-        <v>192</v>
-      </c>
-      <c r="C27" s="65" t="s">
-        <v>202</v>
-      </c>
-      <c r="D27" s="72">
+      <c r="B27" s="56" t="s">
+        <v>191</v>
+      </c>
+      <c r="C27" s="57" t="s">
+        <v>201</v>
+      </c>
+      <c r="D27" s="64">
         <v>0</v>
       </c>
-      <c r="E27" s="73">
+      <c r="E27" s="65">
         <f>(E14+H14)/(D8+G8)</f>
         <v>4.1036269430051814E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B28" s="64"/>
-      <c r="C28" s="65"/>
-      <c r="D28" s="72"/>
-      <c r="E28" s="74"/>
+      <c r="B28" s="56"/>
+      <c r="C28" s="57"/>
+      <c r="D28" s="64"/>
+      <c r="E28" s="66"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B29" s="64" t="s">
-        <v>190</v>
-      </c>
-      <c r="C29" s="65" t="s">
-        <v>217</v>
-      </c>
-      <c r="D29" s="75">
+      <c r="B29" s="56" t="s">
+        <v>189</v>
+      </c>
+      <c r="C29" s="57" t="s">
+        <v>216</v>
+      </c>
+      <c r="D29" s="67">
         <f>SUM(F10,I10)/2</f>
         <v>170.33333333333331</v>
       </c>
-      <c r="E29" s="74">
+      <c r="E29" s="66">
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B30" s="64" t="s">
-        <v>191</v>
-      </c>
-      <c r="C30" s="65" t="s">
-        <v>217</v>
-      </c>
-      <c r="D30" s="72">
+      <c r="B30" s="56" t="s">
+        <v>190</v>
+      </c>
+      <c r="C30" s="57" t="s">
+        <v>216</v>
+      </c>
+      <c r="D30" s="64">
         <v>0</v>
       </c>
-      <c r="E30" s="74">
+      <c r="E30" s="66">
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B31" s="64" t="s">
-        <v>194</v>
-      </c>
-      <c r="C31" s="65" t="s">
-        <v>217</v>
-      </c>
-      <c r="D31" s="75">
+      <c r="B31" s="56" t="s">
+        <v>193</v>
+      </c>
+      <c r="C31" s="57" t="s">
+        <v>216</v>
+      </c>
+      <c r="D31" s="67">
         <f>SUM(F11:F13,F15,I11:I13,I15)</f>
         <v>332.32333333333338</v>
       </c>
-      <c r="E31" s="74">
+      <c r="E31" s="66">
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B32" s="66" t="s">
-        <v>192</v>
-      </c>
-      <c r="C32" s="67" t="s">
-        <v>217</v>
-      </c>
-      <c r="D32" s="76">
+      <c r="B32" s="58" t="s">
+        <v>191</v>
+      </c>
+      <c r="C32" s="59" t="s">
+        <v>216</v>
+      </c>
+      <c r="D32" s="68">
         <v>0</v>
       </c>
-      <c r="E32" s="77">
+      <c r="E32" s="69">
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B34" s="53" t="s">
-        <v>236</v>
-      </c>
-      <c r="C34" s="54"/>
-      <c r="D34" s="54"/>
-      <c r="E34" s="54"/>
-      <c r="F34" s="54"/>
-      <c r="G34" s="54"/>
-      <c r="H34" s="54"/>
-      <c r="I34" s="54"/>
-      <c r="J34" s="54"/>
-      <c r="K34" s="54"/>
-      <c r="L34" s="54"/>
-      <c r="M34" s="54"/>
-      <c r="N34" s="54"/>
-      <c r="O34" s="54"/>
-      <c r="P34" s="54"/>
-      <c r="Q34" s="54"/>
+      <c r="B34" s="46" t="s">
+        <v>235</v>
+      </c>
+      <c r="C34" s="45"/>
+      <c r="D34" s="45"/>
+      <c r="E34" s="45"/>
+      <c r="F34" s="45"/>
+      <c r="G34" s="45"/>
+      <c r="H34" s="45"/>
+      <c r="I34" s="45"/>
+      <c r="J34" s="45"/>
+      <c r="K34" s="45"/>
+      <c r="L34" s="45"/>
+      <c r="M34" s="45"/>
+      <c r="N34" s="45"/>
+      <c r="O34" s="45"/>
+      <c r="P34" s="45"/>
+      <c r="Q34" s="45"/>
     </row>
     <row r="35" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="J35" s="51" t="s">
-        <v>226</v>
+      <c r="J35" s="44" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="36" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="J36" s="46" t="s">
+      <c r="J36" s="40" t="s">
+        <v>290</v>
+      </c>
+      <c r="K36" s="23"/>
+      <c r="L36" s="23"/>
+      <c r="M36" s="24" t="s">
+        <v>295</v>
+      </c>
+      <c r="N36" s="24" t="s">
+        <v>296</v>
+      </c>
+      <c r="O36" s="24" t="s">
+        <v>297</v>
+      </c>
+      <c r="P36" s="43" t="s">
+        <v>298</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="44" t="s">
+        <v>245</v>
+      </c>
+      <c r="J37" s="36" t="s">
+        <v>246</v>
+      </c>
+      <c r="K37" s="11"/>
+      <c r="L37" s="11"/>
+      <c r="M37" s="51" t="s">
         <v>291</v>
       </c>
-      <c r="K36" s="28"/>
-      <c r="L36" s="28"/>
-      <c r="M36" s="29" t="s">
-        <v>296</v>
-      </c>
-      <c r="N36" s="29" t="s">
-        <v>297</v>
-      </c>
-      <c r="O36" s="29" t="s">
-        <v>298</v>
-      </c>
-      <c r="P36" s="50" t="s">
-        <v>299</v>
-      </c>
-      <c r="Q36" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="37" spans="2:19" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="51" t="s">
-        <v>246</v>
-      </c>
-      <c r="J37" s="42" t="s">
+      <c r="N37" s="51" t="s">
+        <v>292</v>
+      </c>
+      <c r="O37" s="51" t="s">
+        <v>293</v>
+      </c>
+      <c r="P37" s="52" t="s">
+        <v>294</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="38" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B38" s="40" t="s">
+        <v>237</v>
+      </c>
+      <c r="C38" s="24"/>
+      <c r="D38" s="24" t="s">
+        <v>239</v>
+      </c>
+      <c r="E38" s="43" t="s">
+        <v>240</v>
+      </c>
+      <c r="J38" s="26" t="s">
+        <v>250</v>
+      </c>
+      <c r="M38">
+        <v>90</v>
+      </c>
+      <c r="N38">
+        <v>13</v>
+      </c>
+      <c r="O38">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="P38" s="27">
+        <v>242</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>304</v>
+      </c>
+      <c r="R38" s="50"/>
+      <c r="S38" s="50"/>
+    </row>
+    <row r="39" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="26" t="s">
+        <v>241</v>
+      </c>
+      <c r="D39">
+        <v>50</v>
+      </c>
+      <c r="E39" s="27">
+        <v>0.4</v>
+      </c>
+      <c r="J39" s="26" t="s">
+        <v>251</v>
+      </c>
+      <c r="M39">
+        <v>654</v>
+      </c>
+      <c r="N39">
+        <v>80</v>
+      </c>
+      <c r="O39">
+        <v>9.6</v>
+      </c>
+      <c r="P39" s="27" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>304</v>
+      </c>
+      <c r="R39" s="50"/>
+      <c r="S39" s="50"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B40" s="26" t="s">
+        <v>242</v>
+      </c>
+      <c r="D40">
+        <v>36.5</v>
+      </c>
+      <c r="E40" s="27">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="J40" s="26" t="s">
+        <v>254</v>
+      </c>
+      <c r="M40">
+        <v>11</v>
+      </c>
+      <c r="N40">
+        <v>12</v>
+      </c>
+      <c r="O40">
+        <v>0.1</v>
+      </c>
+      <c r="P40" s="27">
+        <v>43.2</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>304</v>
+      </c>
+      <c r="R40" s="50"/>
+      <c r="S40" s="50"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B41" s="26" t="s">
+        <v>243</v>
+      </c>
+      <c r="D41">
+        <v>9.5</v>
+      </c>
+      <c r="E41" s="27">
+        <v>0.06</v>
+      </c>
+      <c r="J41" s="26" t="s">
+        <v>284</v>
+      </c>
+      <c r="M41">
+        <v>244</v>
+      </c>
+      <c r="N41">
+        <v>78</v>
+      </c>
+      <c r="O41">
+        <v>1.8</v>
+      </c>
+      <c r="P41" s="27">
+        <v>340</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>304</v>
+      </c>
+      <c r="R41" s="50"/>
+      <c r="S41" s="50"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B42" s="26" t="s">
+        <v>244</v>
+      </c>
+      <c r="D42">
+        <v>3.5</v>
+      </c>
+      <c r="E42" s="27">
+        <v>0.04</v>
+      </c>
+      <c r="J42" s="26" t="s">
         <v>247</v>
       </c>
-      <c r="K37" s="14"/>
-      <c r="L37" s="14"/>
-      <c r="M37" s="59" t="s">
-        <v>292</v>
-      </c>
-      <c r="N37" s="59" t="s">
-        <v>293</v>
-      </c>
-      <c r="O37" s="59" t="s">
-        <v>294</v>
-      </c>
-      <c r="P37" s="60" t="s">
-        <v>295</v>
-      </c>
-      <c r="Q37" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B38" s="46" t="s">
+      <c r="M42">
+        <v>992</v>
+      </c>
+      <c r="N42">
+        <v>93</v>
+      </c>
+      <c r="O42">
+        <v>4.2</v>
+      </c>
+      <c r="P42" s="27" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>304</v>
+      </c>
+      <c r="R42" s="50"/>
+      <c r="S42" s="50"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B43" s="36" t="s">
         <v>238</v>
       </c>
-      <c r="C38" s="29"/>
-      <c r="D38" s="29" t="s">
-        <v>240</v>
-      </c>
-      <c r="E38" s="50" t="s">
-        <v>241</v>
-      </c>
-      <c r="J38" s="31" t="s">
-        <v>251</v>
-      </c>
-      <c r="K38" s="4"/>
-      <c r="L38" s="4"/>
-      <c r="M38" s="4">
-        <v>90</v>
-      </c>
-      <c r="N38" s="4">
-        <v>13</v>
-      </c>
-      <c r="O38" s="4">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="P38" s="32">
-        <v>242</v>
-      </c>
-      <c r="Q38" t="s">
-        <v>305</v>
-      </c>
-      <c r="R38" s="58"/>
-      <c r="S38" s="58"/>
-    </row>
-    <row r="39" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="31" t="s">
-        <v>242</v>
-      </c>
-      <c r="C39" s="4"/>
-      <c r="D39" s="4">
-        <v>50</v>
-      </c>
-      <c r="E39" s="32">
-        <v>0.4</v>
-      </c>
-      <c r="J39" s="31" t="s">
-        <v>252</v>
-      </c>
-      <c r="K39" s="4"/>
-      <c r="L39" s="4"/>
-      <c r="M39" s="4">
-        <v>654</v>
-      </c>
-      <c r="N39" s="4">
-        <v>80</v>
-      </c>
-      <c r="O39" s="4">
-        <v>9.6</v>
-      </c>
-      <c r="P39" s="32" t="s">
-        <v>254</v>
-      </c>
-      <c r="Q39" t="s">
-        <v>305</v>
-      </c>
-      <c r="R39" s="58"/>
-      <c r="S39" s="58"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B40" s="31" t="s">
-        <v>243</v>
-      </c>
-      <c r="C40" s="4"/>
-      <c r="D40" s="4">
-        <v>36.5</v>
-      </c>
-      <c r="E40" s="32">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="J40" s="31" t="s">
-        <v>255</v>
-      </c>
-      <c r="K40" s="4"/>
-      <c r="L40" s="4"/>
-      <c r="M40" s="4">
-        <v>11</v>
-      </c>
-      <c r="N40" s="4">
-        <v>12</v>
-      </c>
-      <c r="O40" s="4">
-        <v>0.1</v>
-      </c>
-      <c r="P40" s="32">
-        <v>43.2</v>
-      </c>
-      <c r="Q40" t="s">
-        <v>305</v>
-      </c>
-      <c r="R40" s="58"/>
-      <c r="S40" s="58"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B41" s="31" t="s">
-        <v>244</v>
-      </c>
-      <c r="C41" s="4"/>
-      <c r="D41" s="4">
-        <v>9.5</v>
-      </c>
-      <c r="E41" s="32">
-        <v>0.06</v>
-      </c>
-      <c r="J41" s="31" t="s">
-        <v>285</v>
-      </c>
-      <c r="K41" s="4"/>
-      <c r="L41" s="4"/>
-      <c r="M41" s="4">
-        <v>244</v>
-      </c>
-      <c r="N41" s="4">
-        <v>78</v>
-      </c>
-      <c r="O41" s="4">
-        <v>1.8</v>
-      </c>
-      <c r="P41" s="32">
-        <v>340</v>
-      </c>
-      <c r="Q41" t="s">
-        <v>305</v>
-      </c>
-      <c r="R41" s="58"/>
-      <c r="S41" s="58"/>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B42" s="31" t="s">
-        <v>245</v>
-      </c>
-      <c r="C42" s="4"/>
-      <c r="D42" s="4">
-        <v>3.5</v>
-      </c>
-      <c r="E42" s="32">
-        <v>0.04</v>
-      </c>
-      <c r="J42" s="31" t="s">
-        <v>248</v>
-      </c>
-      <c r="K42" s="4"/>
-      <c r="L42" s="4"/>
-      <c r="M42" s="4">
-        <v>992</v>
-      </c>
-      <c r="N42" s="4">
-        <v>93</v>
-      </c>
-      <c r="O42" s="4">
-        <v>4.2</v>
-      </c>
-      <c r="P42" s="32" t="s">
-        <v>249</v>
-      </c>
-      <c r="Q42" t="s">
-        <v>305</v>
-      </c>
-      <c r="R42" s="58"/>
-      <c r="S42" s="58"/>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B43" s="42" t="s">
-        <v>239</v>
-      </c>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14">
+      <c r="C43" s="11"/>
+      <c r="D43" s="11">
         <v>0.5</v>
       </c>
-      <c r="E43" s="43">
+      <c r="E43" s="37">
         <v>0.02</v>
       </c>
-      <c r="J43" s="31"/>
-      <c r="M43" s="58">
+      <c r="J43" s="26"/>
+      <c r="M43" s="50">
         <f>M42/M49</f>
         <v>0.40772708590217838</v>
       </c>
-      <c r="N43" s="58">
+      <c r="N43" s="50">
         <f t="shared" ref="N43:O43" si="3">N42/N49</f>
         <v>0.13497822931785197</v>
       </c>
-      <c r="O43" s="58">
+      <c r="O43" s="50">
         <f t="shared" si="3"/>
         <v>0.21319796954314724</v>
       </c>
-      <c r="P43" s="32"/>
-      <c r="Q43" s="92">
+      <c r="P43" s="27"/>
+      <c r="Q43" s="82">
         <f>AVERAGE(M43:O43)</f>
         <v>0.25196776158772582</v>
       </c>
-      <c r="R43" s="58"/>
-      <c r="S43" s="58"/>
+      <c r="R43" s="50"/>
+      <c r="S43" s="50"/>
     </row>
     <row r="44" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="C44" s="68" t="s">
-        <v>309</v>
-      </c>
-      <c r="D44" s="69">
+      <c r="C44" s="60" t="s">
+        <v>308</v>
+      </c>
+      <c r="D44" s="61">
         <f>D39*33+E39*26</f>
         <v>1660.4</v>
       </c>
-      <c r="E44" s="70" t="s">
+      <c r="E44" s="62" t="s">
+        <v>309</v>
+      </c>
+      <c r="J44" s="26" t="s">
+        <v>260</v>
+      </c>
+      <c r="M44" t="s">
+        <v>261</v>
+      </c>
+      <c r="N44">
+        <v>4</v>
+      </c>
+      <c r="O44" t="s">
+        <v>262</v>
+      </c>
+      <c r="P44" s="27" t="s">
+        <v>263</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>304</v>
+      </c>
+      <c r="R44" s="50"/>
+      <c r="S44" s="50"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="J45" s="26" t="s">
+        <v>264</v>
+      </c>
+      <c r="M45">
+        <v>79</v>
+      </c>
+      <c r="N45">
+        <v>7</v>
+      </c>
+      <c r="O45">
+        <v>0.7</v>
+      </c>
+      <c r="P45" s="27" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>304</v>
+      </c>
+      <c r="R45" s="50"/>
+      <c r="S45" s="50"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B46" s="63" t="s">
+        <v>312</v>
+      </c>
+      <c r="J46" s="26" t="s">
+        <v>266</v>
+      </c>
+      <c r="M46" t="s">
+        <v>83</v>
+      </c>
+      <c r="N46">
+        <v>11</v>
+      </c>
+      <c r="O46" t="s">
+        <v>83</v>
+      </c>
+      <c r="P46" s="27" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>304</v>
+      </c>
+      <c r="R46" s="50"/>
+      <c r="S46" s="50"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B47" s="22"/>
+      <c r="C47" s="23"/>
+      <c r="D47" s="76" t="s">
+        <v>314</v>
+      </c>
+      <c r="E47" s="23" t="s">
+        <v>311</v>
+      </c>
+      <c r="F47" s="23"/>
+      <c r="G47" s="23"/>
+      <c r="H47" s="25"/>
+      <c r="J47" s="26" t="s">
+        <v>267</v>
+      </c>
+      <c r="M47">
+        <v>38</v>
+      </c>
+      <c r="N47">
+        <v>15</v>
+      </c>
+      <c r="O47" t="s">
+        <v>268</v>
+      </c>
+      <c r="P47" s="27" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>304</v>
+      </c>
+      <c r="R47" s="50"/>
+      <c r="S47" s="50"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B48" s="36"/>
+      <c r="C48" s="11"/>
+      <c r="D48" s="77" t="s">
+        <v>315</v>
+      </c>
+      <c r="E48" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="F48" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="G48" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="H48" s="37" t="s">
+        <v>140</v>
+      </c>
+      <c r="J48" s="26" t="s">
+        <v>249</v>
+      </c>
+      <c r="M48">
+        <v>164</v>
+      </c>
+      <c r="N48">
+        <v>66</v>
+      </c>
+      <c r="O48">
+        <v>1</v>
+      </c>
+      <c r="P48" s="27" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>304</v>
+      </c>
+      <c r="R48" s="50"/>
+      <c r="S48" s="50"/>
+    </row>
+    <row r="49" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B49" s="75" t="s">
+        <v>189</v>
+      </c>
+      <c r="C49" s="23" t="s">
         <v>310</v>
       </c>
-      <c r="J44" s="31" t="s">
-        <v>261</v>
-      </c>
-      <c r="K44" s="4"/>
-      <c r="L44" s="4"/>
-      <c r="M44" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="N44" s="4">
-        <v>4</v>
-      </c>
-      <c r="O44" s="4" t="s">
-        <v>263</v>
-      </c>
-      <c r="P44" s="32" t="s">
-        <v>264</v>
-      </c>
-      <c r="Q44" t="s">
-        <v>305</v>
-      </c>
-      <c r="R44" s="58"/>
-      <c r="S44" s="58"/>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="J45" s="31" t="s">
-        <v>265</v>
-      </c>
-      <c r="K45" s="4"/>
-      <c r="L45" s="4"/>
-      <c r="M45" s="4">
-        <v>79</v>
-      </c>
-      <c r="N45" s="4">
-        <v>7</v>
-      </c>
-      <c r="O45" s="4">
-        <v>0.7</v>
-      </c>
-      <c r="P45" s="32" t="s">
-        <v>254</v>
-      </c>
-      <c r="Q45" t="s">
-        <v>305</v>
-      </c>
-      <c r="R45" s="58"/>
-      <c r="S45" s="58"/>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B46" s="71" t="s">
-        <v>313</v>
-      </c>
-      <c r="J46" s="31" t="s">
-        <v>267</v>
-      </c>
-      <c r="K46" s="4"/>
-      <c r="L46" s="4"/>
-      <c r="M46" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="N46" s="4">
-        <v>11</v>
-      </c>
-      <c r="O46" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="P46" s="32" t="s">
-        <v>254</v>
-      </c>
-      <c r="Q46" t="s">
-        <v>305</v>
-      </c>
-      <c r="R46" s="58"/>
-      <c r="S46" s="58"/>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B47" s="27"/>
-      <c r="C47" s="28"/>
-      <c r="D47" s="86" t="s">
-        <v>315</v>
-      </c>
-      <c r="E47" s="28" t="s">
-        <v>312</v>
-      </c>
-      <c r="F47" s="28"/>
-      <c r="G47" s="28"/>
-      <c r="H47" s="30"/>
-      <c r="J47" s="31" t="s">
-        <v>268</v>
-      </c>
-      <c r="K47" s="4"/>
-      <c r="L47" s="4"/>
-      <c r="M47" s="4">
-        <v>38</v>
-      </c>
-      <c r="N47" s="4">
-        <v>15</v>
-      </c>
-      <c r="O47" s="4" t="s">
-        <v>269</v>
-      </c>
-      <c r="P47" s="32" t="s">
-        <v>254</v>
-      </c>
-      <c r="Q47" t="s">
-        <v>305</v>
-      </c>
-      <c r="R47" s="58"/>
-      <c r="S47" s="58"/>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B48" s="42"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="87" t="s">
-        <v>316</v>
-      </c>
-      <c r="E48" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="F48" s="83" t="s">
-        <v>144</v>
-      </c>
-      <c r="G48" s="83" t="s">
-        <v>145</v>
-      </c>
-      <c r="H48" s="84" t="s">
-        <v>141</v>
-      </c>
-      <c r="J48" s="31" t="s">
-        <v>250</v>
-      </c>
-      <c r="K48" s="4"/>
-      <c r="L48" s="4"/>
-      <c r="M48" s="4">
-        <v>164</v>
-      </c>
-      <c r="N48" s="4">
-        <v>66</v>
-      </c>
-      <c r="O48" s="4">
-        <v>1</v>
-      </c>
-      <c r="P48" s="32" t="s">
-        <v>254</v>
-      </c>
-      <c r="Q48" t="s">
-        <v>305</v>
-      </c>
-      <c r="R48" s="58"/>
-      <c r="S48" s="58"/>
-    </row>
-    <row r="49" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B49" s="85" t="s">
-        <v>190</v>
-      </c>
-      <c r="C49" s="28" t="s">
-        <v>311</v>
-      </c>
-      <c r="D49" s="88">
+      <c r="D49" s="78">
         <f>D42</f>
         <v>3.5</v>
       </c>
-      <c r="E49" s="75">
+      <c r="E49" s="67">
         <v>100</v>
       </c>
-      <c r="F49" s="75">
+      <c r="F49" s="67">
         <v>0</v>
       </c>
-      <c r="G49" s="75">
+      <c r="G49" s="67">
         <v>0</v>
       </c>
-      <c r="H49" s="78">
+      <c r="H49" s="70">
         <v>0</v>
       </c>
-      <c r="J49" s="46" t="s">
-        <v>271</v>
-      </c>
-      <c r="K49" s="29"/>
-      <c r="L49" s="29"/>
-      <c r="M49" s="29">
+      <c r="J49" s="40" t="s">
+        <v>270</v>
+      </c>
+      <c r="K49" s="24"/>
+      <c r="L49" s="24"/>
+      <c r="M49" s="24">
         <v>2433</v>
       </c>
-      <c r="N49" s="29">
+      <c r="N49" s="24">
         <v>689</v>
       </c>
-      <c r="O49" s="29">
+      <c r="O49" s="24">
         <v>19.7</v>
       </c>
-      <c r="P49" s="50">
+      <c r="P49" s="43">
         <v>1252</v>
       </c>
       <c r="Q49" t="s">
-        <v>305</v>
-      </c>
-      <c r="R49" s="58"/>
-      <c r="S49" s="58"/>
+        <v>304</v>
+      </c>
+      <c r="R49" s="50"/>
+      <c r="S49" s="50"/>
     </row>
     <row r="50" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B50" s="31" t="s">
-        <v>191</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>311</v>
-      </c>
-      <c r="D50" s="88">
+      <c r="B50" s="26" t="s">
+        <v>190</v>
+      </c>
+      <c r="C50" t="s">
+        <v>310</v>
+      </c>
+      <c r="D50" s="78">
         <f>D39*0.25</f>
         <v>12.5</v>
       </c>
-      <c r="E50" s="75">
+      <c r="E50" s="67">
         <v>0</v>
       </c>
-      <c r="F50" s="75">
+      <c r="F50" s="67">
         <f>D43/D50*100</f>
         <v>4</v>
       </c>
-      <c r="G50" s="75">
+      <c r="G50" s="67">
         <f>D41/D50*100</f>
         <v>76</v>
       </c>
-      <c r="H50" s="78">
+      <c r="H50" s="70">
         <f>(D40-D51)/D50*100</f>
         <v>20</v>
       </c>
-      <c r="J50" s="31" t="s">
-        <v>273</v>
-      </c>
-      <c r="K50" s="4"/>
-      <c r="L50" s="4"/>
-      <c r="M50" s="4">
+      <c r="J50" s="26" t="s">
+        <v>272</v>
+      </c>
+      <c r="M50">
         <v>1441</v>
       </c>
-      <c r="N50" s="4">
+      <c r="N50">
         <v>689</v>
       </c>
-      <c r="O50" s="4">
+      <c r="O50">
         <v>15.5</v>
       </c>
-      <c r="P50" s="32">
+      <c r="P50" s="27">
         <v>1218</v>
       </c>
-      <c r="R50" s="58"/>
-      <c r="S50" s="58"/>
+      <c r="R50" s="50"/>
+      <c r="S50" s="50"/>
     </row>
     <row r="51" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B51" s="31" t="s">
-        <v>194</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>311</v>
-      </c>
-      <c r="D51" s="89">
+      <c r="B51" s="26" t="s">
+        <v>193</v>
+      </c>
+      <c r="C51" t="s">
+        <v>310</v>
+      </c>
+      <c r="D51" s="79">
         <f>D39-D49-D50</f>
         <v>34</v>
       </c>
-      <c r="E51" s="72">
+      <c r="E51" s="64">
         <v>0</v>
       </c>
-      <c r="F51" s="72">
+      <c r="F51" s="64">
         <v>0</v>
       </c>
-      <c r="G51" s="72">
+      <c r="G51" s="64">
         <v>0</v>
       </c>
-      <c r="H51" s="74">
+      <c r="H51" s="66">
         <v>100</v>
       </c>
-      <c r="J51" s="61" t="s">
-        <v>307</v>
-      </c>
-      <c r="K51" s="63"/>
-      <c r="L51" s="63"/>
-      <c r="M51" s="63">
+      <c r="J51" s="53" t="s">
+        <v>306</v>
+      </c>
+      <c r="K51" s="55"/>
+      <c r="L51" s="55"/>
+      <c r="M51" s="55">
         <f>M49-M50</f>
         <v>992</v>
       </c>
-      <c r="N51" s="63">
+      <c r="N51" s="55">
         <f>N49-N50</f>
         <v>0</v>
       </c>
-      <c r="O51" s="63">
+      <c r="O51" s="55">
         <f>O49-O50</f>
         <v>4.1999999999999993</v>
       </c>
-      <c r="P51" s="62">
+      <c r="P51" s="54">
         <f>P49-P50</f>
         <v>34</v>
       </c>
       <c r="Q51" t="s">
+        <v>304</v>
+      </c>
+      <c r="R51" s="50"/>
+      <c r="S51" s="50"/>
+    </row>
+    <row r="52" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B52" s="26"/>
+      <c r="D52" s="78"/>
+      <c r="E52" s="64"/>
+      <c r="F52" s="64"/>
+      <c r="G52" s="64"/>
+      <c r="H52" s="66"/>
+      <c r="J52" s="47" t="s">
+        <v>289</v>
+      </c>
+      <c r="K52" s="48"/>
+      <c r="L52" s="48"/>
+      <c r="M52" s="48">
+        <v>23</v>
+      </c>
+      <c r="N52" s="48">
+        <v>38</v>
+      </c>
+      <c r="O52" s="48" t="s">
+        <v>83</v>
+      </c>
+      <c r="P52" s="49" t="s">
         <v>305</v>
       </c>
-      <c r="R51" s="58"/>
-      <c r="S51" s="58"/>
-    </row>
-    <row r="52" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B52" s="31"/>
-      <c r="C52" s="4"/>
-      <c r="D52" s="88"/>
-      <c r="E52" s="72"/>
-      <c r="F52" s="72"/>
-      <c r="G52" s="72"/>
-      <c r="H52" s="74"/>
-      <c r="J52" s="55" t="s">
-        <v>290</v>
-      </c>
-      <c r="K52" s="56"/>
-      <c r="L52" s="56"/>
-      <c r="M52" s="56">
-        <v>23</v>
-      </c>
-      <c r="N52" s="56">
-        <v>38</v>
-      </c>
-      <c r="O52" s="56" t="s">
-        <v>83</v>
-      </c>
-      <c r="P52" s="57" t="s">
-        <v>306</v>
-      </c>
       <c r="Q52" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="53" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B53" s="64" t="s">
-        <v>190</v>
-      </c>
-      <c r="C53" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="D53" s="88">
+      <c r="B53" s="56" t="s">
+        <v>189</v>
+      </c>
+      <c r="C53" t="s">
+        <v>313</v>
+      </c>
+      <c r="D53" s="78">
         <f>E42</f>
         <v>0.04</v>
       </c>
-      <c r="E53" s="75">
+      <c r="E53" s="67">
         <v>100</v>
       </c>
-      <c r="F53" s="75">
+      <c r="F53" s="67">
         <v>0</v>
       </c>
-      <c r="G53" s="75">
+      <c r="G53" s="67">
         <v>0</v>
       </c>
-      <c r="H53" s="78">
+      <c r="H53" s="70">
         <v>0</v>
       </c>
-      <c r="J53" s="31" t="s">
+      <c r="J53" s="26" t="s">
+        <v>277</v>
+      </c>
+      <c r="M53" t="s">
         <v>278</v>
       </c>
-      <c r="K53" s="4"/>
-      <c r="L53" s="4"/>
-      <c r="M53" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="N53" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="O53" s="4" t="s">
+      <c r="N53" t="s">
+        <v>278</v>
+      </c>
+      <c r="O53" t="s">
         <v>83</v>
       </c>
-      <c r="P53" s="32" t="s">
-        <v>279</v>
+      <c r="P53" s="27" t="s">
+        <v>278</v>
       </c>
       <c r="Q53" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="54" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B54" s="31" t="s">
-        <v>191</v>
-      </c>
-      <c r="C54" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="D54" s="90">
+      <c r="B54" s="26" t="s">
+        <v>190</v>
+      </c>
+      <c r="C54" t="s">
+        <v>313</v>
+      </c>
+      <c r="D54" s="80">
         <f>E39*0.25</f>
         <v>0.1</v>
       </c>
-      <c r="E54" s="75">
+      <c r="E54" s="67">
         <v>0</v>
       </c>
-      <c r="F54" s="75">
+      <c r="F54" s="67">
         <f>E43/D54*100</f>
         <v>20</v>
       </c>
-      <c r="G54" s="75">
+      <c r="G54" s="67">
         <f>E41/D54*100</f>
         <v>60</v>
       </c>
-      <c r="H54" s="78">
+      <c r="H54" s="70">
         <f>(E40-D55)/D54*100</f>
         <v>20.000000000000018</v>
       </c>
-      <c r="J54" s="31" t="s">
-        <v>301</v>
-      </c>
-      <c r="K54" s="4"/>
-      <c r="L54" s="4"/>
-      <c r="M54" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="N54" s="4" t="s">
+      <c r="J54" s="26" t="s">
+        <v>300</v>
+      </c>
+      <c r="M54" t="s">
+        <v>278</v>
+      </c>
+      <c r="N54" t="s">
+        <v>303</v>
+      </c>
+      <c r="O54" t="s">
+        <v>83</v>
+      </c>
+      <c r="P54" s="27" t="s">
+        <v>278</v>
+      </c>
+      <c r="Q54" t="s">
         <v>304</v>
       </c>
-      <c r="O54" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="P54" s="32" t="s">
-        <v>279</v>
-      </c>
-      <c r="Q54" t="s">
-        <v>305</v>
-      </c>
     </row>
     <row r="55" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B55" s="42" t="s">
-        <v>194</v>
-      </c>
-      <c r="C55" s="14" t="s">
-        <v>314</v>
-      </c>
-      <c r="D55" s="91">
+      <c r="B55" s="36" t="s">
+        <v>193</v>
+      </c>
+      <c r="C55" s="11" t="s">
+        <v>313</v>
+      </c>
+      <c r="D55" s="81">
         <f>E39-D53-D54</f>
         <v>0.26</v>
       </c>
-      <c r="E55" s="76">
+      <c r="E55" s="68">
         <v>0</v>
       </c>
-      <c r="F55" s="76">
+      <c r="F55" s="68">
         <v>0</v>
       </c>
-      <c r="G55" s="76">
+      <c r="G55" s="68">
         <v>0</v>
       </c>
-      <c r="H55" s="77">
+      <c r="H55" s="69">
         <v>100</v>
       </c>
-      <c r="J55" s="31" t="s">
+      <c r="J55" s="26" t="s">
+        <v>301</v>
+      </c>
+      <c r="M55" t="s">
+        <v>278</v>
+      </c>
+      <c r="O55" t="s">
+        <v>278</v>
+      </c>
+      <c r="P55" s="27" t="s">
+        <v>278</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="56" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="J56" s="36" t="s">
         <v>302</v>
       </c>
-      <c r="K55" s="4"/>
-      <c r="L55" s="4"/>
-      <c r="M55" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="N55" s="4"/>
-      <c r="O55" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="P55" s="32" t="s">
-        <v>279</v>
-      </c>
-      <c r="Q55" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="56" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="J56" s="42" t="s">
-        <v>303</v>
-      </c>
-      <c r="K56" s="14"/>
-      <c r="L56" s="14"/>
-      <c r="M56" s="14">
+      <c r="K56" s="11"/>
+      <c r="L56" s="11"/>
+      <c r="M56" s="11">
         <v>1998</v>
       </c>
-      <c r="N56" s="14">
+      <c r="N56" s="11">
         <v>1999</v>
       </c>
-      <c r="O56" s="14">
+      <c r="O56" s="11">
         <v>1998</v>
       </c>
-      <c r="P56" s="43">
+      <c r="P56" s="37">
         <v>2008</v>
       </c>
     </row>
     <row r="58" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B58" s="53" t="s">
+      <c r="B58" s="46" t="s">
+        <v>381</v>
+      </c>
+      <c r="C58" s="45"/>
+      <c r="D58" s="45"/>
+      <c r="E58" s="45"/>
+      <c r="F58" s="45"/>
+      <c r="G58" s="45"/>
+      <c r="H58" s="45"/>
+      <c r="I58" s="45"/>
+      <c r="J58" s="45"/>
+      <c r="K58" s="45"/>
+      <c r="L58" s="45"/>
+      <c r="M58" s="45"/>
+      <c r="N58" s="45"/>
+      <c r="O58" s="45"/>
+      <c r="P58" s="45"/>
+      <c r="Q58" s="45"/>
+    </row>
+    <row r="59" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="J59" s="44" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="60" spans="2:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J60" s="22" t="s">
+        <v>290</v>
+      </c>
+      <c r="K60" s="23"/>
+      <c r="L60" s="23"/>
+      <c r="M60" s="93" t="s">
+        <v>372</v>
+      </c>
+      <c r="N60" s="93"/>
+      <c r="O60" s="93" t="s">
+        <v>373</v>
+      </c>
+      <c r="P60" s="94"/>
+    </row>
+    <row r="61" spans="2:19" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J61" s="90" t="s">
+        <v>379</v>
+      </c>
+      <c r="K61" s="11"/>
+      <c r="L61" s="11"/>
+      <c r="M61" s="91" t="s">
+        <v>374</v>
+      </c>
+      <c r="N61" s="91"/>
+      <c r="O61" s="91" t="s">
+        <v>363</v>
+      </c>
+      <c r="P61" s="92"/>
+    </row>
+    <row r="62" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B62" s="63" t="s">
         <v>382</v>
       </c>
-      <c r="C58" s="52"/>
-      <c r="D58" s="52"/>
-      <c r="E58" s="52"/>
-      <c r="F58" s="52"/>
-      <c r="G58" s="52"/>
-      <c r="H58" s="52"/>
-      <c r="I58" s="52"/>
-      <c r="J58" s="52"/>
-      <c r="K58" s="52"/>
-      <c r="L58" s="52"/>
-      <c r="M58" s="52"/>
-      <c r="N58" s="52"/>
-      <c r="O58" s="52"/>
-      <c r="P58" s="52"/>
-      <c r="Q58" s="52"/>
-    </row>
-    <row r="59" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="J59" s="51" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="60" spans="2:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J60" s="27" t="s">
-        <v>291</v>
-      </c>
-      <c r="K60" s="28"/>
-      <c r="L60" s="28"/>
-      <c r="M60" s="103" t="s">
-        <v>373</v>
-      </c>
-      <c r="N60" s="103"/>
-      <c r="O60" s="103" t="s">
-        <v>374</v>
-      </c>
-      <c r="P60" s="104"/>
-      <c r="Q60" s="4"/>
-    </row>
-    <row r="61" spans="2:19" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J61" s="100" t="s">
+      <c r="J62" s="22" t="s">
+        <v>250</v>
+      </c>
+      <c r="K62" s="23"/>
+      <c r="L62" s="23"/>
+      <c r="M62" s="23">
+        <v>130</v>
+      </c>
+      <c r="N62" s="86" t="s">
+        <v>357</v>
+      </c>
+      <c r="O62" s="23">
+        <v>106</v>
+      </c>
+      <c r="P62" s="87" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="63" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B63" s="22"/>
+      <c r="C63" s="23"/>
+      <c r="D63" s="76" t="s">
+        <v>314</v>
+      </c>
+      <c r="E63" s="23" t="s">
+        <v>311</v>
+      </c>
+      <c r="F63" s="23"/>
+      <c r="G63" s="23"/>
+      <c r="H63" s="25"/>
+      <c r="J63" s="26" t="s">
+        <v>251</v>
+      </c>
+      <c r="M63">
+        <v>1250</v>
+      </c>
+      <c r="O63">
+        <v>2156</v>
+      </c>
+      <c r="P63" s="27"/>
+    </row>
+    <row r="64" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B64" s="36"/>
+      <c r="C64" s="11"/>
+      <c r="D64" s="77" t="s">
         <v>380</v>
       </c>
-      <c r="K61" s="14"/>
-      <c r="L61" s="14"/>
-      <c r="M61" s="101" t="s">
-        <v>375</v>
-      </c>
-      <c r="N61" s="101"/>
-      <c r="O61" s="101" t="s">
-        <v>364</v>
-      </c>
-      <c r="P61" s="102"/>
-      <c r="Q61" s="4"/>
-    </row>
-    <row r="62" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B62" s="71" t="s">
-        <v>383</v>
-      </c>
-      <c r="J62" s="27" t="s">
-        <v>251</v>
-      </c>
-      <c r="K62" s="28"/>
-      <c r="L62" s="28"/>
-      <c r="M62" s="28">
-        <v>130</v>
-      </c>
-      <c r="N62" s="96" t="s">
-        <v>358</v>
-      </c>
-      <c r="O62" s="28">
-        <v>106</v>
-      </c>
-      <c r="P62" s="97" t="s">
-        <v>359</v>
-      </c>
-      <c r="Q62" s="4"/>
-    </row>
-    <row r="63" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B63" s="27"/>
-      <c r="C63" s="28"/>
-      <c r="D63" s="86" t="s">
-        <v>315</v>
-      </c>
-      <c r="E63" s="28" t="s">
-        <v>312</v>
-      </c>
-      <c r="F63" s="28"/>
-      <c r="G63" s="28"/>
-      <c r="H63" s="30"/>
-      <c r="J63" s="31" t="s">
-        <v>252</v>
-      </c>
-      <c r="K63" s="4"/>
-      <c r="L63" s="4"/>
-      <c r="M63" s="4">
-        <v>1250</v>
-      </c>
-      <c r="N63" s="4"/>
-      <c r="O63" s="4">
-        <v>2156</v>
-      </c>
-      <c r="P63" s="32"/>
-      <c r="Q63" s="4"/>
-    </row>
-    <row r="64" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B64" s="42"/>
-      <c r="C64" s="14"/>
-      <c r="D64" s="87" t="s">
-        <v>381</v>
-      </c>
-      <c r="E64" s="14" t="s">
+      <c r="E64" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="F64" s="83" t="s">
+      <c r="F64" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="G64" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="G64" s="83" t="s">
-        <v>145</v>
-      </c>
-      <c r="H64" s="84" t="s">
-        <v>141</v>
-      </c>
-      <c r="J64" s="31" t="s">
-        <v>255</v>
-      </c>
-      <c r="K64" s="4"/>
-      <c r="L64" s="4"/>
-      <c r="M64" s="4">
+      <c r="H64" s="37" t="s">
+        <v>140</v>
+      </c>
+      <c r="J64" s="26" t="s">
+        <v>254</v>
+      </c>
+      <c r="M64">
         <v>11</v>
       </c>
-      <c r="N64" s="4"/>
-      <c r="O64" s="4">
+      <c r="O64">
         <v>42</v>
       </c>
-      <c r="P64" s="32"/>
-      <c r="Q64" s="4"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B65" s="85" t="s">
-        <v>190</v>
-      </c>
-      <c r="C65" s="28"/>
-      <c r="D65" s="90">
+      <c r="P64" s="27"/>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B65" s="75" t="s">
+        <v>189</v>
+      </c>
+      <c r="C65" s="23"/>
+      <c r="D65" s="80">
         <f>SUM(M62,O62,M64,O64)/2/1000</f>
         <v>0.14449999999999999</v>
       </c>
-      <c r="E65" s="75">
+      <c r="E65" s="67">
         <v>10</v>
       </c>
-      <c r="F65" s="75">
+      <c r="F65" s="67">
         <v>0</v>
       </c>
-      <c r="G65" s="75">
+      <c r="G65" s="67">
         <v>0</v>
       </c>
-      <c r="H65" s="78">
+      <c r="H65" s="70">
         <v>90</v>
       </c>
-      <c r="J65" s="31" t="s">
+      <c r="J65" s="26" t="s">
+        <v>359</v>
+      </c>
+      <c r="M65">
+        <v>1454</v>
+      </c>
+      <c r="O65">
+        <v>2431</v>
+      </c>
+      <c r="P65" s="27"/>
+    </row>
+    <row r="66" spans="2:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B66" s="26" t="s">
+        <v>190</v>
+      </c>
+      <c r="D66" s="78">
+        <v>0</v>
+      </c>
+      <c r="E66" s="67"/>
+      <c r="F66" s="67"/>
+      <c r="G66" s="67"/>
+      <c r="H66" s="70"/>
+      <c r="J66" s="84" t="s">
         <v>360</v>
       </c>
-      <c r="K65" s="4"/>
-      <c r="L65" s="4"/>
-      <c r="M65" s="4">
-        <v>1454</v>
-      </c>
-      <c r="N65" s="4"/>
-      <c r="O65" s="4">
-        <v>2431</v>
-      </c>
-      <c r="P65" s="32"/>
-      <c r="Q65" s="4"/>
-    </row>
-    <row r="66" spans="2:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B66" s="31" t="s">
-        <v>191</v>
-      </c>
-      <c r="C66" s="4"/>
-      <c r="D66" s="88">
-        <v>0</v>
-      </c>
-      <c r="E66" s="75"/>
-      <c r="F66" s="75"/>
-      <c r="G66" s="75"/>
-      <c r="H66" s="78"/>
-      <c r="J66" s="94" t="s">
+      <c r="K66" s="85"/>
+      <c r="L66" s="85"/>
+      <c r="M66" s="85" t="s">
         <v>361</v>
       </c>
-      <c r="K66" s="95"/>
-      <c r="L66" s="95"/>
-      <c r="M66" s="95" t="s">
+      <c r="N66" s="85"/>
+      <c r="O66" s="85" t="s">
         <v>362</v>
       </c>
-      <c r="N66" s="95"/>
-      <c r="O66" s="95" t="s">
-        <v>363</v>
-      </c>
-      <c r="P66" s="44"/>
-      <c r="Q66" s="4"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B67" s="42" t="s">
-        <v>194</v>
-      </c>
-      <c r="C67" s="14"/>
-      <c r="D67" s="91">
+      <c r="P66" s="38"/>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B67" s="36" t="s">
+        <v>193</v>
+      </c>
+      <c r="C67" s="11"/>
+      <c r="D67" s="81">
         <f>SUM(M63,O63,M65,O65,M67,O67,M68,O68,O69,O70,M71,O71)/2/1000</f>
         <v>3.9295</v>
       </c>
-      <c r="E67" s="76">
+      <c r="E67" s="68">
         <v>0</v>
       </c>
-      <c r="F67" s="76">
+      <c r="F67" s="68">
         <v>0</v>
       </c>
-      <c r="G67" s="76">
+      <c r="G67" s="68">
         <v>0</v>
       </c>
-      <c r="H67" s="77">
+      <c r="H67" s="69">
         <v>100</v>
       </c>
-      <c r="J67" s="31" t="s">
+      <c r="J67" s="26" t="s">
+        <v>365</v>
+      </c>
+      <c r="M67">
+        <v>29</v>
+      </c>
+      <c r="O67">
+        <v>26</v>
+      </c>
+      <c r="P67" s="27"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="J68" s="26" t="s">
         <v>366</v>
       </c>
-      <c r="K67" s="4"/>
-      <c r="L67" s="4"/>
-      <c r="M67" s="4">
-        <v>29</v>
-      </c>
-      <c r="N67" s="4"/>
-      <c r="O67" s="4">
-        <v>26</v>
-      </c>
-      <c r="P67" s="32"/>
-      <c r="Q67" s="4"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="J68" s="31" t="s">
+      <c r="M68">
+        <v>16</v>
+      </c>
+      <c r="O68">
+        <v>36</v>
+      </c>
+      <c r="P68" s="27"/>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="J69" s="26" t="s">
         <v>367</v>
       </c>
-      <c r="K68" s="4"/>
-      <c r="L68" s="4"/>
-      <c r="M68" s="4">
-        <v>16</v>
-      </c>
-      <c r="N68" s="4"/>
-      <c r="O68" s="4">
-        <v>36</v>
-      </c>
-      <c r="P68" s="32"/>
-      <c r="Q68" s="4"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="J69" s="31" t="s">
+      <c r="M69" t="s">
         <v>368</v>
       </c>
-      <c r="K69" s="4"/>
-      <c r="L69" s="4"/>
-      <c r="M69" s="4" t="s">
+      <c r="O69">
+        <v>150</v>
+      </c>
+      <c r="P69" s="27"/>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="J70" s="26" t="s">
         <v>369</v>
       </c>
-      <c r="N69" s="4"/>
-      <c r="O69" s="4">
-        <v>150</v>
-      </c>
-      <c r="P69" s="32"/>
-      <c r="Q69" s="4"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="J70" s="31" t="s">
+      <c r="M70" t="s">
         <v>370</v>
       </c>
-      <c r="K70" s="4"/>
-      <c r="L70" s="4"/>
-      <c r="M70" s="4" t="s">
+      <c r="O70">
+        <v>18</v>
+      </c>
+      <c r="P70" s="27"/>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="J71" s="26" t="s">
+        <v>249</v>
+      </c>
+      <c r="M71">
+        <v>228</v>
+      </c>
+      <c r="O71">
+        <v>65</v>
+      </c>
+      <c r="P71" s="27"/>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="J72" s="88" t="s">
         <v>371</v>
       </c>
-      <c r="N70" s="4"/>
-      <c r="O70" s="4">
-        <v>18</v>
-      </c>
-      <c r="P70" s="32"/>
-      <c r="Q70" s="4"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="J71" s="31" t="s">
-        <v>250</v>
-      </c>
-      <c r="K71" s="4"/>
-      <c r="L71" s="4"/>
-      <c r="M71" s="4">
-        <v>228</v>
-      </c>
-      <c r="N71" s="4"/>
-      <c r="O71" s="4">
-        <v>65</v>
-      </c>
-      <c r="P71" s="32"/>
-      <c r="Q71" s="4"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="J72" s="98" t="s">
-        <v>372</v>
-      </c>
-      <c r="K72" s="93"/>
-      <c r="L72" s="93"/>
-      <c r="M72" s="93">
+      <c r="K72" s="83"/>
+      <c r="L72" s="83"/>
+      <c r="M72" s="83">
         <v>3118</v>
       </c>
-      <c r="N72" s="93"/>
-      <c r="O72" s="93">
+      <c r="N72" s="83"/>
+      <c r="O72" s="83">
         <v>5030</v>
       </c>
-      <c r="P72" s="99"/>
-      <c r="Q72" s="4"/>
-    </row>
-    <row r="73" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J73" s="55" t="s">
+      <c r="P72" s="89"/>
+    </row>
+    <row r="73" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J73" s="47" t="s">
+        <v>375</v>
+      </c>
+      <c r="K73" s="48"/>
+      <c r="L73" s="48"/>
+      <c r="M73" s="48" t="s">
         <v>376</v>
       </c>
-      <c r="K73" s="56"/>
-      <c r="L73" s="56"/>
-      <c r="M73" s="56" t="s">
+      <c r="N73" s="48"/>
+      <c r="O73" s="48" t="s">
         <v>377</v>
       </c>
-      <c r="N73" s="56"/>
-      <c r="O73" s="56" t="s">
+      <c r="P73" s="49"/>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="J74" s="26" t="s">
+        <v>364</v>
+      </c>
+      <c r="M74" t="s">
         <v>378</v>
       </c>
-      <c r="P73" s="57"/>
-      <c r="Q73" s="4"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="J74" s="31" t="s">
-        <v>365</v>
-      </c>
-      <c r="K74" s="4"/>
-      <c r="L74" s="4"/>
-      <c r="M74" s="4" t="s">
-        <v>379</v>
-      </c>
-      <c r="N74" s="4"/>
-      <c r="O74" s="4">
+      <c r="O74">
         <v>10</v>
       </c>
-      <c r="P74" s="32"/>
-      <c r="Q74" s="4"/>
-    </row>
-    <row r="75" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J75" s="55" t="s">
-        <v>303</v>
-      </c>
-      <c r="K75" s="56"/>
-      <c r="L75" s="56"/>
-      <c r="M75" s="56">
+      <c r="P74" s="27"/>
+    </row>
+    <row r="75" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J75" s="47" t="s">
+        <v>302</v>
+      </c>
+      <c r="K75" s="48"/>
+      <c r="L75" s="48"/>
+      <c r="M75" s="48">
         <v>2004</v>
       </c>
-      <c r="N75" s="56"/>
-      <c r="O75" s="56">
+      <c r="N75" s="48"/>
+      <c r="O75" s="48">
         <v>2003</v>
       </c>
-      <c r="P75" s="57"/>
-      <c r="Q75" s="4"/>
+      <c r="P75" s="49"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -8395,7 +8139,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="E3:T17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -8404,7 +8148,7 @@
   <sheetData>
     <row r="3" spans="5:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F3">
         <v>90</v>
@@ -8421,7 +8165,7 @@
     </row>
     <row r="4" spans="5:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F4">
         <v>654</v>
@@ -8430,15 +8174,15 @@
         <v>80</v>
       </c>
       <c r="H4" t="s">
+        <v>252</v>
+      </c>
+      <c r="I4" t="s">
         <v>253</v>
-      </c>
-      <c r="I4" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="5" spans="5:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E5" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F5">
         <v>11</v>
@@ -8447,66 +8191,66 @@
         <v>12</v>
       </c>
       <c r="H5" t="s">
+        <v>255</v>
+      </c>
+      <c r="I5" t="s">
         <v>256</v>
-      </c>
-      <c r="I5" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="6" spans="5:20" x14ac:dyDescent="0.25">
       <c r="E6" t="s">
+        <v>284</v>
+      </c>
+      <c r="F6" t="s">
         <v>285</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>286</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>287</v>
       </c>
-      <c r="H6" t="s">
+      <c r="I6" t="s">
         <v>288</v>
-      </c>
-      <c r="I6" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="7" spans="5:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E7" t="s">
+        <v>247</v>
+      </c>
+      <c r="G7" t="s">
+        <v>257</v>
+      </c>
+      <c r="I7" t="s">
+        <v>258</v>
+      </c>
+      <c r="O7" t="s">
+        <v>259</v>
+      </c>
+      <c r="S7" t="s">
         <v>248</v>
-      </c>
-      <c r="G7" t="s">
-        <v>258</v>
-      </c>
-      <c r="I7" t="s">
-        <v>259</v>
-      </c>
-      <c r="O7" t="s">
-        <v>260</v>
-      </c>
-      <c r="S7" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="8" spans="5:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E8" t="s">
+        <v>260</v>
+      </c>
+      <c r="H8" t="s">
         <v>261</v>
-      </c>
-      <c r="H8" t="s">
-        <v>262</v>
       </c>
       <c r="K8">
         <v>4</v>
       </c>
       <c r="P8" t="s">
+        <v>262</v>
+      </c>
+      <c r="T8" t="s">
         <v>263</v>
-      </c>
-      <c r="T8" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="9" spans="5:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H9">
         <v>79</v>
@@ -8515,15 +8259,15 @@
         <v>7</v>
       </c>
       <c r="P9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="T9" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="10" spans="5:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E10" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H10" t="s">
         <v>83</v>
@@ -8535,12 +8279,12 @@
         <v>83</v>
       </c>
       <c r="T10" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="11" spans="5:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E11" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H11">
         <v>38</v>
@@ -8549,15 +8293,15 @@
         <v>15</v>
       </c>
       <c r="P11" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="T11" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="12" spans="5:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E12" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H12">
         <v>164</v>
@@ -8566,15 +8310,15 @@
         <v>66</v>
       </c>
       <c r="P12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="T12" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="13" spans="5:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E13" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H13">
         <v>2433</v>
@@ -8583,7 +8327,7 @@
         <v>689</v>
       </c>
       <c r="P13" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="T13">
         <v>1252</v>
@@ -8591,7 +8335,7 @@
     </row>
     <row r="14" spans="5:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E14" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H14">
         <v>1441</v>
@@ -8600,7 +8344,7 @@
         <v>689</v>
       </c>
       <c r="P14" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="T14">
         <v>1218</v>
@@ -8608,47 +8352,47 @@
     </row>
     <row r="15" spans="5:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E15" t="s">
+        <v>274</v>
+      </c>
+      <c r="L15" t="s">
         <v>275</v>
       </c>
-      <c r="L15" t="s">
+      <c r="Q15" t="s">
         <v>276</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="16" spans="5:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E16" t="s">
+        <v>277</v>
+      </c>
+      <c r="H16" t="s">
         <v>278</v>
       </c>
-      <c r="H16" t="s">
-        <v>279</v>
-      </c>
       <c r="K16" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P16" t="s">
         <v>83</v>
       </c>
       <c r="T16" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="17" spans="5:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E17" t="s">
+        <v>279</v>
+      </c>
+      <c r="H17" t="s">
         <v>280</v>
       </c>
-      <c r="H17" t="s">
+      <c r="K17" t="s">
         <v>281</v>
       </c>
-      <c r="K17" t="s">
+      <c r="P17" t="s">
         <v>282</v>
       </c>
-      <c r="P17" t="s">
+      <c r="T17" t="s">
         <v>283</v>
-      </c>
-      <c r="T17" t="s">
-        <v>284</v>
       </c>
     </row>
   </sheetData>
@@ -8658,7 +8402,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="C3:J21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -8667,47 +8411,47 @@
   <sheetData>
     <row r="3" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
-        <v>291</v>
-      </c>
-      <c r="F3" s="49" t="s">
+        <v>290</v>
+      </c>
+      <c r="F3" s="31" t="s">
+        <v>295</v>
+      </c>
+      <c r="G3" s="31" t="s">
         <v>296</v>
       </c>
-      <c r="G3" s="49" t="s">
+      <c r="H3" s="31" t="s">
         <v>297</v>
       </c>
-      <c r="H3" s="49" t="s">
+      <c r="I3" s="31" t="s">
         <v>298</v>
       </c>
-      <c r="I3" s="49" t="s">
-        <v>299</v>
-      </c>
       <c r="J3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="4" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F4" t="s">
+        <v>291</v>
+      </c>
+      <c r="G4" t="s">
         <v>292</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>293</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>294</v>
       </c>
-      <c r="I4" t="s">
-        <v>295</v>
-      </c>
       <c r="J4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="5" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F5">
         <v>90</v>
@@ -8722,12 +8466,12 @@
         <v>242</v>
       </c>
       <c r="J5" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="6" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F6">
         <v>654</v>
@@ -8739,15 +8483,15 @@
         <v>9.6</v>
       </c>
       <c r="I6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="J6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="7" spans="3:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F7">
         <v>11</v>
@@ -8762,12 +8506,12 @@
         <v>43.2</v>
       </c>
       <c r="J7" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="8" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F8">
         <v>244</v>
@@ -8782,12 +8526,12 @@
         <v>340</v>
       </c>
       <c r="J8" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="9" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F9">
         <v>992</v>
@@ -8799,35 +8543,35 @@
         <v>4.2</v>
       </c>
       <c r="I9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="J9" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="10" spans="3:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
+        <v>260</v>
+      </c>
+      <c r="F10" t="s">
         <v>261</v>
-      </c>
-      <c r="F10" t="s">
-        <v>262</v>
       </c>
       <c r="G10">
         <v>4</v>
       </c>
       <c r="H10" t="s">
+        <v>262</v>
+      </c>
+      <c r="I10" t="s">
         <v>263</v>
       </c>
-      <c r="I10" t="s">
-        <v>264</v>
-      </c>
       <c r="J10" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="11" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F11">
         <v>79</v>
@@ -8839,15 +8583,15 @@
         <v>0.7</v>
       </c>
       <c r="I11" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="J11" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="12" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F12" t="s">
         <v>83</v>
@@ -8859,15 +8603,15 @@
         <v>83</v>
       </c>
       <c r="I12" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="J12" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="13" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F13">
         <v>38</v>
@@ -8876,18 +8620,18 @@
         <v>15</v>
       </c>
       <c r="H13" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="I13" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="J13" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="14" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F14">
         <v>164</v>
@@ -8899,15 +8643,15 @@
         <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="J14" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="15" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F15">
         <v>2433</v>
@@ -8922,12 +8666,12 @@
         <v>1252</v>
       </c>
       <c r="J15" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="16" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C16" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F16">
         <v>1441</v>
@@ -8942,12 +8686,12 @@
         <v>1218</v>
       </c>
       <c r="J16" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="17" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C17" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F17">
         <v>23</v>
@@ -8959,72 +8703,72 @@
         <v>83</v>
       </c>
       <c r="I17" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="J17" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="18" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C18" t="s">
+        <v>277</v>
+      </c>
+      <c r="F18" t="s">
         <v>278</v>
       </c>
-      <c r="F18" t="s">
-        <v>279</v>
-      </c>
       <c r="G18" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H18" t="s">
         <v>83</v>
       </c>
       <c r="I18" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J18" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="19" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C19" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F19" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G19" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H19" t="s">
         <v>83</v>
       </c>
       <c r="I19" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J19" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="20" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C20" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F20" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H20" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="I20" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J20" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="21" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C21" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F21">
         <v>1998</v>
@@ -9039,7 +8783,7 @@
         <v>2008</v>
       </c>
       <c r="J21" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
   </sheetData>
@@ -9049,78 +8793,78 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:A14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="13" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="14" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" s="14" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="14" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="14" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" s="14" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" s="14" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" s="14" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" s="42" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" s="42" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" s="42" t="s">
         <v>393</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="16" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="17" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="17" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="17" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="17" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="17" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="17" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="17" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="48" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="48" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="48" t="s">
-        <v>394</v>
       </c>
     </row>
   </sheetData>

--- a/data/default/MachineryAndEnergyMgmt.xlsx
+++ b/data/default/MachineryAndEnergyMgmt.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9514D7D-5125-4D6B-8BC7-778C4FFA1644}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57F4B909-423C-4DE0-937A-1B1785C1C46E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25320" yWindow="2055" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="default" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
     <sheet name="Sheet2" sheetId="5" r:id="rId4"/>
     <sheet name="references" sheetId="2" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029" iterate="1" concurrentCalc="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -489,7 +489,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1349" uniqueCount="419">
   <si>
     <t>f_crop</t>
   </si>
@@ -1139,21 +1139,6 @@
     <t>Energy use in greenhouses</t>
   </si>
   <si>
-    <r>
-      <t>Fuel combustion emission factors</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (add non-GHG compounds?)</t>
-    </r>
-  </si>
-  <si>
     <t>f_species</t>
   </si>
   <si>
@@ -1876,6 +1861,57 @@
   </si>
   <si>
     <t>ASABE. (2006). Agricultural Machinery Management Data. In. ASABE, St. Joseph, MI, USA: American Society of Agricultural Engineers</t>
+  </si>
+  <si>
+    <t>CO</t>
+  </si>
+  <si>
+    <t>NOx</t>
+  </si>
+  <si>
+    <t>SO2</t>
+  </si>
+  <si>
+    <t>NMVOC</t>
+  </si>
+  <si>
+    <t>PM</t>
+  </si>
+  <si>
+    <t>NH3</t>
+  </si>
+  <si>
+    <t>Fuel combustion emission factors</t>
+  </si>
+  <si>
+    <t>Miljöfaktaboken 2011. Tabell 54</t>
+  </si>
+  <si>
+    <t>Diesel (5 vol% RME), Användning i lätt lastbil</t>
+  </si>
+  <si>
+    <t>Naturgas, Användning i ett specifikt kombikraftverk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eldningsolja 1-5, Användning i storskaligt värmeverk (generellt) </t>
+  </si>
+  <si>
+    <t>Miljöfaktaboken 2011. Tabell 27</t>
+  </si>
+  <si>
+    <t>Miljöfaktaboken 2011. Tabell 30</t>
+  </si>
+  <si>
+    <t>Pellets &amp; briketter från sågverksrester, Användning i  villapanna</t>
+  </si>
+  <si>
+    <t>Miljöfaktaboken 2011. Tabell 11</t>
+  </si>
+  <si>
+    <t>VOC, Pellets &amp; briketter från sågverksrester, Användning i  villapanna</t>
+  </si>
+  <si>
+    <t>No fossil CO2 assumed</t>
   </si>
 </sst>
 </file>
@@ -2683,7 +2719,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q236"/>
+  <dimension ref="A1:Q266"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="8" max="12" width="12.28515625" customWidth="1"/>
@@ -2702,19 +2738,19 @@
         <v>0</v>
       </c>
       <c r="C1" s="83" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D1" s="83" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E1" s="83" t="s">
+        <v>193</v>
+      </c>
+      <c r="F1" s="83" t="s">
         <v>194</v>
       </c>
-      <c r="F1" s="83" t="s">
-        <v>195</v>
-      </c>
       <c r="G1" s="83" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H1" s="83" t="s">
         <v>139</v>
@@ -2766,7 +2802,7 @@
         <v>142</v>
       </c>
       <c r="H4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="M4" t="s">
         <v>146</v>
@@ -2787,7 +2823,7 @@
         <v>142</v>
       </c>
       <c r="H5" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="M5" t="s">
         <v>146</v>
@@ -2808,7 +2844,7 @@
         <v>142</v>
       </c>
       <c r="H6" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="M6" t="s">
         <v>146</v>
@@ -2825,7 +2861,7 @@
         <v>142</v>
       </c>
       <c r="H7" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="M7" t="s">
         <v>146</v>
@@ -2842,13 +2878,13 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D9" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="M9" t="s">
         <v>146</v>
@@ -2862,22 +2898,22 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="N10" s="7"/>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D11" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H11" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="M11" t="s">
         <v>146</v>
@@ -2891,13 +2927,13 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D12" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H12" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="M12" t="s">
         <v>146</v>
@@ -2914,16 +2950,16 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D14" t="s">
+        <v>226</v>
+      </c>
+      <c r="E14" t="s">
         <v>227</v>
       </c>
-      <c r="E14" t="s">
-        <v>228</v>
-      </c>
       <c r="H14" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="M14" t="s">
         <v>146</v>
@@ -2937,16 +2973,16 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D15" t="s">
+        <v>226</v>
+      </c>
+      <c r="E15" t="s">
         <v>227</v>
       </c>
-      <c r="E15" t="s">
-        <v>228</v>
-      </c>
       <c r="H15" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="M15" t="s">
         <v>146</v>
@@ -2960,16 +2996,16 @@
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D16" t="s">
+        <v>226</v>
+      </c>
+      <c r="E16" t="s">
         <v>227</v>
       </c>
-      <c r="E16" t="s">
-        <v>228</v>
-      </c>
       <c r="H16" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="M16" t="s">
         <v>146</v>
@@ -2986,16 +3022,16 @@
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D18" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F18" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H18" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="M18" t="s">
         <v>146</v>
@@ -3007,21 +3043,21 @@
         <v>121</v>
       </c>
       <c r="Q18" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D19" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F19" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H19" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="M19" t="s">
         <v>146</v>
@@ -3033,21 +3069,21 @@
         <v>121</v>
       </c>
       <c r="Q19" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D20" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F20" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H20" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="M20" t="s">
         <v>146</v>
@@ -3059,21 +3095,21 @@
         <v>121</v>
       </c>
       <c r="Q20" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D21" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F21" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H21" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="M21" t="s">
         <v>146</v>
@@ -3085,21 +3121,21 @@
         <v>121</v>
       </c>
       <c r="Q21" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D22" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F22" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H22" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="M22" t="s">
         <v>146</v>
@@ -3111,21 +3147,21 @@
         <v>121</v>
       </c>
       <c r="Q22" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D23" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F23" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H23" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="M23" t="s">
         <v>146</v>
@@ -3137,21 +3173,21 @@
         <v>121</v>
       </c>
       <c r="Q23" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D24" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F24" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H24" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="M24" t="s">
         <v>146</v>
@@ -3163,21 +3199,21 @@
         <v>121</v>
       </c>
       <c r="Q24" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D25" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F25" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H25" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="M25" t="s">
         <v>146</v>
@@ -3189,21 +3225,21 @@
         <v>121</v>
       </c>
       <c r="Q25" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D26" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F26" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H26" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="M26" t="s">
         <v>146</v>
@@ -3215,21 +3251,21 @@
         <v>121</v>
       </c>
       <c r="Q26" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D27" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F27" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H27" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="M27" t="s">
         <v>146</v>
@@ -3241,7 +3277,7 @@
         <v>121</v>
       </c>
       <c r="Q27" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
@@ -3249,16 +3285,16 @@
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D29" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E29" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H29" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="M29" t="s">
         <v>146</v>
@@ -3272,16 +3308,16 @@
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D30" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E30" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H30" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="M30" t="s">
         <v>146</v>
@@ -3295,16 +3331,16 @@
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D31" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E31" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H31" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="M31" t="s">
         <v>146</v>
@@ -3318,16 +3354,16 @@
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D32" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E32" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H32" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="M32" t="s">
         <v>146</v>
@@ -3339,21 +3375,21 @@
         <v>121</v>
       </c>
       <c r="Q32" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D33" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E33" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H33" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="M33" t="s">
         <v>146</v>
@@ -3365,7 +3401,7 @@
         <v>121</v>
       </c>
       <c r="Q33" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
@@ -3373,13 +3409,13 @@
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D35" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H35" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="M35" t="s">
         <v>146</v>
@@ -3391,18 +3427,18 @@
         <v>121</v>
       </c>
       <c r="Q35" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D36" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H36" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="M36" t="s">
         <v>146</v>
@@ -3414,7 +3450,7 @@
         <v>121</v>
       </c>
       <c r="Q36" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
@@ -3425,7 +3461,7 @@
         <v>145</v>
       </c>
       <c r="H38" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="M38" t="s">
         <v>146</v>
@@ -3445,7 +3481,7 @@
         <v>145</v>
       </c>
       <c r="H39" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="M39" t="s">
         <v>146</v>
@@ -3468,7 +3504,7 @@
         <v>145</v>
       </c>
       <c r="H40" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="M40" t="s">
         <v>146</v>
@@ -3491,7 +3527,7 @@
         <v>145</v>
       </c>
       <c r="H41" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="M41" t="s">
         <v>146</v>
@@ -3508,7 +3544,7 @@
         <v>145</v>
       </c>
       <c r="H42" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="M42" t="s">
         <v>146</v>
@@ -3525,7 +3561,7 @@
         <v>145</v>
       </c>
       <c r="H43" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="M43" t="s">
         <v>146</v>
@@ -3542,10 +3578,10 @@
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H45" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="M45" t="s">
         <v>146</v>
@@ -3557,18 +3593,18 @@
         <v>121</v>
       </c>
       <c r="P45" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="Q45" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H46" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="M46" t="s">
         <v>146</v>
@@ -3580,15 +3616,15 @@
         <v>121</v>
       </c>
       <c r="Q46" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H47" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="M47" t="s">
         <v>146</v>
@@ -3644,7 +3680,7 @@
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>185</v>
+        <v>408</v>
       </c>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -3680,7 +3716,7 @@
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H55" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L55" t="s">
         <v>169</v>
@@ -3704,7 +3740,7 @@
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H56" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L56" t="s">
         <v>176</v>
@@ -3719,13 +3755,16 @@
       <c r="O56" t="s">
         <v>178</v>
       </c>
+      <c r="P56" t="s">
+        <v>172</v>
+      </c>
       <c r="Q56" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H57" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L57" t="s">
         <v>170</v>
@@ -3740,2777 +3779,3431 @@
       <c r="O57" t="s">
         <v>178</v>
       </c>
+      <c r="P57" t="s">
+        <v>172</v>
+      </c>
       <c r="Q57" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H58" t="s">
-        <v>318</v>
+        <v>243</v>
       </c>
       <c r="L58" t="s">
-        <v>169</v>
+        <v>402</v>
       </c>
       <c r="M58" t="s">
         <v>168</v>
       </c>
-      <c r="N58" s="15">
-        <v>0</v>
+      <c r="N58" s="8">
+        <f>0.17*1000</f>
+        <v>170</v>
       </c>
       <c r="O58" t="s">
         <v>178</v>
       </c>
+      <c r="P58" t="s">
+        <v>410</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>409</v>
+      </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H59" t="s">
-        <v>318</v>
+        <v>243</v>
       </c>
       <c r="L59" t="s">
-        <v>177</v>
+        <v>403</v>
       </c>
       <c r="M59" t="s">
         <v>168</v>
       </c>
-      <c r="N59" s="17">
-        <f t="shared" ref="N59:N60" si="0">N56</f>
-        <v>3.9</v>
+      <c r="N59" s="8">
+        <f>0.35*1000</f>
+        <v>350</v>
       </c>
       <c r="O59" t="s">
         <v>178</v>
       </c>
       <c r="P59" t="s">
-        <v>174</v>
+        <v>410</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>409</v>
       </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H60" t="s">
-        <v>318</v>
+        <v>243</v>
       </c>
       <c r="L60" t="s">
-        <v>170</v>
+        <v>404</v>
       </c>
       <c r="M60" t="s">
         <v>168</v>
       </c>
-      <c r="N60" s="17">
+      <c r="N60" s="8">
+        <f>0.000093*1000</f>
+        <v>9.2999999999999999E-2</v>
+      </c>
+      <c r="O60" t="s">
+        <v>178</v>
+      </c>
+      <c r="P60" t="s">
+        <v>410</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H61" t="s">
+        <v>243</v>
+      </c>
+      <c r="L61" t="s">
+        <v>405</v>
+      </c>
+      <c r="M61" t="s">
+        <v>168</v>
+      </c>
+      <c r="N61" s="8">
+        <f>0.028*1000</f>
+        <v>28</v>
+      </c>
+      <c r="O61" t="s">
+        <v>178</v>
+      </c>
+      <c r="P61" t="s">
+        <v>410</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H62" t="s">
+        <v>243</v>
+      </c>
+      <c r="L62" t="s">
+        <v>406</v>
+      </c>
+      <c r="M62" t="s">
+        <v>168</v>
+      </c>
+      <c r="N62" s="8">
+        <f>0.034*1000</f>
+        <v>34</v>
+      </c>
+      <c r="O62" t="s">
+        <v>178</v>
+      </c>
+      <c r="P62" t="s">
+        <v>410</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H63" t="s">
+        <v>243</v>
+      </c>
+      <c r="L63" t="s">
+        <v>407</v>
+      </c>
+      <c r="M63" t="s">
+        <v>168</v>
+      </c>
+      <c r="N63" s="8">
+        <f>0.00036*1000</f>
+        <v>0.36000000000000004</v>
+      </c>
+      <c r="O63" t="s">
+        <v>178</v>
+      </c>
+      <c r="P63" t="s">
+        <v>410</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H64" t="s">
+        <v>317</v>
+      </c>
+      <c r="L64" t="s">
+        <v>169</v>
+      </c>
+      <c r="M64" t="s">
+        <v>168</v>
+      </c>
+      <c r="N64" s="15">
+        <v>0</v>
+      </c>
+      <c r="O64" t="s">
+        <v>178</v>
+      </c>
+      <c r="P64" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="65" spans="8:17" x14ac:dyDescent="0.25">
+      <c r="H65" t="s">
+        <v>317</v>
+      </c>
+      <c r="L65" t="s">
+        <v>177</v>
+      </c>
+      <c r="M65" t="s">
+        <v>168</v>
+      </c>
+      <c r="N65" s="17">
+        <f t="shared" ref="N65:N72" si="0">N56</f>
+        <v>3.9</v>
+      </c>
+      <c r="O65" t="s">
+        <v>178</v>
+      </c>
+      <c r="P65" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="66" spans="8:17" x14ac:dyDescent="0.25">
+      <c r="H66" t="s">
+        <v>317</v>
+      </c>
+      <c r="L66" t="s">
+        <v>170</v>
+      </c>
+      <c r="M66" t="s">
+        <v>168</v>
+      </c>
+      <c r="N66" s="17">
         <f t="shared" si="0"/>
         <v>3.9</v>
       </c>
-      <c r="O60" t="s">
-        <v>178</v>
-      </c>
-      <c r="P60" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H61" t="s">
-        <v>321</v>
-      </c>
-      <c r="L61" t="s">
-        <v>169</v>
-      </c>
-      <c r="M61" t="s">
-        <v>168</v>
-      </c>
-      <c r="N61" s="15">
-        <v>73300</v>
-      </c>
-      <c r="O61" t="s">
-        <v>178</v>
-      </c>
-      <c r="P61" t="s">
-        <v>181</v>
-      </c>
-      <c r="Q61" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H62" t="s">
-        <v>321</v>
-      </c>
-      <c r="L62" t="s">
-        <v>176</v>
-      </c>
-      <c r="M62" t="s">
-        <v>168</v>
-      </c>
-      <c r="N62">
-        <v>10</v>
-      </c>
-      <c r="O62" t="s">
-        <v>178</v>
-      </c>
-      <c r="Q62" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H63" t="s">
-        <v>321</v>
-      </c>
-      <c r="L63" t="s">
-        <v>170</v>
-      </c>
-      <c r="M63" t="s">
-        <v>168</v>
-      </c>
-      <c r="N63">
-        <v>0.6</v>
-      </c>
-      <c r="O63" t="s">
-        <v>178</v>
-      </c>
-      <c r="Q63" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H64" t="s">
-        <v>325</v>
-      </c>
-      <c r="L64" t="s">
-        <v>169</v>
-      </c>
-      <c r="M64" t="s">
-        <v>168</v>
-      </c>
-      <c r="N64" s="15">
-        <v>56100</v>
-      </c>
-      <c r="O64" t="s">
-        <v>178</v>
-      </c>
-      <c r="P64" t="s">
-        <v>180</v>
-      </c>
-      <c r="Q64" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H65" t="s">
-        <v>325</v>
-      </c>
-      <c r="L65" t="s">
-        <v>176</v>
-      </c>
-      <c r="M65" t="s">
-        <v>168</v>
-      </c>
-      <c r="N65">
-        <v>5</v>
-      </c>
-      <c r="O65" t="s">
-        <v>178</v>
-      </c>
-      <c r="Q65" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H66" t="s">
-        <v>325</v>
-      </c>
-      <c r="L66" t="s">
-        <v>170</v>
-      </c>
-      <c r="M66" t="s">
-        <v>168</v>
-      </c>
-      <c r="N66">
-        <v>0.1</v>
-      </c>
       <c r="O66" t="s">
         <v>178</v>
       </c>
-      <c r="Q66" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="P66" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="67" spans="8:17" x14ac:dyDescent="0.25">
       <c r="H67" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="L67" t="s">
-        <v>169</v>
+        <v>402</v>
       </c>
       <c r="M67" t="s">
         <v>168</v>
       </c>
-      <c r="N67" s="15">
-        <v>0</v>
+      <c r="N67" s="17">
+        <f t="shared" si="0"/>
+        <v>170</v>
       </c>
       <c r="O67" t="s">
         <v>178</v>
       </c>
       <c r="P67" t="s">
-        <v>179</v>
-      </c>
-      <c r="Q67" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="68" spans="8:17" x14ac:dyDescent="0.25">
       <c r="H68" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="L68" t="s">
-        <v>177</v>
+        <v>403</v>
       </c>
       <c r="M68" t="s">
         <v>168</v>
       </c>
-      <c r="N68" s="15">
-        <v>300</v>
+      <c r="N68" s="17">
+        <f t="shared" si="0"/>
+        <v>350</v>
       </c>
       <c r="O68" t="s">
         <v>178</v>
       </c>
-      <c r="Q68" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="P68" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="69" spans="8:17" x14ac:dyDescent="0.25">
       <c r="H69" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="L69" t="s">
-        <v>170</v>
+        <v>404</v>
       </c>
       <c r="M69" t="s">
         <v>168</v>
       </c>
-      <c r="N69" s="15">
-        <v>4</v>
+      <c r="N69" s="17">
+        <f t="shared" si="0"/>
+        <v>9.2999999999999999E-2</v>
       </c>
       <c r="O69" t="s">
         <v>178</v>
       </c>
-      <c r="Q69" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="P69" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="70" spans="8:17" x14ac:dyDescent="0.25">
       <c r="H70" t="s">
-        <v>324</v>
+        <v>317</v>
+      </c>
+      <c r="L70" t="s">
+        <v>405</v>
       </c>
       <c r="M70" t="s">
         <v>168</v>
       </c>
-      <c r="N70" s="15">
-        <v>0</v>
+      <c r="N70" s="17">
+        <f t="shared" si="0"/>
+        <v>28</v>
       </c>
       <c r="O70" t="s">
         <v>178</v>
       </c>
-      <c r="P70" s="12"/>
-    </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="P70" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="71" spans="8:17" x14ac:dyDescent="0.25">
       <c r="H71" t="s">
-        <v>323</v>
+        <v>317</v>
+      </c>
+      <c r="L71" t="s">
+        <v>406</v>
       </c>
       <c r="M71" t="s">
         <v>168</v>
       </c>
-      <c r="N71" s="15">
-        <v>0</v>
+      <c r="N71" s="17">
+        <f t="shared" si="0"/>
+        <v>34</v>
       </c>
       <c r="O71" t="s">
         <v>178</v>
       </c>
-      <c r="P71" s="12"/>
-    </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="P71" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="72" spans="8:17" x14ac:dyDescent="0.25">
       <c r="H72" t="s">
-        <v>319</v>
+        <v>317</v>
+      </c>
+      <c r="L72" t="s">
+        <v>407</v>
       </c>
       <c r="M72" t="s">
         <v>168</v>
       </c>
-      <c r="N72" s="15">
-        <v>0</v>
+      <c r="N72" s="17">
+        <f t="shared" si="0"/>
+        <v>0.36000000000000004</v>
       </c>
       <c r="O72" t="s">
         <v>178</v>
       </c>
-      <c r="P72" s="12" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="P72" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="73" spans="8:17" x14ac:dyDescent="0.25">
       <c r="H73" t="s">
         <v>320</v>
       </c>
+      <c r="L73" t="s">
+        <v>169</v>
+      </c>
       <c r="M73" t="s">
         <v>168</v>
       </c>
       <c r="N73" s="15">
-        <v>0</v>
+        <v>73300</v>
       </c>
       <c r="O73" t="s">
         <v>178</v>
       </c>
-      <c r="P73" s="12"/>
-    </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N74" s="15"/>
-      <c r="P74" s="12"/>
-    </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A75" s="1" t="s">
+      <c r="P73" t="s">
+        <v>181</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="74" spans="8:17" x14ac:dyDescent="0.25">
+      <c r="H74" t="s">
+        <v>320</v>
+      </c>
+      <c r="L74" t="s">
+        <v>176</v>
+      </c>
+      <c r="M74" t="s">
+        <v>168</v>
+      </c>
+      <c r="N74">
+        <v>10</v>
+      </c>
+      <c r="O74" t="s">
+        <v>178</v>
+      </c>
+      <c r="P74" t="s">
+        <v>181</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="75" spans="8:17" x14ac:dyDescent="0.25">
+      <c r="H75" t="s">
+        <v>320</v>
+      </c>
+      <c r="L75" t="s">
+        <v>170</v>
+      </c>
+      <c r="M75" t="s">
+        <v>168</v>
+      </c>
+      <c r="N75">
+        <v>0.6</v>
+      </c>
+      <c r="O75" t="s">
+        <v>178</v>
+      </c>
+      <c r="P75" t="s">
+        <v>181</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="76" spans="8:17" x14ac:dyDescent="0.25">
+      <c r="H76" t="s">
+        <v>320</v>
+      </c>
+      <c r="L76" t="s">
+        <v>402</v>
+      </c>
+      <c r="M76" t="s">
+        <v>168</v>
+      </c>
+      <c r="N76" s="8">
+        <f>0.015*1000</f>
+        <v>15</v>
+      </c>
+      <c r="O76" t="s">
+        <v>178</v>
+      </c>
+      <c r="P76" t="s">
+        <v>412</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="77" spans="8:17" x14ac:dyDescent="0.25">
+      <c r="H77" t="s">
+        <v>320</v>
+      </c>
+      <c r="L77" t="s">
+        <v>403</v>
+      </c>
+      <c r="M77" t="s">
+        <v>168</v>
+      </c>
+      <c r="N77" s="8">
+        <f>0.2*1000</f>
+        <v>200</v>
+      </c>
+      <c r="O77" t="s">
+        <v>178</v>
+      </c>
+      <c r="P77" t="s">
+        <v>412</v>
+      </c>
+      <c r="Q77" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="78" spans="8:17" x14ac:dyDescent="0.25">
+      <c r="H78" t="s">
+        <v>320</v>
+      </c>
+      <c r="L78" t="s">
+        <v>404</v>
+      </c>
+      <c r="M78" t="s">
+        <v>168</v>
+      </c>
+      <c r="N78" s="8">
+        <f>0.025*1000</f>
+        <v>25</v>
+      </c>
+      <c r="O78" t="s">
+        <v>178</v>
+      </c>
+      <c r="P78" t="s">
+        <v>412</v>
+      </c>
+      <c r="Q78" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="79" spans="8:17" x14ac:dyDescent="0.25">
+      <c r="H79" t="s">
+        <v>320</v>
+      </c>
+      <c r="L79" t="s">
+        <v>405</v>
+      </c>
+      <c r="M79" t="s">
+        <v>168</v>
+      </c>
+      <c r="N79" s="8">
+        <f>0.002*1000</f>
+        <v>2</v>
+      </c>
+      <c r="O79" t="s">
+        <v>178</v>
+      </c>
+      <c r="P79" t="s">
+        <v>412</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="80" spans="8:17" x14ac:dyDescent="0.25">
+      <c r="H80" t="s">
+        <v>320</v>
+      </c>
+      <c r="L80" t="s">
+        <v>406</v>
+      </c>
+      <c r="M80" t="s">
+        <v>168</v>
+      </c>
+      <c r="N80" s="8"/>
+    </row>
+    <row r="81" spans="8:17" x14ac:dyDescent="0.25">
+      <c r="H81" t="s">
+        <v>320</v>
+      </c>
+      <c r="L81" t="s">
+        <v>407</v>
+      </c>
+      <c r="M81" t="s">
+        <v>168</v>
+      </c>
+      <c r="N81" s="8"/>
+    </row>
+    <row r="82" spans="8:17" x14ac:dyDescent="0.25">
+      <c r="H82" t="s">
+        <v>324</v>
+      </c>
+      <c r="L82" t="s">
+        <v>169</v>
+      </c>
+      <c r="M82" t="s">
+        <v>168</v>
+      </c>
+      <c r="N82" s="15">
+        <v>56100</v>
+      </c>
+      <c r="O82" t="s">
+        <v>178</v>
+      </c>
+      <c r="P82" t="s">
+        <v>180</v>
+      </c>
+      <c r="Q82" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="83" spans="8:17" x14ac:dyDescent="0.25">
+      <c r="H83" t="s">
+        <v>324</v>
+      </c>
+      <c r="L83" t="s">
+        <v>176</v>
+      </c>
+      <c r="M83" t="s">
+        <v>168</v>
+      </c>
+      <c r="N83">
+        <v>5</v>
+      </c>
+      <c r="O83" t="s">
+        <v>178</v>
+      </c>
+      <c r="P83" t="s">
+        <v>180</v>
+      </c>
+      <c r="Q83" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="84" spans="8:17" x14ac:dyDescent="0.25">
+      <c r="H84" t="s">
+        <v>324</v>
+      </c>
+      <c r="L84" t="s">
+        <v>170</v>
+      </c>
+      <c r="M84" t="s">
+        <v>168</v>
+      </c>
+      <c r="N84">
+        <v>0.1</v>
+      </c>
+      <c r="O84" t="s">
+        <v>178</v>
+      </c>
+      <c r="P84" t="s">
+        <v>180</v>
+      </c>
+      <c r="Q84" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="85" spans="8:17" x14ac:dyDescent="0.25">
+      <c r="H85" t="s">
+        <v>324</v>
+      </c>
+      <c r="L85" t="s">
+        <v>402</v>
+      </c>
+      <c r="M85" t="s">
+        <v>168</v>
+      </c>
+      <c r="N85" s="8"/>
+    </row>
+    <row r="86" spans="8:17" x14ac:dyDescent="0.25">
+      <c r="H86" t="s">
+        <v>324</v>
+      </c>
+      <c r="L86" t="s">
+        <v>403</v>
+      </c>
+      <c r="M86" t="s">
+        <v>168</v>
+      </c>
+      <c r="N86" s="8">
+        <f>0.0069*1000</f>
+        <v>6.8999999999999995</v>
+      </c>
+      <c r="O86" t="s">
+        <v>178</v>
+      </c>
+      <c r="P86" t="s">
+        <v>411</v>
+      </c>
+      <c r="Q86" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="87" spans="8:17" x14ac:dyDescent="0.25">
+      <c r="H87" t="s">
+        <v>324</v>
+      </c>
+      <c r="L87" t="s">
+        <v>404</v>
+      </c>
+      <c r="M87" t="s">
+        <v>168</v>
+      </c>
+      <c r="N87" s="8"/>
+    </row>
+    <row r="88" spans="8:17" x14ac:dyDescent="0.25">
+      <c r="H88" t="s">
+        <v>324</v>
+      </c>
+      <c r="L88" t="s">
+        <v>405</v>
+      </c>
+      <c r="M88" t="s">
+        <v>168</v>
+      </c>
+      <c r="N88" s="8"/>
+    </row>
+    <row r="89" spans="8:17" x14ac:dyDescent="0.25">
+      <c r="H89" t="s">
+        <v>324</v>
+      </c>
+      <c r="L89" t="s">
+        <v>406</v>
+      </c>
+      <c r="M89" t="s">
+        <v>168</v>
+      </c>
+      <c r="N89" s="8"/>
+    </row>
+    <row r="90" spans="8:17" x14ac:dyDescent="0.25">
+      <c r="H90" t="s">
+        <v>324</v>
+      </c>
+      <c r="L90" t="s">
+        <v>407</v>
+      </c>
+      <c r="M90" t="s">
+        <v>168</v>
+      </c>
+      <c r="N90" s="8">
+        <f>0.00036*1000</f>
+        <v>0.36000000000000004</v>
+      </c>
+      <c r="O90" t="s">
+        <v>178</v>
+      </c>
+      <c r="P90" t="s">
+        <v>411</v>
+      </c>
+      <c r="Q90" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="91" spans="8:17" x14ac:dyDescent="0.25">
+      <c r="H91" t="s">
+        <v>321</v>
+      </c>
+      <c r="L91" t="s">
+        <v>169</v>
+      </c>
+      <c r="M91" t="s">
+        <v>168</v>
+      </c>
+      <c r="N91" s="15">
+        <v>0</v>
+      </c>
+      <c r="O91" t="s">
+        <v>178</v>
+      </c>
+      <c r="P91" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q91" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="92" spans="8:17" x14ac:dyDescent="0.25">
+      <c r="H92" t="s">
+        <v>321</v>
+      </c>
+      <c r="L92" t="s">
+        <v>177</v>
+      </c>
+      <c r="M92" t="s">
+        <v>168</v>
+      </c>
+      <c r="N92" s="15">
+        <v>300</v>
+      </c>
+      <c r="O92" t="s">
+        <v>178</v>
+      </c>
+      <c r="P92" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q92" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="93" spans="8:17" x14ac:dyDescent="0.25">
+      <c r="H93" t="s">
+        <v>321</v>
+      </c>
+      <c r="L93" t="s">
+        <v>170</v>
+      </c>
+      <c r="M93" t="s">
+        <v>168</v>
+      </c>
+      <c r="N93" s="15">
+        <v>4</v>
+      </c>
+      <c r="O93" t="s">
+        <v>178</v>
+      </c>
+      <c r="P93" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q93" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="94" spans="8:17" x14ac:dyDescent="0.25">
+      <c r="H94" t="s">
+        <v>321</v>
+      </c>
+      <c r="L94" t="s">
+        <v>402</v>
+      </c>
+      <c r="M94" t="s">
+        <v>168</v>
+      </c>
+      <c r="N94" s="8">
+        <f>0.12*1000</f>
+        <v>120</v>
+      </c>
+      <c r="O94" t="s">
+        <v>178</v>
+      </c>
+      <c r="P94" t="s">
+        <v>415</v>
+      </c>
+      <c r="Q94" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="95" spans="8:17" x14ac:dyDescent="0.25">
+      <c r="H95" t="s">
+        <v>321</v>
+      </c>
+      <c r="L95" t="s">
+        <v>403</v>
+      </c>
+      <c r="M95" t="s">
+        <v>168</v>
+      </c>
+      <c r="N95" s="8">
+        <f>0.065*1000</f>
+        <v>65</v>
+      </c>
+      <c r="O95" t="s">
+        <v>178</v>
+      </c>
+      <c r="P95" t="s">
+        <v>415</v>
+      </c>
+      <c r="Q95" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="96" spans="8:17" x14ac:dyDescent="0.25">
+      <c r="H96" t="s">
+        <v>321</v>
+      </c>
+      <c r="L96" t="s">
+        <v>404</v>
+      </c>
+      <c r="M96" t="s">
+        <v>168</v>
+      </c>
+      <c r="N96" s="8">
+        <f>0.01*1000</f>
+        <v>10</v>
+      </c>
+      <c r="O96" t="s">
+        <v>178</v>
+      </c>
+      <c r="P96" t="s">
+        <v>415</v>
+      </c>
+      <c r="Q96" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H97" t="s">
+        <v>321</v>
+      </c>
+      <c r="L97" t="s">
+        <v>405</v>
+      </c>
+      <c r="M97" t="s">
+        <v>168</v>
+      </c>
+      <c r="N97" s="8">
+        <f>0.01*1000</f>
+        <v>10</v>
+      </c>
+      <c r="O97" t="s">
+        <v>178</v>
+      </c>
+      <c r="P97" t="s">
+        <v>417</v>
+      </c>
+      <c r="Q97" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H98" t="s">
+        <v>321</v>
+      </c>
+      <c r="L98" t="s">
+        <v>406</v>
+      </c>
+      <c r="M98" t="s">
+        <v>168</v>
+      </c>
+      <c r="N98" s="8">
+        <f>0.009*1000</f>
+        <v>9</v>
+      </c>
+      <c r="O98" t="s">
+        <v>178</v>
+      </c>
+      <c r="P98" t="s">
+        <v>415</v>
+      </c>
+      <c r="Q98" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H99" t="s">
+        <v>321</v>
+      </c>
+      <c r="L99" t="s">
+        <v>407</v>
+      </c>
+      <c r="M99" t="s">
+        <v>168</v>
+      </c>
+      <c r="N99" s="8">
+        <f>0.002*1000</f>
+        <v>2</v>
+      </c>
+      <c r="O99" t="s">
+        <v>178</v>
+      </c>
+      <c r="P99" t="s">
+        <v>415</v>
+      </c>
+      <c r="Q99" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H100" t="s">
+        <v>323</v>
+      </c>
+      <c r="M100" t="s">
+        <v>168</v>
+      </c>
+      <c r="N100" s="15">
+        <v>0</v>
+      </c>
+      <c r="O100" t="s">
+        <v>178</v>
+      </c>
+      <c r="P100" s="12"/>
+    </row>
+    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H101" t="s">
+        <v>322</v>
+      </c>
+      <c r="M101" t="s">
+        <v>168</v>
+      </c>
+      <c r="N101" s="15">
+        <v>0</v>
+      </c>
+      <c r="O101" t="s">
+        <v>178</v>
+      </c>
+      <c r="P101" s="12"/>
+    </row>
+    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H102" t="s">
+        <v>318</v>
+      </c>
+      <c r="M102" t="s">
+        <v>168</v>
+      </c>
+      <c r="N102" s="15">
+        <v>0</v>
+      </c>
+      <c r="O102" t="s">
+        <v>178</v>
+      </c>
+      <c r="P102" s="12" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H103" t="s">
+        <v>319</v>
+      </c>
+      <c r="M103" t="s">
+        <v>168</v>
+      </c>
+      <c r="N103" s="15">
+        <v>0</v>
+      </c>
+      <c r="O103" t="s">
+        <v>178</v>
+      </c>
+      <c r="P103" s="12"/>
+    </row>
+    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="N104" s="15"/>
+      <c r="P104" s="12"/>
+    </row>
+    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A105" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B75" s="1"/>
-      <c r="C75" s="1"/>
-      <c r="D75" s="1"/>
-      <c r="E75" s="1"/>
-      <c r="F75" s="1"/>
-      <c r="G75" s="1"/>
-      <c r="H75" s="1"/>
-      <c r="I75" s="1"/>
-      <c r="J75" s="1"/>
-      <c r="K75" s="1"/>
-      <c r="L75" s="1"/>
-      <c r="M75" s="1"/>
-      <c r="N75" s="1"/>
-      <c r="O75" s="1"/>
-      <c r="P75" s="1"/>
-      <c r="Q75" s="1"/>
-    </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A76" s="2" t="s">
+      <c r="B105" s="1"/>
+      <c r="C105" s="1"/>
+      <c r="D105" s="1"/>
+      <c r="E105" s="1"/>
+      <c r="F105" s="1"/>
+      <c r="G105" s="1"/>
+      <c r="H105" s="1"/>
+      <c r="I105" s="1"/>
+      <c r="J105" s="1"/>
+      <c r="K105" s="1"/>
+      <c r="L105" s="1"/>
+      <c r="M105" s="1"/>
+      <c r="N105" s="1"/>
+      <c r="O105" s="1"/>
+      <c r="P105" s="1"/>
+      <c r="Q105" s="1"/>
+    </row>
+    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A106" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B76" s="2"/>
-      <c r="C76" s="2"/>
-      <c r="D76" s="2"/>
-      <c r="E76" s="2"/>
-      <c r="F76" s="2"/>
-      <c r="G76" s="2"/>
-      <c r="H76" s="2"/>
-      <c r="I76" s="2"/>
-      <c r="J76" s="2"/>
-      <c r="K76" s="2"/>
-      <c r="L76" s="2"/>
-      <c r="M76" s="3"/>
-      <c r="N76" s="3"/>
-      <c r="O76" s="3"/>
-      <c r="P76" s="3"/>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M77" t="s">
+      <c r="B106" s="2"/>
+      <c r="C106" s="2"/>
+      <c r="D106" s="2"/>
+      <c r="E106" s="2"/>
+      <c r="F106" s="2"/>
+      <c r="G106" s="2"/>
+      <c r="H106" s="2"/>
+      <c r="I106" s="2"/>
+      <c r="J106" s="2"/>
+      <c r="K106" s="2"/>
+      <c r="L106" s="2"/>
+      <c r="M106" s="3"/>
+      <c r="N106" s="3"/>
+      <c r="O106" s="3"/>
+      <c r="P106" s="3"/>
+      <c r="Q106" s="3"/>
+    </row>
+    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M107" t="s">
         <v>9</v>
       </c>
-      <c r="N77">
+      <c r="N107">
         <v>10800</v>
       </c>
-      <c r="O77" t="s">
+      <c r="O107" t="s">
         <v>11</v>
       </c>
-      <c r="P77" t="s">
+      <c r="P107" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M78" t="s">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M108" t="s">
         <v>22</v>
       </c>
-      <c r="N78">
+      <c r="N108">
         <v>5</v>
       </c>
-      <c r="O78" t="s">
+      <c r="O108" t="s">
         <v>13</v>
       </c>
-      <c r="P78" t="s">
+      <c r="P108" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M79" t="s">
+    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M109" t="s">
         <v>118</v>
       </c>
-      <c r="N79">
+      <c r="N109">
         <v>2</v>
       </c>
-      <c r="O79" t="s">
+      <c r="O109" t="s">
         <v>119</v>
       </c>
-      <c r="P79" s="4"/>
-    </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M80" t="s">
+      <c r="P109" s="4"/>
+    </row>
+    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M110" t="s">
         <v>23</v>
       </c>
-      <c r="N80">
+      <c r="N110">
         <v>0.2</v>
       </c>
-      <c r="O80" t="s">
+      <c r="O110" t="s">
         <v>15</v>
       </c>
-      <c r="P80" t="s">
+      <c r="P110" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M81" t="s">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M111" t="s">
         <v>24</v>
       </c>
-      <c r="N81">
+      <c r="N111">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="O81" t="s">
+      <c r="O111" t="s">
         <v>17</v>
       </c>
-      <c r="P81" s="4" t="s">
+      <c r="P111" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M82" t="s">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M112" t="s">
         <v>25</v>
       </c>
-      <c r="N82">
+      <c r="N112">
         <v>250</v>
       </c>
-      <c r="O82" t="s">
+      <c r="O112" t="s">
         <v>19</v>
       </c>
-      <c r="P82" s="4" t="s">
+      <c r="P112" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M83" s="6" t="s">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M113" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="N83" s="6">
+      <c r="N113" s="6">
         <v>1</v>
       </c>
-      <c r="O83" s="6"/>
-      <c r="P83" s="16" t="s">
+      <c r="O113" s="6"/>
+      <c r="P113" s="16" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="84" spans="1:17" ht="18" x14ac:dyDescent="0.35">
-      <c r="H84" t="s">
-        <v>244</v>
-      </c>
-      <c r="M84" t="s">
+    <row r="114" spans="1:17" ht="18" x14ac:dyDescent="0.35">
+      <c r="H114" t="s">
+        <v>243</v>
+      </c>
+      <c r="M114" t="s">
         <v>49</v>
       </c>
-      <c r="N84">
+      <c r="N114">
         <v>0.26</v>
       </c>
-      <c r="P84" s="4" t="s">
+      <c r="P114" s="4" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="85" spans="1:17" ht="18" x14ac:dyDescent="0.35">
-      <c r="H85" t="s">
+    <row r="115" spans="1:17" ht="18" x14ac:dyDescent="0.35">
+      <c r="H115" t="s">
+        <v>317</v>
+      </c>
+      <c r="M115" t="s">
+        <v>49</v>
+      </c>
+      <c r="N115">
+        <v>0.26</v>
+      </c>
+      <c r="P115" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="116" spans="1:17" ht="18" x14ac:dyDescent="0.35">
+      <c r="H116" t="s">
         <v>318</v>
       </c>
-      <c r="M85" t="s">
+      <c r="M116" t="s">
         <v>49</v>
       </c>
-      <c r="N85">
-        <v>0.26</v>
-      </c>
-      <c r="P85" s="4" t="s">
+      <c r="N116">
+        <v>0.45</v>
+      </c>
+      <c r="P116" s="4" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="86" spans="1:17" ht="18" x14ac:dyDescent="0.35">
-      <c r="H86" t="s">
+    <row r="117" spans="1:17" ht="18" x14ac:dyDescent="0.35">
+      <c r="H117" t="s">
         <v>319</v>
       </c>
-      <c r="M86" t="s">
+      <c r="M117" t="s">
         <v>49</v>
       </c>
-      <c r="N86">
-        <v>0.45</v>
-      </c>
-      <c r="P86" s="4" t="s">
+      <c r="N117">
+        <v>0.76</v>
+      </c>
+      <c r="P117" s="4" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="87" spans="1:17" ht="18" x14ac:dyDescent="0.35">
-      <c r="H87" t="s">
-        <v>320</v>
-      </c>
-      <c r="M87" t="s">
-        <v>49</v>
-      </c>
-      <c r="N87">
-        <v>0.76</v>
-      </c>
-      <c r="P87" s="4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M88" t="s">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M118" t="s">
         <v>27</v>
       </c>
-      <c r="N88">
+      <c r="N118">
         <v>4</v>
       </c>
-      <c r="O88" t="s">
+      <c r="O118" t="s">
         <v>21</v>
       </c>
-      <c r="P88" s="4" t="s">
+      <c r="P118" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A90" s="2" t="s">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A120" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B90" s="2"/>
-      <c r="C90" s="2"/>
-      <c r="D90" s="2"/>
-      <c r="E90" s="2"/>
-      <c r="F90" s="2"/>
-      <c r="G90" s="2"/>
-      <c r="H90" s="2"/>
-      <c r="I90" s="2"/>
-      <c r="J90" s="2"/>
-      <c r="K90" s="2"/>
-      <c r="L90" s="2"/>
-      <c r="M90" s="2"/>
-      <c r="N90" s="2"/>
-      <c r="O90" s="2"/>
-      <c r="P90" s="2"/>
-      <c r="Q90" s="2"/>
-    </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M91" t="s">
+      <c r="B120" s="2"/>
+      <c r="C120" s="2"/>
+      <c r="D120" s="2"/>
+      <c r="E120" s="2"/>
+      <c r="F120" s="2"/>
+      <c r="G120" s="2"/>
+      <c r="H120" s="2"/>
+      <c r="I120" s="2"/>
+      <c r="J120" s="2"/>
+      <c r="K120" s="2"/>
+      <c r="L120" s="2"/>
+      <c r="M120" s="2"/>
+      <c r="N120" s="2"/>
+      <c r="O120" s="2"/>
+      <c r="P120" s="2"/>
+      <c r="Q120" s="2"/>
+    </row>
+    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M121" t="s">
         <v>120</v>
       </c>
-      <c r="N91">
+      <c r="N121">
         <v>4</v>
       </c>
-      <c r="O91" t="s">
+      <c r="O121" t="s">
         <v>29</v>
       </c>
-      <c r="P91" t="s">
+      <c r="P121" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="92" spans="1:17" ht="18" x14ac:dyDescent="0.35">
-      <c r="M92" t="s">
+    <row r="122" spans="1:17" ht="18" x14ac:dyDescent="0.35">
+      <c r="M122" t="s">
         <v>45</v>
       </c>
-      <c r="N92">
+      <c r="N122">
         <v>0.9</v>
       </c>
-      <c r="P92" t="s">
+      <c r="P122" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="93" spans="1:17" ht="18" x14ac:dyDescent="0.35">
-      <c r="M93" t="s">
+    <row r="123" spans="1:17" ht="18" x14ac:dyDescent="0.35">
+      <c r="M123" t="s">
         <v>38</v>
       </c>
-      <c r="N93">
+      <c r="N123">
         <v>1.2250000000000001</v>
       </c>
-      <c r="O93" t="s">
+      <c r="O123" t="s">
         <v>32</v>
       </c>
-      <c r="P93" t="s">
+      <c r="P123" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="94" spans="1:17" ht="18" x14ac:dyDescent="0.35">
-      <c r="M94" t="s">
+    <row r="124" spans="1:17" ht="18" x14ac:dyDescent="0.35">
+      <c r="M124" t="s">
         <v>39</v>
       </c>
-      <c r="N94">
+      <c r="N124">
         <v>0.1</v>
       </c>
-      <c r="P94" t="s">
+      <c r="P124" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="95" spans="1:17" ht="18" x14ac:dyDescent="0.35">
-      <c r="M95" t="s">
+    <row r="125" spans="1:17" ht="18" x14ac:dyDescent="0.35">
+      <c r="M125" t="s">
         <v>40</v>
       </c>
-      <c r="N95">
+      <c r="N125">
         <v>0.01</v>
       </c>
-      <c r="P95" t="s">
+      <c r="P125" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M96" t="s">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M126" t="s">
         <v>41</v>
       </c>
-      <c r="N96">
+      <c r="N126">
         <v>0.2</v>
       </c>
-      <c r="P96" t="s">
+      <c r="P126" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="18" x14ac:dyDescent="0.35">
-      <c r="M97" t="s">
+    <row r="127" spans="1:17" ht="18" x14ac:dyDescent="0.35">
+      <c r="M127" t="s">
         <v>42</v>
       </c>
-      <c r="N97">
+      <c r="N127">
         <v>0.8</v>
       </c>
-      <c r="P97" t="s">
+      <c r="P127" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="18" x14ac:dyDescent="0.35">
-      <c r="M98" t="s">
+    <row r="128" spans="1:17" ht="18" x14ac:dyDescent="0.35">
+      <c r="M128" t="s">
         <v>43</v>
       </c>
-      <c r="N98">
+      <c r="N128">
         <v>55</v>
       </c>
-      <c r="P98" t="s">
+      <c r="P128" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A100" s="1" t="s">
+    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A130" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B100" s="5"/>
-      <c r="C100" s="5"/>
-      <c r="D100" s="5"/>
-      <c r="E100" s="5"/>
-      <c r="F100" s="5"/>
-      <c r="G100" s="5"/>
-      <c r="H100" s="5"/>
-      <c r="I100" s="5"/>
-      <c r="J100" s="5"/>
-      <c r="K100" s="5"/>
-      <c r="L100" s="5"/>
-      <c r="M100" s="5"/>
-      <c r="N100" s="5"/>
-      <c r="O100" s="5"/>
-      <c r="P100" s="5"/>
-      <c r="Q100" s="5"/>
-    </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M101" s="6" t="s">
+      <c r="B130" s="5"/>
+      <c r="C130" s="5"/>
+      <c r="D130" s="5"/>
+      <c r="E130" s="5"/>
+      <c r="F130" s="5"/>
+      <c r="G130" s="5"/>
+      <c r="H130" s="5"/>
+      <c r="I130" s="5"/>
+      <c r="J130" s="5"/>
+      <c r="K130" s="5"/>
+      <c r="L130" s="5"/>
+      <c r="M130" s="5"/>
+      <c r="N130" s="5"/>
+      <c r="O130" s="5"/>
+      <c r="P130" s="5"/>
+      <c r="Q130" s="5"/>
+    </row>
+    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M131" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="N101" s="6">
+      <c r="N131" s="6">
         <v>0</v>
       </c>
-      <c r="O101" s="6" t="s">
+      <c r="O131" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="P101" s="6"/>
-    </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M102" s="6" t="s">
+      <c r="P131" s="6"/>
+    </row>
+    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M132" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="N102" s="6">
+      <c r="N132" s="6">
         <v>0</v>
       </c>
-      <c r="O102" s="6" t="s">
+      <c r="O132" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="P102" s="6"/>
-    </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M103" s="6" t="s">
+      <c r="P132" s="6"/>
+    </row>
+    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M133" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="N103" s="6">
+      <c r="N133" s="6">
         <v>0</v>
       </c>
-      <c r="O103" s="6" t="s">
+      <c r="O133" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="P103" s="6"/>
-    </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M104" s="6" t="s">
+      <c r="P133" s="6"/>
+    </row>
+    <row r="134" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M134" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="N104" s="6">
+      <c r="N134" s="6">
         <v>0</v>
       </c>
-      <c r="O104" s="6" t="s">
+      <c r="O134" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="P104" s="6"/>
-    </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M105" s="6" t="s">
+      <c r="P134" s="6"/>
+    </row>
+    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M135" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="N105" s="6">
+      <c r="N135" s="6">
         <v>0</v>
       </c>
-      <c r="O105" s="6" t="s">
+      <c r="O135" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="P105" s="6"/>
-    </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M106" s="6" t="s">
+      <c r="P135" s="6"/>
+    </row>
+    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M136" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="N106" s="6">
+      <c r="N136" s="6">
         <v>1</v>
       </c>
-      <c r="O106" s="6" t="s">
+      <c r="O136" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="P106" s="6" t="s">
+      <c r="P136" s="6" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M107" s="6" t="s">
+    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M137" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="N107" s="6">
+      <c r="N137" s="6">
         <v>0</v>
       </c>
-      <c r="O107" s="6" t="s">
+      <c r="O137" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="P107" s="6"/>
-    </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M108" s="6" t="s">
-        <v>398</v>
-      </c>
-      <c r="N108" s="6">
+      <c r="P137" s="6"/>
+    </row>
+    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M138" s="6" t="s">
+        <v>397</v>
+      </c>
+      <c r="N138" s="6">
         <v>0</v>
       </c>
-      <c r="O108" s="6" t="s">
+      <c r="O138" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="P108" s="6" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M109" s="6" t="s">
+      <c r="P138" s="6" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M139" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="N109" s="6">
+      <c r="N139" s="6">
         <v>0</v>
       </c>
-      <c r="O109" s="6" t="s">
+      <c r="O139" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="P109" s="6"/>
-    </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M110" s="6" t="s">
+      <c r="P139" s="6"/>
+    </row>
+    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M140" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="N110" s="6">
+      <c r="N140" s="6">
         <v>0</v>
       </c>
-      <c r="O110" s="6" t="s">
-        <v>326</v>
-      </c>
-      <c r="P110" s="6"/>
-    </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M111" s="6" t="s">
+      <c r="O140" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="P140" s="6"/>
+    </row>
+    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M141" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="N111" s="6">
+      <c r="N141" s="6">
         <v>0</v>
       </c>
-      <c r="O111" s="6" t="s">
+      <c r="O141" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="P111" s="6"/>
-    </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M112" s="6"/>
-      <c r="N112" s="6"/>
-      <c r="O112" s="6"/>
-      <c r="P112" s="6"/>
-    </row>
-    <row r="113" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="I113" t="s">
+      <c r="P141" s="6"/>
+    </row>
+    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M142" s="6"/>
+      <c r="N142" s="6"/>
+      <c r="O142" s="6"/>
+      <c r="P142" s="6"/>
+    </row>
+    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="I143" t="s">
         <v>59</v>
       </c>
-      <c r="M113" s="7" t="s">
+      <c r="M143" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="N113" s="7">
+      <c r="N143" s="7">
         <f>46*10</f>
         <v>460</v>
       </c>
-      <c r="O113" s="7"/>
-      <c r="P113" s="7" t="s">
-        <v>399</v>
-      </c>
-      <c r="Q113" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="114" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="I114" t="s">
+      <c r="O143" s="7"/>
+      <c r="P143" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="Q143" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="I144" t="s">
         <v>59</v>
       </c>
-      <c r="M114" s="7" t="s">
+      <c r="M144" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="N114" s="7">
+      <c r="N144" s="7">
         <f>2.8*10</f>
         <v>28</v>
       </c>
-      <c r="O114" s="7"/>
-      <c r="P114" s="7"/>
-      <c r="Q114" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="115" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="I115" t="s">
+      <c r="O144" s="7"/>
+      <c r="P144" s="7"/>
+      <c r="Q144" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="145" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="I145" t="s">
         <v>59</v>
       </c>
-      <c r="M115" s="7" t="s">
+      <c r="M145" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="N115" s="7">
+      <c r="N145" s="7">
         <v>0</v>
       </c>
-      <c r="O115" s="7"/>
-      <c r="P115" s="7"/>
-      <c r="Q115" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="116" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="I116" t="s">
+      <c r="O145" s="7"/>
+      <c r="P145" s="7"/>
+      <c r="Q145" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="146" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="I146" t="s">
         <v>59</v>
       </c>
-      <c r="M116" s="7" t="s">
+      <c r="M146" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="N116" s="7">
+      <c r="N146" s="7">
         <v>5</v>
       </c>
-      <c r="O116" s="7"/>
-      <c r="P116" s="7"/>
-      <c r="Q116" s="7"/>
-    </row>
-    <row r="117" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="I117" t="s">
+      <c r="O146" s="7"/>
+      <c r="P146" s="7"/>
+      <c r="Q146" s="7"/>
+    </row>
+    <row r="147" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="I147" t="s">
         <v>59</v>
       </c>
-      <c r="J117" t="s">
+      <c r="J147" t="s">
         <v>72</v>
       </c>
-      <c r="M117" s="7" t="s">
+      <c r="M147" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="N117" s="9">
+      <c r="N147" s="9">
         <v>1</v>
       </c>
-      <c r="O117" s="7"/>
-      <c r="P117" s="7"/>
-      <c r="Q117" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="118" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="I118" t="s">
+      <c r="O147" s="7"/>
+      <c r="P147" s="7"/>
+      <c r="Q147" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="148" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="I148" t="s">
         <v>59</v>
       </c>
-      <c r="J118" t="s">
+      <c r="J148" t="s">
         <v>71</v>
       </c>
-      <c r="M118" s="7" t="s">
+      <c r="M148" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="N118" s="7">
+      <c r="N148" s="7">
         <v>0.88</v>
       </c>
-      <c r="O118" s="7"/>
-      <c r="P118" s="7"/>
-      <c r="Q118" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="119" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="I119" t="s">
+      <c r="O148" s="7"/>
+      <c r="P148" s="7"/>
+      <c r="Q148" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="149" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="I149" t="s">
         <v>59</v>
       </c>
-      <c r="J119" t="s">
+      <c r="J149" t="s">
         <v>70</v>
       </c>
-      <c r="M119" s="7" t="s">
+      <c r="M149" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="N119" s="7">
+      <c r="N149" s="7">
         <v>0.78</v>
       </c>
-      <c r="O119" s="7"/>
-      <c r="P119" s="7"/>
-      <c r="Q119" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="120" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="M120" s="7"/>
-      <c r="N120" s="7"/>
-      <c r="O120" s="7"/>
-      <c r="P120" s="7"/>
-      <c r="Q120" s="7"/>
-    </row>
-    <row r="121" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="I121" t="s">
+      <c r="O149" s="7"/>
+      <c r="P149" s="7"/>
+      <c r="Q149" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="150" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="M150" s="7"/>
+      <c r="N150" s="7"/>
+      <c r="O150" s="7"/>
+      <c r="P150" s="7"/>
+      <c r="Q150" s="7"/>
+    </row>
+    <row r="151" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="I151" t="s">
         <v>62</v>
       </c>
-      <c r="M121" s="7" t="s">
+      <c r="M151" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="N121" s="7">
+      <c r="N151" s="7">
         <v>652</v>
       </c>
-      <c r="O121" s="7"/>
-      <c r="P121" s="7" t="s">
+      <c r="O151" s="7"/>
+      <c r="P151" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="Q121" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="122" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="I122" t="s">
+      <c r="Q151" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="152" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="I152" t="s">
         <v>62</v>
       </c>
-      <c r="M122" s="7" t="s">
+      <c r="M152" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="N122" s="7">
+      <c r="N152" s="7">
         <v>0</v>
       </c>
-      <c r="O122" s="7"/>
-      <c r="P122" s="7"/>
-      <c r="Q122" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="123" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="I123" t="s">
+      <c r="O152" s="7"/>
+      <c r="P152" s="7"/>
+      <c r="Q152" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="153" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="I153" t="s">
         <v>62</v>
       </c>
-      <c r="M123" s="7" t="s">
+      <c r="M153" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="N123" s="7">
+      <c r="N153" s="7">
         <v>5.0999999999999996</v>
       </c>
-      <c r="O123" s="7"/>
-      <c r="P123" s="7"/>
-      <c r="Q123" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="124" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="I124" t="s">
+      <c r="O153" s="7"/>
+      <c r="P153" s="7"/>
+      <c r="Q153" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="154" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="I154" t="s">
         <v>62</v>
       </c>
-      <c r="M124" s="7" t="s">
+      <c r="M154" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="N124" s="7">
+      <c r="N154" s="7">
         <v>20</v>
       </c>
-      <c r="O124" s="7"/>
-      <c r="P124" s="7"/>
-      <c r="Q124" s="7"/>
-    </row>
-    <row r="125" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="I125" t="s">
+      <c r="O154" s="7"/>
+      <c r="P154" s="7"/>
+      <c r="Q154" s="7"/>
+    </row>
+    <row r="155" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="I155" t="s">
         <v>62</v>
       </c>
-      <c r="J125" t="s">
+      <c r="J155" t="s">
         <v>72</v>
       </c>
-      <c r="M125" s="7" t="s">
+      <c r="M155" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="N125" s="9">
+      <c r="N155" s="9">
         <v>1</v>
       </c>
-      <c r="O125" s="7"/>
-      <c r="P125" s="7"/>
-      <c r="Q125" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="126" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="I126" t="s">
+      <c r="O155" s="7"/>
+      <c r="P155" s="7"/>
+      <c r="Q155" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="156" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="I156" t="s">
         <v>62</v>
       </c>
-      <c r="J126" t="s">
+      <c r="J156" t="s">
         <v>71</v>
       </c>
-      <c r="M126" s="7" t="s">
+      <c r="M156" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="N126" s="9">
+      <c r="N156" s="9">
         <v>0.7</v>
       </c>
-      <c r="O126" s="7"/>
-      <c r="P126" s="7"/>
-      <c r="Q126" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="127" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="I127" t="s">
+      <c r="O156" s="7"/>
+      <c r="P156" s="7"/>
+      <c r="Q156" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="157" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="I157" t="s">
         <v>62</v>
       </c>
-      <c r="J127" t="s">
+      <c r="J157" t="s">
         <v>70</v>
       </c>
-      <c r="M127" s="7" t="s">
+      <c r="M157" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="N127" s="7">
+      <c r="N157" s="7">
         <v>0.45</v>
       </c>
-      <c r="O127" s="7"/>
-      <c r="P127" s="7"/>
-      <c r="Q127" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="128" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="M128" s="7"/>
-      <c r="N128" s="7"/>
-      <c r="O128" s="7"/>
-      <c r="P128" s="7"/>
-      <c r="Q128" s="7"/>
-    </row>
-    <row r="129" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="I129" t="s">
+      <c r="O157" s="7"/>
+      <c r="P157" s="7"/>
+      <c r="Q157" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="158" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="M158" s="7"/>
+      <c r="N158" s="7"/>
+      <c r="O158" s="7"/>
+      <c r="P158" s="7"/>
+      <c r="Q158" s="7"/>
+    </row>
+    <row r="159" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="I159" t="s">
         <v>61</v>
       </c>
-      <c r="M129" s="7" t="s">
+      <c r="M159" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="N129" s="7">
+      <c r="N159" s="7">
         <f>107*4</f>
         <v>428</v>
       </c>
-      <c r="O129" s="7"/>
-      <c r="P129" s="7" t="s">
+      <c r="O159" s="7"/>
+      <c r="P159" s="7" t="s">
+        <v>399</v>
+      </c>
+      <c r="Q159" t="s">
         <v>400</v>
       </c>
-      <c r="Q129" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="130" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="I130" t="s">
+    </row>
+    <row r="160" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="I160" t="s">
         <v>61</v>
       </c>
-      <c r="M130" s="7" t="s">
+      <c r="M160" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="N130" s="7">
+      <c r="N160" s="7">
         <f>6.3*4</f>
         <v>25.2</v>
       </c>
-      <c r="O130" s="7"/>
-      <c r="P130" s="7"/>
-      <c r="Q130" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="131" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="I131" t="s">
+      <c r="O160" s="7"/>
+      <c r="P160" s="7"/>
+      <c r="Q160" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="161" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="I161" t="s">
         <v>61</v>
       </c>
-      <c r="M131" s="7" t="s">
+      <c r="M161" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="N131" s="7">
+      <c r="N161" s="7">
         <v>0</v>
       </c>
-      <c r="O131" s="7"/>
-      <c r="P131" s="7"/>
-      <c r="Q131" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="132" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="I132" t="s">
+      <c r="O161" s="7"/>
+      <c r="P161" s="7"/>
+      <c r="Q161" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="162" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="I162" t="s">
         <v>61</v>
       </c>
-      <c r="M132" s="7" t="s">
+      <c r="M162" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="N132" s="7">
+      <c r="N162" s="7">
         <v>10</v>
       </c>
-      <c r="O132" s="7"/>
-      <c r="P132" s="7"/>
-      <c r="Q132" s="7"/>
-    </row>
-    <row r="133" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="I133" t="s">
+      <c r="O162" s="7"/>
+      <c r="P162" s="7"/>
+      <c r="Q162" s="7"/>
+    </row>
+    <row r="163" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="I163" t="s">
         <v>61</v>
       </c>
-      <c r="J133" t="s">
+      <c r="J163" t="s">
         <v>72</v>
       </c>
-      <c r="M133" s="7" t="s">
+      <c r="M163" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="N133" s="9">
+      <c r="N163" s="9">
         <v>1</v>
       </c>
-      <c r="O133" s="7"/>
-      <c r="P133" s="7"/>
-      <c r="Q133" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="134" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="I134" t="s">
+      <c r="O163" s="7"/>
+      <c r="P163" s="7"/>
+      <c r="Q163" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="164" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="I164" t="s">
         <v>61</v>
       </c>
-      <c r="J134" t="s">
+      <c r="J164" t="s">
         <v>71</v>
       </c>
-      <c r="M134" s="7" t="s">
+      <c r="M164" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="N134" s="7">
+      <c r="N164" s="7">
         <v>0.85</v>
       </c>
-      <c r="O134" s="7"/>
-      <c r="P134" s="7"/>
-      <c r="Q134" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="135" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="I135" t="s">
+      <c r="O164" s="7"/>
+      <c r="P164" s="7"/>
+      <c r="Q164" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="165" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="I165" t="s">
         <v>61</v>
       </c>
-      <c r="J135" t="s">
+      <c r="J165" t="s">
         <v>70</v>
       </c>
-      <c r="M135" s="7" t="s">
+      <c r="M165" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="N135" s="7">
+      <c r="N165" s="7">
         <v>0.65</v>
       </c>
-      <c r="O135" s="7"/>
-      <c r="P135" s="7"/>
-      <c r="Q135" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="136" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="M136" s="7"/>
-      <c r="N136" s="7"/>
-      <c r="O136" s="7"/>
-      <c r="P136" s="7"/>
-      <c r="Q136" s="7"/>
-    </row>
-    <row r="137" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="I137" t="s">
+      <c r="O165" s="7"/>
+      <c r="P165" s="7"/>
+      <c r="Q165" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="166" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="M166" s="7"/>
+      <c r="N166" s="7"/>
+      <c r="O166" s="7"/>
+      <c r="P166" s="7"/>
+      <c r="Q166" s="7"/>
+    </row>
+    <row r="167" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="I167" t="s">
         <v>64</v>
       </c>
-      <c r="M137" s="7" t="s">
+      <c r="M167" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="N137" s="9">
+      <c r="N167" s="9">
         <v>5.0999999999999996</v>
       </c>
-      <c r="O137" s="7"/>
-      <c r="P137" t="s">
+      <c r="O167" s="7"/>
+      <c r="P167" t="s">
         <v>90</v>
       </c>
-      <c r="Q137" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="138" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="I138" t="s">
+      <c r="Q167" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="168" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="I168" t="s">
         <v>65</v>
       </c>
-      <c r="M138" s="7" t="s">
+      <c r="M168" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="N138" s="9">
+      <c r="N168" s="9">
         <v>7.1</v>
       </c>
-      <c r="O138" s="7"/>
-      <c r="P138" t="s">
+      <c r="O168" s="7"/>
+      <c r="P168" t="s">
         <v>91</v>
       </c>
-      <c r="Q138" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="139" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="M139" s="7"/>
-      <c r="N139" s="7"/>
-      <c r="O139" s="7"/>
-      <c r="P139" s="7"/>
-      <c r="Q139" s="7"/>
-    </row>
-    <row r="140" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="I140" t="s">
+      <c r="Q168" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="169" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="M169" s="7"/>
+      <c r="N169" s="7"/>
+      <c r="O169" s="7"/>
+      <c r="P169" s="7"/>
+      <c r="Q169" s="7"/>
+    </row>
+    <row r="170" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="I170" t="s">
         <v>60</v>
       </c>
-      <c r="M140" s="7" t="s">
+      <c r="M170" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="N140" s="9">
+      <c r="N170" s="9">
         <v>3.7353333333333332</v>
       </c>
-      <c r="O140" s="7"/>
-      <c r="P140" s="7" t="s">
+      <c r="O170" s="7"/>
+      <c r="P170" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="Q140" t="s">
+      <c r="Q170" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="141" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="I141" t="s">
+    <row r="171" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="I171" t="s">
         <v>63</v>
       </c>
-      <c r="M141" s="7" t="s">
+      <c r="M171" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="N141" s="8">
+      <c r="N171" s="8">
         <v>17.096931944444446</v>
       </c>
-      <c r="O141" s="7"/>
-      <c r="P141" t="s">
+      <c r="O171" s="7"/>
+      <c r="P171" t="s">
         <v>86</v>
       </c>
-      <c r="Q141" t="s">
+      <c r="Q171" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="142" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="I142" t="s">
+    <row r="172" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="I172" t="s">
         <v>66</v>
       </c>
-      <c r="M142" s="7" t="s">
+      <c r="M172" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="N142" s="9">
+      <c r="N172" s="9">
         <v>1.2451111111111113</v>
       </c>
-      <c r="O142" s="7"/>
-      <c r="P142" t="s">
+      <c r="O172" s="7"/>
+      <c r="P172" t="s">
         <v>47</v>
       </c>
-      <c r="Q142" s="7" t="s">
+      <c r="Q172" s="7" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="143" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="I143" t="s">
-        <v>396</v>
-      </c>
-      <c r="M143" s="7" t="s">
-        <v>398</v>
-      </c>
-      <c r="N143" s="9">
+    <row r="173" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="I173" t="s">
+        <v>395</v>
+      </c>
+      <c r="M173" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="N173" s="9">
         <f>(3.11+4.67)/2</f>
         <v>3.8899999999999997</v>
       </c>
-      <c r="O143" s="7"/>
-      <c r="P143" t="s">
-        <v>395</v>
-      </c>
-      <c r="Q143" s="7" t="s">
+      <c r="O173" s="7"/>
+      <c r="P173" t="s">
+        <v>394</v>
+      </c>
+      <c r="Q173" s="7" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="144" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="I144" t="s">
+    <row r="174" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="I174" t="s">
         <v>67</v>
       </c>
-      <c r="M144" s="7" t="s">
+      <c r="M174" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="N144" s="9">
+      <c r="N174" s="9">
         <v>3.1127777777777781</v>
       </c>
-      <c r="O144" s="7"/>
-      <c r="P144" t="s">
+      <c r="O174" s="7"/>
+      <c r="P174" t="s">
         <v>92</v>
       </c>
-      <c r="Q144" t="s">
+      <c r="Q174" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="145" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="I145" t="s">
+    <row r="175" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="I175" t="s">
         <v>68</v>
       </c>
-      <c r="M145" s="7" t="s">
+      <c r="M175" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="N145" s="8">
+      <c r="N175" s="8">
         <v>11.828555555555555</v>
       </c>
-      <c r="O145" s="7"/>
-      <c r="P145" t="s">
+      <c r="O175" s="7"/>
+      <c r="P175" t="s">
         <v>96</v>
       </c>
-      <c r="Q145" s="7" t="s">
+      <c r="Q175" s="7" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="146" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="I146" t="s">
+    <row r="176" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="I176" t="s">
         <v>93</v>
       </c>
-      <c r="M146" s="7" t="s">
+      <c r="M176" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="N146" s="8">
+      <c r="N176" s="8">
         <v>26.302972222222223</v>
       </c>
-      <c r="O146" s="7"/>
-      <c r="P146" t="s">
+      <c r="O176" s="7"/>
+      <c r="P176" t="s">
         <v>97</v>
       </c>
-      <c r="Q146" s="7" t="s">
+      <c r="Q176" s="7" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="147" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="I147" t="s">
+    <row r="177" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="I177" t="s">
         <v>94</v>
       </c>
-      <c r="M147" s="7" t="s">
+      <c r="M177" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="N147" s="8">
+      <c r="N177" s="8">
         <v>11.3</v>
       </c>
-      <c r="O147" s="7"/>
-      <c r="P147" t="s">
+      <c r="O177" s="7"/>
+      <c r="P177" t="s">
         <v>99</v>
       </c>
-      <c r="Q147" s="7" t="s">
+      <c r="Q177" s="7" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="148" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="I148" t="s">
+    <row r="178" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="I178" t="s">
         <v>95</v>
       </c>
-      <c r="M148" s="7" t="s">
+      <c r="M178" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="N148" s="8">
+      <c r="N178" s="8">
         <v>23.278130416666666</v>
       </c>
-      <c r="O148" s="7"/>
-      <c r="P148" t="s">
+      <c r="O178" s="7"/>
+      <c r="P178" t="s">
         <v>98</v>
       </c>
-      <c r="Q148" s="7" t="s">
+      <c r="Q178" s="7" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="149" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="I149" t="s">
+    <row r="179" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="I179" t="s">
         <v>69</v>
       </c>
-      <c r="M149" s="7" t="s">
+      <c r="M179" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="N149" s="7">
+      <c r="N179" s="7">
         <v>13.15</v>
       </c>
-      <c r="O149" s="7"/>
-      <c r="P149" s="7" t="s">
+      <c r="O179" s="7"/>
+      <c r="P179" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="Q149" s="7" t="s">
+      <c r="Q179" s="7" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="150" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="I150" t="s">
+    <row r="180" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="I180" t="s">
         <v>69</v>
       </c>
-      <c r="M150" s="7" t="s">
+      <c r="M180" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="N150" s="7">
+      <c r="N180" s="7">
         <v>5.26</v>
       </c>
-      <c r="O150" s="7"/>
-      <c r="P150" s="7" t="s">
+      <c r="O180" s="7"/>
+      <c r="P180" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="Q150" s="7" t="s">
+      <c r="Q180" s="7" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="151" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B151" t="s">
+    <row r="181" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B181" t="s">
         <v>103</v>
       </c>
-      <c r="I151" t="s">
+      <c r="I181" t="s">
         <v>69</v>
       </c>
-      <c r="M151" s="7" t="s">
+      <c r="M181" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="N151" s="9">
+      <c r="N181" s="9">
         <v>1.7546281240590185</v>
       </c>
-      <c r="O151" s="7"/>
-      <c r="P151" s="7" t="s">
+      <c r="O181" s="7"/>
+      <c r="P181" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="Q151" t="s">
+      <c r="Q181" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="152" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B152" t="s">
+    <row r="182" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B182" t="s">
         <v>106</v>
       </c>
-      <c r="I152" t="s">
+      <c r="I182" t="s">
         <v>69</v>
       </c>
-      <c r="M152" s="7" t="s">
+      <c r="M182" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="N152" s="9">
+      <c r="N182" s="9">
         <v>5.1828516694033944</v>
       </c>
-      <c r="O152" s="7"/>
-      <c r="P152" t="s">
+      <c r="O182" s="7"/>
+      <c r="P182" t="s">
         <v>108</v>
       </c>
-      <c r="Q152" t="s">
+      <c r="Q182" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="153" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B153" t="s">
+    <row r="183" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B183" t="s">
         <v>107</v>
       </c>
-      <c r="I153" t="s">
+      <c r="I183" t="s">
         <v>69</v>
       </c>
-      <c r="M153" s="7" t="s">
+      <c r="M183" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="N153" s="10">
+      <c r="N183" s="10">
         <v>4.0531064740502947</v>
       </c>
-      <c r="P153" t="s">
+      <c r="P183" t="s">
         <v>109</v>
       </c>
-      <c r="Q153" t="s">
+      <c r="Q183" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="154" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B154" t="s">
+    <row r="184" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B184" t="s">
         <v>111</v>
       </c>
-      <c r="I154" t="s">
+      <c r="I184" t="s">
         <v>69</v>
       </c>
-      <c r="M154" s="7" t="s">
+      <c r="M184" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="N154" s="10">
+      <c r="N184" s="10">
         <v>4.3591310772039646</v>
       </c>
-      <c r="P154" t="s">
+      <c r="P184" t="s">
         <v>110</v>
       </c>
-      <c r="Q154" t="s">
+      <c r="Q184" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="155" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="M155" s="7"/>
-      <c r="N155" s="10"/>
-    </row>
-    <row r="156" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="I156" t="s">
+    <row r="185" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="M185" s="7"/>
+      <c r="N185" s="10"/>
+    </row>
+    <row r="186" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="I186" t="s">
         <v>113</v>
       </c>
-      <c r="M156" s="7" t="s">
+      <c r="M186" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="N156" s="10">
+      <c r="N186" s="10">
         <v>14.6</v>
       </c>
-      <c r="Q156" t="s">
+      <c r="Q186" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="157" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="I157" t="s">
+    <row r="187" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="I187" t="s">
         <v>117</v>
       </c>
-      <c r="K157" t="s">
+      <c r="K187" t="s">
         <v>114</v>
       </c>
-      <c r="M157" s="7" t="s">
+      <c r="M187" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="N157" s="10">
+      <c r="N187" s="10">
         <v>37.744765138888887</v>
       </c>
-      <c r="Q157" t="s">
+      <c r="Q187" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="158" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="I158" t="s">
+    <row r="188" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="I188" t="s">
         <v>117</v>
       </c>
-      <c r="K158" t="s">
+      <c r="K188" t="s">
         <v>115</v>
       </c>
-      <c r="M158" s="7" t="s">
+      <c r="M188" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="N158" s="10">
+      <c r="N188" s="10">
         <v>50.107162083333336</v>
       </c>
-      <c r="Q158" t="s">
+      <c r="Q188" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="159" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="I159" t="s">
+    <row r="189" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="I189" t="s">
         <v>117</v>
       </c>
-      <c r="K159" t="s">
+      <c r="K189" t="s">
         <v>116</v>
       </c>
-      <c r="M159" s="7" t="s">
+      <c r="M189" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="N159" s="10">
+      <c r="N189" s="10">
         <v>36.955675972222224</v>
       </c>
-      <c r="Q159" t="s">
+      <c r="Q189" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="160" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="M160" s="7"/>
-      <c r="N160" s="10"/>
-    </row>
-    <row r="161" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="I161" t="s">
+    <row r="190" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="M190" s="7"/>
+      <c r="N190" s="10"/>
+    </row>
+    <row r="191" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="I191" t="s">
         <v>124</v>
       </c>
-      <c r="M161" s="7" t="s">
+      <c r="M191" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="N161" s="10">
+      <c r="N191" s="10">
         <v>1.6176327916666666</v>
       </c>
-      <c r="O161" t="s">
+      <c r="O191" t="s">
         <v>56</v>
       </c>
-      <c r="P161" t="s">
+      <c r="P191" t="s">
         <v>128</v>
       </c>
-      <c r="Q161" t="s">
+      <c r="Q191" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="162" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="I162" t="s">
+    <row r="192" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="I192" t="s">
         <v>125</v>
       </c>
-      <c r="M162" s="7" t="s">
+      <c r="M192" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="N162" s="10">
+      <c r="N192" s="10">
         <f>3.07744775/0.85</f>
         <v>3.6205267647058825</v>
       </c>
-      <c r="O162" t="s">
+      <c r="O192" t="s">
+        <v>325</v>
+      </c>
+      <c r="P192" t="s">
         <v>326</v>
       </c>
-      <c r="P162" t="s">
+      <c r="Q192" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="193" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="I193" t="s">
+        <v>126</v>
+      </c>
+      <c r="M193" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="N193" s="10">
+        <v>0.25</v>
+      </c>
+      <c r="O193" t="s">
+        <v>58</v>
+      </c>
+      <c r="P193" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q193" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="195" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A195" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B195" s="1"/>
+      <c r="C195" s="1"/>
+      <c r="D195" s="1"/>
+      <c r="E195" s="1"/>
+      <c r="F195" s="1"/>
+      <c r="G195" s="1"/>
+      <c r="H195" s="1"/>
+      <c r="I195" s="1"/>
+      <c r="J195" s="1"/>
+      <c r="K195" s="1"/>
+      <c r="L195" s="1"/>
+      <c r="M195" s="5"/>
+      <c r="N195" s="5"/>
+      <c r="O195" s="5"/>
+      <c r="P195" s="5"/>
+      <c r="Q195" s="5"/>
+    </row>
+    <row r="196" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M196" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="N196" s="6">
+        <v>0</v>
+      </c>
+      <c r="P196" s="6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="197" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M197" t="s">
+        <v>48</v>
+      </c>
+      <c r="N197" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="199" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A199" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="B199" s="1"/>
+      <c r="C199" s="1"/>
+      <c r="D199" s="1"/>
+      <c r="E199" s="1"/>
+      <c r="F199" s="1"/>
+      <c r="G199" s="1"/>
+      <c r="H199" s="1"/>
+      <c r="I199" s="1"/>
+      <c r="J199" s="1"/>
+      <c r="K199" s="1"/>
+      <c r="L199" s="1"/>
+      <c r="M199" s="5"/>
+      <c r="N199" s="5"/>
+      <c r="O199" s="5"/>
+      <c r="P199" s="5"/>
+      <c r="Q199" s="5"/>
+    </row>
+    <row r="201" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M201" s="6" t="s">
         <v>327</v>
       </c>
-      <c r="Q162" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="163" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="I163" t="s">
-        <v>126</v>
-      </c>
-      <c r="M163" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="N163" s="10">
-        <v>0.25</v>
-      </c>
-      <c r="O163" t="s">
-        <v>58</v>
-      </c>
-      <c r="P163" t="s">
-        <v>129</v>
-      </c>
-      <c r="Q163" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="165" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A165" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B165" s="1"/>
-      <c r="C165" s="1"/>
-      <c r="D165" s="1"/>
-      <c r="E165" s="1"/>
-      <c r="F165" s="1"/>
-      <c r="G165" s="1"/>
-      <c r="H165" s="1"/>
-      <c r="I165" s="1"/>
-      <c r="J165" s="1"/>
-      <c r="K165" s="1"/>
-      <c r="L165" s="1"/>
-      <c r="M165" s="5"/>
-      <c r="N165" s="5"/>
-      <c r="O165" s="5"/>
-      <c r="P165" s="5"/>
-      <c r="Q165" s="5"/>
-    </row>
-    <row r="166" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M166" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="N166" s="6">
-        <v>0</v>
-      </c>
-      <c r="P166" s="6" t="s">
+      <c r="N201" s="6">
+        <v>100</v>
+      </c>
+      <c r="O201" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="P201" s="6" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="167" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M167" t="s">
-        <v>48</v>
-      </c>
-      <c r="N167" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="169" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A169" s="1" t="s">
+    <row r="202" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H202" t="s">
+        <v>321</v>
+      </c>
+      <c r="M202" t="s">
+        <v>327</v>
+      </c>
+      <c r="N202">
+        <v>88</v>
+      </c>
+      <c r="O202" t="s">
+        <v>121</v>
+      </c>
+      <c r="P202" t="s">
+        <v>328</v>
+      </c>
+      <c r="Q202" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="203" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H203" t="s">
+        <v>320</v>
+      </c>
+      <c r="M203" t="s">
+        <v>327</v>
+      </c>
+      <c r="N203">
+        <v>90</v>
+      </c>
+      <c r="O203" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q203" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="205" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M205" t="s">
+        <v>338</v>
+      </c>
+      <c r="N205">
+        <v>1.6E-2</v>
+      </c>
+      <c r="O205" t="s">
+        <v>220</v>
+      </c>
+      <c r="P205" t="s">
+        <v>346</v>
+      </c>
+      <c r="Q205" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="207" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M207" t="s">
         <v>348</v>
       </c>
-      <c r="B169" s="1"/>
-      <c r="C169" s="1"/>
-      <c r="D169" s="1"/>
-      <c r="E169" s="1"/>
-      <c r="F169" s="1"/>
-      <c r="G169" s="1"/>
-      <c r="H169" s="1"/>
-      <c r="I169" s="1"/>
-      <c r="J169" s="1"/>
-      <c r="K169" s="1"/>
-      <c r="L169" s="1"/>
-      <c r="M169" s="5"/>
-      <c r="N169" s="5"/>
-      <c r="O169" s="5"/>
-      <c r="P169" s="5"/>
-      <c r="Q169" s="5"/>
-    </row>
-    <row r="171" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M171" s="6" t="s">
-        <v>328</v>
-      </c>
-      <c r="N171" s="6">
-        <v>100</v>
-      </c>
-      <c r="O171" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="P171" s="6" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="172" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H172" t="s">
-        <v>322</v>
-      </c>
-      <c r="M172" t="s">
-        <v>328</v>
-      </c>
-      <c r="N172">
-        <v>88</v>
-      </c>
-      <c r="O172" t="s">
-        <v>121</v>
-      </c>
-      <c r="P172" t="s">
-        <v>329</v>
-      </c>
-      <c r="Q172" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="173" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H173" t="s">
-        <v>321</v>
-      </c>
-      <c r="M173" t="s">
-        <v>328</v>
-      </c>
-      <c r="N173">
-        <v>90</v>
-      </c>
-      <c r="O173" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q173" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="175" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M175" t="s">
-        <v>339</v>
-      </c>
-      <c r="N175">
-        <v>1.6E-2</v>
-      </c>
-      <c r="O175" t="s">
-        <v>221</v>
-      </c>
-      <c r="P175" t="s">
-        <v>347</v>
-      </c>
-      <c r="Q175" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="177" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M177" t="s">
-        <v>349</v>
-      </c>
-      <c r="N177" s="10">
+      <c r="N207" s="10">
         <f>0.16*10.36*0.9</f>
         <v>1.4918400000000001</v>
       </c>
-      <c r="O177" t="s">
+      <c r="O207" t="s">
+        <v>342</v>
+      </c>
+      <c r="P207" t="s">
         <v>343</v>
       </c>
-      <c r="P177" t="s">
+      <c r="Q207" t="s">
         <v>344</v>
       </c>
-      <c r="Q177" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="180" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M180" s="6" t="s">
+    </row>
+    <row r="210" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M210" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="N210" s="6">
+        <v>-99</v>
+      </c>
+      <c r="O210" s="6"/>
+      <c r="P210" s="6" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="211" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="C211" t="s">
+        <v>332</v>
+      </c>
+      <c r="M211" t="s">
+        <v>329</v>
+      </c>
+      <c r="N211">
+        <v>17</v>
+      </c>
+      <c r="O211" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q211" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="212" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="C212" t="s">
+        <v>333</v>
+      </c>
+      <c r="M212" t="s">
+        <v>329</v>
+      </c>
+      <c r="N212">
+        <v>17</v>
+      </c>
+      <c r="O212" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q212" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="213" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="C213" t="s">
+        <v>334</v>
+      </c>
+      <c r="M213" t="s">
+        <v>329</v>
+      </c>
+      <c r="N213">
+        <v>17</v>
+      </c>
+      <c r="O213" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q213" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="214" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="C214" t="s">
+        <v>335</v>
+      </c>
+      <c r="M214" t="s">
+        <v>329</v>
+      </c>
+      <c r="N214">
+        <v>14</v>
+      </c>
+      <c r="O214" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q214" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="216" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="C216" t="s">
+        <v>332</v>
+      </c>
+      <c r="M216" t="s">
         <v>330</v>
       </c>
-      <c r="N180" s="6">
-        <v>-99</v>
-      </c>
-      <c r="O180" s="6"/>
-      <c r="P180" s="6" t="s">
+      <c r="N216">
+        <v>14</v>
+      </c>
+      <c r="O216" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q216" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="181" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C181" t="s">
+    <row r="217" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="C217" t="s">
         <v>333</v>
       </c>
-      <c r="M181" t="s">
+      <c r="M217" t="s">
         <v>330</v>
       </c>
-      <c r="N181">
-        <v>17</v>
-      </c>
-      <c r="O181" t="s">
+      <c r="N217">
+        <v>14</v>
+      </c>
+      <c r="O217" t="s">
         <v>121</v>
       </c>
-      <c r="Q181" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="182" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C182" t="s">
+      <c r="Q217" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="218" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="C218" t="s">
         <v>334</v>
       </c>
-      <c r="M182" t="s">
+      <c r="M218" t="s">
         <v>330</v>
       </c>
-      <c r="N182">
-        <v>17</v>
-      </c>
-      <c r="O182" t="s">
+      <c r="N218">
+        <v>14</v>
+      </c>
+      <c r="O218" t="s">
         <v>121</v>
       </c>
-      <c r="Q182" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="183" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C183" t="s">
+      <c r="Q218" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="219" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="C219" t="s">
         <v>335</v>
       </c>
-      <c r="M183" t="s">
+      <c r="M219" t="s">
         <v>330</v>
       </c>
-      <c r="N183">
-        <v>17</v>
-      </c>
-      <c r="O183" t="s">
+      <c r="N219">
+        <v>9</v>
+      </c>
+      <c r="O219" t="s">
         <v>121</v>
       </c>
-      <c r="Q183" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="184" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C184" t="s">
-        <v>336</v>
-      </c>
-      <c r="M184" t="s">
-        <v>330</v>
-      </c>
-      <c r="N184">
-        <v>14</v>
-      </c>
-      <c r="O184" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q184" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="186" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C186" t="s">
-        <v>333</v>
-      </c>
-      <c r="M186" t="s">
-        <v>331</v>
-      </c>
-      <c r="N186">
-        <v>14</v>
-      </c>
-      <c r="O186" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q186" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="187" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C187" t="s">
-        <v>334</v>
-      </c>
-      <c r="M187" t="s">
-        <v>331</v>
-      </c>
-      <c r="N187">
-        <v>14</v>
-      </c>
-      <c r="O187" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q187" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="188" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C188" t="s">
-        <v>335</v>
-      </c>
-      <c r="M188" t="s">
-        <v>331</v>
-      </c>
-      <c r="N188">
-        <v>14</v>
-      </c>
-      <c r="O188" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q188" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="189" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C189" t="s">
-        <v>336</v>
-      </c>
-      <c r="M189" t="s">
-        <v>331</v>
-      </c>
-      <c r="N189">
-        <v>9</v>
-      </c>
-      <c r="O189" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q189" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="191" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A191" s="1" t="s">
+      <c r="Q219" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="221" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A221" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="B191" s="1"/>
-      <c r="C191" s="1"/>
-      <c r="D191" s="1"/>
-      <c r="E191" s="1"/>
-      <c r="F191" s="1"/>
-      <c r="G191" s="1"/>
-      <c r="H191" s="1"/>
-      <c r="I191" s="1"/>
-      <c r="J191" s="1"/>
-      <c r="K191" s="1"/>
-      <c r="L191" s="1"/>
-      <c r="M191" s="5"/>
-      <c r="N191" s="5"/>
-      <c r="O191" s="5"/>
-      <c r="P191" s="5"/>
-      <c r="Q191" s="5"/>
-    </row>
-    <row r="195" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M195" s="6" t="s">
+      <c r="B221" s="1"/>
+      <c r="C221" s="1"/>
+      <c r="D221" s="1"/>
+      <c r="E221" s="1"/>
+      <c r="F221" s="1"/>
+      <c r="G221" s="1"/>
+      <c r="H221" s="1"/>
+      <c r="I221" s="1"/>
+      <c r="J221" s="1"/>
+      <c r="K221" s="1"/>
+      <c r="L221" s="1"/>
+      <c r="M221" s="5"/>
+      <c r="N221" s="5"/>
+      <c r="O221" s="5"/>
+      <c r="P221" s="5"/>
+      <c r="Q221" s="5"/>
+    </row>
+    <row r="225" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M225" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="N195" s="6">
+      <c r="N225" s="6">
         <v>0</v>
       </c>
-      <c r="O195" s="6" t="s">
+      <c r="O225" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="P195" s="6" t="s">
+      <c r="P225" s="6" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="196" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B196" t="s">
+    <row r="226" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B226" t="s">
         <v>147</v>
       </c>
-      <c r="M196" t="s">
+      <c r="M226" t="s">
         <v>154</v>
       </c>
-      <c r="N196">
+      <c r="N226">
         <v>302</v>
       </c>
-      <c r="O196" t="s">
+      <c r="O226" t="s">
         <v>155</v>
       </c>
-      <c r="P196" t="s">
+      <c r="P226" t="s">
         <v>156</v>
       </c>
-      <c r="Q196" t="s">
+      <c r="Q226" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="197" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B197" t="s">
+    <row r="227" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B227" t="s">
         <v>148</v>
       </c>
-      <c r="M197" t="s">
+      <c r="M227" t="s">
         <v>154</v>
       </c>
-      <c r="N197">
+      <c r="N227">
         <v>197</v>
       </c>
-      <c r="O197" t="s">
+      <c r="O227" t="s">
         <v>155</v>
       </c>
-      <c r="P197" t="s">
+      <c r="P227" t="s">
         <v>157</v>
       </c>
-      <c r="Q197" t="s">
+      <c r="Q227" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="198" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B198" t="s">
+    <row r="228" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B228" t="s">
         <v>149</v>
       </c>
-      <c r="M198" t="s">
+      <c r="M228" t="s">
         <v>154</v>
       </c>
-      <c r="N198">
+      <c r="N228">
         <v>216</v>
       </c>
-      <c r="O198" t="s">
+      <c r="O228" t="s">
         <v>155</v>
       </c>
-      <c r="P198" t="s">
+      <c r="P228" t="s">
         <v>158</v>
       </c>
-      <c r="Q198" t="s">
+      <c r="Q228" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="199" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B199" t="s">
+    <row r="229" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B229" t="s">
         <v>150</v>
       </c>
-      <c r="M199" t="s">
+      <c r="M229" t="s">
         <v>154</v>
       </c>
-      <c r="N199">
+      <c r="N229">
         <v>216</v>
       </c>
-      <c r="O199" t="s">
+      <c r="O229" t="s">
         <v>155</v>
       </c>
-      <c r="P199" t="s">
+      <c r="P229" t="s">
         <v>158</v>
       </c>
-      <c r="Q199" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="200" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B200" t="s">
+      <c r="Q229" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="230" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B230" t="s">
         <v>151</v>
       </c>
-      <c r="M200" t="s">
+      <c r="M230" t="s">
         <v>154</v>
       </c>
-      <c r="N200">
+      <c r="N230">
         <v>216</v>
       </c>
-      <c r="O200" t="s">
+      <c r="O230" t="s">
         <v>155</v>
       </c>
-      <c r="P200" t="s">
+      <c r="P230" t="s">
         <v>158</v>
       </c>
-      <c r="Q200" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="201" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B201" t="s">
+      <c r="Q230" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="231" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B231" t="s">
         <v>152</v>
       </c>
-      <c r="M201" t="s">
+      <c r="M231" t="s">
         <v>154</v>
       </c>
-      <c r="N201">
+      <c r="N231">
         <v>216</v>
       </c>
-      <c r="O201" t="s">
+      <c r="O231" t="s">
         <v>155</v>
       </c>
-      <c r="P201" t="s">
+      <c r="P231" t="s">
         <v>158</v>
       </c>
-      <c r="Q201" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="202" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B202" t="s">
+      <c r="Q231" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="232" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B232" t="s">
         <v>153</v>
       </c>
-      <c r="M202" t="s">
+      <c r="M232" t="s">
         <v>154</v>
       </c>
-      <c r="N202">
+      <c r="N232">
         <v>216</v>
       </c>
-      <c r="O202" t="s">
+      <c r="O232" t="s">
         <v>155</v>
       </c>
-      <c r="P202" t="s">
+      <c r="P232" t="s">
         <v>158</v>
       </c>
-      <c r="Q202" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="204" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A204" s="1" t="s">
+      <c r="Q232" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="234" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A234" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B234" s="1"/>
+      <c r="C234" s="1"/>
+      <c r="D234" s="1"/>
+      <c r="E234" s="1"/>
+      <c r="F234" s="1"/>
+      <c r="G234" s="1"/>
+      <c r="H234" s="1"/>
+      <c r="I234" s="1"/>
+      <c r="J234" s="1"/>
+      <c r="K234" s="1"/>
+      <c r="L234" s="1"/>
+      <c r="M234" s="5"/>
+      <c r="N234" s="5"/>
+      <c r="O234" s="5"/>
+      <c r="P234" s="5"/>
+      <c r="Q234" s="5"/>
+    </row>
+    <row r="235" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M235" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="N235" s="6">
+        <v>0</v>
+      </c>
+      <c r="O235" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="P235" s="6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="236" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M236" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="N236" s="6">
+        <v>0</v>
+      </c>
+      <c r="O236" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="P236" s="6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="237" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M237" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="N237" s="6">
+        <v>0</v>
+      </c>
+      <c r="O237" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="P237" s="6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="239" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
         <v>188</v>
       </c>
-      <c r="B204" s="1"/>
-      <c r="C204" s="1"/>
-      <c r="D204" s="1"/>
-      <c r="E204" s="1"/>
-      <c r="F204" s="1"/>
-      <c r="G204" s="1"/>
-      <c r="H204" s="1"/>
-      <c r="I204" s="1"/>
-      <c r="J204" s="1"/>
-      <c r="K204" s="1"/>
-      <c r="L204" s="1"/>
-      <c r="M204" s="5"/>
-      <c r="N204" s="5"/>
-      <c r="O204" s="5"/>
-      <c r="P204" s="5"/>
-      <c r="Q204" s="5"/>
-    </row>
-    <row r="205" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M205" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="N205" s="6">
-        <v>0</v>
-      </c>
-      <c r="O205" s="6" t="s">
-        <v>307</v>
-      </c>
-      <c r="P205" s="6" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="206" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M206" s="6" t="s">
-        <v>317</v>
-      </c>
-      <c r="N206" s="6">
-        <v>0</v>
-      </c>
-      <c r="O206" s="6" t="s">
-        <v>316</v>
-      </c>
-      <c r="P206" s="6" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="207" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M207" s="6" t="s">
-        <v>220</v>
-      </c>
-      <c r="N207" s="6">
-        <v>0</v>
-      </c>
-      <c r="O207" s="6" t="s">
+      <c r="D239" t="s">
+        <v>186</v>
+      </c>
+      <c r="E239" t="s">
+        <v>195</v>
+      </c>
+      <c r="F239" t="s">
+        <v>196</v>
+      </c>
+      <c r="G239" t="s">
         <v>221</v>
       </c>
-      <c r="P207" s="6" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="209" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A209" t="s">
-        <v>189</v>
-      </c>
-      <c r="D209" t="s">
-        <v>187</v>
-      </c>
-      <c r="E209" t="s">
-        <v>196</v>
-      </c>
-      <c r="F209" t="s">
-        <v>197</v>
-      </c>
-      <c r="G209" t="s">
-        <v>222</v>
-      </c>
-      <c r="M209" t="s">
-        <v>220</v>
-      </c>
-      <c r="N209" s="20">
+      <c r="M239" t="s">
+        <v>219</v>
+      </c>
+      <c r="N239" s="20">
         <f>'energy stables'!E24</f>
         <v>3.5302245250431775E-2</v>
       </c>
-      <c r="O209" t="s">
+      <c r="O239" t="s">
+        <v>191</v>
+      </c>
+      <c r="P239" t="s">
+        <v>205</v>
+      </c>
+      <c r="Q239" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="240" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
         <v>192</v>
       </c>
-      <c r="P209" t="s">
-        <v>206</v>
-      </c>
-      <c r="Q209" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="210" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A210" t="s">
-        <v>193</v>
-      </c>
-      <c r="D210" t="s">
-        <v>187</v>
-      </c>
-      <c r="E210" t="s">
+      <c r="D240" t="s">
+        <v>186</v>
+      </c>
+      <c r="E240" t="s">
+        <v>195</v>
+      </c>
+      <c r="F240" t="s">
         <v>196</v>
       </c>
-      <c r="F210" t="s">
-        <v>197</v>
-      </c>
-      <c r="M210" t="s">
-        <v>218</v>
-      </c>
-      <c r="N210" s="19">
+      <c r="M240" t="s">
+        <v>217</v>
+      </c>
+      <c r="N240" s="19">
         <f>'energy stables'!D26</f>
         <v>308.33833333333342</v>
       </c>
-      <c r="O210" t="s">
-        <v>307</v>
-      </c>
-      <c r="P210" t="s">
-        <v>226</v>
-      </c>
-      <c r="Q210" t="s">
+      <c r="O240" t="s">
+        <v>306</v>
+      </c>
+      <c r="P240" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="211" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A211" t="s">
-        <v>191</v>
-      </c>
-      <c r="D211" t="s">
-        <v>187</v>
-      </c>
-      <c r="E211" t="s">
+      <c r="Q240" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="241" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>190</v>
+      </c>
+      <c r="D241" t="s">
+        <v>186</v>
+      </c>
+      <c r="E241" t="s">
+        <v>195</v>
+      </c>
+      <c r="F241" t="s">
         <v>196</v>
       </c>
-      <c r="F211" t="s">
-        <v>197</v>
-      </c>
-      <c r="G211" t="s">
-        <v>222</v>
-      </c>
-      <c r="M211" t="s">
-        <v>220</v>
-      </c>
-      <c r="N211" s="20">
+      <c r="G241" t="s">
+        <v>221</v>
+      </c>
+      <c r="M241" t="s">
+        <v>219</v>
+      </c>
+      <c r="N241" s="20">
         <f>'energy stables'!E27</f>
         <v>4.1036269430051814E-2</v>
       </c>
-      <c r="O211" t="s">
-        <v>192</v>
-      </c>
-      <c r="Q211" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="213" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A213" t="s">
-        <v>189</v>
-      </c>
-      <c r="D213" t="s">
-        <v>187</v>
-      </c>
-      <c r="M213" t="s">
-        <v>218</v>
-      </c>
-      <c r="N213" s="19">
+      <c r="O241" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q241" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="243" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
+        <v>188</v>
+      </c>
+      <c r="D243" t="s">
+        <v>186</v>
+      </c>
+      <c r="M243" t="s">
+        <v>217</v>
+      </c>
+      <c r="N243" s="19">
         <f>'energy stables'!D29</f>
         <v>170.33333333333331</v>
       </c>
-      <c r="O213" t="s">
-        <v>307</v>
-      </c>
-      <c r="P213" t="s">
-        <v>231</v>
-      </c>
-      <c r="Q213" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="214" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A214" t="s">
-        <v>193</v>
-      </c>
-      <c r="D214" t="s">
-        <v>187</v>
-      </c>
-      <c r="M214" t="s">
-        <v>218</v>
-      </c>
-      <c r="N214" s="19">
+      <c r="O243" t="s">
+        <v>306</v>
+      </c>
+      <c r="P243" t="s">
+        <v>230</v>
+      </c>
+      <c r="Q243" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="244" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A244" t="s">
+        <v>192</v>
+      </c>
+      <c r="D244" t="s">
+        <v>186</v>
+      </c>
+      <c r="M244" t="s">
+        <v>217</v>
+      </c>
+      <c r="N244" s="19">
         <f>'energy stables'!D31</f>
         <v>332.32333333333338</v>
       </c>
-      <c r="O214" t="s">
-        <v>307</v>
-      </c>
-      <c r="P214" t="s">
+      <c r="O244" t="s">
+        <v>306</v>
+      </c>
+      <c r="P244" t="s">
+        <v>231</v>
+      </c>
+      <c r="Q244" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="245" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="N245" s="19"/>
+    </row>
+    <row r="246" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A246" t="s">
+        <v>188</v>
+      </c>
+      <c r="D246" t="s">
+        <v>226</v>
+      </c>
+      <c r="E246" t="s">
+        <v>227</v>
+      </c>
+      <c r="F246" t="s">
         <v>232</v>
       </c>
-      <c r="Q214" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="215" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N215" s="19"/>
-    </row>
-    <row r="216" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A216" t="s">
-        <v>189</v>
-      </c>
-      <c r="D216" t="s">
-        <v>227</v>
-      </c>
-      <c r="E216" t="s">
-        <v>228</v>
-      </c>
-      <c r="F216" t="s">
-        <v>233</v>
-      </c>
-      <c r="M216" t="s">
-        <v>317</v>
-      </c>
-      <c r="N216" s="20">
+      <c r="M246" t="s">
+        <v>316</v>
+      </c>
+      <c r="N246" s="20">
         <f>(290+1078)/100000</f>
         <v>1.3679999999999999E-2</v>
       </c>
-      <c r="O216" t="s">
+      <c r="O246" t="s">
+        <v>315</v>
+      </c>
+      <c r="P246" t="s">
+        <v>228</v>
+      </c>
+      <c r="Q246" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="247" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A247" t="s">
+        <v>189</v>
+      </c>
+      <c r="D247" t="s">
+        <v>226</v>
+      </c>
+      <c r="E247" t="s">
+        <v>227</v>
+      </c>
+      <c r="F247" t="s">
+        <v>232</v>
+      </c>
+      <c r="M247" t="s">
         <v>316</v>
       </c>
-      <c r="P216" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q216" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="217" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A217" t="s">
-        <v>190</v>
-      </c>
-      <c r="D217" t="s">
-        <v>227</v>
-      </c>
-      <c r="E217" t="s">
-        <v>228</v>
-      </c>
-      <c r="F217" t="s">
-        <v>233</v>
-      </c>
-      <c r="M217" t="s">
-        <v>317</v>
-      </c>
-      <c r="N217" s="20">
+      <c r="N247" s="20">
         <f>77000/100000</f>
         <v>0.77</v>
       </c>
-      <c r="O217" t="s">
+      <c r="O247" t="s">
+        <v>315</v>
+      </c>
+      <c r="Q247" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="248" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A248" t="s">
+        <v>192</v>
+      </c>
+      <c r="D248" t="s">
+        <v>226</v>
+      </c>
+      <c r="E248" t="s">
+        <v>227</v>
+      </c>
+      <c r="F248" t="s">
+        <v>232</v>
+      </c>
+      <c r="M248" t="s">
         <v>316</v>
       </c>
-      <c r="Q217" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="218" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A218" t="s">
-        <v>193</v>
-      </c>
-      <c r="D218" t="s">
-        <v>227</v>
-      </c>
-      <c r="E218" t="s">
-        <v>228</v>
-      </c>
-      <c r="F218" t="s">
-        <v>233</v>
-      </c>
-      <c r="M218" t="s">
-        <v>317</v>
-      </c>
-      <c r="N218" s="20">
+      <c r="N248" s="20">
         <f>(3340+9790)/100000</f>
         <v>0.1313</v>
       </c>
-      <c r="O218" t="s">
+      <c r="O248" t="s">
+        <v>315</v>
+      </c>
+      <c r="P248" t="s">
+        <v>229</v>
+      </c>
+      <c r="Q248" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="250" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A250" t="s">
+        <v>188</v>
+      </c>
+      <c r="D250" t="s">
+        <v>233</v>
+      </c>
+      <c r="F250" t="s">
+        <v>309</v>
+      </c>
+      <c r="M250" t="s">
         <v>316</v>
       </c>
-      <c r="P218" t="s">
-        <v>230</v>
-      </c>
-      <c r="Q218" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="220" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A220" t="s">
-        <v>189</v>
-      </c>
-      <c r="D220" t="s">
-        <v>234</v>
-      </c>
-      <c r="F220" t="s">
-        <v>310</v>
-      </c>
-      <c r="M220" t="s">
-        <v>317</v>
-      </c>
-      <c r="N220">
+      <c r="N250">
         <f>'energy stables'!D49</f>
         <v>3.5</v>
       </c>
-      <c r="O220" t="s">
+      <c r="O250" t="s">
+        <v>315</v>
+      </c>
+      <c r="Q250" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="251" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A251" t="s">
+        <v>189</v>
+      </c>
+      <c r="D251" t="s">
+        <v>233</v>
+      </c>
+      <c r="F251" t="s">
+        <v>309</v>
+      </c>
+      <c r="M251" t="s">
         <v>316</v>
       </c>
-      <c r="Q220" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="221" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A221" t="s">
-        <v>190</v>
-      </c>
-      <c r="D221" t="s">
-        <v>234</v>
-      </c>
-      <c r="F221" t="s">
-        <v>310</v>
-      </c>
-      <c r="M221" t="s">
-        <v>317</v>
-      </c>
-      <c r="N221">
+      <c r="N251">
         <f>'energy stables'!D50</f>
         <v>12.5</v>
       </c>
-      <c r="O221" t="s">
+      <c r="O251" t="s">
+        <v>315</v>
+      </c>
+      <c r="Q251" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="252" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A252" t="s">
+        <v>192</v>
+      </c>
+      <c r="D252" t="s">
+        <v>233</v>
+      </c>
+      <c r="F252" t="s">
+        <v>309</v>
+      </c>
+      <c r="M252" t="s">
         <v>316</v>
       </c>
-      <c r="Q221" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="222" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A222" t="s">
-        <v>193</v>
-      </c>
-      <c r="D222" t="s">
-        <v>234</v>
-      </c>
-      <c r="F222" t="s">
-        <v>310</v>
-      </c>
-      <c r="M222" t="s">
-        <v>317</v>
-      </c>
-      <c r="N222">
+      <c r="N252">
         <f>'energy stables'!D51</f>
         <v>34</v>
       </c>
-      <c r="O222" t="s">
+      <c r="O252" t="s">
+        <v>315</v>
+      </c>
+      <c r="Q252" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="253" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A253" t="s">
+        <v>188</v>
+      </c>
+      <c r="D253" t="s">
+        <v>233</v>
+      </c>
+      <c r="F253" t="s">
+        <v>312</v>
+      </c>
+      <c r="M253" t="s">
         <v>316</v>
       </c>
-      <c r="Q222" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="223" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A223" t="s">
-        <v>189</v>
-      </c>
-      <c r="D223" t="s">
-        <v>234</v>
-      </c>
-      <c r="F223" t="s">
-        <v>313</v>
-      </c>
-      <c r="M223" t="s">
-        <v>317</v>
-      </c>
-      <c r="N223">
+      <c r="N253">
         <f>'energy stables'!D53</f>
         <v>0.04</v>
       </c>
-      <c r="O223" t="s">
+      <c r="O253" t="s">
+        <v>315</v>
+      </c>
+      <c r="Q253" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="254" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A254" t="s">
+        <v>189</v>
+      </c>
+      <c r="D254" t="s">
+        <v>233</v>
+      </c>
+      <c r="F254" t="s">
+        <v>312</v>
+      </c>
+      <c r="M254" t="s">
         <v>316</v>
       </c>
-      <c r="Q223" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="224" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A224" t="s">
-        <v>190</v>
-      </c>
-      <c r="D224" t="s">
-        <v>234</v>
-      </c>
-      <c r="F224" t="s">
-        <v>313</v>
-      </c>
-      <c r="M224" t="s">
-        <v>317</v>
-      </c>
-      <c r="N224" s="10">
+      <c r="N254" s="10">
         <f>'energy stables'!D54</f>
         <v>0.1</v>
       </c>
-      <c r="O224" t="s">
+      <c r="O254" t="s">
+        <v>315</v>
+      </c>
+      <c r="Q254" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="255" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A255" t="s">
+        <v>192</v>
+      </c>
+      <c r="D255" t="s">
+        <v>233</v>
+      </c>
+      <c r="F255" t="s">
+        <v>312</v>
+      </c>
+      <c r="M255" t="s">
         <v>316</v>
       </c>
-      <c r="Q224" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="225" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A225" t="s">
-        <v>193</v>
-      </c>
-      <c r="D225" t="s">
-        <v>234</v>
-      </c>
-      <c r="F225" t="s">
-        <v>313</v>
-      </c>
-      <c r="M225" t="s">
-        <v>317</v>
-      </c>
-      <c r="N225" s="10">
+      <c r="N255" s="10">
         <f>'energy stables'!D55</f>
         <v>0.26</v>
       </c>
-      <c r="O225" t="s">
-        <v>316</v>
-      </c>
-      <c r="Q225" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="227" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A227" t="s">
-        <v>189</v>
-      </c>
-      <c r="D227" t="s">
-        <v>227</v>
-      </c>
-      <c r="E227" t="s">
-        <v>353</v>
-      </c>
-      <c r="M227" t="s">
-        <v>218</v>
-      </c>
-      <c r="N227" s="10">
+      <c r="O255" t="s">
+        <v>315</v>
+      </c>
+      <c r="Q255" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="257" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A257" t="s">
+        <v>188</v>
+      </c>
+      <c r="D257" t="s">
+        <v>226</v>
+      </c>
+      <c r="E257" t="s">
+        <v>352</v>
+      </c>
+      <c r="M257" t="s">
+        <v>217</v>
+      </c>
+      <c r="N257" s="10">
         <f>'energy stables'!D65</f>
         <v>0.14449999999999999</v>
       </c>
-      <c r="O227" t="s">
-        <v>307</v>
-      </c>
-      <c r="P227" t="s">
-        <v>384</v>
-      </c>
-      <c r="Q227" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="228" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A228" t="s">
-        <v>193</v>
-      </c>
-      <c r="D228" t="s">
-        <v>227</v>
-      </c>
-      <c r="E228" t="s">
-        <v>353</v>
-      </c>
-      <c r="M228" t="s">
-        <v>218</v>
-      </c>
-      <c r="N228" s="10">
+      <c r="O257" t="s">
+        <v>306</v>
+      </c>
+      <c r="P257" t="s">
+        <v>383</v>
+      </c>
+      <c r="Q257" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="258" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A258" t="s">
+        <v>192</v>
+      </c>
+      <c r="D258" t="s">
+        <v>226</v>
+      </c>
+      <c r="E258" t="s">
+        <v>352</v>
+      </c>
+      <c r="M258" t="s">
+        <v>217</v>
+      </c>
+      <c r="N258" s="10">
         <f>'energy stables'!D67</f>
         <v>3.9295</v>
       </c>
-      <c r="O228" t="s">
-        <v>307</v>
-      </c>
-      <c r="P228" t="s">
-        <v>385</v>
-      </c>
-      <c r="Q228" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="229" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A229" t="s">
+      <c r="O258" t="s">
+        <v>306</v>
+      </c>
+      <c r="P258" t="s">
+        <v>384</v>
+      </c>
+      <c r="Q258" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="259" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A259" t="s">
+        <v>188</v>
+      </c>
+      <c r="D259" t="s">
+        <v>226</v>
+      </c>
+      <c r="E259" t="s">
+        <v>352</v>
+      </c>
+      <c r="F259" t="s">
+        <v>353</v>
+      </c>
+      <c r="M259" t="s">
+        <v>217</v>
+      </c>
+      <c r="N259">
+        <v>0</v>
+      </c>
+      <c r="O259" t="s">
+        <v>306</v>
+      </c>
+      <c r="P259" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="260" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A260" t="s">
+        <v>192</v>
+      </c>
+      <c r="D260" t="s">
+        <v>226</v>
+      </c>
+      <c r="E260" t="s">
+        <v>352</v>
+      </c>
+      <c r="F260" t="s">
+        <v>353</v>
+      </c>
+      <c r="M260" t="s">
+        <v>217</v>
+      </c>
+      <c r="N260">
+        <v>0</v>
+      </c>
+      <c r="O260">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A261" t="s">
         <v>189</v>
       </c>
-      <c r="D229" t="s">
-        <v>227</v>
-      </c>
-      <c r="E229" t="s">
+      <c r="D261" t="s">
+        <v>226</v>
+      </c>
+      <c r="E261" t="s">
+        <v>352</v>
+      </c>
+      <c r="F261" t="s">
         <v>353</v>
       </c>
-      <c r="F229" t="s">
-        <v>354</v>
-      </c>
-      <c r="M229" t="s">
-        <v>218</v>
-      </c>
-      <c r="N229">
-        <v>0</v>
-      </c>
-      <c r="O229" t="s">
-        <v>307</v>
-      </c>
-      <c r="P229" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="230" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A230" t="s">
-        <v>193</v>
-      </c>
-      <c r="D230" t="s">
-        <v>227</v>
-      </c>
-      <c r="E230" t="s">
-        <v>353</v>
-      </c>
-      <c r="F230" t="s">
-        <v>354</v>
-      </c>
-      <c r="M230" t="s">
-        <v>218</v>
-      </c>
-      <c r="N230">
-        <v>0</v>
-      </c>
-      <c r="O230">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="231" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A231" t="s">
-        <v>190</v>
-      </c>
-      <c r="D231" t="s">
-        <v>227</v>
-      </c>
-      <c r="E231" t="s">
-        <v>353</v>
-      </c>
-      <c r="F231" t="s">
-        <v>354</v>
-      </c>
-      <c r="M231" t="s">
-        <v>317</v>
-      </c>
-      <c r="N231" s="10">
+      <c r="M261" t="s">
+        <v>316</v>
+      </c>
+      <c r="N261" s="10">
         <f>4.7*(1/3.6)</f>
         <v>1.3055555555555556</v>
       </c>
-      <c r="O231" t="s">
-        <v>316</v>
-      </c>
-      <c r="P231" t="s">
-        <v>356</v>
-      </c>
-      <c r="Q231" t="s">
+      <c r="O261" t="s">
+        <v>315</v>
+      </c>
+      <c r="P261" t="s">
         <v>355</v>
       </c>
-    </row>
-    <row r="233" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A233" t="s">
-        <v>189</v>
-      </c>
-      <c r="D233" t="s">
-        <v>386</v>
-      </c>
-      <c r="M233" t="s">
-        <v>218</v>
-      </c>
-      <c r="N233" s="19">
+      <c r="Q261" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="263" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A263" t="s">
+        <v>188</v>
+      </c>
+      <c r="D263" t="s">
+        <v>385</v>
+      </c>
+      <c r="M263" t="s">
+        <v>217</v>
+      </c>
+      <c r="N263" s="19">
         <f>0.05*1000*(1/3.6)</f>
         <v>13.888888888888889</v>
       </c>
-      <c r="O233" t="s">
-        <v>307</v>
-      </c>
-      <c r="P233" t="s">
+      <c r="O263" t="s">
+        <v>306</v>
+      </c>
+      <c r="P263" t="s">
+        <v>388</v>
+      </c>
+      <c r="Q263" t="s">
         <v>389</v>
       </c>
-      <c r="Q233" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="234" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A234" t="s">
-        <v>193</v>
-      </c>
-      <c r="D234" t="s">
-        <v>386</v>
-      </c>
-      <c r="M234" t="s">
-        <v>218</v>
-      </c>
-      <c r="N234" s="19">
+    </row>
+    <row r="264" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A264" t="s">
+        <v>192</v>
+      </c>
+      <c r="D264" t="s">
+        <v>385</v>
+      </c>
+      <c r="M264" t="s">
+        <v>217</v>
+      </c>
+      <c r="N264" s="19">
         <f>0.05*1000*(1/3.6)</f>
         <v>13.888888888888889</v>
       </c>
-      <c r="O234" t="s">
-        <v>307</v>
-      </c>
-      <c r="P234" t="s">
-        <v>391</v>
-      </c>
-      <c r="Q234" t="s">
+      <c r="O264" t="s">
+        <v>306</v>
+      </c>
+      <c r="P264" t="s">
         <v>390</v>
       </c>
-    </row>
-    <row r="235" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A235" t="s">
-        <v>189</v>
-      </c>
-      <c r="D235" t="s">
+      <c r="Q264" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="265" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A265" t="s">
+        <v>188</v>
+      </c>
+      <c r="D265" t="s">
+        <v>385</v>
+      </c>
+      <c r="F265" t="s">
         <v>386</v>
       </c>
-      <c r="F235" t="s">
+      <c r="M265" t="s">
+        <v>217</v>
+      </c>
+      <c r="N265">
+        <v>0</v>
+      </c>
+      <c r="P265" t="s">
         <v>387</v>
       </c>
-      <c r="M235" t="s">
-        <v>218</v>
-      </c>
-      <c r="N235">
-        <v>0</v>
-      </c>
-      <c r="P235" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="236" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A236" t="s">
-        <v>193</v>
-      </c>
-      <c r="D236" t="s">
+    </row>
+    <row r="266" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A266" t="s">
+        <v>192</v>
+      </c>
+      <c r="D266" t="s">
+        <v>385</v>
+      </c>
+      <c r="F266" t="s">
         <v>386</v>
       </c>
-      <c r="F236" t="s">
-        <v>387</v>
-      </c>
-      <c r="M236" t="s">
-        <v>218</v>
-      </c>
-      <c r="N236">
+      <c r="M266" t="s">
+        <v>217</v>
+      </c>
+      <c r="N266">
         <v>0</v>
       </c>
     </row>
@@ -6534,7 +7227,7 @@
   <sheetData>
     <row r="3" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B3" s="46" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C3" s="45"/>
       <c r="D3" s="45"/>
@@ -6554,37 +7247,37 @@
     </row>
     <row r="4" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B4" s="44" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B5" s="22"/>
       <c r="C5" s="25"/>
       <c r="D5" s="40" t="s">
+        <v>198</v>
+      </c>
+      <c r="E5" s="23" t="s">
+        <v>196</v>
+      </c>
+      <c r="F5" s="25" t="s">
+        <v>215</v>
+      </c>
+      <c r="G5" s="24" t="s">
         <v>199</v>
       </c>
-      <c r="E5" s="23" t="s">
-        <v>197</v>
-      </c>
-      <c r="F5" s="25" t="s">
-        <v>216</v>
-      </c>
-      <c r="G5" s="24" t="s">
-        <v>200</v>
-      </c>
       <c r="H5" s="23" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I5" s="25" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="6" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B6" s="26" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C6" s="38" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D6" s="26">
         <v>150</v>
@@ -6597,10 +7290,10 @@
     </row>
     <row r="7" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B7" s="26" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C7" s="38" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D7" s="26">
         <v>150</v>
@@ -6613,10 +7306,10 @@
     </row>
     <row r="8" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B8" s="26" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C8" s="38" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D8" s="26">
         <v>10500</v>
@@ -6636,10 +7329,10 @@
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B10" s="26" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C10" s="38" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D10" s="26">
         <v>652</v>
@@ -6664,15 +7357,15 @@
         <v>123.33333333333333</v>
       </c>
       <c r="J10" s="21" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B11" s="26" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C11" s="38" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D11" s="26">
         <v>3</v>
@@ -6700,10 +7393,10 @@
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B12" s="26" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C12" s="38" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D12" s="26">
         <v>40</v>
@@ -6728,15 +7421,15 @@
         <v>10.333333333333332</v>
       </c>
       <c r="J12" s="21" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B13" s="26" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C13" s="38" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D13" s="26">
         <v>216</v>
@@ -6764,10 +7457,10 @@
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B14" s="26" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C14" s="38" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D14" s="26">
         <v>386</v>
@@ -6790,15 +7483,15 @@
         <v>0</v>
       </c>
       <c r="J14" s="21" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="15" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B15" s="26" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C15" s="38" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D15" s="26">
         <v>216</v>
@@ -6834,10 +7527,10 @@
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B17" s="30" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C17" s="38" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D17" s="30">
         <f>SUM(D10:D15)</f>
@@ -6866,10 +7559,10 @@
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B18" s="26" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C18" s="38" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D18" s="26">
         <v>868</v>
@@ -6924,7 +7617,7 @@
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B20" s="36" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C20" s="39" t="s">
         <v>121</v>
@@ -6942,25 +7635,25 @@
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B22" s="63" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B23" s="71"/>
       <c r="C23" s="72"/>
       <c r="D23" s="73" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E23" s="74" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B24" s="56" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C24" s="57" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D24" s="64">
         <v>0</v>
@@ -6972,10 +7665,10 @@
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B25" s="56" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C25" s="57" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D25" s="64">
         <v>0</v>
@@ -6986,10 +7679,10 @@
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B26" s="56" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C26" s="57" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D26" s="67">
         <f>SUM(E11:E13,E15,H11:H13,H15)/2</f>
@@ -7001,10 +7694,10 @@
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B27" s="56" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C27" s="57" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D27" s="64">
         <v>0</v>
@@ -7022,10 +7715,10 @@
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B29" s="56" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C29" s="57" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D29" s="67">
         <f>SUM(F10,I10)/2</f>
@@ -7037,10 +7730,10 @@
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B30" s="56" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C30" s="57" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D30" s="64">
         <v>0</v>
@@ -7051,10 +7744,10 @@
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B31" s="56" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C31" s="57" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D31" s="67">
         <f>SUM(F11:F13,F15,I11:I13,I15)</f>
@@ -7066,10 +7759,10 @@
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B32" s="58" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C32" s="59" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D32" s="68">
         <v>0</v>
@@ -7080,7 +7773,7 @@
     </row>
     <row r="34" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B34" s="46" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C34" s="45"/>
       <c r="D34" s="45"/>
@@ -7100,69 +7793,69 @@
     </row>
     <row r="35" spans="2:19" x14ac:dyDescent="0.25">
       <c r="J35" s="44" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="36" spans="2:19" x14ac:dyDescent="0.25">
       <c r="J36" s="40" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="K36" s="23"/>
       <c r="L36" s="23"/>
       <c r="M36" s="24" t="s">
+        <v>294</v>
+      </c>
+      <c r="N36" s="24" t="s">
         <v>295</v>
       </c>
-      <c r="N36" s="24" t="s">
+      <c r="O36" s="24" t="s">
         <v>296</v>
       </c>
-      <c r="O36" s="24" t="s">
+      <c r="P36" s="43" t="s">
         <v>297</v>
       </c>
-      <c r="P36" s="43" t="s">
-        <v>298</v>
-      </c>
       <c r="Q36" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="37" spans="2:19" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="44" t="s">
+        <v>244</v>
+      </c>
+      <c r="J37" s="36" t="s">
         <v>245</v>
-      </c>
-      <c r="J37" s="36" t="s">
-        <v>246</v>
       </c>
       <c r="K37" s="11"/>
       <c r="L37" s="11"/>
       <c r="M37" s="51" t="s">
+        <v>290</v>
+      </c>
+      <c r="N37" s="51" t="s">
         <v>291</v>
       </c>
-      <c r="N37" s="51" t="s">
+      <c r="O37" s="51" t="s">
         <v>292</v>
       </c>
-      <c r="O37" s="51" t="s">
+      <c r="P37" s="52" t="s">
         <v>293</v>
       </c>
-      <c r="P37" s="52" t="s">
-        <v>294</v>
-      </c>
       <c r="Q37" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="38" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B38" s="40" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C38" s="24"/>
       <c r="D38" s="24" t="s">
+        <v>238</v>
+      </c>
+      <c r="E38" s="43" t="s">
         <v>239</v>
       </c>
-      <c r="E38" s="43" t="s">
-        <v>240</v>
-      </c>
       <c r="J38" s="26" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="M38">
         <v>90</v>
@@ -7177,14 +7870,14 @@
         <v>242</v>
       </c>
       <c r="Q38" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="R38" s="50"/>
       <c r="S38" s="50"/>
     </row>
     <row r="39" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="26" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D39">
         <v>50</v>
@@ -7193,7 +7886,7 @@
         <v>0.4</v>
       </c>
       <c r="J39" s="26" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="M39">
         <v>654</v>
@@ -7205,17 +7898,17 @@
         <v>9.6</v>
       </c>
       <c r="P39" s="27" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q39" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="R39" s="50"/>
       <c r="S39" s="50"/>
     </row>
     <row r="40" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B40" s="26" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D40">
         <v>36.5</v>
@@ -7224,7 +7917,7 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="J40" s="26" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="M40">
         <v>11</v>
@@ -7239,14 +7932,14 @@
         <v>43.2</v>
       </c>
       <c r="Q40" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="R40" s="50"/>
       <c r="S40" s="50"/>
     </row>
     <row r="41" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B41" s="26" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D41">
         <v>9.5</v>
@@ -7255,7 +7948,7 @@
         <v>0.06</v>
       </c>
       <c r="J41" s="26" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="M41">
         <v>244</v>
@@ -7270,14 +7963,14 @@
         <v>340</v>
       </c>
       <c r="Q41" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="R41" s="50"/>
       <c r="S41" s="50"/>
     </row>
     <row r="42" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B42" s="26" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D42">
         <v>3.5</v>
@@ -7286,7 +7979,7 @@
         <v>0.04</v>
       </c>
       <c r="J42" s="26" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="M42">
         <v>992</v>
@@ -7298,17 +7991,17 @@
         <v>4.2</v>
       </c>
       <c r="P42" s="27" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="Q42" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="R42" s="50"/>
       <c r="S42" s="50"/>
     </row>
     <row r="43" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B43" s="36" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C43" s="11"/>
       <c r="D43" s="11">
@@ -7340,39 +8033,39 @@
     </row>
     <row r="44" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C44" s="60" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D44" s="61">
         <f>D39*33+E39*26</f>
         <v>1660.4</v>
       </c>
       <c r="E44" s="62" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="J44" s="26" t="s">
+        <v>259</v>
+      </c>
+      <c r="M44" t="s">
         <v>260</v>
-      </c>
-      <c r="M44" t="s">
-        <v>261</v>
       </c>
       <c r="N44">
         <v>4</v>
       </c>
       <c r="O44" t="s">
+        <v>261</v>
+      </c>
+      <c r="P44" s="27" t="s">
         <v>262</v>
       </c>
-      <c r="P44" s="27" t="s">
-        <v>263</v>
-      </c>
       <c r="Q44" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="R44" s="50"/>
       <c r="S44" s="50"/>
     </row>
     <row r="45" spans="2:19" x14ac:dyDescent="0.25">
       <c r="J45" s="26" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="M45">
         <v>79</v>
@@ -7384,20 +8077,20 @@
         <v>0.7</v>
       </c>
       <c r="P45" s="27" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q45" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="R45" s="50"/>
       <c r="S45" s="50"/>
     </row>
     <row r="46" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B46" s="63" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J46" s="26" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="M46" t="s">
         <v>83</v>
@@ -7409,10 +8102,10 @@
         <v>83</v>
       </c>
       <c r="P46" s="27" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q46" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="R46" s="50"/>
       <c r="S46" s="50"/>
@@ -7421,16 +8114,16 @@
       <c r="B47" s="22"/>
       <c r="C47" s="23"/>
       <c r="D47" s="76" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E47" s="23" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F47" s="23"/>
       <c r="G47" s="23"/>
       <c r="H47" s="25"/>
       <c r="J47" s="26" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="M47">
         <v>38</v>
@@ -7439,13 +8132,13 @@
         <v>15</v>
       </c>
       <c r="O47" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P47" s="27" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q47" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="R47" s="50"/>
       <c r="S47" s="50"/>
@@ -7454,7 +8147,7 @@
       <c r="B48" s="36"/>
       <c r="C48" s="11"/>
       <c r="D48" s="77" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E48" s="11" t="s">
         <v>26</v>
@@ -7469,7 +8162,7 @@
         <v>140</v>
       </c>
       <c r="J48" s="26" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="M48">
         <v>164</v>
@@ -7481,20 +8174,20 @@
         <v>1</v>
       </c>
       <c r="P48" s="27" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q48" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="R48" s="50"/>
       <c r="S48" s="50"/>
     </row>
     <row r="49" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B49" s="75" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C49" s="23" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D49" s="78">
         <f>D42</f>
@@ -7513,7 +8206,7 @@
         <v>0</v>
       </c>
       <c r="J49" s="40" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="K49" s="24"/>
       <c r="L49" s="24"/>
@@ -7530,17 +8223,17 @@
         <v>1252</v>
       </c>
       <c r="Q49" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="R49" s="50"/>
       <c r="S49" s="50"/>
     </row>
     <row r="50" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B50" s="26" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C50" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D50" s="78">
         <f>D39*0.25</f>
@@ -7562,7 +8255,7 @@
         <v>20</v>
       </c>
       <c r="J50" s="26" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="M50">
         <v>1441</v>
@@ -7581,10 +8274,10 @@
     </row>
     <row r="51" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B51" s="26" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C51" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D51" s="79">
         <f>D39-D49-D50</f>
@@ -7603,7 +8296,7 @@
         <v>100</v>
       </c>
       <c r="J51" s="53" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="K51" s="55"/>
       <c r="L51" s="55"/>
@@ -7624,7 +8317,7 @@
         <v>34</v>
       </c>
       <c r="Q51" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="R51" s="50"/>
       <c r="S51" s="50"/>
@@ -7637,7 +8330,7 @@
       <c r="G52" s="64"/>
       <c r="H52" s="66"/>
       <c r="J52" s="47" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K52" s="48"/>
       <c r="L52" s="48"/>
@@ -7651,18 +8344,18 @@
         <v>83</v>
       </c>
       <c r="P52" s="49" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="Q52" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="53" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B53" s="56" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C53" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D53" s="78">
         <f>E42</f>
@@ -7681,30 +8374,30 @@
         <v>0</v>
       </c>
       <c r="J53" s="26" t="s">
+        <v>276</v>
+      </c>
+      <c r="M53" t="s">
         <v>277</v>
       </c>
-      <c r="M53" t="s">
-        <v>278</v>
-      </c>
       <c r="N53" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="O53" t="s">
         <v>83</v>
       </c>
       <c r="P53" s="27" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="Q53" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="54" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B54" s="26" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C54" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D54" s="80">
         <f>E39*0.25</f>
@@ -7726,30 +8419,30 @@
         <v>20.000000000000018</v>
       </c>
       <c r="J54" s="26" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="M54" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="N54" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O54" t="s">
         <v>83</v>
       </c>
       <c r="P54" s="27" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="Q54" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="55" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B55" s="36" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D55" s="81">
         <f>E39-D53-D54</f>
@@ -7768,24 +8461,24 @@
         <v>100</v>
       </c>
       <c r="J55" s="26" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="M55" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="O55" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="P55" s="27" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="Q55" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="56" spans="2:19" x14ac:dyDescent="0.25">
       <c r="J56" s="36" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="K56" s="11"/>
       <c r="L56" s="11"/>
@@ -7804,7 +8497,7 @@
     </row>
     <row r="58" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B58" s="46" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C58" s="45"/>
       <c r="D58" s="45"/>
@@ -7824,45 +8517,45 @@
     </row>
     <row r="59" spans="2:19" x14ac:dyDescent="0.25">
       <c r="J59" s="44" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="60" spans="2:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J60" s="22" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="K60" s="23"/>
       <c r="L60" s="23"/>
       <c r="M60" s="93" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="N60" s="93"/>
       <c r="O60" s="93" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="P60" s="94"/>
     </row>
     <row r="61" spans="2:19" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J61" s="90" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="K61" s="11"/>
       <c r="L61" s="11"/>
       <c r="M61" s="91" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="N61" s="91"/>
       <c r="O61" s="91" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="P61" s="92"/>
     </row>
     <row r="62" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B62" s="63" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="J62" s="22" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="K62" s="23"/>
       <c r="L62" s="23"/>
@@ -7870,29 +8563,29 @@
         <v>130</v>
       </c>
       <c r="N62" s="86" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="O62" s="23">
         <v>106</v>
       </c>
       <c r="P62" s="87" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="63" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B63" s="22"/>
       <c r="C63" s="23"/>
       <c r="D63" s="76" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E63" s="23" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F63" s="23"/>
       <c r="G63" s="23"/>
       <c r="H63" s="25"/>
       <c r="J63" s="26" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="M63">
         <v>1250</v>
@@ -7906,7 +8599,7 @@
       <c r="B64" s="36"/>
       <c r="C64" s="11"/>
       <c r="D64" s="77" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E64" s="11" t="s">
         <v>26</v>
@@ -7921,7 +8614,7 @@
         <v>140</v>
       </c>
       <c r="J64" s="26" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="M64">
         <v>11</v>
@@ -7933,7 +8626,7 @@
     </row>
     <row r="65" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B65" s="75" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C65" s="23"/>
       <c r="D65" s="80">
@@ -7953,7 +8646,7 @@
         <v>90</v>
       </c>
       <c r="J65" s="26" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="M65">
         <v>1454</v>
@@ -7965,7 +8658,7 @@
     </row>
     <row r="66" spans="2:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B66" s="26" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D66" s="78">
         <v>0</v>
@@ -7975,22 +8668,22 @@
       <c r="G66" s="67"/>
       <c r="H66" s="70"/>
       <c r="J66" s="84" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="K66" s="85"/>
       <c r="L66" s="85"/>
       <c r="M66" s="85" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="N66" s="85"/>
       <c r="O66" s="85" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="P66" s="38"/>
     </row>
     <row r="67" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B67" s="36" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C67" s="11"/>
       <c r="D67" s="81">
@@ -8010,7 +8703,7 @@
         <v>100</v>
       </c>
       <c r="J67" s="26" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="M67">
         <v>29</v>
@@ -8022,7 +8715,7 @@
     </row>
     <row r="68" spans="2:16" x14ac:dyDescent="0.25">
       <c r="J68" s="26" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="M68">
         <v>16</v>
@@ -8034,10 +8727,10 @@
     </row>
     <row r="69" spans="2:16" x14ac:dyDescent="0.25">
       <c r="J69" s="26" t="s">
+        <v>366</v>
+      </c>
+      <c r="M69" t="s">
         <v>367</v>
-      </c>
-      <c r="M69" t="s">
-        <v>368</v>
       </c>
       <c r="O69">
         <v>150</v>
@@ -8046,10 +8739,10 @@
     </row>
     <row r="70" spans="2:16" x14ac:dyDescent="0.25">
       <c r="J70" s="26" t="s">
+        <v>368</v>
+      </c>
+      <c r="M70" t="s">
         <v>369</v>
-      </c>
-      <c r="M70" t="s">
-        <v>370</v>
       </c>
       <c r="O70">
         <v>18</v>
@@ -8058,7 +8751,7 @@
     </row>
     <row r="71" spans="2:16" x14ac:dyDescent="0.25">
       <c r="J71" s="26" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="M71">
         <v>228</v>
@@ -8070,7 +8763,7 @@
     </row>
     <row r="72" spans="2:16" x14ac:dyDescent="0.25">
       <c r="J72" s="88" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="K72" s="83"/>
       <c r="L72" s="83"/>
@@ -8085,25 +8778,25 @@
     </row>
     <row r="73" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J73" s="47" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="K73" s="48"/>
       <c r="L73" s="48"/>
       <c r="M73" s="48" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N73" s="48"/>
       <c r="O73" s="48" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="P73" s="49"/>
     </row>
     <row r="74" spans="2:16" x14ac:dyDescent="0.25">
       <c r="J74" s="26" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="M74" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="O74">
         <v>10</v>
@@ -8112,7 +8805,7 @@
     </row>
     <row r="75" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J75" s="47" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="K75" s="48"/>
       <c r="L75" s="48"/>
@@ -8148,7 +8841,7 @@
   <sheetData>
     <row r="3" spans="5:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F3">
         <v>90</v>
@@ -8165,7 +8858,7 @@
     </row>
     <row r="4" spans="5:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F4">
         <v>654</v>
@@ -8174,15 +8867,15 @@
         <v>80</v>
       </c>
       <c r="H4" t="s">
+        <v>251</v>
+      </c>
+      <c r="I4" t="s">
         <v>252</v>
-      </c>
-      <c r="I4" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="5" spans="5:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E5" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F5">
         <v>11</v>
@@ -8191,66 +8884,66 @@
         <v>12</v>
       </c>
       <c r="H5" t="s">
+        <v>254</v>
+      </c>
+      <c r="I5" t="s">
         <v>255</v>
-      </c>
-      <c r="I5" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="6" spans="5:20" x14ac:dyDescent="0.25">
       <c r="E6" t="s">
+        <v>283</v>
+      </c>
+      <c r="F6" t="s">
         <v>284</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>285</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>286</v>
       </c>
-      <c r="H6" t="s">
+      <c r="I6" t="s">
         <v>287</v>
-      </c>
-      <c r="I6" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="7" spans="5:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E7" t="s">
+        <v>246</v>
+      </c>
+      <c r="G7" t="s">
+        <v>256</v>
+      </c>
+      <c r="I7" t="s">
+        <v>257</v>
+      </c>
+      <c r="O7" t="s">
+        <v>258</v>
+      </c>
+      <c r="S7" t="s">
         <v>247</v>
-      </c>
-      <c r="G7" t="s">
-        <v>257</v>
-      </c>
-      <c r="I7" t="s">
-        <v>258</v>
-      </c>
-      <c r="O7" t="s">
-        <v>259</v>
-      </c>
-      <c r="S7" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="8" spans="5:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E8" t="s">
+        <v>259</v>
+      </c>
+      <c r="H8" t="s">
         <v>260</v>
-      </c>
-      <c r="H8" t="s">
-        <v>261</v>
       </c>
       <c r="K8">
         <v>4</v>
       </c>
       <c r="P8" t="s">
+        <v>261</v>
+      </c>
+      <c r="T8" t="s">
         <v>262</v>
-      </c>
-      <c r="T8" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="9" spans="5:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H9">
         <v>79</v>
@@ -8259,15 +8952,15 @@
         <v>7</v>
       </c>
       <c r="P9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="T9" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="10" spans="5:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E10" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H10" t="s">
         <v>83</v>
@@ -8279,12 +8972,12 @@
         <v>83</v>
       </c>
       <c r="T10" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11" spans="5:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E11" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H11">
         <v>38</v>
@@ -8293,15 +8986,15 @@
         <v>15</v>
       </c>
       <c r="P11" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="T11" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="12" spans="5:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H12">
         <v>164</v>
@@ -8310,15 +9003,15 @@
         <v>66</v>
       </c>
       <c r="P12" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="T12" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="13" spans="5:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E13" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H13">
         <v>2433</v>
@@ -8327,7 +9020,7 @@
         <v>689</v>
       </c>
       <c r="P13" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="T13">
         <v>1252</v>
@@ -8335,7 +9028,7 @@
     </row>
     <row r="14" spans="5:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E14" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H14">
         <v>1441</v>
@@ -8344,7 +9037,7 @@
         <v>689</v>
       </c>
       <c r="P14" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="T14">
         <v>1218</v>
@@ -8352,47 +9045,47 @@
     </row>
     <row r="15" spans="5:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E15" t="s">
+        <v>273</v>
+      </c>
+      <c r="L15" t="s">
         <v>274</v>
       </c>
-      <c r="L15" t="s">
+      <c r="Q15" t="s">
         <v>275</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="16" spans="5:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E16" t="s">
+        <v>276</v>
+      </c>
+      <c r="H16" t="s">
         <v>277</v>
       </c>
-      <c r="H16" t="s">
-        <v>278</v>
-      </c>
       <c r="K16" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="P16" t="s">
         <v>83</v>
       </c>
       <c r="T16" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="17" spans="5:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E17" t="s">
+        <v>278</v>
+      </c>
+      <c r="H17" t="s">
         <v>279</v>
       </c>
-      <c r="H17" t="s">
+      <c r="K17" t="s">
         <v>280</v>
       </c>
-      <c r="K17" t="s">
+      <c r="P17" t="s">
         <v>281</v>
       </c>
-      <c r="P17" t="s">
+      <c r="T17" t="s">
         <v>282</v>
-      </c>
-      <c r="T17" t="s">
-        <v>283</v>
       </c>
     </row>
   </sheetData>
@@ -8411,47 +9104,47 @@
   <sheetData>
     <row r="3" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F3" s="31" t="s">
+        <v>294</v>
+      </c>
+      <c r="G3" s="31" t="s">
         <v>295</v>
       </c>
-      <c r="G3" s="31" t="s">
+      <c r="H3" s="31" t="s">
         <v>296</v>
       </c>
-      <c r="H3" s="31" t="s">
+      <c r="I3" s="31" t="s">
         <v>297</v>
       </c>
-      <c r="I3" s="31" t="s">
-        <v>298</v>
-      </c>
       <c r="J3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="4" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F4" t="s">
+        <v>290</v>
+      </c>
+      <c r="G4" t="s">
         <v>291</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>292</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>293</v>
       </c>
-      <c r="I4" t="s">
-        <v>294</v>
-      </c>
       <c r="J4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="5" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F5">
         <v>90</v>
@@ -8466,12 +9159,12 @@
         <v>242</v>
       </c>
       <c r="J5" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="6" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F6">
         <v>654</v>
@@ -8483,15 +9176,15 @@
         <v>9.6</v>
       </c>
       <c r="I6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="J6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="7" spans="3:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F7">
         <v>11</v>
@@ -8506,12 +9199,12 @@
         <v>43.2</v>
       </c>
       <c r="J7" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="8" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F8">
         <v>244</v>
@@ -8526,12 +9219,12 @@
         <v>340</v>
       </c>
       <c r="J8" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="9" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F9">
         <v>992</v>
@@ -8543,35 +9236,35 @@
         <v>4.2</v>
       </c>
       <c r="I9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="J9" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="10" spans="3:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
+        <v>259</v>
+      </c>
+      <c r="F10" t="s">
         <v>260</v>
-      </c>
-      <c r="F10" t="s">
-        <v>261</v>
       </c>
       <c r="G10">
         <v>4</v>
       </c>
       <c r="H10" t="s">
+        <v>261</v>
+      </c>
+      <c r="I10" t="s">
         <v>262</v>
       </c>
-      <c r="I10" t="s">
-        <v>263</v>
-      </c>
       <c r="J10" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="11" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F11">
         <v>79</v>
@@ -8583,15 +9276,15 @@
         <v>0.7</v>
       </c>
       <c r="I11" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="J11" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="12" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F12" t="s">
         <v>83</v>
@@ -8603,15 +9296,15 @@
         <v>83</v>
       </c>
       <c r="I12" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="J12" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="13" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F13">
         <v>38</v>
@@ -8620,18 +9313,18 @@
         <v>15</v>
       </c>
       <c r="H13" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="I13" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="J13" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="14" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F14">
         <v>164</v>
@@ -8643,15 +9336,15 @@
         <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="J14" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="15" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F15">
         <v>2433</v>
@@ -8666,12 +9359,12 @@
         <v>1252</v>
       </c>
       <c r="J15" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="16" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C16" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F16">
         <v>1441</v>
@@ -8686,12 +9379,12 @@
         <v>1218</v>
       </c>
       <c r="J16" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="17" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C17" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F17">
         <v>23</v>
@@ -8703,72 +9396,72 @@
         <v>83</v>
       </c>
       <c r="I17" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J17" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="18" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C18" t="s">
+        <v>276</v>
+      </c>
+      <c r="F18" t="s">
         <v>277</v>
       </c>
-      <c r="F18" t="s">
-        <v>278</v>
-      </c>
       <c r="G18" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H18" t="s">
         <v>83</v>
       </c>
       <c r="I18" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J18" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="19" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C19" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F19" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G19" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H19" t="s">
         <v>83</v>
       </c>
       <c r="I19" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J19" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="20" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C20" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F20" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H20" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="I20" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J20" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="21" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C21" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F21">
         <v>1998</v>
@@ -8783,7 +9476,7 @@
         <v>2008</v>
       </c>
       <c r="J21" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
   </sheetData>
@@ -8799,7 +9492,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -8849,22 +9542,22 @@
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="42" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="42" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="42" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
   </sheetData>
